--- a/docs/datos/datos_bolivia.xlsx
+++ b/docs/datos/datos_bolivia.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R39"/>
+  <dimension ref="A1:R42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,20 +514,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>noticia:1sg8pi0</t>
+          <t>noticia:1at00ey</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-25 09:59</t>
+          <t>2026-10-25 11:19</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1792936752000</v>
+        <v>1792941547000</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Bus de agrupación musical sufre accidente rumbo al trópico de Cochabamba | VIDEO - Red Uno</t>
+          <t>Dos cisternas chocan y provocan voraz incendio en la ruta a Camiri - Red Uno</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -563,54 +563,54 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>-17.39</v>
+        <v>-20.05</v>
       </c>
       <c r="N2" t="n">
-        <v>-66.16</v>
+        <v>-63.486</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Cochabamba, Cochabamba</t>
+          <t>Camiri, Santa Cruz</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Camiri</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOVDVzVTJNM2JuQ25sMThEaVZNOUNRd3FGT3RhVnFrZXZ2NDQ1YlluTVdhbVNUQnA1MGNESHRSWVUzbC1kRVh3OTR0emtlTG91cmRWeFJ5dk5zb3p2WFRyMEJUV3FNRnY1WHhRUU9WLTlJcmNyNXJZZFdoM0JoZjNpa3hjUXhMM0xrUDJab2VadkM5RWZYQ3lWZTVDdzg1akxJT2lxcDVNNzI0NG1hejdfdkUyTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPTTF0OUdVS1c1a0lZWmk3bGxHdDJIalpWZTRyQTY3eWE2a2dWOHlsaldKZXpSLWN5c3BkUWdBRkJuSzhHdWl2ZjgwTFFFYnd0aTAxZ3dJU0hCekNZNm9aTTJSZUNfQjVIM3FrUUJ4NXAwa3paZ3BEek9xTVZNQWdnN01xRHloV1ZXZHV6N0JpUWo3RE9DMlFGdkNnWkloTjVVY3RBR1RSRUJJWFVtby1fMWFMNTdLZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>noticia:167wlhz</t>
+          <t>noticia:1uf38hl</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-25 07:53</t>
+          <t>2026-10-25 10:59</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1792929231000</v>
+        <v>1792940350000</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>¡A sacar el paraguas! Santa cruz amanece con lluvia, frío y complicaciones en el tránsito vehicular - Red Uno</t>
+          <t>¡Cisterna con combustible en llamas! Reportan impresionante incendio en la carretera a Camiri - Red Uno</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -641,14 +641,14 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>-17.781</v>
+        <v>-20.05</v>
       </c>
       <c r="N3" t="n">
-        <v>-63.139</v>
+        <v>-63.486</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Santa Cruz, Santa Cruz</t>
+          <t>Camiri, Santa Cruz</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -658,45 +658,45 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Camiri</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOY1ZpYktLR3pUQXotUndVR3puUzVHbW1YTzNyUmJvUHB4Q2JmelRvOEdaRldOUm1xLVJnbGR5VWcxTjNEM3ZUYktCUWtVM0hKSjFuRGdpX0JxN0M5MVZBSG1aVURyVWktdmxwbUtRT19ydU5LdzNTZ2Zpb2ozdHlMUUdTVlAyVk4xODBnV0hyTXdVVndyNzV3VC1KMzFnV3lpcFFXSk9MdDZOTWlWakNwT1FnNDh6QVdjazVYZDVVMkdaLU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxORUhqeWpKY1FHRWoxaHN0UXFzS3dpeHh6N0NwLUJOZTlZcDVoNHN0VnI0by1qMWtZZEkxVmtUNjdNTFhjaEFQU2IyMlNwZW95WFBzbFJPVVB6TjJtdjNENk1LWVlsMUxUUzBNVzkxRk1HZ3lQU0s2M1lRVlRuaXlkMmJrd3AyTGpIdXItNkhlU3dhTzBRME56Rm1DSlZCYjNxSnNTbTFqNWRoUkdraHhlREhuYldqeFk2N3poWEx2M08?oc=5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>noticia:bzr7eh</t>
+          <t>noticia:1sg8pi0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25 07:09</t>
+          <t>2026-10-25 09:59</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1792926572000</v>
+        <v>1792936752000</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Alerta naranja por riesgo de desbordes de ríos - El Diario - Bolivia</t>
+          <t>Bus de agrupación musical sufre accidente rumbo al trópico de Cochabamba | VIDEO - Red Uno</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>hidrológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -711,77 +711,77 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia; El Mundo Bolivia; FmBolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>-16.169</v>
+        <v>-17.39</v>
       </c>
       <c r="N4" t="n">
-        <v>-68.09</v>
+        <v>-66.16</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>La Paz, La Paz</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Nuestra Señora de La Paz</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNNGZKSDVaZkowWUFGSEUyTWR3d3dsc04waFBLLWUtcVpiTDYzbmNtYTN1RkFLbjAwN3dxT0xZc3pqc3REUXduZVltQ2Fud1BZLTh1bTNiTEJueVUwV0dERS1iUXZqMHd0UnFrQ3E2SFAzbm5lQ1I4U29MaHJFbWFvdVRTeFY4Wl9rSmc3RkpaQ2xwX0oz?oc=5 | https://news.google.com/rss/articles/CBMipwFBVV95cUxPZW00RkxJSklTelNrS2hqczJDWHlwcENFX2lnSEUyTEFPaDFRQ2JvMUcyd3NfYjg0UE9ORGxHRzB4ZDh3U0hQQ1JSQlhsaUY4N3ByMUUxei1SaUZnNlp6T3hsLVdiMGhKaXhsV1FNSUNQMHlvQ19qdk56SEF0d2RXVFctS0VPT25kNGZCRDdvZ2dxU0VoUUJKU0ZBd0ZycFNEZFh0T3ZjOA?oc=5 | https://news.google.com/rss/articles/CBMiwAFBVV95cUxPZm85aHphekQ4U3BZZkp1ZkF6ZVdSUHgtZmltS1FxUUgza1AwcndWWDJZOWctT0RiVmVabmg5SG42NnJWMlJMMnBlYTlYaVdSb09sR0dnVDdpT29faTdiaDUtZElJdlQ3eTdjR2VsWjlta1FOS1U2Vm1vV3JwWkpvbEw1ZUR3akgwQTZnQnVENjJtVkQtVUpKVEJTeWNJSE1CaEFKa2VqMmZXbWk3ekR4ZWpmZ1Z3elFQaWNaNFJuMXA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOVDVzVTJNM2JuQ25sMThEaVZNOUNRd3FGT3RhVnFrZXZ2NDQ1YlluTVdhbVNUQnA1MGNESHRSWVUzbC1kRVh3OTR0emtlTG91cmRWeFJ5dk5zb3p2WFRyMEJUV3FNRnY1WHhRUU9WLTlJcmNyNXJZZFdoM0JoZjNpa3hjUXhMM0xrUDJab2VadkM5RWZYQ3lWZTVDdzg1akxJT2lxcDVNNzI0NG1hejdfdkUyTQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>noticia:r1uot6</t>
+          <t>noticia:167wlhz</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-24 20:00</t>
+          <t>2026-10-25 07:53</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1792886439000</v>
+        <v>1792929231000</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>vuelco deja heridos en ruta Oruro – Huanuni - La Patria Bolivia</t>
+          <t>¡A sacar el paraguas! Santa cruz amanece con lluvia, frío y complicaciones en el tránsito vehicular - Red Uno</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -793,70 +793,70 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>-17.97</v>
+        <v>-17.781</v>
       </c>
       <c r="N5" t="n">
-        <v>-67.11</v>
+        <v>-63.139</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>Santa Cruz, Santa Cruz</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNNDQtMG1KT1lLWW5nem9Jbm5JWDZKNlRWZmFmRlBxWDlDeXlSWnJ5d2NsTlpxa0JIS25oVWVZOC1majZVbWhOVDIxR0dLOFlzY2VpVzVoVk1mQnF3dXVwLUFZVHc1UjlXZzF5T05CY3U0ZldLVkw1VzBTek5zanpjQW1xalltWHNiaXI3dTNR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOY1ZpYktLR3pUQXotUndVR3puUzVHbW1YTzNyUmJvUHB4Q2JmelRvOEdaRldOUm1xLVJnbGR5VWcxTjNEM3ZUYktCUWtVM0hKSjFuRGdpX0JxN0M5MVZBSG1aVURyVWktdmxwbUtRT19ydU5LdzNTZ2Zpb2ozdHlMUUdTVlAyVk4xODBnV0hyTXdVVndyNzV3VC1KMzFnV3lpcFFXSk9MdDZOTWlWakNwT1FnNDh6QVdjazVYZDVVMkdaLU0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>noticia:1ytw450</t>
+          <t>noticia:bzr7eh</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-24 18:58</t>
+          <t>2026-10-25 07:09</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1792882686000</v>
+        <v>1792926572000</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
+          <t>Alerta naranja por riesgo de desbordes de ríos - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>hidrológica</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>roja</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -867,41 +867,57 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>diarioelpueblo.com.pe</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
+          <t>El Diario - Bolivia; El Mundo Bolivia; FmBolivia</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>-16.169</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-68.09</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>La Paz, La Paz</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>La Paz</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Nuestra Señora de La Paz</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNZ1U3bEVuaVdjVE1zSU9lOHJZTVRZLVZaemhldGNnT1JBWDJvbzdvM3paVVNhLUlyWHF2akNuSXJOLXdyTGRuejRlV1FuMjVkTjA3NmdRdmgtRWlUeTFBV1dEMzBvejBxaXZJdUZZWkRVTF9VLU5BcjFGZGFEQ09WWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNNGZKSDVaZkowWUFGSEUyTWR3d3dsc04waFBLLWUtcVpiTDYzbmNtYTN1RkFLbjAwN3dxT0xZc3pqc3REUXduZVltQ2Fud1BZLTh1bTNiTEJueVUwV0dERS1iUXZqMHd0UnFrQ3E2SFAzbm5lQ1I4U29MaHJFbWFvdVRTeFY4Wl9rSmc3RkpaQ2xwX0oz?oc=5 | https://news.google.com/rss/articles/CBMipwFBVV95cUxPZW00RkxJSklTelNrS2hqczJDWHlwcENFX2lnSEUyTEFPaDFRQ2JvMUcyd3NfYjg0UE9ORGxHRzB4ZDh3U0hQQ1JSQlhsaUY4N3ByMUUxei1SaUZnNlp6T3hsLVdiMGhKaXhsV1FNSUNQMHlvQ19qdk56SEF0d2RXVFctS0VPT25kNGZCRDdvZ2dxU0VoUUJKU0ZBd0ZycFNEZFh0T3ZjOA?oc=5 | https://news.google.com/rss/articles/CBMiwAFBVV95cUxPZm85aHphekQ4U3BZZkp1ZkF6ZVdSUHgtZmltS1FxUUgza1AwcndWWDJZOWctT0RiVmVabmg5SG42NnJWMlJMMnBlYTlYaVdSb09sR0dnVDdpT29faTdiaDUtZElJdlQ3eTdjR2VsWjlta1FOS1U2Vm1vV3JwWkpvbEw1ZUR3akgwQTZnQnVENjJtVkQtVUpKVEJTeWNJSE1CaEFKa2VqMmZXbWk3ekR4ZWpmZ1Z3elFQaWNaNFJuMXA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>noticia:1g006zh</t>
+          <t>noticia:1fo4ig4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-24 17:02</t>
+          <t>2026-10-25 01:08</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1792875752000</v>
+        <v>1792904880000</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a Mayaya deja siete heridos del grupo Los Chicos Fieles - El Potosí</t>
+          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -910,18 +926,18 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>roja</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -929,57 +945,41 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>EL DÍA - Noticias de Bolivia para el mundo; El Potosí; La Razón Digital Bolivia; Opinión Bolivia</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>-19.58</v>
-      </c>
-      <c r="N7" t="n">
-        <v>-65.75</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Potosí, Potosí</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
+          <t>diarioelpueblo.com.pe</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPTGQwaVBfdG1JdVRMUTN4LVVvN0ppc3dreDJVVllDR3RmX0xpMzB4b0pvVTNSV1B6T0ZEWTdEZkNsRUdSNzhLaC1CWHN5WktNWk1nRWpTdVZiYjI3TlJlX2xlVTI5MjlRU2hiY1gteml4YWVFbDNPSVRBZmtITlQzbmhaUXVmcThRa2xsQTJIOXZuNzlSdm12MEdyOEZHdw?oc=5 | https://news.google.com/rss/articles/CBMizwFBVV95cUxPeGd3VWpCWXJ0YTJIeDJLcktzWG1jdUh0TjFXb01wSTkxbHNXZU94VWNDMkxnTjlJZVdpbkprMEY2NE80RXYyUWxUQXVnbl9lUXR2b28zTEh6cTJLVEQ4TUNja2kzRlhadVBFZFVwV1U2TlhseXZMZ20zZTZiUFpWRjdCOWNBMHU5XzdMV3JqQjV4TEE3bHRMOXR6Nm55eHZUNnFHSDdVRk8zVkY4RkVsUUtUN0JYdkREWGZncmJ3ZWc2T1BuUm1ZLTlfcHVabFE?oc=5 | https://news.google.com/rss/articles/CBMizAFBVV95cUxNYjNxaHg3YllRRTJYdFd1clAtUlROSGlFNVg5eUVZUGJoOEZ4MWM5QU5WQm1YTDc4NXc3SjhWMUw0TkZfSHlMLUQ1bmpTME1Kb1JaM0ExamFHYTd3VlU4MXRWdTZ1bzh1SGYtbGE1a3dBaG93bjg1OGc0S0JfRE43c3dVMVltN0dQQzNhQUNhM0FjVUNRUDRSamlJYlk2dEJpUTBuY2hBcTFucTVRN0ZtYnc5bzdmTV9LQm1uVUxaZS1tUE9IejhBVDRCdU_SAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQcmFrT3dwcEs0X3U2NWxnOGJwNnI2WHdWTGZYbzEyNnJzUWhkbU9TRWhfSlB5UkMwX2gyMmxYUmVNWmxNOVR6V0twRHpFMTVIYjBKbHQ2TXN2d2w5dkFpcWJCcUJMZldaX01sNWtQV2ZJOGpRVzR3NDVIU0pJc1BNVg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>noticia:1ukcn97</t>
+          <t>noticia:r1uot6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-24 13:26</t>
+          <t>2026-10-24 20:00</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1792862794000</v>
+        <v>1792886439000</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Esta es la lista preliminar de los heridos en el accidente del grupo 'Los chicos fieles', el conductor está grave - El Deber</t>
+          <t>vuelco deja heridos en ruta Oruro – Huanuni - La Patria Bolivia</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1007,58 +1007,74 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>El Deber; Red Uno</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
+          <t>La Patria Bolivia</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>-17.97</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-67.11</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Oruro, Oruro</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOczZKbFd1QzRpak92LXpPWXZXQXJObnBQTG9qRFBlUUV5dThMWXhzckFFUHAyb2thU1JwRmJDSEZfaEdTUXh1bjZvQWpYMGhfUno3cWZ4MGpldEpoQXhzSlVzTm5LLW9OcjB2MWRsdHQ2UlI2SjEtZ085ZTR5Z3pEVmtBTF9lc29Kd0RhaTRUWkM4eGZJNWhBSXZqWmxuNW10dlQwYW9mdzItcWZWTkU0?oc=5 | https://news.google.com/rss/articles/CBMivAFBVV95cUxPczBQcnE2SzFGMXc3b1lsTkNxVWRmS3Vnb01xOTV2WmVva3J2RVlteWpHZ3VJS2dNWGV5NW5FX3ZncnVKTEVDTGpBRndTU1FxeWxtaS1fb1FscGxXMWNXUE9zbHdob1AxVFl1eHB5OU1yUnNoOXJ6U21oVG9PVDA1ak1xQl9hUlB4V0RaQXJqZENGUm8zMUJEY3J0WW5ENE5ObWJLNmpWN0RkSmFJbnZUZGR5UFRPd3QyUFY4WQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNNDQtMG1KT1lLWW5nem9Jbm5JWDZKNlRWZmFmRlBxWDlDeXlSWnJ5d2NsTlpxa0JIS25oVWVZOC1majZVbWhOVDIxR0dLOFlzY2VpVzVoVk1mQnF3dXVwLUFZVHc1UjlXZzF5T05CY3U0ZldLVkw1VzBTek5zanpjQW1xalltWHNiaXI3dTNR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>noticia:2avehj</t>
+          <t>noticia:1ytw450</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-24 12:53</t>
+          <t>2026-10-24 18:58</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1792860813000</v>
+        <v>1792882686000</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sequía en Cochabamba: más de un centenar de cabezas de ganado murieron en el cono sur - Red Uno</t>
+          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>climatológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>roja</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1073,53 +1089,37 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Red Uno</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>-17.39</v>
-      </c>
-      <c r="N9" t="n">
-        <v>-66.16</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Cochabamba, Cochabamba</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
+          <t>diarioelpueblo.com.pe</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOOFQxc2Vzc0QwS19ydC13RkRPZnZQU3JkSTl5U3kzdUdMSldTcm5HVEhWRzZyN19CLUlwcUs4MW03Ui1obVBtdzQ3QWFQc1RKdzh3MXJ5QkpRS2pRNm50V1lVb09ScGJnaVVlemVfZlRsWjdObnRmR1FGMnlMMHAyc2pMandndy10T2twcWx6OFh4UHdvbVlFbllwME9WQ2pQVjNTQzBxeTg5YnF3bDREeHVDYXpObFFIaTZZQWtYUE12cGQ1ZGRhT0syNjVhZWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNZ1U3bEVuaVdjVE1zSU9lOHJZTVRZLVZaemhldGNnT1JBWDJvbzdvM3paVVNhLUlyWHF2akNuSXJOLXdyTGRuejRlV1FuMjVkTjA3NmdRdmgtRWlUeTFBV1dEMzBvejBxaXZJdUZZWkRVTF9VLU5BcjFGZGFEQ09WWQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>noticia:3dv7b0</t>
+          <t>noticia:1g006zh</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-24 11:43</t>
+          <t>2026-10-24 17:02</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1792856591000</v>
+        <v>1792875752000</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Accidente en Caranavi: vehículo de Los Chicos Fieles cae a un barranco y deja varios heridos - FmBolivia</t>
+          <t>Accidente en la carretera a Mayaya deja siete heridos del grupo Los Chicos Fieles - El Potosí</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1139,7 +1139,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1147,62 +1147,62 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>FmBolivia; La Patria Bolivia; Red Uno</t>
+          <t>EL DÍA - Noticias de Bolivia para el mundo; El Potosí; La Razón Digital Bolivia; Opinión Bolivia</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>-15.813</v>
+        <v>-19.58</v>
       </c>
       <c r="N10" t="n">
-        <v>-67.46299999999999</v>
+        <v>-65.75</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Caranavi, La Paz</t>
+          <t>Potosí, Potosí</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Caranavi</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNeEFrOEtOMHZxMW42REFPU0x1MG5oQjlBMkJucWRLZ292alBXekJKeURBN3NLTVVadWI0OWF4UGtSVXBzTE01eWFSU1kyMUhNZ04zMWNMaUxnMDBBZ0EwTktXbjlaVTBUUmNqa3AwY19KNTU2LWh5LW9IVElVdTdnaHFPanJPd2FqMUxzaUhXZmVpYU1saGc?oc=5 | https://news.google.com/rss/articles/CBMi2wFBVV95cUxOdTVUZUQxVTdvYTdONDQxVlhUTzBOS2hKLW1rS1NUcmRYRnlCVlhIcHZlSjdsaktkQm5CWkFYa3lDQkxnMlh0b3prX0lha1BtbW1qS1VuYnNiX3FiZkYyNDJDR0tqZ0pKMU5TeC04SXV4UUJOTUlPUTB6ek01bzUxTUsydjZqZzI3S3ZLUnRWSUFUVk44WEpKUl9rbzRLb2IwYl9sLVlrYmt5d2ZHNUtGd3lRNnYzMlhuMkJOZW1XSUl2N1BxZWpHbm5XTDJhRUtnR190QWQ1TDlTUVk?oc=5 | https://news.google.com/rss/articles/CBMizAFBVV95cUxNcE1KaHZyUTJCSElxRU9nVzdhTnczWjJGTEhFMEs0bHp2cUdFeHd3VTB0NmVFcjdEN1dsZDZLY2k1ZFFUWkhKV19PU3V2czNyamh1ZE9YajVSVF8xczF6OFhZcWFvYV9EcWg4ZDNCb2p3enhXbFpRYnJMdGdaTXNrWUZSYVhKNTVicWlCLTJ5OE05Z1BvNEx1eEloUk5qTGN3ZHNzbzZWSVljbnRmSERJUWdxRDc0MjJxMGtycWJaaVhXQUUxVUlaWVZLOWE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPTGQwaVBfdG1JdVRMUTN4LVVvN0ppc3dreDJVVllDR3RmX0xpMzB4b0pvVTNSV1B6T0ZEWTdEZkNsRUdSNzhLaC1CWHN5WktNWk1nRWpTdVZiYjI3TlJlX2xlVTI5MjlRU2hiY1gteml4YWVFbDNPSVRBZmtITlQzbmhaUXVmcThRa2xsQTJIOXZuNzlSdm12MEdyOEZHdw?oc=5 | https://news.google.com/rss/articles/CBMizwFBVV95cUxPeGd3VWpCWXJ0YTJIeDJLcktzWG1jdUh0TjFXb01wSTkxbHNXZU94VWNDMkxnTjlJZVdpbkprMEY2NE80RXYyUWxUQXVnbl9lUXR2b28zTEh6cTJLVEQ4TUNja2kzRlhadVBFZFVwV1U2TlhseXZMZ20zZTZiUFpWRjdCOWNBMHU5XzdMV3JqQjV4TEE3bHRMOXR6Nm55eHZUNnFHSDdVRk8zVkY4RkVsUUtUN0JYdkREWGZncmJ3ZWc2T1BuUm1ZLTlfcHVabFE?oc=5 | https://news.google.com/rss/articles/CBMizAFBVV95cUxNYjNxaHg3YllRRTJYdFd1clAtUlROSGlFNVg5eUVZUGJoOEZ4MWM5QU5WQm1YTDc4NXc3SjhWMUw0TkZfSHlMLUQ1bmpTME1Kb1JaM0ExamFHYTd3VlU4MXRWdTZ1bzh1SGYtbGE1a3dBaG93bjg1OGc0S0JfRE43c3dVMVltN0dQQzNhQUNhM0FjVUNRUDRSamlJYlk2dEJpUTBuY2hBcTFucTVRN0ZtYnc5bzdmTV9LQm1uVUxaZS1tUE9IejhBVDRCdU_SAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>clima:Potosí:2026-10-24:viento:1</t>
+          <t>noticia:1ukcn97</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-24 10:55</t>
+          <t>2026-10-24 13:26</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1792853727284</v>
+        <v>1792862794000</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Potosí 2026-10-24: 60.5 km/h de ráfagas pronosticadas</t>
+          <t>Esta es la lista preliminar de los heridos en el accidente del grupo 'Los chicos fieles', el conductor está grave - El Deber</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -1217,7 +1217,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1225,74 +1225,58 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
-        </is>
-      </c>
-      <c r="M11" t="n">
-        <v>-19.58</v>
-      </c>
-      <c r="N11" t="n">
-        <v>-65.75</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
+          <t>El Deber; Red Uno</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOczZKbFd1QzRpak92LXpPWXZXQXJObnBQTG9qRFBlUUV5dThMWXhzckFFUHAyb2thU1JwRmJDSEZfaEdTUXh1bjZvQWpYMGhfUno3cWZ4MGpldEpoQXhzSlVzTm5LLW9OcjB2MWRsdHQ2UlI2SjEtZ085ZTR5Z3pEVmtBTF9lc29Kd0RhaTRUWkM4eGZJNWhBSXZqWmxuNW10dlQwYW9mdzItcWZWTkU0?oc=5 | https://news.google.com/rss/articles/CBMivAFBVV95cUxPczBQcnE2SzFGMXc3b1lsTkNxVWRmS3Vnb01xOTV2WmVva3J2RVlteWpHZ3VJS2dNWGV5NW5FX3ZncnVKTEVDTGpBRndTU1FxeWxtaS1fb1FscGxXMWNXUE9zbHdob1AxVFl1eHB5OU1yUnNoOXJ6U21oVG9PVDA1ak1xQl9hUlB4V0RaQXJqZENGUm8zMUJEY3J0WW5ENE5ObWJLNmpWN0RkSmFJbnZUZGR5UFRPd3QyUFY4WQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>noticia:1ax0bpy</t>
+          <t>noticia:2avehj</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-24 10:32</t>
+          <t>2026-10-24 12:53</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1792852364000</v>
+        <v>1792860813000</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Creció el Bermejo tras la tormenta: así está el puerto de chalanas en este momento - Que Pasa Salta</t>
+          <t>Sequía en Cochabamba: más de un centenar de cabezas de ganado murieron en el cono sur - Red Uno</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>climatológica</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1307,53 +1291,53 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Que Pasa Salta</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>-22.721</v>
+        <v>-17.39</v>
       </c>
       <c r="N12" t="n">
-        <v>-64.32599999999999</v>
+        <v>-66.16</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Bermejo, Tarija</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tarija</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Bermejo</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVld9IBfkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVldw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOOFQxc2Vzc0QwS19ydC13RkRPZnZQU3JkSTl5U3kzdUdMSldTcm5HVEhWRzZyN19CLUlwcUs4MW03Ui1obVBtdzQ3QWFQc1RKdzh3MXJ5QkpRS2pRNm50V1lVb09ScGJnaVVlemVfZlRsWjdObnRmR1FGMnlMMHAyc2pMandndy10T2twcWx6OFh4UHdvbVlFbllwME9WQ2pQVjNTQzBxeTg5YnF3bDREeHVDYXpObFFIaTZZQWtYUE12cGQ1ZGRhT0syNjVhZWs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>gdacs:WF1033142:0</t>
+          <t>noticia:3dv7b0</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-24 07:06</t>
+          <t>2026-10-24 11:43</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1792839995000</v>
+        <v>1792856591000</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Green forest fire notification in Bolivia</t>
+          <t>Accidente en Caranavi: vehículo de Los Chicos Fieles cae a un barranco y deja varios heridos - FmBolivia</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1362,18 +1346,18 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1381,22 +1365,22 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>GDACS</t>
+          <t>FmBolivia; La Patria Bolivia; Red Uno</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>-13.06332</v>
+        <v>-15.813</v>
       </c>
       <c r="N13" t="n">
-        <v>-67.66426</v>
+        <v>-67.46299999999999</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Caranavi, La Paz</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1406,45 +1390,45 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Ixiamas</t>
+          <t>Caranavi</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>http://www.gdacs.org/report.aspx?eventtype=WF&amp;eventid=1033142</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNeEFrOEtOMHZxMW42REFPU0x1MG5oQjlBMkJucWRLZ292alBXekJKeURBN3NLTVVadWI0OWF4UGtSVXBzTE01eWFSU1kyMUhNZ04zMWNMaUxnMDBBZ0EwTktXbjlaVTBUUmNqa3AwY19KNTU2LWh5LW9IVElVdTdnaHFPanJPd2FqMUxzaUhXZmVpYU1saGc?oc=5 | https://news.google.com/rss/articles/CBMi2wFBVV95cUxOdTVUZUQxVTdvYTdONDQxVlhUTzBOS2hKLW1rS1NUcmRYRnlCVlhIcHZlSjdsaktkQm5CWkFYa3lDQkxnMlh0b3prX0lha1BtbW1qS1VuYnNiX3FiZkYyNDJDR0tqZ0pKMU5TeC04SXV4UUJOTUlPUTB6ek01bzUxTUsydjZqZzI3S3ZLUnRWSUFUVk44WEpKUl9rbzRLb2IwYl9sLVlrYmt5d2ZHNUtGd3lRNnYzMlhuMkJOZW1XSUl2N1BxZWpHbm5XTDJhRUtnR190QWQ1TDlTUVk?oc=5 | https://news.google.com/rss/articles/CBMizAFBVV95cUxNcE1KaHZyUTJCSElxRU9nVzdhTnczWjJGTEhFMEs0bHp2cUdFeHd3VTB0NmVFcjdEN1dsZDZLY2k1ZFFUWkhKV19PU3V2czNyamh1ZE9YajVSVF8xczF6OFhZcWFvYV9EcWg4ZDNCb2p3enhXbFpRYnJMdGdaTXNrWUZSYVhKNTVicWlCLTJ5OE05Z1BvNEx1eEloUk5qTGN3ZHNzbzZWSVljbnRmSERJUWdxRDc0MjJxMGtycWJaaVhXQUUxVUlaWVZLOWE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>noticia:1shhqva</t>
+          <t>clima:Potosí:2026-10-24:viento:1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-24 06:33</t>
+          <t>2026-10-24 10:55</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1792838034000</v>
+        <v>1792853727284</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
+          <t>Potosí 2026-10-24: 60.5 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1459,57 +1443,57 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>-17.97</v>
+        <v>-19.58</v>
       </c>
       <c r="N14" t="n">
-        <v>-67.11</v>
+        <v>-65.75</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQYzB6N082XzFRRnVtcDVmUkYyWjcxUzV2Z3Frd1I0WDNXSnZtY0QzOU1PUkNLMktVT1Vra2FSeXhxZDRuOFZYZjFwejl6ejJTbWY2MGJuSGN3ZHdrdG5JUkgzSXBkbDYtaHlackY3OVFuNWdLcFNpdWNHRU9vNGdoVWx2ODFVdzJXYUxnM0tUcjJvZmc?oc=5 | https://news.google.com/rss/articles/CBMikAFBVV95cUxQS2FPaHd3UnFBRjRoa0lKUm1MNUQ5S00zN1RJZE5fWlVUQnhiY0lLcFRkY2JZak1mZ0c2WEVMVUNJVUJTMGFLNHg4S2ZKNTRqLXJHM09ET19hX1pZeTQwUkdEc2huTHVpcno2QTRZbnhralVRWXozcWc1a2pHUEpBeTV1cWgzTWRwaDEweURKeVE?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>clima:Potosí:2026-10-25:viento:1</t>
+          <t>noticia:1ax0bpy</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-24 02:55</t>
+          <t>2026-10-24 10:32</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1792824927736</v>
+        <v>1792852364000</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Potosí 2026-10-25: 60.5 km/h de ráfagas pronosticadas</t>
+          <t>Creció el Bermejo tras la tormenta: así está el puerto de chalanas en este momento - Que Pasa Salta</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1518,11 +1502,11 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1541,53 +1525,53 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>Que Pasa Salta</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>-19.58</v>
+        <v>-22.721</v>
       </c>
       <c r="N15" t="n">
-        <v>-65.75</v>
+        <v>-64.32599999999999</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Bermejo, Tarija</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Tarija</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Bermejo</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVld9IBfkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVldw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>noticia:1uil931</t>
+          <t>gdacs:WF1033142:0</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-23 22:49</t>
+          <t>2026-10-24 07:06</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1792810149000</v>
+        <v>1792839995000</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Accidente de tránsito en la ruta hacia Alto Beni deja varios heridos - El Deber</t>
+          <t>Green forest fire notification in Bolivia</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1596,18 +1580,18 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1615,22 +1599,22 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>El Deber</t>
+          <t>GDACS</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>-15.578</v>
+        <v>-13.06332</v>
       </c>
       <c r="N16" t="n">
-        <v>-67.44</v>
+        <v>-67.66426</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Alto Beni, La Paz</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1640,45 +1624,45 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Alto Beni</t>
+          <t>Ixiamas</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQakFJRmx3RlJEMkVHU0pxWXZ2ZU1ib04tZy1yeTB2OGhrYk9CU3pMaDVpRThNZktZMS14UzA2Y1VIcEQtZDg3cEU2SmlzQnBmUVVvM0ZNYzZWNExWUXQ3aHpnd3lqOHFVV3pNbDRLS1NQNGtwb2RjSFpleHJkOG5zSXVtWjVIS1dLejNybktRWTJVZXh3WkFUQVE5T2tMdFdn?oc=5 | https://news.google.com/rss/articles/CBMilwFBVV95cUxQMF9BNnUzLURKNGRMUUJ1VXVRSXNnMlBsQnVXOG0tRlFtY3pvRDNPQmNJMWN2RzJVaWdoWndmcHFnTkZFZnJxRkZtMThYYWlwN09ueUgtei1pSE1hZ2FtSzN6elY4VXJHbzFxdll0eWh0ZkxwQkQ1SDZ5b0E3MlVENGZEWGZHUGlwVG4wd2x3OFNEMVpibnFr?oc=5 | https://news.google.com/rss/articles/CBMimgFBVV95cUxNbmwzSnd6c2tFMXBWY0tiemJqRm5CNllOT2p1U0FhdW5QNGFBVXlSZVM1ak5jNGZvcXNVaUQzN3ZQQTlPbmVjQ2Y5RFl2dWVLeUN5NUFodDF0alEyZWlmOHFZWkVVbjdQbkl3ZWtmS25wQWM2TmRZZDBGM2xlS0ZhUzAweXRmcmhVWGY5dV9CUnFBNGtWZHZDSWVB?oc=5</t>
+          <t>http://www.gdacs.org/report.aspx?eventtype=WF&amp;eventid=1033142</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-24:viento:1</t>
+          <t>noticia:1shhqva</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-23 20:55</t>
+          <t>2026-10-24 06:33</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1792803329663</v>
+        <v>1792838034000</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-24: 78.1 km/h de ráfagas pronosticadas</t>
+          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1693,57 +1677,57 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>-17.78</v>
+        <v>-17.97</v>
       </c>
       <c r="N17" t="n">
-        <v>-63.18</v>
+        <v>-67.11</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Oruro, Oruro</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Oruro</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Oruro</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQYzB6N082XzFRRnVtcDVmUkYyWjcxUzV2Z3Frd1I0WDNXSnZtY0QzOU1PUkNLMktVT1Vra2FSeXhxZDRuOFZYZjFwejl6ejJTbWY2MGJuSGN3ZHdrdG5JUkgzSXBkbDYtaHlackY3OVFuNWdLcFNpdWNHRU9vNGdoVWx2ODFVdzJXYUxnM0tUcjJvZmc?oc=5 | https://news.google.com/rss/articles/CBMikAFBVV95cUxQS2FPaHd3UnFBRjRoa0lKUm1MNUQ5S00zN1RJZE5fWlVUQnhiY0lLcFRkY2JZak1mZ0c2WEVMVUNJVUJTMGFLNHg4S2ZKNTRqLXJHM09ET19hX1pZeTQwUkdEc2huTHVpcno2QTRZbnhralVRWXozcWc1a2pHUEpBeTV1cWgzTWRwaDEweURKeVE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>noticia:rabz5p</t>
+          <t>clima:Potosí:2026-10-25:viento:1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-23 20:44</t>
+          <t>2026-10-24 02:55</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1792802686000</v>
+        <v>1792824927736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tome previsiones: se pronostican lluvias y ambiente caluroso para este fin de semana en Cochabamba - Red Uno</t>
+          <t>Potosí 2026-10-25: 60.5 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1752,11 +1736,11 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1775,58 +1759,58 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>-17.39</v>
+        <v>-19.58</v>
       </c>
       <c r="N18" t="n">
-        <v>-66.16</v>
+        <v>-65.75</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Cochabamba, Cochabamba</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTlU5NVFpY1RheTN5ZE1IbG5VYTh2Sk5hZHpHeWI3LVdnSFg2cFJFdnBCVkxiUjNKcUgyUW16SWxpMXFkMHdad2xFN043bklJeG1iQ0V1V3hBZk1Ga3NscjdPVWUySmt4bDNTdWlmSUdOMmNlZ2hkSWZFMmk4VGs0Nm9TcnRCTDhINmtnQU9zZDBUY05HcWpxN3FOX3N1dmVJblE0MGc5di1Ma1N2dGNxOUtoV1MzNnl1OXpRaTZ2UGxMc3RDWndubHVQNUd0eVROMGR2OGxVemtOaEc4bTNRaA?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>noticia:1jfk053</t>
+          <t>noticia:1uil931</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-23 19:08</t>
+          <t>2026-10-23 22:49</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1792796931000</v>
+        <v>1792810149000</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sequía en Pasorapa: el ganado muere por falta de agua y alistan declaratoria de desastre - Red Uno</t>
+          <t>Accidente de tránsito en la ruta hacia Alto Beni deja varios heridos - El Deber</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>climatológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1838,10 +1822,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1849,70 +1833,70 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>El Deber</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>-18.38</v>
+        <v>-15.578</v>
       </c>
       <c r="N19" t="n">
-        <v>-64.649</v>
+        <v>-67.44</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Pasorapa, Cochabamba</t>
+          <t>Alto Beni, La Paz</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Pasorapa</t>
+          <t>Alto Beni</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNQVhTWE8zdE1BQ3lueWJPeV9wUDNsSmJpS0NJTWppMUY4QmlQSUFHVjRORmtrVHQ3MHB0T1pyS25PamxnY0hBQUtzOVRvSUNaUkdGb1RWSGl4dFA4Z3VINVpQTk1pZUpDdUIyUU5hZS1oNGhBa1RWcFhScVMwVTFrVlJaOFQ4OWFqRWVUZ051bHVJTlMxRTBhRFVLUEV2dTZFdDgtRkxJM3VvN3YzUWJfVk41ZWR5U1JoNmx0WFFkMmNTWGVleGNIQlNxWUJzdHIxSWtz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQakFJRmx3RlJEMkVHU0pxWXZ2ZU1ib04tZy1yeTB2OGhrYk9CU3pMaDVpRThNZktZMS14UzA2Y1VIcEQtZDg3cEU2SmlzQnBmUVVvM0ZNYzZWNExWUXQ3aHpnd3lqOHFVV3pNbDRLS1NQNGtwb2RjSFpleHJkOG5zSXVtWjVIS1dLejNybktRWTJVZXh3WkFUQVE5T2tMdFdn?oc=5 | https://news.google.com/rss/articles/CBMilwFBVV95cUxQMF9BNnUzLURKNGRMUUJ1VXVRSXNnMlBsQnVXOG0tRlFtY3pvRDNPQmNJMWN2RzJVaWdoWndmcHFnTkZFZnJxRkZtMThYYWlwN09ueUgtei1pSE1hZ2FtSzN6elY4VXJHbzFxdll0eWh0ZkxwQkQ1SDZ5b0E3MlVENGZEWGZHUGlwVG4wd2x3OFNEMVpibnFr?oc=5 | https://news.google.com/rss/articles/CBMimgFBVV95cUxNbmwzSnd6c2tFMXBWY0tiemJqRm5CNllOT2p1U0FhdW5QNGFBVXlSZVM1ak5jNGZvcXNVaUQzN3ZQQTlPbmVjQ2Y5RFl2dWVLeUN5NUFodDF0alEyZWlmOHFZWkVVbjdQbkl3ZWtmS25wQWM2TmRZZDBGM2xlS0ZhUzAweXRmcmhVWGY5dV9CUnFBNGtWZHZDSWVB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>noticia:ix3l8o</t>
+          <t>clima:Santa Cruz:2026-10-24:viento:1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-23 18:25</t>
+          <t>2026-10-23 20:55</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1792794310000</v>
+        <v>1792803329663</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Oruro evalúa suspender clases presenciales por más de 200 casos de Coxsackie - Visión 360</t>
+          <t>Santa Cruz 2026-10-24: 78.1 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1927,77 +1911,77 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Red Uno; Visión 360</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>-17.97</v>
+        <v>-17.78</v>
       </c>
       <c r="N20" t="n">
-        <v>-67.11</v>
+        <v>-63.18</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0c9IBywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0cw?oc=5 | https://news.google.com/rss/articles/CBMiywFBVV95cUxNMFdHaVpKRmMyOENDYm16UXJPenVSQnpmTE94bDc4UFhqakluMUdvZjAwamUxT3BVWUpJQm8xVHBWengxQmhWM1hjU3d2YXFrLXpVU2VrZDJiMXZLMlQ5bGxGOHFETFhYM0s2RjlUTlhkd0g2eXQweDFHaTlKNGNMUlJfOWg2a0JjTklXUWZKc1BmUXZuZFZ2MF9fV2lEYUY4LXNiNmk3cF9FNjVtTl9GWFotT2ltS0xXTnM1dENvSU9kbFRMalFrYVdXOA?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>noticia:1xqv9m7</t>
+          <t>noticia:rabz5p</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-23 18:09</t>
+          <t>2026-10-23 20:44</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1792793370000</v>
+        <v>1792802686000</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tres heridos en tremendo choque cerca de Oncativo - El Diario del centro del país</t>
+          <t>Tome previsiones: se pronostican lluvias y ambiente caluroso para este fin de semana en Cochabamba - Red Uno</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -2009,54 +1993,70 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>El Diario del centro del país</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
+          <t>Red Uno</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>-17.39</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-66.16</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Cochabamba, Cochabamba</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZERhbTJMQUJVb3hmZFlSZmRGZkdBLWdFTGJVQzdqZkE4aGhhWmdQZ2JDRW1ndkJLWU90VTZ6Ti1JOUZzcFZfcE1zbkRHU1B3YTF4UkVzdllFa1p3SUlObURGamF0Vm9kc3dPLTZVWFJ4NWZZQmlySElPNHhZTnRGNGNZUWw2ZlI1eVBEQkNGNEhLWTNiLWJLUS0xYjA0UWRhc0d6bVN4aVVLSVdsQWlpMUZYdWw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTlU5NVFpY1RheTN5ZE1IbG5VYTh2Sk5hZHpHeWI3LVdnSFg2cFJFdnBCVkxiUjNKcUgyUW16SWxpMXFkMHdad2xFN043bklJeG1iQ0V1V3hBZk1Ga3NscjdPVWUySmt4bDNTdWlmSUdOMmNlZ2hkSWZFMmk4VGs0Nm9TcnRCTDhINmtnQU9zZDBUY05HcWpxN3FOX3N1dmVJblE0MGc5di1Ma1N2dGNxOUtoV1MzNnl1OXpRaTZ2UGxMc3RDWndubHVQNUd0eVROMGR2OGxVemtOaEc4bTNRaA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>noticia:1itd1r7</t>
+          <t>noticia:1jfk053</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-23 15:01</t>
+          <t>2026-10-23 19:08</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1792782098000</v>
+        <v>1792796931000</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Intensa lluvia y granizada en La Paz inundan vías y elevan el nivel de los ríos - eju.tv</t>
+          <t>Sequía en Pasorapa: el ganado muere por falta de agua y alistan declaratoria de desastre - Red Uno</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>climatológica</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -2071,73 +2071,73 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>eju.tv</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>-16.169</v>
+        <v>-18.38</v>
       </c>
       <c r="N22" t="n">
-        <v>-68.09</v>
+        <v>-64.649</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>La Paz, La Paz</t>
+          <t>Pasorapa, Cochabamba</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Nuestra Señora de La Paz</t>
+          <t>Pasorapa</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNWU9QWElKQXEyN3UxVm4xbzJzbEJ1TU1NTHZlRUp6YndmeU9GQnJKcTluVEJ2ZHQ5cGp3aWhlMUd5ektWQlBpUVNmZnZuRnJwMXlydzAzX0FBVnY5UDMzQTBkWVRNRUNJSlRvX3MyQVhMcEhIMW9WSUpXckVSd0RJWk1KMFBKWmJNU3diQVlEN1Y5aVV6eVBaZXpOMnFIWWxaMlRlY0ZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNQVhTWE8zdE1BQ3lueWJPeV9wUDNsSmJpS0NJTWppMUY4QmlQSUFHVjRORmtrVHQ3MHB0T1pyS25PamxnY0hBQUtzOVRvSUNaUkdGb1RWSGl4dFA4Z3VINVpQTk1pZUpDdUIyUU5hZS1oNGhBa1RWcFhScVMwVTFrVlJaOFQ4OWFqRWVUZ051bHVJTlMxRTBhRFVLUEV2dTZFdDgtRkxJM3VvN3YzUWJfVk41ZWR5U1JoNmx0WFFkMmNTWGVleGNIQlNxWUJzdHIxSWtz?oc=5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>noticia:51709n</t>
+          <t>noticia:ix3l8o</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-23 13:38</t>
+          <t>2026-10-23 18:25</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1792777139000</v>
+        <v>1792794310000</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - eju.tv</t>
+          <t>Oruro evalúa suspender clases presenciales por más de 200 casos de Coxsackie - Visión 360</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -2149,73 +2149,73 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Red Uno; eju.tv</t>
+          <t>Red Uno; Visión 360</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>-17.764</v>
+        <v>-17.97</v>
       </c>
       <c r="N23" t="n">
-        <v>-62.903</v>
+        <v>-67.11</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Cotoca, Santa Cruz</t>
+          <t>Oruro, Oruro</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Oruro</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Cotoca</t>
+          <t>Oruro</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPcjZTSmprRGVoNlRqQmdBTE5VM3pRQ1ZFakFUbzVyMUhiaDVkT0liaG9UNEZXekV6bWsycUk4X1JCSEY5RjhNVlZaTk9ULUFuZkY3NnZuWmZ1a19leUhFdlIyQV9kLWxlSkxfeXFhcFRTZjZ2YkpQQlJ1dkNLMDBjaGZ4SkhyQ0RfcnhKSEg5WURCQVQwbENYTHEzUzJSaUEzMGo2bWdyS3lsM016LXc?oc=5 | https://news.google.com/rss/articles/CBMi0AFBVV95cUxOVGY3YVRLWWxYM0IycjF4dlNUeUhqZG90Yng4aWhmN3A5ai02WENWYnF4bWpoZHFKMGc1X0JPRHdRRVZfSlA4UmZFa2kxYkNIS3ZtQ1NvNlNCME51eVZTRkRKSUQ5MmRoaWl5Tkt5NHpPUEFwemN2YTV1djFwdHlqQnFqRHNPenhYcTlsanJPcXhpOVV1NmFBUXZyazQ2MkUzM0dSZy02ZllxTGtjcl9ldzdHSktTRlVaalZJc1pubUNQMWFTbzVEOUJ1UmhCdEJt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0c9IBywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0cw?oc=5 | https://news.google.com/rss/articles/CBMiywFBVV95cUxNMFdHaVpKRmMyOENDYm16UXJPenVSQnpmTE94bDc4UFhqakluMUdvZjAwamUxT3BVWUpJQm8xVHBWengxQmhWM1hjU3d2YXFrLXpVU2VrZDJiMXZLMlQ5bGxGOHFETFhYM0s2RjlUTlhkd0g2eXQweDFHaTlKNGNMUlJfOWg2a0JjTklXUWZKc1BmUXZuZFZ2MF9fV2lEYUY4LXNiNmk3cF9FNjVtTl9GWFotT2ltS0xXTnM1dENvSU9kbFRMalFrYVdXOA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>noticia:11rddql</t>
+          <t>noticia:1xqv9m7</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-23 13:22</t>
+          <t>2026-10-23 18:09</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1792776139000</v>
+        <v>1792793370000</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Intensifican acciones preventivas contra el dengue en Caranavi - El Diario - Bolivia</t>
+          <t>Tres heridos en tremendo choque cerca de Oncativo - El Diario del centro del país</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -2227,73 +2227,57 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
-        </is>
-      </c>
-      <c r="M24" t="n">
-        <v>-15.813</v>
-      </c>
-      <c r="N24" t="n">
-        <v>-67.46299999999999</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Caranavi, La Paz</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>La Paz</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>Caranavi</t>
-        </is>
-      </c>
+          <t>El Diario del centro del país</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOMjhSeDJBek5iaFhDcnFzX1lKelgwZmUwLTJnbEhMdDRMelUxNks5Ti1pRHh3dDhTcC1YZEdqM3FJOGdqVHRvcXVhRlpCQzVDTEZMUFBkV1NrYVQ2LXRqTTBhcGRQc21CQ0VabzZaNExXb1BjTzJ2Uk5BcFF0VG5XOFNRa3lqUWlJSnRFUUVXYnNpbXB0LVVmSXVWSzJxcmVpdVVxUC1KOUhTQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZERhbTJMQUJVb3hmZFlSZmRGZkdBLWdFTGJVQzdqZkE4aGhhWmdQZ2JDRW1ndkJLWU90VTZ6Ti1JOUZzcFZfcE1zbkRHU1B3YTF4UkVzdllFa1p3SUlObURGamF0Vm9kc3dPLTZVWFJ4NWZZQmlySElPNHhZTnRGNGNZUWw2ZlI1eVBEQkNGNEhLWTNiLWJLUS0xYjA0UWRhc0d6bVN4aVVLSVdsQWlpMUZYdWw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>noticia:fcm3nx</t>
+          <t>noticia:1itd1r7</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-23 12:58</t>
+          <t>2026-10-23 15:01</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1792774699000</v>
+        <v>1792782098000</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>[VIDEO] Así fue el accidente de moto que dejó un adolescente fallecido y un hombre gravemente herido - Red Uno</t>
+          <t>Intensa lluvia y granizada en La Paz inundan vías y elevan el nivel de los ríos - eju.tv</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2305,57 +2289,73 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Red Uno</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
+          <t>eju.tv</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>-16.169</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-68.09</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>La Paz, La Paz</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>La Paz</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Nuestra Señora de La Paz</t>
+        </is>
+      </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOSmJMazhUemNfRHpWcDBoTVFZMUpwdlVKVUtvUXZNTGRRRHlwLW5KNmNhcmFnd1czbi1yalhFMnpSS1dmUE9jVzNlOS1kMWZtRzBHZ2EtcDRDdU5Gc2JUQVIwM2xPa2lZVmswRi1SUFVPcm8xcHlGN3F2UThTSDdKMDNyYnJmVkcxazNLLVBLOWFYM09FVUpmVnN5RVhpSVo2V1VCVmFwQ1gzTmRUWVp2aXMwcmxHRS1GV2p3NTBtR2RzM2wwVHUzaGJkRXJYbHdvaDlhWm5YMTk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNWU9QWElKQXEyN3UxVm4xbzJzbEJ1TU1NTHZlRUp6YndmeU9GQnJKcTluVEJ2ZHQ5cGp3aWhlMUd5ektWQlBpUVNmZnZuRnJwMXlydzAzX0FBVnY5UDMzQTBkWVRNRUNJSlRvX3MyQVhMcEhIMW9WSUpXckVSd0RJWk1KMFBKWmJNU3diQVlEN1Y5aVV6eVBaZXpOMnFIWWxaMlRlY0ZB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>noticia:1cjx1qd</t>
+          <t>noticia:51709n</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-23 12:39</t>
+          <t>2026-10-23 13:38</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1792773575000</v>
+        <v>1792777139000</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Más de 60 municipios en La Paz sufren falta de lluvias - La Patria Bolivia</t>
+          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - eju.tv</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2363,70 +2363,70 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
+          <t>Red Uno; eju.tv</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>-16.169</v>
+        <v>-17.764</v>
       </c>
       <c r="N26" t="n">
-        <v>-68.09</v>
+        <v>-62.903</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>La Paz, La Paz</t>
+          <t>Cotoca, Santa Cruz</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Nuestra Señora de La Paz</t>
+          <t>Cotoca</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE52Qi03Z1J6OS1CR2liRVZ0VlhCcmVQWFV6RUdGNXdrbzZRNXFjTWRaRnc1b3VoV0xaY3RIdncxNlNnYkxyUXo5MTlJWmMwWDNSMDE4ZHI2VkpWajFPaUF2SmRVYkk2eDZYQ1RfUU9ieENrZG9UVVFiaXZSeGI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPcjZTSmprRGVoNlRqQmdBTE5VM3pRQ1ZFakFUbzVyMUhiaDVkT0liaG9UNEZXekV6bWsycUk4X1JCSEY5RjhNVlZaTk9ULUFuZkY3NnZuWmZ1a19leUhFdlIyQV9kLWxlSkxfeXFhcFRTZjZ2YkpQQlJ1dkNLMDBjaGZ4SkhyQ0RfcnhKSEg5WURCQVQwbENYTHEzUzJSaUEzMGo2bWdyS3lsM016LXc?oc=5 | https://news.google.com/rss/articles/CBMi0AFBVV95cUxOVGY3YVRLWWxYM0IycjF4dlNUeUhqZG90Yng4aWhmN3A5ai02WENWYnF4bWpoZHFKMGc1X0JPRHdRRVZfSlA4UmZFa2kxYkNIS3ZtQ1NvNlNCME51eVZTRkRKSUQ5MmRoaWl5Tkt5NHpPUEFwemN2YTV1djFwdHlqQnFqRHNPenhYcTlsanJPcXhpOVV1NmFBUXZyazQ2MkUzM0dSZy02ZllxTGtjcl9ldzdHSktTRlVaalZJc1pubUNQMWFTbzVEOUJ1UmhCdEJt?oc=5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>clima:Sucre:2026-10-23:viento:1</t>
+          <t>noticia:11rddql</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-23 06:55</t>
+          <t>2026-10-23 13:22</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1792752927735</v>
+        <v>1792776139000</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sucre 2026-10-23: 66.2 km/h de ráfagas pronosticadas</t>
+          <t>Intensifican acciones preventivas contra el dengue en Caranavi - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -2445,73 +2445,73 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>-19.03</v>
+        <v>-15.813</v>
       </c>
       <c r="N27" t="n">
-        <v>-65.26000000000001</v>
+        <v>-67.46299999999999</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Caranavi, La Paz</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Chuquisaca</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Caranavi</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOMjhSeDJBek5iaFhDcnFzX1lKelgwZmUwLTJnbEhMdDRMelUxNks5Ti1pRHh3dDhTcC1YZEdqM3FJOGdqVHRvcXVhRlpCQzVDTEZMUFBkV1NrYVQ2LXRqTTBhcGRQc21CQ0VabzZaNExXb1BjTzJ2Uk5BcFF0VG5XOFNRa3lqUWlJSnRFUUVXYnNpbXB0LVVmSXVWSzJxcmVpdVVxUC1KOUhTQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-24:viento:2</t>
+          <t>noticia:fcm3nx</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-23 06:55</t>
+          <t>2026-10-23 12:58</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1792752927734</v>
+        <v>1792774699000</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-24: 85 km/h de ráfagas pronosticadas</t>
+          <t>[VIDEO] Así fue el accidente de moto que dejó un adolescente fallecido y un hombre gravemente herido - Red Uno</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2523,66 +2523,50 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
-        </is>
-      </c>
-      <c r="M28" t="n">
-        <v>-17.78</v>
-      </c>
-      <c r="N28" t="n">
-        <v>-63.18</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>Santa Cruz</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Santa Cruz</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>Santa Cruz de la Sierra</t>
-        </is>
-      </c>
+          <t>Red Uno</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOSmJMazhUemNfRHpWcDBoTVFZMUpwdlVKVUtvUXZNTGRRRHlwLW5KNmNhcmFnd1czbi1yalhFMnpSS1dmUE9jVzNlOS1kMWZtRzBHZ2EtcDRDdU5Gc2JUQVIwM2xPa2lZVmswRi1SUFVPcm8xcHlGN3F2UThTSDdKMDNyYnJmVkcxazNLLVBLOWFYM09FVUpmVnN5RVhpSVo2V1VCVmFwQ1gzTmRUWVp2aXMwcmxHRS1GV2p3NTBtR2RzM2wwVHUzaGJkRXJYbHdvaDlhWm5YMTk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>usgs:us6000u49c</t>
+          <t>noticia:1cjx1qd</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-22 22:45</t>
+          <t>2026-10-23 12:39</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1792723541183</v>
+        <v>1792773575000</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sismo M 4.5 - 58 km SW of Atocha, Bolivia</t>
+          <t>Más de 60 municipios en La Paz sufren falta de lluvias - La Patria Bolivia</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>geológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -2601,53 +2585,53 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>USGS</t>
+          <t>La Patria Bolivia</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>-21.3469</v>
+        <v>-16.169</v>
       </c>
       <c r="N29" t="n">
-        <v>-66.5795</v>
+        <v>-68.09</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>58 km SW of Atocha, Bolivia</t>
+          <t>La Paz, La Paz</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>San Pablo</t>
+          <t>Nuestra Señora de La Paz</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>https://earthquake.usgs.gov/earthquakes/eventpage/us6000u49c</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE52Qi03Z1J6OS1CR2liRVZ0VlhCcmVQWFV6RUdGNXdrbzZRNXFjTWRaRnc1b3VoV0xaY3RIdncxNlNnYkxyUXo5MTlJWmMwWDNSMDE4ZHI2VkpWajFPaUF2SmRVYkk2eDZYQ1RfUU9ieENrZG9UVVFiaXZSeGI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-22:viento:1</t>
+          <t>clima:Sucre:2026-10-23:viento:1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-22 21:55</t>
+          <t>2026-10-23 06:55</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1792720528712</v>
+        <v>1792752927735</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-22: 67.7 km/h de ráfagas pronosticadas</t>
+          <t>Sucre 2026-10-23: 66.2 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2683,24 +2667,24 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>-17.78</v>
+        <v>-19.03</v>
       </c>
       <c r="N30" t="n">
-        <v>-63.18</v>
+        <v>-65.26000000000001</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Chuquisaca</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2712,20 +2696,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-23:viento:2</t>
+          <t>clima:Santa Cruz:2026-10-24:viento:2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-22 21:55</t>
+          <t>2026-10-23 06:55</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1792720528712</v>
+        <v>1792752927734</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-23: 83.9 km/h de ráfagas pronosticadas</t>
+          <t>Santa Cruz 2026-10-24: 85 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2790,33 +2774,33 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>noticia:1hhvre7</t>
+          <t>usgs:us6000u49c</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-22 19:36</t>
+          <t>2026-10-22 22:45</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1792712202000</v>
+        <v>1792723541183</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Virgen de Cotoca: Controlan incendio en depósito de materiales plásticos - El Mundo Bolivia</t>
+          <t>Sismo M 4.5 - 58 km SW of Atocha, Bolivia</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>geológica</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -2835,66 +2819,66 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>El Mundo Bolivia</t>
+          <t>USGS</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>-17.764</v>
+        <v>-21.3469</v>
       </c>
       <c r="N32" t="n">
-        <v>-62.903</v>
+        <v>-66.5795</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Cotoca, Santa Cruz</t>
+          <t>58 km SW of Atocha, Bolivia</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>Cotoca</t>
+          <t>San Pablo</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcDF6VE5FNzRaWGRuUzFKeXhnZ21DZTRaaEtrVEJEa1Z3ejg2VG1ONG1ENmlDWlkyVjlkQkJwS2F1XzBGMFQwSHd4OEwxTW1PbHdGcUh1ckV6SGpDd2hiN0dkeUVTcnFXT3RjOU1kLXZtVVdZY2hkZS1pcVpVUFhnRktqcHY5UnBrY0xUMDRETjl6N0pXT3A5amxhMA?oc=5</t>
+          <t>https://earthquake.usgs.gov/earthquakes/eventpage/us6000u49c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>noticia:bksnde</t>
+          <t>clima:Santa Cruz:2026-10-22:viento:1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-22 17:01</t>
+          <t>2026-10-22 21:55</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1792702880000</v>
+        <v>1792720528712</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Reportan un incendio cerca de la carretera a Cotoca - eju.tv</t>
+          <t>Santa Cruz 2026-10-22: 67.7 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -2913,18 +2897,18 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>eju.tv</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>-17.764</v>
+        <v>-17.78</v>
       </c>
       <c r="N33" t="n">
-        <v>-62.903</v>
+        <v>-63.18</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Cotoca, Santa Cruz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -2934,37 +2918,37 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>Cotoca</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPNGtpbnBfRnRBalVudnBlZHdVQ0ZSaUplZmtvTGE0aTQzdkxWS3d4My1EZEJ1UE9FNFQ3RmpyZGVsbS1qNEM1QUVFRFAxM2pYT1VqQzRuVjRtZnVNUGlKODNMc0F1a3l6TUpuQmtlUWNlVTVEWWU5ZGZtQm5LWUp3Sg?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>noticia:17hz69v</t>
+          <t>clima:Santa Cruz:2026-10-23:viento:2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-22 13:05</t>
+          <t>2026-10-22 21:55</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1792688709000</v>
+        <v>1792720528712</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Accidente en El Sillar deja al menos 29 heridos - La Razón Digital Bolivia</t>
+          <t>Santa Cruz 2026-10-23: 83.9 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -2979,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2991,37 +2975,53 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>La Razón Digital Bolivia</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
+          <t>Open-Meteo (pronóstico)</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>-17.78</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-63.18</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Santa Cruz de la Sierra</t>
+        </is>
+      </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPaXhTdm45YWZnWVFxVzJnb1ZwbUN4SmUtLVdJN0VJdFZBamRyQmFxN0RZelBfTklaSTVyOUZ3ajQ5MFB2TEN4Ukd6TE5ORFY5SEROVk1CZ25sRWJ1QnRBdTVfTktlby1NWXhaVWI5YnRvaDZWbHVjdDVoeFp5Tk5veFk5a19MSWJqcEJVV0dzV3k?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>noticia:1f1qb0</t>
+          <t>noticia:1hhvre7</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-22 12:09</t>
+          <t>2026-10-22 19:36</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1792685373000</v>
+        <v>1792712202000</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Accidente en el tramo Locotal–Villa Tunari: la vía está transitable con precaución - Red Uno</t>
+          <t>Virgen de Cotoca: Controlan incendio en depósito de materiales plásticos - El Mundo Bolivia</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3053,73 +3053,73 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>El Mundo Bolivia</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>-16.556</v>
+        <v>-17.764</v>
       </c>
       <c r="N35" t="n">
-        <v>-65.569</v>
+        <v>-62.903</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Villa Tunari, Cochabamba</t>
+          <t>Cotoca, Santa Cruz</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>Villa Tunari</t>
+          <t>Cotoca</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTFozcEEwNXBqV19sS2VibXh0MGt0QlhsX1djSTFGQW5zNlFLRHZpNVVnZ1JmWDQ4LVRHX2Rmb3B5UU9qV0FZQmJCaUZYdmwyNG1NenJ4Qzlzd0NJTGs1SjMxdFRtRFBzSUkybGJfZFFaNFZBc21FSUJYSFVkQkVkSEhQaGw0UFVzeXctZHo3cjNsYm5weXJlOU1wcmFncnNhMC1BQUpvNWlDX1NxZXU4b09kVFFWR2tSVEk2UTdXXzB3TjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcDF6VE5FNzRaWGRuUzFKeXhnZ21DZTRaaEtrVEJEa1Z3ejg2VG1ONG1ENmlDWlkyVjlkQkJwS2F1XzBGMFQwSHd4OEwxTW1PbHdGcUh1ckV6SGpDd2hiN0dkeUVTcnFXT3RjOU1kLXZtVVdZY2hkZS1pcVpVUFhnRktqcHY5UnBrY0xUMDRETjl6N0pXT3A5amxhMA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>noticia:wi18tm</t>
+          <t>noticia:bksnde</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-22 11:53</t>
+          <t>2026-10-22 17:01</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1792684426000</v>
+        <v>1792702880000</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Accidente en El Sillar deja heridos y derrame de combustible: esto es lo último que se sabe - Red Uno</t>
+          <t>Reportan un incendio cerca de la carretera a Cotoca - eju.tv</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>tecnológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -3131,37 +3131,53 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Red Uno</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
+          <t>eju.tv</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>-17.764</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-62.903</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Cotoca, Santa Cruz</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Cotoca</t>
+        </is>
+      </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPZHNBTEdaQm5Wby1lTF9mWlQ2aGg0MVc4S0MwVWJ3dUJ5WWU5X3IwYWhKRjk5VWtYWEJHRDF4QldVc29laVNPSTJNWFBDSkNFQlFSYTJUXzNMNF9hckFBN1I2T2xoQUtYQ2V6MDNTZHhHVk9qeTBCdHRpM2ZLd0pyOFRweUUxX19STzRHTHg5VUY5d1lhS0tDeXpCdklqcTZGT1J4R0xnSDhoak1EZ2dtNUhSTUV6b1o0U0VSdWY5X0E3U05Tc1dYVEN2WFZUeFhPMTBJTmowNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPNGtpbnBfRnRBalVudnBlZHdVQ0ZSaUplZmtvTGE0aTQzdkxWS3d4My1EZEJ1UE9FNFQ3RmpyZGVsbS1qNEM1QUVFRFAxM2pYT1VqQzRuVjRtZnVNUGlKODNMc0F1a3l6TUpuQmtlUWNlVTVEWWU5ZGZtQm5LWUp3Sg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>noticia:12gfagq</t>
+          <t>noticia:17hz69v</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-22 11:28</t>
+          <t>2026-10-22 13:05</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1792682880000</v>
+        <v>1792688709000</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Reportan triple colisión entre dos camiones y un bus en la carretera Cochabamba-Santa Cruz - FmBolivia</t>
+          <t>Accidente en El Sillar deja al menos 29 heridos - La Razón Digital Bolivia</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3170,18 +3186,18 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -3189,57 +3205,41 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>FmBolivia; Red Uno</t>
-        </is>
-      </c>
-      <c r="M37" t="n">
-        <v>-17.39</v>
-      </c>
-      <c r="N37" t="n">
-        <v>-66.16</v>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>Cochabamba, Cochabamba</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
+          <t>La Razón Digital Bolivia</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNMTNBaFZNMU9SR25vdVBuNXlZY3g4VkFWYXRiQnNSaUFjemZhUHZWNHg4V2owU2xfNndBak94TnU2cHNUVXdNNWl2eUdHZVNMbVZweTR5M0o0bWdTNUN4QkoxUkI2TDBmVE03M09zRGhJRVFzV0tPZ1NCWEJLUkt1ZGN4UGduOUZMQnJoM0tMYTh0ZlFxaFJNUkJqaWFPazRlMzN3ajhjUEdUYXlZRndpb3RSdTFCX2tCZGJxQ0x4SlBISWJsRVoyN3ZR?oc=5 | https://news.google.com/rss/articles/CBMirwFBVV95cUxNNUROMzd1UDJRWVZZQ011cFd2c1FSdER1ZzdleU04cXpwYk5HaUZrLXoyU2NzdFk1dnNRUndhUWt0cG9DX09rSjlLcDItU0tzcmQtS3E4dDQ4ZF9HdGJLdk13ek9BNHJUWVlCcklrM25rZ01RbXhLalRBT1FGdDNReHdlTFZkNkJ5ZFd3N3NZVFVmOFUxbEhHN0RsaUxiSVZsM0lXVEFYSHVRQlhsOEtJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPaXhTdm45YWZnWVFxVzJnb1ZwbUN4SmUtLVdJN0VJdFZBamRyQmFxN0RZelBfTklaSTVyOUZ3ajQ5MFB2TEN4Ukd6TE5ORFY5SEROVk1CZ25sRWJ1QnRBdTVfTktlby1NWXhaVWI5YnRvaDZWbHVjdDVoeFp5Tk5veFk5a19MSWJqcEJVV0dzV3k?oc=5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>noticia:1jl2oid</t>
+          <t>noticia:1f1qb0</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-22 07:49</t>
+          <t>2026-10-22 12:09</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1792669785000</v>
+        <v>1792685373000</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - eju.tv</t>
+          <t>Accidente en el tramo Locotal–Villa Tunari: la vía está transitable con precaución - Red Uno</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3248,18 +3248,18 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -3267,113 +3267,331 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Red Uno; eju.tv</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>-17.781</v>
+        <v>-16.556</v>
       </c>
       <c r="N38" t="n">
-        <v>-63.139</v>
+        <v>-65.569</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Santa Cruz, Santa Cruz</t>
+          <t>Villa Tunari, Cochabamba</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Villa Tunari</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQbTBrUmlla3FvVU1EX1pxcUI3SXYzbUFFMzlnRzhlSDJwMGpWWURxYjIwSkJBRGdCazMzT01hVy1qMFY3RnJLbC1XNXJ4bU55aDJVeXpNUlRsbzQ3T3hiRXJ5SWlhNmw5cDZFanNoWFBtQ01Gd3dscXltWmU5VHBSQlN3c2IwNGxuVE5tQ3lOT1RmNzRiVi1hc0hn?oc=5 | https://news.google.com/rss/articles/CBMiuwFBVV95cUxNVEh1bFlCanFuOTJid2EzYS1meG5oekFJcGFaME1fTk9sUnZpd3U0UXFHUFVJSW1jc1hzM2VFOFprT2xNYjBzbmswZmdJV3dremRIS0I4MDNzRjBnbEttWEhfOWZBbmFrRnNHWDFVLVFoM0VkZkxkaW4tMmZlSFJLei1heTFHMU0wSmxQVVRZN0cwaXQzcDBtZkdwTUFma0RXU2dwLXRnLTBkNGN3Vm1fV3hEdlM1dWZ1SEsw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTFozcEEwNXBqV19sS2VibXh0MGt0QlhsX1djSTFGQW5zNlFLRHZpNVVnZ1JmWDQ4LVRHX2Rmb3B5UU9qV0FZQmJCaUZYdmwyNG1NenJ4Qzlzd0NJTGs1SjMxdFRtRFBzSUkybGJfZFFaNFZBc21FSUJYSFVkQkVkSEhQaGw0UFVzeXctZHo3cjNsYm5weXJlOU1wcmFncnNhMC1BQUpvNWlDX1NxZXU4b09kVFFWR2tSVEk2UTdXXzB3TjA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>noticia:wi18tm</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-10-22 11:53</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1792684426000</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Accidente en El Sillar deja heridos y derrame de combustible: esto es lo último que se sabe - Red Uno</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>tecnológica</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>amarilla</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Red Uno</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPZHNBTEdaQm5Wby1lTF9mWlQ2aGg0MVc4S0MwVWJ3dUJ5WWU5X3IwYWhKRjk5VWtYWEJHRDF4QldVc29laVNPSTJNWFBDSkNFQlFSYTJUXzNMNF9hckFBN1I2T2xoQUtYQ2V6MDNTZHhHVk9qeTBCdHRpM2ZLd0pyOFRweUUxX19STzRHTHg5VUY5d1lhS0tDeXpCdklqcTZGT1J4R0xnSDhoak1EZ2dtNUhSTUV6b1o0U0VSdWY5X0E3U05Tc1dYVEN2WFZUeFhPMTBJTmowNA?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>noticia:12gfagq</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-10-22 11:28</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1792682880000</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Reportan triple colisión entre dos camiones y un bus en la carretera Cochabamba-Santa Cruz - FmBolivia</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>antropogénica</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>verde</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>2</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>FmBolivia; Red Uno</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>-17.39</v>
+      </c>
+      <c r="N40" t="n">
+        <v>-66.16</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Cochabamba, Cochabamba</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNMTNBaFZNMU9SR25vdVBuNXlZY3g4VkFWYXRiQnNSaUFjemZhUHZWNHg4V2owU2xfNndBak94TnU2cHNUVXdNNWl2eUdHZVNMbVZweTR5M0o0bWdTNUN4QkoxUkI2TDBmVE03M09zRGhJRVFzV0tPZ1NCWEJLUkt1ZGN4UGduOUZMQnJoM0tMYTh0ZlFxaFJNUkJqaWFPazRlMzN3ajhjUEdUYXlZRndpb3RSdTFCX2tCZGJxQ0x4SlBISWJsRVoyN3ZR?oc=5 | https://news.google.com/rss/articles/CBMirwFBVV95cUxNNUROMzd1UDJRWVZZQ011cFd2c1FSdER1ZzdleU04cXpwYk5HaUZrLXoyU2NzdFk1dnNRUndhUWt0cG9DX09rSjlLcDItU0tzcmQtS3E4dDQ4ZF9HdGJLdk13ek9BNHJUWVlCcklrM25rZ01RbXhLalRBT1FGdDNReHdlTFZkNkJ5ZFd3N3NZVFVmOFUxbEhHN0RsaUxiSVZsM0lXVEFYSHVRQlhsOEtJ?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>noticia:1jl2oid</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-10-22 07:49</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1792669785000</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - eju.tv</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>antropogénica</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>amarilla</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>2</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Red Uno; eju.tv</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>-17.781</v>
+      </c>
+      <c r="N41" t="n">
+        <v>-63.139</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Santa Cruz, Santa Cruz</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Santa Cruz de la Sierra</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQbTBrUmlla3FvVU1EX1pxcUI3SXYzbUFFMzlnRzhlSDJwMGpWWURxYjIwSkJBRGdCazMzT01hVy1qMFY3RnJLbC1XNXJ4bU55aDJVeXpNUlRsbzQ3T3hiRXJ5SWlhNmw5cDZFanNoWFBtQ01Gd3dscXltWmU5VHBSQlN3c2IwNGxuVE5tQ3lOT1RmNzRiVi1hc0hn?oc=5 | https://news.google.com/rss/articles/CBMiuwFBVV95cUxNVEh1bFlCanFuOTJid2EzYS1meG5oekFJcGFaME1fTk9sUnZpd3U0UXFHUFVJSW1jc1hzM2VFOFprT2xNYjBzbmswZmdJV3dremRIS0I4MDNzRjBnbEttWEhfOWZBbmFrRnNHWDFVLVFoM0VkZkxkaW4tMmZlSFJLei1heTFHMU0wSmxQVVRZN0cwaXQzcDBtZkdwTUFma0RXU2dwLXRnLTBkNGN3Vm1fV3hEdlM1dWZ1SEsw?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>noticia:n32ahi</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>2026-10-22 05:30</t>
         </is>
       </c>
-      <c r="C39" t="n">
+      <c r="C42" t="n">
         <v>1792661402000</v>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>Senamhi anuncia el inicio de la temporada de lluvias en Bolivia y prevé granizadas como la de La Paz - FmBolivia</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>meteorológica</t>
         </is>
       </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="inlineStr">
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="inlineStr">
         <is>
           <t>verde</t>
         </is>
       </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="inlineStr">
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="K39" t="n">
-        <v>1</v>
-      </c>
-      <c r="L39" t="inlineStr">
+      <c r="K42" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t>FmBolivia</t>
         </is>
       </c>
-      <c r="M39" t="n">
+      <c r="M42" t="n">
         <v>-16.169</v>
       </c>
-      <c r="N39" t="n">
+      <c r="N42" t="n">
         <v>-68.09</v>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>La Paz, La Paz</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>La Paz</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>Nuestra Señora de La Paz</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="R42" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQNmVPRnVBMGQzdEI5SUp3Z3ZGVExwTUR6TWNadGQ1QldUS1o2QVFvUl9sVEZKMDVyQVVrS25rU1RSQlJKWXk1YzE0NUhidjhpcmFaSlhZUDZvcE9XcG1KTFNTYmowUU1CSFJNOVR2UHNmMk1iT3N0RVBteHkzZkgyRFROYk1pdkpxVHZya3N2X2FVLVQxbURFVVZlb1NzRjZzTE95TXFVUXFJNkVZakQ2bUhVQzB0SXk3TVhXUTJXa0dycTE1MWVQRFpDX3lDSWFqUGwzU2NtNA?oc=5</t>
         </is>
@@ -3390,7 +3608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S56"/>
+  <dimension ref="A1:S59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3493,7 +3711,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>noticia:1sg8pi0</t>
+          <t>noticia:1at00ey</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3503,11 +3721,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-25 09:59</t>
+          <t>2026-10-25 11:19</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1792936752000</v>
+        <v>1792941547000</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3529,13 +3747,13 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Bus de agrupación musical sufre accidente rumbo al trópico de Cochabamba | VIDEO - Red Uno</t>
+          <t>Dos cisternas chocan y provocan voraz incendio en la ruta a Camiri - Red Uno</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOVDVzVTJNM2JuQ25sMThEaVZNOUNRd3FGT3RhVnFrZXZ2NDQ1YlluTVdhbVNUQnA1MGNESHRSWVUzbC1kRVh3OTR0emtlTG91cmRWeFJ5dk5zb3p2WFRyMEJUV3FNRnY1WHhRUU9WLTlJcmNyNXJZZFdoM0JoZjNpa3hjUXhMM0xrUDJab2VadkM5RWZYQ3lWZTVDdzg1akxJT2lxcDVNNzI0NG1hejdfdkUyTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPTTF0OUdVS1c1a0lZWmk3bGxHdDJIalpWZTRyQTY3eWE2a2dWOHlsaldKZXpSLWN5c3BkUWdBRkJuSzhHdWl2ZjgwTFFFYnd0aTAxZ3dJU0hCekNZNm9aTTJSZUNfQjVIM3FrUUJ4NXAwa3paZ3BEek9xTVZNQWdnN01xRHloV1ZXZHV6N0JpUWo3RE9DMlFGdkNnWkloTjVVY3RBR1RSRUJJWFVtby1fMWFMNTdLZw?oc=5</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -3545,14 +3763,14 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-17.39</v>
+        <v>-20.05</v>
       </c>
       <c r="O2" t="n">
-        <v>-66.16</v>
+        <v>-63.486</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Cochabamba, Cochabamba</t>
+          <t>Camiri, Santa Cruz</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -3562,19 +3780,19 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Camiri</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>noticia:167wlhz</t>
+          <t>noticia:1uf38hl</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3584,11 +3802,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-25 07:53</t>
+          <t>2026-10-25 10:59</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1792929231000</v>
+        <v>1792940350000</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -3597,7 +3815,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -3610,13 +3828,13 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>¡A sacar el paraguas! Santa cruz amanece con lluvia, frío y complicaciones en el tránsito vehicular - Red Uno</t>
+          <t>¡Cisterna con combustible en llamas! Reportan impresionante incendio en la carretera a Camiri - Red Uno</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOY1ZpYktLR3pUQXotUndVR3puUzVHbW1YTzNyUmJvUHB4Q2JmelRvOEdaRldOUm1xLVJnbGR5VWcxTjNEM3ZUYktCUWtVM0hKSjFuRGdpX0JxN0M5MVZBSG1aVURyVWktdmxwbUtRT19ydU5LdzNTZ2Zpb2ozdHlMUUdTVlAyVk4xODBnV0hyTXdVVndyNzV3VC1KMzFnV3lpcFFXSk9MdDZOTWlWakNwT1FnNDh6QVdjazVYZDVVMkdaLU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxORUhqeWpKY1FHRWoxaHN0UXFzS3dpeHh6N0NwLUJOZTlZcDVoNHN0VnI0by1qMWtZZEkxVmtUNjdNTFhjaEFQU2IyMlNwZW95WFBzbFJPVVB6TjJtdjNENk1LWVlsMUxUUzBNVzkxRk1HZ3lQU0s2M1lRVlRuaXlkMmJrd3AyTGpIdXItNkhlU3dhTzBRME56Rm1DSlZCYjNxSnNTbTFqNWRoUkdraHhlREhuYldqeFk2N3poWEx2M08?oc=5</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -3626,14 +3844,14 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-17.781</v>
+        <v>-20.05</v>
       </c>
       <c r="O3" t="n">
-        <v>-63.139</v>
+        <v>-63.486</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Santa Cruz, Santa Cruz</t>
+          <t>Camiri, Santa Cruz</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -3648,14 +3866,14 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Camiri</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>noticia:bzr7eh</t>
+          <t>noticia:1sg8pi0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3665,39 +3883,39 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-25 07:09</t>
+          <t>2026-10-25 09:59</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1792926572000</v>
+        <v>1792936752000</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>hidrológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Alerta naranja por riesgo de desbordes de ríos - El Diario - Bolivia</t>
+          <t>Bus de agrupación musical sufre accidente rumbo al trópico de Cochabamba | VIDEO - Red Uno</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNNGZKSDVaZkowWUFGSEUyTWR3d3dsc04waFBLLWUtcVpiTDYzbmNtYTN1RkFLbjAwN3dxT0xZc3pqc3REUXduZVltQ2Fud1BZLTh1bTNiTEJueVUwV0dERS1iUXZqMHd0UnFrQ3E2SFAzbm5lQ1I4U29MaHJFbWFvdVRTeFY4Wl9rSmc3RkpaQ2xwX0oz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOVDVzVTJNM2JuQ25sMThEaVZNOUNRd3FGT3RhVnFrZXZ2NDQ1YlluTVdhbVNUQnA1MGNESHRSWVUzbC1kRVh3OTR0emtlTG91cmRWeFJ5dk5zb3p2WFRyMEJUV3FNRnY1WHhRUU9WLTlJcmNyNXJZZFdoM0JoZjNpa3hjUXhMM0xrUDJab2VadkM5RWZYQ3lWZTVDdzg1akxJT2lxcDVNNzI0NG1hejdfdkUyTQ?oc=5</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -3706,21 +3924,37 @@
       <c r="M4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>-17.39</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-66.16</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Cochabamba, Cochabamba</t>
+        </is>
+      </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>noticia:r1uot6</t>
+          <t>noticia:167wlhz</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3730,56 +3964,56 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-24 20:00</t>
+          <t>2026-10-25 07:53</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1792886439000</v>
+        <v>1792929231000</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>vuelco deja heridos en ruta Oruro – Huanuni - La Patria Bolivia</t>
+          <t>¡A sacar el paraguas! Santa cruz amanece con lluvia, frío y complicaciones en el tránsito vehicular - Red Uno</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNNDQtMG1KT1lLWW5nem9Jbm5JWDZKNlRWZmFmRlBxWDlDeXlSWnJ5d2NsTlpxa0JIS25oVWVZOC1majZVbWhOVDIxR0dLOFlzY2VpVzVoVk1mQnF3dXVwLUFZVHc1UjlXZzF5T05CY3U0ZldLVkw1VzBTek5zanpjQW1xalltWHNiaXI3dTNR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOY1ZpYktLR3pUQXotUndVR3puUzVHbW1YTzNyUmJvUHB4Q2JmelRvOEdaRldOUm1xLVJnbGR5VWcxTjNEM3ZUYktCUWtVM0hKSjFuRGdpX0JxN0M5MVZBSG1aVURyVWktdmxwbUtRT19ydU5LdzNTZ2Zpb2ozdHlMUUdTVlAyVk4xODBnV0hyTXdVVndyNzV3VC1KMzFnV3lpcFFXSk9MdDZOTWlWakNwT1FnNDh6QVdjazVYZDVVMkdaLU0?oc=5</t>
         </is>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-17.97</v>
+        <v>-17.781</v>
       </c>
       <c r="O5" t="n">
-        <v>-67.11</v>
+        <v>-63.139</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>Santa Cruz, Santa Cruz</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -3789,19 +4023,19 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>noticia:1ytw450</t>
+          <t>noticia:bzr7eh</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3811,43 +4045,43 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-24 18:58</t>
+          <t>2026-10-25 07:09</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1792882686000</v>
+        <v>1792926572000</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>diarioelpueblo.com.pe</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>hidrológica</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>roja</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
+          <t>Alerta naranja por riesgo de desbordes de ríos - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNZ1U3bEVuaVdjVE1zSU9lOHJZTVRZLVZaemhldGNnT1JBWDJvbzdvM3paVVNhLUlyWHF2akNuSXJOLXdyTGRuejRlV1FuMjVkTjA3NmdRdmgtRWlUeTFBV1dEMzBvejBxaXZJdUZZWkRVTF9VLU5BcjFGZGFEQ09WWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNNGZKSDVaZkowWUFGSEUyTWR3d3dsc04waFBLLWUtcVpiTDYzbmNtYTN1RkFLbjAwN3dxT0xZc3pqc3REUXduZVltQ2Fud1BZLTh1bTNiTEJueVUwV0dERS1iUXZqMHd0UnFrQ3E2SFAzbm5lQ1I4U29MaHJFbWFvdVRTeFY4Wl9rSmc3RkpaQ2xwX0oz?oc=5</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -3866,7 +4100,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>noticia:1wcb22g</t>
+          <t>noticia:1fo4ig4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3876,43 +4110,43 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-24 17:47</t>
+          <t>2026-10-25 01:08</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1792878475000</v>
+        <v>1792904880000</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Mundo Bolivia</t>
+          <t>diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>hidrológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>roja</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Alerta naranja por ingreso de frente frío y desbordes de ríos en 6 departamentos - El Mundo Bolivia</t>
+          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPZW00RkxJSklTelNrS2hqczJDWHlwcENFX2lnSEUyTEFPaDFRQ2JvMUcyd3NfYjg0UE9ORGxHRzB4ZDh3U0hQQ1JSQlhsaUY4N3ByMUUxei1SaUZnNlp6T3hsLVdiMGhKaXhsV1FNSUNQMHlvQ19qdk56SEF0d2RXVFctS0VPT25kNGZCRDdvZ2dxU0VoUUJKU0ZBd0ZycFNEZFh0T3ZjOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQcmFrT3dwcEs0X3U2NWxnOGJwNnI2WHdWTGZYbzEyNnJzUWhkbU9TRWhfSlB5UkMwX2gyMmxYUmVNWmxNOVR6V0twRHpFMTVIYjBKbHQ2TXN2d2w5dkFpcWJCcUJMZldaX01sNWtQV2ZJOGpRVzR3NDVIU0pJc1BNVg?oc=5</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -3931,7 +4165,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>noticia:1c1ju1f</t>
+          <t>noticia:r1uot6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3941,15 +4175,15 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-24 17:02</t>
+          <t>2026-10-24 20:00</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1792875752000</v>
+        <v>1792886439000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>La Razón Digital Bolivia</t>
+          <t>La Patria Bolivia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3967,36 +4201,52 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a los Yungas deja siete heridos - La Razón Digital Bolivia</t>
+          <t>vuelco deja heridos en ruta Oruro – Huanuni - La Patria Bolivia</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPTGQwaVBfdG1JdVRMUTN4LVVvN0ppc3dreDJVVllDR3RmX0xpMzB4b0pvVTNSV1B6T0ZEWTdEZkNsRUdSNzhLaC1CWHN5WktNWk1nRWpTdVZiYjI3TlJlX2xlVTI5MjlRU2hiY1gteml4YWVFbDNPSVRBZmtITlQzbmhaUXVmcThRa2xsQTJIOXZuNzlSdm12MEdyOEZHdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNNDQtMG1KT1lLWW5nem9Jbm5JWDZKNlRWZmFmRlBxWDlDeXlSWnJ5d2NsTlpxa0JIS25oVWVZOC1majZVbWhOVDIxR0dLOFlzY2VpVzVoVk1mQnF3dXVwLUFZVHc1UjlXZzF5T05CY3U0ZldLVkw1VzBTek5zanpjQW1xalltWHNiaXI3dTNR?oc=5</t>
         </is>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>7</v>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-17.97</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-67.11</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Oruro, Oruro</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>noticia:14iwzop</t>
+          <t>noticia:1ytw450</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4006,15 +4256,15 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-24 13:40</t>
+          <t>2026-10-24 18:58</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1792863623000</v>
+        <v>1792882686000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>EL DÍA - Noticias de Bolivia para el mundo</t>
+          <t>diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -4023,29 +4273,29 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>roja</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a Mayaya deja siete heridos de la agrupación Los Chicos Fieles - EL DÍA - Noticias de Bolivia para el mundo</t>
+          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPeGd3VWpCWXJ0YTJIeDJLcktzWG1jdUh0TjFXb01wSTkxbHNXZU94VWNDMkxnTjlJZVdpbkprMEY2NE80RXYyUWxUQXVnbl9lUXR2b28zTEh6cTJLVEQ4TUNja2kzRlhadVBFZFVwV1U2TlhseXZMZ20zZTZiUFpWRjdCOWNBMHU5XzdMV3JqQjV4TEE3bHRMOXR6Nm55eHZUNnFHSDdVRk8zVkY4RkVsUUtUN0JYdkREWGZncmJ3ZWc2T1BuUm1ZLTlfcHVabFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNZ1U3bEVuaVdjVE1zSU9lOHJZTVRZLVZaemhldGNnT1JBWDJvbzdvM3paVVNhLUlyWHF2akNuSXJOLXdyTGRuejRlV1FuMjVkTjA3NmdRdmgtRWlUeTFBV1dEMzBvejBxaXZJdUZZWkRVTF9VLU5BcjFGZGFEQ09WWQ?oc=5</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -4061,7 +4311,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>noticia:1ukcn97</t>
+          <t>noticia:1wcb22g</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4071,46 +4321,46 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-24 13:26</t>
+          <t>2026-10-24 17:47</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1792862794000</v>
+        <v>1792878475000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Deber</t>
+          <t>El Mundo Bolivia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>hidrológica</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Esta es la lista preliminar de los heridos en el accidente del grupo 'Los chicos fieles', el conductor está grave - El Deber</t>
+          <t>Alerta naranja por ingreso de frente frío y desbordes de ríos en 6 departamentos - El Mundo Bolivia</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOczZKbFd1QzRpak92LXpPWXZXQXJObnBQTG9qRFBlUUV5dThMWXhzckFFUHAyb2thU1JwRmJDSEZfaEdTUXh1bjZvQWpYMGhfUno3cWZ4MGpldEpoQXhzSlVzTm5LLW9OcjB2MWRsdHQ2UlI2SjEtZ085ZTR5Z3pEVmtBTF9lc29Kd0RhaTRUWkM4eGZJNWhBSXZqWmxuNW10dlQwYW9mdzItcWZWTkU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPZW00RkxJSklTelNrS2hqczJDWHlwcENFX2lnSEUyTEFPaDFRQ2JvMUcyd3NfYjg0UE9ORGxHRzB4ZDh3U0hQQ1JSQlhsaUY4N3ByMUUxei1SaUZnNlp6T3hsLVdiMGhKaXhsV1FNSUNQMHlvQ19qdk56SEF0d2RXVFctS0VPT25kNGZCRDdvZ2dxU0VoUUJKU0ZBd0ZycFNEZFh0T3ZjOA?oc=5</t>
         </is>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -4126,7 +4376,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>noticia:2avehj</t>
+          <t>noticia:1c1ju1f</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4136,20 +4386,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-24 12:53</t>
+          <t>2026-10-24 17:02</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1792860813000</v>
+        <v>1792875752000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>La Razón Digital Bolivia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>climatológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -4162,52 +4412,36 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Sequía en Cochabamba: más de un centenar de cabezas de ganado murieron en el cono sur - Red Uno</t>
+          <t>Accidente en la carretera a los Yungas deja siete heridos - La Razón Digital Bolivia</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOOFQxc2Vzc0QwS19ydC13RkRPZnZQU3JkSTl5U3kzdUdMSldTcm5HVEhWRzZyN19CLUlwcUs4MW03Ui1obVBtdzQ3QWFQc1RKdzh3MXJ5QkpRS2pRNm50V1lVb09ScGJnaVVlemVfZlRsWjdObnRmR1FGMnlMMHAyc2pMandndy10T2twcWx6OFh4UHdvbVlFbllwME9WQ2pQVjNTQzBxeTg5YnF3bDREeHVDYXpObFFIaTZZQWtYUE12cGQ1ZGRhT0syNjVhZWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPTGQwaVBfdG1JdVRMUTN4LVVvN0ppc3dreDJVVllDR3RmX0xpMzB4b0pvVTNSV1B6T0ZEWTdEZkNsRUdSNzhLaC1CWHN5WktNWk1nRWpTdVZiYjI3TlJlX2xlVTI5MjlRU2hiY1gteml4YWVFbDNPSVRBZmtITlQzbmhaUXVmcThRa2xsQTJIOXZuNzlSdm12MEdyOEZHdw?oc=5</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>-17.39</v>
-      </c>
-      <c r="O11" t="n">
-        <v>-66.16</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Cochabamba, Cochabamba</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>noticia:1ksmg5u</t>
+          <t>noticia:14iwzop</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4217,15 +4451,15 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-24 11:43</t>
+          <t>2026-10-24 13:40</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1792856591000</v>
+        <v>1792863623000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
+          <t>EL DÍA - Noticias de Bolivia para el mundo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -4243,20 +4477,20 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Embarrancamiento deja heridos a integrantes de Los Chicos Fieles - La Patria Bolivia</t>
+          <t>Accidente en la carretera a Mayaya deja siete heridos de la agrupación Los Chicos Fieles - EL DÍA - Noticias de Bolivia para el mundo</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNeEFrOEtOMHZxMW42REFPU0x1MG5oQjlBMkJucWRLZ292alBXekJKeURBN3NLTVVadWI0OWF4UGtSVXBzTE01eWFSU1kyMUhNZ04zMWNMaUxnMDBBZ0EwTktXbjlaVTBUUmNqa3AwY19KNTU2LWh5LW9IVElVdTdnaHFPanJPd2FqMUxzaUhXZmVpYU1saGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPeGd3VWpCWXJ0YTJIeDJLcktzWG1jdUh0TjFXb01wSTkxbHNXZU94VWNDMkxnTjlJZVdpbkprMEY2NE80RXYyUWxUQXVnbl9lUXR2b28zTEh6cTJLVEQ4TUNja2kzRlhadVBFZFVwV1U2TlhseXZMZ20zZTZiUFpWRjdCOWNBMHU5XzdMV3JqQjV4TEE3bHRMOXR6Nm55eHZUNnFHSDdVRk8zVkY4RkVsUUtUN0JYdkREWGZncmJ3ZWc2T1BuUm1ZLTlfcHVabFE?oc=5</t>
         </is>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -4272,7 +4506,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>noticia:mlyqgd</t>
+          <t>noticia:1ukcn97</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4282,15 +4516,15 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-24 11:30</t>
+          <t>2026-10-24 13:26</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1792855818000</v>
+        <v>1792862794000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Opinión Bolivia</t>
+          <t>El Deber</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -4308,20 +4542,20 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a Mayaya deja siete heridos de la agrupación Los Chicos Fieles - Opinión Bolivia</t>
+          <t>Esta es la lista preliminar de los heridos en el accidente del grupo 'Los chicos fieles', el conductor está grave - El Deber</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYjNxaHg3YllRRTJYdFd1clAtUlROSGlFNVg5eUVZUGJoOEZ4MWM5QU5WQm1YTDc4NXc3SjhWMUw0TkZfSHlMLUQ1bmpTME1Kb1JaM0ExamFHYTd3VlU4MXRWdTZ1bzh1SGYtbGE1a3dBaG93bjg1OGc0S0JfRE43c3dVMVltN0dQQzNhQUNhM0FjVUNRUDRSamlJYlk2dEJpUTBuY2hBcTFucTVRN0ZtYnc5bzdmTV9LQm1uVUxaZS1tUE9IejhBVDRCdU_SAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOczZKbFd1QzRpak92LXpPWXZXQXJObnBQTG9qRFBlUUV5dThMWXhzckFFUHAyb2thU1JwRmJDSEZfaEdTUXh1bjZvQWpYMGhfUno3cWZ4MGpldEpoQXhzSlVzTm5LLW9OcjB2MWRsdHQ2UlI2SjEtZ085ZTR5Z3pEVmtBTF9lc29Kd0RhaTRUWkM4eGZJNWhBSXZqWmxuNW10dlQwYW9mdzItcWZWTkU0?oc=5</t>
         </is>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -4337,7 +4571,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>noticia:irf4jl</t>
+          <t>noticia:2avehj</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4347,20 +4581,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-24 11:30</t>
+          <t>2026-10-24 12:53</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1792855818000</v>
+        <v>1792860813000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Opinión Bolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>climatológica</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -4373,36 +4607,52 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a Mayaya deja siete heridos de la agrupación Los Chicos Fieles - Opinión Bolivia</t>
+          <t>Sequía en Cochabamba: más de un centenar de cabezas de ganado murieron en el cono sur - Red Uno</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNMXlMNXFWSWhhWWNDRFFKMncwS2JGWm0tWlJCd2x2RjZhdFhEQ0lBcVlFSS1WRVYxMEVJTWRHcTY3M0stdWhGdnVPRU13X2MwSVRWX25xVUQxa0R6Z1pqQ2dfY0VjUmw2aXFoWFNVNk15N2dBOENZLWlGSWJfMW0zejVoZ3ZwVHVQV1MzbzlnUlpRcWIxMHZxdkItZTc0QmMyRnBmSVRtVnZ5Y3gtdVpYNXFwcGdadGVCU3dRZ3EwOTdiWHU4OXJRdEFoNi1HcnA1U0HSAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOOFQxc2Vzc0QwS19ydC13RkRPZnZQU3JkSTl5U3kzdUdMSldTcm5HVEhWRzZyN19CLUlwcUs4MW03Ui1obVBtdzQ3QWFQc1RKdzh3MXJ5QkpRS2pRNm50V1lVb09ScGJnaVVlemVfZlRsWjdObnRmR1FGMnlMMHAyc2pMandndy10T2twcWx6OFh4UHdvbVlFbllwME9WQ2pQVjNTQzBxeTg5YnF3bDREeHVDYXpObFFIaTZZQWtYUE12cGQ1ZGRhT0syNjVhZWs?oc=5</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>7</v>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-17.39</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-66.16</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Cochabamba, Cochabamba</t>
+        </is>
+      </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>noticia:1g006zh</t>
+          <t>noticia:1ksmg5u</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4412,15 +4662,15 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-24 11:25</t>
+          <t>2026-10-24 11:43</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1792855522000</v>
+        <v>1792856591000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>El Potosí</t>
+          <t>La Patria Bolivia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -4438,75 +4688,59 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a Mayaya deja siete heridos del grupo Los Chicos Fieles - El Potosí</t>
+          <t>Embarrancamiento deja heridos a integrantes de Los Chicos Fieles - La Patria Bolivia</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTC10eC1qSm1WRlY2YzA3VEJqOG1LUkx6bE9PdFYwTFBZMGFjU0RMYXliRkhXcTJHRlVzb0Y4QUU0WWJDQ1plS2NZamZ1YmFadE5qY3g4UE5aYVAwamtCUUNZaDB2YWJTdWRKS3R4a0hHUjVobUl0Y1dYZ2JPczAwak5kN1hjUEwwM1NtUDVWbnAzWTdnRng3RjFValFVVlZPdVZnWFlUODhPOE5aMTROQzVKVjVRS2VoaTlaQnBiUGRTNFk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNeEFrOEtOMHZxMW42REFPU0x1MG5oQjlBMkJucWRLZ292alBXekJKeURBN3NLTVVadWI0OWF4UGtSVXBzTE01eWFSU1kyMUhNZ04zMWNMaUxnMDBBZ0EwTktXbjlaVTBUUmNqa3AwY19KNTU2LWh5LW9IVElVdTdnaHFPanJPd2FqMUxzaUhXZmVpYU1saGc?oc=5</t>
         </is>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>7</v>
-      </c>
-      <c r="N15" t="n">
-        <v>-19.58</v>
-      </c>
-      <c r="O15" t="n">
-        <v>-65.75</v>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Potosí, Potosí</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>clima:Potosí:2026-10-24:viento:1</t>
+          <t>noticia:mlyqgd</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-24 10:55</t>
+          <t>2026-10-24 11:30</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1792853727284</v>
+        <v>1792855818000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>Opinión Bolivia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4519,56 +4753,36 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Potosí 2026-10-24: 60.5 km/h de ráfagas pronosticadas</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
-        </is>
-      </c>
+          <t>Accidente en la carretera a Mayaya deja siete heridos de la agrupación Los Chicos Fieles - Opinión Bolivia</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYjNxaHg3YllRRTJYdFd1clAtUlROSGlFNVg5eUVZUGJoOEZ4MWM5QU5WQm1YTDc4NXc3SjhWMUw0TkZfSHlMLUQ1bmpTME1Kb1JaM0ExamFHYTd3VlU4MXRWdTZ1bzh1SGYtbGE1a3dBaG93bjg1OGc0S0JfRE43c3dVMVltN0dQQzNhQUNhM0FjVUNRUDRSamlJYlk2dEJpUTBuY2hBcTFucTVRN0ZtYnc5bzdmTV9LQm1uVUxaZS1tUE9IejhBVDRCdU_SAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
         </is>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-19.58</v>
-      </c>
-      <c r="O16" t="n">
-        <v>-65.75</v>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>capital (pronóstico puntual)</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>noticia:1ax0bpy</t>
+          <t>noticia:irf4jl</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4578,96 +4792,80 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-24 10:32</t>
+          <t>2026-10-24 11:30</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1792852364000</v>
+        <v>1792855818000</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Que Pasa Salta</t>
+          <t>Opinión Bolivia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Creció el Bermejo tras la tormenta: así está el puerto de chalanas en este momento - Que Pasa Salta</t>
+          <t>Accidente en la carretera a Mayaya deja siete heridos de la agrupación Los Chicos Fieles - Opinión Bolivia</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVld9IBfkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVldw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNMXlMNXFWSWhhWWNDRFFKMncwS2JGWm0tWlJCd2x2RjZhdFhEQ0lBcVlFSS1WRVYxMEVJTWRHcTY3M0stdWhGdnVPRU13X2MwSVRWX25xVUQxa0R6Z1pqQ2dfY0VjUmw2aXFoWFNVNk15N2dBOENZLWlGSWJfMW0zejVoZ3ZwVHVQV1MzbzlnUlpRcWIxMHZxdkItZTc0QmMyRnBmSVRtVnZ5Y3gtdVpYNXFwcGdadGVCU3dRZ3EwOTdiWHU4OXJRdEFoNi1HcnA1U0HSAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
         </is>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-22.721</v>
-      </c>
-      <c r="O17" t="n">
-        <v>-64.32599999999999</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Bermejo, Tarija</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>Tarija</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>Bermejo</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>gdacs:WF1033142:0</t>
+          <t>noticia:1g006zh</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>gdacs</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-24 07:06</t>
+          <t>2026-10-24 11:25</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1792839995000</v>
+        <v>1792855522000</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>GDACS</t>
+          <t>El Potosí</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -4676,107 +4874,107 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Green forest fire notification in Bolivia</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>On 21/10/2026, a forest fire started in Bolivia, until 24/10/2026.</t>
-        </is>
-      </c>
+          <t>Accidente en la carretera a Mayaya deja siete heridos del grupo Los Chicos Fieles - El Potosí</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>http://www.gdacs.org/report.aspx?eventtype=WF&amp;eventid=1033142</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTC10eC1qSm1WRlY2YzA3VEJqOG1LUkx6bE9PdFYwTFBZMGFjU0RMYXliRkhXcTJHRlVzb0Y4QUU0WWJDQ1plS2NZamZ1YmFadE5qY3g4UE5aYVAwamtCUUNZaDB2YWJTdWRKS3R4a0hHUjVobUl0Y1dYZ2JPczAwak5kN1hjUEwwM1NtUDVWbnAzWTdnRng3RjFValFVVlZPdVZnWFlUODhPOE5aMTROQzVKVjVRS2VoaTlaQnBiUGRTNFk?oc=5</t>
         </is>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N18" t="n">
-        <v>-13.06332</v>
+        <v>-19.58</v>
       </c>
       <c r="O18" t="n">
-        <v>-67.66426</v>
+        <v>-65.75</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Potosí, Potosí</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>coordenada de la fuente</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>Ixiamas</t>
+          <t>Potosí</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>noticia:1shhqva</t>
+          <t>clima:Potosí:2026-10-24:viento:1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-24 06:33</t>
+          <t>2026-10-24 10:55</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1792838034000</v>
+        <v>1792853727284</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+          <t>Potosí 2026-10-24: 60.5 km/h de ráfagas pronosticadas</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQYzB6N082XzFRRnVtcDVmUkYyWjcxUzV2Z3Frd1I0WDNXSnZtY0QzOU1PUkNLMktVT1Vra2FSeXhxZDRuOFZYZjFwejl6ejJTbWY2MGJuSGN3ZHdrdG5JUkgzSXBkbDYtaHlackY3OVFuNWdLcFNpdWNHRU9vNGdoVWx2ODFVdzJXYUxnM0tUcjJvZmc?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -4786,54 +4984,54 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-17.97</v>
+        <v>-19.58</v>
       </c>
       <c r="O19" t="n">
-        <v>-67.11</v>
+        <v>-65.75</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
+          <t>capital (pronóstico puntual)</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Potosí</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>clima:Potosí:2026-10-25:viento:1</t>
+          <t>noticia:1ax0bpy</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-24 02:55</t>
+          <t>2026-10-24 10:32</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1792824927736</v>
+        <v>1792852364000</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>Que Pasa Salta</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4842,26 +5040,22 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Potosí 2026-10-25: 60.5 km/h de ráfagas pronosticadas</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
-        </is>
-      </c>
+          <t>Creció el Bermejo tras la tormenta: así está el puerto de chalanas en este momento - Que Pasa Salta</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVld9IBfkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVldw?oc=5</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -4871,54 +5065,54 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-19.58</v>
+        <v>-22.721</v>
       </c>
       <c r="O20" t="n">
-        <v>-65.75</v>
+        <v>-64.32599999999999</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Bermejo, Tarija</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>capital (pronóstico puntual)</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Tarija</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Bermejo</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>noticia:mz6q0s</t>
+          <t>gdacs:WF1033142:0</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>gdacs</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-23 23:09</t>
+          <t>2026-10-24 07:06</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1792811349000</v>
+        <v>1792839995000</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>GDACS</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4927,45 +5121,65 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Revelan lista preliminar de heridos tras accidente de Los Chicos Fieles - Red Uno</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+          <t>Green forest fire notification in Bolivia</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>On 21/10/2026, a forest fire started in Bolivia, until 24/10/2026.</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPczBQcnE2SzFGMXc3b1lsTkNxVWRmS3Vnb01xOTV2WmVva3J2RVlteWpHZ3VJS2dNWGV5NW5FX3ZncnVKTEVDTGpBRndTU1FxeWxtaS1fb1FscGxXMWNXUE9zbHdob1AxVFl1eHB5OU1yUnNoOXJ6U21oVG9PVDA1ak1xQl9hUlB4V0RaQXJqZENGUm8zMUJEY3J0WW5ENE5ObWJLNmpWN0RkSmFJbnZUZGR5UFRPd3QyUFY4WQ?oc=5</t>
+          <t>http://www.gdacs.org/report.aspx?eventtype=WF&amp;eventid=1033142</t>
         </is>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-13.06332</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-67.66426</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
+          <t>coordenada de la fuente</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>La Paz</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Ixiamas</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>noticia:1uil931</t>
+          <t>noticia:1shhqva</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4975,56 +5189,56 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-23 22:49</t>
+          <t>2026-10-24 06:33</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1792810149000</v>
+        <v>1792838034000</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>El Deber</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Accidente de tránsito en la ruta hacia Alto Beni deja varios heridos - El Deber</t>
+          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQakFJRmx3RlJEMkVHU0pxWXZ2ZU1ib04tZy1yeTB2OGhrYk9CU3pMaDVpRThNZktZMS14UzA2Y1VIcEQtZDg3cEU2SmlzQnBmUVVvM0ZNYzZWNExWUXQ3aHpnd3lqOHFVV3pNbDRLS1NQNGtwb2RjSFpleHJkOG5zSXVtWjVIS1dLejNybktRWTJVZXh3WkFUQVE5T2tMdFdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQYzB6N082XzFRRnVtcDVmUkYyWjcxUzV2Z3Frd1I0WDNXSnZtY0QzOU1PUkNLMktVT1Vra2FSeXhxZDRuOFZYZjFwejl6ejJTbWY2MGJuSGN3ZHdrdG5JUkgzSXBkbDYtaHlackY3OVFuNWdLcFNpdWNHRU9vNGdoVWx2ODFVdzJXYUxnM0tUcjJvZmc?oc=5</t>
         </is>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>-15.578</v>
+        <v>-17.97</v>
       </c>
       <c r="O22" t="n">
-        <v>-67.44</v>
+        <v>-67.11</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Alto Beni, La Paz</t>
+          <t>Oruro, Oruro</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -5034,42 +5248,42 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Oruro</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>Alto Beni</t>
+          <t>Oruro</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>noticia:1tliu4i</t>
+          <t>clima:Potosí:2026-10-25:viento:1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-23 22:18</t>
+          <t>2026-10-24 02:55</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1792808330000</v>
+        <v>1792824927736</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>El Deber</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5082,52 +5296,56 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Accidente de tránsito en la ruta hacia Alto Beni deja varios heridos - El Deber</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
+          <t>Potosí 2026-10-25: 60.5 km/h de ráfagas pronosticadas</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQMF9BNnUzLURKNGRMUUJ1VXVRSXNnMlBsQnVXOG0tRlFtY3pvRDNPQmNJMWN2RzJVaWdoWndmcHFnTkZFZnJxRkZtMThYYWlwN09ueUgtei1pSE1hZ2FtSzN6elY4VXJHbzFxdll0eWh0ZkxwQkQ1SDZ5b0E3MlVENGZEWGZHUGlwVG4wd2x3OFNEMVpibnFr?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>-15.578</v>
+        <v>-19.58</v>
       </c>
       <c r="O23" t="n">
-        <v>-67.44</v>
+        <v>-65.75</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Alto Beni, La Paz</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
+          <t>capital (pronóstico puntual)</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Alto Beni</t>
+          <t>Potosí</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>noticia:1twc9ul</t>
+          <t>noticia:mz6q0s</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5137,15 +5355,15 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-23 22:16</t>
+          <t>2026-10-23 23:09</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1792808192000</v>
+        <v>1792811349000</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>El Deber</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -5163,13 +5381,13 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Accidente de tránsito en la ruta hacia Alto Beni deja varios heridos - El Deber</t>
+          <t>Revelan lista preliminar de heridos tras accidente de Los Chicos Fieles - Red Uno</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNbmwzSnd6c2tFMXBWY0tiemJqRm5CNllOT2p1U0FhdW5QNGFBVXlSZVM1ak5jNGZvcXNVaUQzN3ZQQTlPbmVjQ2Y5RFl2dWVLeUN5NUFodDF0alEyZWlmOHFZWkVVbjdQbkl3ZWtmS25wQWM2TmRZZDBGM2xlS0ZhUzAweXRmcmhVWGY5dV9CUnFBNGtWZHZDSWVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPczBQcnE2SzFGMXc3b1lsTkNxVWRmS3Vnb01xOTV2WmVva3J2RVlteWpHZ3VJS2dNWGV5NW5FX3ZncnVKTEVDTGpBRndTU1FxeWxtaS1fb1FscGxXMWNXUE9zbHdob1AxVFl1eHB5OU1yUnNoOXJ6U21oVG9PVDA1ak1xQl9hUlB4V0RaQXJqZENGUm8zMUJEY3J0WW5ENE5ObWJLNmpWN0RkSmFJbnZUZGR5UFRPd3QyUFY4WQ?oc=5</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -5178,37 +5396,21 @@
       <c r="M24" t="n">
         <v>1</v>
       </c>
-      <c r="N24" t="n">
-        <v>-15.578</v>
-      </c>
-      <c r="O24" t="n">
-        <v>-67.44</v>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Alto Beni, La Paz</t>
-        </is>
-      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>La Paz</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>Alto Beni</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>noticia:1dygpkp</t>
+          <t>noticia:1uil931</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5218,15 +5420,15 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-23 21:39</t>
+          <t>2026-10-23 22:49</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1792805983000</v>
+        <v>1792810149000</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>El Deber</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5235,39 +5437,39 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>(Video) Así rescataron a uno de los integrantes de Los Chicos Fieles tras accidente en Caranavi - Red Uno</t>
+          <t>Accidente de tránsito en la ruta hacia Alto Beni deja varios heridos - El Deber</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOdTVUZUQxVTdvYTdONDQxVlhUTzBOS2hKLW1rS1NUcmRYRnlCVlhIcHZlSjdsaktkQm5CWkFYa3lDQkxnMlh0b3prX0lha1BtbW1qS1VuYnNiX3FiZkYyNDJDR0tqZ0pKMU5TeC04SXV4UUJOTUlPUTB6ek01bzUxTUsydjZqZzI3S3ZLUnRWSUFUVk44WEpKUl9rbzRLb2IwYl9sLVlrYmt5d2ZHNUtGd3lRNnYzMlhuMkJOZW1XSUl2N1BxZWpHbm5XTDJhRUtnR190QWQ1TDlTUVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQakFJRmx3RlJEMkVHU0pxWXZ2ZU1ib04tZy1yeTB2OGhrYk9CU3pMaDVpRThNZktZMS14UzA2Y1VIcEQtZDg3cEU2SmlzQnBmUVVvM0ZNYzZWNExWUXQ3aHpnd3lqOHFVV3pNbDRLS1NQNGtwb2RjSFpleHJkOG5zSXVtWjVIS1dLejNybktRWTJVZXh3WkFUQVE5T2tMdFdn?oc=5</t>
         </is>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" t="n">
-        <v>-15.813</v>
+        <v>-15.578</v>
       </c>
       <c r="O25" t="n">
-        <v>-67.46299999999999</v>
+        <v>-67.44</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Caranavi, La Paz</t>
+          <t>Alto Beni, La Paz</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -5282,14 +5484,14 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>Caranavi</t>
+          <t>Alto Beni</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>noticia:3dv7b0</t>
+          <t>noticia:1tliu4i</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5299,15 +5501,15 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-23 21:35</t>
+          <t>2026-10-23 22:18</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1792805700000</v>
+        <v>1792808330000</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FmBolivia</t>
+          <t>El Deber</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5325,13 +5527,13 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Accidente en Caranavi: vehículo de Los Chicos Fieles cae a un barranco y deja varios heridos - FmBolivia</t>
+          <t>Accidente de tránsito en la ruta hacia Alto Beni deja varios heridos - El Deber</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNcE1KaHZyUTJCSElxRU9nVzdhTnczWjJGTEhFMEs0bHp2cUdFeHd3VTB0NmVFcjdEN1dsZDZLY2k1ZFFUWkhKV19PU3V2czNyamh1ZE9YajVSVF8xczF6OFhZcWFvYV9EcWg4ZDNCb2p3enhXbFpRYnJMdGdaTXNrWUZSYVhKNTVicWlCLTJ5OE05Z1BvNEx1eEloUk5qTGN3ZHNzbzZWSVljbnRmSERJUWdxRDc0MjJxMGtycWJaaVhXQUUxVUlaWVZLOWE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQMF9BNnUzLURKNGRMUUJ1VXVRSXNnMlBsQnVXOG0tRlFtY3pvRDNPQmNJMWN2RzJVaWdoWndmcHFnTkZFZnJxRkZtMThYYWlwN09ueUgtei1pSE1hZ2FtSzN6elY4VXJHbzFxdll0eWh0ZkxwQkQ1SDZ5b0E3MlVENGZEWGZHUGlwVG4wd2x3OFNEMVpibnFr?oc=5</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -5341,14 +5543,14 @@
         <v>1</v>
       </c>
       <c r="N26" t="n">
-        <v>-15.813</v>
+        <v>-15.578</v>
       </c>
       <c r="O26" t="n">
-        <v>-67.46299999999999</v>
+        <v>-67.44</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Caranavi, La Paz</t>
+          <t>Alto Beni, La Paz</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -5363,37 +5565,37 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Caranavi</t>
+          <t>Alto Beni</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-24:viento:1</t>
+          <t>noticia:1twc9ul</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-10-23 20:55</t>
+          <t>2026-10-23 22:16</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1792803329663</v>
+        <v>1792808192000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>El Deber</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5406,56 +5608,52 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-24: 78.1 km/h de ráfagas pronosticadas</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
-        </is>
-      </c>
+          <t>Accidente de tránsito en la ruta hacia Alto Beni deja varios heridos - El Deber</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNbmwzSnd6c2tFMXBWY0tiemJqRm5CNllOT2p1U0FhdW5QNGFBVXlSZVM1ak5jNGZvcXNVaUQzN3ZQQTlPbmVjQ2Y5RFl2dWVLeUN5NUFodDF0alEyZWlmOHFZWkVVbjdQbkl3ZWtmS25wQWM2TmRZZDBGM2xlS0ZhUzAweXRmcmhVWGY5dV9CUnFBNGtWZHZDSWVB?oc=5</t>
         </is>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" t="n">
-        <v>-17.78</v>
+        <v>-15.578</v>
       </c>
       <c r="O27" t="n">
-        <v>-63.18</v>
+        <v>-67.44</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Alto Beni, La Paz</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>capital (pronóstico puntual)</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Alto Beni</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>noticia:rabz5p</t>
+          <t>noticia:1dygpkp</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5465,11 +5663,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-10-23 20:44</t>
+          <t>2026-10-23 21:39</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1792802686000</v>
+        <v>1792805983000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -5478,7 +5676,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5491,13 +5689,13 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Tome previsiones: se pronostican lluvias y ambiente caluroso para este fin de semana en Cochabamba - Red Uno</t>
+          <t>(Video) Así rescataron a uno de los integrantes de Los Chicos Fieles tras accidente en Caranavi - Red Uno</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTlU5NVFpY1RheTN5ZE1IbG5VYTh2Sk5hZHpHeWI3LVdnSFg2cFJFdnBCVkxiUjNKcUgyUW16SWxpMXFkMHdad2xFN043bklJeG1iQ0V1V3hBZk1Ga3NscjdPVWUySmt4bDNTdWlmSUdOMmNlZ2hkSWZFMmk4VGs0Nm9TcnRCTDhINmtnQU9zZDBUY05HcWpxN3FOX3N1dmVJblE0MGc5di1Ma1N2dGNxOUtoV1MzNnl1OXpRaTZ2UGxMc3RDWndubHVQNUd0eVROMGR2OGxVemtOaEc4bTNRaA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOdTVUZUQxVTdvYTdONDQxVlhUTzBOS2hKLW1rS1NUcmRYRnlCVlhIcHZlSjdsaktkQm5CWkFYa3lDQkxnMlh0b3prX0lha1BtbW1qS1VuYnNiX3FiZkYyNDJDR0tqZ0pKMU5TeC04SXV4UUJOTUlPUTB6ek01bzUxTUsydjZqZzI3S3ZLUnRWSUFUVk44WEpKUl9rbzRLb2IwYl9sLVlrYmt5d2ZHNUtGd3lRNnYzMlhuMkJOZW1XSUl2N1BxZWpHbm5XTDJhRUtnR190QWQ1TDlTUVk?oc=5</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -5507,14 +5705,14 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>-17.39</v>
+        <v>-15.813</v>
       </c>
       <c r="O28" t="n">
-        <v>-66.16</v>
+        <v>-67.46299999999999</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Cochabamba, Cochabamba</t>
+          <t>Caranavi, La Paz</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -5524,19 +5722,19 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Caranavi</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>noticia:1jfk053</t>
+          <t>noticia:3dv7b0</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5546,20 +5744,20 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-10-23 19:08</t>
+          <t>2026-10-23 21:35</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1792796931000</v>
+        <v>1792805700000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>FmBolivia</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>climatológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5572,30 +5770,30 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Sequía en Pasorapa: el ganado muere por falta de agua y alistan declaratoria de desastre - Red Uno</t>
+          <t>Accidente en Caranavi: vehículo de Los Chicos Fieles cae a un barranco y deja varios heridos - FmBolivia</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNQVhTWE8zdE1BQ3lueWJPeV9wUDNsSmJpS0NJTWppMUY4QmlQSUFHVjRORmtrVHQ3MHB0T1pyS25PamxnY0hBQUtzOVRvSUNaUkdGb1RWSGl4dFA4Z3VINVpQTk1pZUpDdUIyUU5hZS1oNGhBa1RWcFhScVMwVTFrVlJaOFQ4OWFqRWVUZ051bHVJTlMxRTBhRFVLUEV2dTZFdDgtRkxJM3VvN3YzUWJfVk41ZWR5U1JoNmx0WFFkMmNTWGVleGNIQlNxWUJzdHIxSWtz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNcE1KaHZyUTJCSElxRU9nVzdhTnczWjJGTEhFMEs0bHp2cUdFeHd3VTB0NmVFcjdEN1dsZDZLY2k1ZFFUWkhKV19PU3V2czNyamh1ZE9YajVSVF8xczF6OFhZcWFvYV9EcWg4ZDNCb2p3enhXbFpRYnJMdGdaTXNrWUZSYVhKNTVicWlCLTJ5OE05Z1BvNEx1eEloUk5qTGN3ZHNzbzZWSVljbnRmSERJUWdxRDc0MjJxMGtycWJaaVhXQUUxVUlaWVZLOWE?oc=5</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N29" t="n">
-        <v>-18.38</v>
+        <v>-15.813</v>
       </c>
       <c r="O29" t="n">
-        <v>-64.649</v>
+        <v>-67.46299999999999</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Pasorapa, Cochabamba</t>
+          <t>Caranavi, La Paz</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -5605,61 +5803,65 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>Pasorapa</t>
+          <t>Caranavi</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>noticia:ix3l8o</t>
+          <t>clima:Santa Cruz:2026-10-24:viento:1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-10-23 18:25</t>
+          <t>2026-10-23 20:55</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1792794310000</v>
+        <v>1792803329663</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Visión 360</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Oruro evalúa suspender clases presenciales por más de 200 casos de Coxsackie - Visión 360</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
+          <t>Santa Cruz 2026-10-24: 78.1 km/h de ráfagas pronosticadas</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0c9IBywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0cw?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L30" t="n">
@@ -5669,36 +5871,36 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>-17.97</v>
+        <v>-17.78</v>
       </c>
       <c r="O30" t="n">
-        <v>-67.11</v>
+        <v>-63.18</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
+          <t>capital (pronóstico puntual)</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>noticia:1xqv9m7</t>
+          <t>noticia:rabz5p</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5708,62 +5910,78 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-10-23 18:09</t>
+          <t>2026-10-23 20:44</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1792793370000</v>
+        <v>1792802686000</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>El Diario del centro del país</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Tres heridos en tremendo choque cerca de Oncativo - El Diario del centro del país</t>
+          <t>Tome previsiones: se pronostican lluvias y ambiente caluroso para este fin de semana en Cochabamba - Red Uno</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZERhbTJMQUJVb3hmZFlSZmRGZkdBLWdFTGJVQzdqZkE4aGhhWmdQZ2JDRW1ndkJLWU90VTZ6Ti1JOUZzcFZfcE1zbkRHU1B3YTF4UkVzdllFa1p3SUlObURGamF0Vm9kc3dPLTZVWFJ4NWZZQmlySElPNHhZTnRGNGNZUWw2ZlI1eVBEQkNGNEhLWTNiLWJLUS0xYjA0UWRhc0d6bVN4aVVLSVdsQWlpMUZYdWw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTlU5NVFpY1RheTN5ZE1IbG5VYTh2Sk5hZHpHeWI3LVdnSFg2cFJFdnBCVkxiUjNKcUgyUW16SWxpMXFkMHdad2xFN043bklJeG1iQ0V1V3hBZk1Ga3NscjdPVWUySmt4bDNTdWlmSUdOMmNlZ2hkSWZFMmk4VGs0Nm9TcnRCTDhINmtnQU9zZDBUY05HcWpxN3FOX3N1dmVJblE0MGc5di1Ma1N2dGNxOUtoV1MzNnl1OXpRaTZ2UGxMc3RDWndubHVQNUd0eVROMGR2OGxVemtOaEc4bTNRaA?oc=5</t>
         </is>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3</v>
-      </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-17.39</v>
+      </c>
+      <c r="O31" t="n">
+        <v>-66.16</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Cochabamba, Cochabamba</t>
+        </is>
+      </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>noticia:1wuregl</t>
+          <t>noticia:1jfk053</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5773,56 +5991,56 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-23 15:39</t>
+          <t>2026-10-23 19:08</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1792784340000</v>
+        <v>1792796931000</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>FmBolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>hidrológica</t>
+          <t>climatológica</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Intensas lluvias inundan La Paz y activan alertas por el riesgo de desborde de ríos - FmBolivia</t>
+          <t>Sequía en Pasorapa: el ganado muere por falta de agua y alistan declaratoria de desastre - Red Uno</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPZm85aHphekQ4U3BZZkp1ZkF6ZVdSUHgtZmltS1FxUUgza1AwcndWWDJZOWctT0RiVmVabmg5SG42NnJWMlJMMnBlYTlYaVdSb09sR0dnVDdpT29faTdiaDUtZElJdlQ3eTdjR2VsWjlta1FOS1U2Vm1vV3JwWkpvbEw1ZUR3akgwQTZnQnVENjJtVkQtVUpKVEJTeWNJSE1CaEFKa2VqMmZXbWk3ekR4ZWpmZ1Z3elFQaWNaNFJuMXA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNQVhTWE8zdE1BQ3lueWJPeV9wUDNsSmJpS0NJTWppMUY4QmlQSUFHVjRORmtrVHQ3MHB0T1pyS25PamxnY0hBQUtzOVRvSUNaUkdGb1RWSGl4dFA4Z3VINVpQTk1pZUpDdUIyUU5hZS1oNGhBa1RWcFhScVMwVTFrVlJaOFQ4OWFqRWVUZ051bHVJTlMxRTBhRFVLUEV2dTZFdDgtRkxJM3VvN3YzUWJfVk41ZWR5U1JoNmx0WFFkMmNTWGVleGNIQlNxWUJzdHIxSWtz?oc=5</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>-16.169</v>
+        <v>-18.38</v>
       </c>
       <c r="O32" t="n">
-        <v>-68.09</v>
+        <v>-64.649</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>La Paz, La Paz</t>
+          <t>Pasorapa, Cochabamba</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -5832,19 +6050,19 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>Nuestra Señora de La Paz</t>
+          <t>Pasorapa</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>noticia:1570kkf</t>
+          <t>noticia:ix3l8o</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5854,15 +6072,15 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-23 15:28</t>
+          <t>2026-10-23 18:25</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1792783705000</v>
+        <v>1792794310000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>Visión 360</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -5880,13 +6098,13 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>¿Se suspenden las clases en Oruro? Más de 200 casos de Coxsackie activan evaluaciones - Red Uno</t>
+          <t>Oruro evalúa suspender clases presenciales por más de 200 casos de Coxsackie - Visión 360</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNMFdHaVpKRmMyOENDYm16UXJPenVSQnpmTE94bDc4UFhqakluMUdvZjAwamUxT3BVWUpJQm8xVHBWengxQmhWM1hjU3d2YXFrLXpVU2VrZDJiMXZLMlQ5bGxGOHFETFhYM0s2RjlUTlhkd0g2eXQweDFHaTlKNGNMUlJfOWg2a0JjTklXUWZKc1BmUXZuZFZ2MF9fV2lEYUY4LXNiNmk3cF9FNjVtTl9GWFotT2ltS0xXTnM1dENvSU9kbFRMalFrYVdXOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0c9IBywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0cw?oc=5</t>
         </is>
       </c>
       <c r="L33" t="n">
@@ -5925,7 +6143,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>noticia:1nzu2o8</t>
+          <t>noticia:1xqv9m7</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5935,46 +6153,46 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-10-23 15:20</t>
+          <t>2026-10-23 18:09</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1792783236000</v>
+        <v>1792793370000</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>El Diario del centro del país</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>hidrológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Alerta naranja por posibles desbordes en tres departamentos (15:20) - El Diario - Bolivia</t>
+          <t>Tres heridos en tremendo choque cerca de Oncativo - El Diario del centro del país</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPTnBESV9OODZhNjY3T2M2X2NZcmk4clI0eFZsd3VLMVRwaUlSdF9wanZyVGxDNUlNTm5wbGpLN1lvX09mNGxFVkpIZDNGdi1pNDdfSGlESThfeVloQzJsNUMyNUpWUDhzTVJiYWJpNkQ1RHliRWljZlp3SlhtZ2FhU0pvV0syUmZIejJZWHlRdTBOTG4zaTc5cEsycW9IcEx2SkQtN01Gendlb1VR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZERhbTJMQUJVb3hmZFlSZmRGZkdBLWdFTGJVQzdqZkE4aGhhWmdQZ2JDRW1ndkJLWU90VTZ6Ti1JOUZzcFZfcE1zbkRHU1B3YTF4UkVzdllFa1p3SUlObURGamF0Vm9kc3dPLTZVWFJ4NWZZQmlySElPNHhZTnRGNGNZUWw2ZlI1eVBEQkNGNEhLWTNiLWJLUS0xYjA0UWRhc0d6bVN4aVVLSVdsQWlpMUZYdWw?oc=5</t>
         </is>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
@@ -5990,7 +6208,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>noticia:1itd1r7</t>
+          <t>noticia:1wuregl</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -6000,20 +6218,20 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-23 15:01</t>
+          <t>2026-10-23 15:39</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1792782098000</v>
+        <v>1792784340000</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>eju.tv</t>
+          <t>FmBolivia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>hidrológica</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6026,13 +6244,13 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Intensa lluvia y granizada en La Paz inundan vías y elevan el nivel de los ríos - eju.tv</t>
+          <t>Intensas lluvias inundan La Paz y activan alertas por el riesgo de desborde de ríos - FmBolivia</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNWU9QWElKQXEyN3UxVm4xbzJzbEJ1TU1NTHZlRUp6YndmeU9GQnJKcTluVEJ2ZHQ5cGp3aWhlMUd5ektWQlBpUVNmZnZuRnJwMXlydzAzX0FBVnY5UDMzQTBkWVRNRUNJSlRvX3MyQVhMcEhIMW9WSUpXckVSd0RJWk1KMFBKWmJNU3diQVlEN1Y5aVV6eVBaZXpOMnFIWWxaMlRlY0ZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPZm85aHphekQ4U3BZZkp1ZkF6ZVdSUHgtZmltS1FxUUgza1AwcndWWDJZOWctT0RiVmVabmg5SG42NnJWMlJMMnBlYTlYaVdSb09sR0dnVDdpT29faTdiaDUtZElJdlQ3eTdjR2VsWjlta1FOS1U2Vm1vV3JwWkpvbEw1ZUR3akgwQTZnQnVENjJtVkQtVUpKVEJTeWNJSE1CaEFKa2VqMmZXbWk3ekR4ZWpmZ1Z3elFQaWNaNFJuMXA?oc=5</t>
         </is>
       </c>
       <c r="L35" t="n">
@@ -6071,7 +6289,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>noticia:1l4xxfk</t>
+          <t>noticia:1570kkf</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -6081,15 +6299,15 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-10-23 14:51</t>
+          <t>2026-10-23 15:28</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1792781480000</v>
+        <v>1792783705000</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -6107,13 +6325,13 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
+          <t>¿Se suspenden las clases en Oruro? Más de 200 casos de Coxsackie activan evaluaciones - Red Uno</t>
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQS2FPaHd3UnFBRjRoa0lKUm1MNUQ5S00zN1RJZE5fWlVUQnhiY0lLcFRkY2JZak1mZ0c2WEVMVUNJVUJTMGFLNHg4S2ZKNTRqLXJHM09ET19hX1pZeTQwUkdEc2huTHVpcno2QTRZbnhralVRWXozcWc1a2pHUEpBeTV1cWgzTWRwaDEweURKeVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNMFdHaVpKRmMyOENDYm16UXJPenVSQnpmTE94bDc4UFhqakluMUdvZjAwamUxT3BVWUpJQm8xVHBWengxQmhWM1hjU3d2YXFrLXpVU2VrZDJiMXZLMlQ5bGxGOHFETFhYM0s2RjlUTlhkd0g2eXQweDFHaTlKNGNMUlJfOWg2a0JjTklXUWZKc1BmUXZuZFZ2MF9fV2lEYUY4LXNiNmk3cF9FNjVtTl9GWFotT2ltS0xXTnM1dENvSU9kbFRMalFrYVdXOA?oc=5</t>
         </is>
       </c>
       <c r="L36" t="n">
@@ -6152,7 +6370,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>noticia:51709n</t>
+          <t>noticia:1nzu2o8</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -6162,78 +6380,62 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-10-23 13:38</t>
+          <t>2026-10-23 15:20</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1792777139000</v>
+        <v>1792783236000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>eju.tv</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>hidrológica</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - eju.tv</t>
+          <t>Alerta naranja por posibles desbordes en tres departamentos (15:20) - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPcjZTSmprRGVoNlRqQmdBTE5VM3pRQ1ZFakFUbzVyMUhiaDVkT0liaG9UNEZXekV6bWsycUk4X1JCSEY5RjhNVlZaTk9ULUFuZkY3NnZuWmZ1a19leUhFdlIyQV9kLWxlSkxfeXFhcFRTZjZ2YkpQQlJ1dkNLMDBjaGZ4SkhyQ0RfcnhKSEg5WURCQVQwbENYTHEzUzJSaUEzMGo2bWdyS3lsM016LXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPTnBESV9OODZhNjY3T2M2X2NZcmk4clI0eFZsd3VLMVRwaUlSdF9wanZyVGxDNUlNTm5wbGpLN1lvX09mNGxFVkpIZDNGdi1pNDdfSGlESThfeVloQzJsNUMyNUpWUDhzTVJiYWJpNkQ1RHliRWljZlp3SlhtZ2FhU0pvV0syUmZIejJZWHlRdTBOTG4zaTc5cEsycW9IcEx2SkQtN01Gendlb1VR?oc=5</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1</v>
-      </c>
-      <c r="N37" t="n">
-        <v>-17.764</v>
-      </c>
-      <c r="O37" t="n">
-        <v>-62.903</v>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Cotoca, Santa Cruz</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>Santa Cruz</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>Cotoca</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>noticia:11rddql</t>
+          <t>noticia:1itd1r7</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6243,20 +6445,20 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-10-23 13:22</t>
+          <t>2026-10-23 15:01</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1792776139000</v>
+        <v>1792782098000</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>eju.tv</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6269,13 +6471,13 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Intensifican acciones preventivas contra el dengue en Caranavi - El Diario - Bolivia</t>
+          <t>Intensa lluvia y granizada en La Paz inundan vías y elevan el nivel de los ríos - eju.tv</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOMjhSeDJBek5iaFhDcnFzX1lKelgwZmUwLTJnbEhMdDRMelUxNks5Ti1pRHh3dDhTcC1YZEdqM3FJOGdqVHRvcXVhRlpCQzVDTEZMUFBkV1NrYVQ2LXRqTTBhcGRQc21CQ0VabzZaNExXb1BjTzJ2Uk5BcFF0VG5XOFNRa3lqUWlJSnRFUUVXYnNpbXB0LVVmSXVWSzJxcmVpdVVxUC1KOUhTQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNWU9QWElKQXEyN3UxVm4xbzJzbEJ1TU1NTHZlRUp6YndmeU9GQnJKcTluVEJ2ZHQ5cGp3aWhlMUd5ektWQlBpUVNmZnZuRnJwMXlydzAzX0FBVnY5UDMzQTBkWVRNRUNJSlRvX3MyQVhMcEhIMW9WSUpXckVSd0RJWk1KMFBKWmJNU3diQVlEN1Y5aVV6eVBaZXpOMnFIWWxaMlRlY0ZB?oc=5</t>
         </is>
       </c>
       <c r="L38" t="n">
@@ -6285,14 +6487,14 @@
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>-15.813</v>
+        <v>-16.169</v>
       </c>
       <c r="O38" t="n">
-        <v>-67.46299999999999</v>
+        <v>-68.09</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Caranavi, La Paz</t>
+          <t>La Paz, La Paz</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -6307,14 +6509,14 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>Caranavi</t>
+          <t>Nuestra Señora de La Paz</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>noticia:fcm3nx</t>
+          <t>noticia:1l4xxfk</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6324,62 +6526,78 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-10-23 12:58</t>
+          <t>2026-10-23 14:51</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1792774699000</v>
+        <v>1792781480000</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>[VIDEO] Así fue el accidente de moto que dejó un adolescente fallecido y un hombre gravemente herido - Red Uno</t>
+          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOSmJMazhUemNfRHpWcDBoTVFZMUpwdlVKVUtvUXZNTGRRRHlwLW5KNmNhcmFnd1czbi1yalhFMnpSS1dmUE9jVzNlOS1kMWZtRzBHZ2EtcDRDdU5Gc2JUQVIwM2xPa2lZVmswRi1SUFVPcm8xcHlGN3F2UThTSDdKMDNyYnJmVkcxazNLLVBLOWFYM09FVUpmVnN5RVhpSVo2V1VCVmFwQ1gzTmRUWVp2aXMwcmxHRS1GV2p3NTBtR2RzM2wwVHUzaGJkRXJYbHdvaDlhWm5YMTk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQS2FPaHd3UnFBRjRoa0lKUm1MNUQ5S00zN1RJZE5fWlVUQnhiY0lLcFRkY2JZak1mZ0c2WEVMVUNJVUJTMGFLNHg4S2ZKNTRqLXJHM09ET19hX1pZeTQwUkdEc2huTHVpcno2QTRZbnhralVRWXozcWc1a2pHUEpBeTV1cWgzTWRwaDEweURKeVE?oc=5</t>
         </is>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1</v>
-      </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>-17.97</v>
+      </c>
+      <c r="O39" t="n">
+        <v>-67.11</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Oruro, Oruro</t>
+        </is>
+      </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>noticia:1cjx1qd</t>
+          <t>noticia:51709n</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6389,56 +6607,56 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-10-23 12:39</t>
+          <t>2026-10-23 13:38</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1792773575000</v>
+        <v>1792777139000</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
+          <t>eju.tv</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Más de 60 municipios en La Paz sufren falta de lluvias - La Patria Bolivia</t>
+          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - eju.tv</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE52Qi03Z1J6OS1CR2liRVZ0VlhCcmVQWFV6RUdGNXdrbzZRNXFjTWRaRnc1b3VoV0xaY3RIdncxNlNnYkxyUXo5MTlJWmMwWDNSMDE4ZHI2VkpWajFPaUF2SmRVYkk2eDZYQ1RfUU9ieENrZG9UVVFiaXZSeGI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPcjZTSmprRGVoNlRqQmdBTE5VM3pRQ1ZFakFUbzVyMUhiaDVkT0liaG9UNEZXekV6bWsycUk4X1JCSEY5RjhNVlZaTk9ULUFuZkY3NnZuWmZ1a19leUhFdlIyQV9kLWxlSkxfeXFhcFRTZjZ2YkpQQlJ1dkNLMDBjaGZ4SkhyQ0RfcnhKSEg5WURCQVQwbENYTHEzUzJSaUEzMGo2bWdyS3lsM016LXc?oc=5</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N40" t="n">
-        <v>-16.169</v>
+        <v>-17.764</v>
       </c>
       <c r="O40" t="n">
-        <v>-68.09</v>
+        <v>-62.903</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>La Paz, La Paz</t>
+          <t>Cotoca, Santa Cruz</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -6448,19 +6666,19 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>Nuestra Señora de La Paz</t>
+          <t>Cotoca</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>noticia:11y8tre</t>
+          <t>noticia:11rddql</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6470,56 +6688,56 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-10-23 11:43</t>
+          <t>2026-10-23 13:22</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1792770197000</v>
+        <v>1792776139000</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - Red Uno</t>
+          <t>Intensifican acciones preventivas contra el dengue en Caranavi - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOVGY3YVRLWWxYM0IycjF4dlNUeUhqZG90Yng4aWhmN3A5ai02WENWYnF4bWpoZHFKMGc1X0JPRHdRRVZfSlA4UmZFa2kxYkNIS3ZtQ1NvNlNCME51eVZTRkRKSUQ5MmRoaWl5Tkt5NHpPUEFwemN2YTV1djFwdHlqQnFqRHNPenhYcTlsanJPcXhpOVV1NmFBUXZyazQ2MkUzM0dSZy02ZllxTGtjcl9ldzdHSktTRlVaalZJc1pubUNQMWFTbzVEOUJ1UmhCdEJt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOMjhSeDJBek5iaFhDcnFzX1lKelgwZmUwLTJnbEhMdDRMelUxNks5Ti1pRHh3dDhTcC1YZEdqM3FJOGdqVHRvcXVhRlpCQzVDTEZMUFBkV1NrYVQ2LXRqTTBhcGRQc21CQ0VabzZaNExXb1BjTzJ2Uk5BcFF0VG5XOFNRa3lqUWlJSnRFUUVXYnNpbXB0LVVmSXVWSzJxcmVpdVVxUC1KOUhTQQ?oc=5</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>-17.764</v>
+        <v>-15.813</v>
       </c>
       <c r="O41" t="n">
-        <v>-62.903</v>
+        <v>-67.46299999999999</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Cotoca, Santa Cruz</t>
+          <t>Caranavi, La Paz</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -6529,42 +6747,42 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>Cotoca</t>
+          <t>Caranavi</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>clima:Sucre:2026-10-23:viento:1</t>
+          <t>noticia:fcm3nx</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-10-23 06:55</t>
+          <t>2026-10-23 12:58</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1792752927735</v>
+        <v>1792774699000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6577,74 +6795,54 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Sucre 2026-10-23: 66.2 km/h de ráfagas pronosticadas</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
-        </is>
-      </c>
+          <t>[VIDEO] Así fue el accidente de moto que dejó un adolescente fallecido y un hombre gravemente herido - Red Uno</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOSmJMazhUemNfRHpWcDBoTVFZMUpwdlVKVUtvUXZNTGRRRHlwLW5KNmNhcmFnd1czbi1yalhFMnpSS1dmUE9jVzNlOS1kMWZtRzBHZ2EtcDRDdU5Gc2JUQVIwM2xPa2lZVmswRi1SUFVPcm8xcHlGN3F2UThTSDdKMDNyYnJmVkcxazNLLVBLOWFYM09FVUpmVnN5RVhpSVo2V1VCVmFwQ1gzTmRUWVp2aXMwcmxHRS1GV2p3NTBtR2RzM2wwVHUzaGJkRXJYbHdvaDlhWm5YMTk?oc=5</t>
         </is>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="n">
-        <v>-19.03</v>
-      </c>
-      <c r="O42" t="n">
-        <v>-65.26000000000001</v>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Sucre</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>capital (pronóstico puntual)</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>Chuquisaca</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>Sucre</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-24:viento:2</t>
+          <t>noticia:1cjx1qd</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-10-23 06:55</t>
+          <t>2026-10-23 12:39</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1792752927734</v>
+        <v>1792773575000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>La Patria Bolivia</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -6653,26 +6851,22 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-24: 85 km/h de ráfagas pronosticadas</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
-        </is>
-      </c>
+          <t>Más de 60 municipios en La Paz sufren falta de lluvias - La Patria Bolivia</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE52Qi03Z1J6OS1CR2liRVZ0VlhCcmVQWFV6RUdGNXdrbzZRNXFjTWRaRnc1b3VoV0xaY3RIdncxNlNnYkxyUXo5MTlJWmMwWDNSMDE4ZHI2VkpWajFPaUF2SmRVYkk2eDZYQ1RfUU9ieENrZG9UVVFiaXZSeGI?oc=5</t>
         </is>
       </c>
       <c r="L43" t="n">
@@ -6682,59 +6876,59 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>-17.78</v>
+        <v>-16.169</v>
       </c>
       <c r="O43" t="n">
-        <v>-63.18</v>
+        <v>-68.09</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>La Paz, La Paz</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>capital (pronóstico puntual)</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Nuestra Señora de La Paz</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>usgs:us6000u49c</t>
+          <t>noticia:11y8tre</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>usgs</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-10-22 22:45</t>
+          <t>2026-10-23 11:43</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1792723541183</v>
+        <v>1792770197000</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>USGS</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>geológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6747,56 +6941,52 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Sismo M 4.5 - 58 km SW of Atocha, Bolivia</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Profundidad 236 km</t>
-        </is>
-      </c>
+          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - Red Uno</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://earthquake.usgs.gov/earthquakes/eventpage/us6000u49c</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOVGY3YVRLWWxYM0IycjF4dlNUeUhqZG90Yng4aWhmN3A5ai02WENWYnF4bWpoZHFKMGc1X0JPRHdRRVZfSlA4UmZFa2kxYkNIS3ZtQ1NvNlNCME51eVZTRkRKSUQ5MmRoaWl5Tkt5NHpPUEFwemN2YTV1djFwdHlqQnFqRHNPenhYcTlsanJPcXhpOVV1NmFBUXZyazQ2MkUzM0dSZy02ZllxTGtjcl9ldzdHSktTRlVaalZJc1pubUNQMWFTbzVEOUJ1UmhCdEJt?oc=5</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N44" t="n">
-        <v>-21.3469</v>
+        <v>-17.764</v>
       </c>
       <c r="O44" t="n">
-        <v>-66.5795</v>
+        <v>-62.903</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>58 km SW of Atocha, Bolivia</t>
+          <t>Cotoca, Santa Cruz</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>coordenada de la fuente</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>San Pablo</t>
+          <t>Cotoca</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-22:viento:1</t>
+          <t>clima:Sucre:2026-10-23:viento:1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6806,11 +6996,11 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-10-22 21:55</t>
+          <t>2026-10-23 06:55</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1792720528712</v>
+        <v>1792752927735</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -6832,7 +7022,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-22: 67.7 km/h de ráfagas pronosticadas</t>
+          <t>Sucre 2026-10-23: 66.2 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6852,14 +7042,14 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>-17.78</v>
+        <v>-19.03</v>
       </c>
       <c r="O45" t="n">
-        <v>-63.18</v>
+        <v>-65.26000000000001</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -6869,19 +7059,19 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Chuquisaca</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Sucre</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-23:viento:2</t>
+          <t>clima:Santa Cruz:2026-10-24:viento:2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6891,11 +7081,11 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-10-22 21:55</t>
+          <t>2026-10-23 06:55</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1792720528712</v>
+        <v>1792752927734</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -6917,7 +7107,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-23: 83.9 km/h de ráfagas pronosticadas</t>
+          <t>Santa Cruz 2026-10-24: 85 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6966,49 +7156,53 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>noticia:1hhvre7</t>
+          <t>usgs:us6000u49c</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>usgs</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-10-22 19:36</t>
+          <t>2026-10-22 22:45</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1792712202000</v>
+        <v>1792723541183</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>El Mundo Bolivia</t>
+          <t>USGS</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>geológica</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Virgen de Cotoca: Controlan incendio en depósito de materiales plásticos - El Mundo Bolivia</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr"/>
+          <t>Sismo M 4.5 - 58 km SW of Atocha, Bolivia</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Profundidad 236 km</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcDF6VE5FNzRaWGRuUzFKeXhnZ21DZTRaaEtrVEJEa1Z3ejg2VG1ONG1ENmlDWlkyVjlkQkJwS2F1XzBGMFQwSHd4OEwxTW1PbHdGcUh1ckV6SGpDd2hiN0dkeUVTcnFXT3RjOU1kLXZtVVdZY2hkZS1pcVpVUFhnRktqcHY5UnBrY0xUMDRETjl6N0pXT3A5amxhMA?oc=5</t>
+          <t>https://earthquake.usgs.gov/earthquakes/eventpage/us6000u49c</t>
         </is>
       </c>
       <c r="L47" t="n">
@@ -7018,78 +7212,82 @@
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>-17.764</v>
+        <v>-21.3469</v>
       </c>
       <c r="O47" t="n">
-        <v>-62.903</v>
+        <v>-66.5795</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Cotoca, Santa Cruz</t>
+          <t>58 km SW of Atocha, Bolivia</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
+          <t>coordenada de la fuente</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>Cotoca</t>
+          <t>San Pablo</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>noticia:bksnde</t>
+          <t>clima:Santa Cruz:2026-10-22:viento:1</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-10-22 17:01</t>
+          <t>2026-10-22 21:55</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1792702880000</v>
+        <v>1792720528712</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>eju.tv</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Reportan un incendio cerca de la carretera a Cotoca - eju.tv</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
+          <t>Santa Cruz 2026-10-22: 67.7 km/h de ráfagas pronosticadas</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPNGtpbnBfRnRBalVudnBlZHdVQ0ZSaUplZmtvTGE0aTQzdkxWS3d4My1EZEJ1UE9FNFQ3RmpyZGVsbS1qNEM1QUVFRFAxM2pYT1VqQzRuVjRtZnVNUGlKODNMc0F1a3l6TUpuQmtlUWNlVTVEWWU5ZGZtQm5LWUp3Sg?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L48" t="n">
@@ -7099,19 +7297,19 @@
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>-17.764</v>
+        <v>-17.78</v>
       </c>
       <c r="O48" t="n">
-        <v>-62.903</v>
+        <v>-63.18</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Cotoca, Santa Cruz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
+          <t>capital (pronóstico puntual)</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -7121,37 +7319,37 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>Cotoca</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>noticia:17hz69v</t>
+          <t>clima:Santa Cruz:2026-10-23:viento:2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-10-22 13:05</t>
+          <t>2026-10-22 21:55</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1792688709000</v>
+        <v>1792720528712</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>La Razón Digital Bolivia</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7164,36 +7362,56 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Accidente en El Sillar deja al menos 29 heridos - La Razón Digital Bolivia</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr"/>
+          <t>Santa Cruz 2026-10-23: 83.9 km/h de ráfagas pronosticadas</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPaXhTdm45YWZnWVFxVzJnb1ZwbUN4SmUtLVdJN0VJdFZBamRyQmFxN0RZelBfTklaSTVyOUZ3ajQ5MFB2TEN4Ukd6TE5ORFY5SEROVk1CZ25sRWJ1QnRBdTVfTktlby1NWXhaVWI5YnRvaDZWbHVjdDVoeFp5Tk5veFk5a19MSWJqcEJVV0dzV3k?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>29</v>
-      </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>-17.78</v>
+      </c>
+      <c r="O49" t="n">
+        <v>-63.18</v>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
+          <t>capital (pronóstico puntual)</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Santa Cruz de la Sierra</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>noticia:1f1qb0</t>
+          <t>noticia:1hhvre7</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -7203,15 +7421,15 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-10-22 12:09</t>
+          <t>2026-10-22 19:36</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1792685373000</v>
+        <v>1792712202000</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>El Mundo Bolivia</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -7229,13 +7447,13 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Accidente en el tramo Locotal–Villa Tunari: la vía está transitable con precaución - Red Uno</t>
+          <t>Virgen de Cotoca: Controlan incendio en depósito de materiales plásticos - El Mundo Bolivia</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTFozcEEwNXBqV19sS2VibXh0MGt0QlhsX1djSTFGQW5zNlFLRHZpNVVnZ1JmWDQ4LVRHX2Rmb3B5UU9qV0FZQmJCaUZYdmwyNG1NenJ4Qzlzd0NJTGs1SjMxdFRtRFBzSUkybGJfZFFaNFZBc21FSUJYSFVkQkVkSEhQaGw0UFVzeXctZHo3cjNsYm5weXJlOU1wcmFncnNhMC1BQUpvNWlDX1NxZXU4b09kVFFWR2tSVEk2UTdXXzB3TjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcDF6VE5FNzRaWGRuUzFKeXhnZ21DZTRaaEtrVEJEa1Z3ejg2VG1ONG1ENmlDWlkyVjlkQkJwS2F1XzBGMFQwSHd4OEwxTW1PbHdGcUh1ckV6SGpDd2hiN0dkeUVTcnFXT3RjOU1kLXZtVVdZY2hkZS1pcVpVUFhnRktqcHY5UnBrY0xUMDRETjl6N0pXT3A5amxhMA?oc=5</t>
         </is>
       </c>
       <c r="L50" t="n">
@@ -7245,14 +7463,14 @@
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>-16.556</v>
+        <v>-17.764</v>
       </c>
       <c r="O50" t="n">
-        <v>-65.569</v>
+        <v>-62.903</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Villa Tunari, Cochabamba</t>
+          <t>Cotoca, Santa Cruz</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -7262,19 +7480,19 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>Villa Tunari</t>
+          <t>Cotoca</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>noticia:wi18tm</t>
+          <t>noticia:bksnde</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7284,62 +7502,78 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-10-22 11:53</t>
+          <t>2026-10-22 17:01</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1792684426000</v>
+        <v>1792702880000</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>eju.tv</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>tecnológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Accidente en El Sillar deja heridos y derrame de combustible: esto es lo último que se sabe - Red Uno</t>
+          <t>Reportan un incendio cerca de la carretera a Cotoca - eju.tv</t>
         </is>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPZHNBTEdaQm5Wby1lTF9mWlQ2aGg0MVc4S0MwVWJ3dUJ5WWU5X3IwYWhKRjk5VWtYWEJHRDF4QldVc29laVNPSTJNWFBDSkNFQlFSYTJUXzNMNF9hckFBN1I2T2xoQUtYQ2V6MDNTZHhHVk9qeTBCdHRpM2ZLd0pyOFRweUUxX19STzRHTHg5VUY5d1lhS0tDeXpCdklqcTZGT1J4R0xnSDhoak1EZ2dtNUhSTUV6b1o0U0VSdWY5X0E3U05Tc1dYVEN2WFZUeFhPMTBJTmowNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPNGtpbnBfRnRBalVudnBlZHdVQ0ZSaUplZmtvTGE0aTQzdkxWS3d4My1EZEJ1UE9FNFQ3RmpyZGVsbS1qNEM1QUVFRFAxM2pYT1VqQzRuVjRtZnVNUGlKODNMc0F1a3l6TUpuQmtlUWNlVTVEWWU5ZGZtQm5LWUp3Sg?oc=5</t>
         </is>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>1</v>
-      </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>-17.764</v>
+      </c>
+      <c r="O51" t="n">
+        <v>-62.903</v>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Cotoca, Santa Cruz</t>
+        </is>
+      </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>Cotoca</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>noticia:12gfagq</t>
+          <t>noticia:17hz69v</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -7349,15 +7583,15 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-10-22 11:28</t>
+          <t>2026-10-22 13:05</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1792682880000</v>
+        <v>1792688709000</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>FmBolivia</t>
+          <t>La Razón Digital Bolivia</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -7366,61 +7600,45 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Reportan triple colisión entre dos camiones y un bus en la carretera Cochabamba-Santa Cruz - FmBolivia</t>
+          <t>Accidente en El Sillar deja al menos 29 heridos - La Razón Digital Bolivia</t>
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNMTNBaFZNMU9SR25vdVBuNXlZY3g4VkFWYXRiQnNSaUFjemZhUHZWNHg4V2owU2xfNndBak94TnU2cHNUVXdNNWl2eUdHZVNMbVZweTR5M0o0bWdTNUN4QkoxUkI2TDBmVE03M09zRGhJRVFzV0tPZ1NCWEJLUkt1ZGN4UGduOUZMQnJoM0tMYTh0ZlFxaFJNUkJqaWFPazRlMzN3ajhjUEdUYXlZRndpb3RSdTFCX2tCZGJxQ0x4SlBISWJsRVoyN3ZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPaXhTdm45YWZnWVFxVzJnb1ZwbUN4SmUtLVdJN0VJdFZBamRyQmFxN0RZelBfTklaSTVyOUZ3ajQ5MFB2TEN4Ukd6TE5ORFY5SEROVk1CZ25sRWJ1QnRBdTVfTktlby1NWXhaVWI5YnRvaDZWbHVjdDVoeFp5Tk5veFk5a19MSWJqcEJVV0dzV3k?oc=5</t>
         </is>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="n">
-        <v>-17.39</v>
-      </c>
-      <c r="O52" t="n">
-        <v>-66.16</v>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>Cochabamba, Cochabamba</t>
-        </is>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>noticia:1uq1bxy</t>
+          <t>noticia:1f1qb0</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -7430,11 +7648,11 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-10-22 10:44</t>
+          <t>2026-10-22 12:09</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1792680273000</v>
+        <v>1792685373000</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -7456,13 +7674,13 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Reportan triple colisión en la carretera Cochabamba–Santa Cruz - Red Uno</t>
+          <t>Accidente en el tramo Locotal–Villa Tunari: la vía está transitable con precaución - Red Uno</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNNUROMzd1UDJRWVZZQ011cFd2c1FSdER1ZzdleU04cXpwYk5HaUZrLXoyU2NzdFk1dnNRUndhUWt0cG9DX09rSjlLcDItU0tzcmQtS3E4dDQ4ZF9HdGJLdk13ek9BNHJUWVlCcklrM25rZ01RbXhLalRBT1FGdDNReHdlTFZkNkJ5ZFd3N3NZVFVmOFUxbEhHN0RsaUxiSVZsM0lXVEFYSHVRQlhsOEtJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTFozcEEwNXBqV19sS2VibXh0MGt0QlhsX1djSTFGQW5zNlFLRHZpNVVnZ1JmWDQ4LVRHX2Rmb3B5UU9qV0FZQmJCaUZYdmwyNG1NenJ4Qzlzd0NJTGs1SjMxdFRtRFBzSUkybGJfZFFaNFZBc21FSUJYSFVkQkVkSEhQaGw0UFVzeXctZHo3cjNsYm5weXJlOU1wcmFncnNhMC1BQUpvNWlDX1NxZXU4b09kVFFWR2tSVEk2UTdXXzB3TjA?oc=5</t>
         </is>
       </c>
       <c r="L53" t="n">
@@ -7472,14 +7690,14 @@
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>-17.39</v>
+        <v>-16.556</v>
       </c>
       <c r="O53" t="n">
-        <v>-66.16</v>
+        <v>-65.569</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Cochabamba, Cochabamba</t>
+          <t>Villa Tunari, Cochabamba</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -7494,14 +7712,14 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Villa Tunari</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>noticia:1jl2oid</t>
+          <t>noticia:wi18tm</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -7511,20 +7729,20 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-10-22 07:49</t>
+          <t>2026-10-22 11:53</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1792669785000</v>
+        <v>1792684426000</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>eju.tv</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>tecnológica</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7537,13 +7755,13 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - eju.tv</t>
+          <t>Accidente en El Sillar deja heridos y derrame de combustible: esto es lo último que se sabe - Red Uno</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQbTBrUmlla3FvVU1EX1pxcUI3SXYzbUFFMzlnRzhlSDJwMGpWWURxYjIwSkJBRGdCazMzT01hVy1qMFY3RnJLbC1XNXJ4bU55aDJVeXpNUlRsbzQ3T3hiRXJ5SWlhNmw5cDZFanNoWFBtQ01Gd3dscXltWmU5VHBSQlN3c2IwNGxuVE5tQ3lOT1RmNzRiVi1hc0hn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPZHNBTEdaQm5Wby1lTF9mWlQ2aGg0MVc4S0MwVWJ3dUJ5WWU5X3IwYWhKRjk5VWtYWEJHRDF4QldVc29laVNPSTJNWFBDSkNFQlFSYTJUXzNMNF9hckFBN1I2T2xoQUtYQ2V6MDNTZHhHVk9qeTBCdHRpM2ZLd0pyOFRweUUxX19STzRHTHg5VUY5d1lhS0tDeXpCdklqcTZGT1J4R0xnSDhoak1EZ2dtNUhSTUV6b1o0U0VSdWY5X0E3U05Tc1dYVEN2WFZUeFhPMTBJTmowNA?oc=5</t>
         </is>
       </c>
       <c r="L54" t="n">
@@ -7552,37 +7770,21 @@
       <c r="M54" t="n">
         <v>1</v>
       </c>
-      <c r="N54" t="n">
-        <v>-17.781</v>
-      </c>
-      <c r="O54" t="n">
-        <v>-63.139</v>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>Santa Cruz, Santa Cruz</t>
-        </is>
-      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>Santa Cruz</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>Santa Cruz de la Sierra</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>noticia:yqgeq</t>
+          <t>noticia:12gfagq</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -7592,15 +7794,15 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-10-22 07:43</t>
+          <t>2026-10-22 11:28</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1792669426000</v>
+        <v>1792682880000</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>FmBolivia</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -7609,39 +7811,39 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - Red Uno</t>
+          <t>Reportan triple colisión entre dos camiones y un bus en la carretera Cochabamba-Santa Cruz - FmBolivia</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNVEh1bFlCanFuOTJid2EzYS1meG5oekFJcGFaME1fTk9sUnZpd3U0UXFHUFVJSW1jc1hzM2VFOFprT2xNYjBzbmswZmdJV3dremRIS0I4MDNzRjBnbEttWEhfOWZBbmFrRnNHWDFVLVFoM0VkZkxkaW4tMmZlSFJLei1heTFHMU0wSmxQVVRZN0cwaXQzcDBtZkdwTUFma0RXU2dwLXRnLTBkNGN3Vm1fV3hEdlM1dWZ1SEsw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNMTNBaFZNMU9SR25vdVBuNXlZY3g4VkFWYXRiQnNSaUFjemZhUHZWNHg4V2owU2xfNndBak94TnU2cHNUVXdNNWl2eUdHZVNMbVZweTR5M0o0bWdTNUN4QkoxUkI2TDBmVE03M09zRGhJRVFzV0tPZ1NCWEJLUkt1ZGN4UGduOUZMQnJoM0tMYTh0ZlFxaFJNUkJqaWFPazRlMzN3ajhjUEdUYXlZRndpb3RSdTFCX2tCZGJxQ0x4SlBISWJsRVoyN3ZR?oc=5</t>
         </is>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>-17.781</v>
+        <v>-17.39</v>
       </c>
       <c r="O55" t="n">
-        <v>-63.139</v>
+        <v>-66.16</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Santa Cruz, Santa Cruz</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -7651,19 +7853,19 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Cochabamba</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>noticia:n32ahi</t>
+          <t>noticia:1uq1bxy</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7673,20 +7875,20 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-10-22 05:30</t>
+          <t>2026-10-22 10:44</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1792661402000</v>
+        <v>1792680273000</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>FmBolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7699,43 +7901,286 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Senamhi anuncia el inicio de la temporada de lluvias en Bolivia y prevé granizadas como la de La Paz - FmBolivia</t>
+          <t>Reportan triple colisión en la carretera Cochabamba–Santa Cruz - Red Uno</t>
         </is>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNNUROMzd1UDJRWVZZQ011cFd2c1FSdER1ZzdleU04cXpwYk5HaUZrLXoyU2NzdFk1dnNRUndhUWt0cG9DX09rSjlLcDItU0tzcmQtS3E4dDQ4ZF9HdGJLdk13ek9BNHJUWVlCcklrM25rZ01RbXhLalRBT1FGdDNReHdlTFZkNkJ5ZFd3N3NZVFVmOFUxbEhHN0RsaUxiSVZsM0lXVEFYSHVRQlhsOEtJ?oc=5</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>-17.39</v>
+      </c>
+      <c r="O56" t="n">
+        <v>-66.16</v>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Cochabamba, Cochabamba</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>noticia:1jl2oid</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>noticia</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-10-22 07:49</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>1792669785000</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>eju.tv</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>antropogénica</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>amarilla</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - eju.tv</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQbTBrUmlla3FvVU1EX1pxcUI3SXYzbUFFMzlnRzhlSDJwMGpWWURxYjIwSkJBRGdCazMzT01hVy1qMFY3RnJLbC1XNXJ4bU55aDJVeXpNUlRsbzQ3T3hiRXJ5SWlhNmw5cDZFanNoWFBtQ01Gd3dscXltWmU5VHBSQlN3c2IwNGxuVE5tQ3lOT1RmNzRiVi1hc0hn?oc=5</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1</v>
+      </c>
+      <c r="N57" t="n">
+        <v>-17.781</v>
+      </c>
+      <c r="O57" t="n">
+        <v>-63.139</v>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Santa Cruz, Santa Cruz</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>Santa Cruz de la Sierra</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>noticia:yqgeq</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>noticia</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-10-22 07:43</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1792669426000</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Red Uno</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>antropogénica</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>amarilla</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - Red Uno</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNVEh1bFlCanFuOTJid2EzYS1meG5oekFJcGFaME1fTk9sUnZpd3U0UXFHUFVJSW1jc1hzM2VFOFprT2xNYjBzbmswZmdJV3dremRIS0I4MDNzRjBnbEttWEhfOWZBbmFrRnNHWDFVLVFoM0VkZkxkaW4tMmZlSFJLei1heTFHMU0wSmxQVVRZN0cwaXQzcDBtZkdwTUFma0RXU2dwLXRnLTBkNGN3Vm1fV3hEdlM1dWZ1SEsw?oc=5</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1</v>
+      </c>
+      <c r="N58" t="n">
+        <v>-17.781</v>
+      </c>
+      <c r="O58" t="n">
+        <v>-63.139</v>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Santa Cruz, Santa Cruz</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>Santa Cruz de la Sierra</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>noticia:n32ahi</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>noticia</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-10-22 05:30</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>1792661402000</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>FmBolivia</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>meteorológica</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>verde</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Senamhi anuncia el inicio de la temporada de lluvias en Bolivia y prevé granizadas como la de La Paz - FmBolivia</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
           <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQNmVPRnVBMGQzdEI5SUp3Z3ZGVExwTUR6TWNadGQ1QldUS1o2QVFvUl9sVEZKMDVyQVVrS25rU1RSQlJKWXk1YzE0NUhidjhpcmFaSlhZUDZvcE9XcG1KTFNTYmowUU1CSFJNOVR2UHNmMk1iT3N0RVBteHkzZkgyRFROYk1pdkpxVHZya3N2X2FVLVQxbURFVVZlb1NzRjZzTE95TXFVUXFJNkVZakQ2bUhVQzB0SXk3TVhXUTJXa0dycTE1MWVQRFpDX3lDSWFqUGwzU2NtNA?oc=5</t>
         </is>
       </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="n">
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
         <v>-16.169</v>
       </c>
-      <c r="O56" t="n">
+      <c r="O59" t="n">
         <v>-68.09</v>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>La Paz, La Paz</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>nombre de municipio en el titular</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="R59" t="inlineStr">
         <is>
           <t>La Paz</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>Nuestra Señora de La Paz</t>
         </is>
@@ -8305,7 +8750,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-10-25 11:02</t>
+          <t>2026-10-25 11:46</t>
         </is>
       </c>
     </row>
@@ -8328,7 +8773,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4">
@@ -8338,7 +8783,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5">
@@ -8385,7 +8830,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sala de Situación Bolivia – CCES. Base de eventos de amenazas (datos preliminares de fuentes abiertas). Consulta: 2026-10-25 11:02.</t>
+          <t>Sala de Situación Bolivia – CCES. Base de eventos de amenazas (datos preliminares de fuentes abiertas). Consulta: 2026-10-25 11:46.</t>
         </is>
       </c>
     </row>

--- a/docs/datos/datos_bolivia.xlsx
+++ b/docs/datos/datos_bolivia.xlsx
@@ -8750,7 +8750,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-10-25 11:46</t>
+          <t>2026-10-25 11:57</t>
         </is>
       </c>
     </row>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sala de Situación Bolivia – CCES. Base de eventos de amenazas (datos preliminares de fuentes abiertas). Consulta: 2026-10-25 11:46.</t>
+          <t>Sala de Situación Bolivia – CCES. Base de eventos de amenazas (datos preliminares de fuentes abiertas). Consulta: 2026-10-25 11:57.</t>
         </is>
       </c>
     </row>

--- a/docs/datos/datos_bolivia.xlsx
+++ b/docs/datos/datos_bolivia.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R42"/>
+  <dimension ref="A1:R41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,20 +514,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>noticia:1at00ey</t>
+          <t>noticia:oww2zc</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-25 11:19</t>
+          <t>2026-10-25 12:08</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1792941547000</v>
+        <v>1792944531000</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Dos cisternas chocan y provocan voraz incendio en la ruta a Camiri - Red Uno</t>
+          <t>Cierran la carretera a Camiri: dos cisternas chocan y provocan un voraz incendio - Red Uno</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -585,27 +585,27 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPTTF0OUdVS1c1a0lZWmk3bGxHdDJIalpWZTRyQTY3eWE2a2dWOHlsaldKZXpSLWN5c3BkUWdBRkJuSzhHdWl2ZjgwTFFFYnd0aTAxZ3dJU0hCekNZNm9aTTJSZUNfQjVIM3FrUUJ4NXAwa3paZ3BEek9xTVZNQWdnN01xRHloV1ZXZHV6N0JpUWo3RE9DMlFGdkNnWkloTjVVY3RBR1RSRUJJWFVtby1fMWFMNTdLZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQLXlqSFdvWUVhQUNadnpkdE5lUTZQS0lobThzUTZWbDNJTE94alVhaDBaYU9Fd09SSGt3UlR3Y0dfZlNIcml1ZktnWjctNk1Na3V4S0tINFNkMXM0OHBoV2lCTTBiYXlPUTA3T2ZkeXE2RElYWjhfVHd3Nng1Z0E4alBmOFI5NDFwX09kazZlSWl2OVR2ZVR6MDhvSHFnSmJKbTFXSEFDNFFYcWVDNGtYWEQ0bDhJel9CaEpEZWZ4SWN0TE9Ya0E?oc=5 | https://news.google.com/rss/articles/CBMitgFBVV95cUxPTTF0OUdVS1c1a0lZWmk3bGxHdDJIalpWZTRyQTY3eWE2a2dWOHlsaldKZXpSLWN5c3BkUWdBRkJuSzhHdWl2ZjgwTFFFYnd0aTAxZ3dJU0hCekNZNm9aTTJSZUNfQjVIM3FrUUJ4NXAwa3paZ3BEek9xTVZNQWdnN01xRHloV1ZXZHV6N0JpUWo3RE9DMlFGdkNnWkloTjVVY3RBR1RSRUJJWFVtby1fMWFMNTdLZw?oc=5 | https://news.google.com/rss/articles/CBMiwAFBVV95cUxORUhqeWpKY1FHRWoxaHN0UXFzS3dpeHh6N0NwLUJOZTlZcDVoNHN0VnI0by1qMWtZZEkxVmtUNjdNTFhjaEFQU2IyMlNwZW95WFBzbFJPVVB6TjJtdjNENk1LWVlsMUxUUzBNVzkxRk1HZ3lQU0s2M1lRVlRuaXlkMmJrd3AyTGpIdXItNkhlU3dhTzBRME56Rm1DSlZCYjNxSnNTbTFqNWRoUkdraHhlREhuYldqeFk2N3poWEx2M08?oc=5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>noticia:1uf38hl</t>
+          <t>noticia:1sg8pi0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-25 10:59</t>
+          <t>2026-10-25 09:59</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1792940350000</v>
+        <v>1792936752000</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>¡Cisterna con combustible en llamas! Reportan impresionante incendio en la carretera a Camiri - Red Uno</t>
+          <t>Bus de agrupación musical sufre accidente rumbo al trópico de Cochabamba | VIDEO - Red Uno</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -641,54 +641,54 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>-20.05</v>
+        <v>-17.39</v>
       </c>
       <c r="N3" t="n">
-        <v>-63.486</v>
+        <v>-66.16</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Camiri, Santa Cruz</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Camiri</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxORUhqeWpKY1FHRWoxaHN0UXFzS3dpeHh6N0NwLUJOZTlZcDVoNHN0VnI0by1qMWtZZEkxVmtUNjdNTFhjaEFQU2IyMlNwZW95WFBzbFJPVVB6TjJtdjNENk1LWVlsMUxUUzBNVzkxRk1HZ3lQU0s2M1lRVlRuaXlkMmJrd3AyTGpIdXItNkhlU3dhTzBRME56Rm1DSlZCYjNxSnNTbTFqNWRoUkdraHhlREhuYldqeFk2N3poWEx2M08?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOVDVzVTJNM2JuQ25sMThEaVZNOUNRd3FGT3RhVnFrZXZ2NDQ1YlluTVdhbVNUQnA1MGNESHRSWVUzbC1kRVh3OTR0emtlTG91cmRWeFJ5dk5zb3p2WFRyMEJUV3FNRnY1WHhRUU9WLTlJcmNyNXJZZFdoM0JoZjNpa3hjUXhMM0xrUDJab2VadkM5RWZYQ3lWZTVDdzg1akxJT2lxcDVNNzI0NG1hejdfdkUyTQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>noticia:1sg8pi0</t>
+          <t>noticia:167wlhz</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25 09:59</t>
+          <t>2026-10-25 07:53</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1792936752000</v>
+        <v>1792929231000</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bus de agrupación musical sufre accidente rumbo al trópico de Cochabamba | VIDEO - Red Uno</t>
+          <t>¡A sacar el paraguas! Santa cruz amanece con lluvia, frío y complicaciones en el tránsito vehicular - Red Uno</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -719,62 +719,62 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>-17.39</v>
+        <v>-17.781</v>
       </c>
       <c r="N4" t="n">
-        <v>-66.16</v>
+        <v>-63.139</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Cochabamba, Cochabamba</t>
+          <t>Santa Cruz, Santa Cruz</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOVDVzVTJNM2JuQ25sMThEaVZNOUNRd3FGT3RhVnFrZXZ2NDQ1YlluTVdhbVNUQnA1MGNESHRSWVUzbC1kRVh3OTR0emtlTG91cmRWeFJ5dk5zb3p2WFRyMEJUV3FNRnY1WHhRUU9WLTlJcmNyNXJZZFdoM0JoZjNpa3hjUXhMM0xrUDJab2VadkM5RWZYQ3lWZTVDdzg1akxJT2lxcDVNNzI0NG1hejdfdkUyTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOY1ZpYktLR3pUQXotUndVR3puUzVHbW1YTzNyUmJvUHB4Q2JmelRvOEdaRldOUm1xLVJnbGR5VWcxTjNEM3ZUYktCUWtVM0hKSjFuRGdpX0JxN0M5MVZBSG1aVURyVWktdmxwbUtRT19ydU5LdzNTZ2Zpb2ozdHlMUUdTVlAyVk4xODBnV0hyTXdVVndyNzV3VC1KMzFnV3lpcFFXSk9MdDZOTWlWakNwT1FnNDh6QVdjazVYZDVVMkdaLU0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>noticia:167wlhz</t>
+          <t>noticia:bzr7eh</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-25 07:53</t>
+          <t>2026-10-25 07:09</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1792929231000</v>
+        <v>1792926572000</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>¡A sacar el paraguas! Santa cruz amanece con lluvia, frío y complicaciones en el tránsito vehicular - Red Uno</t>
+          <t>Alerta naranja por riesgo de desbordes de ríos - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>hidrológica</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -789,74 +789,74 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>El Diario - Bolivia; El Mundo Bolivia; FmBolivia</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>-17.781</v>
+        <v>-16.169</v>
       </c>
       <c r="N5" t="n">
-        <v>-63.139</v>
+        <v>-68.09</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Santa Cruz, Santa Cruz</t>
+          <t>La Paz, La Paz</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Nuestra Señora de La Paz</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOY1ZpYktLR3pUQXotUndVR3puUzVHbW1YTzNyUmJvUHB4Q2JmelRvOEdaRldOUm1xLVJnbGR5VWcxTjNEM3ZUYktCUWtVM0hKSjFuRGdpX0JxN0M5MVZBSG1aVURyVWktdmxwbUtRT19ydU5LdzNTZ2Zpb2ozdHlMUUdTVlAyVk4xODBnV0hyTXdVVndyNzV3VC1KMzFnV3lpcFFXSk9MdDZOTWlWakNwT1FnNDh6QVdjazVYZDVVMkdaLU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNNGZKSDVaZkowWUFGSEUyTWR3d3dsc04waFBLLWUtcVpiTDYzbmNtYTN1RkFLbjAwN3dxT0xZc3pqc3REUXduZVltQ2Fud1BZLTh1bTNiTEJueVUwV0dERS1iUXZqMHd0UnFrQ3E2SFAzbm5lQ1I4U29MaHJFbWFvdVRTeFY4Wl9rSmc3RkpaQ2xwX0oz?oc=5 | https://news.google.com/rss/articles/CBMipwFBVV95cUxPZW00RkxJSklTelNrS2hqczJDWHlwcENFX2lnSEUyTEFPaDFRQ2JvMUcyd3NfYjg0UE9ORGxHRzB4ZDh3U0hQQ1JSQlhsaUY4N3ByMUUxei1SaUZnNlp6T3hsLVdiMGhKaXhsV1FNSUNQMHlvQ19qdk56SEF0d2RXVFctS0VPT25kNGZCRDdvZ2dxU0VoUUJKU0ZBd0ZycFNEZFh0T3ZjOA?oc=5 | https://news.google.com/rss/articles/CBMiwAFBVV95cUxPZm85aHphekQ4U3BZZkp1ZkF6ZVdSUHgtZmltS1FxUUgza1AwcndWWDJZOWctT0RiVmVabmg5SG42NnJWMlJMMnBlYTlYaVdSb09sR0dnVDdpT29faTdiaDUtZElJdlQ3eTdjR2VsWjlta1FOS1U2Vm1vV3JwWkpvbEw1ZUR3akgwQTZnQnVENjJtVkQtVUpKVEJTeWNJSE1CaEFKa2VqMmZXbWk3ekR4ZWpmZ1Z3elFQaWNaNFJuMXA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>noticia:bzr7eh</t>
+          <t>noticia:1fo4ig4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-25 07:09</t>
+          <t>2026-10-25 01:08</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1792926572000</v>
+        <v>1792904880000</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Alerta naranja por riesgo de desbordes de ríos - El Diario - Bolivia</t>
+          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>hidrológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>roja</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -867,57 +867,41 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia; El Mundo Bolivia; FmBolivia</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>-16.169</v>
-      </c>
-      <c r="N6" t="n">
-        <v>-68.09</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>La Paz, La Paz</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>La Paz</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Nuestra Señora de La Paz</t>
-        </is>
-      </c>
+          <t>diarioelpueblo.com.pe</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNNGZKSDVaZkowWUFGSEUyTWR3d3dsc04waFBLLWUtcVpiTDYzbmNtYTN1RkFLbjAwN3dxT0xZc3pqc3REUXduZVltQ2Fud1BZLTh1bTNiTEJueVUwV0dERS1iUXZqMHd0UnFrQ3E2SFAzbm5lQ1I4U29MaHJFbWFvdVRTeFY4Wl9rSmc3RkpaQ2xwX0oz?oc=5 | https://news.google.com/rss/articles/CBMipwFBVV95cUxPZW00RkxJSklTelNrS2hqczJDWHlwcENFX2lnSEUyTEFPaDFRQ2JvMUcyd3NfYjg0UE9ORGxHRzB4ZDh3U0hQQ1JSQlhsaUY4N3ByMUUxei1SaUZnNlp6T3hsLVdiMGhKaXhsV1FNSUNQMHlvQ19qdk56SEF0d2RXVFctS0VPT25kNGZCRDdvZ2dxU0VoUUJKU0ZBd0ZycFNEZFh0T3ZjOA?oc=5 | https://news.google.com/rss/articles/CBMiwAFBVV95cUxPZm85aHphekQ4U3BZZkp1ZkF6ZVdSUHgtZmltS1FxUUgza1AwcndWWDJZOWctT0RiVmVabmg5SG42NnJWMlJMMnBlYTlYaVdSb09sR0dnVDdpT29faTdiaDUtZElJdlQ3eTdjR2VsWjlta1FOS1U2Vm1vV3JwWkpvbEw1ZUR3akgwQTZnQnVENjJtVkQtVUpKVEJTeWNJSE1CaEFKa2VqMmZXbWk3ekR4ZWpmZ1Z3elFQaWNaNFJuMXA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQcmFrT3dwcEs0X3U2NWxnOGJwNnI2WHdWTGZYbzEyNnJzUWhkbU9TRWhfSlB5UkMwX2gyMmxYUmVNWmxNOVR6V0twRHpFMTVIYjBKbHQ2TXN2d2w5dkFpcWJCcUJMZldaX01sNWtQV2ZJOGpRVzR3NDVIU0pJc1BNVg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>noticia:1fo4ig4</t>
+          <t>noticia:r1uot6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-25 01:08</t>
+          <t>2026-10-24 20:00</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1792904880000</v>
+        <v>1792886439000</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
+          <t>vuelco deja heridos en ruta Oruro – Huanuni - La Patria Bolivia</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -926,18 +910,18 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>roja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -949,37 +933,53 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>diarioelpueblo.com.pe</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
+          <t>La Patria Bolivia</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>-17.97</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-67.11</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Oruro, Oruro</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQcmFrT3dwcEs0X3U2NWxnOGJwNnI2WHdWTGZYbzEyNnJzUWhkbU9TRWhfSlB5UkMwX2gyMmxYUmVNWmxNOVR6V0twRHpFMTVIYjBKbHQ2TXN2d2w5dkFpcWJCcUJMZldaX01sNWtQV2ZJOGpRVzR3NDVIU0pJc1BNVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNNDQtMG1KT1lLWW5nem9Jbm5JWDZKNlRWZmFmRlBxWDlDeXlSWnJ5d2NsTlpxa0JIS25oVWVZOC1majZVbWhOVDIxR0dLOFlzY2VpVzVoVk1mQnF3dXVwLUFZVHc1UjlXZzF5T05CY3U0ZldLVkw1VzBTek5zanpjQW1xalltWHNiaXI3dTNR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>noticia:r1uot6</t>
+          <t>noticia:1ytw450</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-24 20:00</t>
+          <t>2026-10-24 18:58</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1792886439000</v>
+        <v>1792882686000</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>vuelco deja heridos en ruta Oruro – Huanuni - La Patria Bolivia</t>
+          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -988,18 +988,18 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>roja</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1011,53 +1011,37 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>-17.97</v>
-      </c>
-      <c r="N8" t="n">
-        <v>-67.11</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Oruro, Oruro</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Oruro</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Oruro</t>
-        </is>
-      </c>
+          <t>diarioelpueblo.com.pe</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNNDQtMG1KT1lLWW5nem9Jbm5JWDZKNlRWZmFmRlBxWDlDeXlSWnJ5d2NsTlpxa0JIS25oVWVZOC1majZVbWhOVDIxR0dLOFlzY2VpVzVoVk1mQnF3dXVwLUFZVHc1UjlXZzF5T05CY3U0ZldLVkw1VzBTek5zanpjQW1xalltWHNiaXI3dTNR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNZ1U3bEVuaVdjVE1zSU9lOHJZTVRZLVZaemhldGNnT1JBWDJvbzdvM3paVVNhLUlyWHF2akNuSXJOLXdyTGRuejRlV1FuMjVkTjA3NmdRdmgtRWlUeTFBV1dEMzBvejBxaXZJdUZZWkRVTF9VLU5BcjFGZGFEQ09WWQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>noticia:1ytw450</t>
+          <t>noticia:1g006zh</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-24 18:58</t>
+          <t>2026-10-24 17:02</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1792882686000</v>
+        <v>1792875752000</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
+          <t>Accidente en la carretera a Mayaya deja siete heridos del grupo Los Chicos Fieles - El Potosí</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1066,18 +1050,18 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>roja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1085,41 +1069,57 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>diarioelpueblo.com.pe</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
+          <t>EL DÍA - Noticias de Bolivia para el mundo; El Potosí; La Razón Digital Bolivia; Opinión Bolivia</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>-19.58</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-65.75</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Potosí, Potosí</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Potosí</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Potosí</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNZ1U3bEVuaVdjVE1zSU9lOHJZTVRZLVZaemhldGNnT1JBWDJvbzdvM3paVVNhLUlyWHF2akNuSXJOLXdyTGRuejRlV1FuMjVkTjA3NmdRdmgtRWlUeTFBV1dEMzBvejBxaXZJdUZZWkRVTF9VLU5BcjFGZGFEQ09WWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPTGQwaVBfdG1JdVRMUTN4LVVvN0ppc3dreDJVVllDR3RmX0xpMzB4b0pvVTNSV1B6T0ZEWTdEZkNsRUdSNzhLaC1CWHN5WktNWk1nRWpTdVZiYjI3TlJlX2xlVTI5MjlRU2hiY1gteml4YWVFbDNPSVRBZmtITlQzbmhaUXVmcThRa2xsQTJIOXZuNzlSdm12MEdyOEZHdw?oc=5 | https://news.google.com/rss/articles/CBMizwFBVV95cUxPeGd3VWpCWXJ0YTJIeDJLcktzWG1jdUh0TjFXb01wSTkxbHNXZU94VWNDMkxnTjlJZVdpbkprMEY2NE80RXYyUWxUQXVnbl9lUXR2b28zTEh6cTJLVEQ4TUNja2kzRlhadVBFZFVwV1U2TlhseXZMZ20zZTZiUFpWRjdCOWNBMHU5XzdMV3JqQjV4TEE3bHRMOXR6Nm55eHZUNnFHSDdVRk8zVkY4RkVsUUtUN0JYdkREWGZncmJ3ZWc2T1BuUm1ZLTlfcHVabFE?oc=5 | https://news.google.com/rss/articles/CBMizAFBVV95cUxNYjNxaHg3YllRRTJYdFd1clAtUlROSGlFNVg5eUVZUGJoOEZ4MWM5QU5WQm1YTDc4NXc3SjhWMUw0TkZfSHlMLUQ1bmpTME1Kb1JaM0ExamFHYTd3VlU4MXRWdTZ1bzh1SGYtbGE1a3dBaG93bjg1OGc0S0JfRE43c3dVMVltN0dQQzNhQUNhM0FjVUNRUDRSamlJYlk2dEJpUTBuY2hBcTFucTVRN0ZtYnc5bzdmTV9LQm1uVUxaZS1tUE9IejhBVDRCdU_SAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>noticia:1g006zh</t>
+          <t>noticia:1ukcn97</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-24 17:02</t>
+          <t>2026-10-24 13:26</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1792875752000</v>
+        <v>1792862794000</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a Mayaya deja siete heridos del grupo Los Chicos Fieles - El Potosí</t>
+          <t>Esta es la lista preliminar de los heridos en el accidente del grupo 'Los chicos fieles', el conductor está grave - El Deber</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1139,7 +1139,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1147,62 +1147,46 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>EL DÍA - Noticias de Bolivia para el mundo; El Potosí; La Razón Digital Bolivia; Opinión Bolivia</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
-        <v>-19.58</v>
-      </c>
-      <c r="N10" t="n">
-        <v>-65.75</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Potosí, Potosí</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
+          <t>El Deber; Red Uno</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPTGQwaVBfdG1JdVRMUTN4LVVvN0ppc3dreDJVVllDR3RmX0xpMzB4b0pvVTNSV1B6T0ZEWTdEZkNsRUdSNzhLaC1CWHN5WktNWk1nRWpTdVZiYjI3TlJlX2xlVTI5MjlRU2hiY1gteml4YWVFbDNPSVRBZmtITlQzbmhaUXVmcThRa2xsQTJIOXZuNzlSdm12MEdyOEZHdw?oc=5 | https://news.google.com/rss/articles/CBMizwFBVV95cUxPeGd3VWpCWXJ0YTJIeDJLcktzWG1jdUh0TjFXb01wSTkxbHNXZU94VWNDMkxnTjlJZVdpbkprMEY2NE80RXYyUWxUQXVnbl9lUXR2b28zTEh6cTJLVEQ4TUNja2kzRlhadVBFZFVwV1U2TlhseXZMZ20zZTZiUFpWRjdCOWNBMHU5XzdMV3JqQjV4TEE3bHRMOXR6Nm55eHZUNnFHSDdVRk8zVkY4RkVsUUtUN0JYdkREWGZncmJ3ZWc2T1BuUm1ZLTlfcHVabFE?oc=5 | https://news.google.com/rss/articles/CBMizAFBVV95cUxNYjNxaHg3YllRRTJYdFd1clAtUlROSGlFNVg5eUVZUGJoOEZ4MWM5QU5WQm1YTDc4NXc3SjhWMUw0TkZfSHlMLUQ1bmpTME1Kb1JaM0ExamFHYTd3VlU4MXRWdTZ1bzh1SGYtbGE1a3dBaG93bjg1OGc0S0JfRE43c3dVMVltN0dQQzNhQUNhM0FjVUNRUDRSamlJYlk2dEJpUTBuY2hBcTFucTVRN0ZtYnc5bzdmTV9LQm1uVUxaZS1tUE9IejhBVDRCdU_SAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOczZKbFd1QzRpak92LXpPWXZXQXJObnBQTG9qRFBlUUV5dThMWXhzckFFUHAyb2thU1JwRmJDSEZfaEdTUXh1bjZvQWpYMGhfUno3cWZ4MGpldEpoQXhzSlVzTm5LLW9OcjB2MWRsdHQ2UlI2SjEtZ085ZTR5Z3pEVmtBTF9lc29Kd0RhaTRUWkM4eGZJNWhBSXZqWmxuNW10dlQwYW9mdzItcWZWTkU0?oc=5 | https://news.google.com/rss/articles/CBMivAFBVV95cUxPczBQcnE2SzFGMXc3b1lsTkNxVWRmS3Vnb01xOTV2WmVva3J2RVlteWpHZ3VJS2dNWGV5NW5FX3ZncnVKTEVDTGpBRndTU1FxeWxtaS1fb1FscGxXMWNXUE9zbHdob1AxVFl1eHB5OU1yUnNoOXJ6U21oVG9PVDA1ak1xQl9hUlB4V0RaQXJqZENGUm8zMUJEY3J0WW5ENE5ObWJLNmpWN0RkSmFJbnZUZGR5UFRPd3QyUFY4WQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>noticia:1ukcn97</t>
+          <t>noticia:2avehj</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-24 13:26</t>
+          <t>2026-10-24 12:53</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1792862794000</v>
+        <v>1792860813000</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Esta es la lista preliminar de los heridos en el accidente del grupo 'Los chicos fieles', el conductor está grave - El Deber</t>
+          <t>Sequía en Cochabamba: más de un centenar de cabezas de ganado murieron en el cono sur - Red Uno</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>climatológica</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -1214,10 +1198,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1225,46 +1209,62 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>El Deber; Red Uno</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
+          <t>Red Uno</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>-17.39</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-66.16</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Cochabamba, Cochabamba</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOczZKbFd1QzRpak92LXpPWXZXQXJObnBQTG9qRFBlUUV5dThMWXhzckFFUHAyb2thU1JwRmJDSEZfaEdTUXh1bjZvQWpYMGhfUno3cWZ4MGpldEpoQXhzSlVzTm5LLW9OcjB2MWRsdHQ2UlI2SjEtZ085ZTR5Z3pEVmtBTF9lc29Kd0RhaTRUWkM4eGZJNWhBSXZqWmxuNW10dlQwYW9mdzItcWZWTkU0?oc=5 | https://news.google.com/rss/articles/CBMivAFBVV95cUxPczBQcnE2SzFGMXc3b1lsTkNxVWRmS3Vnb01xOTV2WmVva3J2RVlteWpHZ3VJS2dNWGV5NW5FX3ZncnVKTEVDTGpBRndTU1FxeWxtaS1fb1FscGxXMWNXUE9zbHdob1AxVFl1eHB5OU1yUnNoOXJ6U21oVG9PVDA1ak1xQl9hUlB4V0RaQXJqZENGUm8zMUJEY3J0WW5ENE5ObWJLNmpWN0RkSmFJbnZUZGR5UFRPd3QyUFY4WQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOOFQxc2Vzc0QwS19ydC13RkRPZnZQU3JkSTl5U3kzdUdMSldTcm5HVEhWRzZyN19CLUlwcUs4MW03Ui1obVBtdzQ3QWFQc1RKdzh3MXJ5QkpRS2pRNm50V1lVb09ScGJnaVVlemVfZlRsWjdObnRmR1FGMnlMMHAyc2pMandndy10T2twcWx6OFh4UHdvbVlFbllwME9WQ2pQVjNTQzBxeTg5YnF3bDREeHVDYXpObFFIaTZZQWtYUE12cGQ1ZGRhT0syNjVhZWs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>noticia:2avehj</t>
+          <t>noticia:3dv7b0</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-24 12:53</t>
+          <t>2026-10-24 11:43</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1792860813000</v>
+        <v>1792856591000</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sequía en Cochabamba: más de un centenar de cabezas de ganado murieron en el cono sur - Red Uno</t>
+          <t>Accidente en Caranavi: vehículo de Los Chicos Fieles cae a un barranco y deja varios heridos - FmBolivia</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>climatológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1287,62 +1287,62 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>FmBolivia; La Patria Bolivia; Red Uno</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>-17.39</v>
+        <v>-15.813</v>
       </c>
       <c r="N12" t="n">
-        <v>-66.16</v>
+        <v>-67.46299999999999</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Cochabamba, Cochabamba</t>
+          <t>Caranavi, La Paz</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Caranavi</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOOFQxc2Vzc0QwS19ydC13RkRPZnZQU3JkSTl5U3kzdUdMSldTcm5HVEhWRzZyN19CLUlwcUs4MW03Ui1obVBtdzQ3QWFQc1RKdzh3MXJ5QkpRS2pRNm50V1lVb09ScGJnaVVlemVfZlRsWjdObnRmR1FGMnlMMHAyc2pMandndy10T2twcWx6OFh4UHdvbVlFbllwME9WQ2pQVjNTQzBxeTg5YnF3bDREeHVDYXpObFFIaTZZQWtYUE12cGQ1ZGRhT0syNjVhZWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNeEFrOEtOMHZxMW42REFPU0x1MG5oQjlBMkJucWRLZ292alBXekJKeURBN3NLTVVadWI0OWF4UGtSVXBzTE01eWFSU1kyMUhNZ04zMWNMaUxnMDBBZ0EwTktXbjlaVTBUUmNqa3AwY19KNTU2LWh5LW9IVElVdTdnaHFPanJPd2FqMUxzaUhXZmVpYU1saGc?oc=5 | https://news.google.com/rss/articles/CBMi2wFBVV95cUxOdTVUZUQxVTdvYTdONDQxVlhUTzBOS2hKLW1rS1NUcmRYRnlCVlhIcHZlSjdsaktkQm5CWkFYa3lDQkxnMlh0b3prX0lha1BtbW1qS1VuYnNiX3FiZkYyNDJDR0tqZ0pKMU5TeC04SXV4UUJOTUlPUTB6ek01bzUxTUsydjZqZzI3S3ZLUnRWSUFUVk44WEpKUl9rbzRLb2IwYl9sLVlrYmt5d2ZHNUtGd3lRNnYzMlhuMkJOZW1XSUl2N1BxZWpHbm5XTDJhRUtnR190QWQ1TDlTUVk?oc=5 | https://news.google.com/rss/articles/CBMizAFBVV95cUxNcE1KaHZyUTJCSElxRU9nVzdhTnczWjJGTEhFMEs0bHp2cUdFeHd3VTB0NmVFcjdEN1dsZDZLY2k1ZFFUWkhKV19PU3V2czNyamh1ZE9YajVSVF8xczF6OFhZcWFvYV9EcWg4ZDNCb2p3enhXbFpRYnJMdGdaTXNrWUZSYVhKNTVicWlCLTJ5OE05Z1BvNEx1eEloUk5qTGN3ZHNzbzZWSVljbnRmSERJUWdxRDc0MjJxMGtycWJaaVhXQUUxVUlaWVZLOWE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>noticia:3dv7b0</t>
+          <t>clima:Potosí:2026-10-24:viento:1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-24 11:43</t>
+          <t>2026-10-24 10:55</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1792856591000</v>
+        <v>1792853727284</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Accidente en Caranavi: vehículo de Los Chicos Fieles cae a un barranco y deja varios heridos - FmBolivia</t>
+          <t>Potosí 2026-10-24: 60.5 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1365,57 +1365,57 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>FmBolivia; La Patria Bolivia; Red Uno</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>-15.813</v>
+        <v>-19.58</v>
       </c>
       <c r="N13" t="n">
-        <v>-67.46299999999999</v>
+        <v>-65.75</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Caranavi, La Paz</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Caranavi</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNeEFrOEtOMHZxMW42REFPU0x1MG5oQjlBMkJucWRLZ292alBXekJKeURBN3NLTVVadWI0OWF4UGtSVXBzTE01eWFSU1kyMUhNZ04zMWNMaUxnMDBBZ0EwTktXbjlaVTBUUmNqa3AwY19KNTU2LWh5LW9IVElVdTdnaHFPanJPd2FqMUxzaUhXZmVpYU1saGc?oc=5 | https://news.google.com/rss/articles/CBMi2wFBVV95cUxOdTVUZUQxVTdvYTdONDQxVlhUTzBOS2hKLW1rS1NUcmRYRnlCVlhIcHZlSjdsaktkQm5CWkFYa3lDQkxnMlh0b3prX0lha1BtbW1qS1VuYnNiX3FiZkYyNDJDR0tqZ0pKMU5TeC04SXV4UUJOTUlPUTB6ek01bzUxTUsydjZqZzI3S3ZLUnRWSUFUVk44WEpKUl9rbzRLb2IwYl9sLVlrYmt5d2ZHNUtGd3lRNnYzMlhuMkJOZW1XSUl2N1BxZWpHbm5XTDJhRUtnR190QWQ1TDlTUVk?oc=5 | https://news.google.com/rss/articles/CBMizAFBVV95cUxNcE1KaHZyUTJCSElxRU9nVzdhTnczWjJGTEhFMEs0bHp2cUdFeHd3VTB0NmVFcjdEN1dsZDZLY2k1ZFFUWkhKV19PU3V2czNyamh1ZE9YajVSVF8xczF6OFhZcWFvYV9EcWg4ZDNCb2p3enhXbFpRYnJMdGdaTXNrWUZSYVhKNTVicWlCLTJ5OE05Z1BvNEx1eEloUk5qTGN3ZHNzbzZWSVljbnRmSERJUWdxRDc0MjJxMGtycWJaaVhXQUUxVUlaWVZLOWE?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>clima:Potosí:2026-10-24:viento:1</t>
+          <t>noticia:1ax0bpy</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-24 10:55</t>
+          <t>2026-10-24 10:32</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1792853727284</v>
+        <v>1792852364000</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Potosí 2026-10-24: 60.5 km/h de ráfagas pronosticadas</t>
+          <t>Creció el Bermejo tras la tormenta: así está el puerto de chalanas en este momento - Que Pasa Salta</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1424,11 +1424,11 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1447,58 +1447,58 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>Que Pasa Salta</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>-19.58</v>
+        <v>-22.721</v>
       </c>
       <c r="N14" t="n">
-        <v>-65.75</v>
+        <v>-64.32599999999999</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Bermejo, Tarija</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Tarija</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Bermejo</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVld9IBfkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVldw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>noticia:1ax0bpy</t>
+          <t>gdacs:WF1033142:0</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-24 10:32</t>
+          <t>2026-10-24 07:06</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1792852364000</v>
+        <v>1792839995000</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Creció el Bermejo tras la tormenta: así está el puerto de chalanas en este momento - Que Pasa Salta</t>
+          <t>Green forest fire notification in Bolivia</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1525,58 +1525,58 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Que Pasa Salta</t>
+          <t>GDACS</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>-22.721</v>
+        <v>-13.06332</v>
       </c>
       <c r="N15" t="n">
-        <v>-64.32599999999999</v>
+        <v>-67.66426</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Bermejo, Tarija</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tarija</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Bermejo</t>
+          <t>Ixiamas</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVld9IBfkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVldw?oc=5</t>
+          <t>http://www.gdacs.org/report.aspx?eventtype=WF&amp;eventid=1033142</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>gdacs:WF1033142:0</t>
+          <t>noticia:1shhqva</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-24 07:06</t>
+          <t>2026-10-24 06:33</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1792839995000</v>
+        <v>1792838034000</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Green forest fire notification in Bolivia</t>
+          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1599,70 +1599,70 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>GDACS</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>-13.06332</v>
+        <v>-17.97</v>
       </c>
       <c r="N16" t="n">
-        <v>-67.66426</v>
+        <v>-67.11</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Oruro, Oruro</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Oruro</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Ixiamas</t>
+          <t>Oruro</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>http://www.gdacs.org/report.aspx?eventtype=WF&amp;eventid=1033142</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQYzB6N082XzFRRnVtcDVmUkYyWjcxUzV2Z3Frd1I0WDNXSnZtY0QzOU1PUkNLMktVT1Vra2FSeXhxZDRuOFZYZjFwejl6ejJTbWY2MGJuSGN3ZHdrdG5JUkgzSXBkbDYtaHlackY3OVFuNWdLcFNpdWNHRU9vNGdoVWx2ODFVdzJXYUxnM0tUcjJvZmc?oc=5 | https://news.google.com/rss/articles/CBMikAFBVV95cUxQS2FPaHd3UnFBRjRoa0lKUm1MNUQ5S00zN1RJZE5fWlVUQnhiY0lLcFRkY2JZak1mZ0c2WEVMVUNJVUJTMGFLNHg4S2ZKNTRqLXJHM09ET19hX1pZeTQwUkdEc2huTHVpcno2QTRZbnhralVRWXozcWc1a2pHUEpBeTV1cWgzTWRwaDEweURKeVE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>noticia:1shhqva</t>
+          <t>clima:Potosí:2026-10-25:viento:1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-24 06:33</t>
+          <t>2026-10-24 02:55</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1792838034000</v>
+        <v>1792824927736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
+          <t>Potosí 2026-10-25: 60.5 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1677,62 +1677,62 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>-17.97</v>
+        <v>-19.58</v>
       </c>
       <c r="N17" t="n">
-        <v>-67.11</v>
+        <v>-65.75</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQYzB6N082XzFRRnVtcDVmUkYyWjcxUzV2Z3Frd1I0WDNXSnZtY0QzOU1PUkNLMktVT1Vra2FSeXhxZDRuOFZYZjFwejl6ejJTbWY2MGJuSGN3ZHdrdG5JUkgzSXBkbDYtaHlackY3OVFuNWdLcFNpdWNHRU9vNGdoVWx2ODFVdzJXYUxnM0tUcjJvZmc?oc=5 | https://news.google.com/rss/articles/CBMikAFBVV95cUxQS2FPaHd3UnFBRjRoa0lKUm1MNUQ5S00zN1RJZE5fWlVUQnhiY0lLcFRkY2JZak1mZ0c2WEVMVUNJVUJTMGFLNHg4S2ZKNTRqLXJHM09ET19hX1pZeTQwUkdEc2huTHVpcno2QTRZbnhralVRWXozcWc1a2pHUEpBeTV1cWgzTWRwaDEweURKeVE?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>clima:Potosí:2026-10-25:viento:1</t>
+          <t>noticia:1uil931</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-24 02:55</t>
+          <t>2026-10-23 22:49</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1792824927736</v>
+        <v>1792810149000</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Potosí 2026-10-25: 60.5 km/h de ráfagas pronosticadas</t>
+          <t>Accidente de tránsito en la ruta hacia Alto Beni deja varios heridos - El Deber</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1755,62 +1755,62 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>El Deber</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>-19.58</v>
+        <v>-15.578</v>
       </c>
       <c r="N18" t="n">
-        <v>-65.75</v>
+        <v>-67.44</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Alto Beni, La Paz</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Alto Beni</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQakFJRmx3RlJEMkVHU0pxWXZ2ZU1ib04tZy1yeTB2OGhrYk9CU3pMaDVpRThNZktZMS14UzA2Y1VIcEQtZDg3cEU2SmlzQnBmUVVvM0ZNYzZWNExWUXQ3aHpnd3lqOHFVV3pNbDRLS1NQNGtwb2RjSFpleHJkOG5zSXVtWjVIS1dLejNybktRWTJVZXh3WkFUQVE5T2tMdFdn?oc=5 | https://news.google.com/rss/articles/CBMilwFBVV95cUxQMF9BNnUzLURKNGRMUUJ1VXVRSXNnMlBsQnVXOG0tRlFtY3pvRDNPQmNJMWN2RzJVaWdoWndmcHFnTkZFZnJxRkZtMThYYWlwN09ueUgtei1pSE1hZ2FtSzN6elY4VXJHbzFxdll0eWh0ZkxwQkQ1SDZ5b0E3MlVENGZEWGZHUGlwVG4wd2x3OFNEMVpibnFr?oc=5 | https://news.google.com/rss/articles/CBMimgFBVV95cUxNbmwzSnd6c2tFMXBWY0tiemJqRm5CNllOT2p1U0FhdW5QNGFBVXlSZVM1ak5jNGZvcXNVaUQzN3ZQQTlPbmVjQ2Y5RFl2dWVLeUN5NUFodDF0alEyZWlmOHFZWkVVbjdQbkl3ZWtmS25wQWM2TmRZZDBGM2xlS0ZhUzAweXRmcmhVWGY5dV9CUnFBNGtWZHZDSWVB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>noticia:1uil931</t>
+          <t>clima:Santa Cruz:2026-10-24:viento:1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-23 22:49</t>
+          <t>2026-10-23 20:55</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1792810149000</v>
+        <v>1792803329663</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Accidente de tránsito en la ruta hacia Alto Beni deja varios heridos - El Deber</t>
+          <t>Santa Cruz 2026-10-24: 78.1 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1825,7 +1825,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1833,57 +1833,57 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>El Deber</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>-15.578</v>
+        <v>-17.78</v>
       </c>
       <c r="N19" t="n">
-        <v>-67.44</v>
+        <v>-63.18</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Alto Beni, La Paz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Alto Beni</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQakFJRmx3RlJEMkVHU0pxWXZ2ZU1ib04tZy1yeTB2OGhrYk9CU3pMaDVpRThNZktZMS14UzA2Y1VIcEQtZDg3cEU2SmlzQnBmUVVvM0ZNYzZWNExWUXQ3aHpnd3lqOHFVV3pNbDRLS1NQNGtwb2RjSFpleHJkOG5zSXVtWjVIS1dLejNybktRWTJVZXh3WkFUQVE5T2tMdFdn?oc=5 | https://news.google.com/rss/articles/CBMilwFBVV95cUxQMF9BNnUzLURKNGRMUUJ1VXVRSXNnMlBsQnVXOG0tRlFtY3pvRDNPQmNJMWN2RzJVaWdoWndmcHFnTkZFZnJxRkZtMThYYWlwN09ueUgtei1pSE1hZ2FtSzN6elY4VXJHbzFxdll0eWh0ZkxwQkQ1SDZ5b0E3MlVENGZEWGZHUGlwVG4wd2x3OFNEMVpibnFr?oc=5 | https://news.google.com/rss/articles/CBMimgFBVV95cUxNbmwzSnd6c2tFMXBWY0tiemJqRm5CNllOT2p1U0FhdW5QNGFBVXlSZVM1ak5jNGZvcXNVaUQzN3ZQQTlPbmVjQ2Y5RFl2dWVLeUN5NUFodDF0alEyZWlmOHFZWkVVbjdQbkl3ZWtmS25wQWM2TmRZZDBGM2xlS0ZhUzAweXRmcmhVWGY5dV9CUnFBNGtWZHZDSWVB?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-24:viento:1</t>
+          <t>noticia:rabz5p</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-23 20:55</t>
+          <t>2026-10-23 20:44</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1792803329663</v>
+        <v>1792802686000</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-24: 78.1 km/h de ráfagas pronosticadas</t>
+          <t>Tome previsiones: se pronostican lluvias y ambiente caluroso para este fin de semana en Cochabamba - Red Uno</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1892,11 +1892,11 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1915,70 +1915,70 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>-17.78</v>
+        <v>-17.39</v>
       </c>
       <c r="N20" t="n">
-        <v>-63.18</v>
+        <v>-66.16</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTlU5NVFpY1RheTN5ZE1IbG5VYTh2Sk5hZHpHeWI3LVdnSFg2cFJFdnBCVkxiUjNKcUgyUW16SWxpMXFkMHdad2xFN043bklJeG1iQ0V1V3hBZk1Ga3NscjdPVWUySmt4bDNTdWlmSUdOMmNlZ2hkSWZFMmk4VGs0Nm9TcnRCTDhINmtnQU9zZDBUY05HcWpxN3FOX3N1dmVJblE0MGc5di1Ma1N2dGNxOUtoV1MzNnl1OXpRaTZ2UGxMc3RDWndubHVQNUd0eVROMGR2OGxVemtOaEc4bTNRaA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>noticia:rabz5p</t>
+          <t>noticia:1jfk053</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-23 20:44</t>
+          <t>2026-10-23 19:08</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1792802686000</v>
+        <v>1792796931000</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tome previsiones: se pronostican lluvias y ambiente caluroso para este fin de semana en Cochabamba - Red Uno</t>
+          <t>Sequía en Pasorapa: el ganado muere por falta de agua y alistan declaratoria de desastre - Red Uno</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>climatológica</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -1997,14 +1997,14 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>-17.39</v>
+        <v>-18.38</v>
       </c>
       <c r="N21" t="n">
-        <v>-66.16</v>
+        <v>-64.649</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Cochabamba, Cochabamba</t>
+          <t>Pasorapa, Cochabamba</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2014,49 +2014,49 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Pasorapa</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTlU5NVFpY1RheTN5ZE1IbG5VYTh2Sk5hZHpHeWI3LVdnSFg2cFJFdnBCVkxiUjNKcUgyUW16SWxpMXFkMHdad2xFN043bklJeG1iQ0V1V3hBZk1Ga3NscjdPVWUySmt4bDNTdWlmSUdOMmNlZ2hkSWZFMmk4VGs0Nm9TcnRCTDhINmtnQU9zZDBUY05HcWpxN3FOX3N1dmVJblE0MGc5di1Ma1N2dGNxOUtoV1MzNnl1OXpRaTZ2UGxMc3RDWndubHVQNUd0eVROMGR2OGxVemtOaEc4bTNRaA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNQVhTWE8zdE1BQ3lueWJPeV9wUDNsSmJpS0NJTWppMUY4QmlQSUFHVjRORmtrVHQ3MHB0T1pyS25PamxnY0hBQUtzOVRvSUNaUkdGb1RWSGl4dFA4Z3VINVpQTk1pZUpDdUIyUU5hZS1oNGhBa1RWcFhScVMwVTFrVlJaOFQ4OWFqRWVUZ051bHVJTlMxRTBhRFVLUEV2dTZFdDgtRkxJM3VvN3YzUWJfVk41ZWR5U1JoNmx0WFFkMmNTWGVleGNIQlNxWUJzdHIxSWtz?oc=5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>noticia:1jfk053</t>
+          <t>noticia:ix3l8o</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-23 19:08</t>
+          <t>2026-10-23 18:25</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1792796931000</v>
+        <v>1792794310000</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sequía en Pasorapa: el ganado muere por falta de agua y alistan declaratoria de desastre - Red Uno</t>
+          <t>Oruro evalúa suspender clases presenciales por más de 200 casos de Coxsackie - Visión 360</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>climatológica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -2067,77 +2067,77 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>Red Uno; Visión 360</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>-18.38</v>
+        <v>-17.97</v>
       </c>
       <c r="N22" t="n">
-        <v>-64.649</v>
+        <v>-67.11</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Pasorapa, Cochabamba</t>
+          <t>Oruro, Oruro</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Oruro</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Pasorapa</t>
+          <t>Oruro</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNQVhTWE8zdE1BQ3lueWJPeV9wUDNsSmJpS0NJTWppMUY4QmlQSUFHVjRORmtrVHQ3MHB0T1pyS25PamxnY0hBQUtzOVRvSUNaUkdGb1RWSGl4dFA4Z3VINVpQTk1pZUpDdUIyUU5hZS1oNGhBa1RWcFhScVMwVTFrVlJaOFQ4OWFqRWVUZ051bHVJTlMxRTBhRFVLUEV2dTZFdDgtRkxJM3VvN3YzUWJfVk41ZWR5U1JoNmx0WFFkMmNTWGVleGNIQlNxWUJzdHIxSWtz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0c9IBywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0cw?oc=5 | https://news.google.com/rss/articles/CBMiywFBVV95cUxNMFdHaVpKRmMyOENDYm16UXJPenVSQnpmTE94bDc4UFhqakluMUdvZjAwamUxT3BVWUpJQm8xVHBWengxQmhWM1hjU3d2YXFrLXpVU2VrZDJiMXZLMlQ5bGxGOHFETFhYM0s2RjlUTlhkd0g2eXQweDFHaTlKNGNMUlJfOWg2a0JjTklXUWZKc1BmUXZuZFZ2MF9fV2lEYUY4LXNiNmk3cF9FNjVtTl9GWFotT2ltS0xXTnM1dENvSU9kbFRMalFrYVdXOA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>noticia:ix3l8o</t>
+          <t>noticia:1xqv9m7</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-23 18:25</t>
+          <t>2026-10-23 18:09</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1792794310000</v>
+        <v>1792793370000</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Oruro evalúa suspender clases presenciales por más de 200 casos de Coxsackie - Visión 360</t>
+          <t>Tres heridos en tremendo choque cerca de Oncativo - El Diario del centro del país</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -2145,77 +2145,61 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Red Uno; Visión 360</t>
-        </is>
-      </c>
-      <c r="M23" t="n">
-        <v>-17.97</v>
-      </c>
-      <c r="N23" t="n">
-        <v>-67.11</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Oruro, Oruro</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Oruro</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>Oruro</t>
-        </is>
-      </c>
+          <t>El Diario del centro del país</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0c9IBywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0cw?oc=5 | https://news.google.com/rss/articles/CBMiywFBVV95cUxNMFdHaVpKRmMyOENDYm16UXJPenVSQnpmTE94bDc4UFhqakluMUdvZjAwamUxT3BVWUpJQm8xVHBWengxQmhWM1hjU3d2YXFrLXpVU2VrZDJiMXZLMlQ5bGxGOHFETFhYM0s2RjlUTlhkd0g2eXQweDFHaTlKNGNMUlJfOWg2a0JjTklXUWZKc1BmUXZuZFZ2MF9fV2lEYUY4LXNiNmk3cF9FNjVtTl9GWFotT2ltS0xXTnM1dENvSU9kbFRMalFrYVdXOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZERhbTJMQUJVb3hmZFlSZmRGZkdBLWdFTGJVQzdqZkE4aGhhWmdQZ2JDRW1ndkJLWU90VTZ6Ti1JOUZzcFZfcE1zbkRHU1B3YTF4UkVzdllFa1p3SUlObURGamF0Vm9kc3dPLTZVWFJ4NWZZQmlySElPNHhZTnRGNGNZUWw2ZlI1eVBEQkNGNEhLWTNiLWJLUS0xYjA0UWRhc0d6bVN4aVVLSVdsQWlpMUZYdWw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>noticia:1xqv9m7</t>
+          <t>noticia:1itd1r7</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-23 18:09</t>
+          <t>2026-10-23 15:01</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1792793370000</v>
+        <v>1792782098000</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tres heridos en tremendo choque cerca de Oncativo - El Diario del centro del país</t>
+          <t>Intensa lluvia y granizada en La Paz inundan vías y elevan el nivel de los ríos - eju.tv</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -2227,57 +2211,73 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>El Diario del centro del país</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
+          <t>eju.tv</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>-16.169</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-68.09</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>La Paz, La Paz</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>La Paz</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Nuestra Señora de La Paz</t>
+        </is>
+      </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZERhbTJMQUJVb3hmZFlSZmRGZkdBLWdFTGJVQzdqZkE4aGhhWmdQZ2JDRW1ndkJLWU90VTZ6Ti1JOUZzcFZfcE1zbkRHU1B3YTF4UkVzdllFa1p3SUlObURGamF0Vm9kc3dPLTZVWFJ4NWZZQmlySElPNHhZTnRGNGNZUWw2ZlI1eVBEQkNGNEhLWTNiLWJLUS0xYjA0UWRhc0d6bVN4aVVLSVdsQWlpMUZYdWw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNWU9QWElKQXEyN3UxVm4xbzJzbEJ1TU1NTHZlRUp6YndmeU9GQnJKcTluVEJ2ZHQ5cGp3aWhlMUd5ektWQlBpUVNmZnZuRnJwMXlydzAzX0FBVnY5UDMzQTBkWVRNRUNJSlRvX3MyQVhMcEhIMW9WSUpXckVSd0RJWk1KMFBKWmJNU3diQVlEN1Y5aVV6eVBaZXpOMnFIWWxaMlRlY0ZB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>noticia:1itd1r7</t>
+          <t>noticia:51709n</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-23 15:01</t>
+          <t>2026-10-23 13:38</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1792782098000</v>
+        <v>1792777139000</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Intensa lluvia y granizada en La Paz inundan vías y elevan el nivel de los ríos - eju.tv</t>
+          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - eju.tv</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2285,77 +2285,77 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>eju.tv</t>
+          <t>Red Uno; eju.tv</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>-16.169</v>
+        <v>-17.764</v>
       </c>
       <c r="N25" t="n">
-        <v>-68.09</v>
+        <v>-62.903</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>La Paz, La Paz</t>
+          <t>Cotoca, Santa Cruz</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>Nuestra Señora de La Paz</t>
+          <t>Cotoca</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNWU9QWElKQXEyN3UxVm4xbzJzbEJ1TU1NTHZlRUp6YndmeU9GQnJKcTluVEJ2ZHQ5cGp3aWhlMUd5ektWQlBpUVNmZnZuRnJwMXlydzAzX0FBVnY5UDMzQTBkWVRNRUNJSlRvX3MyQVhMcEhIMW9WSUpXckVSd0RJWk1KMFBKWmJNU3diQVlEN1Y5aVV6eVBaZXpOMnFIWWxaMlRlY0ZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPcjZTSmprRGVoNlRqQmdBTE5VM3pRQ1ZFakFUbzVyMUhiaDVkT0liaG9UNEZXekV6bWsycUk4X1JCSEY5RjhNVlZaTk9ULUFuZkY3NnZuWmZ1a19leUhFdlIyQV9kLWxlSkxfeXFhcFRTZjZ2YkpQQlJ1dkNLMDBjaGZ4SkhyQ0RfcnhKSEg5WURCQVQwbENYTHEzUzJSaUEzMGo2bWdyS3lsM016LXc?oc=5 | https://news.google.com/rss/articles/CBMi0AFBVV95cUxOVGY3YVRLWWxYM0IycjF4dlNUeUhqZG90Yng4aWhmN3A5ai02WENWYnF4bWpoZHFKMGc1X0JPRHdRRVZfSlA4UmZFa2kxYkNIS3ZtQ1NvNlNCME51eVZTRkRKSUQ5MmRoaWl5Tkt5NHpPUEFwemN2YTV1djFwdHlqQnFqRHNPenhYcTlsanJPcXhpOVV1NmFBUXZyazQ2MkUzM0dSZy02ZllxTGtjcl9ldzdHSktTRlVaalZJc1pubUNQMWFTbzVEOUJ1UmhCdEJt?oc=5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>noticia:51709n</t>
+          <t>noticia:11rddql</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-23 13:38</t>
+          <t>2026-10-23 13:22</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1792777139000</v>
+        <v>1792776139000</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - eju.tv</t>
+          <t>Intensifican acciones preventivas contra el dengue en Caranavi - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2363,77 +2363,77 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Red Uno; eju.tv</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>-17.764</v>
+        <v>-15.813</v>
       </c>
       <c r="N26" t="n">
-        <v>-62.903</v>
+        <v>-67.46299999999999</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Cotoca, Santa Cruz</t>
+          <t>Caranavi, La Paz</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Cotoca</t>
+          <t>Caranavi</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPcjZTSmprRGVoNlRqQmdBTE5VM3pRQ1ZFakFUbzVyMUhiaDVkT0liaG9UNEZXekV6bWsycUk4X1JCSEY5RjhNVlZaTk9ULUFuZkY3NnZuWmZ1a19leUhFdlIyQV9kLWxlSkxfeXFhcFRTZjZ2YkpQQlJ1dkNLMDBjaGZ4SkhyQ0RfcnhKSEg5WURCQVQwbENYTHEzUzJSaUEzMGo2bWdyS3lsM016LXc?oc=5 | https://news.google.com/rss/articles/CBMi0AFBVV95cUxOVGY3YVRLWWxYM0IycjF4dlNUeUhqZG90Yng4aWhmN3A5ai02WENWYnF4bWpoZHFKMGc1X0JPRHdRRVZfSlA4UmZFa2kxYkNIS3ZtQ1NvNlNCME51eVZTRkRKSUQ5MmRoaWl5Tkt5NHpPUEFwemN2YTV1djFwdHlqQnFqRHNPenhYcTlsanJPcXhpOVV1NmFBUXZyazQ2MkUzM0dSZy02ZllxTGtjcl9ldzdHSktTRlVaalZJc1pubUNQMWFTbzVEOUJ1UmhCdEJt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOMjhSeDJBek5iaFhDcnFzX1lKelgwZmUwLTJnbEhMdDRMelUxNks5Ti1pRHh3dDhTcC1YZEdqM3FJOGdqVHRvcXVhRlpCQzVDTEZMUFBkV1NrYVQ2LXRqTTBhcGRQc21CQ0VabzZaNExXb1BjTzJ2Uk5BcFF0VG5XOFNRa3lqUWlJSnRFUUVXYnNpbXB0LVVmSXVWSzJxcmVpdVVxUC1KOUhTQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>noticia:11rddql</t>
+          <t>noticia:fcm3nx</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-23 13:22</t>
+          <t>2026-10-23 12:58</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1792776139000</v>
+        <v>1792774699000</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Intensifican acciones preventivas contra el dengue en Caranavi - El Diario - Bolivia</t>
+          <t>[VIDEO] Así fue el accidente de moto que dejó un adolescente fallecido y un hombre gravemente herido - Red Uno</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2445,73 +2445,57 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
-        </is>
-      </c>
-      <c r="M27" t="n">
-        <v>-15.813</v>
-      </c>
-      <c r="N27" t="n">
-        <v>-67.46299999999999</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>Caranavi, La Paz</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>La Paz</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>Caranavi</t>
-        </is>
-      </c>
+          <t>Red Uno</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOMjhSeDJBek5iaFhDcnFzX1lKelgwZmUwLTJnbEhMdDRMelUxNks5Ti1pRHh3dDhTcC1YZEdqM3FJOGdqVHRvcXVhRlpCQzVDTEZMUFBkV1NrYVQ2LXRqTTBhcGRQc21CQ0VabzZaNExXb1BjTzJ2Uk5BcFF0VG5XOFNRa3lqUWlJSnRFUUVXYnNpbXB0LVVmSXVWSzJxcmVpdVVxUC1KOUhTQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOSmJMazhUemNfRHpWcDBoTVFZMUpwdlVKVUtvUXZNTGRRRHlwLW5KNmNhcmFnd1czbi1yalhFMnpSS1dmUE9jVzNlOS1kMWZtRzBHZ2EtcDRDdU5Gc2JUQVIwM2xPa2lZVmswRi1SUFVPcm8xcHlGN3F2UThTSDdKMDNyYnJmVkcxazNLLVBLOWFYM09FVUpmVnN5RVhpSVo2V1VCVmFwQ1gzTmRUWVp2aXMwcmxHRS1GV2p3NTBtR2RzM2wwVHUzaGJkRXJYbHdvaDlhWm5YMTk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>noticia:fcm3nx</t>
+          <t>noticia:1cjx1qd</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-23 12:58</t>
+          <t>2026-10-23 12:39</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1792774699000</v>
+        <v>1792773575000</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>[VIDEO] Así fue el accidente de moto que dejó un adolescente fallecido y un hombre gravemente herido - Red Uno</t>
+          <t>Más de 60 municipios en La Paz sufren falta de lluvias - La Patria Bolivia</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2523,37 +2507,53 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Red Uno</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
+          <t>La Patria Bolivia</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>-16.169</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-68.09</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>La Paz, La Paz</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>La Paz</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Nuestra Señora de La Paz</t>
+        </is>
+      </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOSmJMazhUemNfRHpWcDBoTVFZMUpwdlVKVUtvUXZNTGRRRHlwLW5KNmNhcmFnd1czbi1yalhFMnpSS1dmUE9jVzNlOS1kMWZtRzBHZ2EtcDRDdU5Gc2JUQVIwM2xPa2lZVmswRi1SUFVPcm8xcHlGN3F2UThTSDdKMDNyYnJmVkcxazNLLVBLOWFYM09FVUpmVnN5RVhpSVo2V1VCVmFwQ1gzTmRUWVp2aXMwcmxHRS1GV2p3NTBtR2RzM2wwVHUzaGJkRXJYbHdvaDlhWm5YMTk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE52Qi03Z1J6OS1CR2liRVZ0VlhCcmVQWFV6RUdGNXdrbzZRNXFjTWRaRnc1b3VoV0xaY3RIdncxNlNnYkxyUXo5MTlJWmMwWDNSMDE4ZHI2VkpWajFPaUF2SmRVYkk2eDZYQ1RfUU9ieENrZG9UVVFiaXZSeGI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>noticia:1cjx1qd</t>
+          <t>clima:Sucre:2026-10-23:viento:1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-23 12:39</t>
+          <t>2026-10-23 06:55</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1792773575000</v>
+        <v>1792752927735</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Más de 60 municipios en La Paz sufren falta de lluvias - La Patria Bolivia</t>
+          <t>Sucre 2026-10-23: 66.2 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2562,11 +2562,11 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -2585,40 +2585,40 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>-16.169</v>
+        <v>-19.03</v>
       </c>
       <c r="N29" t="n">
-        <v>-68.09</v>
+        <v>-65.26000000000001</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>La Paz, La Paz</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Chuquisaca</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>Nuestra Señora de La Paz</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE52Qi03Z1J6OS1CR2liRVZ0VlhCcmVQWFV6RUdGNXdrbzZRNXFjTWRaRnc1b3VoV0xaY3RIdncxNlNnYkxyUXo5MTlJWmMwWDNSMDE4ZHI2VkpWajFPaUF2SmRVYkk2eDZYQ1RfUU9ieENrZG9UVVFiaXZSeGI?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>clima:Sucre:2026-10-23:viento:1</t>
+          <t>clima:Santa Cruz:2026-10-24:viento:2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2627,11 +2627,11 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1792752927735</v>
+        <v>1792752927734</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sucre 2026-10-23: 66.2 km/h de ráfagas pronosticadas</t>
+          <t>Santa Cruz 2026-10-24: 85 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2640,11 +2640,11 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -2667,24 +2667,24 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>-19.03</v>
+        <v>-17.78</v>
       </c>
       <c r="N30" t="n">
-        <v>-65.26000000000001</v>
+        <v>-63.18</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Chuquisaca</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2696,33 +2696,33 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-24:viento:2</t>
+          <t>usgs:us6000u49c</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-23 06:55</t>
+          <t>2026-10-22 22:45</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1792752927734</v>
+        <v>1792723541183</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-24: 85 km/h de ráfagas pronosticadas</t>
+          <t>Sismo M 4.5 - 58 km SW of Atocha, Bolivia</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>geológica</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -2741,58 +2741,58 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>USGS</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>-17.78</v>
+        <v>-21.3469</v>
       </c>
       <c r="N31" t="n">
-        <v>-63.18</v>
+        <v>-66.5795</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>58 km SW of Atocha, Bolivia</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>San Pablo</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://earthquake.usgs.gov/earthquakes/eventpage/us6000u49c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>usgs:us6000u49c</t>
+          <t>clima:Santa Cruz:2026-10-22:viento:1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-22 22:45</t>
+          <t>2026-10-22 21:55</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1792723541183</v>
+        <v>1792720528712</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sismo M 4.5 - 58 km SW of Atocha, Bolivia</t>
+          <t>Santa Cruz 2026-10-22: 67.7 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>geológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -2819,40 +2819,40 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>USGS</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>-21.3469</v>
+        <v>-17.78</v>
       </c>
       <c r="N32" t="n">
-        <v>-66.5795</v>
+        <v>-63.18</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>58 km SW of Atocha, Bolivia</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>San Pablo</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>https://earthquake.usgs.gov/earthquakes/eventpage/us6000u49c</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-22:viento:1</t>
+          <t>clima:Santa Cruz:2026-10-23:viento:2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-22: 67.7 km/h de ráfagas pronosticadas</t>
+          <t>Santa Cruz 2026-10-23: 83.9 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2874,11 +2874,11 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -2930,33 +2930,33 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-23:viento:2</t>
+          <t>noticia:1hhvre7</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-22 21:55</t>
+          <t>2026-10-22 19:36</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1792720528712</v>
+        <v>1792712202000</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-23: 83.9 km/h de ráfagas pronosticadas</t>
+          <t>Virgen de Cotoca: Controlan incendio en depósito de materiales plásticos - El Mundo Bolivia</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -2975,53 +2975,53 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>El Mundo Bolivia</t>
         </is>
       </c>
       <c r="M34" t="n">
-        <v>-17.78</v>
+        <v>-17.764</v>
       </c>
       <c r="N34" t="n">
-        <v>-63.18</v>
+        <v>-62.903</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
+          <t>Cotoca, Santa Cruz</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
           <t>Santa Cruz</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Santa Cruz</t>
-        </is>
-      </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Cotoca</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcDF6VE5FNzRaWGRuUzFKeXhnZ21DZTRaaEtrVEJEa1Z3ejg2VG1ONG1ENmlDWlkyVjlkQkJwS2F1XzBGMFQwSHd4OEwxTW1PbHdGcUh1ckV6SGpDd2hiN0dkeUVTcnFXT3RjOU1kLXZtVVdZY2hkZS1pcVpVUFhnRktqcHY5UnBrY0xUMDRETjl6N0pXT3A5amxhMA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>noticia:1hhvre7</t>
+          <t>noticia:bksnde</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-22 19:36</t>
+          <t>2026-10-22 17:01</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1792712202000</v>
+        <v>1792702880000</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Virgen de Cotoca: Controlan incendio en depósito de materiales plásticos - El Mundo Bolivia</t>
+          <t>Reportan un incendio cerca de la carretera a Cotoca - eju.tv</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>El Mundo Bolivia</t>
+          <t>eju.tv</t>
         </is>
       </c>
       <c r="M35" t="n">
@@ -3079,27 +3079,27 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcDF6VE5FNzRaWGRuUzFKeXhnZ21DZTRaaEtrVEJEa1Z3ejg2VG1ONG1ENmlDWlkyVjlkQkJwS2F1XzBGMFQwSHd4OEwxTW1PbHdGcUh1ckV6SGpDd2hiN0dkeUVTcnFXT3RjOU1kLXZtVVdZY2hkZS1pcVpVUFhnRktqcHY5UnBrY0xUMDRETjl6N0pXT3A5amxhMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPNGtpbnBfRnRBalVudnBlZHdVQ0ZSaUplZmtvTGE0aTQzdkxWS3d4My1EZEJ1UE9FNFQ3RmpyZGVsbS1qNEM1QUVFRFAxM2pYT1VqQzRuVjRtZnVNUGlKODNMc0F1a3l6TUpuQmtlUWNlVTVEWWU5ZGZtQm5LWUp3Sg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>noticia:bksnde</t>
+          <t>noticia:17hz69v</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-22 17:01</t>
+          <t>2026-10-22 13:05</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1792702880000</v>
+        <v>1792688709000</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Reportan un incendio cerca de la carretera a Cotoca - eju.tv</t>
+          <t>Accidente en El Sillar deja al menos 29 heridos - La Razón Digital Bolivia</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3108,18 +3108,18 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -3131,53 +3131,37 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>eju.tv</t>
-        </is>
-      </c>
-      <c r="M36" t="n">
-        <v>-17.764</v>
-      </c>
-      <c r="N36" t="n">
-        <v>-62.903</v>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>Cotoca, Santa Cruz</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Santa Cruz</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>Cotoca</t>
-        </is>
-      </c>
+          <t>La Razón Digital Bolivia</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPNGtpbnBfRnRBalVudnBlZHdVQ0ZSaUplZmtvTGE0aTQzdkxWS3d4My1EZEJ1UE9FNFQ3RmpyZGVsbS1qNEM1QUVFRFAxM2pYT1VqQzRuVjRtZnVNUGlKODNMc0F1a3l6TUpuQmtlUWNlVTVEWWU5ZGZtQm5LWUp3Sg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPaXhTdm45YWZnWVFxVzJnb1ZwbUN4SmUtLVdJN0VJdFZBamRyQmFxN0RZelBfTklaSTVyOUZ3ajQ5MFB2TEN4Ukd6TE5ORFY5SEROVk1CZ25sRWJ1QnRBdTVfTktlby1NWXhaVWI5YnRvaDZWbHVjdDVoeFp5Tk5veFk5a19MSWJqcEJVV0dzV3k?oc=5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>noticia:17hz69v</t>
+          <t>noticia:1f1qb0</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-22 13:05</t>
+          <t>2026-10-22 12:09</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1792688709000</v>
+        <v>1792685373000</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Accidente en El Sillar deja al menos 29 heridos - La Razón Digital Bolivia</t>
+          <t>Accidente en el tramo Locotal–Villa Tunari: la vía está transitable con precaución - Red Uno</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3186,18 +3170,18 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -3209,57 +3193,73 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>La Razón Digital Bolivia</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
+          <t>Red Uno</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>-16.556</v>
+      </c>
+      <c r="N37" t="n">
+        <v>-65.569</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Villa Tunari, Cochabamba</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Villa Tunari</t>
+        </is>
+      </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPaXhTdm45YWZnWVFxVzJnb1ZwbUN4SmUtLVdJN0VJdFZBamRyQmFxN0RZelBfTklaSTVyOUZ3ajQ5MFB2TEN4Ukd6TE5ORFY5SEROVk1CZ25sRWJ1QnRBdTVfTktlby1NWXhaVWI5YnRvaDZWbHVjdDVoeFp5Tk5veFk5a19MSWJqcEJVV0dzV3k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTFozcEEwNXBqV19sS2VibXh0MGt0QlhsX1djSTFGQW5zNlFLRHZpNVVnZ1JmWDQ4LVRHX2Rmb3B5UU9qV0FZQmJCaUZYdmwyNG1NenJ4Qzlzd0NJTGs1SjMxdFRtRFBzSUkybGJfZFFaNFZBc21FSUJYSFVkQkVkSEhQaGw0UFVzeXctZHo3cjNsYm5weXJlOU1wcmFncnNhMC1BQUpvNWlDX1NxZXU4b09kVFFWR2tSVEk2UTdXXzB3TjA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>noticia:1f1qb0</t>
+          <t>noticia:wi18tm</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-22 12:09</t>
+          <t>2026-10-22 11:53</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1792685373000</v>
+        <v>1792684426000</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Accidente en el tramo Locotal–Villa Tunari: la vía está transitable con precaución - Red Uno</t>
+          <t>Accidente en El Sillar deja heridos y derrame de combustible: esto es lo último que se sabe - Red Uno</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>tecnológica</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -3274,70 +3274,54 @@
           <t>Red Uno</t>
         </is>
       </c>
-      <c r="M38" t="n">
-        <v>-16.556</v>
-      </c>
-      <c r="N38" t="n">
-        <v>-65.569</v>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>Villa Tunari, Cochabamba</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>Villa Tunari</t>
-        </is>
-      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTFozcEEwNXBqV19sS2VibXh0MGt0QlhsX1djSTFGQW5zNlFLRHZpNVVnZ1JmWDQ4LVRHX2Rmb3B5UU9qV0FZQmJCaUZYdmwyNG1NenJ4Qzlzd0NJTGs1SjMxdFRtRFBzSUkybGJfZFFaNFZBc21FSUJYSFVkQkVkSEhQaGw0UFVzeXctZHo3cjNsYm5weXJlOU1wcmFncnNhMC1BQUpvNWlDX1NxZXU4b09kVFFWR2tSVEk2UTdXXzB3TjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPZHNBTEdaQm5Wby1lTF9mWlQ2aGg0MVc4S0MwVWJ3dUJ5WWU5X3IwYWhKRjk5VWtYWEJHRDF4QldVc29laVNPSTJNWFBDSkNFQlFSYTJUXzNMNF9hckFBN1I2T2xoQUtYQ2V6MDNTZHhHVk9qeTBCdHRpM2ZLd0pyOFRweUUxX19STzRHTHg5VUY5d1lhS0tDeXpCdklqcTZGT1J4R0xnSDhoak1EZ2dtNUhSTUV6b1o0U0VSdWY5X0E3U05Tc1dYVEN2WFZUeFhPMTBJTmowNA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>noticia:wi18tm</t>
+          <t>noticia:12gfagq</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-22 11:53</t>
+          <t>2026-10-22 11:28</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1792684426000</v>
+        <v>1792682880000</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Accidente en El Sillar deja heridos y derrame de combustible: esto es lo último que se sabe - Red Uno</t>
+          <t>Reportan triple colisión entre dos camiones y un bus en la carretera Cochabamba-Santa Cruz - FmBolivia</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>tecnológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -3345,41 +3329,57 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Red Uno</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
+          <t>FmBolivia; Red Uno</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>-17.39</v>
+      </c>
+      <c r="N39" t="n">
+        <v>-66.16</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Cochabamba, Cochabamba</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPZHNBTEdaQm5Wby1lTF9mWlQ2aGg0MVc4S0MwVWJ3dUJ5WWU5X3IwYWhKRjk5VWtYWEJHRDF4QldVc29laVNPSTJNWFBDSkNFQlFSYTJUXzNMNF9hckFBN1I2T2xoQUtYQ2V6MDNTZHhHVk9qeTBCdHRpM2ZLd0pyOFRweUUxX19STzRHTHg5VUY5d1lhS0tDeXpCdklqcTZGT1J4R0xnSDhoak1EZ2dtNUhSTUV6b1o0U0VSdWY5X0E3U05Tc1dYVEN2WFZUeFhPMTBJTmowNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNMTNBaFZNMU9SR25vdVBuNXlZY3g4VkFWYXRiQnNSaUFjemZhUHZWNHg4V2owU2xfNndBak94TnU2cHNUVXdNNWl2eUdHZVNMbVZweTR5M0o0bWdTNUN4QkoxUkI2TDBmVE03M09zRGhJRVFzV0tPZ1NCWEJLUkt1ZGN4UGduOUZMQnJoM0tMYTh0ZlFxaFJNUkJqaWFPazRlMzN3ajhjUEdUYXlZRndpb3RSdTFCX2tCZGJxQ0x4SlBISWJsRVoyN3ZR?oc=5 | https://news.google.com/rss/articles/CBMirwFBVV95cUxNNUROMzd1UDJRWVZZQ011cFd2c1FSdER1ZzdleU04cXpwYk5HaUZrLXoyU2NzdFk1dnNRUndhUWt0cG9DX09rSjlLcDItU0tzcmQtS3E4dDQ4ZF9HdGJLdk13ek9BNHJUWVlCcklrM25rZ01RbXhLalRBT1FGdDNReHdlTFZkNkJ5ZFd3N3NZVFVmOFUxbEhHN0RsaUxiSVZsM0lXVEFYSHVRQlhsOEtJ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>noticia:12gfagq</t>
+          <t>noticia:1jl2oid</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-22 11:28</t>
+          <t>2026-10-22 07:49</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1792682880000</v>
+        <v>1792669785000</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Reportan triple colisión entre dos camiones y un bus en la carretera Cochabamba-Santa Cruz - FmBolivia</t>
+          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - eju.tv</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3388,18 +3388,18 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -3411,73 +3411,73 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>FmBolivia; Red Uno</t>
+          <t>Red Uno; eju.tv</t>
         </is>
       </c>
       <c r="M40" t="n">
-        <v>-17.39</v>
+        <v>-17.781</v>
       </c>
       <c r="N40" t="n">
-        <v>-66.16</v>
+        <v>-63.139</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Cochabamba, Cochabamba</t>
+          <t>Santa Cruz, Santa Cruz</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNMTNBaFZNMU9SR25vdVBuNXlZY3g4VkFWYXRiQnNSaUFjemZhUHZWNHg4V2owU2xfNndBak94TnU2cHNUVXdNNWl2eUdHZVNMbVZweTR5M0o0bWdTNUN4QkoxUkI2TDBmVE03M09zRGhJRVFzV0tPZ1NCWEJLUkt1ZGN4UGduOUZMQnJoM0tMYTh0ZlFxaFJNUkJqaWFPazRlMzN3ajhjUEdUYXlZRndpb3RSdTFCX2tCZGJxQ0x4SlBISWJsRVoyN3ZR?oc=5 | https://news.google.com/rss/articles/CBMirwFBVV95cUxNNUROMzd1UDJRWVZZQ011cFd2c1FSdER1ZzdleU04cXpwYk5HaUZrLXoyU2NzdFk1dnNRUndhUWt0cG9DX09rSjlLcDItU0tzcmQtS3E4dDQ4ZF9HdGJLdk13ek9BNHJUWVlCcklrM25rZ01RbXhLalRBT1FGdDNReHdlTFZkNkJ5ZFd3N3NZVFVmOFUxbEhHN0RsaUxiSVZsM0lXVEFYSHVRQlhsOEtJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQbTBrUmlla3FvVU1EX1pxcUI3SXYzbUFFMzlnRzhlSDJwMGpWWURxYjIwSkJBRGdCazMzT01hVy1qMFY3RnJLbC1XNXJ4bU55aDJVeXpNUlRsbzQ3T3hiRXJ5SWlhNmw5cDZFanNoWFBtQ01Gd3dscXltWmU5VHBSQlN3c2IwNGxuVE5tQ3lOT1RmNzRiVi1hc0hn?oc=5 | https://news.google.com/rss/articles/CBMiuwFBVV95cUxNVEh1bFlCanFuOTJid2EzYS1meG5oekFJcGFaME1fTk9sUnZpd3U0UXFHUFVJSW1jc1hzM2VFOFprT2xNYjBzbmswZmdJV3dremRIS0I4MDNzRjBnbEttWEhfOWZBbmFrRnNHWDFVLVFoM0VkZkxkaW4tMmZlSFJLei1heTFHMU0wSmxQVVRZN0cwaXQzcDBtZkdwTUFma0RXU2dwLXRnLTBkNGN3Vm1fV3hEdlM1dWZ1SEsw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>noticia:1jl2oid</t>
+          <t>noticia:n32ahi</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-22 07:49</t>
+          <t>2026-10-22 05:30</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1792669785000</v>
+        <v>1792661402000</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - eju.tv</t>
+          <t>Senamhi anuncia el inicio de la temporada de lluvias en Bolivia y prevé granizadas como la de La Paz - FmBolivia</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -3485,113 +3485,35 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Red Uno; eju.tv</t>
+          <t>FmBolivia</t>
         </is>
       </c>
       <c r="M41" t="n">
-        <v>-17.781</v>
+        <v>-16.169</v>
       </c>
       <c r="N41" t="n">
-        <v>-63.139</v>
+        <v>-68.09</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Santa Cruz, Santa Cruz</t>
+          <t>La Paz, La Paz</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Nuestra Señora de La Paz</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQbTBrUmlla3FvVU1EX1pxcUI3SXYzbUFFMzlnRzhlSDJwMGpWWURxYjIwSkJBRGdCazMzT01hVy1qMFY3RnJLbC1XNXJ4bU55aDJVeXpNUlRsbzQ3T3hiRXJ5SWlhNmw5cDZFanNoWFBtQ01Gd3dscXltWmU5VHBSQlN3c2IwNGxuVE5tQ3lOT1RmNzRiVi1hc0hn?oc=5 | https://news.google.com/rss/articles/CBMiuwFBVV95cUxNVEh1bFlCanFuOTJid2EzYS1meG5oekFJcGFaME1fTk9sUnZpd3U0UXFHUFVJSW1jc1hzM2VFOFprT2xNYjBzbmswZmdJV3dremRIS0I4MDNzRjBnbEttWEhfOWZBbmFrRnNHWDFVLVFoM0VkZkxkaW4tMmZlSFJLei1heTFHMU0wSmxQVVRZN0cwaXQzcDBtZkdwTUFma0RXU2dwLXRnLTBkNGN3Vm1fV3hEdlM1dWZ1SEsw?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>noticia:n32ahi</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-10-22 05:30</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>1792661402000</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Senamhi anuncia el inicio de la temporada de lluvias en Bolivia y prevé granizadas como la de La Paz - FmBolivia</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>meteorológica</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K42" t="n">
-        <v>1</v>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>FmBolivia</t>
-        </is>
-      </c>
-      <c r="M42" t="n">
-        <v>-16.169</v>
-      </c>
-      <c r="N42" t="n">
-        <v>-68.09</v>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>La Paz, La Paz</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>La Paz</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>Nuestra Señora de La Paz</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQNmVPRnVBMGQzdEI5SUp3Z3ZGVExwTUR6TWNadGQ1QldUS1o2QVFvUl9sVEZKMDVyQVVrS25rU1RSQlJKWXk1YzE0NUhidjhpcmFaSlhZUDZvcE9XcG1KTFNTYmowUU1CSFJNOVR2UHNmMk1iT3N0RVBteHkzZkgyRFROYk1pdkpxVHZya3N2X2FVLVQxbURFVVZlb1NzRjZzTE95TXFVUXFJNkVZakQ2bUhVQzB0SXk3TVhXUTJXa0dycTE1MWVQRFpDX3lDSWFqUGwzU2NtNA?oc=5</t>
         </is>
@@ -3608,7 +3530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S59"/>
+  <dimension ref="A1:S60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3711,7 +3633,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>noticia:1at00ey</t>
+          <t>noticia:oww2zc</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3721,11 +3643,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-25 11:19</t>
+          <t>2026-10-25 12:08</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1792941547000</v>
+        <v>1792944531000</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3747,13 +3669,13 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Dos cisternas chocan y provocan voraz incendio en la ruta a Camiri - Red Uno</t>
+          <t>Cierran la carretera a Camiri: dos cisternas chocan y provocan un voraz incendio - Red Uno</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPTTF0OUdVS1c1a0lZWmk3bGxHdDJIalpWZTRyQTY3eWE2a2dWOHlsaldKZXpSLWN5c3BkUWdBRkJuSzhHdWl2ZjgwTFFFYnd0aTAxZ3dJU0hCekNZNm9aTTJSZUNfQjVIM3FrUUJ4NXAwa3paZ3BEek9xTVZNQWdnN01xRHloV1ZXZHV6N0JpUWo3RE9DMlFGdkNnWkloTjVVY3RBR1RSRUJJWFVtby1fMWFMNTdLZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQLXlqSFdvWUVhQUNadnpkdE5lUTZQS0lobThzUTZWbDNJTE94alVhaDBaYU9Fd09SSGt3UlR3Y0dfZlNIcml1ZktnWjctNk1Na3V4S0tINFNkMXM0OHBoV2lCTTBiYXlPUTA3T2ZkeXE2RElYWjhfVHd3Nng1Z0E4alBmOFI5NDFwX09kazZlSWl2OVR2ZVR6MDhvSHFnSmJKbTFXSEFDNFFYcWVDNGtYWEQ0bDhJel9CaEpEZWZ4SWN0TE9Ya0E?oc=5</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -3792,7 +3714,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>noticia:1uf38hl</t>
+          <t>noticia:1at00ey</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3802,11 +3724,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-25 10:59</t>
+          <t>2026-10-25 11:19</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1792940350000</v>
+        <v>1792941547000</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -3828,13 +3750,13 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>¡Cisterna con combustible en llamas! Reportan impresionante incendio en la carretera a Camiri - Red Uno</t>
+          <t>Dos cisternas chocan y provocan voraz incendio en la ruta a Camiri - Red Uno</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxORUhqeWpKY1FHRWoxaHN0UXFzS3dpeHh6N0NwLUJOZTlZcDVoNHN0VnI0by1qMWtZZEkxVmtUNjdNTFhjaEFQU2IyMlNwZW95WFBzbFJPVVB6TjJtdjNENk1LWVlsMUxUUzBNVzkxRk1HZ3lQU0s2M1lRVlRuaXlkMmJrd3AyTGpIdXItNkhlU3dhTzBRME56Rm1DSlZCYjNxSnNTbTFqNWRoUkdraHhlREhuYldqeFk2N3poWEx2M08?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPTTF0OUdVS1c1a0lZWmk3bGxHdDJIalpWZTRyQTY3eWE2a2dWOHlsaldKZXpSLWN5c3BkUWdBRkJuSzhHdWl2ZjgwTFFFYnd0aTAxZ3dJU0hCekNZNm9aTTJSZUNfQjVIM3FrUUJ4NXAwa3paZ3BEek9xTVZNQWdnN01xRHloV1ZXZHV6N0JpUWo3RE9DMlFGdkNnWkloTjVVY3RBR1RSRUJJWFVtby1fMWFMNTdLZw?oc=5</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -3873,7 +3795,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>noticia:1sg8pi0</t>
+          <t>noticia:1uf38hl</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3883,11 +3805,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-25 09:59</t>
+          <t>2026-10-25 10:59</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1792936752000</v>
+        <v>1792940350000</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -3909,13 +3831,13 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Bus de agrupación musical sufre accidente rumbo al trópico de Cochabamba | VIDEO - Red Uno</t>
+          <t>¡Cisterna con combustible en llamas! Reportan impresionante incendio en la carretera a Camiri - Red Uno</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOVDVzVTJNM2JuQ25sMThEaVZNOUNRd3FGT3RhVnFrZXZ2NDQ1YlluTVdhbVNUQnA1MGNESHRSWVUzbC1kRVh3OTR0emtlTG91cmRWeFJ5dk5zb3p2WFRyMEJUV3FNRnY1WHhRUU9WLTlJcmNyNXJZZFdoM0JoZjNpa3hjUXhMM0xrUDJab2VadkM5RWZYQ3lWZTVDdzg1akxJT2lxcDVNNzI0NG1hejdfdkUyTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxORUhqeWpKY1FHRWoxaHN0UXFzS3dpeHh6N0NwLUJOZTlZcDVoNHN0VnI0by1qMWtZZEkxVmtUNjdNTFhjaEFQU2IyMlNwZW95WFBzbFJPVVB6TjJtdjNENk1LWVlsMUxUUzBNVzkxRk1HZ3lQU0s2M1lRVlRuaXlkMmJrd3AyTGpIdXItNkhlU3dhTzBRME56Rm1DSlZCYjNxSnNTbTFqNWRoUkdraHhlREhuYldqeFk2N3poWEx2M08?oc=5</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -3925,14 +3847,14 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-17.39</v>
+        <v>-20.05</v>
       </c>
       <c r="O4" t="n">
-        <v>-66.16</v>
+        <v>-63.486</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Cochabamba, Cochabamba</t>
+          <t>Camiri, Santa Cruz</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -3942,19 +3864,19 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Camiri</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>noticia:167wlhz</t>
+          <t>noticia:1sg8pi0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3964,11 +3886,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-25 07:53</t>
+          <t>2026-10-25 09:59</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1792929231000</v>
+        <v>1792936752000</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -3977,7 +3899,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -3990,13 +3912,13 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>¡A sacar el paraguas! Santa cruz amanece con lluvia, frío y complicaciones en el tránsito vehicular - Red Uno</t>
+          <t>Bus de agrupación musical sufre accidente rumbo al trópico de Cochabamba | VIDEO - Red Uno</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOY1ZpYktLR3pUQXotUndVR3puUzVHbW1YTzNyUmJvUHB4Q2JmelRvOEdaRldOUm1xLVJnbGR5VWcxTjNEM3ZUYktCUWtVM0hKSjFuRGdpX0JxN0M5MVZBSG1aVURyVWktdmxwbUtRT19ydU5LdzNTZ2Zpb2ozdHlMUUdTVlAyVk4xODBnV0hyTXdVVndyNzV3VC1KMzFnV3lpcFFXSk9MdDZOTWlWakNwT1FnNDh6QVdjazVYZDVVMkdaLU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOVDVzVTJNM2JuQ25sMThEaVZNOUNRd3FGT3RhVnFrZXZ2NDQ1YlluTVdhbVNUQnA1MGNESHRSWVUzbC1kRVh3OTR0emtlTG91cmRWeFJ5dk5zb3p2WFRyMEJUV3FNRnY1WHhRUU9WLTlJcmNyNXJZZFdoM0JoZjNpa3hjUXhMM0xrUDJab2VadkM5RWZYQ3lWZTVDdzg1akxJT2lxcDVNNzI0NG1hejdfdkUyTQ?oc=5</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -4006,14 +3928,14 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-17.781</v>
+        <v>-17.39</v>
       </c>
       <c r="O5" t="n">
-        <v>-63.139</v>
+        <v>-66.16</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Santa Cruz, Santa Cruz</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -4023,19 +3945,19 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Cochabamba</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>noticia:bzr7eh</t>
+          <t>noticia:167wlhz</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4045,39 +3967,39 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-25 07:09</t>
+          <t>2026-10-25 07:53</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1792926572000</v>
+        <v>1792929231000</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>hidrológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Alerta naranja por riesgo de desbordes de ríos - El Diario - Bolivia</t>
+          <t>¡A sacar el paraguas! Santa cruz amanece con lluvia, frío y complicaciones en el tránsito vehicular - Red Uno</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNNGZKSDVaZkowWUFGSEUyTWR3d3dsc04waFBLLWUtcVpiTDYzbmNtYTN1RkFLbjAwN3dxT0xZc3pqc3REUXduZVltQ2Fud1BZLTh1bTNiTEJueVUwV0dERS1iUXZqMHd0UnFrQ3E2SFAzbm5lQ1I4U29MaHJFbWFvdVRTeFY4Wl9rSmc3RkpaQ2xwX0oz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOY1ZpYktLR3pUQXotUndVR3puUzVHbW1YTzNyUmJvUHB4Q2JmelRvOEdaRldOUm1xLVJnbGR5VWcxTjNEM3ZUYktCUWtVM0hKSjFuRGdpX0JxN0M5MVZBSG1aVURyVWktdmxwbUtRT19ydU5LdzNTZ2Zpb2ozdHlMUUdTVlAyVk4xODBnV0hyTXdVVndyNzV3VC1KMzFnV3lpcFFXSk9MdDZOTWlWakNwT1FnNDh6QVdjazVYZDVVMkdaLU0?oc=5</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -4086,21 +4008,37 @@
       <c r="M6" t="n">
         <v>0</v>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>-17.781</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-63.139</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Santa Cruz, Santa Cruz</t>
+        </is>
+      </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Santa Cruz de la Sierra</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>noticia:1fo4ig4</t>
+          <t>noticia:bzr7eh</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4110,43 +4048,43 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-25 01:08</t>
+          <t>2026-10-25 07:09</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1792904880000</v>
+        <v>1792926572000</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>diarioelpueblo.com.pe</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>hidrológica</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>roja</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
+          <t>Alerta naranja por riesgo de desbordes de ríos - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQcmFrT3dwcEs0X3U2NWxnOGJwNnI2WHdWTGZYbzEyNnJzUWhkbU9TRWhfSlB5UkMwX2gyMmxYUmVNWmxNOVR6V0twRHpFMTVIYjBKbHQ2TXN2d2w5dkFpcWJCcUJMZldaX01sNWtQV2ZJOGpRVzR3NDVIU0pJc1BNVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNNGZKSDVaZkowWUFGSEUyTWR3d3dsc04waFBLLWUtcVpiTDYzbmNtYTN1RkFLbjAwN3dxT0xZc3pqc3REUXduZVltQ2Fud1BZLTh1bTNiTEJueVUwV0dERS1iUXZqMHd0UnFrQ3E2SFAzbm5lQ1I4U29MaHJFbWFvdVRTeFY4Wl9rSmc3RkpaQ2xwX0oz?oc=5</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -4165,7 +4103,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>noticia:r1uot6</t>
+          <t>noticia:1fo4ig4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4175,15 +4113,15 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-24 20:00</t>
+          <t>2026-10-25 01:08</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1792886439000</v>
+        <v>1792904880000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
+          <t>diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -4192,61 +4130,45 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>roja</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>vuelco deja heridos en ruta Oruro – Huanuni - La Patria Bolivia</t>
+          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNNDQtMG1KT1lLWW5nem9Jbm5JWDZKNlRWZmFmRlBxWDlDeXlSWnJ5d2NsTlpxa0JIS25oVWVZOC1majZVbWhOVDIxR0dLOFlzY2VpVzVoVk1mQnF3dXVwLUFZVHc1UjlXZzF5T05CY3U0ZldLVkw1VzBTek5zanpjQW1xalltWHNiaXI3dTNR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQcmFrT3dwcEs0X3U2NWxnOGJwNnI2WHdWTGZYbzEyNnJzUWhkbU9TRWhfSlB5UkMwX2gyMmxYUmVNWmxNOVR6V0twRHpFMTVIYjBKbHQ2TXN2d2w5dkFpcWJCcUJMZldaX01sNWtQV2ZJOGpRVzR3NDVIU0pJc1BNVg?oc=5</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>-17.97</v>
-      </c>
-      <c r="O8" t="n">
-        <v>-67.11</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Oruro, Oruro</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>Oruro</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>Oruro</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>noticia:1ytw450</t>
+          <t>noticia:r1uot6</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4256,15 +4178,15 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-24 18:58</t>
+          <t>2026-10-24 20:00</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1792882686000</v>
+        <v>1792886439000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>diarioelpueblo.com.pe</t>
+          <t>La Patria Bolivia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -4273,45 +4195,61 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>roja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
+          <t>vuelco deja heridos en ruta Oruro – Huanuni - La Patria Bolivia</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNZ1U3bEVuaVdjVE1zSU9lOHJZTVRZLVZaemhldGNnT1JBWDJvbzdvM3paVVNhLUlyWHF2akNuSXJOLXdyTGRuejRlV1FuMjVkTjA3NmdRdmgtRWlUeTFBV1dEMzBvejBxaXZJdUZZWkRVTF9VLU5BcjFGZGFEQ09WWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNNDQtMG1KT1lLWW5nem9Jbm5JWDZKNlRWZmFmRlBxWDlDeXlSWnJ5d2NsTlpxa0JIS25oVWVZOC1majZVbWhOVDIxR0dLOFlzY2VpVzVoVk1mQnF3dXVwLUFZVHc1UjlXZzF5T05CY3U0ZldLVkw1VzBTek5zanpjQW1xalltWHNiaXI3dTNR?oc=5</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-17.97</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-67.11</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Oruro, Oruro</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>noticia:1wcb22g</t>
+          <t>noticia:1ytw450</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4321,43 +4259,43 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-24 17:47</t>
+          <t>2026-10-24 18:58</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1792878475000</v>
+        <v>1792882686000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Mundo Bolivia</t>
+          <t>diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>hidrológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>roja</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Alerta naranja por ingreso de frente frío y desbordes de ríos en 6 departamentos - El Mundo Bolivia</t>
+          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPZW00RkxJSklTelNrS2hqczJDWHlwcENFX2lnSEUyTEFPaDFRQ2JvMUcyd3NfYjg0UE9ORGxHRzB4ZDh3U0hQQ1JSQlhsaUY4N3ByMUUxei1SaUZnNlp6T3hsLVdiMGhKaXhsV1FNSUNQMHlvQ19qdk56SEF0d2RXVFctS0VPT25kNGZCRDdvZ2dxU0VoUUJKU0ZBd0ZycFNEZFh0T3ZjOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNZ1U3bEVuaVdjVE1zSU9lOHJZTVRZLVZaemhldGNnT1JBWDJvbzdvM3paVVNhLUlyWHF2akNuSXJOLXdyTGRuejRlV1FuMjVkTjA3NmdRdmgtRWlUeTFBV1dEMzBvejBxaXZJdUZZWkRVTF9VLU5BcjFGZGFEQ09WWQ?oc=5</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -4376,7 +4314,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>noticia:1c1ju1f</t>
+          <t>noticia:1wcb22g</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4386,46 +4324,46 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-24 17:02</t>
+          <t>2026-10-24 17:47</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1792875752000</v>
+        <v>1792878475000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>La Razón Digital Bolivia</t>
+          <t>El Mundo Bolivia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>hidrológica</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a los Yungas deja siete heridos - La Razón Digital Bolivia</t>
+          <t>Alerta naranja por ingreso de frente frío y desbordes de ríos en 6 departamentos - El Mundo Bolivia</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPTGQwaVBfdG1JdVRMUTN4LVVvN0ppc3dreDJVVllDR3RmX0xpMzB4b0pvVTNSV1B6T0ZEWTdEZkNsRUdSNzhLaC1CWHN5WktNWk1nRWpTdVZiYjI3TlJlX2xlVTI5MjlRU2hiY1gteml4YWVFbDNPSVRBZmtITlQzbmhaUXVmcThRa2xsQTJIOXZuNzlSdm12MEdyOEZHdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPZW00RkxJSklTelNrS2hqczJDWHlwcENFX2lnSEUyTEFPaDFRQ2JvMUcyd3NfYjg0UE9ORGxHRzB4ZDh3U0hQQ1JSQlhsaUY4N3ByMUUxei1SaUZnNlp6T3hsLVdiMGhKaXhsV1FNSUNQMHlvQ19qdk56SEF0d2RXVFctS0VPT25kNGZCRDdvZ2dxU0VoUUJKU0ZBd0ZycFNEZFh0T3ZjOA?oc=5</t>
         </is>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -4441,7 +4379,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>noticia:14iwzop</t>
+          <t>noticia:1c1ju1f</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4451,15 +4389,15 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-24 13:40</t>
+          <t>2026-10-24 17:02</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1792863623000</v>
+        <v>1792875752000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>EL DÍA - Noticias de Bolivia para el mundo</t>
+          <t>La Razón Digital Bolivia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -4477,13 +4415,13 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a Mayaya deja siete heridos de la agrupación Los Chicos Fieles - EL DÍA - Noticias de Bolivia para el mundo</t>
+          <t>Accidente en la carretera a los Yungas deja siete heridos - La Razón Digital Bolivia</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPeGd3VWpCWXJ0YTJIeDJLcktzWG1jdUh0TjFXb01wSTkxbHNXZU94VWNDMkxnTjlJZVdpbkprMEY2NE80RXYyUWxUQXVnbl9lUXR2b28zTEh6cTJLVEQ4TUNja2kzRlhadVBFZFVwV1U2TlhseXZMZ20zZTZiUFpWRjdCOWNBMHU5XzdMV3JqQjV4TEE3bHRMOXR6Nm55eHZUNnFHSDdVRk8zVkY4RkVsUUtUN0JYdkREWGZncmJ3ZWc2T1BuUm1ZLTlfcHVabFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPTGQwaVBfdG1JdVRMUTN4LVVvN0ppc3dreDJVVllDR3RmX0xpMzB4b0pvVTNSV1B6T0ZEWTdEZkNsRUdSNzhLaC1CWHN5WktNWk1nRWpTdVZiYjI3TlJlX2xlVTI5MjlRU2hiY1gteml4YWVFbDNPSVRBZmtITlQzbmhaUXVmcThRa2xsQTJIOXZuNzlSdm12MEdyOEZHdw?oc=5</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -4506,7 +4444,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>noticia:1ukcn97</t>
+          <t>noticia:14iwzop</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4516,15 +4454,15 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-24 13:26</t>
+          <t>2026-10-24 13:40</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1792862794000</v>
+        <v>1792863623000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Deber</t>
+          <t>EL DÍA - Noticias de Bolivia para el mundo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -4542,20 +4480,20 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Esta es la lista preliminar de los heridos en el accidente del grupo 'Los chicos fieles', el conductor está grave - El Deber</t>
+          <t>Accidente en la carretera a Mayaya deja siete heridos de la agrupación Los Chicos Fieles - EL DÍA - Noticias de Bolivia para el mundo</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOczZKbFd1QzRpak92LXpPWXZXQXJObnBQTG9qRFBlUUV5dThMWXhzckFFUHAyb2thU1JwRmJDSEZfaEdTUXh1bjZvQWpYMGhfUno3cWZ4MGpldEpoQXhzSlVzTm5LLW9OcjB2MWRsdHQ2UlI2SjEtZ085ZTR5Z3pEVmtBTF9lc29Kd0RhaTRUWkM4eGZJNWhBSXZqWmxuNW10dlQwYW9mdzItcWZWTkU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPeGd3VWpCWXJ0YTJIeDJLcktzWG1jdUh0TjFXb01wSTkxbHNXZU94VWNDMkxnTjlJZVdpbkprMEY2NE80RXYyUWxUQXVnbl9lUXR2b28zTEh6cTJLVEQ4TUNja2kzRlhadVBFZFVwV1U2TlhseXZMZ20zZTZiUFpWRjdCOWNBMHU5XzdMV3JqQjV4TEE3bHRMOXR6Nm55eHZUNnFHSDdVRk8zVkY4RkVsUUtUN0JYdkREWGZncmJ3ZWc2T1BuUm1ZLTlfcHVabFE?oc=5</t>
         </is>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -4571,7 +4509,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>noticia:2avehj</t>
+          <t>noticia:1ukcn97</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4581,20 +4519,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-24 12:53</t>
+          <t>2026-10-24 13:26</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1792860813000</v>
+        <v>1792862794000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>El Deber</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>climatológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -4607,52 +4545,36 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Sequía en Cochabamba: más de un centenar de cabezas de ganado murieron en el cono sur - Red Uno</t>
+          <t>Esta es la lista preliminar de los heridos en el accidente del grupo 'Los chicos fieles', el conductor está grave - El Deber</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOOFQxc2Vzc0QwS19ydC13RkRPZnZQU3JkSTl5U3kzdUdMSldTcm5HVEhWRzZyN19CLUlwcUs4MW03Ui1obVBtdzQ3QWFQc1RKdzh3MXJ5QkpRS2pRNm50V1lVb09ScGJnaVVlemVfZlRsWjdObnRmR1FGMnlMMHAyc2pMandndy10T2twcWx6OFh4UHdvbVlFbllwME9WQ2pQVjNTQzBxeTg5YnF3bDREeHVDYXpObFFIaTZZQWtYUE12cGQ1ZGRhT0syNjVhZWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOczZKbFd1QzRpak92LXpPWXZXQXJObnBQTG9qRFBlUUV5dThMWXhzckFFUHAyb2thU1JwRmJDSEZfaEdTUXh1bjZvQWpYMGhfUno3cWZ4MGpldEpoQXhzSlVzTm5LLW9OcjB2MWRsdHQ2UlI2SjEtZ085ZTR5Z3pEVmtBTF9lc29Kd0RhaTRUWkM4eGZJNWhBSXZqWmxuNW10dlQwYW9mdzItcWZWTkU0?oc=5</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>-17.39</v>
-      </c>
-      <c r="O14" t="n">
-        <v>-66.16</v>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Cochabamba, Cochabamba</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>noticia:1ksmg5u</t>
+          <t>noticia:2avehj</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4662,20 +4584,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-24 11:43</t>
+          <t>2026-10-24 12:53</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1792856591000</v>
+        <v>1792860813000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>climatológica</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -4688,36 +4610,52 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Embarrancamiento deja heridos a integrantes de Los Chicos Fieles - La Patria Bolivia</t>
+          <t>Sequía en Cochabamba: más de un centenar de cabezas de ganado murieron en el cono sur - Red Uno</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNeEFrOEtOMHZxMW42REFPU0x1MG5oQjlBMkJucWRLZ292alBXekJKeURBN3NLTVVadWI0OWF4UGtSVXBzTE01eWFSU1kyMUhNZ04zMWNMaUxnMDBBZ0EwTktXbjlaVTBUUmNqa3AwY19KNTU2LWh5LW9IVElVdTdnaHFPanJPd2FqMUxzaUhXZmVpYU1saGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOOFQxc2Vzc0QwS19ydC13RkRPZnZQU3JkSTl5U3kzdUdMSldTcm5HVEhWRzZyN19CLUlwcUs4MW03Ui1obVBtdzQ3QWFQc1RKdzh3MXJ5QkpRS2pRNm50V1lVb09ScGJnaVVlemVfZlRsWjdObnRmR1FGMnlMMHAyc2pMandndy10T2twcWx6OFh4UHdvbVlFbllwME9WQ2pQVjNTQzBxeTg5YnF3bDREeHVDYXpObFFIaTZZQWtYUE12cGQ1ZGRhT0syNjVhZWs?oc=5</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-17.39</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-66.16</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Cochabamba, Cochabamba</t>
+        </is>
+      </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>noticia:mlyqgd</t>
+          <t>noticia:1ksmg5u</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4727,15 +4665,15 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-24 11:30</t>
+          <t>2026-10-24 11:43</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1792855818000</v>
+        <v>1792856591000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Opinión Bolivia</t>
+          <t>La Patria Bolivia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -4753,20 +4691,20 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a Mayaya deja siete heridos de la agrupación Los Chicos Fieles - Opinión Bolivia</t>
+          <t>Embarrancamiento deja heridos a integrantes de Los Chicos Fieles - La Patria Bolivia</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYjNxaHg3YllRRTJYdFd1clAtUlROSGlFNVg5eUVZUGJoOEZ4MWM5QU5WQm1YTDc4NXc3SjhWMUw0TkZfSHlMLUQ1bmpTME1Kb1JaM0ExamFHYTd3VlU4MXRWdTZ1bzh1SGYtbGE1a3dBaG93bjg1OGc0S0JfRE43c3dVMVltN0dQQzNhQUNhM0FjVUNRUDRSamlJYlk2dEJpUTBuY2hBcTFucTVRN0ZtYnc5bzdmTV9LQm1uVUxaZS1tUE9IejhBVDRCdU_SAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNeEFrOEtOMHZxMW42REFPU0x1MG5oQjlBMkJucWRLZ292alBXekJKeURBN3NLTVVadWI0OWF4UGtSVXBzTE01eWFSU1kyMUhNZ04zMWNMaUxnMDBBZ0EwTktXbjlaVTBUUmNqa3AwY19KNTU2LWh5LW9IVElVdTdnaHFPanJPd2FqMUxzaUhXZmVpYU1saGc?oc=5</t>
         </is>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
@@ -4782,7 +4720,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>noticia:irf4jl</t>
+          <t>noticia:mlyqgd</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4824,7 +4762,7 @@
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNMXlMNXFWSWhhWWNDRFFKMncwS2JGWm0tWlJCd2x2RjZhdFhEQ0lBcVlFSS1WRVYxMEVJTWRHcTY3M0stdWhGdnVPRU13X2MwSVRWX25xVUQxa0R6Z1pqQ2dfY0VjUmw2aXFoWFNVNk15N2dBOENZLWlGSWJfMW0zejVoZ3ZwVHVQV1MzbzlnUlpRcWIxMHZxdkItZTc0QmMyRnBmSVRtVnZ5Y3gtdVpYNXFwcGdadGVCU3dRZ3EwOTdiWHU4OXJRdEFoNi1HcnA1U0HSAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYjNxaHg3YllRRTJYdFd1clAtUlROSGlFNVg5eUVZUGJoOEZ4MWM5QU5WQm1YTDc4NXc3SjhWMUw0TkZfSHlMLUQ1bmpTME1Kb1JaM0ExamFHYTd3VlU4MXRWdTZ1bzh1SGYtbGE1a3dBaG93bjg1OGc0S0JfRE43c3dVMVltN0dQQzNhQUNhM0FjVUNRUDRSamlJYlk2dEJpUTBuY2hBcTFucTVRN0ZtYnc5bzdmTV9LQm1uVUxaZS1tUE9IejhBVDRCdU_SAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -4847,7 +4785,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>noticia:1g006zh</t>
+          <t>noticia:irf4jl</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4857,15 +4795,15 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-24 11:25</t>
+          <t>2026-10-24 11:30</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1792855522000</v>
+        <v>1792855818000</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>El Potosí</t>
+          <t>Opinión Bolivia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -4883,13 +4821,13 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a Mayaya deja siete heridos del grupo Los Chicos Fieles - El Potosí</t>
+          <t>Accidente en la carretera a Mayaya deja siete heridos de la agrupación Los Chicos Fieles - Opinión Bolivia</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTC10eC1qSm1WRlY2YzA3VEJqOG1LUkx6bE9PdFYwTFBZMGFjU0RMYXliRkhXcTJHRlVzb0Y4QUU0WWJDQ1plS2NZamZ1YmFadE5qY3g4UE5aYVAwamtCUUNZaDB2YWJTdWRKS3R4a0hHUjVobUl0Y1dYZ2JPczAwak5kN1hjUEwwM1NtUDVWbnAzWTdnRng3RjFValFVVlZPdVZnWFlUODhPOE5aMTROQzVKVjVRS2VoaTlaQnBiUGRTNFk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNMXlMNXFWSWhhWWNDRFFKMncwS2JGWm0tWlJCd2x2RjZhdFhEQ0lBcVlFSS1WRVYxMEVJTWRHcTY3M0stdWhGdnVPRU13X2MwSVRWX25xVUQxa0R6Z1pqQ2dfY0VjUmw2aXFoWFNVNk15N2dBOENZLWlGSWJfMW0zejVoZ3ZwVHVQV1MzbzlnUlpRcWIxMHZxdkItZTc0QmMyRnBmSVRtVnZ5Y3gtdVpYNXFwcGdadGVCU3dRZ3EwOTdiWHU4OXJRdEFoNi1HcnA1U0HSAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -4898,60 +4836,44 @@
       <c r="M18" t="n">
         <v>7</v>
       </c>
-      <c r="N18" t="n">
-        <v>-19.58</v>
-      </c>
-      <c r="O18" t="n">
-        <v>-65.75</v>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Potosí, Potosí</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>clima:Potosí:2026-10-24:viento:1</t>
+          <t>noticia:1g006zh</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-24 10:55</t>
+          <t>2026-10-24 11:25</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1792853727284</v>
+        <v>1792855522000</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>El Potosí</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4964,24 +4886,20 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Potosí 2026-10-24: 60.5 km/h de ráfagas pronosticadas</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
-        </is>
-      </c>
+          <t>Accidente en la carretera a Mayaya deja siete heridos del grupo Los Chicos Fieles - El Potosí</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTC10eC1qSm1WRlY2YzA3VEJqOG1LUkx6bE9PdFYwTFBZMGFjU0RMYXliRkhXcTJHRlVzb0Y4QUU0WWJDQ1plS2NZamZ1YmFadE5qY3g4UE5aYVAwamtCUUNZaDB2YWJTdWRKS3R4a0hHUjVobUl0Y1dYZ2JPczAwak5kN1hjUEwwM1NtUDVWbnAzWTdnRng3RjFValFVVlZPdVZnWFlUODhPOE5aMTROQzVKVjVRS2VoaTlaQnBiUGRTNFk?oc=5</t>
         </is>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N19" t="n">
         <v>-19.58</v>
@@ -4991,12 +4909,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Potosí, Potosí</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>capital (pronóstico puntual)</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -5013,25 +4931,25 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>noticia:1ax0bpy</t>
+          <t>clima:Potosí:2026-10-24:viento:1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-24 10:32</t>
+          <t>2026-10-24 10:55</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1792852364000</v>
+        <v>1792853727284</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Que Pasa Salta</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -5040,22 +4958,26 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Creció el Bermejo tras la tormenta: así está el puerto de chalanas en este momento - Que Pasa Salta</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+          <t>Potosí 2026-10-24: 60.5 km/h de ráfagas pronosticadas</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVld9IBfkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVldw?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -5065,59 +4987,59 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-22.721</v>
+        <v>-19.58</v>
       </c>
       <c r="O20" t="n">
-        <v>-64.32599999999999</v>
+        <v>-65.75</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bermejo, Tarija</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
+          <t>capital (pronóstico puntual)</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Tarija</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>Bermejo</t>
+          <t>Potosí</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>gdacs:WF1033142:0</t>
+          <t>noticia:1ax0bpy</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gdacs</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-24 07:06</t>
+          <t>2026-10-24 10:32</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1792839995000</v>
+        <v>1792852364000</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>GDACS</t>
+          <t>Que Pasa Salta</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -5130,17 +5052,13 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Green forest fire notification in Bolivia</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>On 21/10/2026, a forest fire started in Bolivia, until 24/10/2026.</t>
-        </is>
-      </c>
+          <t>Creció el Bermejo tras la tormenta: así está el puerto de chalanas en este momento - Que Pasa Salta</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>http://www.gdacs.org/report.aspx?eventtype=WF&amp;eventid=1033142</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVld9IBfkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVldw?oc=5</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -5150,59 +5068,59 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>-13.06332</v>
+        <v>-22.721</v>
       </c>
       <c r="O21" t="n">
-        <v>-67.66426</v>
+        <v>-64.32599999999999</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Bermejo, Tarija</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>coordenada de la fuente</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Tarija</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>Ixiamas</t>
+          <t>Bermejo</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>noticia:1shhqva</t>
+          <t>gdacs:WF1033142:0</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>gdacs</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-24 06:33</t>
+          <t>2026-10-24 07:06</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1792838034000</v>
+        <v>1792839995000</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>GDACS</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5215,13 +5133,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+          <t>Green forest fire notification in Bolivia</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>On 21/10/2026, a forest fire started in Bolivia, until 24/10/2026.</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQYzB6N082XzFRRnVtcDVmUkYyWjcxUzV2Z3Frd1I0WDNXSnZtY0QzOU1PUkNLMktVT1Vra2FSeXhxZDRuOFZYZjFwejl6ejJTbWY2MGJuSGN3ZHdrdG5JUkgzSXBkbDYtaHlackY3OVFuNWdLcFNpdWNHRU9vNGdoVWx2ODFVdzJXYUxnM0tUcjJvZmc?oc=5</t>
+          <t>http://www.gdacs.org/report.aspx?eventtype=WF&amp;eventid=1033142</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -5231,82 +5153,78 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>-17.97</v>
+        <v>-13.06332</v>
       </c>
       <c r="O22" t="n">
-        <v>-67.11</v>
+        <v>-67.66426</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
+          <t>coordenada de la fuente</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Ixiamas</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>clima:Potosí:2026-10-25:viento:1</t>
+          <t>noticia:1shhqva</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-24 02:55</t>
+          <t>2026-10-24 06:33</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1792824927736</v>
+        <v>1792838034000</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Potosí 2026-10-25: 60.5 km/h de ráfagas pronosticadas</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
-        </is>
-      </c>
+          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQYzB6N082XzFRRnVtcDVmUkYyWjcxUzV2Z3Frd1I0WDNXSnZtY0QzOU1PUkNLMktVT1Vra2FSeXhxZDRuOFZYZjFwejl6ejJTbWY2MGJuSGN3ZHdrdG5JUkgzSXBkbDYtaHlackY3OVFuNWdLcFNpdWNHRU9vNGdoVWx2ODFVdzJXYUxnM0tUcjJvZmc?oc=5</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -5316,59 +5234,59 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>-19.58</v>
+        <v>-17.97</v>
       </c>
       <c r="O23" t="n">
-        <v>-65.75</v>
+        <v>-67.11</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Oruro, Oruro</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>capital (pronóstico puntual)</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Oruro</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Oruro</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>noticia:mz6q0s</t>
+          <t>clima:Potosí:2026-10-25:viento:1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-23 23:09</t>
+          <t>2026-10-24 02:55</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1792811349000</v>
+        <v>1792824927736</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5381,36 +5299,56 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Revelan lista preliminar de heridos tras accidente de Los Chicos Fieles - Red Uno</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
+          <t>Potosí 2026-10-25: 60.5 km/h de ráfagas pronosticadas</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPczBQcnE2SzFGMXc3b1lsTkNxVWRmS3Vnb01xOTV2WmVva3J2RVlteWpHZ3VJS2dNWGV5NW5FX3ZncnVKTEVDTGpBRndTU1FxeWxtaS1fb1FscGxXMWNXUE9zbHdob1AxVFl1eHB5OU1yUnNoOXJ6U21oVG9PVDA1ak1xQl9hUlB4V0RaQXJqZENGUm8zMUJEY3J0WW5ENE5ObWJLNmpWN0RkSmFJbnZUZGR5UFRPd3QyUFY4WQ?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-19.58</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-65.75</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Potosí</t>
+        </is>
+      </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
+          <t>capital (pronóstico puntual)</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Potosí</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Potosí</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>noticia:1uil931</t>
+          <t>noticia:mz6q0s</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5420,15 +5358,15 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-23 22:49</t>
+          <t>2026-10-23 23:09</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1792810149000</v>
+        <v>1792811349000</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>El Deber</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5446,13 +5384,13 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Accidente de tránsito en la ruta hacia Alto Beni deja varios heridos - El Deber</t>
+          <t>Revelan lista preliminar de heridos tras accidente de Los Chicos Fieles - Red Uno</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQakFJRmx3RlJEMkVHU0pxWXZ2ZU1ib04tZy1yeTB2OGhrYk9CU3pMaDVpRThNZktZMS14UzA2Y1VIcEQtZDg3cEU2SmlzQnBmUVVvM0ZNYzZWNExWUXQ3aHpnd3lqOHFVV3pNbDRLS1NQNGtwb2RjSFpleHJkOG5zSXVtWjVIS1dLejNybktRWTJVZXh3WkFUQVE5T2tMdFdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPczBQcnE2SzFGMXc3b1lsTkNxVWRmS3Vnb01xOTV2WmVva3J2RVlteWpHZ3VJS2dNWGV5NW5FX3ZncnVKTEVDTGpBRndTU1FxeWxtaS1fb1FscGxXMWNXUE9zbHdob1AxVFl1eHB5OU1yUnNoOXJ6U21oVG9PVDA1ak1xQl9hUlB4V0RaQXJqZENGUm8zMUJEY3J0WW5ENE5ObWJLNmpWN0RkSmFJbnZUZGR5UFRPd3QyUFY4WQ?oc=5</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -5461,37 +5399,21 @@
       <c r="M25" t="n">
         <v>1</v>
       </c>
-      <c r="N25" t="n">
-        <v>-15.578</v>
-      </c>
-      <c r="O25" t="n">
-        <v>-67.44</v>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Alto Beni, La Paz</t>
-        </is>
-      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>La Paz</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>Alto Beni</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>noticia:1tliu4i</t>
+          <t>noticia:1uil931</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5501,11 +5423,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-23 22:18</t>
+          <t>2026-10-23 22:49</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1792808330000</v>
+        <v>1792810149000</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -5533,7 +5455,7 @@
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQMF9BNnUzLURKNGRMUUJ1VXVRSXNnMlBsQnVXOG0tRlFtY3pvRDNPQmNJMWN2RzJVaWdoWndmcHFnTkZFZnJxRkZtMThYYWlwN09ueUgtei1pSE1hZ2FtSzN6elY4VXJHbzFxdll0eWh0ZkxwQkQ1SDZ5b0E3MlVENGZEWGZHUGlwVG4wd2x3OFNEMVpibnFr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQakFJRmx3RlJEMkVHU0pxWXZ2ZU1ib04tZy1yeTB2OGhrYk9CU3pMaDVpRThNZktZMS14UzA2Y1VIcEQtZDg3cEU2SmlzQnBmUVVvM0ZNYzZWNExWUXQ3aHpnd3lqOHFVV3pNbDRLS1NQNGtwb2RjSFpleHJkOG5zSXVtWjVIS1dLejNybktRWTJVZXh3WkFUQVE5T2tMdFdn?oc=5</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -5572,7 +5494,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>noticia:1twc9ul</t>
+          <t>noticia:1tliu4i</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5582,11 +5504,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-10-23 22:16</t>
+          <t>2026-10-23 22:18</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1792808192000</v>
+        <v>1792808330000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -5614,7 +5536,7 @@
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNbmwzSnd6c2tFMXBWY0tiemJqRm5CNllOT2p1U0FhdW5QNGFBVXlSZVM1ak5jNGZvcXNVaUQzN3ZQQTlPbmVjQ2Y5RFl2dWVLeUN5NUFodDF0alEyZWlmOHFZWkVVbjdQbkl3ZWtmS25wQWM2TmRZZDBGM2xlS0ZhUzAweXRmcmhVWGY5dV9CUnFBNGtWZHZDSWVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQMF9BNnUzLURKNGRMUUJ1VXVRSXNnMlBsQnVXOG0tRlFtY3pvRDNPQmNJMWN2RzJVaWdoWndmcHFnTkZFZnJxRkZtMThYYWlwN09ueUgtei1pSE1hZ2FtSzN6elY4VXJHbzFxdll0eWh0ZkxwQkQ1SDZ5b0E3MlVENGZEWGZHUGlwVG4wd2x3OFNEMVpibnFr?oc=5</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -5653,7 +5575,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>noticia:1dygpkp</t>
+          <t>noticia:1twc9ul</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5663,15 +5585,15 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-10-23 21:39</t>
+          <t>2026-10-23 22:16</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1792805983000</v>
+        <v>1792808192000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>El Deber</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5680,39 +5602,39 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>(Video) Así rescataron a uno de los integrantes de Los Chicos Fieles tras accidente en Caranavi - Red Uno</t>
+          <t>Accidente de tránsito en la ruta hacia Alto Beni deja varios heridos - El Deber</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOdTVUZUQxVTdvYTdONDQxVlhUTzBOS2hKLW1rS1NUcmRYRnlCVlhIcHZlSjdsaktkQm5CWkFYa3lDQkxnMlh0b3prX0lha1BtbW1qS1VuYnNiX3FiZkYyNDJDR0tqZ0pKMU5TeC04SXV4UUJOTUlPUTB6ek01bzUxTUsydjZqZzI3S3ZLUnRWSUFUVk44WEpKUl9rbzRLb2IwYl9sLVlrYmt5d2ZHNUtGd3lRNnYzMlhuMkJOZW1XSUl2N1BxZWpHbm5XTDJhRUtnR190QWQ1TDlTUVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNbmwzSnd6c2tFMXBWY0tiemJqRm5CNllOT2p1U0FhdW5QNGFBVXlSZVM1ak5jNGZvcXNVaUQzN3ZQQTlPbmVjQ2Y5RFl2dWVLeUN5NUFodDF0alEyZWlmOHFZWkVVbjdQbkl3ZWtmS25wQWM2TmRZZDBGM2xlS0ZhUzAweXRmcmhVWGY5dV9CUnFBNGtWZHZDSWVB?oc=5</t>
         </is>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>-15.813</v>
+        <v>-15.578</v>
       </c>
       <c r="O28" t="n">
-        <v>-67.46299999999999</v>
+        <v>-67.44</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Caranavi, La Paz</t>
+          <t>Alto Beni, La Paz</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -5727,14 +5649,14 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>Caranavi</t>
+          <t>Alto Beni</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>noticia:3dv7b0</t>
+          <t>noticia:1dygpkp</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5744,15 +5666,15 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-10-23 21:35</t>
+          <t>2026-10-23 21:39</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1792805700000</v>
+        <v>1792805983000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FmBolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5761,29 +5683,29 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Accidente en Caranavi: vehículo de Los Chicos Fieles cae a un barranco y deja varios heridos - FmBolivia</t>
+          <t>(Video) Así rescataron a uno de los integrantes de Los Chicos Fieles tras accidente en Caranavi - Red Uno</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNcE1KaHZyUTJCSElxRU9nVzdhTnczWjJGTEhFMEs0bHp2cUdFeHd3VTB0NmVFcjdEN1dsZDZLY2k1ZFFUWkhKV19PU3V2czNyamh1ZE9YajVSVF8xczF6OFhZcWFvYV9EcWg4ZDNCb2p3enhXbFpRYnJMdGdaTXNrWUZSYVhKNTVicWlCLTJ5OE05Z1BvNEx1eEloUk5qTGN3ZHNzbzZWSVljbnRmSERJUWdxRDc0MjJxMGtycWJaaVhXQUUxVUlaWVZLOWE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOdTVUZUQxVTdvYTdONDQxVlhUTzBOS2hKLW1rS1NUcmRYRnlCVlhIcHZlSjdsaktkQm5CWkFYa3lDQkxnMlh0b3prX0lha1BtbW1qS1VuYnNiX3FiZkYyNDJDR0tqZ0pKMU5TeC04SXV4UUJOTUlPUTB6ek01bzUxTUsydjZqZzI3S3ZLUnRWSUFUVk44WEpKUl9rbzRLb2IwYl9sLVlrYmt5d2ZHNUtGd3lRNnYzMlhuMkJOZW1XSUl2N1BxZWpHbm5XTDJhRUtnR190QWQ1TDlTUVk?oc=5</t>
         </is>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>-15.813</v>
@@ -5815,30 +5737,30 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-24:viento:1</t>
+          <t>noticia:3dv7b0</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-10-23 20:55</t>
+          <t>2026-10-23 21:35</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1792803329663</v>
+        <v>1792805700000</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>FmBolivia</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5851,74 +5773,70 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-24: 78.1 km/h de ráfagas pronosticadas</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
-        </is>
-      </c>
+          <t>Accidente en Caranavi: vehículo de Los Chicos Fieles cae a un barranco y deja varios heridos - FmBolivia</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNcE1KaHZyUTJCSElxRU9nVzdhTnczWjJGTEhFMEs0bHp2cUdFeHd3VTB0NmVFcjdEN1dsZDZLY2k1ZFFUWkhKV19PU3V2czNyamh1ZE9YajVSVF8xczF6OFhZcWFvYV9EcWg4ZDNCb2p3enhXbFpRYnJMdGdaTXNrWUZSYVhKNTVicWlCLTJ5OE05Z1BvNEx1eEloUk5qTGN3ZHNzbzZWSVljbnRmSERJUWdxRDc0MjJxMGtycWJaaVhXQUUxVUlaWVZLOWE?oc=5</t>
         </is>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N30" t="n">
-        <v>-17.78</v>
+        <v>-15.813</v>
       </c>
       <c r="O30" t="n">
-        <v>-63.18</v>
+        <v>-67.46299999999999</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Caranavi, La Paz</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>capital (pronóstico puntual)</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Caranavi</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>noticia:rabz5p</t>
+          <t>clima:Santa Cruz:2026-10-24:viento:1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-10-23 20:44</t>
+          <t>2026-10-23 20:55</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1792802686000</v>
+        <v>1792803329663</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -5927,22 +5845,26 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Tome previsiones: se pronostican lluvias y ambiente caluroso para este fin de semana en Cochabamba - Red Uno</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
+          <t>Santa Cruz 2026-10-24: 78.1 km/h de ráfagas pronosticadas</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTlU5NVFpY1RheTN5ZE1IbG5VYTh2Sk5hZHpHeWI3LVdnSFg2cFJFdnBCVkxiUjNKcUgyUW16SWxpMXFkMHdad2xFN043bklJeG1iQ0V1V3hBZk1Ga3NscjdPVWUySmt4bDNTdWlmSUdOMmNlZ2hkSWZFMmk4VGs0Nm9TcnRCTDhINmtnQU9zZDBUY05HcWpxN3FOX3N1dmVJblE0MGc5di1Ma1N2dGNxOUtoV1MzNnl1OXpRaTZ2UGxMc3RDWndubHVQNUd0eVROMGR2OGxVemtOaEc4bTNRaA?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -5952,36 +5874,36 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>-17.39</v>
+        <v>-17.78</v>
       </c>
       <c r="O31" t="n">
-        <v>-66.16</v>
+        <v>-63.18</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Cochabamba, Cochabamba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
+          <t>capital (pronóstico puntual)</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>noticia:1jfk053</t>
+          <t>noticia:rabz5p</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5991,11 +5913,11 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-23 19:08</t>
+          <t>2026-10-23 20:44</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1792796931000</v>
+        <v>1792802686000</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -6004,43 +5926,43 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>climatológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Sequía en Pasorapa: el ganado muere por falta de agua y alistan declaratoria de desastre - Red Uno</t>
+          <t>Tome previsiones: se pronostican lluvias y ambiente caluroso para este fin de semana en Cochabamba - Red Uno</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNQVhTWE8zdE1BQ3lueWJPeV9wUDNsSmJpS0NJTWppMUY4QmlQSUFHVjRORmtrVHQ3MHB0T1pyS25PamxnY0hBQUtzOVRvSUNaUkdGb1RWSGl4dFA4Z3VINVpQTk1pZUpDdUIyUU5hZS1oNGhBa1RWcFhScVMwVTFrVlJaOFQ4OWFqRWVUZ051bHVJTlMxRTBhRFVLUEV2dTZFdDgtRkxJM3VvN3YzUWJfVk41ZWR5U1JoNmx0WFFkMmNTWGVleGNIQlNxWUJzdHIxSWtz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTlU5NVFpY1RheTN5ZE1IbG5VYTh2Sk5hZHpHeWI3LVdnSFg2cFJFdnBCVkxiUjNKcUgyUW16SWxpMXFkMHdad2xFN043bklJeG1iQ0V1V3hBZk1Ga3NscjdPVWUySmt4bDNTdWlmSUdOMmNlZ2hkSWZFMmk4VGs0Nm9TcnRCTDhINmtnQU9zZDBUY05HcWpxN3FOX3N1dmVJblE0MGc5di1Ma1N2dGNxOUtoV1MzNnl1OXpRaTZ2UGxMc3RDWndubHVQNUd0eVROMGR2OGxVemtOaEc4bTNRaA?oc=5</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>-18.38</v>
+        <v>-17.39</v>
       </c>
       <c r="O32" t="n">
-        <v>-64.649</v>
+        <v>-66.16</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Pasorapa, Cochabamba</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -6055,14 +5977,14 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>Pasorapa</t>
+          <t>Cochabamba</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>noticia:ix3l8o</t>
+          <t>noticia:1jfk053</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6072,56 +5994,56 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-23 18:25</t>
+          <t>2026-10-23 19:08</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1792794310000</v>
+        <v>1792796931000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Visión 360</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>climatológica</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Oruro evalúa suspender clases presenciales por más de 200 casos de Coxsackie - Visión 360</t>
+          <t>Sequía en Pasorapa: el ganado muere por falta de agua y alistan declaratoria de desastre - Red Uno</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0c9IBywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNQVhTWE8zdE1BQ3lueWJPeV9wUDNsSmJpS0NJTWppMUY4QmlQSUFHVjRORmtrVHQ3MHB0T1pyS25PamxnY0hBQUtzOVRvSUNaUkdGb1RWSGl4dFA4Z3VINVpQTk1pZUpDdUIyUU5hZS1oNGhBa1RWcFhScVMwVTFrVlJaOFQ4OWFqRWVUZ051bHVJTlMxRTBhRFVLUEV2dTZFdDgtRkxJM3VvN3YzUWJfVk41ZWR5U1JoNmx0WFFkMmNTWGVleGNIQlNxWUJzdHIxSWtz?oc=5</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>-17.97</v>
+        <v>-18.38</v>
       </c>
       <c r="O33" t="n">
-        <v>-67.11</v>
+        <v>-64.649</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>Pasorapa, Cochabamba</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -6131,19 +6053,19 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Pasorapa</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>noticia:1xqv9m7</t>
+          <t>noticia:ix3l8o</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6153,62 +6075,78 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-10-23 18:09</t>
+          <t>2026-10-23 18:25</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1792793370000</v>
+        <v>1792794310000</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>El Diario del centro del país</t>
+          <t>Visión 360</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Tres heridos en tremendo choque cerca de Oncativo - El Diario del centro del país</t>
+          <t>Oruro evalúa suspender clases presenciales por más de 200 casos de Coxsackie - Visión 360</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZERhbTJMQUJVb3hmZFlSZmRGZkdBLWdFTGJVQzdqZkE4aGhhWmdQZ2JDRW1ndkJLWU90VTZ6Ti1JOUZzcFZfcE1zbkRHU1B3YTF4UkVzdllFa1p3SUlObURGamF0Vm9kc3dPLTZVWFJ4NWZZQmlySElPNHhZTnRGNGNZUWw2ZlI1eVBEQkNGNEhLWTNiLWJLUS0xYjA0UWRhc0d6bVN4aVVLSVdsQWlpMUZYdWw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0c9IBywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0cw?oc=5</t>
         </is>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3</v>
-      </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-17.97</v>
+      </c>
+      <c r="O34" t="n">
+        <v>-67.11</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Oruro, Oruro</t>
+        </is>
+      </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>noticia:1wuregl</t>
+          <t>noticia:1xqv9m7</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -6218,78 +6156,62 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-23 15:39</t>
+          <t>2026-10-23 18:09</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1792784340000</v>
+        <v>1792793370000</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FmBolivia</t>
+          <t>El Diario del centro del país</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>hidrológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Intensas lluvias inundan La Paz y activan alertas por el riesgo de desborde de ríos - FmBolivia</t>
+          <t>Tres heridos en tremendo choque cerca de Oncativo - El Diario del centro del país</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPZm85aHphekQ4U3BZZkp1ZkF6ZVdSUHgtZmltS1FxUUgza1AwcndWWDJZOWctT0RiVmVabmg5SG42NnJWMlJMMnBlYTlYaVdSb09sR0dnVDdpT29faTdiaDUtZElJdlQ3eTdjR2VsWjlta1FOS1U2Vm1vV3JwWkpvbEw1ZUR3akgwQTZnQnVENjJtVkQtVUpKVEJTeWNJSE1CaEFKa2VqMmZXbWk3ekR4ZWpmZ1Z3elFQaWNaNFJuMXA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZERhbTJMQUJVb3hmZFlSZmRGZkdBLWdFTGJVQzdqZkE4aGhhWmdQZ2JDRW1ndkJLWU90VTZ6Ti1JOUZzcFZfcE1zbkRHU1B3YTF4UkVzdllFa1p3SUlObURGamF0Vm9kc3dPLTZVWFJ4NWZZQmlySElPNHhZTnRGNGNZUWw2ZlI1eVBEQkNGNEhLWTNiLWJLUS0xYjA0UWRhc0d6bVN4aVVLSVdsQWlpMUZYdWw?oc=5</t>
         </is>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>-16.169</v>
-      </c>
-      <c r="O35" t="n">
-        <v>-68.09</v>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>La Paz, La Paz</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>La Paz</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>Nuestra Señora de La Paz</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>noticia:1570kkf</t>
+          <t>noticia:1wuregl</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -6299,20 +6221,20 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-10-23 15:28</t>
+          <t>2026-10-23 15:39</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1792783705000</v>
+        <v>1792784340000</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>FmBolivia</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>hidrológica</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6325,13 +6247,13 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>¿Se suspenden las clases en Oruro? Más de 200 casos de Coxsackie activan evaluaciones - Red Uno</t>
+          <t>Intensas lluvias inundan La Paz y activan alertas por el riesgo de desborde de ríos - FmBolivia</t>
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNMFdHaVpKRmMyOENDYm16UXJPenVSQnpmTE94bDc4UFhqakluMUdvZjAwamUxT3BVWUpJQm8xVHBWengxQmhWM1hjU3d2YXFrLXpVU2VrZDJiMXZLMlQ5bGxGOHFETFhYM0s2RjlUTlhkd0g2eXQweDFHaTlKNGNMUlJfOWg2a0JjTklXUWZKc1BmUXZuZFZ2MF9fV2lEYUY4LXNiNmk3cF9FNjVtTl9GWFotT2ltS0xXTnM1dENvSU9kbFRMalFrYVdXOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPZm85aHphekQ4U3BZZkp1ZkF6ZVdSUHgtZmltS1FxUUgza1AwcndWWDJZOWctT0RiVmVabmg5SG42NnJWMlJMMnBlYTlYaVdSb09sR0dnVDdpT29faTdiaDUtZElJdlQ3eTdjR2VsWjlta1FOS1U2Vm1vV3JwWkpvbEw1ZUR3akgwQTZnQnVENjJtVkQtVUpKVEJTeWNJSE1CaEFKa2VqMmZXbWk3ekR4ZWpmZ1Z3elFQaWNaNFJuMXA?oc=5</t>
         </is>
       </c>
       <c r="L36" t="n">
@@ -6341,14 +6263,14 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>-17.97</v>
+        <v>-16.169</v>
       </c>
       <c r="O36" t="n">
-        <v>-67.11</v>
+        <v>-68.09</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>La Paz, La Paz</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -6358,19 +6280,19 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Nuestra Señora de La Paz</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>noticia:1nzu2o8</t>
+          <t>noticia:1570kkf</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -6380,39 +6302,39 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-10-23 15:20</t>
+          <t>2026-10-23 15:28</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1792783236000</v>
+        <v>1792783705000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>hidrológica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Alerta naranja por posibles desbordes en tres departamentos (15:20) - El Diario - Bolivia</t>
+          <t>¿Se suspenden las clases en Oruro? Más de 200 casos de Coxsackie activan evaluaciones - Red Uno</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPTnBESV9OODZhNjY3T2M2X2NZcmk4clI0eFZsd3VLMVRwaUlSdF9wanZyVGxDNUlNTm5wbGpLN1lvX09mNGxFVkpIZDNGdi1pNDdfSGlESThfeVloQzJsNUMyNUpWUDhzTVJiYWJpNkQ1RHliRWljZlp3SlhtZ2FhU0pvV0syUmZIejJZWHlRdTBOTG4zaTc5cEsycW9IcEx2SkQtN01Gendlb1VR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNMFdHaVpKRmMyOENDYm16UXJPenVSQnpmTE94bDc4UFhqakluMUdvZjAwamUxT3BVWUpJQm8xVHBWengxQmhWM1hjU3d2YXFrLXpVU2VrZDJiMXZLMlQ5bGxGOHFETFhYM0s2RjlUTlhkd0g2eXQweDFHaTlKNGNMUlJfOWg2a0JjTklXUWZKc1BmUXZuZFZ2MF9fV2lEYUY4LXNiNmk3cF9FNjVtTl9GWFotT2ltS0xXTnM1dENvSU9kbFRMalFrYVdXOA?oc=5</t>
         </is>
       </c>
       <c r="L37" t="n">
@@ -6421,21 +6343,37 @@
       <c r="M37" t="n">
         <v>0</v>
       </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
+      <c r="N37" t="n">
+        <v>-17.97</v>
+      </c>
+      <c r="O37" t="n">
+        <v>-67.11</v>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Oruro, Oruro</t>
+        </is>
+      </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>noticia:1itd1r7</t>
+          <t>noticia:1nzu2o8</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6445,39 +6383,39 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-10-23 15:01</t>
+          <t>2026-10-23 15:20</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1792782098000</v>
+        <v>1792783236000</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>eju.tv</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>hidrológica</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Intensa lluvia y granizada en La Paz inundan vías y elevan el nivel de los ríos - eju.tv</t>
+          <t>Alerta naranja por posibles desbordes en tres departamentos (15:20) - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNWU9QWElKQXEyN3UxVm4xbzJzbEJ1TU1NTHZlRUp6YndmeU9GQnJKcTluVEJ2ZHQ5cGp3aWhlMUd5ektWQlBpUVNmZnZuRnJwMXlydzAzX0FBVnY5UDMzQTBkWVRNRUNJSlRvX3MyQVhMcEhIMW9WSUpXckVSd0RJWk1KMFBKWmJNU3diQVlEN1Y5aVV6eVBaZXpOMnFIWWxaMlRlY0ZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPTnBESV9OODZhNjY3T2M2X2NZcmk4clI0eFZsd3VLMVRwaUlSdF9wanZyVGxDNUlNTm5wbGpLN1lvX09mNGxFVkpIZDNGdi1pNDdfSGlESThfeVloQzJsNUMyNUpWUDhzTVJiYWJpNkQ1RHliRWljZlp3SlhtZ2FhU0pvV0syUmZIejJZWHlRdTBOTG4zaTc5cEsycW9IcEx2SkQtN01Gendlb1VR?oc=5</t>
         </is>
       </c>
       <c r="L38" t="n">
@@ -6486,37 +6424,21 @@
       <c r="M38" t="n">
         <v>0</v>
       </c>
-      <c r="N38" t="n">
-        <v>-16.169</v>
-      </c>
-      <c r="O38" t="n">
-        <v>-68.09</v>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>La Paz, La Paz</t>
-        </is>
-      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>La Paz</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>Nuestra Señora de La Paz</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>noticia:1l4xxfk</t>
+          <t>noticia:1itd1r7</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6526,20 +6448,20 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-10-23 14:51</t>
+          <t>2026-10-23 15:01</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1792781480000</v>
+        <v>1792782098000</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>eju.tv</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6552,13 +6474,13 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
+          <t>Intensa lluvia y granizada en La Paz inundan vías y elevan el nivel de los ríos - eju.tv</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQS2FPaHd3UnFBRjRoa0lKUm1MNUQ5S00zN1RJZE5fWlVUQnhiY0lLcFRkY2JZak1mZ0c2WEVMVUNJVUJTMGFLNHg4S2ZKNTRqLXJHM09ET19hX1pZeTQwUkdEc2huTHVpcno2QTRZbnhralVRWXozcWc1a2pHUEpBeTV1cWgzTWRwaDEweURKeVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNWU9QWElKQXEyN3UxVm4xbzJzbEJ1TU1NTHZlRUp6YndmeU9GQnJKcTluVEJ2ZHQ5cGp3aWhlMUd5ektWQlBpUVNmZnZuRnJwMXlydzAzX0FBVnY5UDMzQTBkWVRNRUNJSlRvX3MyQVhMcEhIMW9WSUpXckVSd0RJWk1KMFBKWmJNU3diQVlEN1Y5aVV6eVBaZXpOMnFIWWxaMlRlY0ZB?oc=5</t>
         </is>
       </c>
       <c r="L39" t="n">
@@ -6568,14 +6490,14 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>-17.97</v>
+        <v>-16.169</v>
       </c>
       <c r="O39" t="n">
-        <v>-67.11</v>
+        <v>-68.09</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>La Paz, La Paz</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -6585,19 +6507,19 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Nuestra Señora de La Paz</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>noticia:51709n</t>
+          <t>noticia:1l4xxfk</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6607,56 +6529,56 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-10-23 13:38</t>
+          <t>2026-10-23 14:51</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1792777139000</v>
+        <v>1792781480000</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>eju.tv</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - eju.tv</t>
+          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPcjZTSmprRGVoNlRqQmdBTE5VM3pRQ1ZFakFUbzVyMUhiaDVkT0liaG9UNEZXekV6bWsycUk4X1JCSEY5RjhNVlZaTk9ULUFuZkY3NnZuWmZ1a19leUhFdlIyQV9kLWxlSkxfeXFhcFRTZjZ2YkpQQlJ1dkNLMDBjaGZ4SkhyQ0RfcnhKSEg5WURCQVQwbENYTHEzUzJSaUEzMGo2bWdyS3lsM016LXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQS2FPaHd3UnFBRjRoa0lKUm1MNUQ5S00zN1RJZE5fWlVUQnhiY0lLcFRkY2JZak1mZ0c2WEVMVUNJVUJTMGFLNHg4S2ZKNTRqLXJHM09ET19hX1pZeTQwUkdEc2huTHVpcno2QTRZbnhralVRWXozcWc1a2pHUEpBeTV1cWgzTWRwaDEweURKeVE?oc=5</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>-17.764</v>
+        <v>-17.97</v>
       </c>
       <c r="O40" t="n">
-        <v>-62.903</v>
+        <v>-67.11</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Cotoca, Santa Cruz</t>
+          <t>Oruro, Oruro</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -6666,19 +6588,19 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Oruro</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>Cotoca</t>
+          <t>Oruro</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>noticia:11rddql</t>
+          <t>noticia:51709n</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6688,56 +6610,56 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-10-23 13:22</t>
+          <t>2026-10-23 13:38</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1792776139000</v>
+        <v>1792777139000</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>eju.tv</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Intensifican acciones preventivas contra el dengue en Caranavi - El Diario - Bolivia</t>
+          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - eju.tv</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOMjhSeDJBek5iaFhDcnFzX1lKelgwZmUwLTJnbEhMdDRMelUxNks5Ti1pRHh3dDhTcC1YZEdqM3FJOGdqVHRvcXVhRlpCQzVDTEZMUFBkV1NrYVQ2LXRqTTBhcGRQc21CQ0VabzZaNExXb1BjTzJ2Uk5BcFF0VG5XOFNRa3lqUWlJSnRFUUVXYnNpbXB0LVVmSXVWSzJxcmVpdVVxUC1KOUhTQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPcjZTSmprRGVoNlRqQmdBTE5VM3pRQ1ZFakFUbzVyMUhiaDVkT0liaG9UNEZXekV6bWsycUk4X1JCSEY5RjhNVlZaTk9ULUFuZkY3NnZuWmZ1a19leUhFdlIyQV9kLWxlSkxfeXFhcFRTZjZ2YkpQQlJ1dkNLMDBjaGZ4SkhyQ0RfcnhKSEg5WURCQVQwbENYTHEzUzJSaUEzMGo2bWdyS3lsM016LXc?oc=5</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N41" t="n">
-        <v>-15.813</v>
+        <v>-17.764</v>
       </c>
       <c r="O41" t="n">
-        <v>-67.46299999999999</v>
+        <v>-62.903</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Caranavi, La Paz</t>
+          <t>Cotoca, Santa Cruz</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -6747,19 +6669,19 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>Caranavi</t>
+          <t>Cotoca</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>noticia:fcm3nx</t>
+          <t>noticia:11rddql</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6769,62 +6691,78 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-10-23 12:58</t>
+          <t>2026-10-23 13:22</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1792774699000</v>
+        <v>1792776139000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>[VIDEO] Así fue el accidente de moto que dejó un adolescente fallecido y un hombre gravemente herido - Red Uno</t>
+          <t>Intensifican acciones preventivas contra el dengue en Caranavi - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOSmJMazhUemNfRHpWcDBoTVFZMUpwdlVKVUtvUXZNTGRRRHlwLW5KNmNhcmFnd1czbi1yalhFMnpSS1dmUE9jVzNlOS1kMWZtRzBHZ2EtcDRDdU5Gc2JUQVIwM2xPa2lZVmswRi1SUFVPcm8xcHlGN3F2UThTSDdKMDNyYnJmVkcxazNLLVBLOWFYM09FVUpmVnN5RVhpSVo2V1VCVmFwQ1gzTmRUWVp2aXMwcmxHRS1GV2p3NTBtR2RzM2wwVHUzaGJkRXJYbHdvaDlhWm5YMTk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOMjhSeDJBek5iaFhDcnFzX1lKelgwZmUwLTJnbEhMdDRMelUxNks5Ti1pRHh3dDhTcC1YZEdqM3FJOGdqVHRvcXVhRlpCQzVDTEZMUFBkV1NrYVQ2LXRqTTBhcGRQc21CQ0VabzZaNExXb1BjTzJ2Uk5BcFF0VG5XOFNRa3lqUWlJSnRFUUVXYnNpbXB0LVVmSXVWSzJxcmVpdVVxUC1KOUhTQQ?oc=5</t>
         </is>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1</v>
-      </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>-15.813</v>
+      </c>
+      <c r="O42" t="n">
+        <v>-67.46299999999999</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Caranavi, La Paz</t>
+        </is>
+      </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>La Paz</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Caranavi</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>noticia:1cjx1qd</t>
+          <t>noticia:fcm3nx</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6834,78 +6772,62 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-10-23 12:39</t>
+          <t>2026-10-23 12:58</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1792773575000</v>
+        <v>1792774699000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Más de 60 municipios en La Paz sufren falta de lluvias - La Patria Bolivia</t>
+          <t>[VIDEO] Así fue el accidente de moto que dejó un adolescente fallecido y un hombre gravemente herido - Red Uno</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE52Qi03Z1J6OS1CR2liRVZ0VlhCcmVQWFV6RUdGNXdrbzZRNXFjTWRaRnc1b3VoV0xaY3RIdncxNlNnYkxyUXo5MTlJWmMwWDNSMDE4ZHI2VkpWajFPaUF2SmRVYkk2eDZYQ1RfUU9ieENrZG9UVVFiaXZSeGI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOSmJMazhUemNfRHpWcDBoTVFZMUpwdlVKVUtvUXZNTGRRRHlwLW5KNmNhcmFnd1czbi1yalhFMnpSS1dmUE9jVzNlOS1kMWZtRzBHZ2EtcDRDdU5Gc2JUQVIwM2xPa2lZVmswRi1SUFVPcm8xcHlGN3F2UThTSDdKMDNyYnJmVkcxazNLLVBLOWFYM09FVUpmVnN5RVhpSVo2V1VCVmFwQ1gzTmRUWVp2aXMwcmxHRS1GV2p3NTBtR2RzM2wwVHUzaGJkRXJYbHdvaDlhWm5YMTk?oc=5</t>
         </is>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="n">
-        <v>-16.169</v>
-      </c>
-      <c r="O43" t="n">
-        <v>-68.09</v>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>La Paz, La Paz</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>La Paz</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>Nuestra Señora de La Paz</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>noticia:11y8tre</t>
+          <t>noticia:1cjx1qd</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6915,56 +6837,56 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-10-23 11:43</t>
+          <t>2026-10-23 12:39</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1792770197000</v>
+        <v>1792773575000</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>La Patria Bolivia</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - Red Uno</t>
+          <t>Más de 60 municipios en La Paz sufren falta de lluvias - La Patria Bolivia</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOVGY3YVRLWWxYM0IycjF4dlNUeUhqZG90Yng4aWhmN3A5ai02WENWYnF4bWpoZHFKMGc1X0JPRHdRRVZfSlA4UmZFa2kxYkNIS3ZtQ1NvNlNCME51eVZTRkRKSUQ5MmRoaWl5Tkt5NHpPUEFwemN2YTV1djFwdHlqQnFqRHNPenhYcTlsanJPcXhpOVV1NmFBUXZyazQ2MkUzM0dSZy02ZllxTGtjcl9ldzdHSktTRlVaalZJc1pubUNQMWFTbzVEOUJ1UmhCdEJt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE52Qi03Z1J6OS1CR2liRVZ0VlhCcmVQWFV6RUdGNXdrbzZRNXFjTWRaRnc1b3VoV0xaY3RIdncxNlNnYkxyUXo5MTlJWmMwWDNSMDE4ZHI2VkpWajFPaUF2SmRVYkk2eDZYQ1RfUU9ieENrZG9UVVFiaXZSeGI?oc=5</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>-17.764</v>
+        <v>-16.169</v>
       </c>
       <c r="O44" t="n">
-        <v>-62.903</v>
+        <v>-68.09</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Cotoca, Santa Cruz</t>
+          <t>La Paz, La Paz</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -6974,42 +6896,42 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>Cotoca</t>
+          <t>Nuestra Señora de La Paz</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>clima:Sucre:2026-10-23:viento:1</t>
+          <t>noticia:11y8tre</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-10-23 06:55</t>
+          <t>2026-10-23 11:43</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1792752927735</v>
+        <v>1792770197000</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7022,56 +6944,52 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Sucre 2026-10-23: 66.2 km/h de ráfagas pronosticadas</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
-        </is>
-      </c>
+          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - Red Uno</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOVGY3YVRLWWxYM0IycjF4dlNUeUhqZG90Yng4aWhmN3A5ai02WENWYnF4bWpoZHFKMGc1X0JPRHdRRVZfSlA4UmZFa2kxYkNIS3ZtQ1NvNlNCME51eVZTRkRKSUQ5MmRoaWl5Tkt5NHpPUEFwemN2YTV1djFwdHlqQnFqRHNPenhYcTlsanJPcXhpOVV1NmFBUXZyazQ2MkUzM0dSZy02ZllxTGtjcl9ldzdHSktTRlVaalZJc1pubUNQMWFTbzVEOUJ1UmhCdEJt?oc=5</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N45" t="n">
-        <v>-19.03</v>
+        <v>-17.764</v>
       </c>
       <c r="O45" t="n">
-        <v>-65.26000000000001</v>
+        <v>-62.903</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Cotoca, Santa Cruz</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>capital (pronóstico puntual)</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>Chuquisaca</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Cotoca</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-24:viento:2</t>
+          <t>clima:Sucre:2026-10-23:viento:1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -7085,7 +7003,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1792752927734</v>
+        <v>1792752927735</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -7098,16 +7016,16 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-24: 85 km/h de ráfagas pronosticadas</t>
+          <t>Sucre 2026-10-23: 66.2 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -7127,14 +7045,14 @@
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>-17.78</v>
+        <v>-19.03</v>
       </c>
       <c r="O46" t="n">
-        <v>-63.18</v>
+        <v>-65.26000000000001</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -7144,65 +7062,65 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Chuquisaca</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Sucre</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>usgs:us6000u49c</t>
+          <t>clima:Santa Cruz:2026-10-24:viento:2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>usgs</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-10-22 22:45</t>
+          <t>2026-10-23 06:55</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1792723541183</v>
+        <v>1792752927734</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>USGS</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>geológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Sismo M 4.5 - 58 km SW of Atocha, Bolivia</t>
+          <t>Santa Cruz 2026-10-24: 85 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Profundidad 236 km</t>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://earthquake.usgs.gov/earthquakes/eventpage/us6000u49c</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L47" t="n">
@@ -7212,59 +7130,59 @@
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>-21.3469</v>
+        <v>-17.78</v>
       </c>
       <c r="O47" t="n">
-        <v>-66.5795</v>
+        <v>-63.18</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>58 km SW of Atocha, Bolivia</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>coordenada de la fuente</t>
+          <t>capital (pronóstico puntual)</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>San Pablo</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-22:viento:1</t>
+          <t>usgs:us6000u49c</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>usgs</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-10-22 21:55</t>
+          <t>2026-10-22 22:45</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1792720528712</v>
+        <v>1792723541183</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>USGS</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>geológica</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7277,17 +7195,17 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-22: 67.7 km/h de ráfagas pronosticadas</t>
+          <t>Sismo M 4.5 - 58 km SW of Atocha, Bolivia</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+          <t>Profundidad 236 km</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://earthquake.usgs.gov/earthquakes/eventpage/us6000u49c</t>
         </is>
       </c>
       <c r="L48" t="n">
@@ -7297,36 +7215,36 @@
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>-17.78</v>
+        <v>-21.3469</v>
       </c>
       <c r="O48" t="n">
-        <v>-63.18</v>
+        <v>-66.5795</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>58 km SW of Atocha, Bolivia</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>capital (pronóstico puntual)</t>
+          <t>coordenada de la fuente</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>San Pablo</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-23:viento:2</t>
+          <t>clima:Santa Cruz:2026-10-22:viento:1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -7353,16 +7271,16 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-23: 83.9 km/h de ráfagas pronosticadas</t>
+          <t>Santa Cruz 2026-10-22: 67.7 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -7411,49 +7329,53 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>noticia:1hhvre7</t>
+          <t>clima:Santa Cruz:2026-10-23:viento:2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-10-22 19:36</t>
+          <t>2026-10-22 21:55</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1792712202000</v>
+        <v>1792720528712</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>El Mundo Bolivia</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Virgen de Cotoca: Controlan incendio en depósito de materiales plásticos - El Mundo Bolivia</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr"/>
+          <t>Santa Cruz 2026-10-23: 83.9 km/h de ráfagas pronosticadas</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcDF6VE5FNzRaWGRuUzFKeXhnZ21DZTRaaEtrVEJEa1Z3ejg2VG1ONG1ENmlDWlkyVjlkQkJwS2F1XzBGMFQwSHd4OEwxTW1PbHdGcUh1ckV6SGpDd2hiN0dkeUVTcnFXT3RjOU1kLXZtVVdZY2hkZS1pcVpVUFhnRktqcHY5UnBrY0xUMDRETjl6N0pXT3A5amxhMA?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L50" t="n">
@@ -7463,19 +7385,19 @@
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>-17.764</v>
+        <v>-17.78</v>
       </c>
       <c r="O50" t="n">
-        <v>-62.903</v>
+        <v>-63.18</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Cotoca, Santa Cruz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
+          <t>capital (pronóstico puntual)</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -7485,14 +7407,14 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>Cotoca</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>noticia:bksnde</t>
+          <t>noticia:1hhvre7</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7502,15 +7424,15 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-10-22 17:01</t>
+          <t>2026-10-22 19:36</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1792702880000</v>
+        <v>1792712202000</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>eju.tv</t>
+          <t>El Mundo Bolivia</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -7528,13 +7450,13 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Reportan un incendio cerca de la carretera a Cotoca - eju.tv</t>
+          <t>Virgen de Cotoca: Controlan incendio en depósito de materiales plásticos - El Mundo Bolivia</t>
         </is>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPNGtpbnBfRnRBalVudnBlZHdVQ0ZSaUplZmtvTGE0aTQzdkxWS3d4My1EZEJ1UE9FNFQ3RmpyZGVsbS1qNEM1QUVFRFAxM2pYT1VqQzRuVjRtZnVNUGlKODNMc0F1a3l6TUpuQmtlUWNlVTVEWWU5ZGZtQm5LWUp3Sg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcDF6VE5FNzRaWGRuUzFKeXhnZ21DZTRaaEtrVEJEa1Z3ejg2VG1ONG1ENmlDWlkyVjlkQkJwS2F1XzBGMFQwSHd4OEwxTW1PbHdGcUh1ckV6SGpDd2hiN0dkeUVTcnFXT3RjOU1kLXZtVVdZY2hkZS1pcVpVUFhnRktqcHY5UnBrY0xUMDRETjl6N0pXT3A5amxhMA?oc=5</t>
         </is>
       </c>
       <c r="L51" t="n">
@@ -7573,7 +7495,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>noticia:17hz69v</t>
+          <t>noticia:bksnde</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -7583,15 +7505,15 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-10-22 13:05</t>
+          <t>2026-10-22 17:01</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1792688709000</v>
+        <v>1792702880000</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>La Razón Digital Bolivia</t>
+          <t>eju.tv</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -7600,45 +7522,61 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Accidente en El Sillar deja al menos 29 heridos - La Razón Digital Bolivia</t>
+          <t>Reportan un incendio cerca de la carretera a Cotoca - eju.tv</t>
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPaXhTdm45YWZnWVFxVzJnb1ZwbUN4SmUtLVdJN0VJdFZBamRyQmFxN0RZelBfTklaSTVyOUZ3ajQ5MFB2TEN4Ukd6TE5ORFY5SEROVk1CZ25sRWJ1QnRBdTVfTktlby1NWXhaVWI5YnRvaDZWbHVjdDVoeFp5Tk5veFk5a19MSWJqcEJVV0dzV3k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPNGtpbnBfRnRBalVudnBlZHdVQ0ZSaUplZmtvTGE0aTQzdkxWS3d4My1EZEJ1UE9FNFQ3RmpyZGVsbS1qNEM1QUVFRFAxM2pYT1VqQzRuVjRtZnVNUGlKODNMc0F1a3l6TUpuQmtlUWNlVTVEWWU5ZGZtQm5LWUp3Sg?oc=5</t>
         </is>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>29</v>
-      </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>-17.764</v>
+      </c>
+      <c r="O52" t="n">
+        <v>-62.903</v>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Cotoca, Santa Cruz</t>
+        </is>
+      </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>Cotoca</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>noticia:1f1qb0</t>
+          <t>noticia:17hz69v</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -7648,15 +7586,15 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-10-22 12:09</t>
+          <t>2026-10-22 13:05</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1792685373000</v>
+        <v>1792688709000</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>La Razón Digital Bolivia</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -7665,61 +7603,45 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Accidente en el tramo Locotal–Villa Tunari: la vía está transitable con precaución - Red Uno</t>
+          <t>Accidente en El Sillar deja al menos 29 heridos - La Razón Digital Bolivia</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTFozcEEwNXBqV19sS2VibXh0MGt0QlhsX1djSTFGQW5zNlFLRHZpNVVnZ1JmWDQ4LVRHX2Rmb3B5UU9qV0FZQmJCaUZYdmwyNG1NenJ4Qzlzd0NJTGs1SjMxdFRtRFBzSUkybGJfZFFaNFZBc21FSUJYSFVkQkVkSEhQaGw0UFVzeXctZHo3cjNsYm5weXJlOU1wcmFncnNhMC1BQUpvNWlDX1NxZXU4b09kVFFWR2tSVEk2UTdXXzB3TjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPaXhTdm45YWZnWVFxVzJnb1ZwbUN4SmUtLVdJN0VJdFZBamRyQmFxN0RZelBfTklaSTVyOUZ3ajQ5MFB2TEN4Ukd6TE5ORFY5SEROVk1CZ25sRWJ1QnRBdTVfTktlby1NWXhaVWI5YnRvaDZWbHVjdDVoeFp5Tk5veFk5a19MSWJqcEJVV0dzV3k?oc=5</t>
         </is>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>-16.556</v>
-      </c>
-      <c r="O53" t="n">
-        <v>-65.569</v>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>Villa Tunari, Cochabamba</t>
-        </is>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>Villa Tunari</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>noticia:wi18tm</t>
+          <t>noticia:1f1qb0</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -7729,11 +7651,11 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-10-22 11:53</t>
+          <t>2026-10-22 12:09</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1792684426000</v>
+        <v>1792685373000</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -7742,49 +7664,65 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>tecnológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Accidente en El Sillar deja heridos y derrame de combustible: esto es lo último que se sabe - Red Uno</t>
+          <t>Accidente en el tramo Locotal–Villa Tunari: la vía está transitable con precaución - Red Uno</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPZHNBTEdaQm5Wby1lTF9mWlQ2aGg0MVc4S0MwVWJ3dUJ5WWU5X3IwYWhKRjk5VWtYWEJHRDF4QldVc29laVNPSTJNWFBDSkNFQlFSYTJUXzNMNF9hckFBN1I2T2xoQUtYQ2V6MDNTZHhHVk9qeTBCdHRpM2ZLd0pyOFRweUUxX19STzRHTHg5VUY5d1lhS0tDeXpCdklqcTZGT1J4R0xnSDhoak1EZ2dtNUhSTUV6b1o0U0VSdWY5X0E3U05Tc1dYVEN2WFZUeFhPMTBJTmowNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTFozcEEwNXBqV19sS2VibXh0MGt0QlhsX1djSTFGQW5zNlFLRHZpNVVnZ1JmWDQ4LVRHX2Rmb3B5UU9qV0FZQmJCaUZYdmwyNG1NenJ4Qzlzd0NJTGs1SjMxdFRtRFBzSUkybGJfZFFaNFZBc21FSUJYSFVkQkVkSEhQaGw0UFVzeXctZHo3cjNsYm5weXJlOU1wcmFncnNhMC1BQUpvNWlDX1NxZXU4b09kVFFWR2tSVEk2UTdXXzB3TjA?oc=5</t>
         </is>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>1</v>
-      </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>-16.556</v>
+      </c>
+      <c r="O54" t="n">
+        <v>-65.569</v>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Villa Tunari, Cochabamba</t>
+        </is>
+      </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Villa Tunari</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>noticia:12gfagq</t>
+          <t>noticia:wi18tm</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -7794,78 +7732,62 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-10-22 11:28</t>
+          <t>2026-10-22 11:53</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1792682880000</v>
+        <v>1792684426000</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>FmBolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>tecnológica</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Reportan triple colisión entre dos camiones y un bus en la carretera Cochabamba-Santa Cruz - FmBolivia</t>
+          <t>Accidente en El Sillar deja heridos y derrame de combustible: esto es lo último que se sabe - Red Uno</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNMTNBaFZNMU9SR25vdVBuNXlZY3g4VkFWYXRiQnNSaUFjemZhUHZWNHg4V2owU2xfNndBak94TnU2cHNUVXdNNWl2eUdHZVNMbVZweTR5M0o0bWdTNUN4QkoxUkI2TDBmVE03M09zRGhJRVFzV0tPZ1NCWEJLUkt1ZGN4UGduOUZMQnJoM0tMYTh0ZlFxaFJNUkJqaWFPazRlMzN3ajhjUEdUYXlZRndpb3RSdTFCX2tCZGJxQ0x4SlBISWJsRVoyN3ZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPZHNBTEdaQm5Wby1lTF9mWlQ2aGg0MVc4S0MwVWJ3dUJ5WWU5X3IwYWhKRjk5VWtYWEJHRDF4QldVc29laVNPSTJNWFBDSkNFQlFSYTJUXzNMNF9hckFBN1I2T2xoQUtYQ2V6MDNTZHhHVk9qeTBCdHRpM2ZLd0pyOFRweUUxX19STzRHTHg5VUY5d1lhS0tDeXpCdklqcTZGT1J4R0xnSDhoak1EZ2dtNUhSTUV6b1o0U0VSdWY5X0E3U05Tc1dYVEN2WFZUeFhPMTBJTmowNA?oc=5</t>
         </is>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="n">
-        <v>-17.39</v>
-      </c>
-      <c r="O55" t="n">
-        <v>-66.16</v>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>Cochabamba, Cochabamba</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>noticia:1uq1bxy</t>
+          <t>noticia:12gfagq</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7875,15 +7797,15 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-10-22 10:44</t>
+          <t>2026-10-22 11:28</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1792680273000</v>
+        <v>1792682880000</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>FmBolivia</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -7901,13 +7823,13 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Reportan triple colisión en la carretera Cochabamba–Santa Cruz - Red Uno</t>
+          <t>Reportan triple colisión entre dos camiones y un bus en la carretera Cochabamba-Santa Cruz - FmBolivia</t>
         </is>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNNUROMzd1UDJRWVZZQ011cFd2c1FSdER1ZzdleU04cXpwYk5HaUZrLXoyU2NzdFk1dnNRUndhUWt0cG9DX09rSjlLcDItU0tzcmQtS3E4dDQ4ZF9HdGJLdk13ek9BNHJUWVlCcklrM25rZ01RbXhLalRBT1FGdDNReHdlTFZkNkJ5ZFd3N3NZVFVmOFUxbEhHN0RsaUxiSVZsM0lXVEFYSHVRQlhsOEtJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNMTNBaFZNMU9SR25vdVBuNXlZY3g4VkFWYXRiQnNSaUFjemZhUHZWNHg4V2owU2xfNndBak94TnU2cHNUVXdNNWl2eUdHZVNMbVZweTR5M0o0bWdTNUN4QkoxUkI2TDBmVE03M09zRGhJRVFzV0tPZ1NCWEJLUkt1ZGN4UGduOUZMQnJoM0tMYTh0ZlFxaFJNUkJqaWFPazRlMzN3ajhjUEdUYXlZRndpb3RSdTFCX2tCZGJxQ0x4SlBISWJsRVoyN3ZR?oc=5</t>
         </is>
       </c>
       <c r="L56" t="n">
@@ -7946,7 +7868,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>noticia:1jl2oid</t>
+          <t>noticia:1uq1bxy</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7956,15 +7878,15 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-10-22 07:49</t>
+          <t>2026-10-22 10:44</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1792669785000</v>
+        <v>1792680273000</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>eju.tv</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -7973,39 +7895,39 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - eju.tv</t>
+          <t>Reportan triple colisión en la carretera Cochabamba–Santa Cruz - Red Uno</t>
         </is>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQbTBrUmlla3FvVU1EX1pxcUI3SXYzbUFFMzlnRzhlSDJwMGpWWURxYjIwSkJBRGdCazMzT01hVy1qMFY3RnJLbC1XNXJ4bU55aDJVeXpNUlRsbzQ3T3hiRXJ5SWlhNmw5cDZFanNoWFBtQ01Gd3dscXltWmU5VHBSQlN3c2IwNGxuVE5tQ3lOT1RmNzRiVi1hc0hn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNNUROMzd1UDJRWVZZQ011cFd2c1FSdER1ZzdleU04cXpwYk5HaUZrLXoyU2NzdFk1dnNRUndhUWt0cG9DX09rSjlLcDItU0tzcmQtS3E4dDQ4ZF9HdGJLdk13ek9BNHJUWVlCcklrM25rZ01RbXhLalRBT1FGdDNReHdlTFZkNkJ5ZFd3N3NZVFVmOFUxbEhHN0RsaUxiSVZsM0lXVEFYSHVRQlhsOEtJ?oc=5</t>
         </is>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>-17.781</v>
+        <v>-17.39</v>
       </c>
       <c r="O57" t="n">
-        <v>-63.139</v>
+        <v>-66.16</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Santa Cruz, Santa Cruz</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -8015,19 +7937,19 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Cochabamba</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>noticia:yqgeq</t>
+          <t>noticia:1jl2oid</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -8037,15 +7959,15 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-10-22 07:43</t>
+          <t>2026-10-22 07:49</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1792669426000</v>
+        <v>1792669785000</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>eju.tv</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -8063,13 +7985,13 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - Red Uno</t>
+          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - eju.tv</t>
         </is>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNVEh1bFlCanFuOTJid2EzYS1meG5oekFJcGFaME1fTk9sUnZpd3U0UXFHUFVJSW1jc1hzM2VFOFprT2xNYjBzbmswZmdJV3dremRIS0I4MDNzRjBnbEttWEhfOWZBbmFrRnNHWDFVLVFoM0VkZkxkaW4tMmZlSFJLei1heTFHMU0wSmxQVVRZN0cwaXQzcDBtZkdwTUFma0RXU2dwLXRnLTBkNGN3Vm1fV3hEdlM1dWZ1SEsw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQbTBrUmlla3FvVU1EX1pxcUI3SXYzbUFFMzlnRzhlSDJwMGpWWURxYjIwSkJBRGdCazMzT01hVy1qMFY3RnJLbC1XNXJ4bU55aDJVeXpNUlRsbzQ3T3hiRXJ5SWlhNmw5cDZFanNoWFBtQ01Gd3dscXltWmU5VHBSQlN3c2IwNGxuVE5tQ3lOT1RmNzRiVi1hc0hn?oc=5</t>
         </is>
       </c>
       <c r="L58" t="n">
@@ -8108,7 +8030,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>noticia:n32ahi</t>
+          <t>noticia:yqgeq</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -8118,69 +8040,150 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-10-22 05:30</t>
+          <t>2026-10-22 07:43</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1792661402000</v>
+        <v>1792669426000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>FmBolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Senamhi anuncia el inicio de la temporada de lluvias en Bolivia y prevé granizadas como la de La Paz - FmBolivia</t>
+          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - Red Uno</t>
         </is>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNVEh1bFlCanFuOTJid2EzYS1meG5oekFJcGFaME1fTk9sUnZpd3U0UXFHUFVJSW1jc1hzM2VFOFprT2xNYjBzbmswZmdJV3dremRIS0I4MDNzRjBnbEttWEhfOWZBbmFrRnNHWDFVLVFoM0VkZkxkaW4tMmZlSFJLei1heTFHMU0wSmxQVVRZN0cwaXQzcDBtZkdwTUFma0RXU2dwLXRnLTBkNGN3Vm1fV3hEdlM1dWZ1SEsw?oc=5</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1</v>
+      </c>
+      <c r="N59" t="n">
+        <v>-17.781</v>
+      </c>
+      <c r="O59" t="n">
+        <v>-63.139</v>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Santa Cruz, Santa Cruz</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Santa Cruz de la Sierra</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>noticia:n32ahi</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>noticia</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-10-22 05:30</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1792661402000</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>FmBolivia</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>meteorológica</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>verde</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Senamhi anuncia el inicio de la temporada de lluvias en Bolivia y prevé granizadas como la de La Paz - FmBolivia</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
           <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQNmVPRnVBMGQzdEI5SUp3Z3ZGVExwTUR6TWNadGQ1QldUS1o2QVFvUl9sVEZKMDVyQVVrS25rU1RSQlJKWXk1YzE0NUhidjhpcmFaSlhZUDZvcE9XcG1KTFNTYmowUU1CSFJNOVR2UHNmMk1iT3N0RVBteHkzZkgyRFROYk1pdkpxVHZya3N2X2FVLVQxbURFVVZlb1NzRjZzTE95TXFVUXFJNkVZakQ2bUhVQzB0SXk3TVhXUTJXa0dycTE1MWVQRFpDX3lDSWFqUGwzU2NtNA?oc=5</t>
         </is>
       </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="n">
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
         <v>-16.169</v>
       </c>
-      <c r="O59" t="n">
+      <c r="O60" t="n">
         <v>-68.09</v>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>La Paz, La Paz</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>nombre de municipio en el titular</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="R60" t="inlineStr">
         <is>
           <t>La Paz</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>Nuestra Señora de La Paz</t>
         </is>
@@ -8750,7 +8753,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-10-25 11:57</t>
+          <t>2026-10-25 12:16</t>
         </is>
       </c>
     </row>
@@ -8773,7 +8776,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4">
@@ -8783,7 +8786,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
@@ -8830,7 +8833,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sala de Situación Bolivia – CCES. Base de eventos de amenazas (datos preliminares de fuentes abiertas). Consulta: 2026-10-25 11:57.</t>
+          <t>Sala de Situación Bolivia – CCES. Base de eventos de amenazas (datos preliminares de fuentes abiertas). Consulta: 2026-10-25 12:16.</t>
         </is>
       </c>
     </row>

--- a/docs/datos/datos_bolivia.xlsx
+++ b/docs/datos/datos_bolivia.xlsx
@@ -8753,7 +8753,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-10-25 12:16</t>
+          <t>2026-10-25 12:17</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sala de Situación Bolivia – CCES. Base de eventos de amenazas (datos preliminares de fuentes abiertas). Consulta: 2026-10-25 12:16.</t>
+          <t>Sala de Situación Bolivia – CCES. Base de eventos de amenazas (datos preliminares de fuentes abiertas). Consulta: 2026-10-25 12:17.</t>
         </is>
       </c>
     </row>

--- a/docs/datos/datos_bolivia.xlsx
+++ b/docs/datos/datos_bolivia.xlsx
@@ -8753,7 +8753,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-10-25 12:17</t>
+          <t>2026-10-25 12:27</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sala de Situación Bolivia – CCES. Base de eventos de amenazas (datos preliminares de fuentes abiertas). Consulta: 2026-10-25 12:17.</t>
+          <t>Sala de Situación Bolivia – CCES. Base de eventos de amenazas (datos preliminares de fuentes abiertas). Consulta: 2026-10-25 12:27.</t>
         </is>
       </c>
     </row>

--- a/docs/datos/datos_bolivia.xlsx
+++ b/docs/datos/datos_bolivia.xlsx
@@ -8753,7 +8753,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-10-25 12:27</t>
+          <t>2026-10-25 12:29</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sala de Situación Bolivia – CCES. Base de eventos de amenazas (datos preliminares de fuentes abiertas). Consulta: 2026-10-25 12:27.</t>
+          <t>Sala de Situación Bolivia – CCES. Base de eventos de amenazas (datos preliminares de fuentes abiertas). Consulta: 2026-10-25 12:29.</t>
         </is>
       </c>
     </row>

--- a/docs/datos/datos_bolivia.xlsx
+++ b/docs/datos/datos_bolivia.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R41"/>
+  <dimension ref="A1:R42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,20 +514,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>noticia:oww2zc</t>
+          <t>manual:1c1299f3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-25 12:08</t>
+          <t>2026-10-25 12:44</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1792944531000</v>
+        <v>1792946640000</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cierran la carretera a Camiri: dos cisternas chocan y provocan un voraz incendio - Red Uno</t>
+          <t>Vuelco de minibus</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -536,18 +536,18 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -555,57 +555,53 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>Registro abierto (sin verificar)</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>-20.05</v>
+        <v>-15.813</v>
       </c>
       <c r="N2" t="n">
-        <v>-63.486</v>
+        <v>-67.46299999999999</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Camiri, Santa Cruz</t>
+          <t>Caranavi, La Paz</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Camiri</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQLXlqSFdvWUVhQUNadnpkdE5lUTZQS0lobThzUTZWbDNJTE94alVhaDBaYU9Fd09SSGt3UlR3Y0dfZlNIcml1ZktnWjctNk1Na3V4S0tINFNkMXM0OHBoV2lCTTBiYXlPUTA3T2ZkeXE2RElYWjhfVHd3Nng1Z0E4alBmOFI5NDFwX09kazZlSWl2OVR2ZVR6MDhvSHFnSmJKbTFXSEFDNFFYcWVDNGtYWEQ0bDhJel9CaEpEZWZ4SWN0TE9Ya0E?oc=5 | https://news.google.com/rss/articles/CBMitgFBVV95cUxPTTF0OUdVS1c1a0lZWmk3bGxHdDJIalpWZTRyQTY3eWE2a2dWOHlsaldKZXpSLWN5c3BkUWdBRkJuSzhHdWl2ZjgwTFFFYnd0aTAxZ3dJU0hCekNZNm9aTTJSZUNfQjVIM3FrUUJ4NXAwa3paZ3BEek9xTVZNQWdnN01xRHloV1ZXZHV6N0JpUWo3RE9DMlFGdkNnWkloTjVVY3RBR1RSRUJJWFVtby1fMWFMNTdLZw?oc=5 | https://news.google.com/rss/articles/CBMiwAFBVV95cUxORUhqeWpKY1FHRWoxaHN0UXFzS3dpeHh6N0NwLUJOZTlZcDVoNHN0VnI0by1qMWtZZEkxVmtUNjdNTFhjaEFQU2IyMlNwZW95WFBzbFJPVVB6TjJtdjNENk1LWVlsMUxUUzBNVzkxRk1HZ3lQU0s2M1lRVlRuaXlkMmJrd3AyTGpIdXItNkhlU3dhTzBRME56Rm1DSlZCYjNxSnNTbTFqNWRoUkdraHhlREhuYldqeFk2N3poWEx2M08?oc=5</t>
-        </is>
-      </c>
+          <t>Caranavi</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>noticia:1sg8pi0</t>
+          <t>noticia:oww2zc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-25 09:59</t>
+          <t>2026-10-25 12:08</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1792936752000</v>
+        <v>1792944531000</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bus de agrupación musical sufre accidente rumbo al trópico de Cochabamba | VIDEO - Red Uno</t>
+          <t>Cierran la carretera a Camiri: dos cisternas chocan y provocan un voraz incendio - Red Uno</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -633,62 +629,62 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>Opinión Bolivia; Red Uno</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>-17.39</v>
+        <v>-20.05</v>
       </c>
       <c r="N3" t="n">
-        <v>-66.16</v>
+        <v>-63.486</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Cochabamba, Cochabamba</t>
+          <t>Camiri, Santa Cruz</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Camiri</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOVDVzVTJNM2JuQ25sMThEaVZNOUNRd3FGT3RhVnFrZXZ2NDQ1YlluTVdhbVNUQnA1MGNESHRSWVUzbC1kRVh3OTR0emtlTG91cmRWeFJ5dk5zb3p2WFRyMEJUV3FNRnY1WHhRUU9WLTlJcmNyNXJZZFdoM0JoZjNpa3hjUXhMM0xrUDJab2VadkM5RWZYQ3lWZTVDdzg1akxJT2lxcDVNNzI0NG1hejdfdkUyTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQLXlqSFdvWUVhQUNadnpkdE5lUTZQS0lobThzUTZWbDNJTE94alVhaDBaYU9Fd09SSGt3UlR3Y0dfZlNIcml1ZktnWjctNk1Na3V4S0tINFNkMXM0OHBoV2lCTTBiYXlPUTA3T2ZkeXE2RElYWjhfVHd3Nng1Z0E4alBmOFI5NDFwX09kazZlSWl2OVR2ZVR6MDhvSHFnSmJKbTFXSEFDNFFYcWVDNGtYWEQ0bDhJel9CaEpEZWZ4SWN0TE9Ya0E?oc=5 | https://news.google.com/rss/articles/CBMiugFBVV95cUxNUTdxSzBJVTZnajZQUXhyTVhwMlpvU0tyZGVBYnFwV2kyZWthenNRT1FDRVJFZnk4ZndGTFQ0cnFXZmZ1WHZaMFhUbWo0SWkzcjcxbjJwU3pKUXR4WEVZLVlRNFpxOUVMY2NNNUZsbmJSMk9xZG1sTklEdEtGSXJyUUp5b0R2dVpYcHJLdTRNRlRjcWpNNXg4c0Z4UWwteFc2dDRqVmpnQnFfQXgwN0twTzl4ZWhYdUtYWGfSAboBQVVfeXFMTVE3cUswSVU2Z2o2UFF4ck1YcDJab1NLcmRlQWJxcFdpMmVrYXpzUU9RQ0VSRWZ5OGZ3RkxUNHJxV2ZmdVh2WjBYVG1qNElpM3I3MW4ycFN6SlF0eFhFWS1ZUTRacTlFTGNjTTVGbG5iUjJPcWRtbE5JRHRLRklyclFKeW9EdnVaWHByS3U0TUZUY3FqTTV4OHNGeFFsLXhXNnQ0alZqZ0JxX0F4MDdLcE85eGVoWHVLWFhn?oc=5 | https://news.google.com/rss/articles/CBMitgFBVV95cUxPTTF0OUdVS1c1a0lZWmk3bGxHdDJIalpWZTRyQTY3eWE2a2dWOHlsaldKZXpSLWN5c3BkUWdBRkJuSzhHdWl2ZjgwTFFFYnd0aTAxZ3dJU0hCekNZNm9aTTJSZUNfQjVIM3FrUUJ4NXAwa3paZ3BEek9xTVZNQWdnN01xRHloV1ZXZHV6N0JpUWo3RE9DMlFGdkNnWkloTjVVY3RBR1RSRUJJWFVtby1fMWFMNTdLZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>noticia:167wlhz</t>
+          <t>noticia:1sg8pi0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25 07:53</t>
+          <t>2026-10-25 09:59</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1792929231000</v>
+        <v>1792936752000</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>¡A sacar el paraguas! Santa cruz amanece con lluvia, frío y complicaciones en el tránsito vehicular - Red Uno</t>
+          <t>Bus de agrupación musical sufre accidente rumbo al trópico de Cochabamba | VIDEO - Red Uno</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -719,62 +715,62 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>-17.781</v>
+        <v>-17.39</v>
       </c>
       <c r="N4" t="n">
-        <v>-63.139</v>
+        <v>-66.16</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Santa Cruz, Santa Cruz</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOY1ZpYktLR3pUQXotUndVR3puUzVHbW1YTzNyUmJvUHB4Q2JmelRvOEdaRldOUm1xLVJnbGR5VWcxTjNEM3ZUYktCUWtVM0hKSjFuRGdpX0JxN0M5MVZBSG1aVURyVWktdmxwbUtRT19ydU5LdzNTZ2Zpb2ozdHlMUUdTVlAyVk4xODBnV0hyTXdVVndyNzV3VC1KMzFnV3lpcFFXSk9MdDZOTWlWakNwT1FnNDh6QVdjazVYZDVVMkdaLU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOVDVzVTJNM2JuQ25sMThEaVZNOUNRd3FGT3RhVnFrZXZ2NDQ1YlluTVdhbVNUQnA1MGNESHRSWVUzbC1kRVh3OTR0emtlTG91cmRWeFJ5dk5zb3p2WFRyMEJUV3FNRnY1WHhRUU9WLTlJcmNyNXJZZFdoM0JoZjNpa3hjUXhMM0xrUDJab2VadkM5RWZYQ3lWZTVDdzg1akxJT2lxcDVNNzI0NG1hejdfdkUyTQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>noticia:bzr7eh</t>
+          <t>noticia:167wlhz</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-25 07:09</t>
+          <t>2026-10-25 07:53</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1792926572000</v>
+        <v>1792929231000</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Alerta naranja por riesgo de desbordes de ríos - El Diario - Bolivia</t>
+          <t>¡A sacar el paraguas! Santa cruz amanece con lluvia, frío y complicaciones en el tránsito vehicular - Red Uno</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>hidrológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -789,74 +785,74 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia; El Mundo Bolivia; FmBolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>-16.169</v>
+        <v>-17.781</v>
       </c>
       <c r="N5" t="n">
-        <v>-68.09</v>
+        <v>-63.139</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>La Paz, La Paz</t>
+          <t>Santa Cruz, Santa Cruz</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Nuestra Señora de La Paz</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNNGZKSDVaZkowWUFGSEUyTWR3d3dsc04waFBLLWUtcVpiTDYzbmNtYTN1RkFLbjAwN3dxT0xZc3pqc3REUXduZVltQ2Fud1BZLTh1bTNiTEJueVUwV0dERS1iUXZqMHd0UnFrQ3E2SFAzbm5lQ1I4U29MaHJFbWFvdVRTeFY4Wl9rSmc3RkpaQ2xwX0oz?oc=5 | https://news.google.com/rss/articles/CBMipwFBVV95cUxPZW00RkxJSklTelNrS2hqczJDWHlwcENFX2lnSEUyTEFPaDFRQ2JvMUcyd3NfYjg0UE9ORGxHRzB4ZDh3U0hQQ1JSQlhsaUY4N3ByMUUxei1SaUZnNlp6T3hsLVdiMGhKaXhsV1FNSUNQMHlvQ19qdk56SEF0d2RXVFctS0VPT25kNGZCRDdvZ2dxU0VoUUJKU0ZBd0ZycFNEZFh0T3ZjOA?oc=5 | https://news.google.com/rss/articles/CBMiwAFBVV95cUxPZm85aHphekQ4U3BZZkp1ZkF6ZVdSUHgtZmltS1FxUUgza1AwcndWWDJZOWctT0RiVmVabmg5SG42NnJWMlJMMnBlYTlYaVdSb09sR0dnVDdpT29faTdiaDUtZElJdlQ3eTdjR2VsWjlta1FOS1U2Vm1vV3JwWkpvbEw1ZUR3akgwQTZnQnVENjJtVkQtVUpKVEJTeWNJSE1CaEFKa2VqMmZXbWk3ekR4ZWpmZ1Z3elFQaWNaNFJuMXA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOY1ZpYktLR3pUQXotUndVR3puUzVHbW1YTzNyUmJvUHB4Q2JmelRvOEdaRldOUm1xLVJnbGR5VWcxTjNEM3ZUYktCUWtVM0hKSjFuRGdpX0JxN0M5MVZBSG1aVURyVWktdmxwbUtRT19ydU5LdzNTZ2Zpb2ozdHlMUUdTVlAyVk4xODBnV0hyTXdVVndyNzV3VC1KMzFnV3lpcFFXSk9MdDZOTWlWakNwT1FnNDh6QVdjazVYZDVVMkdaLU0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>noticia:1fo4ig4</t>
+          <t>noticia:bzr7eh</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-25 01:08</t>
+          <t>2026-10-25 07:09</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1792904880000</v>
+        <v>1792926572000</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
+          <t>Alerta naranja por riesgo de desbordes de ríos - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>hidrológica</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>roja</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -867,41 +863,57 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>diarioelpueblo.com.pe</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
+          <t>El Diario - Bolivia; El Mundo Bolivia; FmBolivia</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>-16.169</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-68.09</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>La Paz, La Paz</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>La Paz</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Nuestra Señora de La Paz</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQcmFrT3dwcEs0X3U2NWxnOGJwNnI2WHdWTGZYbzEyNnJzUWhkbU9TRWhfSlB5UkMwX2gyMmxYUmVNWmxNOVR6V0twRHpFMTVIYjBKbHQ2TXN2d2w5dkFpcWJCcUJMZldaX01sNWtQV2ZJOGpRVzR3NDVIU0pJc1BNVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNNGZKSDVaZkowWUFGSEUyTWR3d3dsc04waFBLLWUtcVpiTDYzbmNtYTN1RkFLbjAwN3dxT0xZc3pqc3REUXduZVltQ2Fud1BZLTh1bTNiTEJueVUwV0dERS1iUXZqMHd0UnFrQ3E2SFAzbm5lQ1I4U29MaHJFbWFvdVRTeFY4Wl9rSmc3RkpaQ2xwX0oz?oc=5 | https://news.google.com/rss/articles/CBMipwFBVV95cUxPZW00RkxJSklTelNrS2hqczJDWHlwcENFX2lnSEUyTEFPaDFRQ2JvMUcyd3NfYjg0UE9ORGxHRzB4ZDh3U0hQQ1JSQlhsaUY4N3ByMUUxei1SaUZnNlp6T3hsLVdiMGhKaXhsV1FNSUNQMHlvQ19qdk56SEF0d2RXVFctS0VPT25kNGZCRDdvZ2dxU0VoUUJKU0ZBd0ZycFNEZFh0T3ZjOA?oc=5 | https://news.google.com/rss/articles/CBMiwAFBVV95cUxPZm85aHphekQ4U3BZZkp1ZkF6ZVdSUHgtZmltS1FxUUgza1AwcndWWDJZOWctT0RiVmVabmg5SG42NnJWMlJMMnBlYTlYaVdSb09sR0dnVDdpT29faTdiaDUtZElJdlQ3eTdjR2VsWjlta1FOS1U2Vm1vV3JwWkpvbEw1ZUR3akgwQTZnQnVENjJtVkQtVUpKVEJTeWNJSE1CaEFKa2VqMmZXbWk3ekR4ZWpmZ1Z3elFQaWNaNFJuMXA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>noticia:r1uot6</t>
+          <t>noticia:1fo4ig4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-24 20:00</t>
+          <t>2026-10-25 01:08</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1792886439000</v>
+        <v>1792904880000</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>vuelco deja heridos en ruta Oruro – Huanuni - La Patria Bolivia</t>
+          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -910,18 +922,18 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>roja</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -933,53 +945,37 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>-17.97</v>
-      </c>
-      <c r="N7" t="n">
-        <v>-67.11</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Oruro, Oruro</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Oruro</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Oruro</t>
-        </is>
-      </c>
+          <t>diarioelpueblo.com.pe</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNNDQtMG1KT1lLWW5nem9Jbm5JWDZKNlRWZmFmRlBxWDlDeXlSWnJ5d2NsTlpxa0JIS25oVWVZOC1majZVbWhOVDIxR0dLOFlzY2VpVzVoVk1mQnF3dXVwLUFZVHc1UjlXZzF5T05CY3U0ZldLVkw1VzBTek5zanpjQW1xalltWHNiaXI3dTNR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQcmFrT3dwcEs0X3U2NWxnOGJwNnI2WHdWTGZYbzEyNnJzUWhkbU9TRWhfSlB5UkMwX2gyMmxYUmVNWmxNOVR6V0twRHpFMTVIYjBKbHQ2TXN2d2w5dkFpcWJCcUJMZldaX01sNWtQV2ZJOGpRVzR3NDVIU0pJc1BNVg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>noticia:1ytw450</t>
+          <t>noticia:r1uot6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-24 18:58</t>
+          <t>2026-10-24 20:00</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1792882686000</v>
+        <v>1792886439000</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
+          <t>vuelco deja heridos en ruta Oruro – Huanuni - La Patria Bolivia</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -988,18 +984,18 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>roja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1011,37 +1007,53 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>diarioelpueblo.com.pe</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
+          <t>La Patria Bolivia</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>-17.97</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-67.11</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Oruro, Oruro</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNZ1U3bEVuaVdjVE1zSU9lOHJZTVRZLVZaemhldGNnT1JBWDJvbzdvM3paVVNhLUlyWHF2akNuSXJOLXdyTGRuejRlV1FuMjVkTjA3NmdRdmgtRWlUeTFBV1dEMzBvejBxaXZJdUZZWkRVTF9VLU5BcjFGZGFEQ09WWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNNDQtMG1KT1lLWW5nem9Jbm5JWDZKNlRWZmFmRlBxWDlDeXlSWnJ5d2NsTlpxa0JIS25oVWVZOC1majZVbWhOVDIxR0dLOFlzY2VpVzVoVk1mQnF3dXVwLUFZVHc1UjlXZzF5T05CY3U0ZldLVkw1VzBTek5zanpjQW1xalltWHNiaXI3dTNR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>noticia:1g006zh</t>
+          <t>noticia:1ytw450</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-24 17:02</t>
+          <t>2026-10-24 18:58</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1792875752000</v>
+        <v>1792882686000</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a Mayaya deja siete heridos del grupo Los Chicos Fieles - El Potosí</t>
+          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1050,18 +1062,18 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>roja</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1069,57 +1081,41 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>EL DÍA - Noticias de Bolivia para el mundo; El Potosí; La Razón Digital Bolivia; Opinión Bolivia</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>-19.58</v>
-      </c>
-      <c r="N9" t="n">
-        <v>-65.75</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Potosí, Potosí</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
+          <t>diarioelpueblo.com.pe</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPTGQwaVBfdG1JdVRMUTN4LVVvN0ppc3dreDJVVllDR3RmX0xpMzB4b0pvVTNSV1B6T0ZEWTdEZkNsRUdSNzhLaC1CWHN5WktNWk1nRWpTdVZiYjI3TlJlX2xlVTI5MjlRU2hiY1gteml4YWVFbDNPSVRBZmtITlQzbmhaUXVmcThRa2xsQTJIOXZuNzlSdm12MEdyOEZHdw?oc=5 | https://news.google.com/rss/articles/CBMizwFBVV95cUxPeGd3VWpCWXJ0YTJIeDJLcktzWG1jdUh0TjFXb01wSTkxbHNXZU94VWNDMkxnTjlJZVdpbkprMEY2NE80RXYyUWxUQXVnbl9lUXR2b28zTEh6cTJLVEQ4TUNja2kzRlhadVBFZFVwV1U2TlhseXZMZ20zZTZiUFpWRjdCOWNBMHU5XzdMV3JqQjV4TEE3bHRMOXR6Nm55eHZUNnFHSDdVRk8zVkY4RkVsUUtUN0JYdkREWGZncmJ3ZWc2T1BuUm1ZLTlfcHVabFE?oc=5 | https://news.google.com/rss/articles/CBMizAFBVV95cUxNYjNxaHg3YllRRTJYdFd1clAtUlROSGlFNVg5eUVZUGJoOEZ4MWM5QU5WQm1YTDc4NXc3SjhWMUw0TkZfSHlMLUQ1bmpTME1Kb1JaM0ExamFHYTd3VlU4MXRWdTZ1bzh1SGYtbGE1a3dBaG93bjg1OGc0S0JfRE43c3dVMVltN0dQQzNhQUNhM0FjVUNRUDRSamlJYlk2dEJpUTBuY2hBcTFucTVRN0ZtYnc5bzdmTV9LQm1uVUxaZS1tUE9IejhBVDRCdU_SAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNZ1U3bEVuaVdjVE1zSU9lOHJZTVRZLVZaemhldGNnT1JBWDJvbzdvM3paVVNhLUlyWHF2akNuSXJOLXdyTGRuejRlV1FuMjVkTjA3NmdRdmgtRWlUeTFBV1dEMzBvejBxaXZJdUZZWkRVTF9VLU5BcjFGZGFEQ09WWQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>noticia:1ukcn97</t>
+          <t>noticia:1g006zh</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-24 13:26</t>
+          <t>2026-10-24 17:02</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1792862794000</v>
+        <v>1792875752000</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Esta es la lista preliminar de los heridos en el accidente del grupo 'Los chicos fieles', el conductor está grave - El Deber</t>
+          <t>Accidente en la carretera a Mayaya deja siete heridos del grupo Los Chicos Fieles - El Potosí</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1139,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1147,46 +1143,62 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>El Deber; Red Uno</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
+          <t>EL DÍA - Noticias de Bolivia para el mundo; El Potosí; La Razón Digital Bolivia; Opinión Bolivia</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>-19.58</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-65.75</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Potosí, Potosí</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Potosí</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Potosí</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOczZKbFd1QzRpak92LXpPWXZXQXJObnBQTG9qRFBlUUV5dThMWXhzckFFUHAyb2thU1JwRmJDSEZfaEdTUXh1bjZvQWpYMGhfUno3cWZ4MGpldEpoQXhzSlVzTm5LLW9OcjB2MWRsdHQ2UlI2SjEtZ085ZTR5Z3pEVmtBTF9lc29Kd0RhaTRUWkM4eGZJNWhBSXZqWmxuNW10dlQwYW9mdzItcWZWTkU0?oc=5 | https://news.google.com/rss/articles/CBMivAFBVV95cUxPczBQcnE2SzFGMXc3b1lsTkNxVWRmS3Vnb01xOTV2WmVva3J2RVlteWpHZ3VJS2dNWGV5NW5FX3ZncnVKTEVDTGpBRndTU1FxeWxtaS1fb1FscGxXMWNXUE9zbHdob1AxVFl1eHB5OU1yUnNoOXJ6U21oVG9PVDA1ak1xQl9hUlB4V0RaQXJqZENGUm8zMUJEY3J0WW5ENE5ObWJLNmpWN0RkSmFJbnZUZGR5UFRPd3QyUFY4WQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPTGQwaVBfdG1JdVRMUTN4LVVvN0ppc3dreDJVVllDR3RmX0xpMzB4b0pvVTNSV1B6T0ZEWTdEZkNsRUdSNzhLaC1CWHN5WktNWk1nRWpTdVZiYjI3TlJlX2xlVTI5MjlRU2hiY1gteml4YWVFbDNPSVRBZmtITlQzbmhaUXVmcThRa2xsQTJIOXZuNzlSdm12MEdyOEZHdw?oc=5 | https://news.google.com/rss/articles/CBMizwFBVV95cUxPeGd3VWpCWXJ0YTJIeDJLcktzWG1jdUh0TjFXb01wSTkxbHNXZU94VWNDMkxnTjlJZVdpbkprMEY2NE80RXYyUWxUQXVnbl9lUXR2b28zTEh6cTJLVEQ4TUNja2kzRlhadVBFZFVwV1U2TlhseXZMZ20zZTZiUFpWRjdCOWNBMHU5XzdMV3JqQjV4TEE3bHRMOXR6Nm55eHZUNnFHSDdVRk8zVkY4RkVsUUtUN0JYdkREWGZncmJ3ZWc2T1BuUm1ZLTlfcHVabFE?oc=5 | https://news.google.com/rss/articles/CBMizAFBVV95cUxNYjNxaHg3YllRRTJYdFd1clAtUlROSGlFNVg5eUVZUGJoOEZ4MWM5QU5WQm1YTDc4NXc3SjhWMUw0TkZfSHlMLUQ1bmpTME1Kb1JaM0ExamFHYTd3VlU4MXRWdTZ1bzh1SGYtbGE1a3dBaG93bjg1OGc0S0JfRE43c3dVMVltN0dQQzNhQUNhM0FjVUNRUDRSamlJYlk2dEJpUTBuY2hBcTFucTVRN0ZtYnc5bzdmTV9LQm1uVUxaZS1tUE9IejhBVDRCdU_SAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>noticia:2avehj</t>
+          <t>noticia:1ukcn97</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-24 12:53</t>
+          <t>2026-10-24 13:26</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1792860813000</v>
+        <v>1792862794000</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sequía en Cochabamba: más de un centenar de cabezas de ganado murieron en el cono sur - Red Uno</t>
+          <t>Esta es la lista preliminar de los heridos en el accidente del grupo 'Los chicos fieles', el conductor está grave - El Deber</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>climatológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -1198,10 +1210,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1209,62 +1221,46 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Red Uno</t>
-        </is>
-      </c>
-      <c r="M11" t="n">
-        <v>-17.39</v>
-      </c>
-      <c r="N11" t="n">
-        <v>-66.16</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Cochabamba, Cochabamba</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
+          <t>El Deber; Red Uno</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOOFQxc2Vzc0QwS19ydC13RkRPZnZQU3JkSTl5U3kzdUdMSldTcm5HVEhWRzZyN19CLUlwcUs4MW03Ui1obVBtdzQ3QWFQc1RKdzh3MXJ5QkpRS2pRNm50V1lVb09ScGJnaVVlemVfZlRsWjdObnRmR1FGMnlMMHAyc2pMandndy10T2twcWx6OFh4UHdvbVlFbllwME9WQ2pQVjNTQzBxeTg5YnF3bDREeHVDYXpObFFIaTZZQWtYUE12cGQ1ZGRhT0syNjVhZWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOczZKbFd1QzRpak92LXpPWXZXQXJObnBQTG9qRFBlUUV5dThMWXhzckFFUHAyb2thU1JwRmJDSEZfaEdTUXh1bjZvQWpYMGhfUno3cWZ4MGpldEpoQXhzSlVzTm5LLW9OcjB2MWRsdHQ2UlI2SjEtZ085ZTR5Z3pEVmtBTF9lc29Kd0RhaTRUWkM4eGZJNWhBSXZqWmxuNW10dlQwYW9mdzItcWZWTkU0?oc=5 | https://news.google.com/rss/articles/CBMivAFBVV95cUxPczBQcnE2SzFGMXc3b1lsTkNxVWRmS3Vnb01xOTV2WmVva3J2RVlteWpHZ3VJS2dNWGV5NW5FX3ZncnVKTEVDTGpBRndTU1FxeWxtaS1fb1FscGxXMWNXUE9zbHdob1AxVFl1eHB5OU1yUnNoOXJ6U21oVG9PVDA1ak1xQl9hUlB4V0RaQXJqZENGUm8zMUJEY3J0WW5ENE5ObWJLNmpWN0RkSmFJbnZUZGR5UFRPd3QyUFY4WQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>noticia:3dv7b0</t>
+          <t>noticia:2avehj</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-24 11:43</t>
+          <t>2026-10-24 12:53</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1792856591000</v>
+        <v>1792860813000</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Accidente en Caranavi: vehículo de Los Chicos Fieles cae a un barranco y deja varios heridos - FmBolivia</t>
+          <t>Sequía en Cochabamba: más de un centenar de cabezas de ganado murieron en el cono sur - Red Uno</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>climatológica</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -1276,10 +1272,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1287,62 +1283,62 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>FmBolivia; La Patria Bolivia; Red Uno</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>-15.813</v>
+        <v>-17.39</v>
       </c>
       <c r="N12" t="n">
-        <v>-67.46299999999999</v>
+        <v>-66.16</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Caranavi, La Paz</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Caranavi</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNeEFrOEtOMHZxMW42REFPU0x1MG5oQjlBMkJucWRLZ292alBXekJKeURBN3NLTVVadWI0OWF4UGtSVXBzTE01eWFSU1kyMUhNZ04zMWNMaUxnMDBBZ0EwTktXbjlaVTBUUmNqa3AwY19KNTU2LWh5LW9IVElVdTdnaHFPanJPd2FqMUxzaUhXZmVpYU1saGc?oc=5 | https://news.google.com/rss/articles/CBMi2wFBVV95cUxOdTVUZUQxVTdvYTdONDQxVlhUTzBOS2hKLW1rS1NUcmRYRnlCVlhIcHZlSjdsaktkQm5CWkFYa3lDQkxnMlh0b3prX0lha1BtbW1qS1VuYnNiX3FiZkYyNDJDR0tqZ0pKMU5TeC04SXV4UUJOTUlPUTB6ek01bzUxTUsydjZqZzI3S3ZLUnRWSUFUVk44WEpKUl9rbzRLb2IwYl9sLVlrYmt5d2ZHNUtGd3lRNnYzMlhuMkJOZW1XSUl2N1BxZWpHbm5XTDJhRUtnR190QWQ1TDlTUVk?oc=5 | https://news.google.com/rss/articles/CBMizAFBVV95cUxNcE1KaHZyUTJCSElxRU9nVzdhTnczWjJGTEhFMEs0bHp2cUdFeHd3VTB0NmVFcjdEN1dsZDZLY2k1ZFFUWkhKV19PU3V2czNyamh1ZE9YajVSVF8xczF6OFhZcWFvYV9EcWg4ZDNCb2p3enhXbFpRYnJMdGdaTXNrWUZSYVhKNTVicWlCLTJ5OE05Z1BvNEx1eEloUk5qTGN3ZHNzbzZWSVljbnRmSERJUWdxRDc0MjJxMGtycWJaaVhXQUUxVUlaWVZLOWE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOOFQxc2Vzc0QwS19ydC13RkRPZnZQU3JkSTl5U3kzdUdMSldTcm5HVEhWRzZyN19CLUlwcUs4MW03Ui1obVBtdzQ3QWFQc1RKdzh3MXJ5QkpRS2pRNm50V1lVb09ScGJnaVVlemVfZlRsWjdObnRmR1FGMnlMMHAyc2pMandndy10T2twcWx6OFh4UHdvbVlFbllwME9WQ2pQVjNTQzBxeTg5YnF3bDREeHVDYXpObFFIaTZZQWtYUE12cGQ1ZGRhT0syNjVhZWs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>clima:Potosí:2026-10-24:viento:1</t>
+          <t>noticia:3dv7b0</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-24 10:55</t>
+          <t>2026-10-24 11:43</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1792853727284</v>
+        <v>1792856591000</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Potosí 2026-10-24: 60.5 km/h de ráfagas pronosticadas</t>
+          <t>Accidente en Caranavi: vehículo de Los Chicos Fieles cae a un barranco y deja varios heridos - FmBolivia</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1357,7 +1353,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1365,57 +1361,57 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>FmBolivia; La Patria Bolivia; Red Uno</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>-19.58</v>
+        <v>-15.813</v>
       </c>
       <c r="N13" t="n">
-        <v>-65.75</v>
+        <v>-67.46299999999999</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Caranavi, La Paz</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Caranavi</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNeEFrOEtOMHZxMW42REFPU0x1MG5oQjlBMkJucWRLZ292alBXekJKeURBN3NLTVVadWI0OWF4UGtSVXBzTE01eWFSU1kyMUhNZ04zMWNMaUxnMDBBZ0EwTktXbjlaVTBUUmNqa3AwY19KNTU2LWh5LW9IVElVdTdnaHFPanJPd2FqMUxzaUhXZmVpYU1saGc?oc=5 | https://news.google.com/rss/articles/CBMi2wFBVV95cUxOdTVUZUQxVTdvYTdONDQxVlhUTzBOS2hKLW1rS1NUcmRYRnlCVlhIcHZlSjdsaktkQm5CWkFYa3lDQkxnMlh0b3prX0lha1BtbW1qS1VuYnNiX3FiZkYyNDJDR0tqZ0pKMU5TeC04SXV4UUJOTUlPUTB6ek01bzUxTUsydjZqZzI3S3ZLUnRWSUFUVk44WEpKUl9rbzRLb2IwYl9sLVlrYmt5d2ZHNUtGd3lRNnYzMlhuMkJOZW1XSUl2N1BxZWpHbm5XTDJhRUtnR190QWQ1TDlTUVk?oc=5 | https://news.google.com/rss/articles/CBMizAFBVV95cUxNcE1KaHZyUTJCSElxRU9nVzdhTnczWjJGTEhFMEs0bHp2cUdFeHd3VTB0NmVFcjdEN1dsZDZLY2k1ZFFUWkhKV19PU3V2czNyamh1ZE9YajVSVF8xczF6OFhZcWFvYV9EcWg4ZDNCb2p3enhXbFpRYnJMdGdaTXNrWUZSYVhKNTVicWlCLTJ5OE05Z1BvNEx1eEloUk5qTGN3ZHNzbzZWSVljbnRmSERJUWdxRDc0MjJxMGtycWJaaVhXQUUxVUlaWVZLOWE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>noticia:1ax0bpy</t>
+          <t>clima:Potosí:2026-10-24:viento:1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-24 10:32</t>
+          <t>2026-10-24 10:55</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1792852364000</v>
+        <v>1792853727284</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Creció el Bermejo tras la tormenta: así está el puerto de chalanas en este momento - Que Pasa Salta</t>
+          <t>Potosí 2026-10-24: 60.5 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1424,11 +1420,11 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1447,58 +1443,58 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Que Pasa Salta</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>-22.721</v>
+        <v>-19.58</v>
       </c>
       <c r="N14" t="n">
-        <v>-64.32599999999999</v>
+        <v>-65.75</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Bermejo, Tarija</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tarija</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Bermejo</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVld9IBfkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVldw?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>gdacs:WF1033142:0</t>
+          <t>noticia:1ax0bpy</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-24 07:06</t>
+          <t>2026-10-24 10:32</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1792839995000</v>
+        <v>1792852364000</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Green forest fire notification in Bolivia</t>
+          <t>Creció el Bermejo tras la tormenta: así está el puerto de chalanas en este momento - Que Pasa Salta</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1525,58 +1521,58 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>GDACS</t>
+          <t>Que Pasa Salta</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>-13.06332</v>
+        <v>-22.721</v>
       </c>
       <c r="N15" t="n">
-        <v>-67.66426</v>
+        <v>-64.32599999999999</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Bermejo, Tarija</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Tarija</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Ixiamas</t>
+          <t>Bermejo</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>http://www.gdacs.org/report.aspx?eventtype=WF&amp;eventid=1033142</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVld9IBfkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVldw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>noticia:1shhqva</t>
+          <t>gdacs:WF1033142:0</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-24 06:33</t>
+          <t>2026-10-24 07:06</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1792838034000</v>
+        <v>1792839995000</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
+          <t>Green forest fire notification in Bolivia</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1599,70 +1595,70 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>GDACS</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>-17.97</v>
+        <v>-13.06332</v>
       </c>
       <c r="N16" t="n">
-        <v>-67.11</v>
+        <v>-67.66426</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Ixiamas</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQYzB6N082XzFRRnVtcDVmUkYyWjcxUzV2Z3Frd1I0WDNXSnZtY0QzOU1PUkNLMktVT1Vra2FSeXhxZDRuOFZYZjFwejl6ejJTbWY2MGJuSGN3ZHdrdG5JUkgzSXBkbDYtaHlackY3OVFuNWdLcFNpdWNHRU9vNGdoVWx2ODFVdzJXYUxnM0tUcjJvZmc?oc=5 | https://news.google.com/rss/articles/CBMikAFBVV95cUxQS2FPaHd3UnFBRjRoa0lKUm1MNUQ5S00zN1RJZE5fWlVUQnhiY0lLcFRkY2JZak1mZ0c2WEVMVUNJVUJTMGFLNHg4S2ZKNTRqLXJHM09ET19hX1pZeTQwUkdEc2huTHVpcno2QTRZbnhralVRWXozcWc1a2pHUEpBeTV1cWgzTWRwaDEweURKeVE?oc=5</t>
+          <t>http://www.gdacs.org/report.aspx?eventtype=WF&amp;eventid=1033142</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>clima:Potosí:2026-10-25:viento:1</t>
+          <t>noticia:1shhqva</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-24 02:55</t>
+          <t>2026-10-24 06:33</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1792824927736</v>
+        <v>1792838034000</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Potosí 2026-10-25: 60.5 km/h de ráfagas pronosticadas</t>
+          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1677,62 +1673,62 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>-19.58</v>
+        <v>-17.97</v>
       </c>
       <c r="N17" t="n">
-        <v>-65.75</v>
+        <v>-67.11</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Oruro, Oruro</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Oruro</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Oruro</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQYzB6N082XzFRRnVtcDVmUkYyWjcxUzV2Z3Frd1I0WDNXSnZtY0QzOU1PUkNLMktVT1Vra2FSeXhxZDRuOFZYZjFwejl6ejJTbWY2MGJuSGN3ZHdrdG5JUkgzSXBkbDYtaHlackY3OVFuNWdLcFNpdWNHRU9vNGdoVWx2ODFVdzJXYUxnM0tUcjJvZmc?oc=5 | https://news.google.com/rss/articles/CBMikAFBVV95cUxQS2FPaHd3UnFBRjRoa0lKUm1MNUQ5S00zN1RJZE5fWlVUQnhiY0lLcFRkY2JZak1mZ0c2WEVMVUNJVUJTMGFLNHg4S2ZKNTRqLXJHM09ET19hX1pZeTQwUkdEc2huTHVpcno2QTRZbnhralVRWXozcWc1a2pHUEpBeTV1cWgzTWRwaDEweURKeVE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>noticia:1uil931</t>
+          <t>clima:Potosí:2026-10-25:viento:1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-23 22:49</t>
+          <t>2026-10-24 02:55</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1792810149000</v>
+        <v>1792824927736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Accidente de tránsito en la ruta hacia Alto Beni deja varios heridos - El Deber</t>
+          <t>Potosí 2026-10-25: 60.5 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1747,7 +1743,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1755,62 +1751,62 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>El Deber</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>-15.578</v>
+        <v>-19.58</v>
       </c>
       <c r="N18" t="n">
-        <v>-67.44</v>
+        <v>-65.75</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Alto Beni, La Paz</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Alto Beni</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQakFJRmx3RlJEMkVHU0pxWXZ2ZU1ib04tZy1yeTB2OGhrYk9CU3pMaDVpRThNZktZMS14UzA2Y1VIcEQtZDg3cEU2SmlzQnBmUVVvM0ZNYzZWNExWUXQ3aHpnd3lqOHFVV3pNbDRLS1NQNGtwb2RjSFpleHJkOG5zSXVtWjVIS1dLejNybktRWTJVZXh3WkFUQVE5T2tMdFdn?oc=5 | https://news.google.com/rss/articles/CBMilwFBVV95cUxQMF9BNnUzLURKNGRMUUJ1VXVRSXNnMlBsQnVXOG0tRlFtY3pvRDNPQmNJMWN2RzJVaWdoWndmcHFnTkZFZnJxRkZtMThYYWlwN09ueUgtei1pSE1hZ2FtSzN6elY4VXJHbzFxdll0eWh0ZkxwQkQ1SDZ5b0E3MlVENGZEWGZHUGlwVG4wd2x3OFNEMVpibnFr?oc=5 | https://news.google.com/rss/articles/CBMimgFBVV95cUxNbmwzSnd6c2tFMXBWY0tiemJqRm5CNllOT2p1U0FhdW5QNGFBVXlSZVM1ak5jNGZvcXNVaUQzN3ZQQTlPbmVjQ2Y5RFl2dWVLeUN5NUFodDF0alEyZWlmOHFZWkVVbjdQbkl3ZWtmS25wQWM2TmRZZDBGM2xlS0ZhUzAweXRmcmhVWGY5dV9CUnFBNGtWZHZDSWVB?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-24:viento:1</t>
+          <t>noticia:1uil931</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-23 20:55</t>
+          <t>2026-10-23 22:49</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1792803329663</v>
+        <v>1792810149000</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-24: 78.1 km/h de ráfagas pronosticadas</t>
+          <t>Accidente de tránsito en la ruta hacia Alto Beni deja varios heridos - El Deber</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1825,7 +1821,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1833,57 +1829,57 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>El Deber</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>-17.78</v>
+        <v>-15.578</v>
       </c>
       <c r="N19" t="n">
-        <v>-63.18</v>
+        <v>-67.44</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Alto Beni, La Paz</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Alto Beni</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQakFJRmx3RlJEMkVHU0pxWXZ2ZU1ib04tZy1yeTB2OGhrYk9CU3pMaDVpRThNZktZMS14UzA2Y1VIcEQtZDg3cEU2SmlzQnBmUVVvM0ZNYzZWNExWUXQ3aHpnd3lqOHFVV3pNbDRLS1NQNGtwb2RjSFpleHJkOG5zSXVtWjVIS1dLejNybktRWTJVZXh3WkFUQVE5T2tMdFdn?oc=5 | https://news.google.com/rss/articles/CBMilwFBVV95cUxQMF9BNnUzLURKNGRMUUJ1VXVRSXNnMlBsQnVXOG0tRlFtY3pvRDNPQmNJMWN2RzJVaWdoWndmcHFnTkZFZnJxRkZtMThYYWlwN09ueUgtei1pSE1hZ2FtSzN6elY4VXJHbzFxdll0eWh0ZkxwQkQ1SDZ5b0E3MlVENGZEWGZHUGlwVG4wd2x3OFNEMVpibnFr?oc=5 | https://news.google.com/rss/articles/CBMimgFBVV95cUxNbmwzSnd6c2tFMXBWY0tiemJqRm5CNllOT2p1U0FhdW5QNGFBVXlSZVM1ak5jNGZvcXNVaUQzN3ZQQTlPbmVjQ2Y5RFl2dWVLeUN5NUFodDF0alEyZWlmOHFZWkVVbjdQbkl3ZWtmS25wQWM2TmRZZDBGM2xlS0ZhUzAweXRmcmhVWGY5dV9CUnFBNGtWZHZDSWVB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>noticia:rabz5p</t>
+          <t>clima:Santa Cruz:2026-10-24:viento:1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-23 20:44</t>
+          <t>2026-10-23 20:55</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1792802686000</v>
+        <v>1792803329663</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tome previsiones: se pronostican lluvias y ambiente caluroso para este fin de semana en Cochabamba - Red Uno</t>
+          <t>Santa Cruz 2026-10-24: 78.1 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1892,11 +1888,11 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1915,70 +1911,70 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>-17.39</v>
+        <v>-17.78</v>
       </c>
       <c r="N20" t="n">
-        <v>-66.16</v>
+        <v>-63.18</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Cochabamba, Cochabamba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTlU5NVFpY1RheTN5ZE1IbG5VYTh2Sk5hZHpHeWI3LVdnSFg2cFJFdnBCVkxiUjNKcUgyUW16SWxpMXFkMHdad2xFN043bklJeG1iQ0V1V3hBZk1Ga3NscjdPVWUySmt4bDNTdWlmSUdOMmNlZ2hkSWZFMmk4VGs0Nm9TcnRCTDhINmtnQU9zZDBUY05HcWpxN3FOX3N1dmVJblE0MGc5di1Ma1N2dGNxOUtoV1MzNnl1OXpRaTZ2UGxMc3RDWndubHVQNUd0eVROMGR2OGxVemtOaEc4bTNRaA?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>noticia:1jfk053</t>
+          <t>noticia:rabz5p</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-23 19:08</t>
+          <t>2026-10-23 20:44</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1792796931000</v>
+        <v>1792802686000</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sequía en Pasorapa: el ganado muere por falta de agua y alistan declaratoria de desastre - Red Uno</t>
+          <t>Tome previsiones: se pronostican lluvias y ambiente caluroso para este fin de semana en Cochabamba - Red Uno</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>climatológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -1997,14 +1993,14 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>-18.38</v>
+        <v>-17.39</v>
       </c>
       <c r="N21" t="n">
-        <v>-64.649</v>
+        <v>-66.16</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Pasorapa, Cochabamba</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2014,49 +2010,49 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Pasorapa</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNQVhTWE8zdE1BQ3lueWJPeV9wUDNsSmJpS0NJTWppMUY4QmlQSUFHVjRORmtrVHQ3MHB0T1pyS25PamxnY0hBQUtzOVRvSUNaUkdGb1RWSGl4dFA4Z3VINVpQTk1pZUpDdUIyUU5hZS1oNGhBa1RWcFhScVMwVTFrVlJaOFQ4OWFqRWVUZ051bHVJTlMxRTBhRFVLUEV2dTZFdDgtRkxJM3VvN3YzUWJfVk41ZWR5U1JoNmx0WFFkMmNTWGVleGNIQlNxWUJzdHIxSWtz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTlU5NVFpY1RheTN5ZE1IbG5VYTh2Sk5hZHpHeWI3LVdnSFg2cFJFdnBCVkxiUjNKcUgyUW16SWxpMXFkMHdad2xFN043bklJeG1iQ0V1V3hBZk1Ga3NscjdPVWUySmt4bDNTdWlmSUdOMmNlZ2hkSWZFMmk4VGs0Nm9TcnRCTDhINmtnQU9zZDBUY05HcWpxN3FOX3N1dmVJblE0MGc5di1Ma1N2dGNxOUtoV1MzNnl1OXpRaTZ2UGxMc3RDWndubHVQNUd0eVROMGR2OGxVemtOaEc4bTNRaA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>noticia:ix3l8o</t>
+          <t>noticia:1jfk053</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-23 18:25</t>
+          <t>2026-10-23 19:08</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1792794310000</v>
+        <v>1792796931000</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Oruro evalúa suspender clases presenciales por más de 200 casos de Coxsackie - Visión 360</t>
+          <t>Sequía en Pasorapa: el ganado muere por falta de agua y alistan declaratoria de desastre - Red Uno</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>climatológica</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -2067,77 +2063,77 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Red Uno; Visión 360</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>-17.97</v>
+        <v>-18.38</v>
       </c>
       <c r="N22" t="n">
-        <v>-67.11</v>
+        <v>-64.649</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>Pasorapa, Cochabamba</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Pasorapa</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0c9IBywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0cw?oc=5 | https://news.google.com/rss/articles/CBMiywFBVV95cUxNMFdHaVpKRmMyOENDYm16UXJPenVSQnpmTE94bDc4UFhqakluMUdvZjAwamUxT3BVWUpJQm8xVHBWengxQmhWM1hjU3d2YXFrLXpVU2VrZDJiMXZLMlQ5bGxGOHFETFhYM0s2RjlUTlhkd0g2eXQweDFHaTlKNGNMUlJfOWg2a0JjTklXUWZKc1BmUXZuZFZ2MF9fV2lEYUY4LXNiNmk3cF9FNjVtTl9GWFotT2ltS0xXTnM1dENvSU9kbFRMalFrYVdXOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNQVhTWE8zdE1BQ3lueWJPeV9wUDNsSmJpS0NJTWppMUY4QmlQSUFHVjRORmtrVHQ3MHB0T1pyS25PamxnY0hBQUtzOVRvSUNaUkdGb1RWSGl4dFA4Z3VINVpQTk1pZUpDdUIyUU5hZS1oNGhBa1RWcFhScVMwVTFrVlJaOFQ4OWFqRWVUZ051bHVJTlMxRTBhRFVLUEV2dTZFdDgtRkxJM3VvN3YzUWJfVk41ZWR5U1JoNmx0WFFkMmNTWGVleGNIQlNxWUJzdHIxSWtz?oc=5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>noticia:1xqv9m7</t>
+          <t>noticia:ix3l8o</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-23 18:09</t>
+          <t>2026-10-23 18:25</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1792793370000</v>
+        <v>1792794310000</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Tres heridos en tremendo choque cerca de Oncativo - El Diario del centro del país</t>
+          <t>Oruro evalúa suspender clases presenciales por más de 200 casos de Coxsackie - Visión 360</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -2145,61 +2141,77 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>El Diario del centro del país</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
+          <t>Red Uno; Visión 360</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>-17.97</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-67.11</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Oruro, Oruro</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZERhbTJMQUJVb3hmZFlSZmRGZkdBLWdFTGJVQzdqZkE4aGhhWmdQZ2JDRW1ndkJLWU90VTZ6Ti1JOUZzcFZfcE1zbkRHU1B3YTF4UkVzdllFa1p3SUlObURGamF0Vm9kc3dPLTZVWFJ4NWZZQmlySElPNHhZTnRGNGNZUWw2ZlI1eVBEQkNGNEhLWTNiLWJLUS0xYjA0UWRhc0d6bVN4aVVLSVdsQWlpMUZYdWw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0c9IBywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0cw?oc=5 | https://news.google.com/rss/articles/CBMiywFBVV95cUxNMFdHaVpKRmMyOENDYm16UXJPenVSQnpmTE94bDc4UFhqakluMUdvZjAwamUxT3BVWUpJQm8xVHBWengxQmhWM1hjU3d2YXFrLXpVU2VrZDJiMXZLMlQ5bGxGOHFETFhYM0s2RjlUTlhkd0g2eXQweDFHaTlKNGNMUlJfOWg2a0JjTklXUWZKc1BmUXZuZFZ2MF9fV2lEYUY4LXNiNmk3cF9FNjVtTl9GWFotT2ltS0xXTnM1dENvSU9kbFRMalFrYVdXOA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>noticia:1itd1r7</t>
+          <t>noticia:1xqv9m7</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-23 15:01</t>
+          <t>2026-10-23 18:09</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1792782098000</v>
+        <v>1792793370000</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Intensa lluvia y granizada en La Paz inundan vías y elevan el nivel de los ríos - eju.tv</t>
+          <t>Tres heridos en tremendo choque cerca de Oncativo - El Diario del centro del país</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -2211,73 +2223,57 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>eju.tv</t>
-        </is>
-      </c>
-      <c r="M24" t="n">
-        <v>-16.169</v>
-      </c>
-      <c r="N24" t="n">
-        <v>-68.09</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>La Paz, La Paz</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>La Paz</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>Nuestra Señora de La Paz</t>
-        </is>
-      </c>
+          <t>El Diario del centro del país</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNWU9QWElKQXEyN3UxVm4xbzJzbEJ1TU1NTHZlRUp6YndmeU9GQnJKcTluVEJ2ZHQ5cGp3aWhlMUd5ektWQlBpUVNmZnZuRnJwMXlydzAzX0FBVnY5UDMzQTBkWVRNRUNJSlRvX3MyQVhMcEhIMW9WSUpXckVSd0RJWk1KMFBKWmJNU3diQVlEN1Y5aVV6eVBaZXpOMnFIWWxaMlRlY0ZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZERhbTJMQUJVb3hmZFlSZmRGZkdBLWdFTGJVQzdqZkE4aGhhWmdQZ2JDRW1ndkJLWU90VTZ6Ti1JOUZzcFZfcE1zbkRHU1B3YTF4UkVzdllFa1p3SUlObURGamF0Vm9kc3dPLTZVWFJ4NWZZQmlySElPNHhZTnRGNGNZUWw2ZlI1eVBEQkNGNEhLWTNiLWJLUS0xYjA0UWRhc0d6bVN4aVVLSVdsQWlpMUZYdWw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>noticia:51709n</t>
+          <t>noticia:1itd1r7</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-23 13:38</t>
+          <t>2026-10-23 15:01</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1792777139000</v>
+        <v>1792782098000</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - eju.tv</t>
+          <t>Intensa lluvia y granizada en La Paz inundan vías y elevan el nivel de los ríos - eju.tv</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2285,77 +2281,77 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Red Uno; eju.tv</t>
+          <t>eju.tv</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>-17.764</v>
+        <v>-16.169</v>
       </c>
       <c r="N25" t="n">
-        <v>-62.903</v>
+        <v>-68.09</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Cotoca, Santa Cruz</t>
+          <t>La Paz, La Paz</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>Cotoca</t>
+          <t>Nuestra Señora de La Paz</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPcjZTSmprRGVoNlRqQmdBTE5VM3pRQ1ZFakFUbzVyMUhiaDVkT0liaG9UNEZXekV6bWsycUk4X1JCSEY5RjhNVlZaTk9ULUFuZkY3NnZuWmZ1a19leUhFdlIyQV9kLWxlSkxfeXFhcFRTZjZ2YkpQQlJ1dkNLMDBjaGZ4SkhyQ0RfcnhKSEg5WURCQVQwbENYTHEzUzJSaUEzMGo2bWdyS3lsM016LXc?oc=5 | https://news.google.com/rss/articles/CBMi0AFBVV95cUxOVGY3YVRLWWxYM0IycjF4dlNUeUhqZG90Yng4aWhmN3A5ai02WENWYnF4bWpoZHFKMGc1X0JPRHdRRVZfSlA4UmZFa2kxYkNIS3ZtQ1NvNlNCME51eVZTRkRKSUQ5MmRoaWl5Tkt5NHpPUEFwemN2YTV1djFwdHlqQnFqRHNPenhYcTlsanJPcXhpOVV1NmFBUXZyazQ2MkUzM0dSZy02ZllxTGtjcl9ldzdHSktTRlVaalZJc1pubUNQMWFTbzVEOUJ1UmhCdEJt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNWU9QWElKQXEyN3UxVm4xbzJzbEJ1TU1NTHZlRUp6YndmeU9GQnJKcTluVEJ2ZHQ5cGp3aWhlMUd5ektWQlBpUVNmZnZuRnJwMXlydzAzX0FBVnY5UDMzQTBkWVRNRUNJSlRvX3MyQVhMcEhIMW9WSUpXckVSd0RJWk1KMFBKWmJNU3diQVlEN1Y5aVV6eVBaZXpOMnFIWWxaMlRlY0ZB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>noticia:11rddql</t>
+          <t>noticia:51709n</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-23 13:22</t>
+          <t>2026-10-23 13:38</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1792776139000</v>
+        <v>1792777139000</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Intensifican acciones preventivas contra el dengue en Caranavi - El Diario - Bolivia</t>
+          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - eju.tv</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2363,77 +2359,77 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>Red Uno; eju.tv</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>-15.813</v>
+        <v>-17.764</v>
       </c>
       <c r="N26" t="n">
-        <v>-67.46299999999999</v>
+        <v>-62.903</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Caranavi, La Paz</t>
+          <t>Cotoca, Santa Cruz</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Caranavi</t>
+          <t>Cotoca</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOMjhSeDJBek5iaFhDcnFzX1lKelgwZmUwLTJnbEhMdDRMelUxNks5Ti1pRHh3dDhTcC1YZEdqM3FJOGdqVHRvcXVhRlpCQzVDTEZMUFBkV1NrYVQ2LXRqTTBhcGRQc21CQ0VabzZaNExXb1BjTzJ2Uk5BcFF0VG5XOFNRa3lqUWlJSnRFUUVXYnNpbXB0LVVmSXVWSzJxcmVpdVVxUC1KOUhTQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPcjZTSmprRGVoNlRqQmdBTE5VM3pRQ1ZFakFUbzVyMUhiaDVkT0liaG9UNEZXekV6bWsycUk4X1JCSEY5RjhNVlZaTk9ULUFuZkY3NnZuWmZ1a19leUhFdlIyQV9kLWxlSkxfeXFhcFRTZjZ2YkpQQlJ1dkNLMDBjaGZ4SkhyQ0RfcnhKSEg5WURCQVQwbENYTHEzUzJSaUEzMGo2bWdyS3lsM016LXc?oc=5 | https://news.google.com/rss/articles/CBMi0AFBVV95cUxOVGY3YVRLWWxYM0IycjF4dlNUeUhqZG90Yng4aWhmN3A5ai02WENWYnF4bWpoZHFKMGc1X0JPRHdRRVZfSlA4UmZFa2kxYkNIS3ZtQ1NvNlNCME51eVZTRkRKSUQ5MmRoaWl5Tkt5NHpPUEFwemN2YTV1djFwdHlqQnFqRHNPenhYcTlsanJPcXhpOVV1NmFBUXZyazQ2MkUzM0dSZy02ZllxTGtjcl9ldzdHSktTRlVaalZJc1pubUNQMWFTbzVEOUJ1UmhCdEJt?oc=5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>noticia:fcm3nx</t>
+          <t>noticia:11rddql</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-23 12:58</t>
+          <t>2026-10-23 13:22</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1792774699000</v>
+        <v>1792776139000</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>[VIDEO] Así fue el accidente de moto que dejó un adolescente fallecido y un hombre gravemente herido - Red Uno</t>
+          <t>Intensifican acciones preventivas contra el dengue en Caranavi - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2445,57 +2441,73 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Red Uno</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
+          <t>El Diario - Bolivia</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>-15.813</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-67.46299999999999</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Caranavi, La Paz</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>La Paz</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Caranavi</t>
+        </is>
+      </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOSmJMazhUemNfRHpWcDBoTVFZMUpwdlVKVUtvUXZNTGRRRHlwLW5KNmNhcmFnd1czbi1yalhFMnpSS1dmUE9jVzNlOS1kMWZtRzBHZ2EtcDRDdU5Gc2JUQVIwM2xPa2lZVmswRi1SUFVPcm8xcHlGN3F2UThTSDdKMDNyYnJmVkcxazNLLVBLOWFYM09FVUpmVnN5RVhpSVo2V1VCVmFwQ1gzTmRUWVp2aXMwcmxHRS1GV2p3NTBtR2RzM2wwVHUzaGJkRXJYbHdvaDlhWm5YMTk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOMjhSeDJBek5iaFhDcnFzX1lKelgwZmUwLTJnbEhMdDRMelUxNks5Ti1pRHh3dDhTcC1YZEdqM3FJOGdqVHRvcXVhRlpCQzVDTEZMUFBkV1NrYVQ2LXRqTTBhcGRQc21CQ0VabzZaNExXb1BjTzJ2Uk5BcFF0VG5XOFNRa3lqUWlJSnRFUUVXYnNpbXB0LVVmSXVWSzJxcmVpdVVxUC1KOUhTQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>noticia:1cjx1qd</t>
+          <t>noticia:fcm3nx</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-23 12:39</t>
+          <t>2026-10-23 12:58</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1792773575000</v>
+        <v>1792774699000</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Más de 60 municipios en La Paz sufren falta de lluvias - La Patria Bolivia</t>
+          <t>[VIDEO] Así fue el accidente de moto que dejó un adolescente fallecido y un hombre gravemente herido - Red Uno</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2507,53 +2519,37 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
-        </is>
-      </c>
-      <c r="M28" t="n">
-        <v>-16.169</v>
-      </c>
-      <c r="N28" t="n">
-        <v>-68.09</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>La Paz, La Paz</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>La Paz</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>Nuestra Señora de La Paz</t>
-        </is>
-      </c>
+          <t>Red Uno</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE52Qi03Z1J6OS1CR2liRVZ0VlhCcmVQWFV6RUdGNXdrbzZRNXFjTWRaRnc1b3VoV0xaY3RIdncxNlNnYkxyUXo5MTlJWmMwWDNSMDE4ZHI2VkpWajFPaUF2SmRVYkk2eDZYQ1RfUU9ieENrZG9UVVFiaXZSeGI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOSmJMazhUemNfRHpWcDBoTVFZMUpwdlVKVUtvUXZNTGRRRHlwLW5KNmNhcmFnd1czbi1yalhFMnpSS1dmUE9jVzNlOS1kMWZtRzBHZ2EtcDRDdU5Gc2JUQVIwM2xPa2lZVmswRi1SUFVPcm8xcHlGN3F2UThTSDdKMDNyYnJmVkcxazNLLVBLOWFYM09FVUpmVnN5RVhpSVo2V1VCVmFwQ1gzTmRUWVp2aXMwcmxHRS1GV2p3NTBtR2RzM2wwVHUzaGJkRXJYbHdvaDlhWm5YMTk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>clima:Sucre:2026-10-23:viento:1</t>
+          <t>noticia:1cjx1qd</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-23 06:55</t>
+          <t>2026-10-23 12:39</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1792752927735</v>
+        <v>1792773575000</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sucre 2026-10-23: 66.2 km/h de ráfagas pronosticadas</t>
+          <t>Más de 60 municipios en La Paz sufren falta de lluvias - La Patria Bolivia</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2562,11 +2558,11 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -2585,40 +2581,40 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>La Patria Bolivia</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>-19.03</v>
+        <v>-16.169</v>
       </c>
       <c r="N29" t="n">
-        <v>-65.26000000000001</v>
+        <v>-68.09</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>La Paz, La Paz</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Chuquisaca</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Nuestra Señora de La Paz</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE52Qi03Z1J6OS1CR2liRVZ0VlhCcmVQWFV6RUdGNXdrbzZRNXFjTWRaRnc1b3VoV0xaY3RIdncxNlNnYkxyUXo5MTlJWmMwWDNSMDE4ZHI2VkpWajFPaUF2SmRVYkk2eDZYQ1RfUU9ieENrZG9UVVFiaXZSeGI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-24:viento:2</t>
+          <t>clima:Sucre:2026-10-23:viento:1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2627,11 +2623,11 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1792752927734</v>
+        <v>1792752927735</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-24: 85 km/h de ráfagas pronosticadas</t>
+          <t>Sucre 2026-10-23: 66.2 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2640,11 +2636,11 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -2667,24 +2663,24 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>-17.78</v>
+        <v>-19.03</v>
       </c>
       <c r="N30" t="n">
-        <v>-63.18</v>
+        <v>-65.26000000000001</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Chuquisaca</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2696,33 +2692,33 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>usgs:us6000u49c</t>
+          <t>clima:Santa Cruz:2026-10-24:viento:2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-22 22:45</t>
+          <t>2026-10-23 06:55</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1792723541183</v>
+        <v>1792752927734</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sismo M 4.5 - 58 km SW of Atocha, Bolivia</t>
+          <t>Santa Cruz 2026-10-24: 85 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>geológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -2741,58 +2737,58 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>USGS</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>-21.3469</v>
+        <v>-17.78</v>
       </c>
       <c r="N31" t="n">
-        <v>-66.5795</v>
+        <v>-63.18</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>58 km SW of Atocha, Bolivia</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>San Pablo</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>https://earthquake.usgs.gov/earthquakes/eventpage/us6000u49c</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-22:viento:1</t>
+          <t>usgs:us6000u49c</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-22 21:55</t>
+          <t>2026-10-22 22:45</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1792720528712</v>
+        <v>1792723541183</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-22: 67.7 km/h de ráfagas pronosticadas</t>
+          <t>Sismo M 4.5 - 58 km SW of Atocha, Bolivia</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>geológica</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -2819,40 +2815,40 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>USGS</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>-17.78</v>
+        <v>-21.3469</v>
       </c>
       <c r="N32" t="n">
-        <v>-63.18</v>
+        <v>-66.5795</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>58 km SW of Atocha, Bolivia</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>San Pablo</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://earthquake.usgs.gov/earthquakes/eventpage/us6000u49c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-23:viento:2</t>
+          <t>clima:Santa Cruz:2026-10-22:viento:1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2865,7 +2861,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-23: 83.9 km/h de ráfagas pronosticadas</t>
+          <t>Santa Cruz 2026-10-22: 67.7 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2874,11 +2870,11 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -2930,33 +2926,33 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>noticia:1hhvre7</t>
+          <t>clima:Santa Cruz:2026-10-23:viento:2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-22 19:36</t>
+          <t>2026-10-22 21:55</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1792712202000</v>
+        <v>1792720528712</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Virgen de Cotoca: Controlan incendio en depósito de materiales plásticos - El Mundo Bolivia</t>
+          <t>Santa Cruz 2026-10-23: 83.9 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -2975,18 +2971,18 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>El Mundo Bolivia</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="M34" t="n">
-        <v>-17.764</v>
+        <v>-17.78</v>
       </c>
       <c r="N34" t="n">
-        <v>-62.903</v>
+        <v>-63.18</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Cotoca, Santa Cruz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -2996,32 +2992,32 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>Cotoca</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcDF6VE5FNzRaWGRuUzFKeXhnZ21DZTRaaEtrVEJEa1Z3ejg2VG1ONG1ENmlDWlkyVjlkQkJwS2F1XzBGMFQwSHd4OEwxTW1PbHdGcUh1ckV6SGpDd2hiN0dkeUVTcnFXT3RjOU1kLXZtVVdZY2hkZS1pcVpVUFhnRktqcHY5UnBrY0xUMDRETjl6N0pXT3A5amxhMA?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>noticia:bksnde</t>
+          <t>noticia:1hhvre7</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-22 17:01</t>
+          <t>2026-10-22 19:36</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1792702880000</v>
+        <v>1792712202000</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Reportan un incendio cerca de la carretera a Cotoca - eju.tv</t>
+          <t>Virgen de Cotoca: Controlan incendio en depósito de materiales plásticos - El Mundo Bolivia</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3053,7 +3049,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>eju.tv</t>
+          <t>El Mundo Bolivia</t>
         </is>
       </c>
       <c r="M35" t="n">
@@ -3079,27 +3075,27 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPNGtpbnBfRnRBalVudnBlZHdVQ0ZSaUplZmtvTGE0aTQzdkxWS3d4My1EZEJ1UE9FNFQ3RmpyZGVsbS1qNEM1QUVFRFAxM2pYT1VqQzRuVjRtZnVNUGlKODNMc0F1a3l6TUpuQmtlUWNlVTVEWWU5ZGZtQm5LWUp3Sg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcDF6VE5FNzRaWGRuUzFKeXhnZ21DZTRaaEtrVEJEa1Z3ejg2VG1ONG1ENmlDWlkyVjlkQkJwS2F1XzBGMFQwSHd4OEwxTW1PbHdGcUh1ckV6SGpDd2hiN0dkeUVTcnFXT3RjOU1kLXZtVVdZY2hkZS1pcVpVUFhnRktqcHY5UnBrY0xUMDRETjl6N0pXT3A5amxhMA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>noticia:17hz69v</t>
+          <t>noticia:bksnde</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-22 13:05</t>
+          <t>2026-10-22 17:01</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1792688709000</v>
+        <v>1792702880000</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Accidente en El Sillar deja al menos 29 heridos - La Razón Digital Bolivia</t>
+          <t>Reportan un incendio cerca de la carretera a Cotoca - eju.tv</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3108,18 +3104,18 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -3131,37 +3127,53 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>La Razón Digital Bolivia</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
+          <t>eju.tv</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>-17.764</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-62.903</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Cotoca, Santa Cruz</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Cotoca</t>
+        </is>
+      </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPaXhTdm45YWZnWVFxVzJnb1ZwbUN4SmUtLVdJN0VJdFZBamRyQmFxN0RZelBfTklaSTVyOUZ3ajQ5MFB2TEN4Ukd6TE5ORFY5SEROVk1CZ25sRWJ1QnRBdTVfTktlby1NWXhaVWI5YnRvaDZWbHVjdDVoeFp5Tk5veFk5a19MSWJqcEJVV0dzV3k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPNGtpbnBfRnRBalVudnBlZHdVQ0ZSaUplZmtvTGE0aTQzdkxWS3d4My1EZEJ1UE9FNFQ3RmpyZGVsbS1qNEM1QUVFRFAxM2pYT1VqQzRuVjRtZnVNUGlKODNMc0F1a3l6TUpuQmtlUWNlVTVEWWU5ZGZtQm5LWUp3Sg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>noticia:1f1qb0</t>
+          <t>noticia:17hz69v</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-22 12:09</t>
+          <t>2026-10-22 13:05</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1792685373000</v>
+        <v>1792688709000</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Accidente en el tramo Locotal–Villa Tunari: la vía está transitable con precaución - Red Uno</t>
+          <t>Accidente en El Sillar deja al menos 29 heridos - La Razón Digital Bolivia</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3170,18 +3182,18 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -3193,73 +3205,57 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Red Uno</t>
-        </is>
-      </c>
-      <c r="M37" t="n">
-        <v>-16.556</v>
-      </c>
-      <c r="N37" t="n">
-        <v>-65.569</v>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>Villa Tunari, Cochabamba</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>Villa Tunari</t>
-        </is>
-      </c>
+          <t>La Razón Digital Bolivia</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTFozcEEwNXBqV19sS2VibXh0MGt0QlhsX1djSTFGQW5zNlFLRHZpNVVnZ1JmWDQ4LVRHX2Rmb3B5UU9qV0FZQmJCaUZYdmwyNG1NenJ4Qzlzd0NJTGs1SjMxdFRtRFBzSUkybGJfZFFaNFZBc21FSUJYSFVkQkVkSEhQaGw0UFVzeXctZHo3cjNsYm5weXJlOU1wcmFncnNhMC1BQUpvNWlDX1NxZXU4b09kVFFWR2tSVEk2UTdXXzB3TjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPaXhTdm45YWZnWVFxVzJnb1ZwbUN4SmUtLVdJN0VJdFZBamRyQmFxN0RZelBfTklaSTVyOUZ3ajQ5MFB2TEN4Ukd6TE5ORFY5SEROVk1CZ25sRWJ1QnRBdTVfTktlby1NWXhaVWI5YnRvaDZWbHVjdDVoeFp5Tk5veFk5a19MSWJqcEJVV0dzV3k?oc=5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>noticia:wi18tm</t>
+          <t>noticia:1f1qb0</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-22 11:53</t>
+          <t>2026-10-22 12:09</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1792684426000</v>
+        <v>1792685373000</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Accidente en El Sillar deja heridos y derrame de combustible: esto es lo último que se sabe - Red Uno</t>
+          <t>Accidente en el tramo Locotal–Villa Tunari: la vía está transitable con precaución - Red Uno</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>tecnológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -3274,54 +3270,70 @@
           <t>Red Uno</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
+      <c r="M38" t="n">
+        <v>-16.556</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-65.569</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Villa Tunari, Cochabamba</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Villa Tunari</t>
+        </is>
+      </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPZHNBTEdaQm5Wby1lTF9mWlQ2aGg0MVc4S0MwVWJ3dUJ5WWU5X3IwYWhKRjk5VWtYWEJHRDF4QldVc29laVNPSTJNWFBDSkNFQlFSYTJUXzNMNF9hckFBN1I2T2xoQUtYQ2V6MDNTZHhHVk9qeTBCdHRpM2ZLd0pyOFRweUUxX19STzRHTHg5VUY5d1lhS0tDeXpCdklqcTZGT1J4R0xnSDhoak1EZ2dtNUhSTUV6b1o0U0VSdWY5X0E3U05Tc1dYVEN2WFZUeFhPMTBJTmowNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTFozcEEwNXBqV19sS2VibXh0MGt0QlhsX1djSTFGQW5zNlFLRHZpNVVnZ1JmWDQ4LVRHX2Rmb3B5UU9qV0FZQmJCaUZYdmwyNG1NenJ4Qzlzd0NJTGs1SjMxdFRtRFBzSUkybGJfZFFaNFZBc21FSUJYSFVkQkVkSEhQaGw0UFVzeXctZHo3cjNsYm5weXJlOU1wcmFncnNhMC1BQUpvNWlDX1NxZXU4b09kVFFWR2tSVEk2UTdXXzB3TjA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>noticia:12gfagq</t>
+          <t>noticia:wi18tm</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-22 11:28</t>
+          <t>2026-10-22 11:53</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1792682880000</v>
+        <v>1792684426000</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Reportan triple colisión entre dos camiones y un bus en la carretera Cochabamba-Santa Cruz - FmBolivia</t>
+          <t>Accidente en El Sillar deja heridos y derrame de combustible: esto es lo último que se sabe - Red Uno</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>tecnológica</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -3329,57 +3341,41 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>FmBolivia; Red Uno</t>
-        </is>
-      </c>
-      <c r="M39" t="n">
-        <v>-17.39</v>
-      </c>
-      <c r="N39" t="n">
-        <v>-66.16</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>Cochabamba, Cochabamba</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
+          <t>Red Uno</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNMTNBaFZNMU9SR25vdVBuNXlZY3g4VkFWYXRiQnNSaUFjemZhUHZWNHg4V2owU2xfNndBak94TnU2cHNUVXdNNWl2eUdHZVNMbVZweTR5M0o0bWdTNUN4QkoxUkI2TDBmVE03M09zRGhJRVFzV0tPZ1NCWEJLUkt1ZGN4UGduOUZMQnJoM0tMYTh0ZlFxaFJNUkJqaWFPazRlMzN3ajhjUEdUYXlZRndpb3RSdTFCX2tCZGJxQ0x4SlBISWJsRVoyN3ZR?oc=5 | https://news.google.com/rss/articles/CBMirwFBVV95cUxNNUROMzd1UDJRWVZZQ011cFd2c1FSdER1ZzdleU04cXpwYk5HaUZrLXoyU2NzdFk1dnNRUndhUWt0cG9DX09rSjlLcDItU0tzcmQtS3E4dDQ4ZF9HdGJLdk13ek9BNHJUWVlCcklrM25rZ01RbXhLalRBT1FGdDNReHdlTFZkNkJ5ZFd3N3NZVFVmOFUxbEhHN0RsaUxiSVZsM0lXVEFYSHVRQlhsOEtJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPZHNBTEdaQm5Wby1lTF9mWlQ2aGg0MVc4S0MwVWJ3dUJ5WWU5X3IwYWhKRjk5VWtYWEJHRDF4QldVc29laVNPSTJNWFBDSkNFQlFSYTJUXzNMNF9hckFBN1I2T2xoQUtYQ2V6MDNTZHhHVk9qeTBCdHRpM2ZLd0pyOFRweUUxX19STzRHTHg5VUY5d1lhS0tDeXpCdklqcTZGT1J4R0xnSDhoak1EZ2dtNUhSTUV6b1o0U0VSdWY5X0E3U05Tc1dYVEN2WFZUeFhPMTBJTmowNA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>noticia:1jl2oid</t>
+          <t>noticia:12gfagq</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-22 07:49</t>
+          <t>2026-10-22 11:28</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1792669785000</v>
+        <v>1792682880000</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - eju.tv</t>
+          <t>Reportan triple colisión entre dos camiones y un bus en la carretera Cochabamba-Santa Cruz - FmBolivia</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3388,18 +3384,18 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -3411,109 +3407,187 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Red Uno; eju.tv</t>
+          <t>FmBolivia; Red Uno</t>
         </is>
       </c>
       <c r="M40" t="n">
-        <v>-17.781</v>
+        <v>-17.39</v>
       </c>
       <c r="N40" t="n">
-        <v>-63.139</v>
+        <v>-66.16</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Santa Cruz, Santa Cruz</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQbTBrUmlla3FvVU1EX1pxcUI3SXYzbUFFMzlnRzhlSDJwMGpWWURxYjIwSkJBRGdCazMzT01hVy1qMFY3RnJLbC1XNXJ4bU55aDJVeXpNUlRsbzQ3T3hiRXJ5SWlhNmw5cDZFanNoWFBtQ01Gd3dscXltWmU5VHBSQlN3c2IwNGxuVE5tQ3lOT1RmNzRiVi1hc0hn?oc=5 | https://news.google.com/rss/articles/CBMiuwFBVV95cUxNVEh1bFlCanFuOTJid2EzYS1meG5oekFJcGFaME1fTk9sUnZpd3U0UXFHUFVJSW1jc1hzM2VFOFprT2xNYjBzbmswZmdJV3dremRIS0I4MDNzRjBnbEttWEhfOWZBbmFrRnNHWDFVLVFoM0VkZkxkaW4tMmZlSFJLei1heTFHMU0wSmxQVVRZN0cwaXQzcDBtZkdwTUFma0RXU2dwLXRnLTBkNGN3Vm1fV3hEdlM1dWZ1SEsw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNMTNBaFZNMU9SR25vdVBuNXlZY3g4VkFWYXRiQnNSaUFjemZhUHZWNHg4V2owU2xfNndBak94TnU2cHNUVXdNNWl2eUdHZVNMbVZweTR5M0o0bWdTNUN4QkoxUkI2TDBmVE03M09zRGhJRVFzV0tPZ1NCWEJLUkt1ZGN4UGduOUZMQnJoM0tMYTh0ZlFxaFJNUkJqaWFPazRlMzN3ajhjUEdUYXlZRndpb3RSdTFCX2tCZGJxQ0x4SlBISWJsRVoyN3ZR?oc=5 | https://news.google.com/rss/articles/CBMirwFBVV95cUxNNUROMzd1UDJRWVZZQ011cFd2c1FSdER1ZzdleU04cXpwYk5HaUZrLXoyU2NzdFk1dnNRUndhUWt0cG9DX09rSjlLcDItU0tzcmQtS3E4dDQ4ZF9HdGJLdk13ek9BNHJUWVlCcklrM25rZ01RbXhLalRBT1FGdDNReHdlTFZkNkJ5ZFd3N3NZVFVmOFUxbEhHN0RsaUxiSVZsM0lXVEFYSHVRQlhsOEtJ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>noticia:1jl2oid</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-10-22 07:49</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1792669785000</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - eju.tv</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>antropogénica</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>amarilla</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>2</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Red Uno; eju.tv</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>-17.781</v>
+      </c>
+      <c r="N41" t="n">
+        <v>-63.139</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Santa Cruz, Santa Cruz</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Santa Cruz de la Sierra</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQbTBrUmlla3FvVU1EX1pxcUI3SXYzbUFFMzlnRzhlSDJwMGpWWURxYjIwSkJBRGdCazMzT01hVy1qMFY3RnJLbC1XNXJ4bU55aDJVeXpNUlRsbzQ3T3hiRXJ5SWlhNmw5cDZFanNoWFBtQ01Gd3dscXltWmU5VHBSQlN3c2IwNGxuVE5tQ3lOT1RmNzRiVi1hc0hn?oc=5 | https://news.google.com/rss/articles/CBMiuwFBVV95cUxNVEh1bFlCanFuOTJid2EzYS1meG5oekFJcGFaME1fTk9sUnZpd3U0UXFHUFVJSW1jc1hzM2VFOFprT2xNYjBzbmswZmdJV3dremRIS0I4MDNzRjBnbEttWEhfOWZBbmFrRnNHWDFVLVFoM0VkZkxkaW4tMmZlSFJLei1heTFHMU0wSmxQVVRZN0cwaXQzcDBtZkdwTUFma0RXU2dwLXRnLTBkNGN3Vm1fV3hEdlM1dWZ1SEsw?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>noticia:n32ahi</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>2026-10-22 05:30</t>
         </is>
       </c>
-      <c r="C41" t="n">
+      <c r="C42" t="n">
         <v>1792661402000</v>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>Senamhi anuncia el inicio de la temporada de lluvias en Bolivia y prevé granizadas como la de La Paz - FmBolivia</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>meteorológica</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" t="inlineStr">
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="inlineStr">
         <is>
           <t>verde</t>
         </is>
       </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" t="inlineStr">
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="K41" t="n">
-        <v>1</v>
-      </c>
-      <c r="L41" t="inlineStr">
+      <c r="K42" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t>FmBolivia</t>
         </is>
       </c>
-      <c r="M41" t="n">
+      <c r="M42" t="n">
         <v>-16.169</v>
       </c>
-      <c r="N41" t="n">
+      <c r="N42" t="n">
         <v>-68.09</v>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>La Paz, La Paz</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>La Paz</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>Nuestra Señora de La Paz</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="R42" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQNmVPRnVBMGQzdEI5SUp3Z3ZGVExwTUR6TWNadGQ1QldUS1o2QVFvUl9sVEZKMDVyQVVrS25rU1RSQlJKWXk1YzE0NUhidjhpcmFaSlhZUDZvcE9XcG1KTFNTYmowUU1CSFJNOVR2UHNmMk1iT3N0RVBteHkzZkgyRFROYk1pdkpxVHZya3N2X2FVLVQxbURFVVZlb1NzRjZzTE95TXFVUXFJNkVZakQ2bUhVQzB0SXk3TVhXUTJXa0dycTE1MWVQRFpDX3lDSWFqUGwzU2NtNA?oc=5</t>
         </is>
@@ -3530,7 +3604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S60"/>
+  <dimension ref="A1:S62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3633,25 +3707,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>noticia:oww2zc</t>
+          <t>manual:1c1299f3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>registro</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-25 12:08</t>
+          <t>2026-10-25 12:44</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1792944531000</v>
+        <v>1792946640000</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>Registro abierto (sin verificar)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -3660,61 +3734,61 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Cierran la carretera a Camiri: dos cisternas chocan y provocan un voraz incendio - Red Uno</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQLXlqSFdvWUVhQUNadnpkdE5lUTZQS0lobThzUTZWbDNJTE94alVhaDBaYU9Fd09SSGt3UlR3Y0dfZlNIcml1ZktnWjctNk1Na3V4S0tINFNkMXM0OHBoV2lCTTBiYXlPUTA3T2ZkeXE2RElYWjhfVHd3Nng1Z0E4alBmOFI5NDFwX09kazZlSWl2OVR2ZVR6MDhvSHFnSmJKbTFXSEFDNFFYcWVDNGtYWEQ0bDhJel9CaEpEZWZ4SWN0TE9Ya0E?oc=5</t>
-        </is>
-      </c>
+          <t>Vuelco de minibus</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Registro de prueba del sistema. Ignorar. | Lugar indicado: Caranavi, La Paz | Registro abierto, sin verificar.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N2" t="n">
-        <v>-20.05</v>
+        <v>-15.813</v>
       </c>
       <c r="O2" t="n">
-        <v>-63.486</v>
+        <v>-67.46299999999999</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Camiri, Santa Cruz</t>
+          <t>Caranavi, La Paz</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
+          <t>nombre de municipio indicado por quien registra</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Camiri</t>
+          <t>Caranavi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>noticia:1at00ey</t>
+          <t>noticia:oww2zc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3724,11 +3798,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-25 11:19</t>
+          <t>2026-10-25 12:08</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1792941547000</v>
+        <v>1792944531000</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -3750,13 +3824,13 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Dos cisternas chocan y provocan voraz incendio en la ruta a Camiri - Red Uno</t>
+          <t>Cierran la carretera a Camiri: dos cisternas chocan y provocan un voraz incendio - Red Uno</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPTTF0OUdVS1c1a0lZWmk3bGxHdDJIalpWZTRyQTY3eWE2a2dWOHlsaldKZXpSLWN5c3BkUWdBRkJuSzhHdWl2ZjgwTFFFYnd0aTAxZ3dJU0hCekNZNm9aTTJSZUNfQjVIM3FrUUJ4NXAwa3paZ3BEek9xTVZNQWdnN01xRHloV1ZXZHV6N0JpUWo3RE9DMlFGdkNnWkloTjVVY3RBR1RSRUJJWFVtby1fMWFMNTdLZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQLXlqSFdvWUVhQUNadnpkdE5lUTZQS0lobThzUTZWbDNJTE94alVhaDBaYU9Fd09SSGt3UlR3Y0dfZlNIcml1ZktnWjctNk1Na3V4S0tINFNkMXM0OHBoV2lCTTBiYXlPUTA3T2ZkeXE2RElYWjhfVHd3Nng1Z0E4alBmOFI5NDFwX09kazZlSWl2OVR2ZVR6MDhvSHFnSmJKbTFXSEFDNFFYcWVDNGtYWEQ0bDhJel9CaEpEZWZ4SWN0TE9Ya0E?oc=5</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -3795,7 +3869,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>noticia:1uf38hl</t>
+          <t>noticia:1a4hhsd</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3805,15 +3879,15 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-25 10:59</t>
+          <t>2026-10-25 11:56</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1792940350000</v>
+        <v>1792943794000</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>Opinión Bolivia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -3831,13 +3905,13 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>¡Cisterna con combustible en llamas! Reportan impresionante incendio en la carretera a Camiri - Red Uno</t>
+          <t>Reportan el incendio de dos camiones cisterna en la carretera a Camiri - Opinión Bolivia</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxORUhqeWpKY1FHRWoxaHN0UXFzS3dpeHh6N0NwLUJOZTlZcDVoNHN0VnI0by1qMWtZZEkxVmtUNjdNTFhjaEFQU2IyMlNwZW95WFBzbFJPVVB6TjJtdjNENk1LWVlsMUxUUzBNVzkxRk1HZ3lQU0s2M1lRVlRuaXlkMmJrd3AyTGpIdXItNkhlU3dhTzBRME56Rm1DSlZCYjNxSnNTbTFqNWRoUkdraHhlREhuYldqeFk2N3poWEx2M08?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNUTdxSzBJVTZnajZQUXhyTVhwMlpvU0tyZGVBYnFwV2kyZWthenNRT1FDRVJFZnk4ZndGTFQ0cnFXZmZ1WHZaMFhUbWo0SWkzcjcxbjJwU3pKUXR4WEVZLVlRNFpxOUVMY2NNNUZsbmJSMk9xZG1sTklEdEtGSXJyUUp5b0R2dVpYcHJLdTRNRlRjcWpNNXg4c0Z4UWwteFc2dDRqVmpnQnFfQXgwN0twTzl4ZWhYdUtYWGfSAboBQVVfeXFMTVE3cUswSVU2Z2o2UFF4ck1YcDJab1NLcmRlQWJxcFdpMmVrYXpzUU9RQ0VSRWZ5OGZ3RkxUNHJxV2ZmdVh2WjBYVG1qNElpM3I3MW4ycFN6SlF0eFhFWS1ZUTRacTlFTGNjTTVGbG5iUjJPcWRtbE5JRHRLRklyclFKeW9EdnVaWHByS3U0TUZUY3FqTTV4OHNGeFFsLXhXNnQ0alZqZ0JxX0F4MDdLcE85eGVoWHVLWFhn?oc=5</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -3876,7 +3950,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>noticia:1sg8pi0</t>
+          <t>noticia:1at00ey</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3886,11 +3960,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-25 09:59</t>
+          <t>2026-10-25 11:19</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1792936752000</v>
+        <v>1792941547000</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -3912,13 +3986,13 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Bus de agrupación musical sufre accidente rumbo al trópico de Cochabamba | VIDEO - Red Uno</t>
+          <t>Dos cisternas chocan y provocan voraz incendio en la ruta a Camiri - Red Uno</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOVDVzVTJNM2JuQ25sMThEaVZNOUNRd3FGT3RhVnFrZXZ2NDQ1YlluTVdhbVNUQnA1MGNESHRSWVUzbC1kRVh3OTR0emtlTG91cmRWeFJ5dk5zb3p2WFRyMEJUV3FNRnY1WHhRUU9WLTlJcmNyNXJZZFdoM0JoZjNpa3hjUXhMM0xrUDJab2VadkM5RWZYQ3lWZTVDdzg1akxJT2lxcDVNNzI0NG1hejdfdkUyTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPTTF0OUdVS1c1a0lZWmk3bGxHdDJIalpWZTRyQTY3eWE2a2dWOHlsaldKZXpSLWN5c3BkUWdBRkJuSzhHdWl2ZjgwTFFFYnd0aTAxZ3dJU0hCekNZNm9aTTJSZUNfQjVIM3FrUUJ4NXAwa3paZ3BEek9xTVZNQWdnN01xRHloV1ZXZHV6N0JpUWo3RE9DMlFGdkNnWkloTjVVY3RBR1RSRUJJWFVtby1fMWFMNTdLZw?oc=5</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -3928,14 +4002,14 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-17.39</v>
+        <v>-20.05</v>
       </c>
       <c r="O5" t="n">
-        <v>-66.16</v>
+        <v>-63.486</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Cochabamba, Cochabamba</t>
+          <t>Camiri, Santa Cruz</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -3945,19 +4019,19 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Camiri</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>noticia:167wlhz</t>
+          <t>noticia:1uf38hl</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3967,11 +4041,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-25 07:53</t>
+          <t>2026-10-25 10:59</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1792929231000</v>
+        <v>1792940350000</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -3980,7 +4054,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -3993,13 +4067,13 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>¡A sacar el paraguas! Santa cruz amanece con lluvia, frío y complicaciones en el tránsito vehicular - Red Uno</t>
+          <t>¡Cisterna con combustible en llamas! Reportan impresionante incendio en la carretera a Camiri - Red Uno</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOY1ZpYktLR3pUQXotUndVR3puUzVHbW1YTzNyUmJvUHB4Q2JmelRvOEdaRldOUm1xLVJnbGR5VWcxTjNEM3ZUYktCUWtVM0hKSjFuRGdpX0JxN0M5MVZBSG1aVURyVWktdmxwbUtRT19ydU5LdzNTZ2Zpb2ozdHlMUUdTVlAyVk4xODBnV0hyTXdVVndyNzV3VC1KMzFnV3lpcFFXSk9MdDZOTWlWakNwT1FnNDh6QVdjazVYZDVVMkdaLU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxORUhqeWpKY1FHRWoxaHN0UXFzS3dpeHh6N0NwLUJOZTlZcDVoNHN0VnI0by1qMWtZZEkxVmtUNjdNTFhjaEFQU2IyMlNwZW95WFBzbFJPVVB6TjJtdjNENk1LWVlsMUxUUzBNVzkxRk1HZ3lQU0s2M1lRVlRuaXlkMmJrd3AyTGpIdXItNkhlU3dhTzBRME56Rm1DSlZCYjNxSnNTbTFqNWRoUkdraHhlREhuYldqeFk2N3poWEx2M08?oc=5</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -4009,14 +4083,14 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-17.781</v>
+        <v>-20.05</v>
       </c>
       <c r="O6" t="n">
-        <v>-63.139</v>
+        <v>-63.486</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Santa Cruz, Santa Cruz</t>
+          <t>Camiri, Santa Cruz</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -4031,14 +4105,14 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Camiri</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>noticia:bzr7eh</t>
+          <t>noticia:1sg8pi0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4048,39 +4122,39 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-25 07:09</t>
+          <t>2026-10-25 09:59</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1792926572000</v>
+        <v>1792936752000</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>hidrológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Alerta naranja por riesgo de desbordes de ríos - El Diario - Bolivia</t>
+          <t>Bus de agrupación musical sufre accidente rumbo al trópico de Cochabamba | VIDEO - Red Uno</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNNGZKSDVaZkowWUFGSEUyTWR3d3dsc04waFBLLWUtcVpiTDYzbmNtYTN1RkFLbjAwN3dxT0xZc3pqc3REUXduZVltQ2Fud1BZLTh1bTNiTEJueVUwV0dERS1iUXZqMHd0UnFrQ3E2SFAzbm5lQ1I4U29MaHJFbWFvdVRTeFY4Wl9rSmc3RkpaQ2xwX0oz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOVDVzVTJNM2JuQ25sMThEaVZNOUNRd3FGT3RhVnFrZXZ2NDQ1YlluTVdhbVNUQnA1MGNESHRSWVUzbC1kRVh3OTR0emtlTG91cmRWeFJ5dk5zb3p2WFRyMEJUV3FNRnY1WHhRUU9WLTlJcmNyNXJZZFdoM0JoZjNpa3hjUXhMM0xrUDJab2VadkM5RWZYQ3lWZTVDdzg1akxJT2lxcDVNNzI0NG1hejdfdkUyTQ?oc=5</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -4089,21 +4163,37 @@
       <c r="M7" t="n">
         <v>0</v>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>-17.39</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-66.16</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Cochabamba, Cochabamba</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>noticia:1fo4ig4</t>
+          <t>noticia:167wlhz</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4113,62 +4203,78 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-25 01:08</t>
+          <t>2026-10-25 07:53</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1792904880000</v>
+        <v>1792929231000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>diarioelpueblo.com.pe</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>roja</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
+          <t>¡A sacar el paraguas! Santa cruz amanece con lluvia, frío y complicaciones en el tránsito vehicular - Red Uno</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQcmFrT3dwcEs0X3U2NWxnOGJwNnI2WHdWTGZYbzEyNnJzUWhkbU9TRWhfSlB5UkMwX2gyMmxYUmVNWmxNOVR6V0twRHpFMTVIYjBKbHQ2TXN2d2w5dkFpcWJCcUJMZldaX01sNWtQV2ZJOGpRVzR3NDVIU0pJc1BNVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOY1ZpYktLR3pUQXotUndVR3puUzVHbW1YTzNyUmJvUHB4Q2JmelRvOEdaRldOUm1xLVJnbGR5VWcxTjNEM3ZUYktCUWtVM0hKSjFuRGdpX0JxN0M5MVZBSG1aVURyVWktdmxwbUtRT19ydU5LdzNTZ2Zpb2ozdHlMUUdTVlAyVk4xODBnV0hyTXdVVndyNzV3VC1KMzFnV3lpcFFXSk9MdDZOTWlWakNwT1FnNDh6QVdjazVYZDVVMkdaLU0?oc=5</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>-17.781</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-63.139</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Santa Cruz, Santa Cruz</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Santa Cruz de la Sierra</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>noticia:r1uot6</t>
+          <t>noticia:bzr7eh</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4178,78 +4284,62 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-24 20:00</t>
+          <t>2026-10-25 07:09</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1792886439000</v>
+        <v>1792926572000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>hidrológica</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>vuelco deja heridos en ruta Oruro – Huanuni - La Patria Bolivia</t>
+          <t>Alerta naranja por riesgo de desbordes de ríos - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNNDQtMG1KT1lLWW5nem9Jbm5JWDZKNlRWZmFmRlBxWDlDeXlSWnJ5d2NsTlpxa0JIS25oVWVZOC1majZVbWhOVDIxR0dLOFlzY2VpVzVoVk1mQnF3dXVwLUFZVHc1UjlXZzF5T05CY3U0ZldLVkw1VzBTek5zanpjQW1xalltWHNiaXI3dTNR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNNGZKSDVaZkowWUFGSEUyTWR3d3dsc04waFBLLWUtcVpiTDYzbmNtYTN1RkFLbjAwN3dxT0xZc3pqc3REUXduZVltQ2Fud1BZLTh1bTNiTEJueVUwV0dERS1iUXZqMHd0UnFrQ3E2SFAzbm5lQ1I4U29MaHJFbWFvdVRTeFY4Wl9rSmc3RkpaQ2xwX0oz?oc=5</t>
         </is>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>-17.97</v>
-      </c>
-      <c r="O9" t="n">
-        <v>-67.11</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Oruro, Oruro</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>Oruro</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>Oruro</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>noticia:1ytw450</t>
+          <t>noticia:1fo4ig4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4259,11 +4349,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-24 18:58</t>
+          <t>2026-10-25 01:08</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1792882686000</v>
+        <v>1792904880000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -4291,7 +4381,7 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNZ1U3bEVuaVdjVE1zSU9lOHJZTVRZLVZaemhldGNnT1JBWDJvbzdvM3paVVNhLUlyWHF2akNuSXJOLXdyTGRuejRlV1FuMjVkTjA3NmdRdmgtRWlUeTFBV1dEMzBvejBxaXZJdUZZWkRVTF9VLU5BcjFGZGFEQ09WWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQcmFrT3dwcEs0X3U2NWxnOGJwNnI2WHdWTGZYbzEyNnJzUWhkbU9TRWhfSlB5UkMwX2gyMmxYUmVNWmxNOVR6V0twRHpFMTVIYjBKbHQ2TXN2d2w5dkFpcWJCcUJMZldaX01sNWtQV2ZJOGpRVzR3NDVIU0pJc1BNVg?oc=5</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -4314,7 +4404,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>noticia:1wcb22g</t>
+          <t>noticia:r1uot6</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4324,62 +4414,78 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-24 17:47</t>
+          <t>2026-10-24 20:00</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1792878475000</v>
+        <v>1792886439000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Mundo Bolivia</t>
+          <t>La Patria Bolivia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>hidrológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Alerta naranja por ingreso de frente frío y desbordes de ríos en 6 departamentos - El Mundo Bolivia</t>
+          <t>vuelco deja heridos en ruta Oruro – Huanuni - La Patria Bolivia</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPZW00RkxJSklTelNrS2hqczJDWHlwcENFX2lnSEUyTEFPaDFRQ2JvMUcyd3NfYjg0UE9ORGxHRzB4ZDh3U0hQQ1JSQlhsaUY4N3ByMUUxei1SaUZnNlp6T3hsLVdiMGhKaXhsV1FNSUNQMHlvQ19qdk56SEF0d2RXVFctS0VPT25kNGZCRDdvZ2dxU0VoUUJKU0ZBd0ZycFNEZFh0T3ZjOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNNDQtMG1KT1lLWW5nem9Jbm5JWDZKNlRWZmFmRlBxWDlDeXlSWnJ5d2NsTlpxa0JIS25oVWVZOC1majZVbWhOVDIxR0dLOFlzY2VpVzVoVk1mQnF3dXVwLUFZVHc1UjlXZzF5T05CY3U0ZldLVkw1VzBTek5zanpjQW1xalltWHNiaXI3dTNR?oc=5</t>
         </is>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-17.97</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-67.11</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Oruro, Oruro</t>
+        </is>
+      </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>noticia:1c1ju1f</t>
+          <t>noticia:1ytw450</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4389,15 +4495,15 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-24 17:02</t>
+          <t>2026-10-24 18:58</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1792875752000</v>
+        <v>1792882686000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>La Razón Digital Bolivia</t>
+          <t>diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -4406,29 +4512,29 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>roja</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a los Yungas deja siete heridos - La Razón Digital Bolivia</t>
+          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPTGQwaVBfdG1JdVRMUTN4LVVvN0ppc3dreDJVVllDR3RmX0xpMzB4b0pvVTNSV1B6T0ZEWTdEZkNsRUdSNzhLaC1CWHN5WktNWk1nRWpTdVZiYjI3TlJlX2xlVTI5MjlRU2hiY1gteml4YWVFbDNPSVRBZmtITlQzbmhaUXVmcThRa2xsQTJIOXZuNzlSdm12MEdyOEZHdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNZ1U3bEVuaVdjVE1zSU9lOHJZTVRZLVZaemhldGNnT1JBWDJvbzdvM3paVVNhLUlyWHF2akNuSXJOLXdyTGRuejRlV1FuMjVkTjA3NmdRdmgtRWlUeTFBV1dEMzBvejBxaXZJdUZZWkRVTF9VLU5BcjFGZGFEQ09WWQ?oc=5</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -4444,7 +4550,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>noticia:14iwzop</t>
+          <t>noticia:1wcb22g</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4454,46 +4560,46 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-24 13:40</t>
+          <t>2026-10-24 17:47</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1792863623000</v>
+        <v>1792878475000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>EL DÍA - Noticias de Bolivia para el mundo</t>
+          <t>El Mundo Bolivia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>hidrológica</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a Mayaya deja siete heridos de la agrupación Los Chicos Fieles - EL DÍA - Noticias de Bolivia para el mundo</t>
+          <t>Alerta naranja por ingreso de frente frío y desbordes de ríos en 6 departamentos - El Mundo Bolivia</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPeGd3VWpCWXJ0YTJIeDJLcktzWG1jdUh0TjFXb01wSTkxbHNXZU94VWNDMkxnTjlJZVdpbkprMEY2NE80RXYyUWxUQXVnbl9lUXR2b28zTEh6cTJLVEQ4TUNja2kzRlhadVBFZFVwV1U2TlhseXZMZ20zZTZiUFpWRjdCOWNBMHU5XzdMV3JqQjV4TEE3bHRMOXR6Nm55eHZUNnFHSDdVRk8zVkY4RkVsUUtUN0JYdkREWGZncmJ3ZWc2T1BuUm1ZLTlfcHVabFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPZW00RkxJSklTelNrS2hqczJDWHlwcENFX2lnSEUyTEFPaDFRQ2JvMUcyd3NfYjg0UE9ORGxHRzB4ZDh3U0hQQ1JSQlhsaUY4N3ByMUUxei1SaUZnNlp6T3hsLVdiMGhKaXhsV1FNSUNQMHlvQ19qdk56SEF0d2RXVFctS0VPT25kNGZCRDdvZ2dxU0VoUUJKU0ZBd0ZycFNEZFh0T3ZjOA?oc=5</t>
         </is>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -4509,7 +4615,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>noticia:1ukcn97</t>
+          <t>noticia:1c1ju1f</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4519,15 +4625,15 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-24 13:26</t>
+          <t>2026-10-24 17:02</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1792862794000</v>
+        <v>1792875752000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Deber</t>
+          <t>La Razón Digital Bolivia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -4545,20 +4651,20 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Esta es la lista preliminar de los heridos en el accidente del grupo 'Los chicos fieles', el conductor está grave - El Deber</t>
+          <t>Accidente en la carretera a los Yungas deja siete heridos - La Razón Digital Bolivia</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOczZKbFd1QzRpak92LXpPWXZXQXJObnBQTG9qRFBlUUV5dThMWXhzckFFUHAyb2thU1JwRmJDSEZfaEdTUXh1bjZvQWpYMGhfUno3cWZ4MGpldEpoQXhzSlVzTm5LLW9OcjB2MWRsdHQ2UlI2SjEtZ085ZTR5Z3pEVmtBTF9lc29Kd0RhaTRUWkM4eGZJNWhBSXZqWmxuNW10dlQwYW9mdzItcWZWTkU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPTGQwaVBfdG1JdVRMUTN4LVVvN0ppc3dreDJVVllDR3RmX0xpMzB4b0pvVTNSV1B6T0ZEWTdEZkNsRUdSNzhLaC1CWHN5WktNWk1nRWpTdVZiYjI3TlJlX2xlVTI5MjlRU2hiY1gteml4YWVFbDNPSVRBZmtITlQzbmhaUXVmcThRa2xsQTJIOXZuNzlSdm12MEdyOEZHdw?oc=5</t>
         </is>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -4574,7 +4680,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>noticia:2avehj</t>
+          <t>noticia:14iwzop</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4584,20 +4690,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-24 12:53</t>
+          <t>2026-10-24 13:40</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1792860813000</v>
+        <v>1792863623000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>EL DÍA - Noticias de Bolivia para el mundo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>climatológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -4610,52 +4716,36 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Sequía en Cochabamba: más de un centenar de cabezas de ganado murieron en el cono sur - Red Uno</t>
+          <t>Accidente en la carretera a Mayaya deja siete heridos de la agrupación Los Chicos Fieles - EL DÍA - Noticias de Bolivia para el mundo</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOOFQxc2Vzc0QwS19ydC13RkRPZnZQU3JkSTl5U3kzdUdMSldTcm5HVEhWRzZyN19CLUlwcUs4MW03Ui1obVBtdzQ3QWFQc1RKdzh3MXJ5QkpRS2pRNm50V1lVb09ScGJnaVVlemVfZlRsWjdObnRmR1FGMnlMMHAyc2pMandndy10T2twcWx6OFh4UHdvbVlFbllwME9WQ2pQVjNTQzBxeTg5YnF3bDREeHVDYXpObFFIaTZZQWtYUE12cGQ1ZGRhT0syNjVhZWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPeGd3VWpCWXJ0YTJIeDJLcktzWG1jdUh0TjFXb01wSTkxbHNXZU94VWNDMkxnTjlJZVdpbkprMEY2NE80RXYyUWxUQXVnbl9lUXR2b28zTEh6cTJLVEQ4TUNja2kzRlhadVBFZFVwV1U2TlhseXZMZ20zZTZiUFpWRjdCOWNBMHU5XzdMV3JqQjV4TEE3bHRMOXR6Nm55eHZUNnFHSDdVRk8zVkY4RkVsUUtUN0JYdkREWGZncmJ3ZWc2T1BuUm1ZLTlfcHVabFE?oc=5</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>-17.39</v>
-      </c>
-      <c r="O15" t="n">
-        <v>-66.16</v>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Cochabamba, Cochabamba</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>noticia:1ksmg5u</t>
+          <t>noticia:1ukcn97</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4665,15 +4755,15 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-24 11:43</t>
+          <t>2026-10-24 13:26</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1792856591000</v>
+        <v>1792862794000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
+          <t>El Deber</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -4691,13 +4781,13 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Embarrancamiento deja heridos a integrantes de Los Chicos Fieles - La Patria Bolivia</t>
+          <t>Esta es la lista preliminar de los heridos en el accidente del grupo 'Los chicos fieles', el conductor está grave - El Deber</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNeEFrOEtOMHZxMW42REFPU0x1MG5oQjlBMkJucWRLZ292alBXekJKeURBN3NLTVVadWI0OWF4UGtSVXBzTE01eWFSU1kyMUhNZ04zMWNMaUxnMDBBZ0EwTktXbjlaVTBUUmNqa3AwY19KNTU2LWh5LW9IVElVdTdnaHFPanJPd2FqMUxzaUhXZmVpYU1saGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOczZKbFd1QzRpak92LXpPWXZXQXJObnBQTG9qRFBlUUV5dThMWXhzckFFUHAyb2thU1JwRmJDSEZfaEdTUXh1bjZvQWpYMGhfUno3cWZ4MGpldEpoQXhzSlVzTm5LLW9OcjB2MWRsdHQ2UlI2SjEtZ085ZTR5Z3pEVmtBTF9lc29Kd0RhaTRUWkM4eGZJNWhBSXZqWmxuNW10dlQwYW9mdzItcWZWTkU0?oc=5</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -4720,7 +4810,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>noticia:mlyqgd</t>
+          <t>noticia:2avehj</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4730,20 +4820,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-24 11:30</t>
+          <t>2026-10-24 12:53</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1792855818000</v>
+        <v>1792860813000</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Opinión Bolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>climatológica</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4756,36 +4846,52 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a Mayaya deja siete heridos de la agrupación Los Chicos Fieles - Opinión Bolivia</t>
+          <t>Sequía en Cochabamba: más de un centenar de cabezas de ganado murieron en el cono sur - Red Uno</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYjNxaHg3YllRRTJYdFd1clAtUlROSGlFNVg5eUVZUGJoOEZ4MWM5QU5WQm1YTDc4NXc3SjhWMUw0TkZfSHlMLUQ1bmpTME1Kb1JaM0ExamFHYTd3VlU4MXRWdTZ1bzh1SGYtbGE1a3dBaG93bjg1OGc0S0JfRE43c3dVMVltN0dQQzNhQUNhM0FjVUNRUDRSamlJYlk2dEJpUTBuY2hBcTFucTVRN0ZtYnc5bzdmTV9LQm1uVUxaZS1tUE9IejhBVDRCdU_SAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOOFQxc2Vzc0QwS19ydC13RkRPZnZQU3JkSTl5U3kzdUdMSldTcm5HVEhWRzZyN19CLUlwcUs4MW03Ui1obVBtdzQ3QWFQc1RKdzh3MXJ5QkpRS2pRNm50V1lVb09ScGJnaVVlemVfZlRsWjdObnRmR1FGMnlMMHAyc2pMandndy10T2twcWx6OFh4UHdvbVlFbllwME9WQ2pQVjNTQzBxeTg5YnF3bDREeHVDYXpObFFIaTZZQWtYUE12cGQ1ZGRhT0syNjVhZWs?oc=5</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>7</v>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-17.39</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-66.16</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Cochabamba, Cochabamba</t>
+        </is>
+      </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>noticia:irf4jl</t>
+          <t>noticia:1ksmg5u</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4795,15 +4901,15 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-24 11:30</t>
+          <t>2026-10-24 11:43</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1792855818000</v>
+        <v>1792856591000</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Opinión Bolivia</t>
+          <t>La Patria Bolivia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -4821,20 +4927,20 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a Mayaya deja siete heridos de la agrupación Los Chicos Fieles - Opinión Bolivia</t>
+          <t>Embarrancamiento deja heridos a integrantes de Los Chicos Fieles - La Patria Bolivia</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNMXlMNXFWSWhhWWNDRFFKMncwS2JGWm0tWlJCd2x2RjZhdFhEQ0lBcVlFSS1WRVYxMEVJTWRHcTY3M0stdWhGdnVPRU13X2MwSVRWX25xVUQxa0R6Z1pqQ2dfY0VjUmw2aXFoWFNVNk15N2dBOENZLWlGSWJfMW0zejVoZ3ZwVHVQV1MzbzlnUlpRcWIxMHZxdkItZTc0QmMyRnBmSVRtVnZ5Y3gtdVpYNXFwcGdadGVCU3dRZ3EwOTdiWHU4OXJRdEFoNi1HcnA1U0HSAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNeEFrOEtOMHZxMW42REFPU0x1MG5oQjlBMkJucWRLZ292alBXekJKeURBN3NLTVVadWI0OWF4UGtSVXBzTE01eWFSU1kyMUhNZ04zMWNMaUxnMDBBZ0EwTktXbjlaVTBUUmNqa3AwY19KNTU2LWh5LW9IVElVdTdnaHFPanJPd2FqMUxzaUhXZmVpYU1saGc?oc=5</t>
         </is>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
@@ -4850,7 +4956,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>noticia:1g006zh</t>
+          <t>noticia:mlyqgd</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4860,15 +4966,15 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-24 11:25</t>
+          <t>2026-10-24 11:30</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1792855522000</v>
+        <v>1792855818000</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>El Potosí</t>
+          <t>Opinión Bolivia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4886,13 +4992,13 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a Mayaya deja siete heridos del grupo Los Chicos Fieles - El Potosí</t>
+          <t>Accidente en la carretera a Mayaya deja siete heridos de la agrupación Los Chicos Fieles - Opinión Bolivia</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTC10eC1qSm1WRlY2YzA3VEJqOG1LUkx6bE9PdFYwTFBZMGFjU0RMYXliRkhXcTJHRlVzb0Y4QUU0WWJDQ1plS2NZamZ1YmFadE5qY3g4UE5aYVAwamtCUUNZaDB2YWJTdWRKS3R4a0hHUjVobUl0Y1dYZ2JPczAwak5kN1hjUEwwM1NtUDVWbnAzWTdnRng3RjFValFVVlZPdVZnWFlUODhPOE5aMTROQzVKVjVRS2VoaTlaQnBiUGRTNFk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYjNxaHg3YllRRTJYdFd1clAtUlROSGlFNVg5eUVZUGJoOEZ4MWM5QU5WQm1YTDc4NXc3SjhWMUw0TkZfSHlMLUQ1bmpTME1Kb1JaM0ExamFHYTd3VlU4MXRWdTZ1bzh1SGYtbGE1a3dBaG93bjg1OGc0S0JfRE43c3dVMVltN0dQQzNhQUNhM0FjVUNRUDRSamlJYlk2dEJpUTBuY2hBcTFucTVRN0ZtYnc5bzdmTV9LQm1uVUxaZS1tUE9IejhBVDRCdU_SAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -4901,60 +5007,44 @@
       <c r="M19" t="n">
         <v>7</v>
       </c>
-      <c r="N19" t="n">
-        <v>-19.58</v>
-      </c>
-      <c r="O19" t="n">
-        <v>-65.75</v>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Potosí, Potosí</t>
-        </is>
-      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>clima:Potosí:2026-10-24:viento:1</t>
+          <t>noticia:irf4jl</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-24 10:55</t>
+          <t>2026-10-24 11:30</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1792853727284</v>
+        <v>1792855818000</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>Opinión Bolivia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4967,56 +5057,36 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Potosí 2026-10-24: 60.5 km/h de ráfagas pronosticadas</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
-        </is>
-      </c>
+          <t>Accidente en la carretera a Mayaya deja siete heridos de la agrupación Los Chicos Fieles - Opinión Bolivia</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNMXlMNXFWSWhhWWNDRFFKMncwS2JGWm0tWlJCd2x2RjZhdFhEQ0lBcVlFSS1WRVYxMEVJTWRHcTY3M0stdWhGdnVPRU13X2MwSVRWX25xVUQxa0R6Z1pqQ2dfY0VjUmw2aXFoWFNVNk15N2dBOENZLWlGSWJfMW0zejVoZ3ZwVHVQV1MzbzlnUlpRcWIxMHZxdkItZTc0QmMyRnBmSVRtVnZ5Y3gtdVpYNXFwcGdadGVCU3dRZ3EwOTdiWHU4OXJRdEFoNi1HcnA1U0HSAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
         </is>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>-19.58</v>
-      </c>
-      <c r="O20" t="n">
-        <v>-65.75</v>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>capital (pronóstico puntual)</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>noticia:1ax0bpy</t>
+          <t>noticia:1g006zh</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5026,56 +5096,56 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-24 10:32</t>
+          <t>2026-10-24 11:25</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1792852364000</v>
+        <v>1792855522000</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Que Pasa Salta</t>
+          <t>El Potosí</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Creció el Bermejo tras la tormenta: así está el puerto de chalanas en este momento - Que Pasa Salta</t>
+          <t>Accidente en la carretera a Mayaya deja siete heridos del grupo Los Chicos Fieles - El Potosí</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVld9IBfkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVldw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTC10eC1qSm1WRlY2YzA3VEJqOG1LUkx6bE9PdFYwTFBZMGFjU0RMYXliRkhXcTJHRlVzb0Y4QUU0WWJDQ1plS2NZamZ1YmFadE5qY3g4UE5aYVAwamtCUUNZaDB2YWJTdWRKS3R4a0hHUjVobUl0Y1dYZ2JPczAwak5kN1hjUEwwM1NtUDVWbnAzWTdnRng3RjFValFVVlZPdVZnWFlUODhPOE5aMTROQzVKVjVRS2VoaTlaQnBiUGRTNFk?oc=5</t>
         </is>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N21" t="n">
-        <v>-22.721</v>
+        <v>-19.58</v>
       </c>
       <c r="O21" t="n">
-        <v>-64.32599999999999</v>
+        <v>-65.75</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bermejo, Tarija</t>
+          <t>Potosí, Potosí</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -5085,65 +5155,65 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Tarija</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>Bermejo</t>
+          <t>Potosí</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>gdacs:WF1033142:0</t>
+          <t>clima:Potosí:2026-10-24:viento:1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>gdacs</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-24 07:06</t>
+          <t>2026-10-24 10:55</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1792839995000</v>
+        <v>1792853727284</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>GDACS</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Green forest fire notification in Bolivia</t>
+          <t>Potosí 2026-10-24: 60.5 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>On 21/10/2026, a forest fire started in Bolivia, until 24/10/2026.</t>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>http://www.gdacs.org/report.aspx?eventtype=WF&amp;eventid=1033142</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -5153,36 +5223,36 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>-13.06332</v>
+        <v>-19.58</v>
       </c>
       <c r="O22" t="n">
-        <v>-67.66426</v>
+        <v>-65.75</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>coordenada de la fuente</t>
+          <t>capital (pronóstico puntual)</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>Ixiamas</t>
+          <t>Potosí</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>noticia:1shhqva</t>
+          <t>noticia:1ax0bpy</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5192,20 +5262,20 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-24 06:33</t>
+          <t>2026-10-24 10:32</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1792838034000</v>
+        <v>1792852364000</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>Que Pasa Salta</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5218,13 +5288,13 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
+          <t>Creció el Bermejo tras la tormenta: así está el puerto de chalanas en este momento - Que Pasa Salta</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQYzB6N082XzFRRnVtcDVmUkYyWjcxUzV2Z3Frd1I0WDNXSnZtY0QzOU1PUkNLMktVT1Vra2FSeXhxZDRuOFZYZjFwejl6ejJTbWY2MGJuSGN3ZHdrdG5JUkgzSXBkbDYtaHlackY3OVFuNWdLcFNpdWNHRU9vNGdoVWx2ODFVdzJXYUxnM0tUcjJvZmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVld9IBfkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVldw?oc=5</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -5234,14 +5304,14 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>-17.97</v>
+        <v>-22.721</v>
       </c>
       <c r="O23" t="n">
-        <v>-67.11</v>
+        <v>-64.32599999999999</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>Bermejo, Tarija</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -5251,65 +5321,65 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Tarija</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Bermejo</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>clima:Potosí:2026-10-25:viento:1</t>
+          <t>gdacs:WF1033142:0</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>gdacs</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-24 02:55</t>
+          <t>2026-10-24 07:06</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1792824927736</v>
+        <v>1792839995000</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>GDACS</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Potosí 2026-10-25: 60.5 km/h de ráfagas pronosticadas</t>
+          <t>Green forest fire notification in Bolivia</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+          <t>On 21/10/2026, a forest fire started in Bolivia, until 24/10/2026.</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>http://www.gdacs.org/report.aspx?eventtype=WF&amp;eventid=1033142</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -5319,36 +5389,36 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>-19.58</v>
+        <v>-13.06332</v>
       </c>
       <c r="O24" t="n">
-        <v>-65.75</v>
+        <v>-67.66426</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>capital (pronóstico puntual)</t>
+          <t>coordenada de la fuente</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Ixiamas</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>noticia:mz6q0s</t>
+          <t>noticia:1shhqva</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5358,85 +5428,101 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-23 23:09</t>
+          <t>2026-10-24 06:33</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1792811349000</v>
+        <v>1792838034000</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Revelan lista preliminar de heridos tras accidente de Los Chicos Fieles - Red Uno</t>
+          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPczBQcnE2SzFGMXc3b1lsTkNxVWRmS3Vnb01xOTV2WmVva3J2RVlteWpHZ3VJS2dNWGV5NW5FX3ZncnVKTEVDTGpBRndTU1FxeWxtaS1fb1FscGxXMWNXUE9zbHdob1AxVFl1eHB5OU1yUnNoOXJ6U21oVG9PVDA1ak1xQl9hUlB4V0RaQXJqZENGUm8zMUJEY3J0WW5ENE5ObWJLNmpWN0RkSmFJbnZUZGR5UFRPd3QyUFY4WQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQYzB6N082XzFRRnVtcDVmUkYyWjcxUzV2Z3Frd1I0WDNXSnZtY0QzOU1PUkNLMktVT1Vra2FSeXhxZDRuOFZYZjFwejl6ejJTbWY2MGJuSGN3ZHdrdG5JUkgzSXBkbDYtaHlackY3OVFuNWdLcFNpdWNHRU9vNGdoVWx2ODFVdzJXYUxnM0tUcjJvZmc?oc=5</t>
         </is>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-17.97</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-67.11</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Oruro, Oruro</t>
+        </is>
+      </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>noticia:1uil931</t>
+          <t>clima:Potosí:2026-10-25:viento:1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-23 22:49</t>
+          <t>2026-10-24 02:55</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1792810149000</v>
+        <v>1792824927736</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>El Deber</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5449,52 +5535,56 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Accidente de tránsito en la ruta hacia Alto Beni deja varios heridos - El Deber</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+          <t>Potosí 2026-10-25: 60.5 km/h de ráfagas pronosticadas</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQakFJRmx3RlJEMkVHU0pxWXZ2ZU1ib04tZy1yeTB2OGhrYk9CU3pMaDVpRThNZktZMS14UzA2Y1VIcEQtZDg3cEU2SmlzQnBmUVVvM0ZNYzZWNExWUXQ3aHpnd3lqOHFVV3pNbDRLS1NQNGtwb2RjSFpleHJkOG5zSXVtWjVIS1dLejNybktRWTJVZXh3WkFUQVE5T2tMdFdn?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>-15.578</v>
+        <v>-19.58</v>
       </c>
       <c r="O26" t="n">
-        <v>-67.44</v>
+        <v>-65.75</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Alto Beni, La Paz</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
+          <t>capital (pronóstico puntual)</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Alto Beni</t>
+          <t>Potosí</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>noticia:1tliu4i</t>
+          <t>noticia:mz6q0s</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5504,15 +5594,15 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-10-23 22:18</t>
+          <t>2026-10-23 23:09</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1792808330000</v>
+        <v>1792811349000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>El Deber</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5530,13 +5620,13 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Accidente de tránsito en la ruta hacia Alto Beni deja varios heridos - El Deber</t>
+          <t>Revelan lista preliminar de heridos tras accidente de Los Chicos Fieles - Red Uno</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQMF9BNnUzLURKNGRMUUJ1VXVRSXNnMlBsQnVXOG0tRlFtY3pvRDNPQmNJMWN2RzJVaWdoWndmcHFnTkZFZnJxRkZtMThYYWlwN09ueUgtei1pSE1hZ2FtSzN6elY4VXJHbzFxdll0eWh0ZkxwQkQ1SDZ5b0E3MlVENGZEWGZHUGlwVG4wd2x3OFNEMVpibnFr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPczBQcnE2SzFGMXc3b1lsTkNxVWRmS3Vnb01xOTV2WmVva3J2RVlteWpHZ3VJS2dNWGV5NW5FX3ZncnVKTEVDTGpBRndTU1FxeWxtaS1fb1FscGxXMWNXUE9zbHdob1AxVFl1eHB5OU1yUnNoOXJ6U21oVG9PVDA1ak1xQl9hUlB4V0RaQXJqZENGUm8zMUJEY3J0WW5ENE5ObWJLNmpWN0RkSmFJbnZUZGR5UFRPd3QyUFY4WQ?oc=5</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -5545,37 +5635,21 @@
       <c r="M27" t="n">
         <v>1</v>
       </c>
-      <c r="N27" t="n">
-        <v>-15.578</v>
-      </c>
-      <c r="O27" t="n">
-        <v>-67.44</v>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Alto Beni, La Paz</t>
-        </is>
-      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>La Paz</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>Alto Beni</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>noticia:1twc9ul</t>
+          <t>noticia:1uil931</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5585,11 +5659,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-10-23 22:16</t>
+          <t>2026-10-23 22:49</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1792808192000</v>
+        <v>1792810149000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -5617,7 +5691,7 @@
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNbmwzSnd6c2tFMXBWY0tiemJqRm5CNllOT2p1U0FhdW5QNGFBVXlSZVM1ak5jNGZvcXNVaUQzN3ZQQTlPbmVjQ2Y5RFl2dWVLeUN5NUFodDF0alEyZWlmOHFZWkVVbjdQbkl3ZWtmS25wQWM2TmRZZDBGM2xlS0ZhUzAweXRmcmhVWGY5dV9CUnFBNGtWZHZDSWVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQakFJRmx3RlJEMkVHU0pxWXZ2ZU1ib04tZy1yeTB2OGhrYk9CU3pMaDVpRThNZktZMS14UzA2Y1VIcEQtZDg3cEU2SmlzQnBmUVVvM0ZNYzZWNExWUXQ3aHpnd3lqOHFVV3pNbDRLS1NQNGtwb2RjSFpleHJkOG5zSXVtWjVIS1dLejNybktRWTJVZXh3WkFUQVE5T2tMdFdn?oc=5</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -5656,7 +5730,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>noticia:1dygpkp</t>
+          <t>noticia:1tliu4i</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5666,15 +5740,15 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-10-23 21:39</t>
+          <t>2026-10-23 22:18</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1792805983000</v>
+        <v>1792808330000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>El Deber</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5683,39 +5757,39 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>(Video) Así rescataron a uno de los integrantes de Los Chicos Fieles tras accidente en Caranavi - Red Uno</t>
+          <t>Accidente de tránsito en la ruta hacia Alto Beni deja varios heridos - El Deber</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOdTVUZUQxVTdvYTdONDQxVlhUTzBOS2hKLW1rS1NUcmRYRnlCVlhIcHZlSjdsaktkQm5CWkFYa3lDQkxnMlh0b3prX0lha1BtbW1qS1VuYnNiX3FiZkYyNDJDR0tqZ0pKMU5TeC04SXV4UUJOTUlPUTB6ek01bzUxTUsydjZqZzI3S3ZLUnRWSUFUVk44WEpKUl9rbzRLb2IwYl9sLVlrYmt5d2ZHNUtGd3lRNnYzMlhuMkJOZW1XSUl2N1BxZWpHbm5XTDJhRUtnR190QWQ1TDlTUVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQMF9BNnUzLURKNGRMUUJ1VXVRSXNnMlBsQnVXOG0tRlFtY3pvRDNPQmNJMWN2RzJVaWdoWndmcHFnTkZFZnJxRkZtMThYYWlwN09ueUgtei1pSE1hZ2FtSzN6elY4VXJHbzFxdll0eWh0ZkxwQkQ1SDZ5b0E3MlVENGZEWGZHUGlwVG4wd2x3OFNEMVpibnFr?oc=5</t>
         </is>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N29" t="n">
-        <v>-15.813</v>
+        <v>-15.578</v>
       </c>
       <c r="O29" t="n">
-        <v>-67.46299999999999</v>
+        <v>-67.44</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Caranavi, La Paz</t>
+          <t>Alto Beni, La Paz</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -5730,14 +5804,14 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>Caranavi</t>
+          <t>Alto Beni</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>noticia:3dv7b0</t>
+          <t>noticia:1twc9ul</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5747,15 +5821,15 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-10-23 21:35</t>
+          <t>2026-10-23 22:16</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1792805700000</v>
+        <v>1792808192000</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FmBolivia</t>
+          <t>El Deber</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -5773,13 +5847,13 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Accidente en Caranavi: vehículo de Los Chicos Fieles cae a un barranco y deja varios heridos - FmBolivia</t>
+          <t>Accidente de tránsito en la ruta hacia Alto Beni deja varios heridos - El Deber</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNcE1KaHZyUTJCSElxRU9nVzdhTnczWjJGTEhFMEs0bHp2cUdFeHd3VTB0NmVFcjdEN1dsZDZLY2k1ZFFUWkhKV19PU3V2czNyamh1ZE9YajVSVF8xczF6OFhZcWFvYV9EcWg4ZDNCb2p3enhXbFpRYnJMdGdaTXNrWUZSYVhKNTVicWlCLTJ5OE05Z1BvNEx1eEloUk5qTGN3ZHNzbzZWSVljbnRmSERJUWdxRDc0MjJxMGtycWJaaVhXQUUxVUlaWVZLOWE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNbmwzSnd6c2tFMXBWY0tiemJqRm5CNllOT2p1U0FhdW5QNGFBVXlSZVM1ak5jNGZvcXNVaUQzN3ZQQTlPbmVjQ2Y5RFl2dWVLeUN5NUFodDF0alEyZWlmOHFZWkVVbjdQbkl3ZWtmS25wQWM2TmRZZDBGM2xlS0ZhUzAweXRmcmhVWGY5dV9CUnFBNGtWZHZDSWVB?oc=5</t>
         </is>
       </c>
       <c r="L30" t="n">
@@ -5789,14 +5863,14 @@
         <v>1</v>
       </c>
       <c r="N30" t="n">
-        <v>-15.813</v>
+        <v>-15.578</v>
       </c>
       <c r="O30" t="n">
-        <v>-67.46299999999999</v>
+        <v>-67.44</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Caranavi, La Paz</t>
+          <t>Alto Beni, La Paz</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -5811,60 +5885,56 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>Caranavi</t>
+          <t>Alto Beni</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-24:viento:1</t>
+          <t>noticia:1dygpkp</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-10-23 20:55</t>
+          <t>2026-10-23 21:39</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1792803329663</v>
+        <v>1792805983000</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-24: 78.1 km/h de ráfagas pronosticadas</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
-        </is>
-      </c>
+          <t>(Video) Así rescataron a uno de los integrantes de Los Chicos Fieles tras accidente en Caranavi - Red Uno</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOdTVUZUQxVTdvYTdONDQxVlhUTzBOS2hKLW1rS1NUcmRYRnlCVlhIcHZlSjdsaktkQm5CWkFYa3lDQkxnMlh0b3prX0lha1BtbW1qS1VuYnNiX3FiZkYyNDJDR0tqZ0pKMU5TeC04SXV4UUJOTUlPUTB6ek01bzUxTUsydjZqZzI3S3ZLUnRWSUFUVk44WEpKUl9rbzRLb2IwYl9sLVlrYmt5d2ZHNUtGd3lRNnYzMlhuMkJOZW1XSUl2N1BxZWpHbm5XTDJhRUtnR190QWQ1TDlTUVk?oc=5</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -5874,36 +5944,36 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>-17.78</v>
+        <v>-15.813</v>
       </c>
       <c r="O31" t="n">
-        <v>-63.18</v>
+        <v>-67.46299999999999</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Caranavi, La Paz</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>capital (pronóstico puntual)</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Caranavi</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>noticia:rabz5p</t>
+          <t>noticia:3dv7b0</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5913,56 +5983,56 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-23 20:44</t>
+          <t>2026-10-23 21:35</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1792802686000</v>
+        <v>1792805700000</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>FmBolivia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Tome previsiones: se pronostican lluvias y ambiente caluroso para este fin de semana en Cochabamba - Red Uno</t>
+          <t>Accidente en Caranavi: vehículo de Los Chicos Fieles cae a un barranco y deja varios heridos - FmBolivia</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTlU5NVFpY1RheTN5ZE1IbG5VYTh2Sk5hZHpHeWI3LVdnSFg2cFJFdnBCVkxiUjNKcUgyUW16SWxpMXFkMHdad2xFN043bklJeG1iQ0V1V3hBZk1Ga3NscjdPVWUySmt4bDNTdWlmSUdOMmNlZ2hkSWZFMmk4VGs0Nm9TcnRCTDhINmtnQU9zZDBUY05HcWpxN3FOX3N1dmVJblE0MGc5di1Ma1N2dGNxOUtoV1MzNnl1OXpRaTZ2UGxMc3RDWndubHVQNUd0eVROMGR2OGxVemtOaEc4bTNRaA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNcE1KaHZyUTJCSElxRU9nVzdhTnczWjJGTEhFMEs0bHp2cUdFeHd3VTB0NmVFcjdEN1dsZDZLY2k1ZFFUWkhKV19PU3V2czNyamh1ZE9YajVSVF8xczF6OFhZcWFvYV9EcWg4ZDNCb2p3enhXbFpRYnJMdGdaTXNrWUZSYVhKNTVicWlCLTJ5OE05Z1BvNEx1eEloUk5qTGN3ZHNzbzZWSVljbnRmSERJUWdxRDc0MjJxMGtycWJaaVhXQUUxVUlaWVZLOWE?oc=5</t>
         </is>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N32" t="n">
-        <v>-17.39</v>
+        <v>-15.813</v>
       </c>
       <c r="O32" t="n">
-        <v>-66.16</v>
+        <v>-67.46299999999999</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Cochabamba, Cochabamba</t>
+          <t>Caranavi, La Paz</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -5972,42 +6042,42 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Caranavi</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>noticia:1jfk053</t>
+          <t>clima:Santa Cruz:2026-10-24:viento:1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-23 19:08</t>
+          <t>2026-10-23 20:55</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1792796931000</v>
+        <v>1792803329663</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>climatológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6020,52 +6090,56 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Sequía en Pasorapa: el ganado muere por falta de agua y alistan declaratoria de desastre - Red Uno</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
+          <t>Santa Cruz 2026-10-24: 78.1 km/h de ráfagas pronosticadas</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNQVhTWE8zdE1BQ3lueWJPeV9wUDNsSmJpS0NJTWppMUY4QmlQSUFHVjRORmtrVHQ3MHB0T1pyS25PamxnY0hBQUtzOVRvSUNaUkdGb1RWSGl4dFA4Z3VINVpQTk1pZUpDdUIyUU5hZS1oNGhBa1RWcFhScVMwVTFrVlJaOFQ4OWFqRWVUZ051bHVJTlMxRTBhRFVLUEV2dTZFdDgtRkxJM3VvN3YzUWJfVk41ZWR5U1JoNmx0WFFkMmNTWGVleGNIQlNxWUJzdHIxSWtz?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>-18.38</v>
+        <v>-17.78</v>
       </c>
       <c r="O33" t="n">
-        <v>-64.649</v>
+        <v>-63.18</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Pasorapa, Cochabamba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
+          <t>capital (pronóstico puntual)</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>Pasorapa</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>noticia:ix3l8o</t>
+          <t>noticia:rabz5p</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6075,20 +6149,20 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-10-23 18:25</t>
+          <t>2026-10-23 20:44</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1792794310000</v>
+        <v>1792802686000</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Visión 360</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -6101,13 +6175,13 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Oruro evalúa suspender clases presenciales por más de 200 casos de Coxsackie - Visión 360</t>
+          <t>Tome previsiones: se pronostican lluvias y ambiente caluroso para este fin de semana en Cochabamba - Red Uno</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0c9IBywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTlU5NVFpY1RheTN5ZE1IbG5VYTh2Sk5hZHpHeWI3LVdnSFg2cFJFdnBCVkxiUjNKcUgyUW16SWxpMXFkMHdad2xFN043bklJeG1iQ0V1V3hBZk1Ga3NscjdPVWUySmt4bDNTdWlmSUdOMmNlZ2hkSWZFMmk4VGs0Nm9TcnRCTDhINmtnQU9zZDBUY05HcWpxN3FOX3N1dmVJblE0MGc5di1Ma1N2dGNxOUtoV1MzNnl1OXpRaTZ2UGxMc3RDWndubHVQNUd0eVROMGR2OGxVemtOaEc4bTNRaA?oc=5</t>
         </is>
       </c>
       <c r="L34" t="n">
@@ -6117,14 +6191,14 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>-17.97</v>
+        <v>-17.39</v>
       </c>
       <c r="O34" t="n">
-        <v>-67.11</v>
+        <v>-66.16</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -6134,19 +6208,19 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Cochabamba</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>noticia:1xqv9m7</t>
+          <t>noticia:1jfk053</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -6156,20 +6230,20 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-23 18:09</t>
+          <t>2026-10-23 19:08</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1792793370000</v>
+        <v>1792796931000</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>El Diario del centro del país</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>climatológica</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6182,36 +6256,52 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Tres heridos en tremendo choque cerca de Oncativo - El Diario del centro del país</t>
+          <t>Sequía en Pasorapa: el ganado muere por falta de agua y alistan declaratoria de desastre - Red Uno</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZERhbTJMQUJVb3hmZFlSZmRGZkdBLWdFTGJVQzdqZkE4aGhhWmdQZ2JDRW1ndkJLWU90VTZ6Ti1JOUZzcFZfcE1zbkRHU1B3YTF4UkVzdllFa1p3SUlObURGamF0Vm9kc3dPLTZVWFJ4NWZZQmlySElPNHhZTnRGNGNZUWw2ZlI1eVBEQkNGNEhLWTNiLWJLUS0xYjA0UWRhc0d6bVN4aVVLSVdsQWlpMUZYdWw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNQVhTWE8zdE1BQ3lueWJPeV9wUDNsSmJpS0NJTWppMUY4QmlQSUFHVjRORmtrVHQ3MHB0T1pyS25PamxnY0hBQUtzOVRvSUNaUkdGb1RWSGl4dFA4Z3VINVpQTk1pZUpDdUIyUU5hZS1oNGhBa1RWcFhScVMwVTFrVlJaOFQ4OWFqRWVUZ051bHVJTlMxRTBhRFVLUEV2dTZFdDgtRkxJM3VvN3YzUWJfVk41ZWR5U1JoNmx0WFFkMmNTWGVleGNIQlNxWUJzdHIxSWtz?oc=5</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>3</v>
-      </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>-18.38</v>
+      </c>
+      <c r="O35" t="n">
+        <v>-64.649</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Pasorapa, Cochabamba</t>
+        </is>
+      </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Pasorapa</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>noticia:1wuregl</t>
+          <t>noticia:ix3l8o</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -6221,20 +6311,20 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-10-23 15:39</t>
+          <t>2026-10-23 18:25</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1792784340000</v>
+        <v>1792794310000</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FmBolivia</t>
+          <t>Visión 360</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>hidrológica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6247,13 +6337,13 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Intensas lluvias inundan La Paz y activan alertas por el riesgo de desborde de ríos - FmBolivia</t>
+          <t>Oruro evalúa suspender clases presenciales por más de 200 casos de Coxsackie - Visión 360</t>
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPZm85aHphekQ4U3BZZkp1ZkF6ZVdSUHgtZmltS1FxUUgza1AwcndWWDJZOWctT0RiVmVabmg5SG42NnJWMlJMMnBlYTlYaVdSb09sR0dnVDdpT29faTdiaDUtZElJdlQ3eTdjR2VsWjlta1FOS1U2Vm1vV3JwWkpvbEw1ZUR3akgwQTZnQnVENjJtVkQtVUpKVEJTeWNJSE1CaEFKa2VqMmZXbWk3ekR4ZWpmZ1Z3elFQaWNaNFJuMXA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0c9IBywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0cw?oc=5</t>
         </is>
       </c>
       <c r="L36" t="n">
@@ -6263,14 +6353,14 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>-16.169</v>
+        <v>-17.97</v>
       </c>
       <c r="O36" t="n">
-        <v>-68.09</v>
+        <v>-67.11</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>La Paz, La Paz</t>
+          <t>Oruro, Oruro</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -6280,19 +6370,19 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Oruro</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>Nuestra Señora de La Paz</t>
+          <t>Oruro</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>noticia:1570kkf</t>
+          <t>noticia:1xqv9m7</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -6302,78 +6392,62 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-10-23 15:28</t>
+          <t>2026-10-23 18:09</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1792783705000</v>
+        <v>1792793370000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>El Diario del centro del país</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>¿Se suspenden las clases en Oruro? Más de 200 casos de Coxsackie activan evaluaciones - Red Uno</t>
+          <t>Tres heridos en tremendo choque cerca de Oncativo - El Diario del centro del país</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNMFdHaVpKRmMyOENDYm16UXJPenVSQnpmTE94bDc4UFhqakluMUdvZjAwamUxT3BVWUpJQm8xVHBWengxQmhWM1hjU3d2YXFrLXpVU2VrZDJiMXZLMlQ5bGxGOHFETFhYM0s2RjlUTlhkd0g2eXQweDFHaTlKNGNMUlJfOWg2a0JjTklXUWZKc1BmUXZuZFZ2MF9fV2lEYUY4LXNiNmk3cF9FNjVtTl9GWFotT2ltS0xXTnM1dENvSU9kbFRMalFrYVdXOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZERhbTJMQUJVb3hmZFlSZmRGZkdBLWdFTGJVQzdqZkE4aGhhWmdQZ2JDRW1ndkJLWU90VTZ6Ti1JOUZzcFZfcE1zbkRHU1B3YTF4UkVzdllFa1p3SUlObURGamF0Vm9kc3dPLTZVWFJ4NWZZQmlySElPNHhZTnRGNGNZUWw2ZlI1eVBEQkNGNEhLWTNiLWJLUS0xYjA0UWRhc0d6bVN4aVVLSVdsQWlpMUZYdWw?oc=5</t>
         </is>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>-17.97</v>
-      </c>
-      <c r="O37" t="n">
-        <v>-67.11</v>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Oruro, Oruro</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>Oruro</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>Oruro</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>noticia:1nzu2o8</t>
+          <t>noticia:1wuregl</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6383,15 +6457,15 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-10-23 15:20</t>
+          <t>2026-10-23 15:39</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1792783236000</v>
+        <v>1792784340000</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>FmBolivia</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -6400,22 +6474,22 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Alerta naranja por posibles desbordes en tres departamentos (15:20) - El Diario - Bolivia</t>
+          <t>Intensas lluvias inundan La Paz y activan alertas por el riesgo de desborde de ríos - FmBolivia</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPTnBESV9OODZhNjY3T2M2X2NZcmk4clI0eFZsd3VLMVRwaUlSdF9wanZyVGxDNUlNTm5wbGpLN1lvX09mNGxFVkpIZDNGdi1pNDdfSGlESThfeVloQzJsNUMyNUpWUDhzTVJiYWJpNkQ1RHliRWljZlp3SlhtZ2FhU0pvV0syUmZIejJZWHlRdTBOTG4zaTc5cEsycW9IcEx2SkQtN01Gendlb1VR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPZm85aHphekQ4U3BZZkp1ZkF6ZVdSUHgtZmltS1FxUUgza1AwcndWWDJZOWctT0RiVmVabmg5SG42NnJWMlJMMnBlYTlYaVdSb09sR0dnVDdpT29faTdiaDUtZElJdlQ3eTdjR2VsWjlta1FOS1U2Vm1vV3JwWkpvbEw1ZUR3akgwQTZnQnVENjJtVkQtVUpKVEJTeWNJSE1CaEFKa2VqMmZXbWk3ekR4ZWpmZ1Z3elFQaWNaNFJuMXA?oc=5</t>
         </is>
       </c>
       <c r="L38" t="n">
@@ -6424,21 +6498,37 @@
       <c r="M38" t="n">
         <v>0</v>
       </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
+      <c r="N38" t="n">
+        <v>-16.169</v>
+      </c>
+      <c r="O38" t="n">
+        <v>-68.09</v>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>La Paz, La Paz</t>
+        </is>
+      </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>La Paz</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Nuestra Señora de La Paz</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>noticia:1itd1r7</t>
+          <t>noticia:1570kkf</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6448,20 +6538,20 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-10-23 15:01</t>
+          <t>2026-10-23 15:28</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1792782098000</v>
+        <v>1792783705000</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>eju.tv</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6474,13 +6564,13 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Intensa lluvia y granizada en La Paz inundan vías y elevan el nivel de los ríos - eju.tv</t>
+          <t>¿Se suspenden las clases en Oruro? Más de 200 casos de Coxsackie activan evaluaciones - Red Uno</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNWU9QWElKQXEyN3UxVm4xbzJzbEJ1TU1NTHZlRUp6YndmeU9GQnJKcTluVEJ2ZHQ5cGp3aWhlMUd5ektWQlBpUVNmZnZuRnJwMXlydzAzX0FBVnY5UDMzQTBkWVRNRUNJSlRvX3MyQVhMcEhIMW9WSUpXckVSd0RJWk1KMFBKWmJNU3diQVlEN1Y5aVV6eVBaZXpOMnFIWWxaMlRlY0ZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNMFdHaVpKRmMyOENDYm16UXJPenVSQnpmTE94bDc4UFhqakluMUdvZjAwamUxT3BVWUpJQm8xVHBWengxQmhWM1hjU3d2YXFrLXpVU2VrZDJiMXZLMlQ5bGxGOHFETFhYM0s2RjlUTlhkd0g2eXQweDFHaTlKNGNMUlJfOWg2a0JjTklXUWZKc1BmUXZuZFZ2MF9fV2lEYUY4LXNiNmk3cF9FNjVtTl9GWFotT2ltS0xXTnM1dENvSU9kbFRMalFrYVdXOA?oc=5</t>
         </is>
       </c>
       <c r="L39" t="n">
@@ -6490,14 +6580,14 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>-16.169</v>
+        <v>-17.97</v>
       </c>
       <c r="O39" t="n">
-        <v>-68.09</v>
+        <v>-67.11</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>La Paz, La Paz</t>
+          <t>Oruro, Oruro</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -6507,19 +6597,19 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Oruro</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>Nuestra Señora de La Paz</t>
+          <t>Oruro</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>noticia:1l4xxfk</t>
+          <t>noticia:1nzu2o8</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6529,11 +6619,11 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-10-23 14:51</t>
+          <t>2026-10-23 15:20</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1792781480000</v>
+        <v>1792783236000</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -6542,26 +6632,26 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>hidrológica</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
+          <t>Alerta naranja por posibles desbordes en tres departamentos (15:20) - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQS2FPaHd3UnFBRjRoa0lKUm1MNUQ5S00zN1RJZE5fWlVUQnhiY0lLcFRkY2JZak1mZ0c2WEVMVUNJVUJTMGFLNHg4S2ZKNTRqLXJHM09ET19hX1pZeTQwUkdEc2huTHVpcno2QTRZbnhralVRWXozcWc1a2pHUEpBeTV1cWgzTWRwaDEweURKeVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPTnBESV9OODZhNjY3T2M2X2NZcmk4clI0eFZsd3VLMVRwaUlSdF9wanZyVGxDNUlNTm5wbGpLN1lvX09mNGxFVkpIZDNGdi1pNDdfSGlESThfeVloQzJsNUMyNUpWUDhzTVJiYWJpNkQ1RHliRWljZlp3SlhtZ2FhU0pvV0syUmZIejJZWHlRdTBOTG4zaTc5cEsycW9IcEx2SkQtN01Gendlb1VR?oc=5</t>
         </is>
       </c>
       <c r="L40" t="n">
@@ -6570,37 +6660,21 @@
       <c r="M40" t="n">
         <v>0</v>
       </c>
-      <c r="N40" t="n">
-        <v>-17.97</v>
-      </c>
-      <c r="O40" t="n">
-        <v>-67.11</v>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Oruro, Oruro</t>
-        </is>
-      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>Oruro</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>Oruro</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>noticia:51709n</t>
+          <t>noticia:1itd1r7</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6610,11 +6684,11 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-10-23 13:38</t>
+          <t>2026-10-23 15:01</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1792777139000</v>
+        <v>1792782098000</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -6623,43 +6697,43 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - eju.tv</t>
+          <t>Intensa lluvia y granizada en La Paz inundan vías y elevan el nivel de los ríos - eju.tv</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPcjZTSmprRGVoNlRqQmdBTE5VM3pRQ1ZFakFUbzVyMUhiaDVkT0liaG9UNEZXekV6bWsycUk4X1JCSEY5RjhNVlZaTk9ULUFuZkY3NnZuWmZ1a19leUhFdlIyQV9kLWxlSkxfeXFhcFRTZjZ2YkpQQlJ1dkNLMDBjaGZ4SkhyQ0RfcnhKSEg5WURCQVQwbENYTHEzUzJSaUEzMGo2bWdyS3lsM016LXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNWU9QWElKQXEyN3UxVm4xbzJzbEJ1TU1NTHZlRUp6YndmeU9GQnJKcTluVEJ2ZHQ5cGp3aWhlMUd5ektWQlBpUVNmZnZuRnJwMXlydzAzX0FBVnY5UDMzQTBkWVRNRUNJSlRvX3MyQVhMcEhIMW9WSUpXckVSd0RJWk1KMFBKWmJNU3diQVlEN1Y5aVV6eVBaZXpOMnFIWWxaMlRlY0ZB?oc=5</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>-17.764</v>
+        <v>-16.169</v>
       </c>
       <c r="O41" t="n">
-        <v>-62.903</v>
+        <v>-68.09</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Cotoca, Santa Cruz</t>
+          <t>La Paz, La Paz</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -6669,19 +6743,19 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>Cotoca</t>
+          <t>Nuestra Señora de La Paz</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>noticia:11rddql</t>
+          <t>noticia:1l4xxfk</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6691,11 +6765,11 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-10-23 13:22</t>
+          <t>2026-10-23 14:51</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1792776139000</v>
+        <v>1792781480000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -6717,13 +6791,13 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Intensifican acciones preventivas contra el dengue en Caranavi - El Diario - Bolivia</t>
+          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOMjhSeDJBek5iaFhDcnFzX1lKelgwZmUwLTJnbEhMdDRMelUxNks5Ti1pRHh3dDhTcC1YZEdqM3FJOGdqVHRvcXVhRlpCQzVDTEZMUFBkV1NrYVQ2LXRqTTBhcGRQc21CQ0VabzZaNExXb1BjTzJ2Uk5BcFF0VG5XOFNRa3lqUWlJSnRFUUVXYnNpbXB0LVVmSXVWSzJxcmVpdVVxUC1KOUhTQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQS2FPaHd3UnFBRjRoa0lKUm1MNUQ5S00zN1RJZE5fWlVUQnhiY0lLcFRkY2JZak1mZ0c2WEVMVUNJVUJTMGFLNHg4S2ZKNTRqLXJHM09ET19hX1pZeTQwUkdEc2huTHVpcno2QTRZbnhralVRWXozcWc1a2pHUEpBeTV1cWgzTWRwaDEweURKeVE?oc=5</t>
         </is>
       </c>
       <c r="L42" t="n">
@@ -6733,14 +6807,14 @@
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>-15.813</v>
+        <v>-17.97</v>
       </c>
       <c r="O42" t="n">
-        <v>-67.46299999999999</v>
+        <v>-67.11</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Caranavi, La Paz</t>
+          <t>Oruro, Oruro</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -6750,19 +6824,19 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Oruro</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>Caranavi</t>
+          <t>Oruro</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>noticia:fcm3nx</t>
+          <t>noticia:51709n</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6772,15 +6846,15 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-10-23 12:58</t>
+          <t>2026-10-23 13:38</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1792774699000</v>
+        <v>1792777139000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>eju.tv</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -6798,36 +6872,52 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>[VIDEO] Así fue el accidente de moto que dejó un adolescente fallecido y un hombre gravemente herido - Red Uno</t>
+          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - eju.tv</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOSmJMazhUemNfRHpWcDBoTVFZMUpwdlVKVUtvUXZNTGRRRHlwLW5KNmNhcmFnd1czbi1yalhFMnpSS1dmUE9jVzNlOS1kMWZtRzBHZ2EtcDRDdU5Gc2JUQVIwM2xPa2lZVmswRi1SUFVPcm8xcHlGN3F2UThTSDdKMDNyYnJmVkcxazNLLVBLOWFYM09FVUpmVnN5RVhpSVo2V1VCVmFwQ1gzTmRUWVp2aXMwcmxHRS1GV2p3NTBtR2RzM2wwVHUzaGJkRXJYbHdvaDlhWm5YMTk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPcjZTSmprRGVoNlRqQmdBTE5VM3pRQ1ZFakFUbzVyMUhiaDVkT0liaG9UNEZXekV6bWsycUk4X1JCSEY5RjhNVlZaTk9ULUFuZkY3NnZuWmZ1a19leUhFdlIyQV9kLWxlSkxfeXFhcFRTZjZ2YkpQQlJ1dkNLMDBjaGZ4SkhyQ0RfcnhKSEg5WURCQVQwbENYTHEzUzJSaUEzMGo2bWdyS3lsM016LXc?oc=5</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" t="n">
         <v>1</v>
       </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
+      <c r="N43" t="n">
+        <v>-17.764</v>
+      </c>
+      <c r="O43" t="n">
+        <v>-62.903</v>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Cotoca, Santa Cruz</t>
+        </is>
+      </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Cotoca</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>noticia:1cjx1qd</t>
+          <t>noticia:11rddql</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6837,20 +6927,20 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-10-23 12:39</t>
+          <t>2026-10-23 13:22</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1792773575000</v>
+        <v>1792776139000</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6863,13 +6953,13 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Más de 60 municipios en La Paz sufren falta de lluvias - La Patria Bolivia</t>
+          <t>Intensifican acciones preventivas contra el dengue en Caranavi - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE52Qi03Z1J6OS1CR2liRVZ0VlhCcmVQWFV6RUdGNXdrbzZRNXFjTWRaRnc1b3VoV0xaY3RIdncxNlNnYkxyUXo5MTlJWmMwWDNSMDE4ZHI2VkpWajFPaUF2SmRVYkk2eDZYQ1RfUU9ieENrZG9UVVFiaXZSeGI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOMjhSeDJBek5iaFhDcnFzX1lKelgwZmUwLTJnbEhMdDRMelUxNks5Ti1pRHh3dDhTcC1YZEdqM3FJOGdqVHRvcXVhRlpCQzVDTEZMUFBkV1NrYVQ2LXRqTTBhcGRQc21CQ0VabzZaNExXb1BjTzJ2Uk5BcFF0VG5XOFNRa3lqUWlJSnRFUUVXYnNpbXB0LVVmSXVWSzJxcmVpdVVxUC1KOUhTQQ?oc=5</t>
         </is>
       </c>
       <c r="L44" t="n">
@@ -6879,14 +6969,14 @@
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>-16.169</v>
+        <v>-15.813</v>
       </c>
       <c r="O44" t="n">
-        <v>-68.09</v>
+        <v>-67.46299999999999</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>La Paz, La Paz</t>
+          <t>Caranavi, La Paz</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -6901,14 +6991,14 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>Nuestra Señora de La Paz</t>
+          <t>Caranavi</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>noticia:11y8tre</t>
+          <t>noticia:fcm3nx</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6918,11 +7008,11 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-10-23 11:43</t>
+          <t>2026-10-23 12:58</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1792770197000</v>
+        <v>1792774699000</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -6944,70 +7034,54 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - Red Uno</t>
+          <t>[VIDEO] Así fue el accidente de moto que dejó un adolescente fallecido y un hombre gravemente herido - Red Uno</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOVGY3YVRLWWxYM0IycjF4dlNUeUhqZG90Yng4aWhmN3A5ai02WENWYnF4bWpoZHFKMGc1X0JPRHdRRVZfSlA4UmZFa2kxYkNIS3ZtQ1NvNlNCME51eVZTRkRKSUQ5MmRoaWl5Tkt5NHpPUEFwemN2YTV1djFwdHlqQnFqRHNPenhYcTlsanJPcXhpOVV1NmFBUXZyazQ2MkUzM0dSZy02ZllxTGtjcl9ldzdHSktTRlVaalZJc1pubUNQMWFTbzVEOUJ1UmhCdEJt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOSmJMazhUemNfRHpWcDBoTVFZMUpwdlVKVUtvUXZNTGRRRHlwLW5KNmNhcmFnd1czbi1yalhFMnpSS1dmUE9jVzNlOS1kMWZtRzBHZ2EtcDRDdU5Gc2JUQVIwM2xPa2lZVmswRi1SUFVPcm8xcHlGN3F2UThTSDdKMDNyYnJmVkcxazNLLVBLOWFYM09FVUpmVnN5RVhpSVo2V1VCVmFwQ1gzTmRUWVp2aXMwcmxHRS1GV2p3NTBtR2RzM2wwVHUzaGJkRXJYbHdvaDlhWm5YMTk?oc=5</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
         <v>1</v>
       </c>
-      <c r="N45" t="n">
-        <v>-17.764</v>
-      </c>
-      <c r="O45" t="n">
-        <v>-62.903</v>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Cotoca, Santa Cruz</t>
-        </is>
-      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>Santa Cruz</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>Cotoca</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>clima:Sucre:2026-10-23:viento:1</t>
+          <t>noticia:1cjx1qd</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-10-23 06:55</t>
+          <t>2026-10-23 12:39</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1792752927735</v>
+        <v>1792773575000</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>La Patria Bolivia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -7016,26 +7090,22 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Sucre 2026-10-23: 66.2 km/h de ráfagas pronosticadas</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
-        </is>
-      </c>
+          <t>Más de 60 municipios en La Paz sufren falta de lluvias - La Patria Bolivia</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE52Qi03Z1J6OS1CR2liRVZ0VlhCcmVQWFV6RUdGNXdrbzZRNXFjTWRaRnc1b3VoV0xaY3RIdncxNlNnYkxyUXo5MTlJWmMwWDNSMDE4ZHI2VkpWajFPaUF2SmRVYkk2eDZYQ1RfUU9ieENrZG9UVVFiaXZSeGI?oc=5</t>
         </is>
       </c>
       <c r="L46" t="n">
@@ -7045,144 +7115,140 @@
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>-19.03</v>
+        <v>-16.169</v>
       </c>
       <c r="O46" t="n">
-        <v>-65.26000000000001</v>
+        <v>-68.09</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>La Paz, La Paz</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>capital (pronóstico puntual)</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>Chuquisaca</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Nuestra Señora de La Paz</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-24:viento:2</t>
+          <t>noticia:11y8tre</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-10-23 06:55</t>
+          <t>2026-10-23 11:43</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1792752927734</v>
+        <v>1792770197000</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-24: 85 km/h de ráfagas pronosticadas</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
-        </is>
-      </c>
+          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - Red Uno</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOVGY3YVRLWWxYM0IycjF4dlNUeUhqZG90Yng4aWhmN3A5ai02WENWYnF4bWpoZHFKMGc1X0JPRHdRRVZfSlA4UmZFa2kxYkNIS3ZtQ1NvNlNCME51eVZTRkRKSUQ5MmRoaWl5Tkt5NHpPUEFwemN2YTV1djFwdHlqQnFqRHNPenhYcTlsanJPcXhpOVV1NmFBUXZyazQ2MkUzM0dSZy02ZllxTGtjcl9ldzdHSktTRlVaalZJc1pubUNQMWFTbzVEOUJ1UmhCdEJt?oc=5</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N47" t="n">
-        <v>-17.78</v>
+        <v>-17.764</v>
       </c>
       <c r="O47" t="n">
-        <v>-63.18</v>
+        <v>-62.903</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
+          <t>Cotoca, Santa Cruz</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
           <t>Santa Cruz</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>capital (pronóstico puntual)</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>Santa Cruz</t>
-        </is>
-      </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Cotoca</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>usgs:us6000u49c</t>
+          <t>clima:Sucre:2026-10-23:viento:1</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>usgs</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-10-22 22:45</t>
+          <t>2026-10-23 06:55</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1792723541183</v>
+        <v>1792752927735</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>USGS</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>geológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7195,17 +7261,17 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Sismo M 4.5 - 58 km SW of Atocha, Bolivia</t>
+          <t>Sucre 2026-10-23: 66.2 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Profundidad 236 km</t>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://earthquake.usgs.gov/earthquakes/eventpage/us6000u49c</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L48" t="n">
@@ -7215,36 +7281,36 @@
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>-21.3469</v>
+        <v>-19.03</v>
       </c>
       <c r="O48" t="n">
-        <v>-66.5795</v>
+        <v>-65.26000000000001</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>58 km SW of Atocha, Bolivia</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>coordenada de la fuente</t>
+          <t>capital (pronóstico puntual)</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Chuquisaca</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>San Pablo</t>
+          <t>Sucre</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-22:viento:1</t>
+          <t>clima:Santa Cruz:2026-10-24:viento:2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -7254,11 +7320,11 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-10-22 21:55</t>
+          <t>2026-10-23 06:55</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1792720528712</v>
+        <v>1792752927734</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -7271,16 +7337,16 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-22: 67.7 km/h de ráfagas pronosticadas</t>
+          <t>Santa Cruz 2026-10-24: 85 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -7329,53 +7395,53 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-23:viento:2</t>
+          <t>usgs:us6000u49c</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>usgs</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-10-22 21:55</t>
+          <t>2026-10-22 22:45</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1792720528712</v>
+        <v>1792723541183</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>USGS</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>geológica</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-23: 83.9 km/h de ráfagas pronosticadas</t>
+          <t>Sismo M 4.5 - 58 km SW of Atocha, Bolivia</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+          <t>Profundidad 236 km</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://earthquake.usgs.gov/earthquakes/eventpage/us6000u49c</t>
         </is>
       </c>
       <c r="L50" t="n">
@@ -7385,78 +7451,82 @@
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>-17.78</v>
+        <v>-21.3469</v>
       </c>
       <c r="O50" t="n">
-        <v>-63.18</v>
+        <v>-66.5795</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>58 km SW of Atocha, Bolivia</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>capital (pronóstico puntual)</t>
+          <t>coordenada de la fuente</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>San Pablo</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>noticia:1hhvre7</t>
+          <t>clima:Santa Cruz:2026-10-22:viento:1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-10-22 19:36</t>
+          <t>2026-10-22 21:55</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1792712202000</v>
+        <v>1792720528712</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>El Mundo Bolivia</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Virgen de Cotoca: Controlan incendio en depósito de materiales plásticos - El Mundo Bolivia</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
+          <t>Santa Cruz 2026-10-22: 67.7 km/h de ráfagas pronosticadas</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcDF6VE5FNzRaWGRuUzFKeXhnZ21DZTRaaEtrVEJEa1Z3ejg2VG1ONG1ENmlDWlkyVjlkQkJwS2F1XzBGMFQwSHd4OEwxTW1PbHdGcUh1ckV6SGpDd2hiN0dkeUVTcnFXT3RjOU1kLXZtVVdZY2hkZS1pcVpVUFhnRktqcHY5UnBrY0xUMDRETjl6N0pXT3A5amxhMA?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L51" t="n">
@@ -7466,19 +7536,19 @@
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>-17.764</v>
+        <v>-17.78</v>
       </c>
       <c r="O51" t="n">
-        <v>-62.903</v>
+        <v>-63.18</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Cotoca, Santa Cruz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
+          <t>capital (pronóstico puntual)</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -7488,56 +7558,60 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>Cotoca</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>noticia:bksnde</t>
+          <t>clima:Santa Cruz:2026-10-23:viento:2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-10-22 17:01</t>
+          <t>2026-10-22 21:55</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1792702880000</v>
+        <v>1792720528712</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>eju.tv</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Reportan un incendio cerca de la carretera a Cotoca - eju.tv</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
+          <t>Santa Cruz 2026-10-23: 83.9 km/h de ráfagas pronosticadas</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPNGtpbnBfRnRBalVudnBlZHdVQ0ZSaUplZmtvTGE0aTQzdkxWS3d4My1EZEJ1UE9FNFQ3RmpyZGVsbS1qNEM1QUVFRFAxM2pYT1VqQzRuVjRtZnVNUGlKODNMc0F1a3l6TUpuQmtlUWNlVTVEWWU5ZGZtQm5LWUp3Sg?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L52" t="n">
@@ -7547,19 +7621,19 @@
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>-17.764</v>
+        <v>-17.78</v>
       </c>
       <c r="O52" t="n">
-        <v>-62.903</v>
+        <v>-63.18</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Cotoca, Santa Cruz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
+          <t>capital (pronóstico puntual)</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -7569,14 +7643,14 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>Cotoca</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>noticia:17hz69v</t>
+          <t>noticia:1hhvre7</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -7586,15 +7660,15 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-10-22 13:05</t>
+          <t>2026-10-22 19:36</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1792688709000</v>
+        <v>1792712202000</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>La Razón Digital Bolivia</t>
+          <t>El Mundo Bolivia</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -7603,45 +7677,61 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Accidente en El Sillar deja al menos 29 heridos - La Razón Digital Bolivia</t>
+          <t>Virgen de Cotoca: Controlan incendio en depósito de materiales plásticos - El Mundo Bolivia</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPaXhTdm45YWZnWVFxVzJnb1ZwbUN4SmUtLVdJN0VJdFZBamRyQmFxN0RZelBfTklaSTVyOUZ3ajQ5MFB2TEN4Ukd6TE5ORFY5SEROVk1CZ25sRWJ1QnRBdTVfTktlby1NWXhaVWI5YnRvaDZWbHVjdDVoeFp5Tk5veFk5a19MSWJqcEJVV0dzV3k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcDF6VE5FNzRaWGRuUzFKeXhnZ21DZTRaaEtrVEJEa1Z3ejg2VG1ONG1ENmlDWlkyVjlkQkJwS2F1XzBGMFQwSHd4OEwxTW1PbHdGcUh1ckV6SGpDd2hiN0dkeUVTcnFXT3RjOU1kLXZtVVdZY2hkZS1pcVpVUFhnRktqcHY5UnBrY0xUMDRETjl6N0pXT3A5amxhMA?oc=5</t>
         </is>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>29</v>
-      </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>-17.764</v>
+      </c>
+      <c r="O53" t="n">
+        <v>-62.903</v>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Cotoca, Santa Cruz</t>
+        </is>
+      </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Cotoca</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>noticia:1f1qb0</t>
+          <t>noticia:bksnde</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -7651,15 +7741,15 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-10-22 12:09</t>
+          <t>2026-10-22 17:01</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1792685373000</v>
+        <v>1792702880000</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>eju.tv</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -7677,13 +7767,13 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Accidente en el tramo Locotal–Villa Tunari: la vía está transitable con precaución - Red Uno</t>
+          <t>Reportan un incendio cerca de la carretera a Cotoca - eju.tv</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTFozcEEwNXBqV19sS2VibXh0MGt0QlhsX1djSTFGQW5zNlFLRHZpNVVnZ1JmWDQ4LVRHX2Rmb3B5UU9qV0FZQmJCaUZYdmwyNG1NenJ4Qzlzd0NJTGs1SjMxdFRtRFBzSUkybGJfZFFaNFZBc21FSUJYSFVkQkVkSEhQaGw0UFVzeXctZHo3cjNsYm5weXJlOU1wcmFncnNhMC1BQUpvNWlDX1NxZXU4b09kVFFWR2tSVEk2UTdXXzB3TjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPNGtpbnBfRnRBalVudnBlZHdVQ0ZSaUplZmtvTGE0aTQzdkxWS3d4My1EZEJ1UE9FNFQ3RmpyZGVsbS1qNEM1QUVFRFAxM2pYT1VqQzRuVjRtZnVNUGlKODNMc0F1a3l6TUpuQmtlUWNlVTVEWWU5ZGZtQm5LWUp3Sg?oc=5</t>
         </is>
       </c>
       <c r="L54" t="n">
@@ -7693,14 +7783,14 @@
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>-16.556</v>
+        <v>-17.764</v>
       </c>
       <c r="O54" t="n">
-        <v>-65.569</v>
+        <v>-62.903</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Villa Tunari, Cochabamba</t>
+          <t>Cotoca, Santa Cruz</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -7710,19 +7800,19 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>Villa Tunari</t>
+          <t>Cotoca</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>noticia:wi18tm</t>
+          <t>noticia:17hz69v</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -7732,46 +7822,46 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-10-22 11:53</t>
+          <t>2026-10-22 13:05</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1792684426000</v>
+        <v>1792688709000</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>La Razón Digital Bolivia</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>tecnológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Accidente en El Sillar deja heridos y derrame de combustible: esto es lo último que se sabe - Red Uno</t>
+          <t>Accidente en El Sillar deja al menos 29 heridos - La Razón Digital Bolivia</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPZHNBTEdaQm5Wby1lTF9mWlQ2aGg0MVc4S0MwVWJ3dUJ5WWU5X3IwYWhKRjk5VWtYWEJHRDF4QldVc29laVNPSTJNWFBDSkNFQlFSYTJUXzNMNF9hckFBN1I2T2xoQUtYQ2V6MDNTZHhHVk9qeTBCdHRpM2ZLd0pyOFRweUUxX19STzRHTHg5VUY5d1lhS0tDeXpCdklqcTZGT1J4R0xnSDhoak1EZ2dtNUhSTUV6b1o0U0VSdWY5X0E3U05Tc1dYVEN2WFZUeFhPMTBJTmowNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPaXhTdm45YWZnWVFxVzJnb1ZwbUN4SmUtLVdJN0VJdFZBamRyQmFxN0RZelBfTklaSTVyOUZ3ajQ5MFB2TEN4Ukd6TE5ORFY5SEROVk1CZ25sRWJ1QnRBdTVfTktlby1NWXhaVWI5YnRvaDZWbHVjdDVoeFp5Tk5veFk5a19MSWJqcEJVV0dzV3k?oc=5</t>
         </is>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
@@ -7787,7 +7877,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>noticia:12gfagq</t>
+          <t>noticia:1f1qb0</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7797,15 +7887,15 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-10-22 11:28</t>
+          <t>2026-10-22 12:09</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1792682880000</v>
+        <v>1792685373000</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>FmBolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -7823,13 +7913,13 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Reportan triple colisión entre dos camiones y un bus en la carretera Cochabamba-Santa Cruz - FmBolivia</t>
+          <t>Accidente en el tramo Locotal–Villa Tunari: la vía está transitable con precaución - Red Uno</t>
         </is>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNMTNBaFZNMU9SR25vdVBuNXlZY3g4VkFWYXRiQnNSaUFjemZhUHZWNHg4V2owU2xfNndBak94TnU2cHNUVXdNNWl2eUdHZVNMbVZweTR5M0o0bWdTNUN4QkoxUkI2TDBmVE03M09zRGhJRVFzV0tPZ1NCWEJLUkt1ZGN4UGduOUZMQnJoM0tMYTh0ZlFxaFJNUkJqaWFPazRlMzN3ajhjUEdUYXlZRndpb3RSdTFCX2tCZGJxQ0x4SlBISWJsRVoyN3ZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTFozcEEwNXBqV19sS2VibXh0MGt0QlhsX1djSTFGQW5zNlFLRHZpNVVnZ1JmWDQ4LVRHX2Rmb3B5UU9qV0FZQmJCaUZYdmwyNG1NenJ4Qzlzd0NJTGs1SjMxdFRtRFBzSUkybGJfZFFaNFZBc21FSUJYSFVkQkVkSEhQaGw0UFVzeXctZHo3cjNsYm5weXJlOU1wcmFncnNhMC1BQUpvNWlDX1NxZXU4b09kVFFWR2tSVEk2UTdXXzB3TjA?oc=5</t>
         </is>
       </c>
       <c r="L56" t="n">
@@ -7839,14 +7929,14 @@
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>-17.39</v>
+        <v>-16.556</v>
       </c>
       <c r="O56" t="n">
-        <v>-66.16</v>
+        <v>-65.569</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Cochabamba, Cochabamba</t>
+          <t>Villa Tunari, Cochabamba</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -7861,14 +7951,14 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Villa Tunari</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>noticia:1uq1bxy</t>
+          <t>noticia:wi18tm</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7878,11 +7968,11 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-10-22 10:44</t>
+          <t>2026-10-22 11:53</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1792680273000</v>
+        <v>1792684426000</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -7891,65 +7981,49 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>tecnológica</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Reportan triple colisión en la carretera Cochabamba–Santa Cruz - Red Uno</t>
+          <t>Accidente en El Sillar deja heridos y derrame de combustible: esto es lo último que se sabe - Red Uno</t>
         </is>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNNUROMzd1UDJRWVZZQ011cFd2c1FSdER1ZzdleU04cXpwYk5HaUZrLXoyU2NzdFk1dnNRUndhUWt0cG9DX09rSjlLcDItU0tzcmQtS3E4dDQ4ZF9HdGJLdk13ek9BNHJUWVlCcklrM25rZ01RbXhLalRBT1FGdDNReHdlTFZkNkJ5ZFd3N3NZVFVmOFUxbEhHN0RsaUxiSVZsM0lXVEFYSHVRQlhsOEtJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPZHNBTEdaQm5Wby1lTF9mWlQ2aGg0MVc4S0MwVWJ3dUJ5WWU5X3IwYWhKRjk5VWtYWEJHRDF4QldVc29laVNPSTJNWFBDSkNFQlFSYTJUXzNMNF9hckFBN1I2T2xoQUtYQ2V6MDNTZHhHVk9qeTBCdHRpM2ZLd0pyOFRweUUxX19STzRHTHg5VUY5d1lhS0tDeXpCdklqcTZGT1J4R0xnSDhoak1EZ2dtNUhSTUV6b1o0U0VSdWY5X0E3U05Tc1dYVEN2WFZUeFhPMTBJTmowNA?oc=5</t>
         </is>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="n">
-        <v>-17.39</v>
-      </c>
-      <c r="O57" t="n">
-        <v>-66.16</v>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>Cochabamba, Cochabamba</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>noticia:1jl2oid</t>
+          <t>noticia:12gfagq</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -7959,15 +8033,15 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-10-22 07:49</t>
+          <t>2026-10-22 11:28</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1792669785000</v>
+        <v>1792682880000</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>eju.tv</t>
+          <t>FmBolivia</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -7976,39 +8050,39 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - eju.tv</t>
+          <t>Reportan triple colisión entre dos camiones y un bus en la carretera Cochabamba-Santa Cruz - FmBolivia</t>
         </is>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQbTBrUmlla3FvVU1EX1pxcUI3SXYzbUFFMzlnRzhlSDJwMGpWWURxYjIwSkJBRGdCazMzT01hVy1qMFY3RnJLbC1XNXJ4bU55aDJVeXpNUlRsbzQ3T3hiRXJ5SWlhNmw5cDZFanNoWFBtQ01Gd3dscXltWmU5VHBSQlN3c2IwNGxuVE5tQ3lOT1RmNzRiVi1hc0hn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNMTNBaFZNMU9SR25vdVBuNXlZY3g4VkFWYXRiQnNSaUFjemZhUHZWNHg4V2owU2xfNndBak94TnU2cHNUVXdNNWl2eUdHZVNMbVZweTR5M0o0bWdTNUN4QkoxUkI2TDBmVE03M09zRGhJRVFzV0tPZ1NCWEJLUkt1ZGN4UGduOUZMQnJoM0tMYTh0ZlFxaFJNUkJqaWFPazRlMzN3ajhjUEdUYXlZRndpb3RSdTFCX2tCZGJxQ0x4SlBISWJsRVoyN3ZR?oc=5</t>
         </is>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>-17.781</v>
+        <v>-17.39</v>
       </c>
       <c r="O58" t="n">
-        <v>-63.139</v>
+        <v>-66.16</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Santa Cruz, Santa Cruz</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -8018,19 +8092,19 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Cochabamba</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>noticia:yqgeq</t>
+          <t>noticia:1uq1bxy</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -8040,11 +8114,11 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-10-22 07:43</t>
+          <t>2026-10-22 10:44</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1792669426000</v>
+        <v>1792680273000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -8057,39 +8131,39 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - Red Uno</t>
+          <t>Reportan triple colisión en la carretera Cochabamba–Santa Cruz - Red Uno</t>
         </is>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNVEh1bFlCanFuOTJid2EzYS1meG5oekFJcGFaME1fTk9sUnZpd3U0UXFHUFVJSW1jc1hzM2VFOFprT2xNYjBzbmswZmdJV3dremRIS0I4MDNzRjBnbEttWEhfOWZBbmFrRnNHWDFVLVFoM0VkZkxkaW4tMmZlSFJLei1heTFHMU0wSmxQVVRZN0cwaXQzcDBtZkdwTUFma0RXU2dwLXRnLTBkNGN3Vm1fV3hEdlM1dWZ1SEsw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNNUROMzd1UDJRWVZZQ011cFd2c1FSdER1ZzdleU04cXpwYk5HaUZrLXoyU2NzdFk1dnNRUndhUWt0cG9DX09rSjlLcDItU0tzcmQtS3E4dDQ4ZF9HdGJLdk13ek9BNHJUWVlCcklrM25rZ01RbXhLalRBT1FGdDNReHdlTFZkNkJ5ZFd3N3NZVFVmOFUxbEhHN0RsaUxiSVZsM0lXVEFYSHVRQlhsOEtJ?oc=5</t>
         </is>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>-17.781</v>
+        <v>-17.39</v>
       </c>
       <c r="O59" t="n">
-        <v>-63.139</v>
+        <v>-66.16</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Santa Cruz, Santa Cruz</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -8099,19 +8173,19 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Cochabamba</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>noticia:n32ahi</t>
+          <t>noticia:1jl2oid</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -8121,69 +8195,231 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-10-22 05:30</t>
+          <t>2026-10-22 07:49</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1792661402000</v>
+        <v>1792669785000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>FmBolivia</t>
+          <t>eju.tv</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Senamhi anuncia el inicio de la temporada de lluvias en Bolivia y prevé granizadas como la de La Paz - FmBolivia</t>
+          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - eju.tv</t>
         </is>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQbTBrUmlla3FvVU1EX1pxcUI3SXYzbUFFMzlnRzhlSDJwMGpWWURxYjIwSkJBRGdCazMzT01hVy1qMFY3RnJLbC1XNXJ4bU55aDJVeXpNUlRsbzQ3T3hiRXJ5SWlhNmw5cDZFanNoWFBtQ01Gd3dscXltWmU5VHBSQlN3c2IwNGxuVE5tQ3lOT1RmNzRiVi1hc0hn?oc=5</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1</v>
+      </c>
+      <c r="N60" t="n">
+        <v>-17.781</v>
+      </c>
+      <c r="O60" t="n">
+        <v>-63.139</v>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Santa Cruz, Santa Cruz</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>Santa Cruz de la Sierra</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>noticia:yqgeq</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>noticia</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-10-22 07:43</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>1792669426000</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Red Uno</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>antropogénica</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>amarilla</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - Red Uno</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNVEh1bFlCanFuOTJid2EzYS1meG5oekFJcGFaME1fTk9sUnZpd3U0UXFHUFVJSW1jc1hzM2VFOFprT2xNYjBzbmswZmdJV3dremRIS0I4MDNzRjBnbEttWEhfOWZBbmFrRnNHWDFVLVFoM0VkZkxkaW4tMmZlSFJLei1heTFHMU0wSmxQVVRZN0cwaXQzcDBtZkdwTUFma0RXU2dwLXRnLTBkNGN3Vm1fV3hEdlM1dWZ1SEsw?oc=5</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1</v>
+      </c>
+      <c r="N61" t="n">
+        <v>-17.781</v>
+      </c>
+      <c r="O61" t="n">
+        <v>-63.139</v>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Santa Cruz, Santa Cruz</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Santa Cruz de la Sierra</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>noticia:n32ahi</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>noticia</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-10-22 05:30</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1792661402000</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>FmBolivia</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>meteorológica</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>verde</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Senamhi anuncia el inicio de la temporada de lluvias en Bolivia y prevé granizadas como la de La Paz - FmBolivia</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
           <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQNmVPRnVBMGQzdEI5SUp3Z3ZGVExwTUR6TWNadGQ1QldUS1o2QVFvUl9sVEZKMDVyQVVrS25rU1RSQlJKWXk1YzE0NUhidjhpcmFaSlhZUDZvcE9XcG1KTFNTYmowUU1CSFJNOVR2UHNmMk1iT3N0RVBteHkzZkgyRFROYk1pdkpxVHZya3N2X2FVLVQxbURFVVZlb1NzRjZzTE95TXFVUXFJNkVZakQ2bUhVQzB0SXk3TVhXUTJXa0dycTE1MWVQRFpDX3lDSWFqUGwzU2NtNA?oc=5</t>
         </is>
       </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="n">
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
         <v>-16.169</v>
       </c>
-      <c r="O60" t="n">
+      <c r="O62" t="n">
         <v>-68.09</v>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>La Paz, La Paz</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>nombre de municipio en el titular</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="R62" t="inlineStr">
         <is>
           <t>La Paz</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>Nuestra Señora de La Paz</t>
         </is>
@@ -8753,7 +8989,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-10-25 12:29</t>
+          <t>2026-10-25 12:47</t>
         </is>
       </c>
     </row>
@@ -8776,7 +9012,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4">
@@ -8786,7 +9022,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5">
@@ -8833,7 +9069,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sala de Situación Bolivia – CCES. Base de eventos de amenazas (datos preliminares de fuentes abiertas). Consulta: 2026-10-25 12:29.</t>
+          <t>Sala de Situación Bolivia – CCES. Base de eventos de amenazas (datos preliminares de fuentes abiertas). Consulta: 2026-10-25 12:47.</t>
         </is>
       </c>
     </row>

--- a/docs/datos/datos_bolivia.xlsx
+++ b/docs/datos/datos_bolivia.xlsx
@@ -3720,8 +3720,10 @@
           <t>2026-10-25 12:44</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>1792946640000</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1792946640000</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3733,8 +3735,10 @@
           <t>antropogénica</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>1</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -3752,17 +3756,25 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-15.813</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-67.46299999999999</v>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>-15.813</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>-67.463</t>
+        </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -8989,7 +9001,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-10-25 12:47</t>
+          <t>2026-10-25 13:00</t>
         </is>
       </c>
     </row>
@@ -9069,7 +9081,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sala de Situación Bolivia – CCES. Base de eventos de amenazas (datos preliminares de fuentes abiertas). Consulta: 2026-10-25 12:47.</t>
+          <t>Sala de Situación Bolivia – CCES. Base de eventos de amenazas (datos preliminares de fuentes abiertas). Consulta: 2026-10-25 13:00.</t>
         </is>
       </c>
     </row>

--- a/docs/datos/datos_bolivia.xlsx
+++ b/docs/datos/datos_bolivia.xlsx
@@ -514,20 +514,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>manual:1c1299f3</t>
+          <t>noticia:4blj1l</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-25 12:44</t>
+          <t>2026-10-25 12:59</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1792946640000</v>
+        <v>1792947573000</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Vuelco de minibus</t>
+          <t>Santa Cruz: Dos cisternas se incendian tras colisionar - La Patria Bolivia</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -536,18 +536,18 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -555,53 +555,57 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Registro abierto (sin verificar)</t>
+          <t>FmBolivia; La Patria Bolivia; Opinión Bolivia; Red Uno</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>-15.813</v>
+        <v>-17.781</v>
       </c>
       <c r="N2" t="n">
-        <v>-67.46299999999999</v>
+        <v>-63.139</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Caranavi, La Paz</t>
+          <t>Santa Cruz, Santa Cruz</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Caranavi</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
+          <t>Santa Cruz de la Sierra</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQbHdpcUF6dXpjaW1TT1ZmdGJtUUVLMTNMRTVqVkFUdkNsZlRvenVkckFUWmI4NDFmc2ZHd2RVcWRSSE5YRVpOTUlESGw2V3JONXpwS0RISGNZd01SejNuMkY4NzFYYXp4aWo2RE9VMkFYUkVwZ3JRRmM5MWlRSjlBWk16azdkQ3FjdEtkaWc5NERkTzk2SllVOQ?oc=5 | https://news.google.com/rss/articles/CBMixgFBVV95cUxQLXlqSFdvWUVhQUNadnpkdE5lUTZQS0lobThzUTZWbDNJTE94alVhaDBaYU9Fd09SSGt3UlR3Y0dfZlNIcml1ZktnWjctNk1Na3V4S0tINFNkMXM0OHBoV2lCTTBiYXlPUTA3T2ZkeXE2RElYWjhfVHd3Nng1Z0E4alBmOFI5NDFwX09kazZlSWl2OVR2ZVR6MDhvSHFnSmJKbTFXSEFDNFFYcWVDNGtYWEQ0bDhJel9CaEpEZWZ4SWN0TE9Ya0E?oc=5 | https://news.google.com/rss/articles/CBMiugFBVV95cUxNUTdxSzBJVTZnajZQUXhyTVhwMlpvU0tyZGVBYnFwV2kyZWthenNRT1FDRVJFZnk4ZndGTFQ0cnFXZmZ1WHZaMFhUbWo0SWkzcjcxbjJwU3pKUXR4WEVZLVlRNFpxOUVMY2NNNUZsbmJSMk9xZG1sTklEdEtGSXJyUUp5b0R2dVpYcHJLdTRNRlRjcWpNNXg4c0Z4UWwteFc2dDRqVmpnQnFfQXgwN0twTzl4ZWhYdUtYWGfSAboBQVVfeXFMTVE3cUswSVU2Z2o2UFF4ck1YcDJab1NLcmRlQWJxcFdpMmVrYXpzUU9RQ0VSRWZ5OGZ3RkxUNHJxV2ZmdVh2WjBYVG1qNElpM3I3MW4ycFN6SlF0eFhFWS1ZUTRacTlFTGNjTTVGbG5iUjJPcWRtbE5JRHRLRklyclFKeW9EdnVaWHByS3U0TUZUY3FqTTV4OHNGeFFsLXhXNnQ0alZqZ0JxX0F4MDdLcE85eGVoWHVLWFhn?oc=5</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>noticia:oww2zc</t>
+          <t>manual:1c1299f3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-25 12:08</t>
+          <t>2026-10-25 12:44</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1792944531000</v>
+        <v>1792946640000</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cierran la carretera a Camiri: dos cisternas chocan y provocan un voraz incendio - Red Uno</t>
+          <t>Vuelco de minibus</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,18 +614,18 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -629,57 +633,53 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Opinión Bolivia; Red Uno</t>
+          <t>Registro abierto (sin verificar)</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>-20.05</v>
+        <v>-15.813</v>
       </c>
       <c r="N3" t="n">
-        <v>-63.486</v>
+        <v>-67.46299999999999</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Camiri, Santa Cruz</t>
+          <t>Caranavi, La Paz</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Camiri</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQLXlqSFdvWUVhQUNadnpkdE5lUTZQS0lobThzUTZWbDNJTE94alVhaDBaYU9Fd09SSGt3UlR3Y0dfZlNIcml1ZktnWjctNk1Na3V4S0tINFNkMXM0OHBoV2lCTTBiYXlPUTA3T2ZkeXE2RElYWjhfVHd3Nng1Z0E4alBmOFI5NDFwX09kazZlSWl2OVR2ZVR6MDhvSHFnSmJKbTFXSEFDNFFYcWVDNGtYWEQ0bDhJel9CaEpEZWZ4SWN0TE9Ya0E?oc=5 | https://news.google.com/rss/articles/CBMiugFBVV95cUxNUTdxSzBJVTZnajZQUXhyTVhwMlpvU0tyZGVBYnFwV2kyZWthenNRT1FDRVJFZnk4ZndGTFQ0cnFXZmZ1WHZaMFhUbWo0SWkzcjcxbjJwU3pKUXR4WEVZLVlRNFpxOUVMY2NNNUZsbmJSMk9xZG1sTklEdEtGSXJyUUp5b0R2dVpYcHJLdTRNRlRjcWpNNXg4c0Z4UWwteFc2dDRqVmpnQnFfQXgwN0twTzl4ZWhYdUtYWGfSAboBQVVfeXFMTVE3cUswSVU2Z2o2UFF4ck1YcDJab1NLcmRlQWJxcFdpMmVrYXpzUU9RQ0VSRWZ5OGZ3RkxUNHJxV2ZmdVh2WjBYVG1qNElpM3I3MW4ycFN6SlF0eFhFWS1ZUTRacTlFTGNjTTVGbG5iUjJPcWRtbE5JRHRLRklyclFKeW9EdnVaWHByS3U0TUZUY3FqTTV4OHNGeFFsLXhXNnQ0alZqZ0JxX0F4MDdLcE85eGVoWHVLWFhn?oc=5 | https://news.google.com/rss/articles/CBMitgFBVV95cUxPTTF0OUdVS1c1a0lZWmk3bGxHdDJIalpWZTRyQTY3eWE2a2dWOHlsaldKZXpSLWN5c3BkUWdBRkJuSzhHdWl2ZjgwTFFFYnd0aTAxZ3dJU0hCekNZNm9aTTJSZUNfQjVIM3FrUUJ4NXAwa3paZ3BEek9xTVZNQWdnN01xRHloV1ZXZHV6N0JpUWo3RE9DMlFGdkNnWkloTjVVY3RBR1RSRUJJWFVtby1fMWFMNTdLZw?oc=5</t>
-        </is>
-      </c>
+          <t>Caranavi</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>noticia:1sg8pi0</t>
+          <t>noticia:1uf38hl</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25 09:59</t>
+          <t>2026-10-25 10:59</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1792936752000</v>
+        <v>1792940350000</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bus de agrupación musical sufre accidente rumbo al trópico de Cochabamba | VIDEO - Red Uno</t>
+          <t>¡Cisterna con combustible en llamas! Reportan impresionante incendio en la carretera a Camiri - Red Uno</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -715,54 +715,54 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>-17.39</v>
+        <v>-20.05</v>
       </c>
       <c r="N4" t="n">
-        <v>-66.16</v>
+        <v>-63.486</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Cochabamba, Cochabamba</t>
+          <t>Camiri, Santa Cruz</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Camiri</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOVDVzVTJNM2JuQ25sMThEaVZNOUNRd3FGT3RhVnFrZXZ2NDQ1YlluTVdhbVNUQnA1MGNESHRSWVUzbC1kRVh3OTR0emtlTG91cmRWeFJ5dk5zb3p2WFRyMEJUV3FNRnY1WHhRUU9WLTlJcmNyNXJZZFdoM0JoZjNpa3hjUXhMM0xrUDJab2VadkM5RWZYQ3lWZTVDdzg1akxJT2lxcDVNNzI0NG1hejdfdkUyTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxORUhqeWpKY1FHRWoxaHN0UXFzS3dpeHh6N0NwLUJOZTlZcDVoNHN0VnI0by1qMWtZZEkxVmtUNjdNTFhjaEFQU2IyMlNwZW95WFBzbFJPVVB6TjJtdjNENk1LWVlsMUxUUzBNVzkxRk1HZ3lQU0s2M1lRVlRuaXlkMmJrd3AyTGpIdXItNkhlU3dhTzBRME56Rm1DSlZCYjNxSnNTbTFqNWRoUkdraHhlREhuYldqeFk2N3poWEx2M08?oc=5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>noticia:167wlhz</t>
+          <t>noticia:1sg8pi0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-25 07:53</t>
+          <t>2026-10-25 09:59</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1792929231000</v>
+        <v>1792936752000</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>¡A sacar el paraguas! Santa cruz amanece con lluvia, frío y complicaciones en el tránsito vehicular - Red Uno</t>
+          <t>Bus de agrupación musical sufre accidente rumbo al trópico de Cochabamba | VIDEO - Red Uno</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -793,62 +793,62 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>-17.781</v>
+        <v>-17.39</v>
       </c>
       <c r="N5" t="n">
-        <v>-63.139</v>
+        <v>-66.16</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Santa Cruz, Santa Cruz</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOY1ZpYktLR3pUQXotUndVR3puUzVHbW1YTzNyUmJvUHB4Q2JmelRvOEdaRldOUm1xLVJnbGR5VWcxTjNEM3ZUYktCUWtVM0hKSjFuRGdpX0JxN0M5MVZBSG1aVURyVWktdmxwbUtRT19ydU5LdzNTZ2Zpb2ozdHlMUUdTVlAyVk4xODBnV0hyTXdVVndyNzV3VC1KMzFnV3lpcFFXSk9MdDZOTWlWakNwT1FnNDh6QVdjazVYZDVVMkdaLU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOVDVzVTJNM2JuQ25sMThEaVZNOUNRd3FGT3RhVnFrZXZ2NDQ1YlluTVdhbVNUQnA1MGNESHRSWVUzbC1kRVh3OTR0emtlTG91cmRWeFJ5dk5zb3p2WFRyMEJUV3FNRnY1WHhRUU9WLTlJcmNyNXJZZFdoM0JoZjNpa3hjUXhMM0xrUDJab2VadkM5RWZYQ3lWZTVDdzg1akxJT2lxcDVNNzI0NG1hejdfdkUyTQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>noticia:bzr7eh</t>
+          <t>noticia:167wlhz</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-25 07:09</t>
+          <t>2026-10-25 07:53</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1792926572000</v>
+        <v>1792929231000</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Alerta naranja por riesgo de desbordes de ríos - El Diario - Bolivia</t>
+          <t>¡A sacar el paraguas! Santa cruz amanece con lluvia, frío y complicaciones en el tránsito vehicular - Red Uno</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>hidrológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -863,74 +863,74 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia; El Mundo Bolivia; FmBolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>-16.169</v>
+        <v>-17.781</v>
       </c>
       <c r="N6" t="n">
-        <v>-68.09</v>
+        <v>-63.139</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>La Paz, La Paz</t>
+          <t>Santa Cruz, Santa Cruz</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Nuestra Señora de La Paz</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNNGZKSDVaZkowWUFGSEUyTWR3d3dsc04waFBLLWUtcVpiTDYzbmNtYTN1RkFLbjAwN3dxT0xZc3pqc3REUXduZVltQ2Fud1BZLTh1bTNiTEJueVUwV0dERS1iUXZqMHd0UnFrQ3E2SFAzbm5lQ1I4U29MaHJFbWFvdVRTeFY4Wl9rSmc3RkpaQ2xwX0oz?oc=5 | https://news.google.com/rss/articles/CBMipwFBVV95cUxPZW00RkxJSklTelNrS2hqczJDWHlwcENFX2lnSEUyTEFPaDFRQ2JvMUcyd3NfYjg0UE9ORGxHRzB4ZDh3U0hQQ1JSQlhsaUY4N3ByMUUxei1SaUZnNlp6T3hsLVdiMGhKaXhsV1FNSUNQMHlvQ19qdk56SEF0d2RXVFctS0VPT25kNGZCRDdvZ2dxU0VoUUJKU0ZBd0ZycFNEZFh0T3ZjOA?oc=5 | https://news.google.com/rss/articles/CBMiwAFBVV95cUxPZm85aHphekQ4U3BZZkp1ZkF6ZVdSUHgtZmltS1FxUUgza1AwcndWWDJZOWctT0RiVmVabmg5SG42NnJWMlJMMnBlYTlYaVdSb09sR0dnVDdpT29faTdiaDUtZElJdlQ3eTdjR2VsWjlta1FOS1U2Vm1vV3JwWkpvbEw1ZUR3akgwQTZnQnVENjJtVkQtVUpKVEJTeWNJSE1CaEFKa2VqMmZXbWk3ekR4ZWpmZ1Z3elFQaWNaNFJuMXA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOY1ZpYktLR3pUQXotUndVR3puUzVHbW1YTzNyUmJvUHB4Q2JmelRvOEdaRldOUm1xLVJnbGR5VWcxTjNEM3ZUYktCUWtVM0hKSjFuRGdpX0JxN0M5MVZBSG1aVURyVWktdmxwbUtRT19ydU5LdzNTZ2Zpb2ozdHlMUUdTVlAyVk4xODBnV0hyTXdVVndyNzV3VC1KMzFnV3lpcFFXSk9MdDZOTWlWakNwT1FnNDh6QVdjazVYZDVVMkdaLU0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>noticia:1fo4ig4</t>
+          <t>noticia:bzr7eh</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-25 01:08</t>
+          <t>2026-10-25 07:09</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1792904880000</v>
+        <v>1792926572000</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
+          <t>Alerta naranja por riesgo de desbordes de ríos - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>hidrológica</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>roja</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -941,41 +941,57 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>diarioelpueblo.com.pe</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
+          <t>El Diario - Bolivia; El Mundo Bolivia; FmBolivia</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>-16.169</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-68.09</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>La Paz, La Paz</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>La Paz</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Nuestra Señora de La Paz</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQcmFrT3dwcEs0X3U2NWxnOGJwNnI2WHdWTGZYbzEyNnJzUWhkbU9TRWhfSlB5UkMwX2gyMmxYUmVNWmxNOVR6V0twRHpFMTVIYjBKbHQ2TXN2d2w5dkFpcWJCcUJMZldaX01sNWtQV2ZJOGpRVzR3NDVIU0pJc1BNVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNNGZKSDVaZkowWUFGSEUyTWR3d3dsc04waFBLLWUtcVpiTDYzbmNtYTN1RkFLbjAwN3dxT0xZc3pqc3REUXduZVltQ2Fud1BZLTh1bTNiTEJueVUwV0dERS1iUXZqMHd0UnFrQ3E2SFAzbm5lQ1I4U29MaHJFbWFvdVRTeFY4Wl9rSmc3RkpaQ2xwX0oz?oc=5 | https://news.google.com/rss/articles/CBMipwFBVV95cUxPZW00RkxJSklTelNrS2hqczJDWHlwcENFX2lnSEUyTEFPaDFRQ2JvMUcyd3NfYjg0UE9ORGxHRzB4ZDh3U0hQQ1JSQlhsaUY4N3ByMUUxei1SaUZnNlp6T3hsLVdiMGhKaXhsV1FNSUNQMHlvQ19qdk56SEF0d2RXVFctS0VPT25kNGZCRDdvZ2dxU0VoUUJKU0ZBd0ZycFNEZFh0T3ZjOA?oc=5 | https://news.google.com/rss/articles/CBMiwAFBVV95cUxPZm85aHphekQ4U3BZZkp1ZkF6ZVdSUHgtZmltS1FxUUgza1AwcndWWDJZOWctT0RiVmVabmg5SG42NnJWMlJMMnBlYTlYaVdSb09sR0dnVDdpT29faTdiaDUtZElJdlQ3eTdjR2VsWjlta1FOS1U2Vm1vV3JwWkpvbEw1ZUR3akgwQTZnQnVENjJtVkQtVUpKVEJTeWNJSE1CaEFKa2VqMmZXbWk3ekR4ZWpmZ1Z3elFQaWNaNFJuMXA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>noticia:r1uot6</t>
+          <t>noticia:1fo4ig4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-24 20:00</t>
+          <t>2026-10-25 01:08</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1792886439000</v>
+        <v>1792904880000</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>vuelco deja heridos en ruta Oruro – Huanuni - La Patria Bolivia</t>
+          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -984,18 +1000,18 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>roja</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1007,53 +1023,37 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>-17.97</v>
-      </c>
-      <c r="N8" t="n">
-        <v>-67.11</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Oruro, Oruro</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Oruro</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Oruro</t>
-        </is>
-      </c>
+          <t>diarioelpueblo.com.pe</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNNDQtMG1KT1lLWW5nem9Jbm5JWDZKNlRWZmFmRlBxWDlDeXlSWnJ5d2NsTlpxa0JIS25oVWVZOC1majZVbWhOVDIxR0dLOFlzY2VpVzVoVk1mQnF3dXVwLUFZVHc1UjlXZzF5T05CY3U0ZldLVkw1VzBTek5zanpjQW1xalltWHNiaXI3dTNR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQcmFrT3dwcEs0X3U2NWxnOGJwNnI2WHdWTGZYbzEyNnJzUWhkbU9TRWhfSlB5UkMwX2gyMmxYUmVNWmxNOVR6V0twRHpFMTVIYjBKbHQ2TXN2d2w5dkFpcWJCcUJMZldaX01sNWtQV2ZJOGpRVzR3NDVIU0pJc1BNVg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>noticia:1ytw450</t>
+          <t>noticia:r1uot6</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-24 18:58</t>
+          <t>2026-10-24 20:00</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1792882686000</v>
+        <v>1792886439000</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
+          <t>vuelco deja heridos en ruta Oruro – Huanuni - La Patria Bolivia</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1062,18 +1062,18 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>roja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1085,37 +1085,53 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>diarioelpueblo.com.pe</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
+          <t>La Patria Bolivia</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>-17.97</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-67.11</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Oruro, Oruro</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNZ1U3bEVuaVdjVE1zSU9lOHJZTVRZLVZaemhldGNnT1JBWDJvbzdvM3paVVNhLUlyWHF2akNuSXJOLXdyTGRuejRlV1FuMjVkTjA3NmdRdmgtRWlUeTFBV1dEMzBvejBxaXZJdUZZWkRVTF9VLU5BcjFGZGFEQ09WWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNNDQtMG1KT1lLWW5nem9Jbm5JWDZKNlRWZmFmRlBxWDlDeXlSWnJ5d2NsTlpxa0JIS25oVWVZOC1majZVbWhOVDIxR0dLOFlzY2VpVzVoVk1mQnF3dXVwLUFZVHc1UjlXZzF5T05CY3U0ZldLVkw1VzBTek5zanpjQW1xalltWHNiaXI3dTNR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>noticia:1g006zh</t>
+          <t>noticia:1ytw450</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-24 17:02</t>
+          <t>2026-10-24 18:58</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1792875752000</v>
+        <v>1792882686000</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a Mayaya deja siete heridos del grupo Los Chicos Fieles - El Potosí</t>
+          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1124,18 +1140,18 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>roja</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1143,57 +1159,41 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>EL DÍA - Noticias de Bolivia para el mundo; El Potosí; La Razón Digital Bolivia; Opinión Bolivia</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
-        <v>-19.58</v>
-      </c>
-      <c r="N10" t="n">
-        <v>-65.75</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Potosí, Potosí</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
+          <t>diarioelpueblo.com.pe</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPTGQwaVBfdG1JdVRMUTN4LVVvN0ppc3dreDJVVllDR3RmX0xpMzB4b0pvVTNSV1B6T0ZEWTdEZkNsRUdSNzhLaC1CWHN5WktNWk1nRWpTdVZiYjI3TlJlX2xlVTI5MjlRU2hiY1gteml4YWVFbDNPSVRBZmtITlQzbmhaUXVmcThRa2xsQTJIOXZuNzlSdm12MEdyOEZHdw?oc=5 | https://news.google.com/rss/articles/CBMizwFBVV95cUxPeGd3VWpCWXJ0YTJIeDJLcktzWG1jdUh0TjFXb01wSTkxbHNXZU94VWNDMkxnTjlJZVdpbkprMEY2NE80RXYyUWxUQXVnbl9lUXR2b28zTEh6cTJLVEQ4TUNja2kzRlhadVBFZFVwV1U2TlhseXZMZ20zZTZiUFpWRjdCOWNBMHU5XzdMV3JqQjV4TEE3bHRMOXR6Nm55eHZUNnFHSDdVRk8zVkY4RkVsUUtUN0JYdkREWGZncmJ3ZWc2T1BuUm1ZLTlfcHVabFE?oc=5 | https://news.google.com/rss/articles/CBMizAFBVV95cUxNYjNxaHg3YllRRTJYdFd1clAtUlROSGlFNVg5eUVZUGJoOEZ4MWM5QU5WQm1YTDc4NXc3SjhWMUw0TkZfSHlMLUQ1bmpTME1Kb1JaM0ExamFHYTd3VlU4MXRWdTZ1bzh1SGYtbGE1a3dBaG93bjg1OGc0S0JfRE43c3dVMVltN0dQQzNhQUNhM0FjVUNRUDRSamlJYlk2dEJpUTBuY2hBcTFucTVRN0ZtYnc5bzdmTV9LQm1uVUxaZS1tUE9IejhBVDRCdU_SAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNZ1U3bEVuaVdjVE1zSU9lOHJZTVRZLVZaemhldGNnT1JBWDJvbzdvM3paVVNhLUlyWHF2akNuSXJOLXdyTGRuejRlV1FuMjVkTjA3NmdRdmgtRWlUeTFBV1dEMzBvejBxaXZJdUZZWkRVTF9VLU5BcjFGZGFEQ09WWQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>noticia:1ukcn97</t>
+          <t>noticia:1g006zh</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-24 13:26</t>
+          <t>2026-10-24 17:02</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1792862794000</v>
+        <v>1792875752000</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Esta es la lista preliminar de los heridos en el accidente del grupo 'Los chicos fieles', el conductor está grave - El Deber</t>
+          <t>Accidente en la carretera a Mayaya deja siete heridos del grupo Los Chicos Fieles - El Potosí</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1213,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1221,46 +1221,62 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>El Deber; Red Uno</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
+          <t>EL DÍA - Noticias de Bolivia para el mundo; El Potosí; La Razón Digital Bolivia; Opinión Bolivia</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>-19.58</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-65.75</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Potosí, Potosí</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Potosí</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Potosí</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOczZKbFd1QzRpak92LXpPWXZXQXJObnBQTG9qRFBlUUV5dThMWXhzckFFUHAyb2thU1JwRmJDSEZfaEdTUXh1bjZvQWpYMGhfUno3cWZ4MGpldEpoQXhzSlVzTm5LLW9OcjB2MWRsdHQ2UlI2SjEtZ085ZTR5Z3pEVmtBTF9lc29Kd0RhaTRUWkM4eGZJNWhBSXZqWmxuNW10dlQwYW9mdzItcWZWTkU0?oc=5 | https://news.google.com/rss/articles/CBMivAFBVV95cUxPczBQcnE2SzFGMXc3b1lsTkNxVWRmS3Vnb01xOTV2WmVva3J2RVlteWpHZ3VJS2dNWGV5NW5FX3ZncnVKTEVDTGpBRndTU1FxeWxtaS1fb1FscGxXMWNXUE9zbHdob1AxVFl1eHB5OU1yUnNoOXJ6U21oVG9PVDA1ak1xQl9hUlB4V0RaQXJqZENGUm8zMUJEY3J0WW5ENE5ObWJLNmpWN0RkSmFJbnZUZGR5UFRPd3QyUFY4WQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPTGQwaVBfdG1JdVRMUTN4LVVvN0ppc3dreDJVVllDR3RmX0xpMzB4b0pvVTNSV1B6T0ZEWTdEZkNsRUdSNzhLaC1CWHN5WktNWk1nRWpTdVZiYjI3TlJlX2xlVTI5MjlRU2hiY1gteml4YWVFbDNPSVRBZmtITlQzbmhaUXVmcThRa2xsQTJIOXZuNzlSdm12MEdyOEZHdw?oc=5 | https://news.google.com/rss/articles/CBMizwFBVV95cUxPeGd3VWpCWXJ0YTJIeDJLcktzWG1jdUh0TjFXb01wSTkxbHNXZU94VWNDMkxnTjlJZVdpbkprMEY2NE80RXYyUWxUQXVnbl9lUXR2b28zTEh6cTJLVEQ4TUNja2kzRlhadVBFZFVwV1U2TlhseXZMZ20zZTZiUFpWRjdCOWNBMHU5XzdMV3JqQjV4TEE3bHRMOXR6Nm55eHZUNnFHSDdVRk8zVkY4RkVsUUtUN0JYdkREWGZncmJ3ZWc2T1BuUm1ZLTlfcHVabFE?oc=5 | https://news.google.com/rss/articles/CBMizAFBVV95cUxNYjNxaHg3YllRRTJYdFd1clAtUlROSGlFNVg5eUVZUGJoOEZ4MWM5QU5WQm1YTDc4NXc3SjhWMUw0TkZfSHlMLUQ1bmpTME1Kb1JaM0ExamFHYTd3VlU4MXRWdTZ1bzh1SGYtbGE1a3dBaG93bjg1OGc0S0JfRE43c3dVMVltN0dQQzNhQUNhM0FjVUNRUDRSamlJYlk2dEJpUTBuY2hBcTFucTVRN0ZtYnc5bzdmTV9LQm1uVUxaZS1tUE9IejhBVDRCdU_SAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>noticia:2avehj</t>
+          <t>noticia:1ukcn97</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-24 12:53</t>
+          <t>2026-10-24 13:26</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1792860813000</v>
+        <v>1792862794000</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sequía en Cochabamba: más de un centenar de cabezas de ganado murieron en el cono sur - Red Uno</t>
+          <t>Esta es la lista preliminar de los heridos en el accidente del grupo 'Los chicos fieles', el conductor está grave - El Deber</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>climatológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -1272,10 +1288,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1283,62 +1299,46 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Red Uno</t>
-        </is>
-      </c>
-      <c r="M12" t="n">
-        <v>-17.39</v>
-      </c>
-      <c r="N12" t="n">
-        <v>-66.16</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Cochabamba, Cochabamba</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
+          <t>El Deber; Red Uno</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOOFQxc2Vzc0QwS19ydC13RkRPZnZQU3JkSTl5U3kzdUdMSldTcm5HVEhWRzZyN19CLUlwcUs4MW03Ui1obVBtdzQ3QWFQc1RKdzh3MXJ5QkpRS2pRNm50V1lVb09ScGJnaVVlemVfZlRsWjdObnRmR1FGMnlMMHAyc2pMandndy10T2twcWx6OFh4UHdvbVlFbllwME9WQ2pQVjNTQzBxeTg5YnF3bDREeHVDYXpObFFIaTZZQWtYUE12cGQ1ZGRhT0syNjVhZWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOczZKbFd1QzRpak92LXpPWXZXQXJObnBQTG9qRFBlUUV5dThMWXhzckFFUHAyb2thU1JwRmJDSEZfaEdTUXh1bjZvQWpYMGhfUno3cWZ4MGpldEpoQXhzSlVzTm5LLW9OcjB2MWRsdHQ2UlI2SjEtZ085ZTR5Z3pEVmtBTF9lc29Kd0RhaTRUWkM4eGZJNWhBSXZqWmxuNW10dlQwYW9mdzItcWZWTkU0?oc=5 | https://news.google.com/rss/articles/CBMivAFBVV95cUxPczBQcnE2SzFGMXc3b1lsTkNxVWRmS3Vnb01xOTV2WmVva3J2RVlteWpHZ3VJS2dNWGV5NW5FX3ZncnVKTEVDTGpBRndTU1FxeWxtaS1fb1FscGxXMWNXUE9zbHdob1AxVFl1eHB5OU1yUnNoOXJ6U21oVG9PVDA1ak1xQl9hUlB4V0RaQXJqZENGUm8zMUJEY3J0WW5ENE5ObWJLNmpWN0RkSmFJbnZUZGR5UFRPd3QyUFY4WQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>noticia:3dv7b0</t>
+          <t>noticia:2avehj</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-24 11:43</t>
+          <t>2026-10-24 12:53</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1792856591000</v>
+        <v>1792860813000</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Accidente en Caranavi: vehículo de Los Chicos Fieles cae a un barranco y deja varios heridos - FmBolivia</t>
+          <t>Sequía en Cochabamba: más de un centenar de cabezas de ganado murieron en el cono sur - Red Uno</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>climatológica</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1361,62 +1361,62 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>FmBolivia; La Patria Bolivia; Red Uno</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>-15.813</v>
+        <v>-17.39</v>
       </c>
       <c r="N13" t="n">
-        <v>-67.46299999999999</v>
+        <v>-66.16</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Caranavi, La Paz</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Caranavi</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNeEFrOEtOMHZxMW42REFPU0x1MG5oQjlBMkJucWRLZ292alBXekJKeURBN3NLTVVadWI0OWF4UGtSVXBzTE01eWFSU1kyMUhNZ04zMWNMaUxnMDBBZ0EwTktXbjlaVTBUUmNqa3AwY19KNTU2LWh5LW9IVElVdTdnaHFPanJPd2FqMUxzaUhXZmVpYU1saGc?oc=5 | https://news.google.com/rss/articles/CBMi2wFBVV95cUxOdTVUZUQxVTdvYTdONDQxVlhUTzBOS2hKLW1rS1NUcmRYRnlCVlhIcHZlSjdsaktkQm5CWkFYa3lDQkxnMlh0b3prX0lha1BtbW1qS1VuYnNiX3FiZkYyNDJDR0tqZ0pKMU5TeC04SXV4UUJOTUlPUTB6ek01bzUxTUsydjZqZzI3S3ZLUnRWSUFUVk44WEpKUl9rbzRLb2IwYl9sLVlrYmt5d2ZHNUtGd3lRNnYzMlhuMkJOZW1XSUl2N1BxZWpHbm5XTDJhRUtnR190QWQ1TDlTUVk?oc=5 | https://news.google.com/rss/articles/CBMizAFBVV95cUxNcE1KaHZyUTJCSElxRU9nVzdhTnczWjJGTEhFMEs0bHp2cUdFeHd3VTB0NmVFcjdEN1dsZDZLY2k1ZFFUWkhKV19PU3V2czNyamh1ZE9YajVSVF8xczF6OFhZcWFvYV9EcWg4ZDNCb2p3enhXbFpRYnJMdGdaTXNrWUZSYVhKNTVicWlCLTJ5OE05Z1BvNEx1eEloUk5qTGN3ZHNzbzZWSVljbnRmSERJUWdxRDc0MjJxMGtycWJaaVhXQUUxVUlaWVZLOWE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOOFQxc2Vzc0QwS19ydC13RkRPZnZQU3JkSTl5U3kzdUdMSldTcm5HVEhWRzZyN19CLUlwcUs4MW03Ui1obVBtdzQ3QWFQc1RKdzh3MXJ5QkpRS2pRNm50V1lVb09ScGJnaVVlemVfZlRsWjdObnRmR1FGMnlMMHAyc2pMandndy10T2twcWx6OFh4UHdvbVlFbllwME9WQ2pQVjNTQzBxeTg5YnF3bDREeHVDYXpObFFIaTZZQWtYUE12cGQ1ZGRhT0syNjVhZWs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>clima:Potosí:2026-10-24:viento:1</t>
+          <t>noticia:3dv7b0</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-24 10:55</t>
+          <t>2026-10-24 11:43</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1792853727284</v>
+        <v>1792856591000</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Potosí 2026-10-24: 60.5 km/h de ráfagas pronosticadas</t>
+          <t>Accidente en Caranavi: vehículo de Los Chicos Fieles cae a un barranco y deja varios heridos - FmBolivia</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1431,7 +1431,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1439,57 +1439,57 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>FmBolivia; La Patria Bolivia; Red Uno</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>-19.58</v>
+        <v>-15.813</v>
       </c>
       <c r="N14" t="n">
-        <v>-65.75</v>
+        <v>-67.46299999999999</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Caranavi, La Paz</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Caranavi</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNeEFrOEtOMHZxMW42REFPU0x1MG5oQjlBMkJucWRLZ292alBXekJKeURBN3NLTVVadWI0OWF4UGtSVXBzTE01eWFSU1kyMUhNZ04zMWNMaUxnMDBBZ0EwTktXbjlaVTBUUmNqa3AwY19KNTU2LWh5LW9IVElVdTdnaHFPanJPd2FqMUxzaUhXZmVpYU1saGc?oc=5 | https://news.google.com/rss/articles/CBMi2wFBVV95cUxOdTVUZUQxVTdvYTdONDQxVlhUTzBOS2hKLW1rS1NUcmRYRnlCVlhIcHZlSjdsaktkQm5CWkFYa3lDQkxnMlh0b3prX0lha1BtbW1qS1VuYnNiX3FiZkYyNDJDR0tqZ0pKMU5TeC04SXV4UUJOTUlPUTB6ek01bzUxTUsydjZqZzI3S3ZLUnRWSUFUVk44WEpKUl9rbzRLb2IwYl9sLVlrYmt5d2ZHNUtGd3lRNnYzMlhuMkJOZW1XSUl2N1BxZWpHbm5XTDJhRUtnR190QWQ1TDlTUVk?oc=5 | https://news.google.com/rss/articles/CBMizAFBVV95cUxNcE1KaHZyUTJCSElxRU9nVzdhTnczWjJGTEhFMEs0bHp2cUdFeHd3VTB0NmVFcjdEN1dsZDZLY2k1ZFFUWkhKV19PU3V2czNyamh1ZE9YajVSVF8xczF6OFhZcWFvYV9EcWg4ZDNCb2p3enhXbFpRYnJMdGdaTXNrWUZSYVhKNTVicWlCLTJ5OE05Z1BvNEx1eEloUk5qTGN3ZHNzbzZWSVljbnRmSERJUWdxRDc0MjJxMGtycWJaaVhXQUUxVUlaWVZLOWE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>noticia:1ax0bpy</t>
+          <t>clima:Potosí:2026-10-24:viento:1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-24 10:32</t>
+          <t>2026-10-24 10:55</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1792852364000</v>
+        <v>1792853727284</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Creció el Bermejo tras la tormenta: así está el puerto de chalanas en este momento - Que Pasa Salta</t>
+          <t>Potosí 2026-10-24: 60.5 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1498,11 +1498,11 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1521,58 +1521,58 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Que Pasa Salta</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>-22.721</v>
+        <v>-19.58</v>
       </c>
       <c r="N15" t="n">
-        <v>-64.32599999999999</v>
+        <v>-65.75</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Bermejo, Tarija</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tarija</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Bermejo</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVld9IBfkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVldw?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>gdacs:WF1033142:0</t>
+          <t>noticia:1ax0bpy</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-24 07:06</t>
+          <t>2026-10-24 10:32</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1792839995000</v>
+        <v>1792852364000</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Green forest fire notification in Bolivia</t>
+          <t>Creció el Bermejo tras la tormenta: así está el puerto de chalanas en este momento - Que Pasa Salta</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1599,58 +1599,58 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>GDACS</t>
+          <t>Que Pasa Salta</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>-13.06332</v>
+        <v>-22.721</v>
       </c>
       <c r="N16" t="n">
-        <v>-67.66426</v>
+        <v>-64.32599999999999</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Bermejo, Tarija</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Tarija</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Ixiamas</t>
+          <t>Bermejo</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>http://www.gdacs.org/report.aspx?eventtype=WF&amp;eventid=1033142</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVld9IBfkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVldw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>noticia:1shhqva</t>
+          <t>gdacs:WF1033142:0</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-24 06:33</t>
+          <t>2026-10-24 07:06</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1792838034000</v>
+        <v>1792839995000</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
+          <t>Green forest fire notification in Bolivia</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1673,70 +1673,70 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>GDACS</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>-17.97</v>
+        <v>-13.06332</v>
       </c>
       <c r="N17" t="n">
-        <v>-67.11</v>
+        <v>-67.66426</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Ixiamas</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQYzB6N082XzFRRnVtcDVmUkYyWjcxUzV2Z3Frd1I0WDNXSnZtY0QzOU1PUkNLMktVT1Vra2FSeXhxZDRuOFZYZjFwejl6ejJTbWY2MGJuSGN3ZHdrdG5JUkgzSXBkbDYtaHlackY3OVFuNWdLcFNpdWNHRU9vNGdoVWx2ODFVdzJXYUxnM0tUcjJvZmc?oc=5 | https://news.google.com/rss/articles/CBMikAFBVV95cUxQS2FPaHd3UnFBRjRoa0lKUm1MNUQ5S00zN1RJZE5fWlVUQnhiY0lLcFRkY2JZak1mZ0c2WEVMVUNJVUJTMGFLNHg4S2ZKNTRqLXJHM09ET19hX1pZeTQwUkdEc2huTHVpcno2QTRZbnhralVRWXozcWc1a2pHUEpBeTV1cWgzTWRwaDEweURKeVE?oc=5</t>
+          <t>http://www.gdacs.org/report.aspx?eventtype=WF&amp;eventid=1033142</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>clima:Potosí:2026-10-25:viento:1</t>
+          <t>noticia:1shhqva</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-24 02:55</t>
+          <t>2026-10-24 06:33</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1792824927736</v>
+        <v>1792838034000</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Potosí 2026-10-25: 60.5 km/h de ráfagas pronosticadas</t>
+          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1751,62 +1751,62 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>-19.58</v>
+        <v>-17.97</v>
       </c>
       <c r="N18" t="n">
-        <v>-65.75</v>
+        <v>-67.11</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Oruro, Oruro</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Oruro</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Oruro</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQYzB6N082XzFRRnVtcDVmUkYyWjcxUzV2Z3Frd1I0WDNXSnZtY0QzOU1PUkNLMktVT1Vra2FSeXhxZDRuOFZYZjFwejl6ejJTbWY2MGJuSGN3ZHdrdG5JUkgzSXBkbDYtaHlackY3OVFuNWdLcFNpdWNHRU9vNGdoVWx2ODFVdzJXYUxnM0tUcjJvZmc?oc=5 | https://news.google.com/rss/articles/CBMikAFBVV95cUxQS2FPaHd3UnFBRjRoa0lKUm1MNUQ5S00zN1RJZE5fWlVUQnhiY0lLcFRkY2JZak1mZ0c2WEVMVUNJVUJTMGFLNHg4S2ZKNTRqLXJHM09ET19hX1pZeTQwUkdEc2huTHVpcno2QTRZbnhralVRWXozcWc1a2pHUEpBeTV1cWgzTWRwaDEweURKeVE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>noticia:1uil931</t>
+          <t>clima:Potosí:2026-10-25:viento:1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-23 22:49</t>
+          <t>2026-10-24 02:55</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1792810149000</v>
+        <v>1792824927736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Accidente de tránsito en la ruta hacia Alto Beni deja varios heridos - El Deber</t>
+          <t>Potosí 2026-10-25: 60.5 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1821,7 +1821,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1829,62 +1829,62 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>El Deber</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>-15.578</v>
+        <v>-19.58</v>
       </c>
       <c r="N19" t="n">
-        <v>-67.44</v>
+        <v>-65.75</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Alto Beni, La Paz</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Alto Beni</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQakFJRmx3RlJEMkVHU0pxWXZ2ZU1ib04tZy1yeTB2OGhrYk9CU3pMaDVpRThNZktZMS14UzA2Y1VIcEQtZDg3cEU2SmlzQnBmUVVvM0ZNYzZWNExWUXQ3aHpnd3lqOHFVV3pNbDRLS1NQNGtwb2RjSFpleHJkOG5zSXVtWjVIS1dLejNybktRWTJVZXh3WkFUQVE5T2tMdFdn?oc=5 | https://news.google.com/rss/articles/CBMilwFBVV95cUxQMF9BNnUzLURKNGRMUUJ1VXVRSXNnMlBsQnVXOG0tRlFtY3pvRDNPQmNJMWN2RzJVaWdoWndmcHFnTkZFZnJxRkZtMThYYWlwN09ueUgtei1pSE1hZ2FtSzN6elY4VXJHbzFxdll0eWh0ZkxwQkQ1SDZ5b0E3MlVENGZEWGZHUGlwVG4wd2x3OFNEMVpibnFr?oc=5 | https://news.google.com/rss/articles/CBMimgFBVV95cUxNbmwzSnd6c2tFMXBWY0tiemJqRm5CNllOT2p1U0FhdW5QNGFBVXlSZVM1ak5jNGZvcXNVaUQzN3ZQQTlPbmVjQ2Y5RFl2dWVLeUN5NUFodDF0alEyZWlmOHFZWkVVbjdQbkl3ZWtmS25wQWM2TmRZZDBGM2xlS0ZhUzAweXRmcmhVWGY5dV9CUnFBNGtWZHZDSWVB?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-24:viento:1</t>
+          <t>noticia:1uil931</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-23 20:55</t>
+          <t>2026-10-23 22:49</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1792803329663</v>
+        <v>1792810149000</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-24: 78.1 km/h de ráfagas pronosticadas</t>
+          <t>Accidente de tránsito en la ruta hacia Alto Beni deja varios heridos - El Deber</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1899,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1907,57 +1907,57 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>El Deber</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>-17.78</v>
+        <v>-15.578</v>
       </c>
       <c r="N20" t="n">
-        <v>-63.18</v>
+        <v>-67.44</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Alto Beni, La Paz</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Alto Beni</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQakFJRmx3RlJEMkVHU0pxWXZ2ZU1ib04tZy1yeTB2OGhrYk9CU3pMaDVpRThNZktZMS14UzA2Y1VIcEQtZDg3cEU2SmlzQnBmUVVvM0ZNYzZWNExWUXQ3aHpnd3lqOHFVV3pNbDRLS1NQNGtwb2RjSFpleHJkOG5zSXVtWjVIS1dLejNybktRWTJVZXh3WkFUQVE5T2tMdFdn?oc=5 | https://news.google.com/rss/articles/CBMilwFBVV95cUxQMF9BNnUzLURKNGRMUUJ1VXVRSXNnMlBsQnVXOG0tRlFtY3pvRDNPQmNJMWN2RzJVaWdoWndmcHFnTkZFZnJxRkZtMThYYWlwN09ueUgtei1pSE1hZ2FtSzN6elY4VXJHbzFxdll0eWh0ZkxwQkQ1SDZ5b0E3MlVENGZEWGZHUGlwVG4wd2x3OFNEMVpibnFr?oc=5 | https://news.google.com/rss/articles/CBMimgFBVV95cUxNbmwzSnd6c2tFMXBWY0tiemJqRm5CNllOT2p1U0FhdW5QNGFBVXlSZVM1ak5jNGZvcXNVaUQzN3ZQQTlPbmVjQ2Y5RFl2dWVLeUN5NUFodDF0alEyZWlmOHFZWkVVbjdQbkl3ZWtmS25wQWM2TmRZZDBGM2xlS0ZhUzAweXRmcmhVWGY5dV9CUnFBNGtWZHZDSWVB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>noticia:rabz5p</t>
+          <t>clima:Santa Cruz:2026-10-24:viento:1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-23 20:44</t>
+          <t>2026-10-23 20:55</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1792802686000</v>
+        <v>1792803329663</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tome previsiones: se pronostican lluvias y ambiente caluroso para este fin de semana en Cochabamba - Red Uno</t>
+          <t>Santa Cruz 2026-10-24: 78.1 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1966,11 +1966,11 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -1989,70 +1989,70 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>-17.39</v>
+        <v>-17.78</v>
       </c>
       <c r="N21" t="n">
-        <v>-66.16</v>
+        <v>-63.18</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Cochabamba, Cochabamba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTlU5NVFpY1RheTN5ZE1IbG5VYTh2Sk5hZHpHeWI3LVdnSFg2cFJFdnBCVkxiUjNKcUgyUW16SWxpMXFkMHdad2xFN043bklJeG1iQ0V1V3hBZk1Ga3NscjdPVWUySmt4bDNTdWlmSUdOMmNlZ2hkSWZFMmk4VGs0Nm9TcnRCTDhINmtnQU9zZDBUY05HcWpxN3FOX3N1dmVJblE0MGc5di1Ma1N2dGNxOUtoV1MzNnl1OXpRaTZ2UGxMc3RDWndubHVQNUd0eVROMGR2OGxVemtOaEc4bTNRaA?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>noticia:1jfk053</t>
+          <t>noticia:rabz5p</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-23 19:08</t>
+          <t>2026-10-23 20:44</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1792796931000</v>
+        <v>1792802686000</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sequía en Pasorapa: el ganado muere por falta de agua y alistan declaratoria de desastre - Red Uno</t>
+          <t>Tome previsiones: se pronostican lluvias y ambiente caluroso para este fin de semana en Cochabamba - Red Uno</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>climatológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -2071,14 +2071,14 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>-18.38</v>
+        <v>-17.39</v>
       </c>
       <c r="N22" t="n">
-        <v>-64.649</v>
+        <v>-66.16</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Pasorapa, Cochabamba</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2088,49 +2088,49 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Pasorapa</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNQVhTWE8zdE1BQ3lueWJPeV9wUDNsSmJpS0NJTWppMUY4QmlQSUFHVjRORmtrVHQ3MHB0T1pyS25PamxnY0hBQUtzOVRvSUNaUkdGb1RWSGl4dFA4Z3VINVpQTk1pZUpDdUIyUU5hZS1oNGhBa1RWcFhScVMwVTFrVlJaOFQ4OWFqRWVUZ051bHVJTlMxRTBhRFVLUEV2dTZFdDgtRkxJM3VvN3YzUWJfVk41ZWR5U1JoNmx0WFFkMmNTWGVleGNIQlNxWUJzdHIxSWtz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTlU5NVFpY1RheTN5ZE1IbG5VYTh2Sk5hZHpHeWI3LVdnSFg2cFJFdnBCVkxiUjNKcUgyUW16SWxpMXFkMHdad2xFN043bklJeG1iQ0V1V3hBZk1Ga3NscjdPVWUySmt4bDNTdWlmSUdOMmNlZ2hkSWZFMmk4VGs0Nm9TcnRCTDhINmtnQU9zZDBUY05HcWpxN3FOX3N1dmVJblE0MGc5di1Ma1N2dGNxOUtoV1MzNnl1OXpRaTZ2UGxMc3RDWndubHVQNUd0eVROMGR2OGxVemtOaEc4bTNRaA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>noticia:ix3l8o</t>
+          <t>noticia:1jfk053</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-23 18:25</t>
+          <t>2026-10-23 19:08</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1792794310000</v>
+        <v>1792796931000</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Oruro evalúa suspender clases presenciales por más de 200 casos de Coxsackie - Visión 360</t>
+          <t>Sequía en Pasorapa: el ganado muere por falta de agua y alistan declaratoria de desastre - Red Uno</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>climatológica</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2141,77 +2141,77 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Red Uno; Visión 360</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>-17.97</v>
+        <v>-18.38</v>
       </c>
       <c r="N23" t="n">
-        <v>-67.11</v>
+        <v>-64.649</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>Pasorapa, Cochabamba</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Pasorapa</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0c9IBywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0cw?oc=5 | https://news.google.com/rss/articles/CBMiywFBVV95cUxNMFdHaVpKRmMyOENDYm16UXJPenVSQnpmTE94bDc4UFhqakluMUdvZjAwamUxT3BVWUpJQm8xVHBWengxQmhWM1hjU3d2YXFrLXpVU2VrZDJiMXZLMlQ5bGxGOHFETFhYM0s2RjlUTlhkd0g2eXQweDFHaTlKNGNMUlJfOWg2a0JjTklXUWZKc1BmUXZuZFZ2MF9fV2lEYUY4LXNiNmk3cF9FNjVtTl9GWFotT2ltS0xXTnM1dENvSU9kbFRMalFrYVdXOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNQVhTWE8zdE1BQ3lueWJPeV9wUDNsSmJpS0NJTWppMUY4QmlQSUFHVjRORmtrVHQ3MHB0T1pyS25PamxnY0hBQUtzOVRvSUNaUkdGb1RWSGl4dFA4Z3VINVpQTk1pZUpDdUIyUU5hZS1oNGhBa1RWcFhScVMwVTFrVlJaOFQ4OWFqRWVUZ051bHVJTlMxRTBhRFVLUEV2dTZFdDgtRkxJM3VvN3YzUWJfVk41ZWR5U1JoNmx0WFFkMmNTWGVleGNIQlNxWUJzdHIxSWtz?oc=5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>noticia:1xqv9m7</t>
+          <t>noticia:ix3l8o</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-23 18:09</t>
+          <t>2026-10-23 18:25</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1792793370000</v>
+        <v>1792794310000</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tres heridos en tremendo choque cerca de Oncativo - El Diario del centro del país</t>
+          <t>Oruro evalúa suspender clases presenciales por más de 200 casos de Coxsackie - Visión 360</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -2219,61 +2219,77 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>El Diario del centro del país</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
+          <t>Red Uno; Visión 360</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>-17.97</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-67.11</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Oruro, Oruro</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZERhbTJMQUJVb3hmZFlSZmRGZkdBLWdFTGJVQzdqZkE4aGhhWmdQZ2JDRW1ndkJLWU90VTZ6Ti1JOUZzcFZfcE1zbkRHU1B3YTF4UkVzdllFa1p3SUlObURGamF0Vm9kc3dPLTZVWFJ4NWZZQmlySElPNHhZTnRGNGNZUWw2ZlI1eVBEQkNGNEhLWTNiLWJLUS0xYjA0UWRhc0d6bVN4aVVLSVdsQWlpMUZYdWw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0c9IBywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0cw?oc=5 | https://news.google.com/rss/articles/CBMiywFBVV95cUxNMFdHaVpKRmMyOENDYm16UXJPenVSQnpmTE94bDc4UFhqakluMUdvZjAwamUxT3BVWUpJQm8xVHBWengxQmhWM1hjU3d2YXFrLXpVU2VrZDJiMXZLMlQ5bGxGOHFETFhYM0s2RjlUTlhkd0g2eXQweDFHaTlKNGNMUlJfOWg2a0JjTklXUWZKc1BmUXZuZFZ2MF9fV2lEYUY4LXNiNmk3cF9FNjVtTl9GWFotT2ltS0xXTnM1dENvSU9kbFRMalFrYVdXOA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>noticia:1itd1r7</t>
+          <t>noticia:1xqv9m7</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-23 15:01</t>
+          <t>2026-10-23 18:09</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1792782098000</v>
+        <v>1792793370000</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Intensa lluvia y granizada en La Paz inundan vías y elevan el nivel de los ríos - eju.tv</t>
+          <t>Tres heridos en tremendo choque cerca de Oncativo - El Diario del centro del país</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2285,73 +2301,57 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>eju.tv</t>
-        </is>
-      </c>
-      <c r="M25" t="n">
-        <v>-16.169</v>
-      </c>
-      <c r="N25" t="n">
-        <v>-68.09</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>La Paz, La Paz</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>La Paz</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>Nuestra Señora de La Paz</t>
-        </is>
-      </c>
+          <t>El Diario del centro del país</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNWU9QWElKQXEyN3UxVm4xbzJzbEJ1TU1NTHZlRUp6YndmeU9GQnJKcTluVEJ2ZHQ5cGp3aWhlMUd5ektWQlBpUVNmZnZuRnJwMXlydzAzX0FBVnY5UDMzQTBkWVRNRUNJSlRvX3MyQVhMcEhIMW9WSUpXckVSd0RJWk1KMFBKWmJNU3diQVlEN1Y5aVV6eVBaZXpOMnFIWWxaMlRlY0ZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZERhbTJMQUJVb3hmZFlSZmRGZkdBLWdFTGJVQzdqZkE4aGhhWmdQZ2JDRW1ndkJLWU90VTZ6Ti1JOUZzcFZfcE1zbkRHU1B3YTF4UkVzdllFa1p3SUlObURGamF0Vm9kc3dPLTZVWFJ4NWZZQmlySElPNHhZTnRGNGNZUWw2ZlI1eVBEQkNGNEhLWTNiLWJLUS0xYjA0UWRhc0d6bVN4aVVLSVdsQWlpMUZYdWw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>noticia:51709n</t>
+          <t>noticia:1itd1r7</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-23 13:38</t>
+          <t>2026-10-23 15:01</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1792777139000</v>
+        <v>1792782098000</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - eju.tv</t>
+          <t>Intensa lluvia y granizada en La Paz inundan vías y elevan el nivel de los ríos - eju.tv</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2359,77 +2359,77 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Red Uno; eju.tv</t>
+          <t>eju.tv</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>-17.764</v>
+        <v>-16.169</v>
       </c>
       <c r="N26" t="n">
-        <v>-62.903</v>
+        <v>-68.09</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Cotoca, Santa Cruz</t>
+          <t>La Paz, La Paz</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Cotoca</t>
+          <t>Nuestra Señora de La Paz</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPcjZTSmprRGVoNlRqQmdBTE5VM3pRQ1ZFakFUbzVyMUhiaDVkT0liaG9UNEZXekV6bWsycUk4X1JCSEY5RjhNVlZaTk9ULUFuZkY3NnZuWmZ1a19leUhFdlIyQV9kLWxlSkxfeXFhcFRTZjZ2YkpQQlJ1dkNLMDBjaGZ4SkhyQ0RfcnhKSEg5WURCQVQwbENYTHEzUzJSaUEzMGo2bWdyS3lsM016LXc?oc=5 | https://news.google.com/rss/articles/CBMi0AFBVV95cUxOVGY3YVRLWWxYM0IycjF4dlNUeUhqZG90Yng4aWhmN3A5ai02WENWYnF4bWpoZHFKMGc1X0JPRHdRRVZfSlA4UmZFa2kxYkNIS3ZtQ1NvNlNCME51eVZTRkRKSUQ5MmRoaWl5Tkt5NHpPUEFwemN2YTV1djFwdHlqQnFqRHNPenhYcTlsanJPcXhpOVV1NmFBUXZyazQ2MkUzM0dSZy02ZllxTGtjcl9ldzdHSktTRlVaalZJc1pubUNQMWFTbzVEOUJ1UmhCdEJt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNWU9QWElKQXEyN3UxVm4xbzJzbEJ1TU1NTHZlRUp6YndmeU9GQnJKcTluVEJ2ZHQ5cGp3aWhlMUd5ektWQlBpUVNmZnZuRnJwMXlydzAzX0FBVnY5UDMzQTBkWVRNRUNJSlRvX3MyQVhMcEhIMW9WSUpXckVSd0RJWk1KMFBKWmJNU3diQVlEN1Y5aVV6eVBaZXpOMnFIWWxaMlRlY0ZB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>noticia:11rddql</t>
+          <t>noticia:51709n</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-23 13:22</t>
+          <t>2026-10-23 13:38</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1792776139000</v>
+        <v>1792777139000</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Intensifican acciones preventivas contra el dengue en Caranavi - El Diario - Bolivia</t>
+          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - eju.tv</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2437,77 +2437,77 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>Red Uno; eju.tv</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>-15.813</v>
+        <v>-17.764</v>
       </c>
       <c r="N27" t="n">
-        <v>-67.46299999999999</v>
+        <v>-62.903</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Caranavi, La Paz</t>
+          <t>Cotoca, Santa Cruz</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>Caranavi</t>
+          <t>Cotoca</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOMjhSeDJBek5iaFhDcnFzX1lKelgwZmUwLTJnbEhMdDRMelUxNks5Ti1pRHh3dDhTcC1YZEdqM3FJOGdqVHRvcXVhRlpCQzVDTEZMUFBkV1NrYVQ2LXRqTTBhcGRQc21CQ0VabzZaNExXb1BjTzJ2Uk5BcFF0VG5XOFNRa3lqUWlJSnRFUUVXYnNpbXB0LVVmSXVWSzJxcmVpdVVxUC1KOUhTQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPcjZTSmprRGVoNlRqQmdBTE5VM3pRQ1ZFakFUbzVyMUhiaDVkT0liaG9UNEZXekV6bWsycUk4X1JCSEY5RjhNVlZaTk9ULUFuZkY3NnZuWmZ1a19leUhFdlIyQV9kLWxlSkxfeXFhcFRTZjZ2YkpQQlJ1dkNLMDBjaGZ4SkhyQ0RfcnhKSEg5WURCQVQwbENYTHEzUzJSaUEzMGo2bWdyS3lsM016LXc?oc=5 | https://news.google.com/rss/articles/CBMi0AFBVV95cUxOVGY3YVRLWWxYM0IycjF4dlNUeUhqZG90Yng4aWhmN3A5ai02WENWYnF4bWpoZHFKMGc1X0JPRHdRRVZfSlA4UmZFa2kxYkNIS3ZtQ1NvNlNCME51eVZTRkRKSUQ5MmRoaWl5Tkt5NHpPUEFwemN2YTV1djFwdHlqQnFqRHNPenhYcTlsanJPcXhpOVV1NmFBUXZyazQ2MkUzM0dSZy02ZllxTGtjcl9ldzdHSktTRlVaalZJc1pubUNQMWFTbzVEOUJ1UmhCdEJt?oc=5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>noticia:fcm3nx</t>
+          <t>noticia:11rddql</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-23 12:58</t>
+          <t>2026-10-23 13:22</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1792774699000</v>
+        <v>1792776139000</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>[VIDEO] Así fue el accidente de moto que dejó un adolescente fallecido y un hombre gravemente herido - Red Uno</t>
+          <t>Intensifican acciones preventivas contra el dengue en Caranavi - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2519,57 +2519,73 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Red Uno</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
+          <t>El Diario - Bolivia</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>-15.813</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-67.46299999999999</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Caranavi, La Paz</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>La Paz</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Caranavi</t>
+        </is>
+      </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOSmJMazhUemNfRHpWcDBoTVFZMUpwdlVKVUtvUXZNTGRRRHlwLW5KNmNhcmFnd1czbi1yalhFMnpSS1dmUE9jVzNlOS1kMWZtRzBHZ2EtcDRDdU5Gc2JUQVIwM2xPa2lZVmswRi1SUFVPcm8xcHlGN3F2UThTSDdKMDNyYnJmVkcxazNLLVBLOWFYM09FVUpmVnN5RVhpSVo2V1VCVmFwQ1gzTmRUWVp2aXMwcmxHRS1GV2p3NTBtR2RzM2wwVHUzaGJkRXJYbHdvaDlhWm5YMTk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOMjhSeDJBek5iaFhDcnFzX1lKelgwZmUwLTJnbEhMdDRMelUxNks5Ti1pRHh3dDhTcC1YZEdqM3FJOGdqVHRvcXVhRlpCQzVDTEZMUFBkV1NrYVQ2LXRqTTBhcGRQc21CQ0VabzZaNExXb1BjTzJ2Uk5BcFF0VG5XOFNRa3lqUWlJSnRFUUVXYnNpbXB0LVVmSXVWSzJxcmVpdVVxUC1KOUhTQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>noticia:1cjx1qd</t>
+          <t>noticia:fcm3nx</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-23 12:39</t>
+          <t>2026-10-23 12:58</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1792773575000</v>
+        <v>1792774699000</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Más de 60 municipios en La Paz sufren falta de lluvias - La Patria Bolivia</t>
+          <t>[VIDEO] Así fue el accidente de moto que dejó un adolescente fallecido y un hombre gravemente herido - Red Uno</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2581,53 +2597,37 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
-        </is>
-      </c>
-      <c r="M29" t="n">
-        <v>-16.169</v>
-      </c>
-      <c r="N29" t="n">
-        <v>-68.09</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>La Paz, La Paz</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>La Paz</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>Nuestra Señora de La Paz</t>
-        </is>
-      </c>
+          <t>Red Uno</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE52Qi03Z1J6OS1CR2liRVZ0VlhCcmVQWFV6RUdGNXdrbzZRNXFjTWRaRnc1b3VoV0xaY3RIdncxNlNnYkxyUXo5MTlJWmMwWDNSMDE4ZHI2VkpWajFPaUF2SmRVYkk2eDZYQ1RfUU9ieENrZG9UVVFiaXZSeGI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOSmJMazhUemNfRHpWcDBoTVFZMUpwdlVKVUtvUXZNTGRRRHlwLW5KNmNhcmFnd1czbi1yalhFMnpSS1dmUE9jVzNlOS1kMWZtRzBHZ2EtcDRDdU5Gc2JUQVIwM2xPa2lZVmswRi1SUFVPcm8xcHlGN3F2UThTSDdKMDNyYnJmVkcxazNLLVBLOWFYM09FVUpmVnN5RVhpSVo2V1VCVmFwQ1gzTmRUWVp2aXMwcmxHRS1GV2p3NTBtR2RzM2wwVHUzaGJkRXJYbHdvaDlhWm5YMTk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>clima:Sucre:2026-10-23:viento:1</t>
+          <t>noticia:1cjx1qd</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-23 06:55</t>
+          <t>2026-10-23 12:39</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1792752927735</v>
+        <v>1792773575000</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sucre 2026-10-23: 66.2 km/h de ráfagas pronosticadas</t>
+          <t>Más de 60 municipios en La Paz sufren falta de lluvias - La Patria Bolivia</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2636,11 +2636,11 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -2659,40 +2659,40 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>La Patria Bolivia</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>-19.03</v>
+        <v>-16.169</v>
       </c>
       <c r="N30" t="n">
-        <v>-65.26000000000001</v>
+        <v>-68.09</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>La Paz, La Paz</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Chuquisaca</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Nuestra Señora de La Paz</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE52Qi03Z1J6OS1CR2liRVZ0VlhCcmVQWFV6RUdGNXdrbzZRNXFjTWRaRnc1b3VoV0xaY3RIdncxNlNnYkxyUXo5MTlJWmMwWDNSMDE4ZHI2VkpWajFPaUF2SmRVYkk2eDZYQ1RfUU9ieENrZG9UVVFiaXZSeGI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-24:viento:2</t>
+          <t>clima:Sucre:2026-10-23:viento:1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2701,11 +2701,11 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1792752927734</v>
+        <v>1792752927735</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-24: 85 km/h de ráfagas pronosticadas</t>
+          <t>Sucre 2026-10-23: 66.2 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2714,11 +2714,11 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -2741,24 +2741,24 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>-17.78</v>
+        <v>-19.03</v>
       </c>
       <c r="N31" t="n">
-        <v>-63.18</v>
+        <v>-65.26000000000001</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Chuquisaca</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2770,33 +2770,33 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>usgs:us6000u49c</t>
+          <t>clima:Santa Cruz:2026-10-24:viento:2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-22 22:45</t>
+          <t>2026-10-23 06:55</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1792723541183</v>
+        <v>1792752927734</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sismo M 4.5 - 58 km SW of Atocha, Bolivia</t>
+          <t>Santa Cruz 2026-10-24: 85 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>geológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -2815,58 +2815,58 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>USGS</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>-21.3469</v>
+        <v>-17.78</v>
       </c>
       <c r="N32" t="n">
-        <v>-66.5795</v>
+        <v>-63.18</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>58 km SW of Atocha, Bolivia</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>San Pablo</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>https://earthquake.usgs.gov/earthquakes/eventpage/us6000u49c</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-22:viento:1</t>
+          <t>usgs:us6000u49c</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-22 21:55</t>
+          <t>2026-10-22 22:45</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1792720528712</v>
+        <v>1792723541183</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-22: 67.7 km/h de ráfagas pronosticadas</t>
+          <t>Sismo M 4.5 - 58 km SW of Atocha, Bolivia</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>geológica</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -2893,40 +2893,40 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>USGS</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>-17.78</v>
+        <v>-21.3469</v>
       </c>
       <c r="N33" t="n">
-        <v>-63.18</v>
+        <v>-66.5795</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>58 km SW of Atocha, Bolivia</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>San Pablo</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://earthquake.usgs.gov/earthquakes/eventpage/us6000u49c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-23:viento:2</t>
+          <t>clima:Santa Cruz:2026-10-22:viento:1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-23: 83.9 km/h de ráfagas pronosticadas</t>
+          <t>Santa Cruz 2026-10-22: 67.7 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2948,11 +2948,11 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -3004,33 +3004,33 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>noticia:1hhvre7</t>
+          <t>clima:Santa Cruz:2026-10-23:viento:2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-22 19:36</t>
+          <t>2026-10-22 21:55</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1792712202000</v>
+        <v>1792720528712</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Virgen de Cotoca: Controlan incendio en depósito de materiales plásticos - El Mundo Bolivia</t>
+          <t>Santa Cruz 2026-10-23: 83.9 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -3049,18 +3049,18 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>El Mundo Bolivia</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>-17.764</v>
+        <v>-17.78</v>
       </c>
       <c r="N35" t="n">
-        <v>-62.903</v>
+        <v>-63.18</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Cotoca, Santa Cruz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -3070,32 +3070,32 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>Cotoca</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcDF6VE5FNzRaWGRuUzFKeXhnZ21DZTRaaEtrVEJEa1Z3ejg2VG1ONG1ENmlDWlkyVjlkQkJwS2F1XzBGMFQwSHd4OEwxTW1PbHdGcUh1ckV6SGpDd2hiN0dkeUVTcnFXT3RjOU1kLXZtVVdZY2hkZS1pcVpVUFhnRktqcHY5UnBrY0xUMDRETjl6N0pXT3A5amxhMA?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>noticia:bksnde</t>
+          <t>noticia:1hhvre7</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-22 17:01</t>
+          <t>2026-10-22 19:36</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1792702880000</v>
+        <v>1792712202000</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Reportan un incendio cerca de la carretera a Cotoca - eju.tv</t>
+          <t>Virgen de Cotoca: Controlan incendio en depósito de materiales plásticos - El Mundo Bolivia</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>eju.tv</t>
+          <t>El Mundo Bolivia</t>
         </is>
       </c>
       <c r="M36" t="n">
@@ -3153,27 +3153,27 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPNGtpbnBfRnRBalVudnBlZHdVQ0ZSaUplZmtvTGE0aTQzdkxWS3d4My1EZEJ1UE9FNFQ3RmpyZGVsbS1qNEM1QUVFRFAxM2pYT1VqQzRuVjRtZnVNUGlKODNMc0F1a3l6TUpuQmtlUWNlVTVEWWU5ZGZtQm5LWUp3Sg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcDF6VE5FNzRaWGRuUzFKeXhnZ21DZTRaaEtrVEJEa1Z3ejg2VG1ONG1ENmlDWlkyVjlkQkJwS2F1XzBGMFQwSHd4OEwxTW1PbHdGcUh1ckV6SGpDd2hiN0dkeUVTcnFXT3RjOU1kLXZtVVdZY2hkZS1pcVpVUFhnRktqcHY5UnBrY0xUMDRETjl6N0pXT3A5amxhMA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>noticia:17hz69v</t>
+          <t>noticia:bksnde</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-22 13:05</t>
+          <t>2026-10-22 17:01</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1792688709000</v>
+        <v>1792702880000</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Accidente en El Sillar deja al menos 29 heridos - La Razón Digital Bolivia</t>
+          <t>Reportan un incendio cerca de la carretera a Cotoca - eju.tv</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3182,18 +3182,18 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -3205,37 +3205,53 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>La Razón Digital Bolivia</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
+          <t>eju.tv</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>-17.764</v>
+      </c>
+      <c r="N37" t="n">
+        <v>-62.903</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Cotoca, Santa Cruz</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Cotoca</t>
+        </is>
+      </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPaXhTdm45YWZnWVFxVzJnb1ZwbUN4SmUtLVdJN0VJdFZBamRyQmFxN0RZelBfTklaSTVyOUZ3ajQ5MFB2TEN4Ukd6TE5ORFY5SEROVk1CZ25sRWJ1QnRBdTVfTktlby1NWXhaVWI5YnRvaDZWbHVjdDVoeFp5Tk5veFk5a19MSWJqcEJVV0dzV3k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPNGtpbnBfRnRBalVudnBlZHdVQ0ZSaUplZmtvTGE0aTQzdkxWS3d4My1EZEJ1UE9FNFQ3RmpyZGVsbS1qNEM1QUVFRFAxM2pYT1VqQzRuVjRtZnVNUGlKODNMc0F1a3l6TUpuQmtlUWNlVTVEWWU5ZGZtQm5LWUp3Sg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>noticia:1f1qb0</t>
+          <t>noticia:17hz69v</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-22 12:09</t>
+          <t>2026-10-22 13:05</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1792685373000</v>
+        <v>1792688709000</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Accidente en el tramo Locotal–Villa Tunari: la vía está transitable con precaución - Red Uno</t>
+          <t>Accidente en El Sillar deja al menos 29 heridos - La Razón Digital Bolivia</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3244,18 +3260,18 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -3267,73 +3283,57 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Red Uno</t>
-        </is>
-      </c>
-      <c r="M38" t="n">
-        <v>-16.556</v>
-      </c>
-      <c r="N38" t="n">
-        <v>-65.569</v>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>Villa Tunari, Cochabamba</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>Villa Tunari</t>
-        </is>
-      </c>
+          <t>La Razón Digital Bolivia</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTFozcEEwNXBqV19sS2VibXh0MGt0QlhsX1djSTFGQW5zNlFLRHZpNVVnZ1JmWDQ4LVRHX2Rmb3B5UU9qV0FZQmJCaUZYdmwyNG1NenJ4Qzlzd0NJTGs1SjMxdFRtRFBzSUkybGJfZFFaNFZBc21FSUJYSFVkQkVkSEhQaGw0UFVzeXctZHo3cjNsYm5weXJlOU1wcmFncnNhMC1BQUpvNWlDX1NxZXU4b09kVFFWR2tSVEk2UTdXXzB3TjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPaXhTdm45YWZnWVFxVzJnb1ZwbUN4SmUtLVdJN0VJdFZBamRyQmFxN0RZelBfTklaSTVyOUZ3ajQ5MFB2TEN4Ukd6TE5ORFY5SEROVk1CZ25sRWJ1QnRBdTVfTktlby1NWXhaVWI5YnRvaDZWbHVjdDVoeFp5Tk5veFk5a19MSWJqcEJVV0dzV3k?oc=5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>noticia:wi18tm</t>
+          <t>noticia:1f1qb0</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-22 11:53</t>
+          <t>2026-10-22 12:09</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1792684426000</v>
+        <v>1792685373000</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Accidente en El Sillar deja heridos y derrame de combustible: esto es lo último que se sabe - Red Uno</t>
+          <t>Accidente en el tramo Locotal–Villa Tunari: la vía está transitable con precaución - Red Uno</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>tecnológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -3348,54 +3348,70 @@
           <t>Red Uno</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
+      <c r="M39" t="n">
+        <v>-16.556</v>
+      </c>
+      <c r="N39" t="n">
+        <v>-65.569</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Villa Tunari, Cochabamba</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Villa Tunari</t>
+        </is>
+      </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPZHNBTEdaQm5Wby1lTF9mWlQ2aGg0MVc4S0MwVWJ3dUJ5WWU5X3IwYWhKRjk5VWtYWEJHRDF4QldVc29laVNPSTJNWFBDSkNFQlFSYTJUXzNMNF9hckFBN1I2T2xoQUtYQ2V6MDNTZHhHVk9qeTBCdHRpM2ZLd0pyOFRweUUxX19STzRHTHg5VUY5d1lhS0tDeXpCdklqcTZGT1J4R0xnSDhoak1EZ2dtNUhSTUV6b1o0U0VSdWY5X0E3U05Tc1dYVEN2WFZUeFhPMTBJTmowNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTFozcEEwNXBqV19sS2VibXh0MGt0QlhsX1djSTFGQW5zNlFLRHZpNVVnZ1JmWDQ4LVRHX2Rmb3B5UU9qV0FZQmJCaUZYdmwyNG1NenJ4Qzlzd0NJTGs1SjMxdFRtRFBzSUkybGJfZFFaNFZBc21FSUJYSFVkQkVkSEhQaGw0UFVzeXctZHo3cjNsYm5weXJlOU1wcmFncnNhMC1BQUpvNWlDX1NxZXU4b09kVFFWR2tSVEk2UTdXXzB3TjA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>noticia:12gfagq</t>
+          <t>noticia:wi18tm</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-22 11:28</t>
+          <t>2026-10-22 11:53</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1792682880000</v>
+        <v>1792684426000</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Reportan triple colisión entre dos camiones y un bus en la carretera Cochabamba-Santa Cruz - FmBolivia</t>
+          <t>Accidente en El Sillar deja heridos y derrame de combustible: esto es lo último que se sabe - Red Uno</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>tecnológica</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -3403,37 +3419,21 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>FmBolivia; Red Uno</t>
-        </is>
-      </c>
-      <c r="M40" t="n">
-        <v>-17.39</v>
-      </c>
-      <c r="N40" t="n">
-        <v>-66.16</v>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>Cochabamba, Cochabamba</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
+          <t>Red Uno</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNMTNBaFZNMU9SR25vdVBuNXlZY3g4VkFWYXRiQnNSaUFjemZhUHZWNHg4V2owU2xfNndBak94TnU2cHNUVXdNNWl2eUdHZVNMbVZweTR5M0o0bWdTNUN4QkoxUkI2TDBmVE03M09zRGhJRVFzV0tPZ1NCWEJLUkt1ZGN4UGduOUZMQnJoM0tMYTh0ZlFxaFJNUkJqaWFPazRlMzN3ajhjUEdUYXlZRndpb3RSdTFCX2tCZGJxQ0x4SlBISWJsRVoyN3ZR?oc=5 | https://news.google.com/rss/articles/CBMirwFBVV95cUxNNUROMzd1UDJRWVZZQ011cFd2c1FSdER1ZzdleU04cXpwYk5HaUZrLXoyU2NzdFk1dnNRUndhUWt0cG9DX09rSjlLcDItU0tzcmQtS3E4dDQ4ZF9HdGJLdk13ek9BNHJUWVlCcklrM25rZ01RbXhLalRBT1FGdDNReHdlTFZkNkJ5ZFd3N3NZVFVmOFUxbEhHN0RsaUxiSVZsM0lXVEFYSHVRQlhsOEtJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPZHNBTEdaQm5Wby1lTF9mWlQ2aGg0MVc4S0MwVWJ3dUJ5WWU5X3IwYWhKRjk5VWtYWEJHRDF4QldVc29laVNPSTJNWFBDSkNFQlFSYTJUXzNMNF9hckFBN1I2T2xoQUtYQ2V6MDNTZHhHVk9qeTBCdHRpM2ZLd0pyOFRweUUxX19STzRHTHg5VUY5d1lhS0tDeXpCdklqcTZGT1J4R0xnSDhoak1EZ2dtNUhSTUV6b1o0U0VSdWY5X0E3U05Tc1dYVEN2WFZUeFhPMTBJTmowNA?oc=5</t>
         </is>
       </c>
     </row>
@@ -3604,7 +3604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S62"/>
+  <dimension ref="A1:S63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3707,27 +3707,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>manual:1c1299f3</t>
+          <t>noticia:4blj1l</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>registro</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-25 12:44</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1792946640000</t>
-        </is>
+          <t>2026-10-25 12:59</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1792947573000</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Registro abierto (sin verificar)</t>
+          <t>La Patria Bolivia</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -3735,90 +3733,82 @@
           <t>antropogénica</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G2" t="n">
+        <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Vuelco de minibus</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Registro de prueba del sistema. Ignorar. | Lugar indicado: Caranavi, La Paz | Registro abierto, sin verificar.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>-15.813</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>-67.463</t>
-        </is>
+          <t>Santa Cruz: Dos cisternas se incendian tras colisionar - La Patria Bolivia</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQbHdpcUF6dXpjaW1TT1ZmdGJtUUVLMTNMRTVqVkFUdkNsZlRvenVkckFUWmI4NDFmc2ZHd2RVcWRSSE5YRVpOTUlESGw2V3JONXpwS0RISGNZd01SejNuMkY4NzFYYXp4aWo2RE9VMkFYUkVwZ3JRRmM5MWlRSjlBWk16azdkQ3FjdEtkaWc5NERkTzk2SllVOQ?oc=5</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-17.781</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-63.139</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Caranavi, La Paz</t>
+          <t>Santa Cruz, Santa Cruz</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>nombre de municipio indicado por quien registra</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Caranavi</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>noticia:oww2zc</t>
+          <t>manual:1c1299f3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>registro</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-25 12:08</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>1792944531000</v>
+          <t>2026-10-25 12:44</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1792946640000</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>Registro abierto (sin verificar)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -3826,62 +3816,72 @@
           <t>antropogénica</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Cierran la carretera a Camiri: dos cisternas chocan y provocan un voraz incendio - Red Uno</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQLXlqSFdvWUVhQUNadnpkdE5lUTZQS0lobThzUTZWbDNJTE94alVhaDBaYU9Fd09SSGt3UlR3Y0dfZlNIcml1ZktnWjctNk1Na3V4S0tINFNkMXM0OHBoV2lCTTBiYXlPUTA3T2ZkeXE2RElYWjhfVHd3Nng1Z0E4alBmOFI5NDFwX09kazZlSWl2OVR2ZVR6MDhvSHFnSmJKbTFXSEFDNFFYcWVDNGtYWEQ0bDhJel9CaEpEZWZ4SWN0TE9Ya0E?oc=5</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>-20.05</v>
-      </c>
-      <c r="O3" t="n">
-        <v>-63.486</v>
+          <t>Vuelco de minibus</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Registro de prueba del sistema. Ignorar. | Lugar indicado: Caranavi, La Paz | Registro abierto, sin verificar.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>-15.813</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>-67.463</t>
+        </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Camiri, Santa Cruz</t>
+          <t>Caranavi, La Paz</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
+          <t>nombre de municipio indicado por quien registra</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Camiri</t>
+          <t>Caranavi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>noticia:1a4hhsd</t>
+          <t>noticia:oww2zc</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3891,15 +3891,15 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-25 11:56</t>
+          <t>2026-10-25 12:08</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1792943794000</v>
+        <v>1792944531000</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Opinión Bolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -3917,13 +3917,13 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Reportan el incendio de dos camiones cisterna en la carretera a Camiri - Opinión Bolivia</t>
+          <t>Cierran la carretera a Camiri: dos cisternas chocan y provocan un voraz incendio - Red Uno</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNUTdxSzBJVTZnajZQUXhyTVhwMlpvU0tyZGVBYnFwV2kyZWthenNRT1FDRVJFZnk4ZndGTFQ0cnFXZmZ1WHZaMFhUbWo0SWkzcjcxbjJwU3pKUXR4WEVZLVlRNFpxOUVMY2NNNUZsbmJSMk9xZG1sTklEdEtGSXJyUUp5b0R2dVpYcHJLdTRNRlRjcWpNNXg4c0Z4UWwteFc2dDRqVmpnQnFfQXgwN0twTzl4ZWhYdUtYWGfSAboBQVVfeXFMTVE3cUswSVU2Z2o2UFF4ck1YcDJab1NLcmRlQWJxcFdpMmVrYXpzUU9RQ0VSRWZ5OGZ3RkxUNHJxV2ZmdVh2WjBYVG1qNElpM3I3MW4ycFN6SlF0eFhFWS1ZUTRacTlFTGNjTTVGbG5iUjJPcWRtbE5JRHRLRklyclFKeW9EdnVaWHByS3U0TUZUY3FqTTV4OHNGeFFsLXhXNnQ0alZqZ0JxX0F4MDdLcE85eGVoWHVLWFhn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQLXlqSFdvWUVhQUNadnpkdE5lUTZQS0lobThzUTZWbDNJTE94alVhaDBaYU9Fd09SSGt3UlR3Y0dfZlNIcml1ZktnWjctNk1Na3V4S0tINFNkMXM0OHBoV2lCTTBiYXlPUTA3T2ZkeXE2RElYWjhfVHd3Nng1Z0E4alBmOFI5NDFwX09kazZlSWl2OVR2ZVR6MDhvSHFnSmJKbTFXSEFDNFFYcWVDNGtYWEQ0bDhJel9CaEpEZWZ4SWN0TE9Ya0E?oc=5</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -3962,7 +3962,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>noticia:1at00ey</t>
+          <t>noticia:1a4hhsd</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3972,15 +3972,15 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-25 11:19</t>
+          <t>2026-10-25 11:56</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1792941547000</v>
+        <v>1792943794000</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>Opinión Bolivia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3998,13 +3998,13 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Dos cisternas chocan y provocan voraz incendio en la ruta a Camiri - Red Uno</t>
+          <t>Reportan el incendio de dos camiones cisterna en la carretera a Camiri - Opinión Bolivia</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPTTF0OUdVS1c1a0lZWmk3bGxHdDJIalpWZTRyQTY3eWE2a2dWOHlsaldKZXpSLWN5c3BkUWdBRkJuSzhHdWl2ZjgwTFFFYnd0aTAxZ3dJU0hCekNZNm9aTTJSZUNfQjVIM3FrUUJ4NXAwa3paZ3BEek9xTVZNQWdnN01xRHloV1ZXZHV6N0JpUWo3RE9DMlFGdkNnWkloTjVVY3RBR1RSRUJJWFVtby1fMWFMNTdLZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNUTdxSzBJVTZnajZQUXhyTVhwMlpvU0tyZGVBYnFwV2kyZWthenNRT1FDRVJFZnk4ZndGTFQ0cnFXZmZ1WHZaMFhUbWo0SWkzcjcxbjJwU3pKUXR4WEVZLVlRNFpxOUVMY2NNNUZsbmJSMk9xZG1sTklEdEtGSXJyUUp5b0R2dVpYcHJLdTRNRlRjcWpNNXg4c0Z4UWwteFc2dDRqVmpnQnFfQXgwN0twTzl4ZWhYdUtYWGfSAboBQVVfeXFMTVE3cUswSVU2Z2o2UFF4ck1YcDJab1NLcmRlQWJxcFdpMmVrYXpzUU9RQ0VSRWZ5OGZ3RkxUNHJxV2ZmdVh2WjBYVG1qNElpM3I3MW4ycFN6SlF0eFhFWS1ZUTRacTlFTGNjTTVGbG5iUjJPcWRtbE5JRHRLRklyclFKeW9EdnVaWHByS3U0TUZUY3FqTTV4OHNGeFFsLXhXNnQ0alZqZ0JxX0F4MDdLcE85eGVoWHVLWFhn?oc=5</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -4043,7 +4043,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>noticia:1uf38hl</t>
+          <t>noticia:1at00ey</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4053,11 +4053,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-25 10:59</t>
+          <t>2026-10-25 11:19</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1792940350000</v>
+        <v>1792941547000</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -4079,13 +4079,13 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>¡Cisterna con combustible en llamas! Reportan impresionante incendio en la carretera a Camiri - Red Uno</t>
+          <t>Dos cisternas chocan y provocan voraz incendio en la ruta a Camiri - Red Uno</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxORUhqeWpKY1FHRWoxaHN0UXFzS3dpeHh6N0NwLUJOZTlZcDVoNHN0VnI0by1qMWtZZEkxVmtUNjdNTFhjaEFQU2IyMlNwZW95WFBzbFJPVVB6TjJtdjNENk1LWVlsMUxUUzBNVzkxRk1HZ3lQU0s2M1lRVlRuaXlkMmJrd3AyTGpIdXItNkhlU3dhTzBRME56Rm1DSlZCYjNxSnNTbTFqNWRoUkdraHhlREhuYldqeFk2N3poWEx2M08?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPTTF0OUdVS1c1a0lZWmk3bGxHdDJIalpWZTRyQTY3eWE2a2dWOHlsaldKZXpSLWN5c3BkUWdBRkJuSzhHdWl2ZjgwTFFFYnd0aTAxZ3dJU0hCekNZNm9aTTJSZUNfQjVIM3FrUUJ4NXAwa3paZ3BEek9xTVZNQWdnN01xRHloV1ZXZHV6N0JpUWo3RE9DMlFGdkNnWkloTjVVY3RBR1RSRUJJWFVtby1fMWFMNTdLZw?oc=5</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -4124,7 +4124,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>noticia:1sg8pi0</t>
+          <t>noticia:1uf38hl</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4134,11 +4134,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-25 09:59</t>
+          <t>2026-10-25 10:59</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1792936752000</v>
+        <v>1792940350000</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -4160,13 +4160,13 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Bus de agrupación musical sufre accidente rumbo al trópico de Cochabamba | VIDEO - Red Uno</t>
+          <t>¡Cisterna con combustible en llamas! Reportan impresionante incendio en la carretera a Camiri - Red Uno</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOVDVzVTJNM2JuQ25sMThEaVZNOUNRd3FGT3RhVnFrZXZ2NDQ1YlluTVdhbVNUQnA1MGNESHRSWVUzbC1kRVh3OTR0emtlTG91cmRWeFJ5dk5zb3p2WFRyMEJUV3FNRnY1WHhRUU9WLTlJcmNyNXJZZFdoM0JoZjNpa3hjUXhMM0xrUDJab2VadkM5RWZYQ3lWZTVDdzg1akxJT2lxcDVNNzI0NG1hejdfdkUyTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxORUhqeWpKY1FHRWoxaHN0UXFzS3dpeHh6N0NwLUJOZTlZcDVoNHN0VnI0by1qMWtZZEkxVmtUNjdNTFhjaEFQU2IyMlNwZW95WFBzbFJPVVB6TjJtdjNENk1LWVlsMUxUUzBNVzkxRk1HZ3lQU0s2M1lRVlRuaXlkMmJrd3AyTGpIdXItNkhlU3dhTzBRME56Rm1DSlZCYjNxSnNTbTFqNWRoUkdraHhlREhuYldqeFk2N3poWEx2M08?oc=5</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -4176,14 +4176,14 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-17.39</v>
+        <v>-20.05</v>
       </c>
       <c r="O7" t="n">
-        <v>-66.16</v>
+        <v>-63.486</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Cochabamba, Cochabamba</t>
+          <t>Camiri, Santa Cruz</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -4193,19 +4193,19 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Camiri</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>noticia:167wlhz</t>
+          <t>noticia:1sg8pi0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4215,11 +4215,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-25 07:53</t>
+          <t>2026-10-25 09:59</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1792929231000</v>
+        <v>1792936752000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -4241,13 +4241,13 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>¡A sacar el paraguas! Santa cruz amanece con lluvia, frío y complicaciones en el tránsito vehicular - Red Uno</t>
+          <t>Bus de agrupación musical sufre accidente rumbo al trópico de Cochabamba | VIDEO - Red Uno</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOY1ZpYktLR3pUQXotUndVR3puUzVHbW1YTzNyUmJvUHB4Q2JmelRvOEdaRldOUm1xLVJnbGR5VWcxTjNEM3ZUYktCUWtVM0hKSjFuRGdpX0JxN0M5MVZBSG1aVURyVWktdmxwbUtRT19ydU5LdzNTZ2Zpb2ozdHlMUUdTVlAyVk4xODBnV0hyTXdVVndyNzV3VC1KMzFnV3lpcFFXSk9MdDZOTWlWakNwT1FnNDh6QVdjazVYZDVVMkdaLU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOVDVzVTJNM2JuQ25sMThEaVZNOUNRd3FGT3RhVnFrZXZ2NDQ1YlluTVdhbVNUQnA1MGNESHRSWVUzbC1kRVh3OTR0emtlTG91cmRWeFJ5dk5zb3p2WFRyMEJUV3FNRnY1WHhRUU9WLTlJcmNyNXJZZFdoM0JoZjNpa3hjUXhMM0xrUDJab2VadkM5RWZYQ3lWZTVDdzg1akxJT2lxcDVNNzI0NG1hejdfdkUyTQ?oc=5</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -4257,14 +4257,14 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-17.781</v>
+        <v>-17.39</v>
       </c>
       <c r="O8" t="n">
-        <v>-63.139</v>
+        <v>-66.16</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Santa Cruz, Santa Cruz</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -4274,19 +4274,19 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Cochabamba</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>noticia:bzr7eh</t>
+          <t>noticia:167wlhz</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4296,39 +4296,39 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-25 07:09</t>
+          <t>2026-10-25 07:53</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1792926572000</v>
+        <v>1792929231000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>hidrológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Alerta naranja por riesgo de desbordes de ríos - El Diario - Bolivia</t>
+          <t>¡A sacar el paraguas! Santa cruz amanece con lluvia, frío y complicaciones en el tránsito vehicular - Red Uno</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNNGZKSDVaZkowWUFGSEUyTWR3d3dsc04waFBLLWUtcVpiTDYzbmNtYTN1RkFLbjAwN3dxT0xZc3pqc3REUXduZVltQ2Fud1BZLTh1bTNiTEJueVUwV0dERS1iUXZqMHd0UnFrQ3E2SFAzbm5lQ1I4U29MaHJFbWFvdVRTeFY4Wl9rSmc3RkpaQ2xwX0oz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOY1ZpYktLR3pUQXotUndVR3puUzVHbW1YTzNyUmJvUHB4Q2JmelRvOEdaRldOUm1xLVJnbGR5VWcxTjNEM3ZUYktCUWtVM0hKSjFuRGdpX0JxN0M5MVZBSG1aVURyVWktdmxwbUtRT19ydU5LdzNTZ2Zpb2ozdHlMUUdTVlAyVk4xODBnV0hyTXdVVndyNzV3VC1KMzFnV3lpcFFXSk9MdDZOTWlWakNwT1FnNDh6QVdjazVYZDVVMkdaLU0?oc=5</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -4337,21 +4337,37 @@
       <c r="M9" t="n">
         <v>0</v>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>-17.781</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-63.139</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Santa Cruz, Santa Cruz</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Santa Cruz de la Sierra</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>noticia:1fo4ig4</t>
+          <t>noticia:bzr7eh</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4361,43 +4377,43 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-25 01:08</t>
+          <t>2026-10-25 07:09</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1792904880000</v>
+        <v>1792926572000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>diarioelpueblo.com.pe</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>hidrológica</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>roja</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
+          <t>Alerta naranja por riesgo de desbordes de ríos - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQcmFrT3dwcEs0X3U2NWxnOGJwNnI2WHdWTGZYbzEyNnJzUWhkbU9TRWhfSlB5UkMwX2gyMmxYUmVNWmxNOVR6V0twRHpFMTVIYjBKbHQ2TXN2d2w5dkFpcWJCcUJMZldaX01sNWtQV2ZJOGpRVzR3NDVIU0pJc1BNVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNNGZKSDVaZkowWUFGSEUyTWR3d3dsc04waFBLLWUtcVpiTDYzbmNtYTN1RkFLbjAwN3dxT0xZc3pqc3REUXduZVltQ2Fud1BZLTh1bTNiTEJueVUwV0dERS1iUXZqMHd0UnFrQ3E2SFAzbm5lQ1I4U29MaHJFbWFvdVRTeFY4Wl9rSmc3RkpaQ2xwX0oz?oc=5</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -4416,7 +4432,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>noticia:r1uot6</t>
+          <t>noticia:1fo4ig4</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4426,15 +4442,15 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-24 20:00</t>
+          <t>2026-10-25 01:08</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1792886439000</v>
+        <v>1792904880000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
+          <t>diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -4443,61 +4459,45 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>roja</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>vuelco deja heridos en ruta Oruro – Huanuni - La Patria Bolivia</t>
+          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNNDQtMG1KT1lLWW5nem9Jbm5JWDZKNlRWZmFmRlBxWDlDeXlSWnJ5d2NsTlpxa0JIS25oVWVZOC1majZVbWhOVDIxR0dLOFlzY2VpVzVoVk1mQnF3dXVwLUFZVHc1UjlXZzF5T05CY3U0ZldLVkw1VzBTek5zanpjQW1xalltWHNiaXI3dTNR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQcmFrT3dwcEs0X3U2NWxnOGJwNnI2WHdWTGZYbzEyNnJzUWhkbU9TRWhfSlB5UkMwX2gyMmxYUmVNWmxNOVR6V0twRHpFMTVIYjBKbHQ2TXN2d2w5dkFpcWJCcUJMZldaX01sNWtQV2ZJOGpRVzR3NDVIU0pJc1BNVg?oc=5</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>-17.97</v>
-      </c>
-      <c r="O11" t="n">
-        <v>-67.11</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Oruro, Oruro</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>Oruro</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>Oruro</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>noticia:1ytw450</t>
+          <t>noticia:r1uot6</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4507,15 +4507,15 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-24 18:58</t>
+          <t>2026-10-24 20:00</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1792882686000</v>
+        <v>1792886439000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>diarioelpueblo.com.pe</t>
+          <t>La Patria Bolivia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -4524,45 +4524,61 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>roja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
+          <t>vuelco deja heridos en ruta Oruro – Huanuni - La Patria Bolivia</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNZ1U3bEVuaVdjVE1zSU9lOHJZTVRZLVZaemhldGNnT1JBWDJvbzdvM3paVVNhLUlyWHF2akNuSXJOLXdyTGRuejRlV1FuMjVkTjA3NmdRdmgtRWlUeTFBV1dEMzBvejBxaXZJdUZZWkRVTF9VLU5BcjFGZGFEQ09WWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNNDQtMG1KT1lLWW5nem9Jbm5JWDZKNlRWZmFmRlBxWDlDeXlSWnJ5d2NsTlpxa0JIS25oVWVZOC1majZVbWhOVDIxR0dLOFlzY2VpVzVoVk1mQnF3dXVwLUFZVHc1UjlXZzF5T05CY3U0ZldLVkw1VzBTek5zanpjQW1xalltWHNiaXI3dTNR?oc=5</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-17.97</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-67.11</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Oruro, Oruro</t>
+        </is>
+      </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>noticia:1wcb22g</t>
+          <t>noticia:1ytw450</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4572,43 +4588,43 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-24 17:47</t>
+          <t>2026-10-24 18:58</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1792878475000</v>
+        <v>1792882686000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Mundo Bolivia</t>
+          <t>diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>hidrológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>roja</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Alerta naranja por ingreso de frente frío y desbordes de ríos en 6 departamentos - El Mundo Bolivia</t>
+          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPZW00RkxJSklTelNrS2hqczJDWHlwcENFX2lnSEUyTEFPaDFRQ2JvMUcyd3NfYjg0UE9ORGxHRzB4ZDh3U0hQQ1JSQlhsaUY4N3ByMUUxei1SaUZnNlp6T3hsLVdiMGhKaXhsV1FNSUNQMHlvQ19qdk56SEF0d2RXVFctS0VPT25kNGZCRDdvZ2dxU0VoUUJKU0ZBd0ZycFNEZFh0T3ZjOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNZ1U3bEVuaVdjVE1zSU9lOHJZTVRZLVZaemhldGNnT1JBWDJvbzdvM3paVVNhLUlyWHF2akNuSXJOLXdyTGRuejRlV1FuMjVkTjA3NmdRdmgtRWlUeTFBV1dEMzBvejBxaXZJdUZZWkRVTF9VLU5BcjFGZGFEQ09WWQ?oc=5</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -4627,7 +4643,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>noticia:1c1ju1f</t>
+          <t>noticia:1wcb22g</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4637,46 +4653,46 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-24 17:02</t>
+          <t>2026-10-24 17:47</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1792875752000</v>
+        <v>1792878475000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>La Razón Digital Bolivia</t>
+          <t>El Mundo Bolivia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>hidrológica</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a los Yungas deja siete heridos - La Razón Digital Bolivia</t>
+          <t>Alerta naranja por ingreso de frente frío y desbordes de ríos en 6 departamentos - El Mundo Bolivia</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPTGQwaVBfdG1JdVRMUTN4LVVvN0ppc3dreDJVVllDR3RmX0xpMzB4b0pvVTNSV1B6T0ZEWTdEZkNsRUdSNzhLaC1CWHN5WktNWk1nRWpTdVZiYjI3TlJlX2xlVTI5MjlRU2hiY1gteml4YWVFbDNPSVRBZmtITlQzbmhaUXVmcThRa2xsQTJIOXZuNzlSdm12MEdyOEZHdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPZW00RkxJSklTelNrS2hqczJDWHlwcENFX2lnSEUyTEFPaDFRQ2JvMUcyd3NfYjg0UE9ORGxHRzB4ZDh3U0hQQ1JSQlhsaUY4N3ByMUUxei1SaUZnNlp6T3hsLVdiMGhKaXhsV1FNSUNQMHlvQ19qdk56SEF0d2RXVFctS0VPT25kNGZCRDdvZ2dxU0VoUUJKU0ZBd0ZycFNEZFh0T3ZjOA?oc=5</t>
         </is>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -4692,7 +4708,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>noticia:14iwzop</t>
+          <t>noticia:1c1ju1f</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4702,15 +4718,15 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-24 13:40</t>
+          <t>2026-10-24 17:02</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1792863623000</v>
+        <v>1792875752000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>EL DÍA - Noticias de Bolivia para el mundo</t>
+          <t>La Razón Digital Bolivia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -4728,13 +4744,13 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a Mayaya deja siete heridos de la agrupación Los Chicos Fieles - EL DÍA - Noticias de Bolivia para el mundo</t>
+          <t>Accidente en la carretera a los Yungas deja siete heridos - La Razón Digital Bolivia</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPeGd3VWpCWXJ0YTJIeDJLcktzWG1jdUh0TjFXb01wSTkxbHNXZU94VWNDMkxnTjlJZVdpbkprMEY2NE80RXYyUWxUQXVnbl9lUXR2b28zTEh6cTJLVEQ4TUNja2kzRlhadVBFZFVwV1U2TlhseXZMZ20zZTZiUFpWRjdCOWNBMHU5XzdMV3JqQjV4TEE3bHRMOXR6Nm55eHZUNnFHSDdVRk8zVkY4RkVsUUtUN0JYdkREWGZncmJ3ZWc2T1BuUm1ZLTlfcHVabFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPTGQwaVBfdG1JdVRMUTN4LVVvN0ppc3dreDJVVllDR3RmX0xpMzB4b0pvVTNSV1B6T0ZEWTdEZkNsRUdSNzhLaC1CWHN5WktNWk1nRWpTdVZiYjI3TlJlX2xlVTI5MjlRU2hiY1gteml4YWVFbDNPSVRBZmtITlQzbmhaUXVmcThRa2xsQTJIOXZuNzlSdm12MEdyOEZHdw?oc=5</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -4757,7 +4773,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>noticia:1ukcn97</t>
+          <t>noticia:14iwzop</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4767,15 +4783,15 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-24 13:26</t>
+          <t>2026-10-24 13:40</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1792862794000</v>
+        <v>1792863623000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>El Deber</t>
+          <t>EL DÍA - Noticias de Bolivia para el mundo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -4793,20 +4809,20 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Esta es la lista preliminar de los heridos en el accidente del grupo 'Los chicos fieles', el conductor está grave - El Deber</t>
+          <t>Accidente en la carretera a Mayaya deja siete heridos de la agrupación Los Chicos Fieles - EL DÍA - Noticias de Bolivia para el mundo</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOczZKbFd1QzRpak92LXpPWXZXQXJObnBQTG9qRFBlUUV5dThMWXhzckFFUHAyb2thU1JwRmJDSEZfaEdTUXh1bjZvQWpYMGhfUno3cWZ4MGpldEpoQXhzSlVzTm5LLW9OcjB2MWRsdHQ2UlI2SjEtZ085ZTR5Z3pEVmtBTF9lc29Kd0RhaTRUWkM4eGZJNWhBSXZqWmxuNW10dlQwYW9mdzItcWZWTkU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPeGd3VWpCWXJ0YTJIeDJLcktzWG1jdUh0TjFXb01wSTkxbHNXZU94VWNDMkxnTjlJZVdpbkprMEY2NE80RXYyUWxUQXVnbl9lUXR2b28zTEh6cTJLVEQ4TUNja2kzRlhadVBFZFVwV1U2TlhseXZMZ20zZTZiUFpWRjdCOWNBMHU5XzdMV3JqQjV4TEE3bHRMOXR6Nm55eHZUNnFHSDdVRk8zVkY4RkVsUUtUN0JYdkREWGZncmJ3ZWc2T1BuUm1ZLTlfcHVabFE?oc=5</t>
         </is>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
@@ -4822,7 +4838,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>noticia:2avehj</t>
+          <t>noticia:1ukcn97</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4832,20 +4848,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-24 12:53</t>
+          <t>2026-10-24 13:26</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1792860813000</v>
+        <v>1792862794000</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>El Deber</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>climatológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4858,52 +4874,36 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Sequía en Cochabamba: más de un centenar de cabezas de ganado murieron en el cono sur - Red Uno</t>
+          <t>Esta es la lista preliminar de los heridos en el accidente del grupo 'Los chicos fieles', el conductor está grave - El Deber</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOOFQxc2Vzc0QwS19ydC13RkRPZnZQU3JkSTl5U3kzdUdMSldTcm5HVEhWRzZyN19CLUlwcUs4MW03Ui1obVBtdzQ3QWFQc1RKdzh3MXJ5QkpRS2pRNm50V1lVb09ScGJnaVVlemVfZlRsWjdObnRmR1FGMnlMMHAyc2pMandndy10T2twcWx6OFh4UHdvbVlFbllwME9WQ2pQVjNTQzBxeTg5YnF3bDREeHVDYXpObFFIaTZZQWtYUE12cGQ1ZGRhT0syNjVhZWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOczZKbFd1QzRpak92LXpPWXZXQXJObnBQTG9qRFBlUUV5dThMWXhzckFFUHAyb2thU1JwRmJDSEZfaEdTUXh1bjZvQWpYMGhfUno3cWZ4MGpldEpoQXhzSlVzTm5LLW9OcjB2MWRsdHQ2UlI2SjEtZ085ZTR5Z3pEVmtBTF9lc29Kd0RhaTRUWkM4eGZJNWhBSXZqWmxuNW10dlQwYW9mdzItcWZWTkU0?oc=5</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-17.39</v>
-      </c>
-      <c r="O17" t="n">
-        <v>-66.16</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Cochabamba, Cochabamba</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>noticia:1ksmg5u</t>
+          <t>noticia:2avehj</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4913,20 +4913,20 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-24 11:43</t>
+          <t>2026-10-24 12:53</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1792856591000</v>
+        <v>1792860813000</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>climatológica</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4939,36 +4939,52 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Embarrancamiento deja heridos a integrantes de Los Chicos Fieles - La Patria Bolivia</t>
+          <t>Sequía en Cochabamba: más de un centenar de cabezas de ganado murieron en el cono sur - Red Uno</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNeEFrOEtOMHZxMW42REFPU0x1MG5oQjlBMkJucWRLZ292alBXekJKeURBN3NLTVVadWI0OWF4UGtSVXBzTE01eWFSU1kyMUhNZ04zMWNMaUxnMDBBZ0EwTktXbjlaVTBUUmNqa3AwY19KNTU2LWh5LW9IVElVdTdnaHFPanJPd2FqMUxzaUhXZmVpYU1saGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOOFQxc2Vzc0QwS19ydC13RkRPZnZQU3JkSTl5U3kzdUdMSldTcm5HVEhWRzZyN19CLUlwcUs4MW03Ui1obVBtdzQ3QWFQc1RKdzh3MXJ5QkpRS2pRNm50V1lVb09ScGJnaVVlemVfZlRsWjdObnRmR1FGMnlMMHAyc2pMandndy10T2twcWx6OFh4UHdvbVlFbllwME9WQ2pQVjNTQzBxeTg5YnF3bDREeHVDYXpObFFIaTZZQWtYUE12cGQ1ZGRhT0syNjVhZWs?oc=5</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-17.39</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-66.16</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Cochabamba, Cochabamba</t>
+        </is>
+      </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>noticia:mlyqgd</t>
+          <t>noticia:1ksmg5u</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4978,15 +4994,15 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-24 11:30</t>
+          <t>2026-10-24 11:43</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1792855818000</v>
+        <v>1792856591000</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Opinión Bolivia</t>
+          <t>La Patria Bolivia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -5004,20 +5020,20 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a Mayaya deja siete heridos de la agrupación Los Chicos Fieles - Opinión Bolivia</t>
+          <t>Embarrancamiento deja heridos a integrantes de Los Chicos Fieles - La Patria Bolivia</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYjNxaHg3YllRRTJYdFd1clAtUlROSGlFNVg5eUVZUGJoOEZ4MWM5QU5WQm1YTDc4NXc3SjhWMUw0TkZfSHlMLUQ1bmpTME1Kb1JaM0ExamFHYTd3VlU4MXRWdTZ1bzh1SGYtbGE1a3dBaG93bjg1OGc0S0JfRE43c3dVMVltN0dQQzNhQUNhM0FjVUNRUDRSamlJYlk2dEJpUTBuY2hBcTFucTVRN0ZtYnc5bzdmTV9LQm1uVUxaZS1tUE9IejhBVDRCdU_SAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNeEFrOEtOMHZxMW42REFPU0x1MG5oQjlBMkJucWRLZ292alBXekJKeURBN3NLTVVadWI0OWF4UGtSVXBzTE01eWFSU1kyMUhNZ04zMWNMaUxnMDBBZ0EwTktXbjlaVTBUUmNqa3AwY19KNTU2LWh5LW9IVElVdTdnaHFPanJPd2FqMUxzaUhXZmVpYU1saGc?oc=5</t>
         </is>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
@@ -5033,7 +5049,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>noticia:irf4jl</t>
+          <t>noticia:mlyqgd</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5075,7 +5091,7 @@
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNMXlMNXFWSWhhWWNDRFFKMncwS2JGWm0tWlJCd2x2RjZhdFhEQ0lBcVlFSS1WRVYxMEVJTWRHcTY3M0stdWhGdnVPRU13X2MwSVRWX25xVUQxa0R6Z1pqQ2dfY0VjUmw2aXFoWFNVNk15N2dBOENZLWlGSWJfMW0zejVoZ3ZwVHVQV1MzbzlnUlpRcWIxMHZxdkItZTc0QmMyRnBmSVRtVnZ5Y3gtdVpYNXFwcGdadGVCU3dRZ3EwOTdiWHU4OXJRdEFoNi1HcnA1U0HSAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYjNxaHg3YllRRTJYdFd1clAtUlROSGlFNVg5eUVZUGJoOEZ4MWM5QU5WQm1YTDc4NXc3SjhWMUw0TkZfSHlMLUQ1bmpTME1Kb1JaM0ExamFHYTd3VlU4MXRWdTZ1bzh1SGYtbGE1a3dBaG93bjg1OGc0S0JfRE43c3dVMVltN0dQQzNhQUNhM0FjVUNRUDRSamlJYlk2dEJpUTBuY2hBcTFucTVRN0ZtYnc5bzdmTV9LQm1uVUxaZS1tUE9IejhBVDRCdU_SAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -5098,7 +5114,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>noticia:1g006zh</t>
+          <t>noticia:irf4jl</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5108,15 +5124,15 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-24 11:25</t>
+          <t>2026-10-24 11:30</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1792855522000</v>
+        <v>1792855818000</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>El Potosí</t>
+          <t>Opinión Bolivia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -5134,13 +5150,13 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a Mayaya deja siete heridos del grupo Los Chicos Fieles - El Potosí</t>
+          <t>Accidente en la carretera a Mayaya deja siete heridos de la agrupación Los Chicos Fieles - Opinión Bolivia</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTC10eC1qSm1WRlY2YzA3VEJqOG1LUkx6bE9PdFYwTFBZMGFjU0RMYXliRkhXcTJHRlVzb0Y4QUU0WWJDQ1plS2NZamZ1YmFadE5qY3g4UE5aYVAwamtCUUNZaDB2YWJTdWRKS3R4a0hHUjVobUl0Y1dYZ2JPczAwak5kN1hjUEwwM1NtUDVWbnAzWTdnRng3RjFValFVVlZPdVZnWFlUODhPOE5aMTROQzVKVjVRS2VoaTlaQnBiUGRTNFk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNMXlMNXFWSWhhWWNDRFFKMncwS2JGWm0tWlJCd2x2RjZhdFhEQ0lBcVlFSS1WRVYxMEVJTWRHcTY3M0stdWhGdnVPRU13X2MwSVRWX25xVUQxa0R6Z1pqQ2dfY0VjUmw2aXFoWFNVNk15N2dBOENZLWlGSWJfMW0zejVoZ3ZwVHVQV1MzbzlnUlpRcWIxMHZxdkItZTc0QmMyRnBmSVRtVnZ5Y3gtdVpYNXFwcGdadGVCU3dRZ3EwOTdiWHU4OXJRdEFoNi1HcnA1U0HSAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -5149,60 +5165,44 @@
       <c r="M21" t="n">
         <v>7</v>
       </c>
-      <c r="N21" t="n">
-        <v>-19.58</v>
-      </c>
-      <c r="O21" t="n">
-        <v>-65.75</v>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Potosí, Potosí</t>
-        </is>
-      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>clima:Potosí:2026-10-24:viento:1</t>
+          <t>noticia:1g006zh</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-24 10:55</t>
+          <t>2026-10-24 11:25</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1792853727284</v>
+        <v>1792855522000</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>El Potosí</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5215,24 +5215,20 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Potosí 2026-10-24: 60.5 km/h de ráfagas pronosticadas</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
-        </is>
-      </c>
+          <t>Accidente en la carretera a Mayaya deja siete heridos del grupo Los Chicos Fieles - El Potosí</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTC10eC1qSm1WRlY2YzA3VEJqOG1LUkx6bE9PdFYwTFBZMGFjU0RMYXliRkhXcTJHRlVzb0Y4QUU0WWJDQ1plS2NZamZ1YmFadE5qY3g4UE5aYVAwamtCUUNZaDB2YWJTdWRKS3R4a0hHUjVobUl0Y1dYZ2JPczAwak5kN1hjUEwwM1NtUDVWbnAzWTdnRng3RjFValFVVlZPdVZnWFlUODhPOE5aMTROQzVKVjVRS2VoaTlaQnBiUGRTNFk?oc=5</t>
         </is>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N22" t="n">
         <v>-19.58</v>
@@ -5242,12 +5238,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Potosí, Potosí</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>capital (pronóstico puntual)</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -5264,25 +5260,25 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>noticia:1ax0bpy</t>
+          <t>clima:Potosí:2026-10-24:viento:1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-24 10:32</t>
+          <t>2026-10-24 10:55</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1792852364000</v>
+        <v>1792853727284</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Que Pasa Salta</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -5291,22 +5287,26 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Creció el Bermejo tras la tormenta: así está el puerto de chalanas en este momento - Que Pasa Salta</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
+          <t>Potosí 2026-10-24: 60.5 km/h de ráfagas pronosticadas</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVld9IBfkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVldw?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -5316,59 +5316,59 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>-22.721</v>
+        <v>-19.58</v>
       </c>
       <c r="O23" t="n">
-        <v>-64.32599999999999</v>
+        <v>-65.75</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bermejo, Tarija</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
+          <t>capital (pronóstico puntual)</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Tarija</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Bermejo</t>
+          <t>Potosí</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>gdacs:WF1033142:0</t>
+          <t>noticia:1ax0bpy</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gdacs</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-24 07:06</t>
+          <t>2026-10-24 10:32</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1792839995000</v>
+        <v>1792852364000</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>GDACS</t>
+          <t>Que Pasa Salta</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5381,17 +5381,13 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Green forest fire notification in Bolivia</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>On 21/10/2026, a forest fire started in Bolivia, until 24/10/2026.</t>
-        </is>
-      </c>
+          <t>Creció el Bermejo tras la tormenta: así está el puerto de chalanas en este momento - Que Pasa Salta</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>http://www.gdacs.org/report.aspx?eventtype=WF&amp;eventid=1033142</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVld9IBfkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVldw?oc=5</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -5401,59 +5397,59 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>-13.06332</v>
+        <v>-22.721</v>
       </c>
       <c r="O24" t="n">
-        <v>-67.66426</v>
+        <v>-64.32599999999999</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Bermejo, Tarija</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>coordenada de la fuente</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Tarija</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>Ixiamas</t>
+          <t>Bermejo</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>noticia:1shhqva</t>
+          <t>gdacs:WF1033142:0</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>gdacs</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-24 06:33</t>
+          <t>2026-10-24 07:06</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1792838034000</v>
+        <v>1792839995000</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>GDACS</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5466,13 +5462,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+          <t>Green forest fire notification in Bolivia</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>On 21/10/2026, a forest fire started in Bolivia, until 24/10/2026.</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQYzB6N082XzFRRnVtcDVmUkYyWjcxUzV2Z3Frd1I0WDNXSnZtY0QzOU1PUkNLMktVT1Vra2FSeXhxZDRuOFZYZjFwejl6ejJTbWY2MGJuSGN3ZHdrdG5JUkgzSXBkbDYtaHlackY3OVFuNWdLcFNpdWNHRU9vNGdoVWx2ODFVdzJXYUxnM0tUcjJvZmc?oc=5</t>
+          <t>http://www.gdacs.org/report.aspx?eventtype=WF&amp;eventid=1033142</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -5482,82 +5482,78 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>-17.97</v>
+        <v>-13.06332</v>
       </c>
       <c r="O25" t="n">
-        <v>-67.11</v>
+        <v>-67.66426</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
+          <t>coordenada de la fuente</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Ixiamas</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>clima:Potosí:2026-10-25:viento:1</t>
+          <t>noticia:1shhqva</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-24 02:55</t>
+          <t>2026-10-24 06:33</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1792824927736</v>
+        <v>1792838034000</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Potosí 2026-10-25: 60.5 km/h de ráfagas pronosticadas</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
-        </is>
-      </c>
+          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQYzB6N082XzFRRnVtcDVmUkYyWjcxUzV2Z3Frd1I0WDNXSnZtY0QzOU1PUkNLMktVT1Vra2FSeXhxZDRuOFZYZjFwejl6ejJTbWY2MGJuSGN3ZHdrdG5JUkgzSXBkbDYtaHlackY3OVFuNWdLcFNpdWNHRU9vNGdoVWx2ODFVdzJXYUxnM0tUcjJvZmc?oc=5</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -5567,59 +5563,59 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>-19.58</v>
+        <v>-17.97</v>
       </c>
       <c r="O26" t="n">
-        <v>-65.75</v>
+        <v>-67.11</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Oruro, Oruro</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>capital (pronóstico puntual)</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Oruro</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Oruro</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>noticia:mz6q0s</t>
+          <t>clima:Potosí:2026-10-25:viento:1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-10-23 23:09</t>
+          <t>2026-10-24 02:55</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1792811349000</v>
+        <v>1792824927736</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5632,36 +5628,56 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Revelan lista preliminar de heridos tras accidente de Los Chicos Fieles - Red Uno</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
+          <t>Potosí 2026-10-25: 60.5 km/h de ráfagas pronosticadas</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPczBQcnE2SzFGMXc3b1lsTkNxVWRmS3Vnb01xOTV2WmVva3J2RVlteWpHZ3VJS2dNWGV5NW5FX3ZncnVKTEVDTGpBRndTU1FxeWxtaS1fb1FscGxXMWNXUE9zbHdob1AxVFl1eHB5OU1yUnNoOXJ6U21oVG9PVDA1ak1xQl9hUlB4V0RaQXJqZENGUm8zMUJEY3J0WW5ENE5ObWJLNmpWN0RkSmFJbnZUZGR5UFRPd3QyUFY4WQ?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
-      </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-19.58</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-65.75</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Potosí</t>
+        </is>
+      </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
+          <t>capital (pronóstico puntual)</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Potosí</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Potosí</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>noticia:1uil931</t>
+          <t>noticia:mz6q0s</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5671,15 +5687,15 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-10-23 22:49</t>
+          <t>2026-10-23 23:09</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1792810149000</v>
+        <v>1792811349000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>El Deber</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5697,13 +5713,13 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Accidente de tránsito en la ruta hacia Alto Beni deja varios heridos - El Deber</t>
+          <t>Revelan lista preliminar de heridos tras accidente de Los Chicos Fieles - Red Uno</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQakFJRmx3RlJEMkVHU0pxWXZ2ZU1ib04tZy1yeTB2OGhrYk9CU3pMaDVpRThNZktZMS14UzA2Y1VIcEQtZDg3cEU2SmlzQnBmUVVvM0ZNYzZWNExWUXQ3aHpnd3lqOHFVV3pNbDRLS1NQNGtwb2RjSFpleHJkOG5zSXVtWjVIS1dLejNybktRWTJVZXh3WkFUQVE5T2tMdFdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPczBQcnE2SzFGMXc3b1lsTkNxVWRmS3Vnb01xOTV2WmVva3J2RVlteWpHZ3VJS2dNWGV5NW5FX3ZncnVKTEVDTGpBRndTU1FxeWxtaS1fb1FscGxXMWNXUE9zbHdob1AxVFl1eHB5OU1yUnNoOXJ6U21oVG9PVDA1ak1xQl9hUlB4V0RaQXJqZENGUm8zMUJEY3J0WW5ENE5ObWJLNmpWN0RkSmFJbnZUZGR5UFRPd3QyUFY4WQ?oc=5</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -5712,37 +5728,21 @@
       <c r="M28" t="n">
         <v>1</v>
       </c>
-      <c r="N28" t="n">
-        <v>-15.578</v>
-      </c>
-      <c r="O28" t="n">
-        <v>-67.44</v>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Alto Beni, La Paz</t>
-        </is>
-      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>La Paz</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>Alto Beni</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>noticia:1tliu4i</t>
+          <t>noticia:1uil931</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5752,11 +5752,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-10-23 22:18</t>
+          <t>2026-10-23 22:49</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1792808330000</v>
+        <v>1792810149000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQMF9BNnUzLURKNGRMUUJ1VXVRSXNnMlBsQnVXOG0tRlFtY3pvRDNPQmNJMWN2RzJVaWdoWndmcHFnTkZFZnJxRkZtMThYYWlwN09ueUgtei1pSE1hZ2FtSzN6elY4VXJHbzFxdll0eWh0ZkxwQkQ1SDZ5b0E3MlVENGZEWGZHUGlwVG4wd2x3OFNEMVpibnFr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQakFJRmx3RlJEMkVHU0pxWXZ2ZU1ib04tZy1yeTB2OGhrYk9CU3pMaDVpRThNZktZMS14UzA2Y1VIcEQtZDg3cEU2SmlzQnBmUVVvM0ZNYzZWNExWUXQ3aHpnd3lqOHFVV3pNbDRLS1NQNGtwb2RjSFpleHJkOG5zSXVtWjVIS1dLejNybktRWTJVZXh3WkFUQVE5T2tMdFdn?oc=5</t>
         </is>
       </c>
       <c r="L29" t="n">
@@ -5823,7 +5823,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>noticia:1twc9ul</t>
+          <t>noticia:1tliu4i</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5833,11 +5833,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-10-23 22:16</t>
+          <t>2026-10-23 22:18</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1792808192000</v>
+        <v>1792808330000</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNbmwzSnd6c2tFMXBWY0tiemJqRm5CNllOT2p1U0FhdW5QNGFBVXlSZVM1ak5jNGZvcXNVaUQzN3ZQQTlPbmVjQ2Y5RFl2dWVLeUN5NUFodDF0alEyZWlmOHFZWkVVbjdQbkl3ZWtmS25wQWM2TmRZZDBGM2xlS0ZhUzAweXRmcmhVWGY5dV9CUnFBNGtWZHZDSWVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQMF9BNnUzLURKNGRMUUJ1VXVRSXNnMlBsQnVXOG0tRlFtY3pvRDNPQmNJMWN2RzJVaWdoWndmcHFnTkZFZnJxRkZtMThYYWlwN09ueUgtei1pSE1hZ2FtSzN6elY4VXJHbzFxdll0eWh0ZkxwQkQ1SDZ5b0E3MlVENGZEWGZHUGlwVG4wd2x3OFNEMVpibnFr?oc=5</t>
         </is>
       </c>
       <c r="L30" t="n">
@@ -5904,7 +5904,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>noticia:1dygpkp</t>
+          <t>noticia:1twc9ul</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5914,15 +5914,15 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-10-23 21:39</t>
+          <t>2026-10-23 22:16</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1792805983000</v>
+        <v>1792808192000</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>El Deber</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -5931,39 +5931,39 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>(Video) Así rescataron a uno de los integrantes de Los Chicos Fieles tras accidente en Caranavi - Red Uno</t>
+          <t>Accidente de tránsito en la ruta hacia Alto Beni deja varios heridos - El Deber</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOdTVUZUQxVTdvYTdONDQxVlhUTzBOS2hKLW1rS1NUcmRYRnlCVlhIcHZlSjdsaktkQm5CWkFYa3lDQkxnMlh0b3prX0lha1BtbW1qS1VuYnNiX3FiZkYyNDJDR0tqZ0pKMU5TeC04SXV4UUJOTUlPUTB6ek01bzUxTUsydjZqZzI3S3ZLUnRWSUFUVk44WEpKUl9rbzRLb2IwYl9sLVlrYmt5d2ZHNUtGd3lRNnYzMlhuMkJOZW1XSUl2N1BxZWpHbm5XTDJhRUtnR190QWQ1TDlTUVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNbmwzSnd6c2tFMXBWY0tiemJqRm5CNllOT2p1U0FhdW5QNGFBVXlSZVM1ak5jNGZvcXNVaUQzN3ZQQTlPbmVjQ2Y5RFl2dWVLeUN5NUFodDF0alEyZWlmOHFZWkVVbjdQbkl3ZWtmS25wQWM2TmRZZDBGM2xlS0ZhUzAweXRmcmhVWGY5dV9CUnFBNGtWZHZDSWVB?oc=5</t>
         </is>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N31" t="n">
-        <v>-15.813</v>
+        <v>-15.578</v>
       </c>
       <c r="O31" t="n">
-        <v>-67.46299999999999</v>
+        <v>-67.44</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Caranavi, La Paz</t>
+          <t>Alto Beni, La Paz</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -5978,14 +5978,14 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>Caranavi</t>
+          <t>Alto Beni</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>noticia:3dv7b0</t>
+          <t>noticia:1dygpkp</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5995,15 +5995,15 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-23 21:35</t>
+          <t>2026-10-23 21:39</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1792805700000</v>
+        <v>1792805983000</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>FmBolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6012,29 +6012,29 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Accidente en Caranavi: vehículo de Los Chicos Fieles cae a un barranco y deja varios heridos - FmBolivia</t>
+          <t>(Video) Así rescataron a uno de los integrantes de Los Chicos Fieles tras accidente en Caranavi - Red Uno</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNcE1KaHZyUTJCSElxRU9nVzdhTnczWjJGTEhFMEs0bHp2cUdFeHd3VTB0NmVFcjdEN1dsZDZLY2k1ZFFUWkhKV19PU3V2czNyamh1ZE9YajVSVF8xczF6OFhZcWFvYV9EcWg4ZDNCb2p3enhXbFpRYnJMdGdaTXNrWUZSYVhKNTVicWlCLTJ5OE05Z1BvNEx1eEloUk5qTGN3ZHNzbzZWSVljbnRmSERJUWdxRDc0MjJxMGtycWJaaVhXQUUxVUlaWVZLOWE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOdTVUZUQxVTdvYTdONDQxVlhUTzBOS2hKLW1rS1NUcmRYRnlCVlhIcHZlSjdsaktkQm5CWkFYa3lDQkxnMlh0b3prX0lha1BtbW1qS1VuYnNiX3FiZkYyNDJDR0tqZ0pKMU5TeC04SXV4UUJOTUlPUTB6ek01bzUxTUsydjZqZzI3S3ZLUnRWSUFUVk44WEpKUl9rbzRLb2IwYl9sLVlrYmt5d2ZHNUtGd3lRNnYzMlhuMkJOZW1XSUl2N1BxZWpHbm5XTDJhRUtnR190QWQ1TDlTUVk?oc=5</t>
         </is>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>-15.813</v>
@@ -6066,30 +6066,30 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-24:viento:1</t>
+          <t>noticia:3dv7b0</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-23 20:55</t>
+          <t>2026-10-23 21:35</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1792803329663</v>
+        <v>1792805700000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>FmBolivia</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6102,74 +6102,70 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-24: 78.1 km/h de ráfagas pronosticadas</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
-        </is>
-      </c>
+          <t>Accidente en Caranavi: vehículo de Los Chicos Fieles cae a un barranco y deja varios heridos - FmBolivia</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNcE1KaHZyUTJCSElxRU9nVzdhTnczWjJGTEhFMEs0bHp2cUdFeHd3VTB0NmVFcjdEN1dsZDZLY2k1ZFFUWkhKV19PU3V2czNyamh1ZE9YajVSVF8xczF6OFhZcWFvYV9EcWg4ZDNCb2p3enhXbFpRYnJMdGdaTXNrWUZSYVhKNTVicWlCLTJ5OE05Z1BvNEx1eEloUk5qTGN3ZHNzbzZWSVljbnRmSERJUWdxRDc0MjJxMGtycWJaaVhXQUUxVUlaWVZLOWE?oc=5</t>
         </is>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N33" t="n">
-        <v>-17.78</v>
+        <v>-15.813</v>
       </c>
       <c r="O33" t="n">
-        <v>-63.18</v>
+        <v>-67.46299999999999</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Caranavi, La Paz</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>capital (pronóstico puntual)</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Caranavi</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>noticia:rabz5p</t>
+          <t>clima:Santa Cruz:2026-10-24:viento:1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-10-23 20:44</t>
+          <t>2026-10-23 20:55</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1792802686000</v>
+        <v>1792803329663</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6178,22 +6174,26 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Tome previsiones: se pronostican lluvias y ambiente caluroso para este fin de semana en Cochabamba - Red Uno</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
+          <t>Santa Cruz 2026-10-24: 78.1 km/h de ráfagas pronosticadas</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTlU5NVFpY1RheTN5ZE1IbG5VYTh2Sk5hZHpHeWI3LVdnSFg2cFJFdnBCVkxiUjNKcUgyUW16SWxpMXFkMHdad2xFN043bklJeG1iQ0V1V3hBZk1Ga3NscjdPVWUySmt4bDNTdWlmSUdOMmNlZ2hkSWZFMmk4VGs0Nm9TcnRCTDhINmtnQU9zZDBUY05HcWpxN3FOX3N1dmVJblE0MGc5di1Ma1N2dGNxOUtoV1MzNnl1OXpRaTZ2UGxMc3RDWndubHVQNUd0eVROMGR2OGxVemtOaEc4bTNRaA?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L34" t="n">
@@ -6203,36 +6203,36 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>-17.39</v>
+        <v>-17.78</v>
       </c>
       <c r="O34" t="n">
-        <v>-66.16</v>
+        <v>-63.18</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Cochabamba, Cochabamba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
+          <t>capital (pronóstico puntual)</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>noticia:1jfk053</t>
+          <t>noticia:rabz5p</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -6242,11 +6242,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-23 19:08</t>
+          <t>2026-10-23 20:44</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1792796931000</v>
+        <v>1792802686000</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -6255,43 +6255,43 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>climatológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Sequía en Pasorapa: el ganado muere por falta de agua y alistan declaratoria de desastre - Red Uno</t>
+          <t>Tome previsiones: se pronostican lluvias y ambiente caluroso para este fin de semana en Cochabamba - Red Uno</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNQVhTWE8zdE1BQ3lueWJPeV9wUDNsSmJpS0NJTWppMUY4QmlQSUFHVjRORmtrVHQ3MHB0T1pyS25PamxnY0hBQUtzOVRvSUNaUkdGb1RWSGl4dFA4Z3VINVpQTk1pZUpDdUIyUU5hZS1oNGhBa1RWcFhScVMwVTFrVlJaOFQ4OWFqRWVUZ051bHVJTlMxRTBhRFVLUEV2dTZFdDgtRkxJM3VvN3YzUWJfVk41ZWR5U1JoNmx0WFFkMmNTWGVleGNIQlNxWUJzdHIxSWtz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTlU5NVFpY1RheTN5ZE1IbG5VYTh2Sk5hZHpHeWI3LVdnSFg2cFJFdnBCVkxiUjNKcUgyUW16SWxpMXFkMHdad2xFN043bklJeG1iQ0V1V3hBZk1Ga3NscjdPVWUySmt4bDNTdWlmSUdOMmNlZ2hkSWZFMmk4VGs0Nm9TcnRCTDhINmtnQU9zZDBUY05HcWpxN3FOX3N1dmVJblE0MGc5di1Ma1N2dGNxOUtoV1MzNnl1OXpRaTZ2UGxMc3RDWndubHVQNUd0eVROMGR2OGxVemtOaEc4bTNRaA?oc=5</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>-18.38</v>
+        <v>-17.39</v>
       </c>
       <c r="O35" t="n">
-        <v>-64.649</v>
+        <v>-66.16</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Pasorapa, Cochabamba</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -6306,14 +6306,14 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>Pasorapa</t>
+          <t>Cochabamba</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>noticia:ix3l8o</t>
+          <t>noticia:1jfk053</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -6323,56 +6323,56 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-10-23 18:25</t>
+          <t>2026-10-23 19:08</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1792794310000</v>
+        <v>1792796931000</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Visión 360</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>climatológica</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Oruro evalúa suspender clases presenciales por más de 200 casos de Coxsackie - Visión 360</t>
+          <t>Sequía en Pasorapa: el ganado muere por falta de agua y alistan declaratoria de desastre - Red Uno</t>
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0c9IBywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNQVhTWE8zdE1BQ3lueWJPeV9wUDNsSmJpS0NJTWppMUY4QmlQSUFHVjRORmtrVHQ3MHB0T1pyS25PamxnY0hBQUtzOVRvSUNaUkdGb1RWSGl4dFA4Z3VINVpQTk1pZUpDdUIyUU5hZS1oNGhBa1RWcFhScVMwVTFrVlJaOFQ4OWFqRWVUZ051bHVJTlMxRTBhRFVLUEV2dTZFdDgtRkxJM3VvN3YzUWJfVk41ZWR5U1JoNmx0WFFkMmNTWGVleGNIQlNxWUJzdHIxSWtz?oc=5</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>-17.97</v>
+        <v>-18.38</v>
       </c>
       <c r="O36" t="n">
-        <v>-67.11</v>
+        <v>-64.649</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>Pasorapa, Cochabamba</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -6382,19 +6382,19 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Pasorapa</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>noticia:1xqv9m7</t>
+          <t>noticia:ix3l8o</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -6404,62 +6404,78 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-10-23 18:09</t>
+          <t>2026-10-23 18:25</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1792793370000</v>
+        <v>1792794310000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>El Diario del centro del país</t>
+          <t>Visión 360</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Tres heridos en tremendo choque cerca de Oncativo - El Diario del centro del país</t>
+          <t>Oruro evalúa suspender clases presenciales por más de 200 casos de Coxsackie - Visión 360</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZERhbTJMQUJVb3hmZFlSZmRGZkdBLWdFTGJVQzdqZkE4aGhhWmdQZ2JDRW1ndkJLWU90VTZ6Ti1JOUZzcFZfcE1zbkRHU1B3YTF4UkVzdllFa1p3SUlObURGamF0Vm9kc3dPLTZVWFJ4NWZZQmlySElPNHhZTnRGNGNZUWw2ZlI1eVBEQkNGNEhLWTNiLWJLUS0xYjA0UWRhc0d6bVN4aVVLSVdsQWlpMUZYdWw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0c9IBywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0cw?oc=5</t>
         </is>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3</v>
-      </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>-17.97</v>
+      </c>
+      <c r="O37" t="n">
+        <v>-67.11</v>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Oruro, Oruro</t>
+        </is>
+      </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>noticia:1wuregl</t>
+          <t>noticia:1xqv9m7</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6469,78 +6485,62 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-10-23 15:39</t>
+          <t>2026-10-23 18:09</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1792784340000</v>
+        <v>1792793370000</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FmBolivia</t>
+          <t>El Diario del centro del país</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>hidrológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Intensas lluvias inundan La Paz y activan alertas por el riesgo de desborde de ríos - FmBolivia</t>
+          <t>Tres heridos en tremendo choque cerca de Oncativo - El Diario del centro del país</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPZm85aHphekQ4U3BZZkp1ZkF6ZVdSUHgtZmltS1FxUUgza1AwcndWWDJZOWctT0RiVmVabmg5SG42NnJWMlJMMnBlYTlYaVdSb09sR0dnVDdpT29faTdiaDUtZElJdlQ3eTdjR2VsWjlta1FOS1U2Vm1vV3JwWkpvbEw1ZUR3akgwQTZnQnVENjJtVkQtVUpKVEJTeWNJSE1CaEFKa2VqMmZXbWk3ekR4ZWpmZ1Z3elFQaWNaNFJuMXA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZERhbTJMQUJVb3hmZFlSZmRGZkdBLWdFTGJVQzdqZkE4aGhhWmdQZ2JDRW1ndkJLWU90VTZ6Ti1JOUZzcFZfcE1zbkRHU1B3YTF4UkVzdllFa1p3SUlObURGamF0Vm9kc3dPLTZVWFJ4NWZZQmlySElPNHhZTnRGNGNZUWw2ZlI1eVBEQkNGNEhLWTNiLWJLUS0xYjA0UWRhc0d6bVN4aVVLSVdsQWlpMUZYdWw?oc=5</t>
         </is>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>-16.169</v>
-      </c>
-      <c r="O38" t="n">
-        <v>-68.09</v>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>La Paz, La Paz</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>La Paz</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>Nuestra Señora de La Paz</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>noticia:1570kkf</t>
+          <t>noticia:1wuregl</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6550,20 +6550,20 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-10-23 15:28</t>
+          <t>2026-10-23 15:39</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1792783705000</v>
+        <v>1792784340000</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>FmBolivia</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>hidrológica</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6576,13 +6576,13 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>¿Se suspenden las clases en Oruro? Más de 200 casos de Coxsackie activan evaluaciones - Red Uno</t>
+          <t>Intensas lluvias inundan La Paz y activan alertas por el riesgo de desborde de ríos - FmBolivia</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNMFdHaVpKRmMyOENDYm16UXJPenVSQnpmTE94bDc4UFhqakluMUdvZjAwamUxT3BVWUpJQm8xVHBWengxQmhWM1hjU3d2YXFrLXpVU2VrZDJiMXZLMlQ5bGxGOHFETFhYM0s2RjlUTlhkd0g2eXQweDFHaTlKNGNMUlJfOWg2a0JjTklXUWZKc1BmUXZuZFZ2MF9fV2lEYUY4LXNiNmk3cF9FNjVtTl9GWFotT2ltS0xXTnM1dENvSU9kbFRMalFrYVdXOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPZm85aHphekQ4U3BZZkp1ZkF6ZVdSUHgtZmltS1FxUUgza1AwcndWWDJZOWctT0RiVmVabmg5SG42NnJWMlJMMnBlYTlYaVdSb09sR0dnVDdpT29faTdiaDUtZElJdlQ3eTdjR2VsWjlta1FOS1U2Vm1vV3JwWkpvbEw1ZUR3akgwQTZnQnVENjJtVkQtVUpKVEJTeWNJSE1CaEFKa2VqMmZXbWk3ekR4ZWpmZ1Z3elFQaWNaNFJuMXA?oc=5</t>
         </is>
       </c>
       <c r="L39" t="n">
@@ -6592,14 +6592,14 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>-17.97</v>
+        <v>-16.169</v>
       </c>
       <c r="O39" t="n">
-        <v>-67.11</v>
+        <v>-68.09</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>La Paz, La Paz</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -6609,19 +6609,19 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Nuestra Señora de La Paz</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>noticia:1nzu2o8</t>
+          <t>noticia:1570kkf</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6631,39 +6631,39 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-10-23 15:20</t>
+          <t>2026-10-23 15:28</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1792783236000</v>
+        <v>1792783705000</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>hidrológica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Alerta naranja por posibles desbordes en tres departamentos (15:20) - El Diario - Bolivia</t>
+          <t>¿Se suspenden las clases en Oruro? Más de 200 casos de Coxsackie activan evaluaciones - Red Uno</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPTnBESV9OODZhNjY3T2M2X2NZcmk4clI0eFZsd3VLMVRwaUlSdF9wanZyVGxDNUlNTm5wbGpLN1lvX09mNGxFVkpIZDNGdi1pNDdfSGlESThfeVloQzJsNUMyNUpWUDhzTVJiYWJpNkQ1RHliRWljZlp3SlhtZ2FhU0pvV0syUmZIejJZWHlRdTBOTG4zaTc5cEsycW9IcEx2SkQtN01Gendlb1VR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNMFdHaVpKRmMyOENDYm16UXJPenVSQnpmTE94bDc4UFhqakluMUdvZjAwamUxT3BVWUpJQm8xVHBWengxQmhWM1hjU3d2YXFrLXpVU2VrZDJiMXZLMlQ5bGxGOHFETFhYM0s2RjlUTlhkd0g2eXQweDFHaTlKNGNMUlJfOWg2a0JjTklXUWZKc1BmUXZuZFZ2MF9fV2lEYUY4LXNiNmk3cF9FNjVtTl9GWFotT2ltS0xXTnM1dENvSU9kbFRMalFrYVdXOA?oc=5</t>
         </is>
       </c>
       <c r="L40" t="n">
@@ -6672,21 +6672,37 @@
       <c r="M40" t="n">
         <v>0</v>
       </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
+      <c r="N40" t="n">
+        <v>-17.97</v>
+      </c>
+      <c r="O40" t="n">
+        <v>-67.11</v>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Oruro, Oruro</t>
+        </is>
+      </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>noticia:1itd1r7</t>
+          <t>noticia:1nzu2o8</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6696,39 +6712,39 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-10-23 15:01</t>
+          <t>2026-10-23 15:20</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1792782098000</v>
+        <v>1792783236000</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>eju.tv</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>hidrológica</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Intensa lluvia y granizada en La Paz inundan vías y elevan el nivel de los ríos - eju.tv</t>
+          <t>Alerta naranja por posibles desbordes en tres departamentos (15:20) - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNWU9QWElKQXEyN3UxVm4xbzJzbEJ1TU1NTHZlRUp6YndmeU9GQnJKcTluVEJ2ZHQ5cGp3aWhlMUd5ektWQlBpUVNmZnZuRnJwMXlydzAzX0FBVnY5UDMzQTBkWVRNRUNJSlRvX3MyQVhMcEhIMW9WSUpXckVSd0RJWk1KMFBKWmJNU3diQVlEN1Y5aVV6eVBaZXpOMnFIWWxaMlRlY0ZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPTnBESV9OODZhNjY3T2M2X2NZcmk4clI0eFZsd3VLMVRwaUlSdF9wanZyVGxDNUlNTm5wbGpLN1lvX09mNGxFVkpIZDNGdi1pNDdfSGlESThfeVloQzJsNUMyNUpWUDhzTVJiYWJpNkQ1RHliRWljZlp3SlhtZ2FhU0pvV0syUmZIejJZWHlRdTBOTG4zaTc5cEsycW9IcEx2SkQtN01Gendlb1VR?oc=5</t>
         </is>
       </c>
       <c r="L41" t="n">
@@ -6737,37 +6753,21 @@
       <c r="M41" t="n">
         <v>0</v>
       </c>
-      <c r="N41" t="n">
-        <v>-16.169</v>
-      </c>
-      <c r="O41" t="n">
-        <v>-68.09</v>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>La Paz, La Paz</t>
-        </is>
-      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>La Paz</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>Nuestra Señora de La Paz</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>noticia:1l4xxfk</t>
+          <t>noticia:1itd1r7</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6777,20 +6777,20 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-10-23 14:51</t>
+          <t>2026-10-23 15:01</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1792781480000</v>
+        <v>1792782098000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>eju.tv</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6803,13 +6803,13 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
+          <t>Intensa lluvia y granizada en La Paz inundan vías y elevan el nivel de los ríos - eju.tv</t>
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQS2FPaHd3UnFBRjRoa0lKUm1MNUQ5S00zN1RJZE5fWlVUQnhiY0lLcFRkY2JZak1mZ0c2WEVMVUNJVUJTMGFLNHg4S2ZKNTRqLXJHM09ET19hX1pZeTQwUkdEc2huTHVpcno2QTRZbnhralVRWXozcWc1a2pHUEpBeTV1cWgzTWRwaDEweURKeVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNWU9QWElKQXEyN3UxVm4xbzJzbEJ1TU1NTHZlRUp6YndmeU9GQnJKcTluVEJ2ZHQ5cGp3aWhlMUd5ektWQlBpUVNmZnZuRnJwMXlydzAzX0FBVnY5UDMzQTBkWVRNRUNJSlRvX3MyQVhMcEhIMW9WSUpXckVSd0RJWk1KMFBKWmJNU3diQVlEN1Y5aVV6eVBaZXpOMnFIWWxaMlRlY0ZB?oc=5</t>
         </is>
       </c>
       <c r="L42" t="n">
@@ -6819,14 +6819,14 @@
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>-17.97</v>
+        <v>-16.169</v>
       </c>
       <c r="O42" t="n">
-        <v>-67.11</v>
+        <v>-68.09</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>La Paz, La Paz</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -6836,19 +6836,19 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Nuestra Señora de La Paz</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>noticia:51709n</t>
+          <t>noticia:1l4xxfk</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6858,56 +6858,56 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-10-23 13:38</t>
+          <t>2026-10-23 14:51</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1792777139000</v>
+        <v>1792781480000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>eju.tv</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - eju.tv</t>
+          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPcjZTSmprRGVoNlRqQmdBTE5VM3pRQ1ZFakFUbzVyMUhiaDVkT0liaG9UNEZXekV6bWsycUk4X1JCSEY5RjhNVlZaTk9ULUFuZkY3NnZuWmZ1a19leUhFdlIyQV9kLWxlSkxfeXFhcFRTZjZ2YkpQQlJ1dkNLMDBjaGZ4SkhyQ0RfcnhKSEg5WURCQVQwbENYTHEzUzJSaUEzMGo2bWdyS3lsM016LXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQS2FPaHd3UnFBRjRoa0lKUm1MNUQ5S00zN1RJZE5fWlVUQnhiY0lLcFRkY2JZak1mZ0c2WEVMVUNJVUJTMGFLNHg4S2ZKNTRqLXJHM09ET19hX1pZeTQwUkdEc2huTHVpcno2QTRZbnhralVRWXozcWc1a2pHUEpBeTV1cWgzTWRwaDEweURKeVE?oc=5</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>-17.764</v>
+        <v>-17.97</v>
       </c>
       <c r="O43" t="n">
-        <v>-62.903</v>
+        <v>-67.11</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Cotoca, Santa Cruz</t>
+          <t>Oruro, Oruro</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -6917,19 +6917,19 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Oruro</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>Cotoca</t>
+          <t>Oruro</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>noticia:11rddql</t>
+          <t>noticia:51709n</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6939,56 +6939,56 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-10-23 13:22</t>
+          <t>2026-10-23 13:38</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1792776139000</v>
+        <v>1792777139000</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>eju.tv</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Intensifican acciones preventivas contra el dengue en Caranavi - El Diario - Bolivia</t>
+          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - eju.tv</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOMjhSeDJBek5iaFhDcnFzX1lKelgwZmUwLTJnbEhMdDRMelUxNks5Ti1pRHh3dDhTcC1YZEdqM3FJOGdqVHRvcXVhRlpCQzVDTEZMUFBkV1NrYVQ2LXRqTTBhcGRQc21CQ0VabzZaNExXb1BjTzJ2Uk5BcFF0VG5XOFNRa3lqUWlJSnRFUUVXYnNpbXB0LVVmSXVWSzJxcmVpdVVxUC1KOUhTQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPcjZTSmprRGVoNlRqQmdBTE5VM3pRQ1ZFakFUbzVyMUhiaDVkT0liaG9UNEZXekV6bWsycUk4X1JCSEY5RjhNVlZaTk9ULUFuZkY3NnZuWmZ1a19leUhFdlIyQV9kLWxlSkxfeXFhcFRTZjZ2YkpQQlJ1dkNLMDBjaGZ4SkhyQ0RfcnhKSEg5WURCQVQwbENYTHEzUzJSaUEzMGo2bWdyS3lsM016LXc?oc=5</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N44" t="n">
-        <v>-15.813</v>
+        <v>-17.764</v>
       </c>
       <c r="O44" t="n">
-        <v>-67.46299999999999</v>
+        <v>-62.903</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Caranavi, La Paz</t>
+          <t>Cotoca, Santa Cruz</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -6998,19 +6998,19 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>Caranavi</t>
+          <t>Cotoca</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>noticia:fcm3nx</t>
+          <t>noticia:11rddql</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -7020,62 +7020,78 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-10-23 12:58</t>
+          <t>2026-10-23 13:22</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1792774699000</v>
+        <v>1792776139000</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>[VIDEO] Así fue el accidente de moto que dejó un adolescente fallecido y un hombre gravemente herido - Red Uno</t>
+          <t>Intensifican acciones preventivas contra el dengue en Caranavi - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOSmJMazhUemNfRHpWcDBoTVFZMUpwdlVKVUtvUXZNTGRRRHlwLW5KNmNhcmFnd1czbi1yalhFMnpSS1dmUE9jVzNlOS1kMWZtRzBHZ2EtcDRDdU5Gc2JUQVIwM2xPa2lZVmswRi1SUFVPcm8xcHlGN3F2UThTSDdKMDNyYnJmVkcxazNLLVBLOWFYM09FVUpmVnN5RVhpSVo2V1VCVmFwQ1gzTmRUWVp2aXMwcmxHRS1GV2p3NTBtR2RzM2wwVHUzaGJkRXJYbHdvaDlhWm5YMTk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOMjhSeDJBek5iaFhDcnFzX1lKelgwZmUwLTJnbEhMdDRMelUxNks5Ti1pRHh3dDhTcC1YZEdqM3FJOGdqVHRvcXVhRlpCQzVDTEZMUFBkV1NrYVQ2LXRqTTBhcGRQc21CQ0VabzZaNExXb1BjTzJ2Uk5BcFF0VG5XOFNRa3lqUWlJSnRFUUVXYnNpbXB0LVVmSXVWSzJxcmVpdVVxUC1KOUhTQQ?oc=5</t>
         </is>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>1</v>
-      </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>-15.813</v>
+      </c>
+      <c r="O45" t="n">
+        <v>-67.46299999999999</v>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Caranavi, La Paz</t>
+        </is>
+      </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>La Paz</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Caranavi</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>noticia:1cjx1qd</t>
+          <t>noticia:fcm3nx</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -7085,78 +7101,62 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-10-23 12:39</t>
+          <t>2026-10-23 12:58</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1792773575000</v>
+        <v>1792774699000</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Más de 60 municipios en La Paz sufren falta de lluvias - La Patria Bolivia</t>
+          <t>[VIDEO] Así fue el accidente de moto que dejó un adolescente fallecido y un hombre gravemente herido - Red Uno</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE52Qi03Z1J6OS1CR2liRVZ0VlhCcmVQWFV6RUdGNXdrbzZRNXFjTWRaRnc1b3VoV0xaY3RIdncxNlNnYkxyUXo5MTlJWmMwWDNSMDE4ZHI2VkpWajFPaUF2SmRVYkk2eDZYQ1RfUU9ieENrZG9UVVFiaXZSeGI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOSmJMazhUemNfRHpWcDBoTVFZMUpwdlVKVUtvUXZNTGRRRHlwLW5KNmNhcmFnd1czbi1yalhFMnpSS1dmUE9jVzNlOS1kMWZtRzBHZ2EtcDRDdU5Gc2JUQVIwM2xPa2lZVmswRi1SUFVPcm8xcHlGN3F2UThTSDdKMDNyYnJmVkcxazNLLVBLOWFYM09FVUpmVnN5RVhpSVo2V1VCVmFwQ1gzTmRUWVp2aXMwcmxHRS1GV2p3NTBtR2RzM2wwVHUzaGJkRXJYbHdvaDlhWm5YMTk?oc=5</t>
         </is>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>-16.169</v>
-      </c>
-      <c r="O46" t="n">
-        <v>-68.09</v>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>La Paz, La Paz</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>La Paz</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>Nuestra Señora de La Paz</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>noticia:11y8tre</t>
+          <t>noticia:1cjx1qd</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -7166,56 +7166,56 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-10-23 11:43</t>
+          <t>2026-10-23 12:39</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1792770197000</v>
+        <v>1792773575000</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>La Patria Bolivia</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - Red Uno</t>
+          <t>Más de 60 municipios en La Paz sufren falta de lluvias - La Patria Bolivia</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOVGY3YVRLWWxYM0IycjF4dlNUeUhqZG90Yng4aWhmN3A5ai02WENWYnF4bWpoZHFKMGc1X0JPRHdRRVZfSlA4UmZFa2kxYkNIS3ZtQ1NvNlNCME51eVZTRkRKSUQ5MmRoaWl5Tkt5NHpPUEFwemN2YTV1djFwdHlqQnFqRHNPenhYcTlsanJPcXhpOVV1NmFBUXZyazQ2MkUzM0dSZy02ZllxTGtjcl9ldzdHSktTRlVaalZJc1pubUNQMWFTbzVEOUJ1UmhCdEJt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE52Qi03Z1J6OS1CR2liRVZ0VlhCcmVQWFV6RUdGNXdrbzZRNXFjTWRaRnc1b3VoV0xaY3RIdncxNlNnYkxyUXo5MTlJWmMwWDNSMDE4ZHI2VkpWajFPaUF2SmRVYkk2eDZYQ1RfUU9ieENrZG9UVVFiaXZSeGI?oc=5</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>-17.764</v>
+        <v>-16.169</v>
       </c>
       <c r="O47" t="n">
-        <v>-62.903</v>
+        <v>-68.09</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Cotoca, Santa Cruz</t>
+          <t>La Paz, La Paz</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -7225,42 +7225,42 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>Cotoca</t>
+          <t>Nuestra Señora de La Paz</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>clima:Sucre:2026-10-23:viento:1</t>
+          <t>noticia:11y8tre</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-10-23 06:55</t>
+          <t>2026-10-23 11:43</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1792752927735</v>
+        <v>1792770197000</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7273,56 +7273,52 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Sucre 2026-10-23: 66.2 km/h de ráfagas pronosticadas</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
-        </is>
-      </c>
+          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - Red Uno</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOVGY3YVRLWWxYM0IycjF4dlNUeUhqZG90Yng4aWhmN3A5ai02WENWYnF4bWpoZHFKMGc1X0JPRHdRRVZfSlA4UmZFa2kxYkNIS3ZtQ1NvNlNCME51eVZTRkRKSUQ5MmRoaWl5Tkt5NHpPUEFwemN2YTV1djFwdHlqQnFqRHNPenhYcTlsanJPcXhpOVV1NmFBUXZyazQ2MkUzM0dSZy02ZllxTGtjcl9ldzdHSktTRlVaalZJc1pubUNQMWFTbzVEOUJ1UmhCdEJt?oc=5</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N48" t="n">
-        <v>-19.03</v>
+        <v>-17.764</v>
       </c>
       <c r="O48" t="n">
-        <v>-65.26000000000001</v>
+        <v>-62.903</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Cotoca, Santa Cruz</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>capital (pronóstico puntual)</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Chuquisaca</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Cotoca</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-24:viento:2</t>
+          <t>clima:Sucre:2026-10-23:viento:1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -7336,7 +7332,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1792752927734</v>
+        <v>1792752927735</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -7349,16 +7345,16 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-24: 85 km/h de ráfagas pronosticadas</t>
+          <t>Sucre 2026-10-23: 66.2 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -7378,14 +7374,14 @@
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>-17.78</v>
+        <v>-19.03</v>
       </c>
       <c r="O49" t="n">
-        <v>-63.18</v>
+        <v>-65.26000000000001</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -7395,65 +7391,65 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Chuquisaca</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Sucre</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>usgs:us6000u49c</t>
+          <t>clima:Santa Cruz:2026-10-24:viento:2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>usgs</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-10-22 22:45</t>
+          <t>2026-10-23 06:55</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1792723541183</v>
+        <v>1792752927734</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>USGS</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>geológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Sismo M 4.5 - 58 km SW of Atocha, Bolivia</t>
+          <t>Santa Cruz 2026-10-24: 85 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Profundidad 236 km</t>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://earthquake.usgs.gov/earthquakes/eventpage/us6000u49c</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L50" t="n">
@@ -7463,59 +7459,59 @@
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>-21.3469</v>
+        <v>-17.78</v>
       </c>
       <c r="O50" t="n">
-        <v>-66.5795</v>
+        <v>-63.18</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>58 km SW of Atocha, Bolivia</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>coordenada de la fuente</t>
+          <t>capital (pronóstico puntual)</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>San Pablo</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-22:viento:1</t>
+          <t>usgs:us6000u49c</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>usgs</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-10-22 21:55</t>
+          <t>2026-10-22 22:45</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1792720528712</v>
+        <v>1792723541183</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>USGS</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>geológica</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7528,17 +7524,17 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-22: 67.7 km/h de ráfagas pronosticadas</t>
+          <t>Sismo M 4.5 - 58 km SW of Atocha, Bolivia</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+          <t>Profundidad 236 km</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://earthquake.usgs.gov/earthquakes/eventpage/us6000u49c</t>
         </is>
       </c>
       <c r="L51" t="n">
@@ -7548,36 +7544,36 @@
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>-17.78</v>
+        <v>-21.3469</v>
       </c>
       <c r="O51" t="n">
-        <v>-63.18</v>
+        <v>-66.5795</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>58 km SW of Atocha, Bolivia</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>capital (pronóstico puntual)</t>
+          <t>coordenada de la fuente</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>San Pablo</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-23:viento:2</t>
+          <t>clima:Santa Cruz:2026-10-22:viento:1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -7604,16 +7600,16 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-23: 83.9 km/h de ráfagas pronosticadas</t>
+          <t>Santa Cruz 2026-10-22: 67.7 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -7662,49 +7658,53 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>noticia:1hhvre7</t>
+          <t>clima:Santa Cruz:2026-10-23:viento:2</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-10-22 19:36</t>
+          <t>2026-10-22 21:55</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1792712202000</v>
+        <v>1792720528712</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>El Mundo Bolivia</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Virgen de Cotoca: Controlan incendio en depósito de materiales plásticos - El Mundo Bolivia</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
+          <t>Santa Cruz 2026-10-23: 83.9 km/h de ráfagas pronosticadas</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcDF6VE5FNzRaWGRuUzFKeXhnZ21DZTRaaEtrVEJEa1Z3ejg2VG1ONG1ENmlDWlkyVjlkQkJwS2F1XzBGMFQwSHd4OEwxTW1PbHdGcUh1ckV6SGpDd2hiN0dkeUVTcnFXT3RjOU1kLXZtVVdZY2hkZS1pcVpVUFhnRktqcHY5UnBrY0xUMDRETjl6N0pXT3A5amxhMA?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L53" t="n">
@@ -7714,19 +7714,19 @@
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>-17.764</v>
+        <v>-17.78</v>
       </c>
       <c r="O53" t="n">
-        <v>-62.903</v>
+        <v>-63.18</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Cotoca, Santa Cruz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
+          <t>capital (pronóstico puntual)</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -7736,14 +7736,14 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>Cotoca</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>noticia:bksnde</t>
+          <t>noticia:1hhvre7</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -7753,15 +7753,15 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-10-22 17:01</t>
+          <t>2026-10-22 19:36</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1792702880000</v>
+        <v>1792712202000</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>eju.tv</t>
+          <t>El Mundo Bolivia</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -7779,13 +7779,13 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Reportan un incendio cerca de la carretera a Cotoca - eju.tv</t>
+          <t>Virgen de Cotoca: Controlan incendio en depósito de materiales plásticos - El Mundo Bolivia</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPNGtpbnBfRnRBalVudnBlZHdVQ0ZSaUplZmtvTGE0aTQzdkxWS3d4My1EZEJ1UE9FNFQ3RmpyZGVsbS1qNEM1QUVFRFAxM2pYT1VqQzRuVjRtZnVNUGlKODNMc0F1a3l6TUpuQmtlUWNlVTVEWWU5ZGZtQm5LWUp3Sg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcDF6VE5FNzRaWGRuUzFKeXhnZ21DZTRaaEtrVEJEa1Z3ejg2VG1ONG1ENmlDWlkyVjlkQkJwS2F1XzBGMFQwSHd4OEwxTW1PbHdGcUh1ckV6SGpDd2hiN0dkeUVTcnFXT3RjOU1kLXZtVVdZY2hkZS1pcVpVUFhnRktqcHY5UnBrY0xUMDRETjl6N0pXT3A5amxhMA?oc=5</t>
         </is>
       </c>
       <c r="L54" t="n">
@@ -7824,7 +7824,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>noticia:17hz69v</t>
+          <t>noticia:bksnde</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -7834,15 +7834,15 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-10-22 13:05</t>
+          <t>2026-10-22 17:01</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1792688709000</v>
+        <v>1792702880000</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>La Razón Digital Bolivia</t>
+          <t>eju.tv</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -7851,45 +7851,61 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Accidente en El Sillar deja al menos 29 heridos - La Razón Digital Bolivia</t>
+          <t>Reportan un incendio cerca de la carretera a Cotoca - eju.tv</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPaXhTdm45YWZnWVFxVzJnb1ZwbUN4SmUtLVdJN0VJdFZBamRyQmFxN0RZelBfTklaSTVyOUZ3ajQ5MFB2TEN4Ukd6TE5ORFY5SEROVk1CZ25sRWJ1QnRBdTVfTktlby1NWXhaVWI5YnRvaDZWbHVjdDVoeFp5Tk5veFk5a19MSWJqcEJVV0dzV3k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPNGtpbnBfRnRBalVudnBlZHdVQ0ZSaUplZmtvTGE0aTQzdkxWS3d4My1EZEJ1UE9FNFQ3RmpyZGVsbS1qNEM1QUVFRFAxM2pYT1VqQzRuVjRtZnVNUGlKODNMc0F1a3l6TUpuQmtlUWNlVTVEWWU5ZGZtQm5LWUp3Sg?oc=5</t>
         </is>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>29</v>
-      </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>-17.764</v>
+      </c>
+      <c r="O55" t="n">
+        <v>-62.903</v>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Cotoca, Santa Cruz</t>
+        </is>
+      </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Cotoca</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>noticia:1f1qb0</t>
+          <t>noticia:17hz69v</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7899,15 +7915,15 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-10-22 12:09</t>
+          <t>2026-10-22 13:05</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1792685373000</v>
+        <v>1792688709000</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>La Razón Digital Bolivia</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -7916,61 +7932,45 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Accidente en el tramo Locotal–Villa Tunari: la vía está transitable con precaución - Red Uno</t>
+          <t>Accidente en El Sillar deja al menos 29 heridos - La Razón Digital Bolivia</t>
         </is>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTFozcEEwNXBqV19sS2VibXh0MGt0QlhsX1djSTFGQW5zNlFLRHZpNVVnZ1JmWDQ4LVRHX2Rmb3B5UU9qV0FZQmJCaUZYdmwyNG1NenJ4Qzlzd0NJTGs1SjMxdFRtRFBzSUkybGJfZFFaNFZBc21FSUJYSFVkQkVkSEhQaGw0UFVzeXctZHo3cjNsYm5weXJlOU1wcmFncnNhMC1BQUpvNWlDX1NxZXU4b09kVFFWR2tSVEk2UTdXXzB3TjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPaXhTdm45YWZnWVFxVzJnb1ZwbUN4SmUtLVdJN0VJdFZBamRyQmFxN0RZelBfTklaSTVyOUZ3ajQ5MFB2TEN4Ukd6TE5ORFY5SEROVk1CZ25sRWJ1QnRBdTVfTktlby1NWXhaVWI5YnRvaDZWbHVjdDVoeFp5Tk5veFk5a19MSWJqcEJVV0dzV3k?oc=5</t>
         </is>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="n">
-        <v>-16.556</v>
-      </c>
-      <c r="O56" t="n">
-        <v>-65.569</v>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>Villa Tunari, Cochabamba</t>
-        </is>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>Villa Tunari</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>noticia:wi18tm</t>
+          <t>noticia:1f1qb0</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7980,11 +7980,11 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-10-22 11:53</t>
+          <t>2026-10-22 12:09</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1792684426000</v>
+        <v>1792685373000</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -7993,49 +7993,65 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>tecnológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Accidente en El Sillar deja heridos y derrame de combustible: esto es lo último que se sabe - Red Uno</t>
+          <t>Accidente en el tramo Locotal–Villa Tunari: la vía está transitable con precaución - Red Uno</t>
         </is>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPZHNBTEdaQm5Wby1lTF9mWlQ2aGg0MVc4S0MwVWJ3dUJ5WWU5X3IwYWhKRjk5VWtYWEJHRDF4QldVc29laVNPSTJNWFBDSkNFQlFSYTJUXzNMNF9hckFBN1I2T2xoQUtYQ2V6MDNTZHhHVk9qeTBCdHRpM2ZLd0pyOFRweUUxX19STzRHTHg5VUY5d1lhS0tDeXpCdklqcTZGT1J4R0xnSDhoak1EZ2dtNUhSTUV6b1o0U0VSdWY5X0E3U05Tc1dYVEN2WFZUeFhPMTBJTmowNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTFozcEEwNXBqV19sS2VibXh0MGt0QlhsX1djSTFGQW5zNlFLRHZpNVVnZ1JmWDQ4LVRHX2Rmb3B5UU9qV0FZQmJCaUZYdmwyNG1NenJ4Qzlzd0NJTGs1SjMxdFRtRFBzSUkybGJfZFFaNFZBc21FSUJYSFVkQkVkSEhQaGw0UFVzeXctZHo3cjNsYm5weXJlOU1wcmFncnNhMC1BQUpvNWlDX1NxZXU4b09kVFFWR2tSVEk2UTdXXzB3TjA?oc=5</t>
         </is>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>1</v>
-      </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>-16.556</v>
+      </c>
+      <c r="O57" t="n">
+        <v>-65.569</v>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Villa Tunari, Cochabamba</t>
+        </is>
+      </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>Villa Tunari</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>noticia:12gfagq</t>
+          <t>noticia:wi18tm</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -8045,78 +8061,62 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-10-22 11:28</t>
+          <t>2026-10-22 11:53</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1792682880000</v>
+        <v>1792684426000</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>FmBolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>tecnológica</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Reportan triple colisión entre dos camiones y un bus en la carretera Cochabamba-Santa Cruz - FmBolivia</t>
+          <t>Accidente en El Sillar deja heridos y derrame de combustible: esto es lo último que se sabe - Red Uno</t>
         </is>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNMTNBaFZNMU9SR25vdVBuNXlZY3g4VkFWYXRiQnNSaUFjemZhUHZWNHg4V2owU2xfNndBak94TnU2cHNUVXdNNWl2eUdHZVNMbVZweTR5M0o0bWdTNUN4QkoxUkI2TDBmVE03M09zRGhJRVFzV0tPZ1NCWEJLUkt1ZGN4UGduOUZMQnJoM0tMYTh0ZlFxaFJNUkJqaWFPazRlMzN3ajhjUEdUYXlZRndpb3RSdTFCX2tCZGJxQ0x4SlBISWJsRVoyN3ZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPZHNBTEdaQm5Wby1lTF9mWlQ2aGg0MVc4S0MwVWJ3dUJ5WWU5X3IwYWhKRjk5VWtYWEJHRDF4QldVc29laVNPSTJNWFBDSkNFQlFSYTJUXzNMNF9hckFBN1I2T2xoQUtYQ2V6MDNTZHhHVk9qeTBCdHRpM2ZLd0pyOFRweUUxX19STzRHTHg5VUY5d1lhS0tDeXpCdklqcTZGT1J4R0xnSDhoak1EZ2dtNUhSTUV6b1o0U0VSdWY5X0E3U05Tc1dYVEN2WFZUeFhPMTBJTmowNA?oc=5</t>
         </is>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" t="n">
-        <v>-17.39</v>
-      </c>
-      <c r="O58" t="n">
-        <v>-66.16</v>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>Cochabamba, Cochabamba</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>noticia:1uq1bxy</t>
+          <t>noticia:12gfagq</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -8126,15 +8126,15 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-10-22 10:44</t>
+          <t>2026-10-22 11:28</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1792680273000</v>
+        <v>1792682880000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>FmBolivia</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -8152,13 +8152,13 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Reportan triple colisión en la carretera Cochabamba–Santa Cruz - Red Uno</t>
+          <t>Reportan triple colisión entre dos camiones y un bus en la carretera Cochabamba-Santa Cruz - FmBolivia</t>
         </is>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNNUROMzd1UDJRWVZZQ011cFd2c1FSdER1ZzdleU04cXpwYk5HaUZrLXoyU2NzdFk1dnNRUndhUWt0cG9DX09rSjlLcDItU0tzcmQtS3E4dDQ4ZF9HdGJLdk13ek9BNHJUWVlCcklrM25rZ01RbXhLalRBT1FGdDNReHdlTFZkNkJ5ZFd3N3NZVFVmOFUxbEhHN0RsaUxiSVZsM0lXVEFYSHVRQlhsOEtJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNMTNBaFZNMU9SR25vdVBuNXlZY3g4VkFWYXRiQnNSaUFjemZhUHZWNHg4V2owU2xfNndBak94TnU2cHNUVXdNNWl2eUdHZVNMbVZweTR5M0o0bWdTNUN4QkoxUkI2TDBmVE03M09zRGhJRVFzV0tPZ1NCWEJLUkt1ZGN4UGduOUZMQnJoM0tMYTh0ZlFxaFJNUkJqaWFPazRlMzN3ajhjUEdUYXlZRndpb3RSdTFCX2tCZGJxQ0x4SlBISWJsRVoyN3ZR?oc=5</t>
         </is>
       </c>
       <c r="L59" t="n">
@@ -8197,7 +8197,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>noticia:1jl2oid</t>
+          <t>noticia:1uq1bxy</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -8207,15 +8207,15 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-10-22 07:49</t>
+          <t>2026-10-22 10:44</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1792669785000</v>
+        <v>1792680273000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>eju.tv</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -8224,39 +8224,39 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - eju.tv</t>
+          <t>Reportan triple colisión en la carretera Cochabamba–Santa Cruz - Red Uno</t>
         </is>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQbTBrUmlla3FvVU1EX1pxcUI3SXYzbUFFMzlnRzhlSDJwMGpWWURxYjIwSkJBRGdCazMzT01hVy1qMFY3RnJLbC1XNXJ4bU55aDJVeXpNUlRsbzQ3T3hiRXJ5SWlhNmw5cDZFanNoWFBtQ01Gd3dscXltWmU5VHBSQlN3c2IwNGxuVE5tQ3lOT1RmNzRiVi1hc0hn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNNUROMzd1UDJRWVZZQ011cFd2c1FSdER1ZzdleU04cXpwYk5HaUZrLXoyU2NzdFk1dnNRUndhUWt0cG9DX09rSjlLcDItU0tzcmQtS3E4dDQ4ZF9HdGJLdk13ek9BNHJUWVlCcklrM25rZ01RbXhLalRBT1FGdDNReHdlTFZkNkJ5ZFd3N3NZVFVmOFUxbEhHN0RsaUxiSVZsM0lXVEFYSHVRQlhsOEtJ?oc=5</t>
         </is>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>-17.781</v>
+        <v>-17.39</v>
       </c>
       <c r="O60" t="n">
-        <v>-63.139</v>
+        <v>-66.16</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Santa Cruz, Santa Cruz</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -8266,19 +8266,19 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Cochabamba</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>noticia:yqgeq</t>
+          <t>noticia:1jl2oid</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -8288,15 +8288,15 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-10-22 07:43</t>
+          <t>2026-10-22 07:49</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1792669426000</v>
+        <v>1792669785000</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>eju.tv</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -8314,13 +8314,13 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - Red Uno</t>
+          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - eju.tv</t>
         </is>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNVEh1bFlCanFuOTJid2EzYS1meG5oekFJcGFaME1fTk9sUnZpd3U0UXFHUFVJSW1jc1hzM2VFOFprT2xNYjBzbmswZmdJV3dremRIS0I4MDNzRjBnbEttWEhfOWZBbmFrRnNHWDFVLVFoM0VkZkxkaW4tMmZlSFJLei1heTFHMU0wSmxQVVRZN0cwaXQzcDBtZkdwTUFma0RXU2dwLXRnLTBkNGN3Vm1fV3hEdlM1dWZ1SEsw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQbTBrUmlla3FvVU1EX1pxcUI3SXYzbUFFMzlnRzhlSDJwMGpWWURxYjIwSkJBRGdCazMzT01hVy1qMFY3RnJLbC1XNXJ4bU55aDJVeXpNUlRsbzQ3T3hiRXJ5SWlhNmw5cDZFanNoWFBtQ01Gd3dscXltWmU5VHBSQlN3c2IwNGxuVE5tQ3lOT1RmNzRiVi1hc0hn?oc=5</t>
         </is>
       </c>
       <c r="L61" t="n">
@@ -8359,7 +8359,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>noticia:n32ahi</t>
+          <t>noticia:yqgeq</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -8369,69 +8369,150 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-10-22 05:30</t>
+          <t>2026-10-22 07:43</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1792661402000</v>
+        <v>1792669426000</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>FmBolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Senamhi anuncia el inicio de la temporada de lluvias en Bolivia y prevé granizadas como la de La Paz - FmBolivia</t>
+          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - Red Uno</t>
         </is>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNVEh1bFlCanFuOTJid2EzYS1meG5oekFJcGFaME1fTk9sUnZpd3U0UXFHUFVJSW1jc1hzM2VFOFprT2xNYjBzbmswZmdJV3dremRIS0I4MDNzRjBnbEttWEhfOWZBbmFrRnNHWDFVLVFoM0VkZkxkaW4tMmZlSFJLei1heTFHMU0wSmxQVVRZN0cwaXQzcDBtZkdwTUFma0RXU2dwLXRnLTBkNGN3Vm1fV3hEdlM1dWZ1SEsw?oc=5</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>1</v>
+      </c>
+      <c r="N62" t="n">
+        <v>-17.781</v>
+      </c>
+      <c r="O62" t="n">
+        <v>-63.139</v>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Santa Cruz, Santa Cruz</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>Santa Cruz de la Sierra</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>noticia:n32ahi</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>noticia</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-10-22 05:30</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>1792661402000</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>FmBolivia</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>meteorológica</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>verde</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Senamhi anuncia el inicio de la temporada de lluvias en Bolivia y prevé granizadas como la de La Paz - FmBolivia</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
           <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQNmVPRnVBMGQzdEI5SUp3Z3ZGVExwTUR6TWNadGQ1QldUS1o2QVFvUl9sVEZKMDVyQVVrS25rU1RSQlJKWXk1YzE0NUhidjhpcmFaSlhZUDZvcE9XcG1KTFNTYmowUU1CSFJNOVR2UHNmMk1iT3N0RVBteHkzZkgyRFROYk1pdkpxVHZya3N2X2FVLVQxbURFVVZlb1NzRjZzTE95TXFVUXFJNkVZakQ2bUhVQzB0SXk3TVhXUTJXa0dycTE1MWVQRFpDX3lDSWFqUGwzU2NtNA?oc=5</t>
         </is>
       </c>
-      <c r="L62" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="n">
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
         <v>-16.169</v>
       </c>
-      <c r="O62" t="n">
+      <c r="O63" t="n">
         <v>-68.09</v>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>La Paz, La Paz</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>nombre de municipio en el titular</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="R63" t="inlineStr">
         <is>
           <t>La Paz</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>Nuestra Señora de La Paz</t>
         </is>
@@ -9001,7 +9082,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-10-25 13:00</t>
+          <t>2026-10-25 13:29</t>
         </is>
       </c>
     </row>
@@ -9024,7 +9105,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4">
@@ -9081,7 +9162,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sala de Situación Bolivia – CCES. Base de eventos de amenazas (datos preliminares de fuentes abiertas). Consulta: 2026-10-25 13:00.</t>
+          <t>Sala de Situación Bolivia – CCES. Base de eventos de amenazas (datos preliminares de fuentes abiertas). Consulta: 2026-10-25 13:29.</t>
         </is>
       </c>
     </row>

--- a/docs/datos/datos_bolivia.xlsx
+++ b/docs/datos/datos_bolivia.xlsx
@@ -9082,7 +9082,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-10-25 13:29</t>
+          <t>2026-10-25 13:57</t>
         </is>
       </c>
     </row>
@@ -9162,7 +9162,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sala de Situación Bolivia – CCES. Base de eventos de amenazas (datos preliminares de fuentes abiertas). Consulta: 2026-10-25 13:29.</t>
+          <t>Sala de Situación Bolivia – CCES. Base de eventos de amenazas (datos preliminares de fuentes abiertas). Consulta: 2026-10-25 13:57.</t>
         </is>
       </c>
     </row>

--- a/docs/datos/datos_bolivia.xlsx
+++ b/docs/datos/datos_bolivia.xlsx
@@ -514,20 +514,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>noticia:4blj1l</t>
+          <t>noticia:1xi48lm</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-25 12:59</t>
+          <t>2026-10-25 13:02</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1792947573000</v>
+        <v>1792947732000</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Santa Cruz: Dos cisternas se incendian tras colisionar - La Patria Bolivia</t>
+          <t>Reportan el incendio de dos camiones cisterna en la carretera a Camiri - EL DÍA - Noticias de Bolivia para el mundo</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -559,18 +559,18 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>FmBolivia; La Patria Bolivia; Opinión Bolivia; Red Uno</t>
+          <t>EL DÍA - Noticias de Bolivia para el mundo; La Patria Bolivia; Opinión Bolivia; Red Uno</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>-17.781</v>
+        <v>-20.05</v>
       </c>
       <c r="N2" t="n">
-        <v>-63.139</v>
+        <v>-63.486</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Santa Cruz, Santa Cruz</t>
+          <t>Camiri, Santa Cruz</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -580,12 +580,12 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Camiri</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQbHdpcUF6dXpjaW1TT1ZmdGJtUUVLMTNMRTVqVkFUdkNsZlRvenVkckFUWmI4NDFmc2ZHd2RVcWRSSE5YRVpOTUlESGw2V3JONXpwS0RISGNZd01SejNuMkY4NzFYYXp4aWo2RE9VMkFYUkVwZ3JRRmM5MWlRSjlBWk16azdkQ3FjdEtkaWc5NERkTzk2SllVOQ?oc=5 | https://news.google.com/rss/articles/CBMixgFBVV95cUxQLXlqSFdvWUVhQUNadnpkdE5lUTZQS0lobThzUTZWbDNJTE94alVhaDBaYU9Fd09SSGt3UlR3Y0dfZlNIcml1ZktnWjctNk1Na3V4S0tINFNkMXM0OHBoV2lCTTBiYXlPUTA3T2ZkeXE2RElYWjhfVHd3Nng1Z0E4alBmOFI5NDFwX09kazZlSWl2OVR2ZVR6MDhvSHFnSmJKbTFXSEFDNFFYcWVDNGtYWEQ0bDhJel9CaEpEZWZ4SWN0TE9Ya0E?oc=5 | https://news.google.com/rss/articles/CBMiugFBVV95cUxNUTdxSzBJVTZnajZQUXhyTVhwMlpvU0tyZGVBYnFwV2kyZWthenNRT1FDRVJFZnk4ZndGTFQ0cnFXZmZ1WHZaMFhUbWo0SWkzcjcxbjJwU3pKUXR4WEVZLVlRNFpxOUVMY2NNNUZsbmJSMk9xZG1sTklEdEtGSXJyUUp5b0R2dVpYcHJLdTRNRlRjcWpNNXg4c0Z4UWwteFc2dDRqVmpnQnFfQXgwN0twTzl4ZWhYdUtYWGfSAboBQVVfeXFMTVE3cUswSVU2Z2o2UFF4ck1YcDJab1NLcmRlQWJxcFdpMmVrYXpzUU9RQ0VSRWZ5OGZ3RkxUNHJxV2ZmdVh2WjBYVG1qNElpM3I3MW4ycFN6SlF0eFhFWS1ZUTRacTlFTGNjTTVGbG5iUjJPcWRtbE5JRHRLRklyclFKeW9EdnVaWHByS3U0TUZUY3FqTTV4OHNGeFFsLXhXNnQ0alZqZ0JxX0F4MDdLcE85eGVoWHVLWFhn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNN0traUpaNVFIOU0zeFZod2tkQWhZZFQ1Q3dxc2xCVy1RNnJIX2xQbTlhT3RVckdNdHV4ZFVLQThvd2UzNDlCa3VmaWprTnU3R05rVkVkdEVCU1hFMlFsLTJ6REIySnl5VFJfdV9pQmVDTzlqUWFUSi1GQ0JvTVJVQ2dpeVBydnpMV0dYOThENTFRUDgxVFloSVg3bnN4dGo2aEVCbDFKaUgydWNISnJVUTNB?oc=5 | https://news.google.com/rss/articles/CBMimAFBVV95cUxQbHdpcUF6dXpjaW1TT1ZmdGJtUUVLMTNMRTVqVkFUdkNsZlRvenVkckFUWmI4NDFmc2ZHd2RVcWRSSE5YRVpOTUlESGw2V3JONXpwS0RISGNZd01SejNuMkY4NzFYYXp4aWo2RE9VMkFYUkVwZ3JRRmM5MWlRSjlBWk16azdkQ3FjdEtkaWc5NERkTzk2SllVOQ?oc=5 | https://news.google.com/rss/articles/CBMixgFBVV95cUxQLXlqSFdvWUVhQUNadnpkdE5lUTZQS0lobThzUTZWbDNJTE94alVhaDBaYU9Fd09SSGt3UlR3Y0dfZlNIcml1ZktnWjctNk1Na3V4S0tINFNkMXM0OHBoV2lCTTBiYXlPUTA3T2ZkeXE2RElYWjhfVHd3Nng1Z0E4alBmOFI5NDFwX09kazZlSWl2OVR2ZVR6MDhvSHFnSmJKbTFXSEFDNFFYcWVDNGtYWEQ0bDhJel9CaEpEZWZ4SWN0TE9Ya0E?oc=5</t>
         </is>
       </c>
     </row>
@@ -666,20 +666,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>noticia:1uf38hl</t>
+          <t>noticia:1sg8pi0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25 10:59</t>
+          <t>2026-10-25 09:59</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1792940350000</v>
+        <v>1792936752000</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>¡Cisterna con combustible en llamas! Reportan impresionante incendio en la carretera a Camiri - Red Uno</t>
+          <t>Bus de agrupación musical sufre accidente rumbo al trópico de Cochabamba | VIDEO - Red Uno</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -715,54 +715,54 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>-20.05</v>
+        <v>-17.39</v>
       </c>
       <c r="N4" t="n">
-        <v>-63.486</v>
+        <v>-66.16</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Camiri, Santa Cruz</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Camiri</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxORUhqeWpKY1FHRWoxaHN0UXFzS3dpeHh6N0NwLUJOZTlZcDVoNHN0VnI0by1qMWtZZEkxVmtUNjdNTFhjaEFQU2IyMlNwZW95WFBzbFJPVVB6TjJtdjNENk1LWVlsMUxUUzBNVzkxRk1HZ3lQU0s2M1lRVlRuaXlkMmJrd3AyTGpIdXItNkhlU3dhTzBRME56Rm1DSlZCYjNxSnNTbTFqNWRoUkdraHhlREhuYldqeFk2N3poWEx2M08?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOVDVzVTJNM2JuQ25sMThEaVZNOUNRd3FGT3RhVnFrZXZ2NDQ1YlluTVdhbVNUQnA1MGNESHRSWVUzbC1kRVh3OTR0emtlTG91cmRWeFJ5dk5zb3p2WFRyMEJUV3FNRnY1WHhRUU9WLTlJcmNyNXJZZFdoM0JoZjNpa3hjUXhMM0xrUDJab2VadkM5RWZYQ3lWZTVDdzg1akxJT2lxcDVNNzI0NG1hejdfdkUyTQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>noticia:1sg8pi0</t>
+          <t>noticia:167wlhz</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-25 09:59</t>
+          <t>2026-10-25 07:53</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1792936752000</v>
+        <v>1792929231000</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bus de agrupación musical sufre accidente rumbo al trópico de Cochabamba | VIDEO - Red Uno</t>
+          <t>¡A sacar el paraguas! Santa cruz amanece con lluvia, frío y complicaciones en el tránsito vehicular - Red Uno</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -793,62 +793,62 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>-17.39</v>
+        <v>-17.781</v>
       </c>
       <c r="N5" t="n">
-        <v>-66.16</v>
+        <v>-63.139</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Cochabamba, Cochabamba</t>
+          <t>Santa Cruz, Santa Cruz</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOVDVzVTJNM2JuQ25sMThEaVZNOUNRd3FGT3RhVnFrZXZ2NDQ1YlluTVdhbVNUQnA1MGNESHRSWVUzbC1kRVh3OTR0emtlTG91cmRWeFJ5dk5zb3p2WFRyMEJUV3FNRnY1WHhRUU9WLTlJcmNyNXJZZFdoM0JoZjNpa3hjUXhMM0xrUDJab2VadkM5RWZYQ3lWZTVDdzg1akxJT2lxcDVNNzI0NG1hejdfdkUyTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOY1ZpYktLR3pUQXotUndVR3puUzVHbW1YTzNyUmJvUHB4Q2JmelRvOEdaRldOUm1xLVJnbGR5VWcxTjNEM3ZUYktCUWtVM0hKSjFuRGdpX0JxN0M5MVZBSG1aVURyVWktdmxwbUtRT19ydU5LdzNTZ2Zpb2ozdHlMUUdTVlAyVk4xODBnV0hyTXdVVndyNzV3VC1KMzFnV3lpcFFXSk9MdDZOTWlWakNwT1FnNDh6QVdjazVYZDVVMkdaLU0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>noticia:167wlhz</t>
+          <t>noticia:bzr7eh</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-25 07:53</t>
+          <t>2026-10-25 07:09</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1792929231000</v>
+        <v>1792926572000</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>¡A sacar el paraguas! Santa cruz amanece con lluvia, frío y complicaciones en el tránsito vehicular - Red Uno</t>
+          <t>Alerta naranja por riesgo de desbordes de ríos - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>hidrológica</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -863,74 +863,74 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>El Diario - Bolivia; El Mundo Bolivia; FmBolivia</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>-17.781</v>
+        <v>-16.169</v>
       </c>
       <c r="N6" t="n">
-        <v>-63.139</v>
+        <v>-68.09</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Santa Cruz, Santa Cruz</t>
+          <t>La Paz, La Paz</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Nuestra Señora de La Paz</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOY1ZpYktLR3pUQXotUndVR3puUzVHbW1YTzNyUmJvUHB4Q2JmelRvOEdaRldOUm1xLVJnbGR5VWcxTjNEM3ZUYktCUWtVM0hKSjFuRGdpX0JxN0M5MVZBSG1aVURyVWktdmxwbUtRT19ydU5LdzNTZ2Zpb2ozdHlMUUdTVlAyVk4xODBnV0hyTXdVVndyNzV3VC1KMzFnV3lpcFFXSk9MdDZOTWlWakNwT1FnNDh6QVdjazVYZDVVMkdaLU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNNGZKSDVaZkowWUFGSEUyTWR3d3dsc04waFBLLWUtcVpiTDYzbmNtYTN1RkFLbjAwN3dxT0xZc3pqc3REUXduZVltQ2Fud1BZLTh1bTNiTEJueVUwV0dERS1iUXZqMHd0UnFrQ3E2SFAzbm5lQ1I4U29MaHJFbWFvdVRTeFY4Wl9rSmc3RkpaQ2xwX0oz?oc=5 | https://news.google.com/rss/articles/CBMipwFBVV95cUxPZW00RkxJSklTelNrS2hqczJDWHlwcENFX2lnSEUyTEFPaDFRQ2JvMUcyd3NfYjg0UE9ORGxHRzB4ZDh3U0hQQ1JSQlhsaUY4N3ByMUUxei1SaUZnNlp6T3hsLVdiMGhKaXhsV1FNSUNQMHlvQ19qdk56SEF0d2RXVFctS0VPT25kNGZCRDdvZ2dxU0VoUUJKU0ZBd0ZycFNEZFh0T3ZjOA?oc=5 | https://news.google.com/rss/articles/CBMiwAFBVV95cUxPZm85aHphekQ4U3BZZkp1ZkF6ZVdSUHgtZmltS1FxUUgza1AwcndWWDJZOWctT0RiVmVabmg5SG42NnJWMlJMMnBlYTlYaVdSb09sR0dnVDdpT29faTdiaDUtZElJdlQ3eTdjR2VsWjlta1FOS1U2Vm1vV3JwWkpvbEw1ZUR3akgwQTZnQnVENjJtVkQtVUpKVEJTeWNJSE1CaEFKa2VqMmZXbWk3ekR4ZWpmZ1Z3elFQaWNaNFJuMXA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>noticia:bzr7eh</t>
+          <t>noticia:1fo4ig4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-25 07:09</t>
+          <t>2026-10-25 01:08</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1792926572000</v>
+        <v>1792904880000</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Alerta naranja por riesgo de desbordes de ríos - El Diario - Bolivia</t>
+          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>hidrológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>roja</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -941,57 +941,41 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia; El Mundo Bolivia; FmBolivia</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>-16.169</v>
-      </c>
-      <c r="N7" t="n">
-        <v>-68.09</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>La Paz, La Paz</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>La Paz</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Nuestra Señora de La Paz</t>
-        </is>
-      </c>
+          <t>diarioelpueblo.com.pe</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNNGZKSDVaZkowWUFGSEUyTWR3d3dsc04waFBLLWUtcVpiTDYzbmNtYTN1RkFLbjAwN3dxT0xZc3pqc3REUXduZVltQ2Fud1BZLTh1bTNiTEJueVUwV0dERS1iUXZqMHd0UnFrQ3E2SFAzbm5lQ1I4U29MaHJFbWFvdVRTeFY4Wl9rSmc3RkpaQ2xwX0oz?oc=5 | https://news.google.com/rss/articles/CBMipwFBVV95cUxPZW00RkxJSklTelNrS2hqczJDWHlwcENFX2lnSEUyTEFPaDFRQ2JvMUcyd3NfYjg0UE9ORGxHRzB4ZDh3U0hQQ1JSQlhsaUY4N3ByMUUxei1SaUZnNlp6T3hsLVdiMGhKaXhsV1FNSUNQMHlvQ19qdk56SEF0d2RXVFctS0VPT25kNGZCRDdvZ2dxU0VoUUJKU0ZBd0ZycFNEZFh0T3ZjOA?oc=5 | https://news.google.com/rss/articles/CBMiwAFBVV95cUxPZm85aHphekQ4U3BZZkp1ZkF6ZVdSUHgtZmltS1FxUUgza1AwcndWWDJZOWctT0RiVmVabmg5SG42NnJWMlJMMnBlYTlYaVdSb09sR0dnVDdpT29faTdiaDUtZElJdlQ3eTdjR2VsWjlta1FOS1U2Vm1vV3JwWkpvbEw1ZUR3akgwQTZnQnVENjJtVkQtVUpKVEJTeWNJSE1CaEFKa2VqMmZXbWk3ekR4ZWpmZ1Z3elFQaWNaNFJuMXA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQcmFrT3dwcEs0X3U2NWxnOGJwNnI2WHdWTGZYbzEyNnJzUWhkbU9TRWhfSlB5UkMwX2gyMmxYUmVNWmxNOVR6V0twRHpFMTVIYjBKbHQ2TXN2d2w5dkFpcWJCcUJMZldaX01sNWtQV2ZJOGpRVzR3NDVIU0pJc1BNVg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>noticia:1fo4ig4</t>
+          <t>noticia:r1uot6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-25 01:08</t>
+          <t>2026-10-24 20:00</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1792904880000</v>
+        <v>1792886439000</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
+          <t>vuelco deja heridos en ruta Oruro – Huanuni - La Patria Bolivia</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1000,18 +984,18 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>roja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1023,37 +1007,53 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>diarioelpueblo.com.pe</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
+          <t>La Patria Bolivia</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>-17.97</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-67.11</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Oruro, Oruro</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQcmFrT3dwcEs0X3U2NWxnOGJwNnI2WHdWTGZYbzEyNnJzUWhkbU9TRWhfSlB5UkMwX2gyMmxYUmVNWmxNOVR6V0twRHpFMTVIYjBKbHQ2TXN2d2w5dkFpcWJCcUJMZldaX01sNWtQV2ZJOGpRVzR3NDVIU0pJc1BNVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNNDQtMG1KT1lLWW5nem9Jbm5JWDZKNlRWZmFmRlBxWDlDeXlSWnJ5d2NsTlpxa0JIS25oVWVZOC1majZVbWhOVDIxR0dLOFlzY2VpVzVoVk1mQnF3dXVwLUFZVHc1UjlXZzF5T05CY3U0ZldLVkw1VzBTek5zanpjQW1xalltWHNiaXI3dTNR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>noticia:r1uot6</t>
+          <t>noticia:1ytw450</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-24 20:00</t>
+          <t>2026-10-24 18:58</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1792886439000</v>
+        <v>1792882686000</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>vuelco deja heridos en ruta Oruro – Huanuni - La Patria Bolivia</t>
+          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1062,18 +1062,18 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>roja</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1085,53 +1085,37 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>-17.97</v>
-      </c>
-      <c r="N9" t="n">
-        <v>-67.11</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Oruro, Oruro</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Oruro</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Oruro</t>
-        </is>
-      </c>
+          <t>diarioelpueblo.com.pe</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNNDQtMG1KT1lLWW5nem9Jbm5JWDZKNlRWZmFmRlBxWDlDeXlSWnJ5d2NsTlpxa0JIS25oVWVZOC1majZVbWhOVDIxR0dLOFlzY2VpVzVoVk1mQnF3dXVwLUFZVHc1UjlXZzF5T05CY3U0ZldLVkw1VzBTek5zanpjQW1xalltWHNiaXI3dTNR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNZ1U3bEVuaVdjVE1zSU9lOHJZTVRZLVZaemhldGNnT1JBWDJvbzdvM3paVVNhLUlyWHF2akNuSXJOLXdyTGRuejRlV1FuMjVkTjA3NmdRdmgtRWlUeTFBV1dEMzBvejBxaXZJdUZZWkRVTF9VLU5BcjFGZGFEQ09WWQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>noticia:1ytw450</t>
+          <t>noticia:1g006zh</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-24 18:58</t>
+          <t>2026-10-24 17:02</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1792882686000</v>
+        <v>1792875752000</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
+          <t>Accidente en la carretera a Mayaya deja siete heridos del grupo Los Chicos Fieles - El Potosí</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1140,18 +1124,18 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>roja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1159,41 +1143,57 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>diarioelpueblo.com.pe</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
+          <t>EL DÍA - Noticias de Bolivia para el mundo; El Potosí; La Razón Digital Bolivia; Opinión Bolivia</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>-19.58</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-65.75</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Potosí, Potosí</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Potosí</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Potosí</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNZ1U3bEVuaVdjVE1zSU9lOHJZTVRZLVZaemhldGNnT1JBWDJvbzdvM3paVVNhLUlyWHF2akNuSXJOLXdyTGRuejRlV1FuMjVkTjA3NmdRdmgtRWlUeTFBV1dEMzBvejBxaXZJdUZZWkRVTF9VLU5BcjFGZGFEQ09WWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPTGQwaVBfdG1JdVRMUTN4LVVvN0ppc3dreDJVVllDR3RmX0xpMzB4b0pvVTNSV1B6T0ZEWTdEZkNsRUdSNzhLaC1CWHN5WktNWk1nRWpTdVZiYjI3TlJlX2xlVTI5MjlRU2hiY1gteml4YWVFbDNPSVRBZmtITlQzbmhaUXVmcThRa2xsQTJIOXZuNzlSdm12MEdyOEZHdw?oc=5 | https://news.google.com/rss/articles/CBMizwFBVV95cUxPeGd3VWpCWXJ0YTJIeDJLcktzWG1jdUh0TjFXb01wSTkxbHNXZU94VWNDMkxnTjlJZVdpbkprMEY2NE80RXYyUWxUQXVnbl9lUXR2b28zTEh6cTJLVEQ4TUNja2kzRlhadVBFZFVwV1U2TlhseXZMZ20zZTZiUFpWRjdCOWNBMHU5XzdMV3JqQjV4TEE3bHRMOXR6Nm55eHZUNnFHSDdVRk8zVkY4RkVsUUtUN0JYdkREWGZncmJ3ZWc2T1BuUm1ZLTlfcHVabFE?oc=5 | https://news.google.com/rss/articles/CBMizAFBVV95cUxNYjNxaHg3YllRRTJYdFd1clAtUlROSGlFNVg5eUVZUGJoOEZ4MWM5QU5WQm1YTDc4NXc3SjhWMUw0TkZfSHlMLUQ1bmpTME1Kb1JaM0ExamFHYTd3VlU4MXRWdTZ1bzh1SGYtbGE1a3dBaG93bjg1OGc0S0JfRE43c3dVMVltN0dQQzNhQUNhM0FjVUNRUDRSamlJYlk2dEJpUTBuY2hBcTFucTVRN0ZtYnc5bzdmTV9LQm1uVUxaZS1tUE9IejhBVDRCdU_SAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>noticia:1g006zh</t>
+          <t>noticia:1ukcn97</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-24 17:02</t>
+          <t>2026-10-24 13:26</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1792875752000</v>
+        <v>1792862794000</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a Mayaya deja siete heridos del grupo Los Chicos Fieles - El Potosí</t>
+          <t>Esta es la lista preliminar de los heridos en el accidente del grupo 'Los chicos fieles', el conductor está grave - El Deber</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1213,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1221,62 +1221,46 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>EL DÍA - Noticias de Bolivia para el mundo; El Potosí; La Razón Digital Bolivia; Opinión Bolivia</t>
-        </is>
-      </c>
-      <c r="M11" t="n">
-        <v>-19.58</v>
-      </c>
-      <c r="N11" t="n">
-        <v>-65.75</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Potosí, Potosí</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
+          <t>El Deber; Red Uno</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPTGQwaVBfdG1JdVRMUTN4LVVvN0ppc3dreDJVVllDR3RmX0xpMzB4b0pvVTNSV1B6T0ZEWTdEZkNsRUdSNzhLaC1CWHN5WktNWk1nRWpTdVZiYjI3TlJlX2xlVTI5MjlRU2hiY1gteml4YWVFbDNPSVRBZmtITlQzbmhaUXVmcThRa2xsQTJIOXZuNzlSdm12MEdyOEZHdw?oc=5 | https://news.google.com/rss/articles/CBMizwFBVV95cUxPeGd3VWpCWXJ0YTJIeDJLcktzWG1jdUh0TjFXb01wSTkxbHNXZU94VWNDMkxnTjlJZVdpbkprMEY2NE80RXYyUWxUQXVnbl9lUXR2b28zTEh6cTJLVEQ4TUNja2kzRlhadVBFZFVwV1U2TlhseXZMZ20zZTZiUFpWRjdCOWNBMHU5XzdMV3JqQjV4TEE3bHRMOXR6Nm55eHZUNnFHSDdVRk8zVkY4RkVsUUtUN0JYdkREWGZncmJ3ZWc2T1BuUm1ZLTlfcHVabFE?oc=5 | https://news.google.com/rss/articles/CBMizAFBVV95cUxNYjNxaHg3YllRRTJYdFd1clAtUlROSGlFNVg5eUVZUGJoOEZ4MWM5QU5WQm1YTDc4NXc3SjhWMUw0TkZfSHlMLUQ1bmpTME1Kb1JaM0ExamFHYTd3VlU4MXRWdTZ1bzh1SGYtbGE1a3dBaG93bjg1OGc0S0JfRE43c3dVMVltN0dQQzNhQUNhM0FjVUNRUDRSamlJYlk2dEJpUTBuY2hBcTFucTVRN0ZtYnc5bzdmTV9LQm1uVUxaZS1tUE9IejhBVDRCdU_SAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOczZKbFd1QzRpak92LXpPWXZXQXJObnBQTG9qRFBlUUV5dThMWXhzckFFUHAyb2thU1JwRmJDSEZfaEdTUXh1bjZvQWpYMGhfUno3cWZ4MGpldEpoQXhzSlVzTm5LLW9OcjB2MWRsdHQ2UlI2SjEtZ085ZTR5Z3pEVmtBTF9lc29Kd0RhaTRUWkM4eGZJNWhBSXZqWmxuNW10dlQwYW9mdzItcWZWTkU0?oc=5 | https://news.google.com/rss/articles/CBMivAFBVV95cUxPczBQcnE2SzFGMXc3b1lsTkNxVWRmS3Vnb01xOTV2WmVva3J2RVlteWpHZ3VJS2dNWGV5NW5FX3ZncnVKTEVDTGpBRndTU1FxeWxtaS1fb1FscGxXMWNXUE9zbHdob1AxVFl1eHB5OU1yUnNoOXJ6U21oVG9PVDA1ak1xQl9hUlB4V0RaQXJqZENGUm8zMUJEY3J0WW5ENE5ObWJLNmpWN0RkSmFJbnZUZGR5UFRPd3QyUFY4WQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>noticia:1ukcn97</t>
+          <t>noticia:2avehj</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-24 13:26</t>
+          <t>2026-10-24 12:53</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1792862794000</v>
+        <v>1792860813000</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Esta es la lista preliminar de los heridos en el accidente del grupo 'Los chicos fieles', el conductor está grave - El Deber</t>
+          <t>Sequía en Cochabamba: más de un centenar de cabezas de ganado murieron en el cono sur - Red Uno</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>climatológica</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -1288,10 +1272,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1299,46 +1283,62 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>El Deber; Red Uno</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
+          <t>Red Uno</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>-17.39</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-66.16</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Cochabamba, Cochabamba</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOczZKbFd1QzRpak92LXpPWXZXQXJObnBQTG9qRFBlUUV5dThMWXhzckFFUHAyb2thU1JwRmJDSEZfaEdTUXh1bjZvQWpYMGhfUno3cWZ4MGpldEpoQXhzSlVzTm5LLW9OcjB2MWRsdHQ2UlI2SjEtZ085ZTR5Z3pEVmtBTF9lc29Kd0RhaTRUWkM4eGZJNWhBSXZqWmxuNW10dlQwYW9mdzItcWZWTkU0?oc=5 | https://news.google.com/rss/articles/CBMivAFBVV95cUxPczBQcnE2SzFGMXc3b1lsTkNxVWRmS3Vnb01xOTV2WmVva3J2RVlteWpHZ3VJS2dNWGV5NW5FX3ZncnVKTEVDTGpBRndTU1FxeWxtaS1fb1FscGxXMWNXUE9zbHdob1AxVFl1eHB5OU1yUnNoOXJ6U21oVG9PVDA1ak1xQl9hUlB4V0RaQXJqZENGUm8zMUJEY3J0WW5ENE5ObWJLNmpWN0RkSmFJbnZUZGR5UFRPd3QyUFY4WQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOOFQxc2Vzc0QwS19ydC13RkRPZnZQU3JkSTl5U3kzdUdMSldTcm5HVEhWRzZyN19CLUlwcUs4MW03Ui1obVBtdzQ3QWFQc1RKdzh3MXJ5QkpRS2pRNm50V1lVb09ScGJnaVVlemVfZlRsWjdObnRmR1FGMnlMMHAyc2pMandndy10T2twcWx6OFh4UHdvbVlFbllwME9WQ2pQVjNTQzBxeTg5YnF3bDREeHVDYXpObFFIaTZZQWtYUE12cGQ1ZGRhT0syNjVhZWs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>noticia:2avehj</t>
+          <t>noticia:3dv7b0</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-24 12:53</t>
+          <t>2026-10-24 11:43</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1792860813000</v>
+        <v>1792856591000</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sequía en Cochabamba: más de un centenar de cabezas de ganado murieron en el cono sur - Red Uno</t>
+          <t>Accidente en Caranavi: vehículo de Los Chicos Fieles cae a un barranco y deja varios heridos - FmBolivia</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>climatológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1361,62 +1361,62 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>FmBolivia; La Patria Bolivia; Red Uno</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>-17.39</v>
+        <v>-15.813</v>
       </c>
       <c r="N13" t="n">
-        <v>-66.16</v>
+        <v>-67.46299999999999</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Cochabamba, Cochabamba</t>
+          <t>Caranavi, La Paz</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Caranavi</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOOFQxc2Vzc0QwS19ydC13RkRPZnZQU3JkSTl5U3kzdUdMSldTcm5HVEhWRzZyN19CLUlwcUs4MW03Ui1obVBtdzQ3QWFQc1RKdzh3MXJ5QkpRS2pRNm50V1lVb09ScGJnaVVlemVfZlRsWjdObnRmR1FGMnlMMHAyc2pMandndy10T2twcWx6OFh4UHdvbVlFbllwME9WQ2pQVjNTQzBxeTg5YnF3bDREeHVDYXpObFFIaTZZQWtYUE12cGQ1ZGRhT0syNjVhZWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNeEFrOEtOMHZxMW42REFPU0x1MG5oQjlBMkJucWRLZ292alBXekJKeURBN3NLTVVadWI0OWF4UGtSVXBzTE01eWFSU1kyMUhNZ04zMWNMaUxnMDBBZ0EwTktXbjlaVTBUUmNqa3AwY19KNTU2LWh5LW9IVElVdTdnaHFPanJPd2FqMUxzaUhXZmVpYU1saGc?oc=5 | https://news.google.com/rss/articles/CBMi2wFBVV95cUxOdTVUZUQxVTdvYTdONDQxVlhUTzBOS2hKLW1rS1NUcmRYRnlCVlhIcHZlSjdsaktkQm5CWkFYa3lDQkxnMlh0b3prX0lha1BtbW1qS1VuYnNiX3FiZkYyNDJDR0tqZ0pKMU5TeC04SXV4UUJOTUlPUTB6ek01bzUxTUsydjZqZzI3S3ZLUnRWSUFUVk44WEpKUl9rbzRLb2IwYl9sLVlrYmt5d2ZHNUtGd3lRNnYzMlhuMkJOZW1XSUl2N1BxZWpHbm5XTDJhRUtnR190QWQ1TDlTUVk?oc=5 | https://news.google.com/rss/articles/CBMizAFBVV95cUxNcE1KaHZyUTJCSElxRU9nVzdhTnczWjJGTEhFMEs0bHp2cUdFeHd3VTB0NmVFcjdEN1dsZDZLY2k1ZFFUWkhKV19PU3V2czNyamh1ZE9YajVSVF8xczF6OFhZcWFvYV9EcWg4ZDNCb2p3enhXbFpRYnJMdGdaTXNrWUZSYVhKNTVicWlCLTJ5OE05Z1BvNEx1eEloUk5qTGN3ZHNzbzZWSVljbnRmSERJUWdxRDc0MjJxMGtycWJaaVhXQUUxVUlaWVZLOWE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>noticia:3dv7b0</t>
+          <t>clima:Potosí:2026-10-24:viento:1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-24 11:43</t>
+          <t>2026-10-24 10:55</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1792856591000</v>
+        <v>1792853727284</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Accidente en Caranavi: vehículo de Los Chicos Fieles cae a un barranco y deja varios heridos - FmBolivia</t>
+          <t>Potosí 2026-10-24: 60.5 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1431,7 +1431,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1439,57 +1439,57 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>FmBolivia; La Patria Bolivia; Red Uno</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>-15.813</v>
+        <v>-19.58</v>
       </c>
       <c r="N14" t="n">
-        <v>-67.46299999999999</v>
+        <v>-65.75</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Caranavi, La Paz</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Caranavi</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNeEFrOEtOMHZxMW42REFPU0x1MG5oQjlBMkJucWRLZ292alBXekJKeURBN3NLTVVadWI0OWF4UGtSVXBzTE01eWFSU1kyMUhNZ04zMWNMaUxnMDBBZ0EwTktXbjlaVTBUUmNqa3AwY19KNTU2LWh5LW9IVElVdTdnaHFPanJPd2FqMUxzaUhXZmVpYU1saGc?oc=5 | https://news.google.com/rss/articles/CBMi2wFBVV95cUxOdTVUZUQxVTdvYTdONDQxVlhUTzBOS2hKLW1rS1NUcmRYRnlCVlhIcHZlSjdsaktkQm5CWkFYa3lDQkxnMlh0b3prX0lha1BtbW1qS1VuYnNiX3FiZkYyNDJDR0tqZ0pKMU5TeC04SXV4UUJOTUlPUTB6ek01bzUxTUsydjZqZzI3S3ZLUnRWSUFUVk44WEpKUl9rbzRLb2IwYl9sLVlrYmt5d2ZHNUtGd3lRNnYzMlhuMkJOZW1XSUl2N1BxZWpHbm5XTDJhRUtnR190QWQ1TDlTUVk?oc=5 | https://news.google.com/rss/articles/CBMizAFBVV95cUxNcE1KaHZyUTJCSElxRU9nVzdhTnczWjJGTEhFMEs0bHp2cUdFeHd3VTB0NmVFcjdEN1dsZDZLY2k1ZFFUWkhKV19PU3V2czNyamh1ZE9YajVSVF8xczF6OFhZcWFvYV9EcWg4ZDNCb2p3enhXbFpRYnJMdGdaTXNrWUZSYVhKNTVicWlCLTJ5OE05Z1BvNEx1eEloUk5qTGN3ZHNzbzZWSVljbnRmSERJUWdxRDc0MjJxMGtycWJaaVhXQUUxVUlaWVZLOWE?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>clima:Potosí:2026-10-24:viento:1</t>
+          <t>noticia:1ax0bpy</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-24 10:55</t>
+          <t>2026-10-24 10:32</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1792853727284</v>
+        <v>1792852364000</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Potosí 2026-10-24: 60.5 km/h de ráfagas pronosticadas</t>
+          <t>Creció el Bermejo tras la tormenta: así está el puerto de chalanas en este momento - Que Pasa Salta</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1498,11 +1498,11 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1521,58 +1521,58 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>Que Pasa Salta</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>-19.58</v>
+        <v>-22.721</v>
       </c>
       <c r="N15" t="n">
-        <v>-65.75</v>
+        <v>-64.32599999999999</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Bermejo, Tarija</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Tarija</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Bermejo</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVld9IBfkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVldw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>noticia:1ax0bpy</t>
+          <t>gdacs:WF1033142:0</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-24 10:32</t>
+          <t>2026-10-24 07:06</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1792852364000</v>
+        <v>1792839995000</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Creció el Bermejo tras la tormenta: así está el puerto de chalanas en este momento - Que Pasa Salta</t>
+          <t>Green forest fire notification in Bolivia</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1599,58 +1599,58 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Que Pasa Salta</t>
+          <t>GDACS</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>-22.721</v>
+        <v>-13.06332</v>
       </c>
       <c r="N16" t="n">
-        <v>-64.32599999999999</v>
+        <v>-67.66426</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Bermejo, Tarija</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Tarija</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Bermejo</t>
+          <t>Ixiamas</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVld9IBfkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVldw?oc=5</t>
+          <t>http://www.gdacs.org/report.aspx?eventtype=WF&amp;eventid=1033142</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>gdacs:WF1033142:0</t>
+          <t>noticia:1shhqva</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-24 07:06</t>
+          <t>2026-10-24 06:33</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1792839995000</v>
+        <v>1792838034000</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Green forest fire notification in Bolivia</t>
+          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1673,70 +1673,70 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>GDACS</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>-13.06332</v>
+        <v>-17.97</v>
       </c>
       <c r="N17" t="n">
-        <v>-67.66426</v>
+        <v>-67.11</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Oruro, Oruro</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Oruro</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Ixiamas</t>
+          <t>Oruro</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>http://www.gdacs.org/report.aspx?eventtype=WF&amp;eventid=1033142</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQYzB6N082XzFRRnVtcDVmUkYyWjcxUzV2Z3Frd1I0WDNXSnZtY0QzOU1PUkNLMktVT1Vra2FSeXhxZDRuOFZYZjFwejl6ejJTbWY2MGJuSGN3ZHdrdG5JUkgzSXBkbDYtaHlackY3OVFuNWdLcFNpdWNHRU9vNGdoVWx2ODFVdzJXYUxnM0tUcjJvZmc?oc=5 | https://news.google.com/rss/articles/CBMikAFBVV95cUxQS2FPaHd3UnFBRjRoa0lKUm1MNUQ5S00zN1RJZE5fWlVUQnhiY0lLcFRkY2JZak1mZ0c2WEVMVUNJVUJTMGFLNHg4S2ZKNTRqLXJHM09ET19hX1pZeTQwUkdEc2huTHVpcno2QTRZbnhralVRWXozcWc1a2pHUEpBeTV1cWgzTWRwaDEweURKeVE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>noticia:1shhqva</t>
+          <t>clima:Potosí:2026-10-25:viento:1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-24 06:33</t>
+          <t>2026-10-24 02:55</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1792838034000</v>
+        <v>1792824927736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
+          <t>Potosí 2026-10-25: 60.5 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1751,62 +1751,62 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>-17.97</v>
+        <v>-19.58</v>
       </c>
       <c r="N18" t="n">
-        <v>-67.11</v>
+        <v>-65.75</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQYzB6N082XzFRRnVtcDVmUkYyWjcxUzV2Z3Frd1I0WDNXSnZtY0QzOU1PUkNLMktVT1Vra2FSeXhxZDRuOFZYZjFwejl6ejJTbWY2MGJuSGN3ZHdrdG5JUkgzSXBkbDYtaHlackY3OVFuNWdLcFNpdWNHRU9vNGdoVWx2ODFVdzJXYUxnM0tUcjJvZmc?oc=5 | https://news.google.com/rss/articles/CBMikAFBVV95cUxQS2FPaHd3UnFBRjRoa0lKUm1MNUQ5S00zN1RJZE5fWlVUQnhiY0lLcFRkY2JZak1mZ0c2WEVMVUNJVUJTMGFLNHg4S2ZKNTRqLXJHM09ET19hX1pZeTQwUkdEc2huTHVpcno2QTRZbnhralVRWXozcWc1a2pHUEpBeTV1cWgzTWRwaDEweURKeVE?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>clima:Potosí:2026-10-25:viento:1</t>
+          <t>noticia:1uil931</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-24 02:55</t>
+          <t>2026-10-23 22:49</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1792824927736</v>
+        <v>1792810149000</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Potosí 2026-10-25: 60.5 km/h de ráfagas pronosticadas</t>
+          <t>Accidente de tránsito en la ruta hacia Alto Beni deja varios heridos - El Deber</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1821,7 +1821,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1829,62 +1829,62 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>El Deber</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>-19.58</v>
+        <v>-15.578</v>
       </c>
       <c r="N19" t="n">
-        <v>-65.75</v>
+        <v>-67.44</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Alto Beni, La Paz</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Alto Beni</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQakFJRmx3RlJEMkVHU0pxWXZ2ZU1ib04tZy1yeTB2OGhrYk9CU3pMaDVpRThNZktZMS14UzA2Y1VIcEQtZDg3cEU2SmlzQnBmUVVvM0ZNYzZWNExWUXQ3aHpnd3lqOHFVV3pNbDRLS1NQNGtwb2RjSFpleHJkOG5zSXVtWjVIS1dLejNybktRWTJVZXh3WkFUQVE5T2tMdFdn?oc=5 | https://news.google.com/rss/articles/CBMilwFBVV95cUxQMF9BNnUzLURKNGRMUUJ1VXVRSXNnMlBsQnVXOG0tRlFtY3pvRDNPQmNJMWN2RzJVaWdoWndmcHFnTkZFZnJxRkZtMThYYWlwN09ueUgtei1pSE1hZ2FtSzN6elY4VXJHbzFxdll0eWh0ZkxwQkQ1SDZ5b0E3MlVENGZEWGZHUGlwVG4wd2x3OFNEMVpibnFr?oc=5 | https://news.google.com/rss/articles/CBMimgFBVV95cUxNbmwzSnd6c2tFMXBWY0tiemJqRm5CNllOT2p1U0FhdW5QNGFBVXlSZVM1ak5jNGZvcXNVaUQzN3ZQQTlPbmVjQ2Y5RFl2dWVLeUN5NUFodDF0alEyZWlmOHFZWkVVbjdQbkl3ZWtmS25wQWM2TmRZZDBGM2xlS0ZhUzAweXRmcmhVWGY5dV9CUnFBNGtWZHZDSWVB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>noticia:1uil931</t>
+          <t>clima:Santa Cruz:2026-10-24:viento:1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-23 22:49</t>
+          <t>2026-10-23 20:55</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1792810149000</v>
+        <v>1792803329663</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Accidente de tránsito en la ruta hacia Alto Beni deja varios heridos - El Deber</t>
+          <t>Santa Cruz 2026-10-24: 78.1 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1899,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1907,57 +1907,57 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>El Deber</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>-15.578</v>
+        <v>-17.78</v>
       </c>
       <c r="N20" t="n">
-        <v>-67.44</v>
+        <v>-63.18</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Alto Beni, La Paz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Alto Beni</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQakFJRmx3RlJEMkVHU0pxWXZ2ZU1ib04tZy1yeTB2OGhrYk9CU3pMaDVpRThNZktZMS14UzA2Y1VIcEQtZDg3cEU2SmlzQnBmUVVvM0ZNYzZWNExWUXQ3aHpnd3lqOHFVV3pNbDRLS1NQNGtwb2RjSFpleHJkOG5zSXVtWjVIS1dLejNybktRWTJVZXh3WkFUQVE5T2tMdFdn?oc=5 | https://news.google.com/rss/articles/CBMilwFBVV95cUxQMF9BNnUzLURKNGRMUUJ1VXVRSXNnMlBsQnVXOG0tRlFtY3pvRDNPQmNJMWN2RzJVaWdoWndmcHFnTkZFZnJxRkZtMThYYWlwN09ueUgtei1pSE1hZ2FtSzN6elY4VXJHbzFxdll0eWh0ZkxwQkQ1SDZ5b0E3MlVENGZEWGZHUGlwVG4wd2x3OFNEMVpibnFr?oc=5 | https://news.google.com/rss/articles/CBMimgFBVV95cUxNbmwzSnd6c2tFMXBWY0tiemJqRm5CNllOT2p1U0FhdW5QNGFBVXlSZVM1ak5jNGZvcXNVaUQzN3ZQQTlPbmVjQ2Y5RFl2dWVLeUN5NUFodDF0alEyZWlmOHFZWkVVbjdQbkl3ZWtmS25wQWM2TmRZZDBGM2xlS0ZhUzAweXRmcmhVWGY5dV9CUnFBNGtWZHZDSWVB?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-24:viento:1</t>
+          <t>noticia:rabz5p</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-23 20:55</t>
+          <t>2026-10-23 20:44</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1792803329663</v>
+        <v>1792802686000</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-24: 78.1 km/h de ráfagas pronosticadas</t>
+          <t>Tome previsiones: se pronostican lluvias y ambiente caluroso para este fin de semana en Cochabamba - Red Uno</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1966,11 +1966,11 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -1989,70 +1989,70 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>-17.78</v>
+        <v>-17.39</v>
       </c>
       <c r="N21" t="n">
-        <v>-63.18</v>
+        <v>-66.16</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTlU5NVFpY1RheTN5ZE1IbG5VYTh2Sk5hZHpHeWI3LVdnSFg2cFJFdnBCVkxiUjNKcUgyUW16SWxpMXFkMHdad2xFN043bklJeG1iQ0V1V3hBZk1Ga3NscjdPVWUySmt4bDNTdWlmSUdOMmNlZ2hkSWZFMmk4VGs0Nm9TcnRCTDhINmtnQU9zZDBUY05HcWpxN3FOX3N1dmVJblE0MGc5di1Ma1N2dGNxOUtoV1MzNnl1OXpRaTZ2UGxMc3RDWndubHVQNUd0eVROMGR2OGxVemtOaEc4bTNRaA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>noticia:rabz5p</t>
+          <t>noticia:1jfk053</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-23 20:44</t>
+          <t>2026-10-23 19:08</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1792802686000</v>
+        <v>1792796931000</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Tome previsiones: se pronostican lluvias y ambiente caluroso para este fin de semana en Cochabamba - Red Uno</t>
+          <t>Sequía en Pasorapa: el ganado muere por falta de agua y alistan declaratoria de desastre - Red Uno</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>climatológica</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -2071,14 +2071,14 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>-17.39</v>
+        <v>-18.38</v>
       </c>
       <c r="N22" t="n">
-        <v>-66.16</v>
+        <v>-64.649</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Cochabamba, Cochabamba</t>
+          <t>Pasorapa, Cochabamba</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2088,49 +2088,49 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Pasorapa</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTlU5NVFpY1RheTN5ZE1IbG5VYTh2Sk5hZHpHeWI3LVdnSFg2cFJFdnBCVkxiUjNKcUgyUW16SWxpMXFkMHdad2xFN043bklJeG1iQ0V1V3hBZk1Ga3NscjdPVWUySmt4bDNTdWlmSUdOMmNlZ2hkSWZFMmk4VGs0Nm9TcnRCTDhINmtnQU9zZDBUY05HcWpxN3FOX3N1dmVJblE0MGc5di1Ma1N2dGNxOUtoV1MzNnl1OXpRaTZ2UGxMc3RDWndubHVQNUd0eVROMGR2OGxVemtOaEc4bTNRaA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNQVhTWE8zdE1BQ3lueWJPeV9wUDNsSmJpS0NJTWppMUY4QmlQSUFHVjRORmtrVHQ3MHB0T1pyS25PamxnY0hBQUtzOVRvSUNaUkdGb1RWSGl4dFA4Z3VINVpQTk1pZUpDdUIyUU5hZS1oNGhBa1RWcFhScVMwVTFrVlJaOFQ4OWFqRWVUZ051bHVJTlMxRTBhRFVLUEV2dTZFdDgtRkxJM3VvN3YzUWJfVk41ZWR5U1JoNmx0WFFkMmNTWGVleGNIQlNxWUJzdHIxSWtz?oc=5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>noticia:1jfk053</t>
+          <t>noticia:ix3l8o</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-23 19:08</t>
+          <t>2026-10-23 18:25</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1792796931000</v>
+        <v>1792794310000</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sequía en Pasorapa: el ganado muere por falta de agua y alistan declaratoria de desastre - Red Uno</t>
+          <t>Oruro evalúa suspender clases presenciales por más de 200 casos de Coxsackie - Visión 360</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>climatológica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2141,77 +2141,77 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>Red Uno; Visión 360</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>-18.38</v>
+        <v>-17.97</v>
       </c>
       <c r="N23" t="n">
-        <v>-64.649</v>
+        <v>-67.11</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Pasorapa, Cochabamba</t>
+          <t>Oruro, Oruro</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Oruro</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Pasorapa</t>
+          <t>Oruro</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNQVhTWE8zdE1BQ3lueWJPeV9wUDNsSmJpS0NJTWppMUY4QmlQSUFHVjRORmtrVHQ3MHB0T1pyS25PamxnY0hBQUtzOVRvSUNaUkdGb1RWSGl4dFA4Z3VINVpQTk1pZUpDdUIyUU5hZS1oNGhBa1RWcFhScVMwVTFrVlJaOFQ4OWFqRWVUZ051bHVJTlMxRTBhRFVLUEV2dTZFdDgtRkxJM3VvN3YzUWJfVk41ZWR5U1JoNmx0WFFkMmNTWGVleGNIQlNxWUJzdHIxSWtz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0c9IBywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0cw?oc=5 | https://news.google.com/rss/articles/CBMiywFBVV95cUxNMFdHaVpKRmMyOENDYm16UXJPenVSQnpmTE94bDc4UFhqakluMUdvZjAwamUxT3BVWUpJQm8xVHBWengxQmhWM1hjU3d2YXFrLXpVU2VrZDJiMXZLMlQ5bGxGOHFETFhYM0s2RjlUTlhkd0g2eXQweDFHaTlKNGNMUlJfOWg2a0JjTklXUWZKc1BmUXZuZFZ2MF9fV2lEYUY4LXNiNmk3cF9FNjVtTl9GWFotT2ltS0xXTnM1dENvSU9kbFRMalFrYVdXOA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>noticia:ix3l8o</t>
+          <t>noticia:1xqv9m7</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-23 18:25</t>
+          <t>2026-10-23 18:09</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1792794310000</v>
+        <v>1792793370000</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Oruro evalúa suspender clases presenciales por más de 200 casos de Coxsackie - Visión 360</t>
+          <t>Tres heridos en tremendo choque cerca de Oncativo - El Diario del centro del país</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -2219,77 +2219,61 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Red Uno; Visión 360</t>
-        </is>
-      </c>
-      <c r="M24" t="n">
-        <v>-17.97</v>
-      </c>
-      <c r="N24" t="n">
-        <v>-67.11</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Oruro, Oruro</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Oruro</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>Oruro</t>
-        </is>
-      </c>
+          <t>El Diario del centro del país</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0c9IBywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0cw?oc=5 | https://news.google.com/rss/articles/CBMiywFBVV95cUxNMFdHaVpKRmMyOENDYm16UXJPenVSQnpmTE94bDc4UFhqakluMUdvZjAwamUxT3BVWUpJQm8xVHBWengxQmhWM1hjU3d2YXFrLXpVU2VrZDJiMXZLMlQ5bGxGOHFETFhYM0s2RjlUTlhkd0g2eXQweDFHaTlKNGNMUlJfOWg2a0JjTklXUWZKc1BmUXZuZFZ2MF9fV2lEYUY4LXNiNmk3cF9FNjVtTl9GWFotT2ltS0xXTnM1dENvSU9kbFRMalFrYVdXOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZERhbTJMQUJVb3hmZFlSZmRGZkdBLWdFTGJVQzdqZkE4aGhhWmdQZ2JDRW1ndkJLWU90VTZ6Ti1JOUZzcFZfcE1zbkRHU1B3YTF4UkVzdllFa1p3SUlObURGamF0Vm9kc3dPLTZVWFJ4NWZZQmlySElPNHhZTnRGNGNZUWw2ZlI1eVBEQkNGNEhLWTNiLWJLUS0xYjA0UWRhc0d6bVN4aVVLSVdsQWlpMUZYdWw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>noticia:1xqv9m7</t>
+          <t>noticia:1itd1r7</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-23 18:09</t>
+          <t>2026-10-23 15:01</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1792793370000</v>
+        <v>1792782098000</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tres heridos en tremendo choque cerca de Oncativo - El Diario del centro del país</t>
+          <t>Intensa lluvia y granizada en La Paz inundan vías y elevan el nivel de los ríos - eju.tv</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2301,57 +2285,73 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>El Diario del centro del país</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
+          <t>eju.tv</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>-16.169</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-68.09</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>La Paz, La Paz</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>La Paz</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Nuestra Señora de La Paz</t>
+        </is>
+      </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZERhbTJMQUJVb3hmZFlSZmRGZkdBLWdFTGJVQzdqZkE4aGhhWmdQZ2JDRW1ndkJLWU90VTZ6Ti1JOUZzcFZfcE1zbkRHU1B3YTF4UkVzdllFa1p3SUlObURGamF0Vm9kc3dPLTZVWFJ4NWZZQmlySElPNHhZTnRGNGNZUWw2ZlI1eVBEQkNGNEhLWTNiLWJLUS0xYjA0UWRhc0d6bVN4aVVLSVdsQWlpMUZYdWw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNWU9QWElKQXEyN3UxVm4xbzJzbEJ1TU1NTHZlRUp6YndmeU9GQnJKcTluVEJ2ZHQ5cGp3aWhlMUd5ektWQlBpUVNmZnZuRnJwMXlydzAzX0FBVnY5UDMzQTBkWVRNRUNJSlRvX3MyQVhMcEhIMW9WSUpXckVSd0RJWk1KMFBKWmJNU3diQVlEN1Y5aVV6eVBaZXpOMnFIWWxaMlRlY0ZB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>noticia:1itd1r7</t>
+          <t>noticia:51709n</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-23 15:01</t>
+          <t>2026-10-23 13:38</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1792782098000</v>
+        <v>1792777139000</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Intensa lluvia y granizada en La Paz inundan vías y elevan el nivel de los ríos - eju.tv</t>
+          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - eju.tv</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2359,77 +2359,77 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>eju.tv</t>
+          <t>Red Uno; eju.tv</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>-16.169</v>
+        <v>-17.764</v>
       </c>
       <c r="N26" t="n">
-        <v>-68.09</v>
+        <v>-62.903</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>La Paz, La Paz</t>
+          <t>Cotoca, Santa Cruz</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Nuestra Señora de La Paz</t>
+          <t>Cotoca</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNWU9QWElKQXEyN3UxVm4xbzJzbEJ1TU1NTHZlRUp6YndmeU9GQnJKcTluVEJ2ZHQ5cGp3aWhlMUd5ektWQlBpUVNmZnZuRnJwMXlydzAzX0FBVnY5UDMzQTBkWVRNRUNJSlRvX3MyQVhMcEhIMW9WSUpXckVSd0RJWk1KMFBKWmJNU3diQVlEN1Y5aVV6eVBaZXpOMnFIWWxaMlRlY0ZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPcjZTSmprRGVoNlRqQmdBTE5VM3pRQ1ZFakFUbzVyMUhiaDVkT0liaG9UNEZXekV6bWsycUk4X1JCSEY5RjhNVlZaTk9ULUFuZkY3NnZuWmZ1a19leUhFdlIyQV9kLWxlSkxfeXFhcFRTZjZ2YkpQQlJ1dkNLMDBjaGZ4SkhyQ0RfcnhKSEg5WURCQVQwbENYTHEzUzJSaUEzMGo2bWdyS3lsM016LXc?oc=5 | https://news.google.com/rss/articles/CBMi0AFBVV95cUxOVGY3YVRLWWxYM0IycjF4dlNUeUhqZG90Yng4aWhmN3A5ai02WENWYnF4bWpoZHFKMGc1X0JPRHdRRVZfSlA4UmZFa2kxYkNIS3ZtQ1NvNlNCME51eVZTRkRKSUQ5MmRoaWl5Tkt5NHpPUEFwemN2YTV1djFwdHlqQnFqRHNPenhYcTlsanJPcXhpOVV1NmFBUXZyazQ2MkUzM0dSZy02ZllxTGtjcl9ldzdHSktTRlVaalZJc1pubUNQMWFTbzVEOUJ1UmhCdEJt?oc=5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>noticia:51709n</t>
+          <t>noticia:11rddql</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-23 13:38</t>
+          <t>2026-10-23 13:22</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1792777139000</v>
+        <v>1792776139000</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - eju.tv</t>
+          <t>Intensifican acciones preventivas contra el dengue en Caranavi - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2437,77 +2437,77 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Red Uno; eju.tv</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>-17.764</v>
+        <v>-15.813</v>
       </c>
       <c r="N27" t="n">
-        <v>-62.903</v>
+        <v>-67.46299999999999</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Cotoca, Santa Cruz</t>
+          <t>Caranavi, La Paz</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>Cotoca</t>
+          <t>Caranavi</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPcjZTSmprRGVoNlRqQmdBTE5VM3pRQ1ZFakFUbzVyMUhiaDVkT0liaG9UNEZXekV6bWsycUk4X1JCSEY5RjhNVlZaTk9ULUFuZkY3NnZuWmZ1a19leUhFdlIyQV9kLWxlSkxfeXFhcFRTZjZ2YkpQQlJ1dkNLMDBjaGZ4SkhyQ0RfcnhKSEg5WURCQVQwbENYTHEzUzJSaUEzMGo2bWdyS3lsM016LXc?oc=5 | https://news.google.com/rss/articles/CBMi0AFBVV95cUxOVGY3YVRLWWxYM0IycjF4dlNUeUhqZG90Yng4aWhmN3A5ai02WENWYnF4bWpoZHFKMGc1X0JPRHdRRVZfSlA4UmZFa2kxYkNIS3ZtQ1NvNlNCME51eVZTRkRKSUQ5MmRoaWl5Tkt5NHpPUEFwemN2YTV1djFwdHlqQnFqRHNPenhYcTlsanJPcXhpOVV1NmFBUXZyazQ2MkUzM0dSZy02ZllxTGtjcl9ldzdHSktTRlVaalZJc1pubUNQMWFTbzVEOUJ1UmhCdEJt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOMjhSeDJBek5iaFhDcnFzX1lKelgwZmUwLTJnbEhMdDRMelUxNks5Ti1pRHh3dDhTcC1YZEdqM3FJOGdqVHRvcXVhRlpCQzVDTEZMUFBkV1NrYVQ2LXRqTTBhcGRQc21CQ0VabzZaNExXb1BjTzJ2Uk5BcFF0VG5XOFNRa3lqUWlJSnRFUUVXYnNpbXB0LVVmSXVWSzJxcmVpdVVxUC1KOUhTQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>noticia:11rddql</t>
+          <t>noticia:fcm3nx</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-23 13:22</t>
+          <t>2026-10-23 12:58</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1792776139000</v>
+        <v>1792774699000</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Intensifican acciones preventivas contra el dengue en Caranavi - El Diario - Bolivia</t>
+          <t>[VIDEO] Así fue el accidente de moto que dejó un adolescente fallecido y un hombre gravemente herido - Red Uno</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2519,73 +2519,57 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
-        </is>
-      </c>
-      <c r="M28" t="n">
-        <v>-15.813</v>
-      </c>
-      <c r="N28" t="n">
-        <v>-67.46299999999999</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>Caranavi, La Paz</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>La Paz</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>Caranavi</t>
-        </is>
-      </c>
+          <t>Red Uno</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOMjhSeDJBek5iaFhDcnFzX1lKelgwZmUwLTJnbEhMdDRMelUxNks5Ti1pRHh3dDhTcC1YZEdqM3FJOGdqVHRvcXVhRlpCQzVDTEZMUFBkV1NrYVQ2LXRqTTBhcGRQc21CQ0VabzZaNExXb1BjTzJ2Uk5BcFF0VG5XOFNRa3lqUWlJSnRFUUVXYnNpbXB0LVVmSXVWSzJxcmVpdVVxUC1KOUhTQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOSmJMazhUemNfRHpWcDBoTVFZMUpwdlVKVUtvUXZNTGRRRHlwLW5KNmNhcmFnd1czbi1yalhFMnpSS1dmUE9jVzNlOS1kMWZtRzBHZ2EtcDRDdU5Gc2JUQVIwM2xPa2lZVmswRi1SUFVPcm8xcHlGN3F2UThTSDdKMDNyYnJmVkcxazNLLVBLOWFYM09FVUpmVnN5RVhpSVo2V1VCVmFwQ1gzTmRUWVp2aXMwcmxHRS1GV2p3NTBtR2RzM2wwVHUzaGJkRXJYbHdvaDlhWm5YMTk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>noticia:fcm3nx</t>
+          <t>noticia:1cjx1qd</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-23 12:58</t>
+          <t>2026-10-23 12:39</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1792774699000</v>
+        <v>1792773575000</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>[VIDEO] Así fue el accidente de moto que dejó un adolescente fallecido y un hombre gravemente herido - Red Uno</t>
+          <t>Más de 60 municipios en La Paz sufren falta de lluvias - La Patria Bolivia</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2597,37 +2581,53 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Red Uno</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
+          <t>La Patria Bolivia</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>-16.169</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-68.09</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>La Paz, La Paz</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>La Paz</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Nuestra Señora de La Paz</t>
+        </is>
+      </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOSmJMazhUemNfRHpWcDBoTVFZMUpwdlVKVUtvUXZNTGRRRHlwLW5KNmNhcmFnd1czbi1yalhFMnpSS1dmUE9jVzNlOS1kMWZtRzBHZ2EtcDRDdU5Gc2JUQVIwM2xPa2lZVmswRi1SUFVPcm8xcHlGN3F2UThTSDdKMDNyYnJmVkcxazNLLVBLOWFYM09FVUpmVnN5RVhpSVo2V1VCVmFwQ1gzTmRUWVp2aXMwcmxHRS1GV2p3NTBtR2RzM2wwVHUzaGJkRXJYbHdvaDlhWm5YMTk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE52Qi03Z1J6OS1CR2liRVZ0VlhCcmVQWFV6RUdGNXdrbzZRNXFjTWRaRnc1b3VoV0xaY3RIdncxNlNnYkxyUXo5MTlJWmMwWDNSMDE4ZHI2VkpWajFPaUF2SmRVYkk2eDZYQ1RfUU9ieENrZG9UVVFiaXZSeGI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>noticia:1cjx1qd</t>
+          <t>clima:Sucre:2026-10-23:viento:1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-23 12:39</t>
+          <t>2026-10-23 06:55</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1792773575000</v>
+        <v>1792752927735</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Más de 60 municipios en La Paz sufren falta de lluvias - La Patria Bolivia</t>
+          <t>Sucre 2026-10-23: 66.2 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2636,11 +2636,11 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -2659,40 +2659,40 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>-16.169</v>
+        <v>-19.03</v>
       </c>
       <c r="N30" t="n">
-        <v>-68.09</v>
+        <v>-65.26000000000001</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>La Paz, La Paz</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Chuquisaca</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>Nuestra Señora de La Paz</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE52Qi03Z1J6OS1CR2liRVZ0VlhCcmVQWFV6RUdGNXdrbzZRNXFjTWRaRnc1b3VoV0xaY3RIdncxNlNnYkxyUXo5MTlJWmMwWDNSMDE4ZHI2VkpWajFPaUF2SmRVYkk2eDZYQ1RfUU9ieENrZG9UVVFiaXZSeGI?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>clima:Sucre:2026-10-23:viento:1</t>
+          <t>clima:Santa Cruz:2026-10-24:viento:2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2701,11 +2701,11 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1792752927735</v>
+        <v>1792752927734</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sucre 2026-10-23: 66.2 km/h de ráfagas pronosticadas</t>
+          <t>Santa Cruz 2026-10-24: 85 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2714,11 +2714,11 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -2741,24 +2741,24 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>-19.03</v>
+        <v>-17.78</v>
       </c>
       <c r="N31" t="n">
-        <v>-65.26000000000001</v>
+        <v>-63.18</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Chuquisaca</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2770,33 +2770,33 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-24:viento:2</t>
+          <t>usgs:us6000u49c</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-23 06:55</t>
+          <t>2026-10-22 22:45</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1792752927734</v>
+        <v>1792723541183</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-24: 85 km/h de ráfagas pronosticadas</t>
+          <t>Sismo M 4.5 - 58 km SW of Atocha, Bolivia</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>geológica</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -2815,58 +2815,58 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>USGS</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>-17.78</v>
+        <v>-21.3469</v>
       </c>
       <c r="N32" t="n">
-        <v>-63.18</v>
+        <v>-66.5795</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>58 km SW of Atocha, Bolivia</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>San Pablo</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://earthquake.usgs.gov/earthquakes/eventpage/us6000u49c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>usgs:us6000u49c</t>
+          <t>clima:Santa Cruz:2026-10-22:viento:1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-22 22:45</t>
+          <t>2026-10-22 21:55</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1792723541183</v>
+        <v>1792720528712</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sismo M 4.5 - 58 km SW of Atocha, Bolivia</t>
+          <t>Santa Cruz 2026-10-22: 67.7 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>geológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -2893,40 +2893,40 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>USGS</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>-21.3469</v>
+        <v>-17.78</v>
       </c>
       <c r="N33" t="n">
-        <v>-66.5795</v>
+        <v>-63.18</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>58 km SW of Atocha, Bolivia</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>San Pablo</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>https://earthquake.usgs.gov/earthquakes/eventpage/us6000u49c</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-22:viento:1</t>
+          <t>clima:Santa Cruz:2026-10-23:viento:2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-22: 67.7 km/h de ráfagas pronosticadas</t>
+          <t>Santa Cruz 2026-10-23: 83.9 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2948,11 +2948,11 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -3004,33 +3004,33 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-23:viento:2</t>
+          <t>noticia:1hhvre7</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-22 21:55</t>
+          <t>2026-10-22 19:36</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1792720528712</v>
+        <v>1792712202000</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-23: 83.9 km/h de ráfagas pronosticadas</t>
+          <t>Virgen de Cotoca: Controlan incendio en depósito de materiales plásticos - El Mundo Bolivia</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -3049,53 +3049,53 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>El Mundo Bolivia</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>-17.78</v>
+        <v>-17.764</v>
       </c>
       <c r="N35" t="n">
-        <v>-63.18</v>
+        <v>-62.903</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
+          <t>Cotoca, Santa Cruz</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
           <t>Santa Cruz</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Santa Cruz</t>
-        </is>
-      </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Cotoca</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcDF6VE5FNzRaWGRuUzFKeXhnZ21DZTRaaEtrVEJEa1Z3ejg2VG1ONG1ENmlDWlkyVjlkQkJwS2F1XzBGMFQwSHd4OEwxTW1PbHdGcUh1ckV6SGpDd2hiN0dkeUVTcnFXT3RjOU1kLXZtVVdZY2hkZS1pcVpVUFhnRktqcHY5UnBrY0xUMDRETjl6N0pXT3A5amxhMA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>noticia:1hhvre7</t>
+          <t>noticia:bksnde</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-22 19:36</t>
+          <t>2026-10-22 17:01</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1792712202000</v>
+        <v>1792702880000</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Virgen de Cotoca: Controlan incendio en depósito de materiales plásticos - El Mundo Bolivia</t>
+          <t>Reportan un incendio cerca de la carretera a Cotoca - eju.tv</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>El Mundo Bolivia</t>
+          <t>eju.tv</t>
         </is>
       </c>
       <c r="M36" t="n">
@@ -3153,27 +3153,27 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcDF6VE5FNzRaWGRuUzFKeXhnZ21DZTRaaEtrVEJEa1Z3ejg2VG1ONG1ENmlDWlkyVjlkQkJwS2F1XzBGMFQwSHd4OEwxTW1PbHdGcUh1ckV6SGpDd2hiN0dkeUVTcnFXT3RjOU1kLXZtVVdZY2hkZS1pcVpVUFhnRktqcHY5UnBrY0xUMDRETjl6N0pXT3A5amxhMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPNGtpbnBfRnRBalVudnBlZHdVQ0ZSaUplZmtvTGE0aTQzdkxWS3d4My1EZEJ1UE9FNFQ3RmpyZGVsbS1qNEM1QUVFRFAxM2pYT1VqQzRuVjRtZnVNUGlKODNMc0F1a3l6TUpuQmtlUWNlVTVEWWU5ZGZtQm5LWUp3Sg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>noticia:bksnde</t>
+          <t>noticia:17hz69v</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-22 17:01</t>
+          <t>2026-10-22 13:05</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1792702880000</v>
+        <v>1792688709000</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Reportan un incendio cerca de la carretera a Cotoca - eju.tv</t>
+          <t>Accidente en El Sillar deja al menos 29 heridos - La Razón Digital Bolivia</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3182,18 +3182,18 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -3205,53 +3205,37 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>eju.tv</t>
-        </is>
-      </c>
-      <c r="M37" t="n">
-        <v>-17.764</v>
-      </c>
-      <c r="N37" t="n">
-        <v>-62.903</v>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>Cotoca, Santa Cruz</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Santa Cruz</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>Cotoca</t>
-        </is>
-      </c>
+          <t>La Razón Digital Bolivia</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPNGtpbnBfRnRBalVudnBlZHdVQ0ZSaUplZmtvTGE0aTQzdkxWS3d4My1EZEJ1UE9FNFQ3RmpyZGVsbS1qNEM1QUVFRFAxM2pYT1VqQzRuVjRtZnVNUGlKODNMc0F1a3l6TUpuQmtlUWNlVTVEWWU5ZGZtQm5LWUp3Sg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPaXhTdm45YWZnWVFxVzJnb1ZwbUN4SmUtLVdJN0VJdFZBamRyQmFxN0RZelBfTklaSTVyOUZ3ajQ5MFB2TEN4Ukd6TE5ORFY5SEROVk1CZ25sRWJ1QnRBdTVfTktlby1NWXhaVWI5YnRvaDZWbHVjdDVoeFp5Tk5veFk5a19MSWJqcEJVV0dzV3k?oc=5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>noticia:17hz69v</t>
+          <t>noticia:1f1qb0</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-22 13:05</t>
+          <t>2026-10-22 12:09</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1792688709000</v>
+        <v>1792685373000</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Accidente en El Sillar deja al menos 29 heridos - La Razón Digital Bolivia</t>
+          <t>Accidente en el tramo Locotal–Villa Tunari: la vía está transitable con precaución - Red Uno</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3260,18 +3244,18 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -3283,57 +3267,73 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>La Razón Digital Bolivia</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
+          <t>Red Uno</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>-16.556</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-65.569</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Villa Tunari, Cochabamba</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Villa Tunari</t>
+        </is>
+      </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPaXhTdm45YWZnWVFxVzJnb1ZwbUN4SmUtLVdJN0VJdFZBamRyQmFxN0RZelBfTklaSTVyOUZ3ajQ5MFB2TEN4Ukd6TE5ORFY5SEROVk1CZ25sRWJ1QnRBdTVfTktlby1NWXhaVWI5YnRvaDZWbHVjdDVoeFp5Tk5veFk5a19MSWJqcEJVV0dzV3k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTFozcEEwNXBqV19sS2VibXh0MGt0QlhsX1djSTFGQW5zNlFLRHZpNVVnZ1JmWDQ4LVRHX2Rmb3B5UU9qV0FZQmJCaUZYdmwyNG1NenJ4Qzlzd0NJTGs1SjMxdFRtRFBzSUkybGJfZFFaNFZBc21FSUJYSFVkQkVkSEhQaGw0UFVzeXctZHo3cjNsYm5weXJlOU1wcmFncnNhMC1BQUpvNWlDX1NxZXU4b09kVFFWR2tSVEk2UTdXXzB3TjA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>noticia:1f1qb0</t>
+          <t>noticia:wi18tm</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-22 12:09</t>
+          <t>2026-10-22 11:53</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1792685373000</v>
+        <v>1792684426000</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Accidente en el tramo Locotal–Villa Tunari: la vía está transitable con precaución - Red Uno</t>
+          <t>Accidente en El Sillar deja heridos y derrame de combustible: esto es lo último que se sabe - Red Uno</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>tecnológica</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -3348,70 +3348,54 @@
           <t>Red Uno</t>
         </is>
       </c>
-      <c r="M39" t="n">
-        <v>-16.556</v>
-      </c>
-      <c r="N39" t="n">
-        <v>-65.569</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>Villa Tunari, Cochabamba</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>Villa Tunari</t>
-        </is>
-      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTFozcEEwNXBqV19sS2VibXh0MGt0QlhsX1djSTFGQW5zNlFLRHZpNVVnZ1JmWDQ4LVRHX2Rmb3B5UU9qV0FZQmJCaUZYdmwyNG1NenJ4Qzlzd0NJTGs1SjMxdFRtRFBzSUkybGJfZFFaNFZBc21FSUJYSFVkQkVkSEhQaGw0UFVzeXctZHo3cjNsYm5weXJlOU1wcmFncnNhMC1BQUpvNWlDX1NxZXU4b09kVFFWR2tSVEk2UTdXXzB3TjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPZHNBTEdaQm5Wby1lTF9mWlQ2aGg0MVc4S0MwVWJ3dUJ5WWU5X3IwYWhKRjk5VWtYWEJHRDF4QldVc29laVNPSTJNWFBDSkNFQlFSYTJUXzNMNF9hckFBN1I2T2xoQUtYQ2V6MDNTZHhHVk9qeTBCdHRpM2ZLd0pyOFRweUUxX19STzRHTHg5VUY5d1lhS0tDeXpCdklqcTZGT1J4R0xnSDhoak1EZ2dtNUhSTUV6b1o0U0VSdWY5X0E3U05Tc1dYVEN2WFZUeFhPMTBJTmowNA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>noticia:wi18tm</t>
+          <t>noticia:12gfagq</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-22 11:53</t>
+          <t>2026-10-22 11:28</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1792684426000</v>
+        <v>1792682880000</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Accidente en El Sillar deja heridos y derrame de combustible: esto es lo último que se sabe - Red Uno</t>
+          <t>Reportan triple colisión entre dos camiones y un bus en la carretera Cochabamba-Santa Cruz - FmBolivia</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>tecnológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -3419,21 +3403,37 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Red Uno</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
+          <t>FmBolivia; Red Uno</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>-17.39</v>
+      </c>
+      <c r="N40" t="n">
+        <v>-66.16</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Cochabamba, Cochabamba</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPZHNBTEdaQm5Wby1lTF9mWlQ2aGg0MVc4S0MwVWJ3dUJ5WWU5X3IwYWhKRjk5VWtYWEJHRDF4QldVc29laVNPSTJNWFBDSkNFQlFSYTJUXzNMNF9hckFBN1I2T2xoQUtYQ2V6MDNTZHhHVk9qeTBCdHRpM2ZLd0pyOFRweUUxX19STzRHTHg5VUY5d1lhS0tDeXpCdklqcTZGT1J4R0xnSDhoak1EZ2dtNUhSTUV6b1o0U0VSdWY5X0E3U05Tc1dYVEN2WFZUeFhPMTBJTmowNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNMTNBaFZNMU9SR25vdVBuNXlZY3g4VkFWYXRiQnNSaUFjemZhUHZWNHg4V2owU2xfNndBak94TnU2cHNUVXdNNWl2eUdHZVNMbVZweTR5M0o0bWdTNUN4QkoxUkI2TDBmVE03M09zRGhJRVFzV0tPZ1NCWEJLUkt1ZGN4UGduOUZMQnJoM0tMYTh0ZlFxaFJNUkJqaWFPazRlMzN3ajhjUEdUYXlZRndpb3RSdTFCX2tCZGJxQ0x4SlBISWJsRVoyN3ZR?oc=5 | https://news.google.com/rss/articles/CBMirwFBVV95cUxNNUROMzd1UDJRWVZZQ011cFd2c1FSdER1ZzdleU04cXpwYk5HaUZrLXoyU2NzdFk1dnNRUndhUWt0cG9DX09rSjlLcDItU0tzcmQtS3E4dDQ4ZF9HdGJLdk13ek9BNHJUWVlCcklrM25rZ01RbXhLalRBT1FGdDNReHdlTFZkNkJ5ZFd3N3NZVFVmOFUxbEhHN0RsaUxiSVZsM0lXVEFYSHVRQlhsOEtJ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3604,7 +3604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S63"/>
+  <dimension ref="A1:S64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3707,7 +3707,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>noticia:4blj1l</t>
+          <t>noticia:1xi48lm</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3717,15 +3717,15 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-25 12:59</t>
+          <t>2026-10-25 13:02</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1792947573000</v>
+        <v>1792947732000</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
+          <t>EL DÍA - Noticias de Bolivia para el mundo</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -3743,13 +3743,13 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Santa Cruz: Dos cisternas se incendian tras colisionar - La Patria Bolivia</t>
+          <t>Reportan el incendio de dos camiones cisterna en la carretera a Camiri - EL DÍA - Noticias de Bolivia para el mundo</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQbHdpcUF6dXpjaW1TT1ZmdGJtUUVLMTNMRTVqVkFUdkNsZlRvenVkckFUWmI4NDFmc2ZHd2RVcWRSSE5YRVpOTUlESGw2V3JONXpwS0RISGNZd01SejNuMkY4NzFYYXp4aWo2RE9VMkFYUkVwZ3JRRmM5MWlRSjlBWk16azdkQ3FjdEtkaWc5NERkTzk2SllVOQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNN0traUpaNVFIOU0zeFZod2tkQWhZZFQ1Q3dxc2xCVy1RNnJIX2xQbTlhT3RVckdNdHV4ZFVLQThvd2UzNDlCa3VmaWprTnU3R05rVkVkdEVCU1hFMlFsLTJ6REIySnl5VFJfdV9pQmVDTzlqUWFUSi1GQ0JvTVJVQ2dpeVBydnpMV0dYOThENTFRUDgxVFloSVg3bnN4dGo2aEVCbDFKaUgydWNISnJVUTNB?oc=5</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -3759,14 +3759,14 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-17.781</v>
+        <v>-20.05</v>
       </c>
       <c r="O2" t="n">
-        <v>-63.139</v>
+        <v>-63.486</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Santa Cruz, Santa Cruz</t>
+          <t>Camiri, Santa Cruz</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -3781,34 +3781,32 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Camiri</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>manual:1c1299f3</t>
+          <t>noticia:4blj1l</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>registro</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-25 12:44</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>1792946640000</t>
-        </is>
+          <t>2026-10-25 12:59</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1792947573000</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Registro abierto (sin verificar)</t>
+          <t>La Patria Bolivia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -3816,90 +3814,82 @@
           <t>antropogénica</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G3" t="n">
+        <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Vuelco de minibus</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Registro de prueba del sistema. Ignorar. | Lugar indicado: Caranavi, La Paz | Registro abierto, sin verificar.</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>-15.813</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>-67.463</t>
-        </is>
+          <t>Santa Cruz: Dos cisternas se incendian tras colisionar - La Patria Bolivia</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQbHdpcUF6dXpjaW1TT1ZmdGJtUUVLMTNMRTVqVkFUdkNsZlRvenVkckFUWmI4NDFmc2ZHd2RVcWRSSE5YRVpOTUlESGw2V3JONXpwS0RISGNZd01SejNuMkY4NzFYYXp4aWo2RE9VMkFYUkVwZ3JRRmM5MWlRSjlBWk16azdkQ3FjdEtkaWc5NERkTzk2SllVOQ?oc=5</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-17.781</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-63.139</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Caranavi, La Paz</t>
+          <t>Santa Cruz, Santa Cruz</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>nombre de municipio indicado por quien registra</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Caranavi</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>noticia:oww2zc</t>
+          <t>manual:1c1299f3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>registro</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-25 12:08</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>1792944531000</v>
+          <t>2026-10-25 12:44</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1792946640000</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>Registro abierto (sin verificar)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -3907,62 +3897,72 @@
           <t>antropogénica</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Cierran la carretera a Camiri: dos cisternas chocan y provocan un voraz incendio - Red Uno</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQLXlqSFdvWUVhQUNadnpkdE5lUTZQS0lobThzUTZWbDNJTE94alVhaDBaYU9Fd09SSGt3UlR3Y0dfZlNIcml1ZktnWjctNk1Na3V4S0tINFNkMXM0OHBoV2lCTTBiYXlPUTA3T2ZkeXE2RElYWjhfVHd3Nng1Z0E4alBmOFI5NDFwX09kazZlSWl2OVR2ZVR6MDhvSHFnSmJKbTFXSEFDNFFYcWVDNGtYWEQ0bDhJel9CaEpEZWZ4SWN0TE9Ya0E?oc=5</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>-20.05</v>
-      </c>
-      <c r="O4" t="n">
-        <v>-63.486</v>
+          <t>Vuelco de minibus</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Registro de prueba del sistema. Ignorar. | Lugar indicado: Caranavi, La Paz | Registro abierto, sin verificar.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>-15.813</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>-67.463</t>
+        </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Camiri, Santa Cruz</t>
+          <t>Caranavi, La Paz</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
+          <t>nombre de municipio indicado por quien registra</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Camiri</t>
+          <t>Caranavi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>noticia:1a4hhsd</t>
+          <t>noticia:oww2zc</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3972,15 +3972,15 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-25 11:56</t>
+          <t>2026-10-25 12:08</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1792943794000</v>
+        <v>1792944531000</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Opinión Bolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3998,13 +3998,13 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Reportan el incendio de dos camiones cisterna en la carretera a Camiri - Opinión Bolivia</t>
+          <t>Cierran la carretera a Camiri: dos cisternas chocan y provocan un voraz incendio - Red Uno</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNUTdxSzBJVTZnajZQUXhyTVhwMlpvU0tyZGVBYnFwV2kyZWthenNRT1FDRVJFZnk4ZndGTFQ0cnFXZmZ1WHZaMFhUbWo0SWkzcjcxbjJwU3pKUXR4WEVZLVlRNFpxOUVMY2NNNUZsbmJSMk9xZG1sTklEdEtGSXJyUUp5b0R2dVpYcHJLdTRNRlRjcWpNNXg4c0Z4UWwteFc2dDRqVmpnQnFfQXgwN0twTzl4ZWhYdUtYWGfSAboBQVVfeXFMTVE3cUswSVU2Z2o2UFF4ck1YcDJab1NLcmRlQWJxcFdpMmVrYXpzUU9RQ0VSRWZ5OGZ3RkxUNHJxV2ZmdVh2WjBYVG1qNElpM3I3MW4ycFN6SlF0eFhFWS1ZUTRacTlFTGNjTTVGbG5iUjJPcWRtbE5JRHRLRklyclFKeW9EdnVaWHByS3U0TUZUY3FqTTV4OHNGeFFsLXhXNnQ0alZqZ0JxX0F4MDdLcE85eGVoWHVLWFhn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQLXlqSFdvWUVhQUNadnpkdE5lUTZQS0lobThzUTZWbDNJTE94alVhaDBaYU9Fd09SSGt3UlR3Y0dfZlNIcml1ZktnWjctNk1Na3V4S0tINFNkMXM0OHBoV2lCTTBiYXlPUTA3T2ZkeXE2RElYWjhfVHd3Nng1Z0E4alBmOFI5NDFwX09kazZlSWl2OVR2ZVR6MDhvSHFnSmJKbTFXSEFDNFFYcWVDNGtYWEQ0bDhJel9CaEpEZWZ4SWN0TE9Ya0E?oc=5</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -4043,7 +4043,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>noticia:1at00ey</t>
+          <t>noticia:1a4hhsd</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4053,15 +4053,15 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-25 11:19</t>
+          <t>2026-10-25 11:56</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1792941547000</v>
+        <v>1792943794000</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>Opinión Bolivia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -4079,13 +4079,13 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Dos cisternas chocan y provocan voraz incendio en la ruta a Camiri - Red Uno</t>
+          <t>Reportan el incendio de dos camiones cisterna en la carretera a Camiri - Opinión Bolivia</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPTTF0OUdVS1c1a0lZWmk3bGxHdDJIalpWZTRyQTY3eWE2a2dWOHlsaldKZXpSLWN5c3BkUWdBRkJuSzhHdWl2ZjgwTFFFYnd0aTAxZ3dJU0hCekNZNm9aTTJSZUNfQjVIM3FrUUJ4NXAwa3paZ3BEek9xTVZNQWdnN01xRHloV1ZXZHV6N0JpUWo3RE9DMlFGdkNnWkloTjVVY3RBR1RSRUJJWFVtby1fMWFMNTdLZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNUTdxSzBJVTZnajZQUXhyTVhwMlpvU0tyZGVBYnFwV2kyZWthenNRT1FDRVJFZnk4ZndGTFQ0cnFXZmZ1WHZaMFhUbWo0SWkzcjcxbjJwU3pKUXR4WEVZLVlRNFpxOUVMY2NNNUZsbmJSMk9xZG1sTklEdEtGSXJyUUp5b0R2dVpYcHJLdTRNRlRjcWpNNXg4c0Z4UWwteFc2dDRqVmpnQnFfQXgwN0twTzl4ZWhYdUtYWGfSAboBQVVfeXFMTVE3cUswSVU2Z2o2UFF4ck1YcDJab1NLcmRlQWJxcFdpMmVrYXpzUU9RQ0VSRWZ5OGZ3RkxUNHJxV2ZmdVh2WjBYVG1qNElpM3I3MW4ycFN6SlF0eFhFWS1ZUTRacTlFTGNjTTVGbG5iUjJPcWRtbE5JRHRLRklyclFKeW9EdnVaWHByS3U0TUZUY3FqTTV4OHNGeFFsLXhXNnQ0alZqZ0JxX0F4MDdLcE85eGVoWHVLWFhn?oc=5</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -4124,7 +4124,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>noticia:1uf38hl</t>
+          <t>noticia:1at00ey</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4134,11 +4134,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-25 10:59</t>
+          <t>2026-10-25 11:19</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1792940350000</v>
+        <v>1792941547000</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -4160,13 +4160,13 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>¡Cisterna con combustible en llamas! Reportan impresionante incendio en la carretera a Camiri - Red Uno</t>
+          <t>Dos cisternas chocan y provocan voraz incendio en la ruta a Camiri - Red Uno</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxORUhqeWpKY1FHRWoxaHN0UXFzS3dpeHh6N0NwLUJOZTlZcDVoNHN0VnI0by1qMWtZZEkxVmtUNjdNTFhjaEFQU2IyMlNwZW95WFBzbFJPVVB6TjJtdjNENk1LWVlsMUxUUzBNVzkxRk1HZ3lQU0s2M1lRVlRuaXlkMmJrd3AyTGpIdXItNkhlU3dhTzBRME56Rm1DSlZCYjNxSnNTbTFqNWRoUkdraHhlREhuYldqeFk2N3poWEx2M08?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPTTF0OUdVS1c1a0lZWmk3bGxHdDJIalpWZTRyQTY3eWE2a2dWOHlsaldKZXpSLWN5c3BkUWdBRkJuSzhHdWl2ZjgwTFFFYnd0aTAxZ3dJU0hCekNZNm9aTTJSZUNfQjVIM3FrUUJ4NXAwa3paZ3BEek9xTVZNQWdnN01xRHloV1ZXZHV6N0JpUWo3RE9DMlFGdkNnWkloTjVVY3RBR1RSRUJJWFVtby1fMWFMNTdLZw?oc=5</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -4205,7 +4205,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>noticia:1sg8pi0</t>
+          <t>noticia:1uf38hl</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4215,11 +4215,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-25 09:59</t>
+          <t>2026-10-25 10:59</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1792936752000</v>
+        <v>1792940350000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -4241,13 +4241,13 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Bus de agrupación musical sufre accidente rumbo al trópico de Cochabamba | VIDEO - Red Uno</t>
+          <t>¡Cisterna con combustible en llamas! Reportan impresionante incendio en la carretera a Camiri - Red Uno</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOVDVzVTJNM2JuQ25sMThEaVZNOUNRd3FGT3RhVnFrZXZ2NDQ1YlluTVdhbVNUQnA1MGNESHRSWVUzbC1kRVh3OTR0emtlTG91cmRWeFJ5dk5zb3p2WFRyMEJUV3FNRnY1WHhRUU9WLTlJcmNyNXJZZFdoM0JoZjNpa3hjUXhMM0xrUDJab2VadkM5RWZYQ3lWZTVDdzg1akxJT2lxcDVNNzI0NG1hejdfdkUyTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxORUhqeWpKY1FHRWoxaHN0UXFzS3dpeHh6N0NwLUJOZTlZcDVoNHN0VnI0by1qMWtZZEkxVmtUNjdNTFhjaEFQU2IyMlNwZW95WFBzbFJPVVB6TjJtdjNENk1LWVlsMUxUUzBNVzkxRk1HZ3lQU0s2M1lRVlRuaXlkMmJrd3AyTGpIdXItNkhlU3dhTzBRME56Rm1DSlZCYjNxSnNTbTFqNWRoUkdraHhlREhuYldqeFk2N3poWEx2M08?oc=5</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -4257,14 +4257,14 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-17.39</v>
+        <v>-20.05</v>
       </c>
       <c r="O8" t="n">
-        <v>-66.16</v>
+        <v>-63.486</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Cochabamba, Cochabamba</t>
+          <t>Camiri, Santa Cruz</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -4274,19 +4274,19 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Camiri</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>noticia:167wlhz</t>
+          <t>noticia:1sg8pi0</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4296,11 +4296,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-25 07:53</t>
+          <t>2026-10-25 09:59</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1792929231000</v>
+        <v>1792936752000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -4322,13 +4322,13 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>¡A sacar el paraguas! Santa cruz amanece con lluvia, frío y complicaciones en el tránsito vehicular - Red Uno</t>
+          <t>Bus de agrupación musical sufre accidente rumbo al trópico de Cochabamba | VIDEO - Red Uno</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOY1ZpYktLR3pUQXotUndVR3puUzVHbW1YTzNyUmJvUHB4Q2JmelRvOEdaRldOUm1xLVJnbGR5VWcxTjNEM3ZUYktCUWtVM0hKSjFuRGdpX0JxN0M5MVZBSG1aVURyVWktdmxwbUtRT19ydU5LdzNTZ2Zpb2ozdHlMUUdTVlAyVk4xODBnV0hyTXdVVndyNzV3VC1KMzFnV3lpcFFXSk9MdDZOTWlWakNwT1FnNDh6QVdjazVYZDVVMkdaLU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOVDVzVTJNM2JuQ25sMThEaVZNOUNRd3FGT3RhVnFrZXZ2NDQ1YlluTVdhbVNUQnA1MGNESHRSWVUzbC1kRVh3OTR0emtlTG91cmRWeFJ5dk5zb3p2WFRyMEJUV3FNRnY1WHhRUU9WLTlJcmNyNXJZZFdoM0JoZjNpa3hjUXhMM0xrUDJab2VadkM5RWZYQ3lWZTVDdzg1akxJT2lxcDVNNzI0NG1hejdfdkUyTQ?oc=5</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -4338,14 +4338,14 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-17.781</v>
+        <v>-17.39</v>
       </c>
       <c r="O9" t="n">
-        <v>-63.139</v>
+        <v>-66.16</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Santa Cruz, Santa Cruz</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -4355,19 +4355,19 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Cochabamba</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>noticia:bzr7eh</t>
+          <t>noticia:167wlhz</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4377,39 +4377,39 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-25 07:09</t>
+          <t>2026-10-25 07:53</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1792926572000</v>
+        <v>1792929231000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>hidrológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Alerta naranja por riesgo de desbordes de ríos - El Diario - Bolivia</t>
+          <t>¡A sacar el paraguas! Santa cruz amanece con lluvia, frío y complicaciones en el tránsito vehicular - Red Uno</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNNGZKSDVaZkowWUFGSEUyTWR3d3dsc04waFBLLWUtcVpiTDYzbmNtYTN1RkFLbjAwN3dxT0xZc3pqc3REUXduZVltQ2Fud1BZLTh1bTNiTEJueVUwV0dERS1iUXZqMHd0UnFrQ3E2SFAzbm5lQ1I4U29MaHJFbWFvdVRTeFY4Wl9rSmc3RkpaQ2xwX0oz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOY1ZpYktLR3pUQXotUndVR3puUzVHbW1YTzNyUmJvUHB4Q2JmelRvOEdaRldOUm1xLVJnbGR5VWcxTjNEM3ZUYktCUWtVM0hKSjFuRGdpX0JxN0M5MVZBSG1aVURyVWktdmxwbUtRT19ydU5LdzNTZ2Zpb2ozdHlMUUdTVlAyVk4xODBnV0hyTXdVVndyNzV3VC1KMzFnV3lpcFFXSk9MdDZOTWlWakNwT1FnNDh6QVdjazVYZDVVMkdaLU0?oc=5</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -4418,21 +4418,37 @@
       <c r="M10" t="n">
         <v>0</v>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>-17.781</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-63.139</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Santa Cruz, Santa Cruz</t>
+        </is>
+      </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Santa Cruz de la Sierra</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>noticia:1fo4ig4</t>
+          <t>noticia:bzr7eh</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4442,43 +4458,43 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-25 01:08</t>
+          <t>2026-10-25 07:09</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1792904880000</v>
+        <v>1792926572000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>diarioelpueblo.com.pe</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>hidrológica</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>roja</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
+          <t>Alerta naranja por riesgo de desbordes de ríos - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQcmFrT3dwcEs0X3U2NWxnOGJwNnI2WHdWTGZYbzEyNnJzUWhkbU9TRWhfSlB5UkMwX2gyMmxYUmVNWmxNOVR6V0twRHpFMTVIYjBKbHQ2TXN2d2w5dkFpcWJCcUJMZldaX01sNWtQV2ZJOGpRVzR3NDVIU0pJc1BNVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNNGZKSDVaZkowWUFGSEUyTWR3d3dsc04waFBLLWUtcVpiTDYzbmNtYTN1RkFLbjAwN3dxT0xZc3pqc3REUXduZVltQ2Fud1BZLTh1bTNiTEJueVUwV0dERS1iUXZqMHd0UnFrQ3E2SFAzbm5lQ1I4U29MaHJFbWFvdVRTeFY4Wl9rSmc3RkpaQ2xwX0oz?oc=5</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -4497,7 +4513,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>noticia:r1uot6</t>
+          <t>noticia:1fo4ig4</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4507,15 +4523,15 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-24 20:00</t>
+          <t>2026-10-25 01:08</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1792886439000</v>
+        <v>1792904880000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
+          <t>diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -4524,61 +4540,45 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>roja</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>vuelco deja heridos en ruta Oruro – Huanuni - La Patria Bolivia</t>
+          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNNDQtMG1KT1lLWW5nem9Jbm5JWDZKNlRWZmFmRlBxWDlDeXlSWnJ5d2NsTlpxa0JIS25oVWVZOC1majZVbWhOVDIxR0dLOFlzY2VpVzVoVk1mQnF3dXVwLUFZVHc1UjlXZzF5T05CY3U0ZldLVkw1VzBTek5zanpjQW1xalltWHNiaXI3dTNR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQcmFrT3dwcEs0X3U2NWxnOGJwNnI2WHdWTGZYbzEyNnJzUWhkbU9TRWhfSlB5UkMwX2gyMmxYUmVNWmxNOVR6V0twRHpFMTVIYjBKbHQ2TXN2d2w5dkFpcWJCcUJMZldaX01sNWtQV2ZJOGpRVzR3NDVIU0pJc1BNVg?oc=5</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>-17.97</v>
-      </c>
-      <c r="O12" t="n">
-        <v>-67.11</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Oruro, Oruro</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>Oruro</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>Oruro</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>noticia:1ytw450</t>
+          <t>noticia:r1uot6</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4588,15 +4588,15 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-24 18:58</t>
+          <t>2026-10-24 20:00</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1792882686000</v>
+        <v>1792886439000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>diarioelpueblo.com.pe</t>
+          <t>La Patria Bolivia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -4605,45 +4605,61 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>roja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
+          <t>vuelco deja heridos en ruta Oruro – Huanuni - La Patria Bolivia</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNZ1U3bEVuaVdjVE1zSU9lOHJZTVRZLVZaemhldGNnT1JBWDJvbzdvM3paVVNhLUlyWHF2akNuSXJOLXdyTGRuejRlV1FuMjVkTjA3NmdRdmgtRWlUeTFBV1dEMzBvejBxaXZJdUZZWkRVTF9VLU5BcjFGZGFEQ09WWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNNDQtMG1KT1lLWW5nem9Jbm5JWDZKNlRWZmFmRlBxWDlDeXlSWnJ5d2NsTlpxa0JIS25oVWVZOC1majZVbWhOVDIxR0dLOFlzY2VpVzVoVk1mQnF3dXVwLUFZVHc1UjlXZzF5T05CY3U0ZldLVkw1VzBTek5zanpjQW1xalltWHNiaXI3dTNR?oc=5</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-17.97</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-67.11</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Oruro, Oruro</t>
+        </is>
+      </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>noticia:1wcb22g</t>
+          <t>noticia:1ytw450</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4653,43 +4669,43 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-24 17:47</t>
+          <t>2026-10-24 18:58</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1792878475000</v>
+        <v>1792882686000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Mundo Bolivia</t>
+          <t>diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>hidrológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>roja</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Alerta naranja por ingreso de frente frío y desbordes de ríos en 6 departamentos - El Mundo Bolivia</t>
+          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPZW00RkxJSklTelNrS2hqczJDWHlwcENFX2lnSEUyTEFPaDFRQ2JvMUcyd3NfYjg0UE9ORGxHRzB4ZDh3U0hQQ1JSQlhsaUY4N3ByMUUxei1SaUZnNlp6T3hsLVdiMGhKaXhsV1FNSUNQMHlvQ19qdk56SEF0d2RXVFctS0VPT25kNGZCRDdvZ2dxU0VoUUJKU0ZBd0ZycFNEZFh0T3ZjOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNZ1U3bEVuaVdjVE1zSU9lOHJZTVRZLVZaemhldGNnT1JBWDJvbzdvM3paVVNhLUlyWHF2akNuSXJOLXdyTGRuejRlV1FuMjVkTjA3NmdRdmgtRWlUeTFBV1dEMzBvejBxaXZJdUZZWkRVTF9VLU5BcjFGZGFEQ09WWQ?oc=5</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -4708,7 +4724,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>noticia:1c1ju1f</t>
+          <t>noticia:1wcb22g</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4718,46 +4734,46 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-24 17:02</t>
+          <t>2026-10-24 17:47</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1792875752000</v>
+        <v>1792878475000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>La Razón Digital Bolivia</t>
+          <t>El Mundo Bolivia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>hidrológica</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a los Yungas deja siete heridos - La Razón Digital Bolivia</t>
+          <t>Alerta naranja por ingreso de frente frío y desbordes de ríos en 6 departamentos - El Mundo Bolivia</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPTGQwaVBfdG1JdVRMUTN4LVVvN0ppc3dreDJVVllDR3RmX0xpMzB4b0pvVTNSV1B6T0ZEWTdEZkNsRUdSNzhLaC1CWHN5WktNWk1nRWpTdVZiYjI3TlJlX2xlVTI5MjlRU2hiY1gteml4YWVFbDNPSVRBZmtITlQzbmhaUXVmcThRa2xsQTJIOXZuNzlSdm12MEdyOEZHdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPZW00RkxJSklTelNrS2hqczJDWHlwcENFX2lnSEUyTEFPaDFRQ2JvMUcyd3NfYjg0UE9ORGxHRzB4ZDh3U0hQQ1JSQlhsaUY4N3ByMUUxei1SaUZnNlp6T3hsLVdiMGhKaXhsV1FNSUNQMHlvQ19qdk56SEF0d2RXVFctS0VPT25kNGZCRDdvZ2dxU0VoUUJKU0ZBd0ZycFNEZFh0T3ZjOA?oc=5</t>
         </is>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
@@ -4773,7 +4789,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>noticia:14iwzop</t>
+          <t>noticia:1c1ju1f</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4783,15 +4799,15 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-24 13:40</t>
+          <t>2026-10-24 17:02</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1792863623000</v>
+        <v>1792875752000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>EL DÍA - Noticias de Bolivia para el mundo</t>
+          <t>La Razón Digital Bolivia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -4809,13 +4825,13 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a Mayaya deja siete heridos de la agrupación Los Chicos Fieles - EL DÍA - Noticias de Bolivia para el mundo</t>
+          <t>Accidente en la carretera a los Yungas deja siete heridos - La Razón Digital Bolivia</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPeGd3VWpCWXJ0YTJIeDJLcktzWG1jdUh0TjFXb01wSTkxbHNXZU94VWNDMkxnTjlJZVdpbkprMEY2NE80RXYyUWxUQXVnbl9lUXR2b28zTEh6cTJLVEQ4TUNja2kzRlhadVBFZFVwV1U2TlhseXZMZ20zZTZiUFpWRjdCOWNBMHU5XzdMV3JqQjV4TEE3bHRMOXR6Nm55eHZUNnFHSDdVRk8zVkY4RkVsUUtUN0JYdkREWGZncmJ3ZWc2T1BuUm1ZLTlfcHVabFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPTGQwaVBfdG1JdVRMUTN4LVVvN0ppc3dreDJVVllDR3RmX0xpMzB4b0pvVTNSV1B6T0ZEWTdEZkNsRUdSNzhLaC1CWHN5WktNWk1nRWpTdVZiYjI3TlJlX2xlVTI5MjlRU2hiY1gteml4YWVFbDNPSVRBZmtITlQzbmhaUXVmcThRa2xsQTJIOXZuNzlSdm12MEdyOEZHdw?oc=5</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -4838,7 +4854,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>noticia:1ukcn97</t>
+          <t>noticia:14iwzop</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4848,15 +4864,15 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-24 13:26</t>
+          <t>2026-10-24 13:40</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1792862794000</v>
+        <v>1792863623000</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>El Deber</t>
+          <t>EL DÍA - Noticias de Bolivia para el mundo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -4874,20 +4890,20 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Esta es la lista preliminar de los heridos en el accidente del grupo 'Los chicos fieles', el conductor está grave - El Deber</t>
+          <t>Accidente en la carretera a Mayaya deja siete heridos de la agrupación Los Chicos Fieles - EL DÍA - Noticias de Bolivia para el mundo</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOczZKbFd1QzRpak92LXpPWXZXQXJObnBQTG9qRFBlUUV5dThMWXhzckFFUHAyb2thU1JwRmJDSEZfaEdTUXh1bjZvQWpYMGhfUno3cWZ4MGpldEpoQXhzSlVzTm5LLW9OcjB2MWRsdHQ2UlI2SjEtZ085ZTR5Z3pEVmtBTF9lc29Kd0RhaTRUWkM4eGZJNWhBSXZqWmxuNW10dlQwYW9mdzItcWZWTkU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPeGd3VWpCWXJ0YTJIeDJLcktzWG1jdUh0TjFXb01wSTkxbHNXZU94VWNDMkxnTjlJZVdpbkprMEY2NE80RXYyUWxUQXVnbl9lUXR2b28zTEh6cTJLVEQ4TUNja2kzRlhadVBFZFVwV1U2TlhseXZMZ20zZTZiUFpWRjdCOWNBMHU5XzdMV3JqQjV4TEE3bHRMOXR6Nm55eHZUNnFHSDdVRk8zVkY4RkVsUUtUN0JYdkREWGZncmJ3ZWc2T1BuUm1ZLTlfcHVabFE?oc=5</t>
         </is>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
@@ -4903,7 +4919,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>noticia:2avehj</t>
+          <t>noticia:1ukcn97</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4913,20 +4929,20 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-24 12:53</t>
+          <t>2026-10-24 13:26</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1792860813000</v>
+        <v>1792862794000</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>El Deber</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>climatológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4939,52 +4955,36 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Sequía en Cochabamba: más de un centenar de cabezas de ganado murieron en el cono sur - Red Uno</t>
+          <t>Esta es la lista preliminar de los heridos en el accidente del grupo 'Los chicos fieles', el conductor está grave - El Deber</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOOFQxc2Vzc0QwS19ydC13RkRPZnZQU3JkSTl5U3kzdUdMSldTcm5HVEhWRzZyN19CLUlwcUs4MW03Ui1obVBtdzQ3QWFQc1RKdzh3MXJ5QkpRS2pRNm50V1lVb09ScGJnaVVlemVfZlRsWjdObnRmR1FGMnlMMHAyc2pMandndy10T2twcWx6OFh4UHdvbVlFbllwME9WQ2pQVjNTQzBxeTg5YnF3bDREeHVDYXpObFFIaTZZQWtYUE12cGQ1ZGRhT0syNjVhZWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOczZKbFd1QzRpak92LXpPWXZXQXJObnBQTG9qRFBlUUV5dThMWXhzckFFUHAyb2thU1JwRmJDSEZfaEdTUXh1bjZvQWpYMGhfUno3cWZ4MGpldEpoQXhzSlVzTm5LLW9OcjB2MWRsdHQ2UlI2SjEtZ085ZTR5Z3pEVmtBTF9lc29Kd0RhaTRUWkM4eGZJNWhBSXZqWmxuNW10dlQwYW9mdzItcWZWTkU0?oc=5</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-17.39</v>
-      </c>
-      <c r="O18" t="n">
-        <v>-66.16</v>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Cochabamba, Cochabamba</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>noticia:1ksmg5u</t>
+          <t>noticia:2avehj</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4994,20 +4994,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-24 11:43</t>
+          <t>2026-10-24 12:53</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1792856591000</v>
+        <v>1792860813000</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>climatológica</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -5020,36 +5020,52 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Embarrancamiento deja heridos a integrantes de Los Chicos Fieles - La Patria Bolivia</t>
+          <t>Sequía en Cochabamba: más de un centenar de cabezas de ganado murieron en el cono sur - Red Uno</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNeEFrOEtOMHZxMW42REFPU0x1MG5oQjlBMkJucWRLZ292alBXekJKeURBN3NLTVVadWI0OWF4UGtSVXBzTE01eWFSU1kyMUhNZ04zMWNMaUxnMDBBZ0EwTktXbjlaVTBUUmNqa3AwY19KNTU2LWh5LW9IVElVdTdnaHFPanJPd2FqMUxzaUhXZmVpYU1saGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOOFQxc2Vzc0QwS19ydC13RkRPZnZQU3JkSTl5U3kzdUdMSldTcm5HVEhWRzZyN19CLUlwcUs4MW03Ui1obVBtdzQ3QWFQc1RKdzh3MXJ5QkpRS2pRNm50V1lVb09ScGJnaVVlemVfZlRsWjdObnRmR1FGMnlMMHAyc2pMandndy10T2twcWx6OFh4UHdvbVlFbllwME9WQ2pQVjNTQzBxeTg5YnF3bDREeHVDYXpObFFIaTZZQWtYUE12cGQ1ZGRhT0syNjVhZWs?oc=5</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-17.39</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-66.16</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Cochabamba, Cochabamba</t>
+        </is>
+      </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>noticia:mlyqgd</t>
+          <t>noticia:1ksmg5u</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5059,15 +5075,15 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-24 11:30</t>
+          <t>2026-10-24 11:43</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1792855818000</v>
+        <v>1792856591000</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Opinión Bolivia</t>
+          <t>La Patria Bolivia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -5085,20 +5101,20 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a Mayaya deja siete heridos de la agrupación Los Chicos Fieles - Opinión Bolivia</t>
+          <t>Embarrancamiento deja heridos a integrantes de Los Chicos Fieles - La Patria Bolivia</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYjNxaHg3YllRRTJYdFd1clAtUlROSGlFNVg5eUVZUGJoOEZ4MWM5QU5WQm1YTDc4NXc3SjhWMUw0TkZfSHlMLUQ1bmpTME1Kb1JaM0ExamFHYTd3VlU4MXRWdTZ1bzh1SGYtbGE1a3dBaG93bjg1OGc0S0JfRE43c3dVMVltN0dQQzNhQUNhM0FjVUNRUDRSamlJYlk2dEJpUTBuY2hBcTFucTVRN0ZtYnc5bzdmTV9LQm1uVUxaZS1tUE9IejhBVDRCdU_SAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNeEFrOEtOMHZxMW42REFPU0x1MG5oQjlBMkJucWRLZ292alBXekJKeURBN3NLTVVadWI0OWF4UGtSVXBzTE01eWFSU1kyMUhNZ04zMWNMaUxnMDBBZ0EwTktXbjlaVTBUUmNqa3AwY19KNTU2LWh5LW9IVElVdTdnaHFPanJPd2FqMUxzaUhXZmVpYU1saGc?oc=5</t>
         </is>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
@@ -5114,7 +5130,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>noticia:irf4jl</t>
+          <t>noticia:mlyqgd</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5156,7 +5172,7 @@
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNMXlMNXFWSWhhWWNDRFFKMncwS2JGWm0tWlJCd2x2RjZhdFhEQ0lBcVlFSS1WRVYxMEVJTWRHcTY3M0stdWhGdnVPRU13X2MwSVRWX25xVUQxa0R6Z1pqQ2dfY0VjUmw2aXFoWFNVNk15N2dBOENZLWlGSWJfMW0zejVoZ3ZwVHVQV1MzbzlnUlpRcWIxMHZxdkItZTc0QmMyRnBmSVRtVnZ5Y3gtdVpYNXFwcGdadGVCU3dRZ3EwOTdiWHU4OXJRdEFoNi1HcnA1U0HSAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYjNxaHg3YllRRTJYdFd1clAtUlROSGlFNVg5eUVZUGJoOEZ4MWM5QU5WQm1YTDc4NXc3SjhWMUw0TkZfSHlMLUQ1bmpTME1Kb1JaM0ExamFHYTd3VlU4MXRWdTZ1bzh1SGYtbGE1a3dBaG93bjg1OGc0S0JfRE43c3dVMVltN0dQQzNhQUNhM0FjVUNRUDRSamlJYlk2dEJpUTBuY2hBcTFucTVRN0ZtYnc5bzdmTV9LQm1uVUxaZS1tUE9IejhBVDRCdU_SAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -5179,7 +5195,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>noticia:1g006zh</t>
+          <t>noticia:irf4jl</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5189,15 +5205,15 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-24 11:25</t>
+          <t>2026-10-24 11:30</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1792855522000</v>
+        <v>1792855818000</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>El Potosí</t>
+          <t>Opinión Bolivia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -5215,13 +5231,13 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a Mayaya deja siete heridos del grupo Los Chicos Fieles - El Potosí</t>
+          <t>Accidente en la carretera a Mayaya deja siete heridos de la agrupación Los Chicos Fieles - Opinión Bolivia</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTC10eC1qSm1WRlY2YzA3VEJqOG1LUkx6bE9PdFYwTFBZMGFjU0RMYXliRkhXcTJHRlVzb0Y4QUU0WWJDQ1plS2NZamZ1YmFadE5qY3g4UE5aYVAwamtCUUNZaDB2YWJTdWRKS3R4a0hHUjVobUl0Y1dYZ2JPczAwak5kN1hjUEwwM1NtUDVWbnAzWTdnRng3RjFValFVVlZPdVZnWFlUODhPOE5aMTROQzVKVjVRS2VoaTlaQnBiUGRTNFk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNMXlMNXFWSWhhWWNDRFFKMncwS2JGWm0tWlJCd2x2RjZhdFhEQ0lBcVlFSS1WRVYxMEVJTWRHcTY3M0stdWhGdnVPRU13X2MwSVRWX25xVUQxa0R6Z1pqQ2dfY0VjUmw2aXFoWFNVNk15N2dBOENZLWlGSWJfMW0zejVoZ3ZwVHVQV1MzbzlnUlpRcWIxMHZxdkItZTc0QmMyRnBmSVRtVnZ5Y3gtdVpYNXFwcGdadGVCU3dRZ3EwOTdiWHU4OXJRdEFoNi1HcnA1U0HSAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -5230,60 +5246,44 @@
       <c r="M22" t="n">
         <v>7</v>
       </c>
-      <c r="N22" t="n">
-        <v>-19.58</v>
-      </c>
-      <c r="O22" t="n">
-        <v>-65.75</v>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Potosí, Potosí</t>
-        </is>
-      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>clima:Potosí:2026-10-24:viento:1</t>
+          <t>noticia:1g006zh</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-24 10:55</t>
+          <t>2026-10-24 11:25</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1792853727284</v>
+        <v>1792855522000</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>El Potosí</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5296,24 +5296,20 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Potosí 2026-10-24: 60.5 km/h de ráfagas pronosticadas</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
-        </is>
-      </c>
+          <t>Accidente en la carretera a Mayaya deja siete heridos del grupo Los Chicos Fieles - El Potosí</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTC10eC1qSm1WRlY2YzA3VEJqOG1LUkx6bE9PdFYwTFBZMGFjU0RMYXliRkhXcTJHRlVzb0Y4QUU0WWJDQ1plS2NZamZ1YmFadE5qY3g4UE5aYVAwamtCUUNZaDB2YWJTdWRKS3R4a0hHUjVobUl0Y1dYZ2JPczAwak5kN1hjUEwwM1NtUDVWbnAzWTdnRng3RjFValFVVlZPdVZnWFlUODhPOE5aMTROQzVKVjVRS2VoaTlaQnBiUGRTNFk?oc=5</t>
         </is>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N23" t="n">
         <v>-19.58</v>
@@ -5323,12 +5319,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Potosí, Potosí</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>capital (pronóstico puntual)</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -5345,25 +5341,25 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>noticia:1ax0bpy</t>
+          <t>clima:Potosí:2026-10-24:viento:1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-24 10:32</t>
+          <t>2026-10-24 10:55</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1792852364000</v>
+        <v>1792853727284</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Que Pasa Salta</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -5372,22 +5368,26 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Creció el Bermejo tras la tormenta: así está el puerto de chalanas en este momento - Que Pasa Salta</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
+          <t>Potosí 2026-10-24: 60.5 km/h de ráfagas pronosticadas</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVld9IBfkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVldw?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -5397,59 +5397,59 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>-22.721</v>
+        <v>-19.58</v>
       </c>
       <c r="O24" t="n">
-        <v>-64.32599999999999</v>
+        <v>-65.75</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bermejo, Tarija</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
+          <t>capital (pronóstico puntual)</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Tarija</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>Bermejo</t>
+          <t>Potosí</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>gdacs:WF1033142:0</t>
+          <t>noticia:1ax0bpy</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdacs</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-24 07:06</t>
+          <t>2026-10-24 10:32</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1792839995000</v>
+        <v>1792852364000</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>GDACS</t>
+          <t>Que Pasa Salta</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5462,17 +5462,13 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Green forest fire notification in Bolivia</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>On 21/10/2026, a forest fire started in Bolivia, until 24/10/2026.</t>
-        </is>
-      </c>
+          <t>Creció el Bermejo tras la tormenta: así está el puerto de chalanas en este momento - Que Pasa Salta</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>http://www.gdacs.org/report.aspx?eventtype=WF&amp;eventid=1033142</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVld9IBfkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVldw?oc=5</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -5482,59 +5478,59 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>-13.06332</v>
+        <v>-22.721</v>
       </c>
       <c r="O25" t="n">
-        <v>-67.66426</v>
+        <v>-64.32599999999999</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Bermejo, Tarija</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>coordenada de la fuente</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Tarija</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>Ixiamas</t>
+          <t>Bermejo</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>noticia:1shhqva</t>
+          <t>gdacs:WF1033142:0</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>gdacs</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-24 06:33</t>
+          <t>2026-10-24 07:06</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1792838034000</v>
+        <v>1792839995000</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>GDACS</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5547,13 +5543,17 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+          <t>Green forest fire notification in Bolivia</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>On 21/10/2026, a forest fire started in Bolivia, until 24/10/2026.</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQYzB6N082XzFRRnVtcDVmUkYyWjcxUzV2Z3Frd1I0WDNXSnZtY0QzOU1PUkNLMktVT1Vra2FSeXhxZDRuOFZYZjFwejl6ejJTbWY2MGJuSGN3ZHdrdG5JUkgzSXBkbDYtaHlackY3OVFuNWdLcFNpdWNHRU9vNGdoVWx2ODFVdzJXYUxnM0tUcjJvZmc?oc=5</t>
+          <t>http://www.gdacs.org/report.aspx?eventtype=WF&amp;eventid=1033142</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -5563,82 +5563,78 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>-17.97</v>
+        <v>-13.06332</v>
       </c>
       <c r="O26" t="n">
-        <v>-67.11</v>
+        <v>-67.66426</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
+          <t>coordenada de la fuente</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Ixiamas</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>clima:Potosí:2026-10-25:viento:1</t>
+          <t>noticia:1shhqva</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-10-24 02:55</t>
+          <t>2026-10-24 06:33</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1792824927736</v>
+        <v>1792838034000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Potosí 2026-10-25: 60.5 km/h de ráfagas pronosticadas</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
-        </is>
-      </c>
+          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQYzB6N082XzFRRnVtcDVmUkYyWjcxUzV2Z3Frd1I0WDNXSnZtY0QzOU1PUkNLMktVT1Vra2FSeXhxZDRuOFZYZjFwejl6ejJTbWY2MGJuSGN3ZHdrdG5JUkgzSXBkbDYtaHlackY3OVFuNWdLcFNpdWNHRU9vNGdoVWx2ODFVdzJXYUxnM0tUcjJvZmc?oc=5</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -5648,59 +5644,59 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>-19.58</v>
+        <v>-17.97</v>
       </c>
       <c r="O27" t="n">
-        <v>-65.75</v>
+        <v>-67.11</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Oruro, Oruro</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>capital (pronóstico puntual)</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Oruro</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Oruro</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>noticia:mz6q0s</t>
+          <t>clima:Potosí:2026-10-25:viento:1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-10-23 23:09</t>
+          <t>2026-10-24 02:55</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1792811349000</v>
+        <v>1792824927736</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5713,36 +5709,56 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Revelan lista preliminar de heridos tras accidente de Los Chicos Fieles - Red Uno</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+          <t>Potosí 2026-10-25: 60.5 km/h de ráfagas pronosticadas</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPczBQcnE2SzFGMXc3b1lsTkNxVWRmS3Vnb01xOTV2WmVva3J2RVlteWpHZ3VJS2dNWGV5NW5FX3ZncnVKTEVDTGpBRndTU1FxeWxtaS1fb1FscGxXMWNXUE9zbHdob1AxVFl1eHB5OU1yUnNoOXJ6U21oVG9PVDA1ak1xQl9hUlB4V0RaQXJqZENGUm8zMUJEY3J0WW5ENE5ObWJLNmpWN0RkSmFJbnZUZGR5UFRPd3QyUFY4WQ?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
-      </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-19.58</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-65.75</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Potosí</t>
+        </is>
+      </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
+          <t>capital (pronóstico puntual)</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Potosí</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Potosí</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>noticia:1uil931</t>
+          <t>noticia:mz6q0s</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5752,15 +5768,15 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-10-23 22:49</t>
+          <t>2026-10-23 23:09</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1792810149000</v>
+        <v>1792811349000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>El Deber</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5778,13 +5794,13 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Accidente de tránsito en la ruta hacia Alto Beni deja varios heridos - El Deber</t>
+          <t>Revelan lista preliminar de heridos tras accidente de Los Chicos Fieles - Red Uno</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQakFJRmx3RlJEMkVHU0pxWXZ2ZU1ib04tZy1yeTB2OGhrYk9CU3pMaDVpRThNZktZMS14UzA2Y1VIcEQtZDg3cEU2SmlzQnBmUVVvM0ZNYzZWNExWUXQ3aHpnd3lqOHFVV3pNbDRLS1NQNGtwb2RjSFpleHJkOG5zSXVtWjVIS1dLejNybktRWTJVZXh3WkFUQVE5T2tMdFdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPczBQcnE2SzFGMXc3b1lsTkNxVWRmS3Vnb01xOTV2WmVva3J2RVlteWpHZ3VJS2dNWGV5NW5FX3ZncnVKTEVDTGpBRndTU1FxeWxtaS1fb1FscGxXMWNXUE9zbHdob1AxVFl1eHB5OU1yUnNoOXJ6U21oVG9PVDA1ak1xQl9hUlB4V0RaQXJqZENGUm8zMUJEY3J0WW5ENE5ObWJLNmpWN0RkSmFJbnZUZGR5UFRPd3QyUFY4WQ?oc=5</t>
         </is>
       </c>
       <c r="L29" t="n">
@@ -5793,37 +5809,21 @@
       <c r="M29" t="n">
         <v>1</v>
       </c>
-      <c r="N29" t="n">
-        <v>-15.578</v>
-      </c>
-      <c r="O29" t="n">
-        <v>-67.44</v>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Alto Beni, La Paz</t>
-        </is>
-      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>La Paz</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>Alto Beni</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>noticia:1tliu4i</t>
+          <t>noticia:1uil931</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5833,11 +5833,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-10-23 22:18</t>
+          <t>2026-10-23 22:49</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1792808330000</v>
+        <v>1792810149000</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQMF9BNnUzLURKNGRMUUJ1VXVRSXNnMlBsQnVXOG0tRlFtY3pvRDNPQmNJMWN2RzJVaWdoWndmcHFnTkZFZnJxRkZtMThYYWlwN09ueUgtei1pSE1hZ2FtSzN6elY4VXJHbzFxdll0eWh0ZkxwQkQ1SDZ5b0E3MlVENGZEWGZHUGlwVG4wd2x3OFNEMVpibnFr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQakFJRmx3RlJEMkVHU0pxWXZ2ZU1ib04tZy1yeTB2OGhrYk9CU3pMaDVpRThNZktZMS14UzA2Y1VIcEQtZDg3cEU2SmlzQnBmUVVvM0ZNYzZWNExWUXQ3aHpnd3lqOHFVV3pNbDRLS1NQNGtwb2RjSFpleHJkOG5zSXVtWjVIS1dLejNybktRWTJVZXh3WkFUQVE5T2tMdFdn?oc=5</t>
         </is>
       </c>
       <c r="L30" t="n">
@@ -5904,7 +5904,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>noticia:1twc9ul</t>
+          <t>noticia:1tliu4i</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5914,11 +5914,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-10-23 22:16</t>
+          <t>2026-10-23 22:18</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1792808192000</v>
+        <v>1792808330000</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNbmwzSnd6c2tFMXBWY0tiemJqRm5CNllOT2p1U0FhdW5QNGFBVXlSZVM1ak5jNGZvcXNVaUQzN3ZQQTlPbmVjQ2Y5RFl2dWVLeUN5NUFodDF0alEyZWlmOHFZWkVVbjdQbkl3ZWtmS25wQWM2TmRZZDBGM2xlS0ZhUzAweXRmcmhVWGY5dV9CUnFBNGtWZHZDSWVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQMF9BNnUzLURKNGRMUUJ1VXVRSXNnMlBsQnVXOG0tRlFtY3pvRDNPQmNJMWN2RzJVaWdoWndmcHFnTkZFZnJxRkZtMThYYWlwN09ueUgtei1pSE1hZ2FtSzN6elY4VXJHbzFxdll0eWh0ZkxwQkQ1SDZ5b0E3MlVENGZEWGZHUGlwVG4wd2x3OFNEMVpibnFr?oc=5</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -5985,7 +5985,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>noticia:1dygpkp</t>
+          <t>noticia:1twc9ul</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5995,15 +5995,15 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-23 21:39</t>
+          <t>2026-10-23 22:16</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1792805983000</v>
+        <v>1792808192000</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>El Deber</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6012,39 +6012,39 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>(Video) Así rescataron a uno de los integrantes de Los Chicos Fieles tras accidente en Caranavi - Red Uno</t>
+          <t>Accidente de tránsito en la ruta hacia Alto Beni deja varios heridos - El Deber</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOdTVUZUQxVTdvYTdONDQxVlhUTzBOS2hKLW1rS1NUcmRYRnlCVlhIcHZlSjdsaktkQm5CWkFYa3lDQkxnMlh0b3prX0lha1BtbW1qS1VuYnNiX3FiZkYyNDJDR0tqZ0pKMU5TeC04SXV4UUJOTUlPUTB6ek01bzUxTUsydjZqZzI3S3ZLUnRWSUFUVk44WEpKUl9rbzRLb2IwYl9sLVlrYmt5d2ZHNUtGd3lRNnYzMlhuMkJOZW1XSUl2N1BxZWpHbm5XTDJhRUtnR190QWQ1TDlTUVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNbmwzSnd6c2tFMXBWY0tiemJqRm5CNllOT2p1U0FhdW5QNGFBVXlSZVM1ak5jNGZvcXNVaUQzN3ZQQTlPbmVjQ2Y5RFl2dWVLeUN5NUFodDF0alEyZWlmOHFZWkVVbjdQbkl3ZWtmS25wQWM2TmRZZDBGM2xlS0ZhUzAweXRmcmhVWGY5dV9CUnFBNGtWZHZDSWVB?oc=5</t>
         </is>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N32" t="n">
-        <v>-15.813</v>
+        <v>-15.578</v>
       </c>
       <c r="O32" t="n">
-        <v>-67.46299999999999</v>
+        <v>-67.44</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Caranavi, La Paz</t>
+          <t>Alto Beni, La Paz</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -6059,14 +6059,14 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>Caranavi</t>
+          <t>Alto Beni</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>noticia:3dv7b0</t>
+          <t>noticia:1dygpkp</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6076,15 +6076,15 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-23 21:35</t>
+          <t>2026-10-23 21:39</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1792805700000</v>
+        <v>1792805983000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FmBolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6093,29 +6093,29 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Accidente en Caranavi: vehículo de Los Chicos Fieles cae a un barranco y deja varios heridos - FmBolivia</t>
+          <t>(Video) Así rescataron a uno de los integrantes de Los Chicos Fieles tras accidente en Caranavi - Red Uno</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNcE1KaHZyUTJCSElxRU9nVzdhTnczWjJGTEhFMEs0bHp2cUdFeHd3VTB0NmVFcjdEN1dsZDZLY2k1ZFFUWkhKV19PU3V2czNyamh1ZE9YajVSVF8xczF6OFhZcWFvYV9EcWg4ZDNCb2p3enhXbFpRYnJMdGdaTXNrWUZSYVhKNTVicWlCLTJ5OE05Z1BvNEx1eEloUk5qTGN3ZHNzbzZWSVljbnRmSERJUWdxRDc0MjJxMGtycWJaaVhXQUUxVUlaWVZLOWE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOdTVUZUQxVTdvYTdONDQxVlhUTzBOS2hKLW1rS1NUcmRYRnlCVlhIcHZlSjdsaktkQm5CWkFYa3lDQkxnMlh0b3prX0lha1BtbW1qS1VuYnNiX3FiZkYyNDJDR0tqZ0pKMU5TeC04SXV4UUJOTUlPUTB6ek01bzUxTUsydjZqZzI3S3ZLUnRWSUFUVk44WEpKUl9rbzRLb2IwYl9sLVlrYmt5d2ZHNUtGd3lRNnYzMlhuMkJOZW1XSUl2N1BxZWpHbm5XTDJhRUtnR190QWQ1TDlTUVk?oc=5</t>
         </is>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
         <v>-15.813</v>
@@ -6147,30 +6147,30 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-24:viento:1</t>
+          <t>noticia:3dv7b0</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-10-23 20:55</t>
+          <t>2026-10-23 21:35</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1792803329663</v>
+        <v>1792805700000</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>FmBolivia</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -6183,74 +6183,70 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-24: 78.1 km/h de ráfagas pronosticadas</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
-        </is>
-      </c>
+          <t>Accidente en Caranavi: vehículo de Los Chicos Fieles cae a un barranco y deja varios heridos - FmBolivia</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNcE1KaHZyUTJCSElxRU9nVzdhTnczWjJGTEhFMEs0bHp2cUdFeHd3VTB0NmVFcjdEN1dsZDZLY2k1ZFFUWkhKV19PU3V2czNyamh1ZE9YajVSVF8xczF6OFhZcWFvYV9EcWg4ZDNCb2p3enhXbFpRYnJMdGdaTXNrWUZSYVhKNTVicWlCLTJ5OE05Z1BvNEx1eEloUk5qTGN3ZHNzbzZWSVljbnRmSERJUWdxRDc0MjJxMGtycWJaaVhXQUUxVUlaWVZLOWE?oc=5</t>
         </is>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N34" t="n">
-        <v>-17.78</v>
+        <v>-15.813</v>
       </c>
       <c r="O34" t="n">
-        <v>-63.18</v>
+        <v>-67.46299999999999</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Caranavi, La Paz</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>capital (pronóstico puntual)</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Caranavi</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>noticia:rabz5p</t>
+          <t>clima:Santa Cruz:2026-10-24:viento:1</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-23 20:44</t>
+          <t>2026-10-23 20:55</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1792802686000</v>
+        <v>1792803329663</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -6259,22 +6255,26 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Tome previsiones: se pronostican lluvias y ambiente caluroso para este fin de semana en Cochabamba - Red Uno</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
+          <t>Santa Cruz 2026-10-24: 78.1 km/h de ráfagas pronosticadas</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTlU5NVFpY1RheTN5ZE1IbG5VYTh2Sk5hZHpHeWI3LVdnSFg2cFJFdnBCVkxiUjNKcUgyUW16SWxpMXFkMHdad2xFN043bklJeG1iQ0V1V3hBZk1Ga3NscjdPVWUySmt4bDNTdWlmSUdOMmNlZ2hkSWZFMmk4VGs0Nm9TcnRCTDhINmtnQU9zZDBUY05HcWpxN3FOX3N1dmVJblE0MGc5di1Ma1N2dGNxOUtoV1MzNnl1OXpRaTZ2UGxMc3RDWndubHVQNUd0eVROMGR2OGxVemtOaEc4bTNRaA?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L35" t="n">
@@ -6284,36 +6284,36 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>-17.39</v>
+        <v>-17.78</v>
       </c>
       <c r="O35" t="n">
-        <v>-66.16</v>
+        <v>-63.18</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Cochabamba, Cochabamba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
+          <t>capital (pronóstico puntual)</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>noticia:1jfk053</t>
+          <t>noticia:rabz5p</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -6323,11 +6323,11 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-10-23 19:08</t>
+          <t>2026-10-23 20:44</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1792796931000</v>
+        <v>1792802686000</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -6336,43 +6336,43 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>climatológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Sequía en Pasorapa: el ganado muere por falta de agua y alistan declaratoria de desastre - Red Uno</t>
+          <t>Tome previsiones: se pronostican lluvias y ambiente caluroso para este fin de semana en Cochabamba - Red Uno</t>
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNQVhTWE8zdE1BQ3lueWJPeV9wUDNsSmJpS0NJTWppMUY4QmlQSUFHVjRORmtrVHQ3MHB0T1pyS25PamxnY0hBQUtzOVRvSUNaUkdGb1RWSGl4dFA4Z3VINVpQTk1pZUpDdUIyUU5hZS1oNGhBa1RWcFhScVMwVTFrVlJaOFQ4OWFqRWVUZ051bHVJTlMxRTBhRFVLUEV2dTZFdDgtRkxJM3VvN3YzUWJfVk41ZWR5U1JoNmx0WFFkMmNTWGVleGNIQlNxWUJzdHIxSWtz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTlU5NVFpY1RheTN5ZE1IbG5VYTh2Sk5hZHpHeWI3LVdnSFg2cFJFdnBCVkxiUjNKcUgyUW16SWxpMXFkMHdad2xFN043bklJeG1iQ0V1V3hBZk1Ga3NscjdPVWUySmt4bDNTdWlmSUdOMmNlZ2hkSWZFMmk4VGs0Nm9TcnRCTDhINmtnQU9zZDBUY05HcWpxN3FOX3N1dmVJblE0MGc5di1Ma1N2dGNxOUtoV1MzNnl1OXpRaTZ2UGxMc3RDWndubHVQNUd0eVROMGR2OGxVemtOaEc4bTNRaA?oc=5</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>-18.38</v>
+        <v>-17.39</v>
       </c>
       <c r="O36" t="n">
-        <v>-64.649</v>
+        <v>-66.16</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Pasorapa, Cochabamba</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -6387,14 +6387,14 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>Pasorapa</t>
+          <t>Cochabamba</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>noticia:ix3l8o</t>
+          <t>noticia:1jfk053</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -6404,56 +6404,56 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-10-23 18:25</t>
+          <t>2026-10-23 19:08</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1792794310000</v>
+        <v>1792796931000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Visión 360</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>climatológica</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Oruro evalúa suspender clases presenciales por más de 200 casos de Coxsackie - Visión 360</t>
+          <t>Sequía en Pasorapa: el ganado muere por falta de agua y alistan declaratoria de desastre - Red Uno</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0c9IBywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNQVhTWE8zdE1BQ3lueWJPeV9wUDNsSmJpS0NJTWppMUY4QmlQSUFHVjRORmtrVHQ3MHB0T1pyS25PamxnY0hBQUtzOVRvSUNaUkdGb1RWSGl4dFA4Z3VINVpQTk1pZUpDdUIyUU5hZS1oNGhBa1RWcFhScVMwVTFrVlJaOFQ4OWFqRWVUZ051bHVJTlMxRTBhRFVLUEV2dTZFdDgtRkxJM3VvN3YzUWJfVk41ZWR5U1JoNmx0WFFkMmNTWGVleGNIQlNxWUJzdHIxSWtz?oc=5</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>-17.97</v>
+        <v>-18.38</v>
       </c>
       <c r="O37" t="n">
-        <v>-67.11</v>
+        <v>-64.649</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>Pasorapa, Cochabamba</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -6463,19 +6463,19 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Pasorapa</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>noticia:1xqv9m7</t>
+          <t>noticia:ix3l8o</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6485,62 +6485,78 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-10-23 18:09</t>
+          <t>2026-10-23 18:25</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1792793370000</v>
+        <v>1792794310000</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>El Diario del centro del país</t>
+          <t>Visión 360</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Tres heridos en tremendo choque cerca de Oncativo - El Diario del centro del país</t>
+          <t>Oruro evalúa suspender clases presenciales por más de 200 casos de Coxsackie - Visión 360</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZERhbTJMQUJVb3hmZFlSZmRGZkdBLWdFTGJVQzdqZkE4aGhhWmdQZ2JDRW1ndkJLWU90VTZ6Ti1JOUZzcFZfcE1zbkRHU1B3YTF4UkVzdllFa1p3SUlObURGamF0Vm9kc3dPLTZVWFJ4NWZZQmlySElPNHhZTnRGNGNZUWw2ZlI1eVBEQkNGNEhLWTNiLWJLUS0xYjA0UWRhc0d6bVN4aVVLSVdsQWlpMUZYdWw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0c9IBywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0cw?oc=5</t>
         </is>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3</v>
-      </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-17.97</v>
+      </c>
+      <c r="O38" t="n">
+        <v>-67.11</v>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Oruro, Oruro</t>
+        </is>
+      </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>noticia:1wuregl</t>
+          <t>noticia:1xqv9m7</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6550,78 +6566,62 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-10-23 15:39</t>
+          <t>2026-10-23 18:09</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1792784340000</v>
+        <v>1792793370000</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>FmBolivia</t>
+          <t>El Diario del centro del país</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>hidrológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Intensas lluvias inundan La Paz y activan alertas por el riesgo de desborde de ríos - FmBolivia</t>
+          <t>Tres heridos en tremendo choque cerca de Oncativo - El Diario del centro del país</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPZm85aHphekQ4U3BZZkp1ZkF6ZVdSUHgtZmltS1FxUUgza1AwcndWWDJZOWctT0RiVmVabmg5SG42NnJWMlJMMnBlYTlYaVdSb09sR0dnVDdpT29faTdiaDUtZElJdlQ3eTdjR2VsWjlta1FOS1U2Vm1vV3JwWkpvbEw1ZUR3akgwQTZnQnVENjJtVkQtVUpKVEJTeWNJSE1CaEFKa2VqMmZXbWk3ekR4ZWpmZ1Z3elFQaWNaNFJuMXA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZERhbTJMQUJVb3hmZFlSZmRGZkdBLWdFTGJVQzdqZkE4aGhhWmdQZ2JDRW1ndkJLWU90VTZ6Ti1JOUZzcFZfcE1zbkRHU1B3YTF4UkVzdllFa1p3SUlObURGamF0Vm9kc3dPLTZVWFJ4NWZZQmlySElPNHhZTnRGNGNZUWw2ZlI1eVBEQkNGNEhLWTNiLWJLUS0xYjA0UWRhc0d6bVN4aVVLSVdsQWlpMUZYdWw?oc=5</t>
         </is>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>-16.169</v>
-      </c>
-      <c r="O39" t="n">
-        <v>-68.09</v>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>La Paz, La Paz</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>La Paz</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>Nuestra Señora de La Paz</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>noticia:1570kkf</t>
+          <t>noticia:1wuregl</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6631,20 +6631,20 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-10-23 15:28</t>
+          <t>2026-10-23 15:39</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1792783705000</v>
+        <v>1792784340000</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>FmBolivia</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>hidrológica</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6657,13 +6657,13 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>¿Se suspenden las clases en Oruro? Más de 200 casos de Coxsackie activan evaluaciones - Red Uno</t>
+          <t>Intensas lluvias inundan La Paz y activan alertas por el riesgo de desborde de ríos - FmBolivia</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNMFdHaVpKRmMyOENDYm16UXJPenVSQnpmTE94bDc4UFhqakluMUdvZjAwamUxT3BVWUpJQm8xVHBWengxQmhWM1hjU3d2YXFrLXpVU2VrZDJiMXZLMlQ5bGxGOHFETFhYM0s2RjlUTlhkd0g2eXQweDFHaTlKNGNMUlJfOWg2a0JjTklXUWZKc1BmUXZuZFZ2MF9fV2lEYUY4LXNiNmk3cF9FNjVtTl9GWFotT2ltS0xXTnM1dENvSU9kbFRMalFrYVdXOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPZm85aHphekQ4U3BZZkp1ZkF6ZVdSUHgtZmltS1FxUUgza1AwcndWWDJZOWctT0RiVmVabmg5SG42NnJWMlJMMnBlYTlYaVdSb09sR0dnVDdpT29faTdiaDUtZElJdlQ3eTdjR2VsWjlta1FOS1U2Vm1vV3JwWkpvbEw1ZUR3akgwQTZnQnVENjJtVkQtVUpKVEJTeWNJSE1CaEFKa2VqMmZXbWk3ekR4ZWpmZ1Z3elFQaWNaNFJuMXA?oc=5</t>
         </is>
       </c>
       <c r="L40" t="n">
@@ -6673,14 +6673,14 @@
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>-17.97</v>
+        <v>-16.169</v>
       </c>
       <c r="O40" t="n">
-        <v>-67.11</v>
+        <v>-68.09</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>La Paz, La Paz</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -6690,19 +6690,19 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Nuestra Señora de La Paz</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>noticia:1nzu2o8</t>
+          <t>noticia:1570kkf</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6712,39 +6712,39 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-10-23 15:20</t>
+          <t>2026-10-23 15:28</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1792783236000</v>
+        <v>1792783705000</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>hidrológica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Alerta naranja por posibles desbordes en tres departamentos (15:20) - El Diario - Bolivia</t>
+          <t>¿Se suspenden las clases en Oruro? Más de 200 casos de Coxsackie activan evaluaciones - Red Uno</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPTnBESV9OODZhNjY3T2M2X2NZcmk4clI0eFZsd3VLMVRwaUlSdF9wanZyVGxDNUlNTm5wbGpLN1lvX09mNGxFVkpIZDNGdi1pNDdfSGlESThfeVloQzJsNUMyNUpWUDhzTVJiYWJpNkQ1RHliRWljZlp3SlhtZ2FhU0pvV0syUmZIejJZWHlRdTBOTG4zaTc5cEsycW9IcEx2SkQtN01Gendlb1VR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNMFdHaVpKRmMyOENDYm16UXJPenVSQnpmTE94bDc4UFhqakluMUdvZjAwamUxT3BVWUpJQm8xVHBWengxQmhWM1hjU3d2YXFrLXpVU2VrZDJiMXZLMlQ5bGxGOHFETFhYM0s2RjlUTlhkd0g2eXQweDFHaTlKNGNMUlJfOWg2a0JjTklXUWZKc1BmUXZuZFZ2MF9fV2lEYUY4LXNiNmk3cF9FNjVtTl9GWFotT2ltS0xXTnM1dENvSU9kbFRMalFrYVdXOA?oc=5</t>
         </is>
       </c>
       <c r="L41" t="n">
@@ -6753,21 +6753,37 @@
       <c r="M41" t="n">
         <v>0</v>
       </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
+      <c r="N41" t="n">
+        <v>-17.97</v>
+      </c>
+      <c r="O41" t="n">
+        <v>-67.11</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Oruro, Oruro</t>
+        </is>
+      </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>noticia:1itd1r7</t>
+          <t>noticia:1nzu2o8</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6777,39 +6793,39 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-10-23 15:01</t>
+          <t>2026-10-23 15:20</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1792782098000</v>
+        <v>1792783236000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>eju.tv</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>hidrológica</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Intensa lluvia y granizada en La Paz inundan vías y elevan el nivel de los ríos - eju.tv</t>
+          <t>Alerta naranja por posibles desbordes en tres departamentos (15:20) - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNWU9QWElKQXEyN3UxVm4xbzJzbEJ1TU1NTHZlRUp6YndmeU9GQnJKcTluVEJ2ZHQ5cGp3aWhlMUd5ektWQlBpUVNmZnZuRnJwMXlydzAzX0FBVnY5UDMzQTBkWVRNRUNJSlRvX3MyQVhMcEhIMW9WSUpXckVSd0RJWk1KMFBKWmJNU3diQVlEN1Y5aVV6eVBaZXpOMnFIWWxaMlRlY0ZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPTnBESV9OODZhNjY3T2M2X2NZcmk4clI0eFZsd3VLMVRwaUlSdF9wanZyVGxDNUlNTm5wbGpLN1lvX09mNGxFVkpIZDNGdi1pNDdfSGlESThfeVloQzJsNUMyNUpWUDhzTVJiYWJpNkQ1RHliRWljZlp3SlhtZ2FhU0pvV0syUmZIejJZWHlRdTBOTG4zaTc5cEsycW9IcEx2SkQtN01Gendlb1VR?oc=5</t>
         </is>
       </c>
       <c r="L42" t="n">
@@ -6818,37 +6834,21 @@
       <c r="M42" t="n">
         <v>0</v>
       </c>
-      <c r="N42" t="n">
-        <v>-16.169</v>
-      </c>
-      <c r="O42" t="n">
-        <v>-68.09</v>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>La Paz, La Paz</t>
-        </is>
-      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>La Paz</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>Nuestra Señora de La Paz</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>noticia:1l4xxfk</t>
+          <t>noticia:1itd1r7</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6858,20 +6858,20 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-10-23 14:51</t>
+          <t>2026-10-23 15:01</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1792781480000</v>
+        <v>1792782098000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>eju.tv</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6884,13 +6884,13 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
+          <t>Intensa lluvia y granizada en La Paz inundan vías y elevan el nivel de los ríos - eju.tv</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQS2FPaHd3UnFBRjRoa0lKUm1MNUQ5S00zN1RJZE5fWlVUQnhiY0lLcFRkY2JZak1mZ0c2WEVMVUNJVUJTMGFLNHg4S2ZKNTRqLXJHM09ET19hX1pZeTQwUkdEc2huTHVpcno2QTRZbnhralVRWXozcWc1a2pHUEpBeTV1cWgzTWRwaDEweURKeVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNWU9QWElKQXEyN3UxVm4xbzJzbEJ1TU1NTHZlRUp6YndmeU9GQnJKcTluVEJ2ZHQ5cGp3aWhlMUd5ektWQlBpUVNmZnZuRnJwMXlydzAzX0FBVnY5UDMzQTBkWVRNRUNJSlRvX3MyQVhMcEhIMW9WSUpXckVSd0RJWk1KMFBKWmJNU3diQVlEN1Y5aVV6eVBaZXpOMnFIWWxaMlRlY0ZB?oc=5</t>
         </is>
       </c>
       <c r="L43" t="n">
@@ -6900,14 +6900,14 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>-17.97</v>
+        <v>-16.169</v>
       </c>
       <c r="O43" t="n">
-        <v>-67.11</v>
+        <v>-68.09</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>La Paz, La Paz</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -6917,19 +6917,19 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Nuestra Señora de La Paz</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>noticia:51709n</t>
+          <t>noticia:1l4xxfk</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6939,56 +6939,56 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-10-23 13:38</t>
+          <t>2026-10-23 14:51</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1792777139000</v>
+        <v>1792781480000</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>eju.tv</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - eju.tv</t>
+          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPcjZTSmprRGVoNlRqQmdBTE5VM3pRQ1ZFakFUbzVyMUhiaDVkT0liaG9UNEZXekV6bWsycUk4X1JCSEY5RjhNVlZaTk9ULUFuZkY3NnZuWmZ1a19leUhFdlIyQV9kLWxlSkxfeXFhcFRTZjZ2YkpQQlJ1dkNLMDBjaGZ4SkhyQ0RfcnhKSEg5WURCQVQwbENYTHEzUzJSaUEzMGo2bWdyS3lsM016LXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQS2FPaHd3UnFBRjRoa0lKUm1MNUQ5S00zN1RJZE5fWlVUQnhiY0lLcFRkY2JZak1mZ0c2WEVMVUNJVUJTMGFLNHg4S2ZKNTRqLXJHM09ET19hX1pZeTQwUkdEc2huTHVpcno2QTRZbnhralVRWXozcWc1a2pHUEpBeTV1cWgzTWRwaDEweURKeVE?oc=5</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>-17.764</v>
+        <v>-17.97</v>
       </c>
       <c r="O44" t="n">
-        <v>-62.903</v>
+        <v>-67.11</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Cotoca, Santa Cruz</t>
+          <t>Oruro, Oruro</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -6998,19 +6998,19 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Oruro</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>Cotoca</t>
+          <t>Oruro</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>noticia:11rddql</t>
+          <t>noticia:51709n</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -7020,56 +7020,56 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-10-23 13:22</t>
+          <t>2026-10-23 13:38</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1792776139000</v>
+        <v>1792777139000</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>eju.tv</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Intensifican acciones preventivas contra el dengue en Caranavi - El Diario - Bolivia</t>
+          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - eju.tv</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOMjhSeDJBek5iaFhDcnFzX1lKelgwZmUwLTJnbEhMdDRMelUxNks5Ti1pRHh3dDhTcC1YZEdqM3FJOGdqVHRvcXVhRlpCQzVDTEZMUFBkV1NrYVQ2LXRqTTBhcGRQc21CQ0VabzZaNExXb1BjTzJ2Uk5BcFF0VG5XOFNRa3lqUWlJSnRFUUVXYnNpbXB0LVVmSXVWSzJxcmVpdVVxUC1KOUhTQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPcjZTSmprRGVoNlRqQmdBTE5VM3pRQ1ZFakFUbzVyMUhiaDVkT0liaG9UNEZXekV6bWsycUk4X1JCSEY5RjhNVlZaTk9ULUFuZkY3NnZuWmZ1a19leUhFdlIyQV9kLWxlSkxfeXFhcFRTZjZ2YkpQQlJ1dkNLMDBjaGZ4SkhyQ0RfcnhKSEg5WURCQVQwbENYTHEzUzJSaUEzMGo2bWdyS3lsM016LXc?oc=5</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N45" t="n">
-        <v>-15.813</v>
+        <v>-17.764</v>
       </c>
       <c r="O45" t="n">
-        <v>-67.46299999999999</v>
+        <v>-62.903</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Caranavi, La Paz</t>
+          <t>Cotoca, Santa Cruz</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -7079,19 +7079,19 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>Caranavi</t>
+          <t>Cotoca</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>noticia:fcm3nx</t>
+          <t>noticia:11rddql</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -7101,62 +7101,78 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-10-23 12:58</t>
+          <t>2026-10-23 13:22</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1792774699000</v>
+        <v>1792776139000</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>[VIDEO] Así fue el accidente de moto que dejó un adolescente fallecido y un hombre gravemente herido - Red Uno</t>
+          <t>Intensifican acciones preventivas contra el dengue en Caranavi - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOSmJMazhUemNfRHpWcDBoTVFZMUpwdlVKVUtvUXZNTGRRRHlwLW5KNmNhcmFnd1czbi1yalhFMnpSS1dmUE9jVzNlOS1kMWZtRzBHZ2EtcDRDdU5Gc2JUQVIwM2xPa2lZVmswRi1SUFVPcm8xcHlGN3F2UThTSDdKMDNyYnJmVkcxazNLLVBLOWFYM09FVUpmVnN5RVhpSVo2V1VCVmFwQ1gzTmRUWVp2aXMwcmxHRS1GV2p3NTBtR2RzM2wwVHUzaGJkRXJYbHdvaDlhWm5YMTk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOMjhSeDJBek5iaFhDcnFzX1lKelgwZmUwLTJnbEhMdDRMelUxNks5Ti1pRHh3dDhTcC1YZEdqM3FJOGdqVHRvcXVhRlpCQzVDTEZMUFBkV1NrYVQ2LXRqTTBhcGRQc21CQ0VabzZaNExXb1BjTzJ2Uk5BcFF0VG5XOFNRa3lqUWlJSnRFUUVXYnNpbXB0LVVmSXVWSzJxcmVpdVVxUC1KOUhTQQ?oc=5</t>
         </is>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>1</v>
-      </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>-15.813</v>
+      </c>
+      <c r="O46" t="n">
+        <v>-67.46299999999999</v>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Caranavi, La Paz</t>
+        </is>
+      </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>La Paz</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Caranavi</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>noticia:1cjx1qd</t>
+          <t>noticia:fcm3nx</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -7166,78 +7182,62 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-10-23 12:39</t>
+          <t>2026-10-23 12:58</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1792773575000</v>
+        <v>1792774699000</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Más de 60 municipios en La Paz sufren falta de lluvias - La Patria Bolivia</t>
+          <t>[VIDEO] Así fue el accidente de moto que dejó un adolescente fallecido y un hombre gravemente herido - Red Uno</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE52Qi03Z1J6OS1CR2liRVZ0VlhCcmVQWFV6RUdGNXdrbzZRNXFjTWRaRnc1b3VoV0xaY3RIdncxNlNnYkxyUXo5MTlJWmMwWDNSMDE4ZHI2VkpWajFPaUF2SmRVYkk2eDZYQ1RfUU9ieENrZG9UVVFiaXZSeGI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOSmJMazhUemNfRHpWcDBoTVFZMUpwdlVKVUtvUXZNTGRRRHlwLW5KNmNhcmFnd1czbi1yalhFMnpSS1dmUE9jVzNlOS1kMWZtRzBHZ2EtcDRDdU5Gc2JUQVIwM2xPa2lZVmswRi1SUFVPcm8xcHlGN3F2UThTSDdKMDNyYnJmVkcxazNLLVBLOWFYM09FVUpmVnN5RVhpSVo2V1VCVmFwQ1gzTmRUWVp2aXMwcmxHRS1GV2p3NTBtR2RzM2wwVHUzaGJkRXJYbHdvaDlhWm5YMTk?oc=5</t>
         </is>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>-16.169</v>
-      </c>
-      <c r="O47" t="n">
-        <v>-68.09</v>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>La Paz, La Paz</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>La Paz</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>Nuestra Señora de La Paz</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>noticia:11y8tre</t>
+          <t>noticia:1cjx1qd</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -7247,56 +7247,56 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-10-23 11:43</t>
+          <t>2026-10-23 12:39</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1792770197000</v>
+        <v>1792773575000</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>La Patria Bolivia</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - Red Uno</t>
+          <t>Más de 60 municipios en La Paz sufren falta de lluvias - La Patria Bolivia</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOVGY3YVRLWWxYM0IycjF4dlNUeUhqZG90Yng4aWhmN3A5ai02WENWYnF4bWpoZHFKMGc1X0JPRHdRRVZfSlA4UmZFa2kxYkNIS3ZtQ1NvNlNCME51eVZTRkRKSUQ5MmRoaWl5Tkt5NHpPUEFwemN2YTV1djFwdHlqQnFqRHNPenhYcTlsanJPcXhpOVV1NmFBUXZyazQ2MkUzM0dSZy02ZllxTGtjcl9ldzdHSktTRlVaalZJc1pubUNQMWFTbzVEOUJ1UmhCdEJt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE52Qi03Z1J6OS1CR2liRVZ0VlhCcmVQWFV6RUdGNXdrbzZRNXFjTWRaRnc1b3VoV0xaY3RIdncxNlNnYkxyUXo5MTlJWmMwWDNSMDE4ZHI2VkpWajFPaUF2SmRVYkk2eDZYQ1RfUU9ieENrZG9UVVFiaXZSeGI?oc=5</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>-17.764</v>
+        <v>-16.169</v>
       </c>
       <c r="O48" t="n">
-        <v>-62.903</v>
+        <v>-68.09</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Cotoca, Santa Cruz</t>
+          <t>La Paz, La Paz</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -7306,42 +7306,42 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>Cotoca</t>
+          <t>Nuestra Señora de La Paz</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>clima:Sucre:2026-10-23:viento:1</t>
+          <t>noticia:11y8tre</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-10-23 06:55</t>
+          <t>2026-10-23 11:43</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1792752927735</v>
+        <v>1792770197000</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7354,56 +7354,52 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Sucre 2026-10-23: 66.2 km/h de ráfagas pronosticadas</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
-        </is>
-      </c>
+          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - Red Uno</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOVGY3YVRLWWxYM0IycjF4dlNUeUhqZG90Yng4aWhmN3A5ai02WENWYnF4bWpoZHFKMGc1X0JPRHdRRVZfSlA4UmZFa2kxYkNIS3ZtQ1NvNlNCME51eVZTRkRKSUQ5MmRoaWl5Tkt5NHpPUEFwemN2YTV1djFwdHlqQnFqRHNPenhYcTlsanJPcXhpOVV1NmFBUXZyazQ2MkUzM0dSZy02ZllxTGtjcl9ldzdHSktTRlVaalZJc1pubUNQMWFTbzVEOUJ1UmhCdEJt?oc=5</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N49" t="n">
-        <v>-19.03</v>
+        <v>-17.764</v>
       </c>
       <c r="O49" t="n">
-        <v>-65.26000000000001</v>
+        <v>-62.903</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Cotoca, Santa Cruz</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>capital (pronóstico puntual)</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Chuquisaca</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Cotoca</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-24:viento:2</t>
+          <t>clima:Sucre:2026-10-23:viento:1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -7417,7 +7413,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1792752927734</v>
+        <v>1792752927735</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -7430,16 +7426,16 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-24: 85 km/h de ráfagas pronosticadas</t>
+          <t>Sucre 2026-10-23: 66.2 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -7459,14 +7455,14 @@
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>-17.78</v>
+        <v>-19.03</v>
       </c>
       <c r="O50" t="n">
-        <v>-63.18</v>
+        <v>-65.26000000000001</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -7476,65 +7472,65 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Chuquisaca</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Sucre</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>usgs:us6000u49c</t>
+          <t>clima:Santa Cruz:2026-10-24:viento:2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>usgs</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-10-22 22:45</t>
+          <t>2026-10-23 06:55</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1792723541183</v>
+        <v>1792752927734</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>USGS</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>geológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Sismo M 4.5 - 58 km SW of Atocha, Bolivia</t>
+          <t>Santa Cruz 2026-10-24: 85 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Profundidad 236 km</t>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://earthquake.usgs.gov/earthquakes/eventpage/us6000u49c</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L51" t="n">
@@ -7544,59 +7540,59 @@
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>-21.3469</v>
+        <v>-17.78</v>
       </c>
       <c r="O51" t="n">
-        <v>-66.5795</v>
+        <v>-63.18</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>58 km SW of Atocha, Bolivia</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>coordenada de la fuente</t>
+          <t>capital (pronóstico puntual)</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>San Pablo</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-22:viento:1</t>
+          <t>usgs:us6000u49c</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>usgs</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-10-22 21:55</t>
+          <t>2026-10-22 22:45</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1792720528712</v>
+        <v>1792723541183</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>USGS</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>geológica</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7609,17 +7605,17 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-22: 67.7 km/h de ráfagas pronosticadas</t>
+          <t>Sismo M 4.5 - 58 km SW of Atocha, Bolivia</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+          <t>Profundidad 236 km</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://earthquake.usgs.gov/earthquakes/eventpage/us6000u49c</t>
         </is>
       </c>
       <c r="L52" t="n">
@@ -7629,36 +7625,36 @@
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>-17.78</v>
+        <v>-21.3469</v>
       </c>
       <c r="O52" t="n">
-        <v>-63.18</v>
+        <v>-66.5795</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>58 km SW of Atocha, Bolivia</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>capital (pronóstico puntual)</t>
+          <t>coordenada de la fuente</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>San Pablo</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-23:viento:2</t>
+          <t>clima:Santa Cruz:2026-10-22:viento:1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -7685,16 +7681,16 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-23: 83.9 km/h de ráfagas pronosticadas</t>
+          <t>Santa Cruz 2026-10-22: 67.7 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -7743,49 +7739,53 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>noticia:1hhvre7</t>
+          <t>clima:Santa Cruz:2026-10-23:viento:2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-10-22 19:36</t>
+          <t>2026-10-22 21:55</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1792712202000</v>
+        <v>1792720528712</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>El Mundo Bolivia</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Virgen de Cotoca: Controlan incendio en depósito de materiales plásticos - El Mundo Bolivia</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr"/>
+          <t>Santa Cruz 2026-10-23: 83.9 km/h de ráfagas pronosticadas</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcDF6VE5FNzRaWGRuUzFKeXhnZ21DZTRaaEtrVEJEa1Z3ejg2VG1ONG1ENmlDWlkyVjlkQkJwS2F1XzBGMFQwSHd4OEwxTW1PbHdGcUh1ckV6SGpDd2hiN0dkeUVTcnFXT3RjOU1kLXZtVVdZY2hkZS1pcVpVUFhnRktqcHY5UnBrY0xUMDRETjl6N0pXT3A5amxhMA?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L54" t="n">
@@ -7795,19 +7795,19 @@
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>-17.764</v>
+        <v>-17.78</v>
       </c>
       <c r="O54" t="n">
-        <v>-62.903</v>
+        <v>-63.18</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Cotoca, Santa Cruz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
+          <t>capital (pronóstico puntual)</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -7817,14 +7817,14 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>Cotoca</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>noticia:bksnde</t>
+          <t>noticia:1hhvre7</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -7834,15 +7834,15 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-10-22 17:01</t>
+          <t>2026-10-22 19:36</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1792702880000</v>
+        <v>1792712202000</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>eju.tv</t>
+          <t>El Mundo Bolivia</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -7860,13 +7860,13 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Reportan un incendio cerca de la carretera a Cotoca - eju.tv</t>
+          <t>Virgen de Cotoca: Controlan incendio en depósito de materiales plásticos - El Mundo Bolivia</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPNGtpbnBfRnRBalVudnBlZHdVQ0ZSaUplZmtvTGE0aTQzdkxWS3d4My1EZEJ1UE9FNFQ3RmpyZGVsbS1qNEM1QUVFRFAxM2pYT1VqQzRuVjRtZnVNUGlKODNMc0F1a3l6TUpuQmtlUWNlVTVEWWU5ZGZtQm5LWUp3Sg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcDF6VE5FNzRaWGRuUzFKeXhnZ21DZTRaaEtrVEJEa1Z3ejg2VG1ONG1ENmlDWlkyVjlkQkJwS2F1XzBGMFQwSHd4OEwxTW1PbHdGcUh1ckV6SGpDd2hiN0dkeUVTcnFXT3RjOU1kLXZtVVdZY2hkZS1pcVpVUFhnRktqcHY5UnBrY0xUMDRETjl6N0pXT3A5amxhMA?oc=5</t>
         </is>
       </c>
       <c r="L55" t="n">
@@ -7905,7 +7905,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>noticia:17hz69v</t>
+          <t>noticia:bksnde</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7915,15 +7915,15 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-10-22 13:05</t>
+          <t>2026-10-22 17:01</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1792688709000</v>
+        <v>1792702880000</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>La Razón Digital Bolivia</t>
+          <t>eju.tv</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -7932,45 +7932,61 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Accidente en El Sillar deja al menos 29 heridos - La Razón Digital Bolivia</t>
+          <t>Reportan un incendio cerca de la carretera a Cotoca - eju.tv</t>
         </is>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPaXhTdm45YWZnWVFxVzJnb1ZwbUN4SmUtLVdJN0VJdFZBamRyQmFxN0RZelBfTklaSTVyOUZ3ajQ5MFB2TEN4Ukd6TE5ORFY5SEROVk1CZ25sRWJ1QnRBdTVfTktlby1NWXhaVWI5YnRvaDZWbHVjdDVoeFp5Tk5veFk5a19MSWJqcEJVV0dzV3k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPNGtpbnBfRnRBalVudnBlZHdVQ0ZSaUplZmtvTGE0aTQzdkxWS3d4My1EZEJ1UE9FNFQ3RmpyZGVsbS1qNEM1QUVFRFAxM2pYT1VqQzRuVjRtZnVNUGlKODNMc0F1a3l6TUpuQmtlUWNlVTVEWWU5ZGZtQm5LWUp3Sg?oc=5</t>
         </is>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>29</v>
-      </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>-17.764</v>
+      </c>
+      <c r="O56" t="n">
+        <v>-62.903</v>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Cotoca, Santa Cruz</t>
+        </is>
+      </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Cotoca</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>noticia:1f1qb0</t>
+          <t>noticia:17hz69v</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7980,15 +7996,15 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-10-22 12:09</t>
+          <t>2026-10-22 13:05</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1792685373000</v>
+        <v>1792688709000</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>La Razón Digital Bolivia</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -7997,61 +8013,45 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Accidente en el tramo Locotal–Villa Tunari: la vía está transitable con precaución - Red Uno</t>
+          <t>Accidente en El Sillar deja al menos 29 heridos - La Razón Digital Bolivia</t>
         </is>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTFozcEEwNXBqV19sS2VibXh0MGt0QlhsX1djSTFGQW5zNlFLRHZpNVVnZ1JmWDQ4LVRHX2Rmb3B5UU9qV0FZQmJCaUZYdmwyNG1NenJ4Qzlzd0NJTGs1SjMxdFRtRFBzSUkybGJfZFFaNFZBc21FSUJYSFVkQkVkSEhQaGw0UFVzeXctZHo3cjNsYm5weXJlOU1wcmFncnNhMC1BQUpvNWlDX1NxZXU4b09kVFFWR2tSVEk2UTdXXzB3TjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPaXhTdm45YWZnWVFxVzJnb1ZwbUN4SmUtLVdJN0VJdFZBamRyQmFxN0RZelBfTklaSTVyOUZ3ajQ5MFB2TEN4Ukd6TE5ORFY5SEROVk1CZ25sRWJ1QnRBdTVfTktlby1NWXhaVWI5YnRvaDZWbHVjdDVoeFp5Tk5veFk5a19MSWJqcEJVV0dzV3k?oc=5</t>
         </is>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="n">
-        <v>-16.556</v>
-      </c>
-      <c r="O57" t="n">
-        <v>-65.569</v>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>Villa Tunari, Cochabamba</t>
-        </is>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>Villa Tunari</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>noticia:wi18tm</t>
+          <t>noticia:1f1qb0</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -8061,11 +8061,11 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-10-22 11:53</t>
+          <t>2026-10-22 12:09</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1792684426000</v>
+        <v>1792685373000</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -8074,49 +8074,65 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>tecnológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Accidente en El Sillar deja heridos y derrame de combustible: esto es lo último que se sabe - Red Uno</t>
+          <t>Accidente en el tramo Locotal–Villa Tunari: la vía está transitable con precaución - Red Uno</t>
         </is>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPZHNBTEdaQm5Wby1lTF9mWlQ2aGg0MVc4S0MwVWJ3dUJ5WWU5X3IwYWhKRjk5VWtYWEJHRDF4QldVc29laVNPSTJNWFBDSkNFQlFSYTJUXzNMNF9hckFBN1I2T2xoQUtYQ2V6MDNTZHhHVk9qeTBCdHRpM2ZLd0pyOFRweUUxX19STzRHTHg5VUY5d1lhS0tDeXpCdklqcTZGT1J4R0xnSDhoak1EZ2dtNUhSTUV6b1o0U0VSdWY5X0E3U05Tc1dYVEN2WFZUeFhPMTBJTmowNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTFozcEEwNXBqV19sS2VibXh0MGt0QlhsX1djSTFGQW5zNlFLRHZpNVVnZ1JmWDQ4LVRHX2Rmb3B5UU9qV0FZQmJCaUZYdmwyNG1NenJ4Qzlzd0NJTGs1SjMxdFRtRFBzSUkybGJfZFFaNFZBc21FSUJYSFVkQkVkSEhQaGw0UFVzeXctZHo3cjNsYm5weXJlOU1wcmFncnNhMC1BQUpvNWlDX1NxZXU4b09kVFFWR2tSVEk2UTdXXzB3TjA?oc=5</t>
         </is>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>1</v>
-      </c>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>-16.556</v>
+      </c>
+      <c r="O58" t="n">
+        <v>-65.569</v>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Villa Tunari, Cochabamba</t>
+        </is>
+      </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>Villa Tunari</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>noticia:12gfagq</t>
+          <t>noticia:wi18tm</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -8126,78 +8142,62 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-10-22 11:28</t>
+          <t>2026-10-22 11:53</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1792682880000</v>
+        <v>1792684426000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>FmBolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>tecnológica</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Reportan triple colisión entre dos camiones y un bus en la carretera Cochabamba-Santa Cruz - FmBolivia</t>
+          <t>Accidente en El Sillar deja heridos y derrame de combustible: esto es lo último que se sabe - Red Uno</t>
         </is>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNMTNBaFZNMU9SR25vdVBuNXlZY3g4VkFWYXRiQnNSaUFjemZhUHZWNHg4V2owU2xfNndBak94TnU2cHNUVXdNNWl2eUdHZVNMbVZweTR5M0o0bWdTNUN4QkoxUkI2TDBmVE03M09zRGhJRVFzV0tPZ1NCWEJLUkt1ZGN4UGduOUZMQnJoM0tMYTh0ZlFxaFJNUkJqaWFPazRlMzN3ajhjUEdUYXlZRndpb3RSdTFCX2tCZGJxQ0x4SlBISWJsRVoyN3ZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPZHNBTEdaQm5Wby1lTF9mWlQ2aGg0MVc4S0MwVWJ3dUJ5WWU5X3IwYWhKRjk5VWtYWEJHRDF4QldVc29laVNPSTJNWFBDSkNFQlFSYTJUXzNMNF9hckFBN1I2T2xoQUtYQ2V6MDNTZHhHVk9qeTBCdHRpM2ZLd0pyOFRweUUxX19STzRHTHg5VUY5d1lhS0tDeXpCdklqcTZGT1J4R0xnSDhoak1EZ2dtNUhSTUV6b1o0U0VSdWY5X0E3U05Tc1dYVEN2WFZUeFhPMTBJTmowNA?oc=5</t>
         </is>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="n">
-        <v>-17.39</v>
-      </c>
-      <c r="O59" t="n">
-        <v>-66.16</v>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>Cochabamba, Cochabamba</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>noticia:1uq1bxy</t>
+          <t>noticia:12gfagq</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -8207,15 +8207,15 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-10-22 10:44</t>
+          <t>2026-10-22 11:28</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1792680273000</v>
+        <v>1792682880000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>FmBolivia</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -8233,13 +8233,13 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Reportan triple colisión en la carretera Cochabamba–Santa Cruz - Red Uno</t>
+          <t>Reportan triple colisión entre dos camiones y un bus en la carretera Cochabamba-Santa Cruz - FmBolivia</t>
         </is>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNNUROMzd1UDJRWVZZQ011cFd2c1FSdER1ZzdleU04cXpwYk5HaUZrLXoyU2NzdFk1dnNRUndhUWt0cG9DX09rSjlLcDItU0tzcmQtS3E4dDQ4ZF9HdGJLdk13ek9BNHJUWVlCcklrM25rZ01RbXhLalRBT1FGdDNReHdlTFZkNkJ5ZFd3N3NZVFVmOFUxbEhHN0RsaUxiSVZsM0lXVEFYSHVRQlhsOEtJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNMTNBaFZNMU9SR25vdVBuNXlZY3g4VkFWYXRiQnNSaUFjemZhUHZWNHg4V2owU2xfNndBak94TnU2cHNUVXdNNWl2eUdHZVNMbVZweTR5M0o0bWdTNUN4QkoxUkI2TDBmVE03M09zRGhJRVFzV0tPZ1NCWEJLUkt1ZGN4UGduOUZMQnJoM0tMYTh0ZlFxaFJNUkJqaWFPazRlMzN3ajhjUEdUYXlZRndpb3RSdTFCX2tCZGJxQ0x4SlBISWJsRVoyN3ZR?oc=5</t>
         </is>
       </c>
       <c r="L60" t="n">
@@ -8278,7 +8278,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>noticia:1jl2oid</t>
+          <t>noticia:1uq1bxy</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -8288,15 +8288,15 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-10-22 07:49</t>
+          <t>2026-10-22 10:44</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1792669785000</v>
+        <v>1792680273000</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>eju.tv</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -8305,39 +8305,39 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - eju.tv</t>
+          <t>Reportan triple colisión en la carretera Cochabamba–Santa Cruz - Red Uno</t>
         </is>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQbTBrUmlla3FvVU1EX1pxcUI3SXYzbUFFMzlnRzhlSDJwMGpWWURxYjIwSkJBRGdCazMzT01hVy1qMFY3RnJLbC1XNXJ4bU55aDJVeXpNUlRsbzQ3T3hiRXJ5SWlhNmw5cDZFanNoWFBtQ01Gd3dscXltWmU5VHBSQlN3c2IwNGxuVE5tQ3lOT1RmNzRiVi1hc0hn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNNUROMzd1UDJRWVZZQ011cFd2c1FSdER1ZzdleU04cXpwYk5HaUZrLXoyU2NzdFk1dnNRUndhUWt0cG9DX09rSjlLcDItU0tzcmQtS3E4dDQ4ZF9HdGJLdk13ek9BNHJUWVlCcklrM25rZ01RbXhLalRBT1FGdDNReHdlTFZkNkJ5ZFd3N3NZVFVmOFUxbEhHN0RsaUxiSVZsM0lXVEFYSHVRQlhsOEtJ?oc=5</t>
         </is>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>-17.781</v>
+        <v>-17.39</v>
       </c>
       <c r="O61" t="n">
-        <v>-63.139</v>
+        <v>-66.16</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Santa Cruz, Santa Cruz</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -8347,19 +8347,19 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Cochabamba</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>noticia:yqgeq</t>
+          <t>noticia:1jl2oid</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -8369,15 +8369,15 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-10-22 07:43</t>
+          <t>2026-10-22 07:49</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1792669426000</v>
+        <v>1792669785000</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>eju.tv</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -8395,13 +8395,13 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - Red Uno</t>
+          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - eju.tv</t>
         </is>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNVEh1bFlCanFuOTJid2EzYS1meG5oekFJcGFaME1fTk9sUnZpd3U0UXFHUFVJSW1jc1hzM2VFOFprT2xNYjBzbmswZmdJV3dremRIS0I4MDNzRjBnbEttWEhfOWZBbmFrRnNHWDFVLVFoM0VkZkxkaW4tMmZlSFJLei1heTFHMU0wSmxQVVRZN0cwaXQzcDBtZkdwTUFma0RXU2dwLXRnLTBkNGN3Vm1fV3hEdlM1dWZ1SEsw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQbTBrUmlla3FvVU1EX1pxcUI3SXYzbUFFMzlnRzhlSDJwMGpWWURxYjIwSkJBRGdCazMzT01hVy1qMFY3RnJLbC1XNXJ4bU55aDJVeXpNUlRsbzQ3T3hiRXJ5SWlhNmw5cDZFanNoWFBtQ01Gd3dscXltWmU5VHBSQlN3c2IwNGxuVE5tQ3lOT1RmNzRiVi1hc0hn?oc=5</t>
         </is>
       </c>
       <c r="L62" t="n">
@@ -8440,7 +8440,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>noticia:n32ahi</t>
+          <t>noticia:yqgeq</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -8450,69 +8450,150 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-10-22 05:30</t>
+          <t>2026-10-22 07:43</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1792661402000</v>
+        <v>1792669426000</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FmBolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Senamhi anuncia el inicio de la temporada de lluvias en Bolivia y prevé granizadas como la de La Paz - FmBolivia</t>
+          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - Red Uno</t>
         </is>
       </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNVEh1bFlCanFuOTJid2EzYS1meG5oekFJcGFaME1fTk9sUnZpd3U0UXFHUFVJSW1jc1hzM2VFOFprT2xNYjBzbmswZmdJV3dremRIS0I4MDNzRjBnbEttWEhfOWZBbmFrRnNHWDFVLVFoM0VkZkxkaW4tMmZlSFJLei1heTFHMU0wSmxQVVRZN0cwaXQzcDBtZkdwTUFma0RXU2dwLXRnLTBkNGN3Vm1fV3hEdlM1dWZ1SEsw?oc=5</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1</v>
+      </c>
+      <c r="N63" t="n">
+        <v>-17.781</v>
+      </c>
+      <c r="O63" t="n">
+        <v>-63.139</v>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Santa Cruz, Santa Cruz</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Santa Cruz de la Sierra</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>noticia:n32ahi</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>noticia</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-10-22 05:30</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>1792661402000</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>FmBolivia</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>meteorológica</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>verde</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Senamhi anuncia el inicio de la temporada de lluvias en Bolivia y prevé granizadas como la de La Paz - FmBolivia</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
           <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQNmVPRnVBMGQzdEI5SUp3Z3ZGVExwTUR6TWNadGQ1QldUS1o2QVFvUl9sVEZKMDVyQVVrS25rU1RSQlJKWXk1YzE0NUhidjhpcmFaSlhZUDZvcE9XcG1KTFNTYmowUU1CSFJNOVR2UHNmMk1iT3N0RVBteHkzZkgyRFROYk1pdkpxVHZya3N2X2FVLVQxbURFVVZlb1NzRjZzTE95TXFVUXFJNkVZakQ2bUhVQzB0SXk3TVhXUTJXa0dycTE1MWVQRFpDX3lDSWFqUGwzU2NtNA?oc=5</t>
         </is>
       </c>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" t="n">
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
         <v>-16.169</v>
       </c>
-      <c r="O63" t="n">
+      <c r="O64" t="n">
         <v>-68.09</v>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>La Paz, La Paz</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>nombre de municipio en el titular</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="R64" t="inlineStr">
         <is>
           <t>La Paz</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>Nuestra Señora de La Paz</t>
         </is>
@@ -9082,7 +9163,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-10-25 13:57</t>
+          <t>2026-10-25 14:29</t>
         </is>
       </c>
     </row>
@@ -9105,7 +9186,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4">
@@ -9162,7 +9243,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sala de Situación Bolivia – CCES. Base de eventos de amenazas (datos preliminares de fuentes abiertas). Consulta: 2026-10-25 13:57.</t>
+          <t>Sala de Situación Bolivia – CCES. Base de eventos de amenazas (datos preliminares de fuentes abiertas). Consulta: 2026-10-25 14:29.</t>
         </is>
       </c>
     </row>

--- a/docs/datos/datos_bolivia.xlsx
+++ b/docs/datos/datos_bolivia.xlsx
@@ -9163,7 +9163,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-10-25 14:29</t>
+          <t>2026-10-25 15:05</t>
         </is>
       </c>
     </row>
@@ -9243,7 +9243,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sala de Situación Bolivia – CCES. Base de eventos de amenazas (datos preliminares de fuentes abiertas). Consulta: 2026-10-25 14:29.</t>
+          <t>Sala de Situación Bolivia – CCES. Base de eventos de amenazas (datos preliminares de fuentes abiertas). Consulta: 2026-10-25 15:05.</t>
         </is>
       </c>
     </row>

--- a/docs/datos/datos_bolivia.xlsx
+++ b/docs/datos/datos_bolivia.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R42"/>
+  <dimension ref="A1:R43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,25 +514,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>noticia:1xi48lm</t>
+          <t>noticia:kaqalb</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-25 13:02</t>
+          <t>2026-10-25 15:29</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1792947732000</v>
+        <v>1792956564000</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Reportan el incendio de dos camiones cisterna en la carretera a Camiri - EL DÍA - Noticias de Bolivia para el mundo</t>
+          <t>“El bolsillo no alcanza”: la sequía golpea al ganado en Pasorapa y piden tanques de agua - Red Uno</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>climatológica</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -555,57 +555,57 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>EL DÍA - Noticias de Bolivia para el mundo; La Patria Bolivia; Opinión Bolivia; Red Uno</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>-20.05</v>
+        <v>-18.38</v>
       </c>
       <c r="N2" t="n">
-        <v>-63.486</v>
+        <v>-64.649</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Camiri, Santa Cruz</t>
+          <t>Pasorapa, Cochabamba</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Camiri</t>
+          <t>Pasorapa</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNN0traUpaNVFIOU0zeFZod2tkQWhZZFQ1Q3dxc2xCVy1RNnJIX2xQbTlhT3RVckdNdHV4ZFVLQThvd2UzNDlCa3VmaWprTnU3R05rVkVkdEVCU1hFMlFsLTJ6REIySnl5VFJfdV9pQmVDTzlqUWFUSi1GQ0JvTVJVQ2dpeVBydnpMV0dYOThENTFRUDgxVFloSVg3bnN4dGo2aEVCbDFKaUgydWNISnJVUTNB?oc=5 | https://news.google.com/rss/articles/CBMimAFBVV95cUxQbHdpcUF6dXpjaW1TT1ZmdGJtUUVLMTNMRTVqVkFUdkNsZlRvenVkckFUWmI4NDFmc2ZHd2RVcWRSSE5YRVpOTUlESGw2V3JONXpwS0RISGNZd01SejNuMkY4NzFYYXp4aWo2RE9VMkFYUkVwZ3JRRmM5MWlRSjlBWk16azdkQ3FjdEtkaWc5NERkTzk2SllVOQ?oc=5 | https://news.google.com/rss/articles/CBMixgFBVV95cUxQLXlqSFdvWUVhQUNadnpkdE5lUTZQS0lobThzUTZWbDNJTE94alVhaDBaYU9Fd09SSGt3UlR3Y0dfZlNIcml1ZktnWjctNk1Na3V4S0tINFNkMXM0OHBoV2lCTTBiYXlPUTA3T2ZkeXE2RElYWjhfVHd3Nng1Z0E4alBmOFI5NDFwX09kazZlSWl2OVR2ZVR6MDhvSHFnSmJKbTFXSEFDNFFYcWVDNGtYWEQ0bDhJel9CaEpEZWZ4SWN0TE9Ya0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNRm5FbDhxTlliZHdPdnplYVNrWVdsSFF2ZGp3c2t1MEJCdWJkOE5fLWU5SXhXc25JLU9leVNsdnJZUEFFRmlTOUtJLW5SZ3JpRDFlYmlaYlFLYVJrM3pud0plS2lXVllqdEd0cWRiMUlmRzZkdnRpT2twaGU4cm1TRm9uSEw4WkhjeEJGUVZMNlJmRnFnY0M2UWw3T3NqMXdFcXhETjdrRi1hSjh3UDIxZl9CamxvYXdHRDRkZGR0ZEtZNHREX0c5Ul9Fa3VKMlJh?oc=5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>manual:1c1299f3</t>
+          <t>noticia:1xi48lm</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-25 12:44</t>
+          <t>2026-10-25 13:02</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1792946640000</v>
+        <v>1792947732000</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Vuelco de minibus</t>
+          <t>Reportan el incendio de dos camiones cisterna en la carretera a Camiri - EL DÍA - Noticias de Bolivia para el mundo</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -614,18 +614,18 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -633,53 +633,57 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Registro abierto (sin verificar)</t>
+          <t>EL DÍA - Noticias de Bolivia para el mundo; La Patria Bolivia; Opinión Bolivia; Red Uno</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>-15.813</v>
+        <v>-20.05</v>
       </c>
       <c r="N3" t="n">
-        <v>-67.46299999999999</v>
+        <v>-63.486</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Caranavi, La Paz</t>
+          <t>Camiri, Santa Cruz</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Caranavi</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
+          <t>Camiri</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNN0traUpaNVFIOU0zeFZod2tkQWhZZFQ1Q3dxc2xCVy1RNnJIX2xQbTlhT3RVckdNdHV4ZFVLQThvd2UzNDlCa3VmaWprTnU3R05rVkVkdEVCU1hFMlFsLTJ6REIySnl5VFJfdV9pQmVDTzlqUWFUSi1GQ0JvTVJVQ2dpeVBydnpMV0dYOThENTFRUDgxVFloSVg3bnN4dGo2aEVCbDFKaUgydWNISnJVUTNB?oc=5 | https://news.google.com/rss/articles/CBMimAFBVV95cUxQbHdpcUF6dXpjaW1TT1ZmdGJtUUVLMTNMRTVqVkFUdkNsZlRvenVkckFUWmI4NDFmc2ZHd2RVcWRSSE5YRVpOTUlESGw2V3JONXpwS0RISGNZd01SejNuMkY4NzFYYXp4aWo2RE9VMkFYUkVwZ3JRRmM5MWlRSjlBWk16azdkQ3FjdEtkaWc5NERkTzk2SllVOQ?oc=5 | https://news.google.com/rss/articles/CBMixgFBVV95cUxQLXlqSFdvWUVhQUNadnpkdE5lUTZQS0lobThzUTZWbDNJTE94alVhaDBaYU9Fd09SSGt3UlR3Y0dfZlNIcml1ZktnWjctNk1Na3V4S0tINFNkMXM0OHBoV2lCTTBiYXlPUTA3T2ZkeXE2RElYWjhfVHd3Nng1Z0E4alBmOFI5NDFwX09kazZlSWl2OVR2ZVR6MDhvSHFnSmJKbTFXSEFDNFFYcWVDNGtYWEQ0bDhJel9CaEpEZWZ4SWN0TE9Ya0E?oc=5</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>noticia:1sg8pi0</t>
+          <t>manual:1c1299f3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25 09:59</t>
+          <t>2026-10-25 12:44</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1792936752000</v>
+        <v>1792946640000</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bus de agrupación musical sufre accidente rumbo al trópico de Cochabamba | VIDEO - Red Uno</t>
+          <t>Vuelco de minibus</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -688,18 +692,18 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -711,58 +715,54 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>Registro abierto (sin verificar)</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>-17.39</v>
+        <v>-15.813</v>
       </c>
       <c r="N4" t="n">
-        <v>-66.16</v>
+        <v>-67.46299999999999</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Cochabamba, Cochabamba</t>
+          <t>Caranavi, La Paz</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOVDVzVTJNM2JuQ25sMThEaVZNOUNRd3FGT3RhVnFrZXZ2NDQ1YlluTVdhbVNUQnA1MGNESHRSWVUzbC1kRVh3OTR0emtlTG91cmRWeFJ5dk5zb3p2WFRyMEJUV3FNRnY1WHhRUU9WLTlJcmNyNXJZZFdoM0JoZjNpa3hjUXhMM0xrUDJab2VadkM5RWZYQ3lWZTVDdzg1akxJT2lxcDVNNzI0NG1hejdfdkUyTQ?oc=5</t>
-        </is>
-      </c>
+          <t>Caranavi</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>noticia:167wlhz</t>
+          <t>noticia:1sg8pi0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-25 07:53</t>
+          <t>2026-10-25 09:59</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1792929231000</v>
+        <v>1792936752000</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>¡A sacar el paraguas! Santa cruz amanece con lluvia, frío y complicaciones en el tránsito vehicular - Red Uno</t>
+          <t>Bus de agrupación musical sufre accidente rumbo al trópico de Cochabamba | VIDEO - Red Uno</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -793,62 +793,62 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>-17.781</v>
+        <v>-17.39</v>
       </c>
       <c r="N5" t="n">
-        <v>-63.139</v>
+        <v>-66.16</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Santa Cruz, Santa Cruz</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOY1ZpYktLR3pUQXotUndVR3puUzVHbW1YTzNyUmJvUHB4Q2JmelRvOEdaRldOUm1xLVJnbGR5VWcxTjNEM3ZUYktCUWtVM0hKSjFuRGdpX0JxN0M5MVZBSG1aVURyVWktdmxwbUtRT19ydU5LdzNTZ2Zpb2ozdHlMUUdTVlAyVk4xODBnV0hyTXdVVndyNzV3VC1KMzFnV3lpcFFXSk9MdDZOTWlWakNwT1FnNDh6QVdjazVYZDVVMkdaLU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOVDVzVTJNM2JuQ25sMThEaVZNOUNRd3FGT3RhVnFrZXZ2NDQ1YlluTVdhbVNUQnA1MGNESHRSWVUzbC1kRVh3OTR0emtlTG91cmRWeFJ5dk5zb3p2WFRyMEJUV3FNRnY1WHhRUU9WLTlJcmNyNXJZZFdoM0JoZjNpa3hjUXhMM0xrUDJab2VadkM5RWZYQ3lWZTVDdzg1akxJT2lxcDVNNzI0NG1hejdfdkUyTQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>noticia:bzr7eh</t>
+          <t>noticia:167wlhz</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-25 07:09</t>
+          <t>2026-10-25 07:53</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1792926572000</v>
+        <v>1792929231000</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Alerta naranja por riesgo de desbordes de ríos - El Diario - Bolivia</t>
+          <t>¡A sacar el paraguas! Santa cruz amanece con lluvia, frío y complicaciones en el tránsito vehicular - Red Uno</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>hidrológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -863,74 +863,74 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia; El Mundo Bolivia; FmBolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>-16.169</v>
+        <v>-17.781</v>
       </c>
       <c r="N6" t="n">
-        <v>-68.09</v>
+        <v>-63.139</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>La Paz, La Paz</t>
+          <t>Santa Cruz, Santa Cruz</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Nuestra Señora de La Paz</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNNGZKSDVaZkowWUFGSEUyTWR3d3dsc04waFBLLWUtcVpiTDYzbmNtYTN1RkFLbjAwN3dxT0xZc3pqc3REUXduZVltQ2Fud1BZLTh1bTNiTEJueVUwV0dERS1iUXZqMHd0UnFrQ3E2SFAzbm5lQ1I4U29MaHJFbWFvdVRTeFY4Wl9rSmc3RkpaQ2xwX0oz?oc=5 | https://news.google.com/rss/articles/CBMipwFBVV95cUxPZW00RkxJSklTelNrS2hqczJDWHlwcENFX2lnSEUyTEFPaDFRQ2JvMUcyd3NfYjg0UE9ORGxHRzB4ZDh3U0hQQ1JSQlhsaUY4N3ByMUUxei1SaUZnNlp6T3hsLVdiMGhKaXhsV1FNSUNQMHlvQ19qdk56SEF0d2RXVFctS0VPT25kNGZCRDdvZ2dxU0VoUUJKU0ZBd0ZycFNEZFh0T3ZjOA?oc=5 | https://news.google.com/rss/articles/CBMiwAFBVV95cUxPZm85aHphekQ4U3BZZkp1ZkF6ZVdSUHgtZmltS1FxUUgza1AwcndWWDJZOWctT0RiVmVabmg5SG42NnJWMlJMMnBlYTlYaVdSb09sR0dnVDdpT29faTdiaDUtZElJdlQ3eTdjR2VsWjlta1FOS1U2Vm1vV3JwWkpvbEw1ZUR3akgwQTZnQnVENjJtVkQtVUpKVEJTeWNJSE1CaEFKa2VqMmZXbWk3ekR4ZWpmZ1Z3elFQaWNaNFJuMXA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOY1ZpYktLR3pUQXotUndVR3puUzVHbW1YTzNyUmJvUHB4Q2JmelRvOEdaRldOUm1xLVJnbGR5VWcxTjNEM3ZUYktCUWtVM0hKSjFuRGdpX0JxN0M5MVZBSG1aVURyVWktdmxwbUtRT19ydU5LdzNTZ2Zpb2ozdHlMUUdTVlAyVk4xODBnV0hyTXdVVndyNzV3VC1KMzFnV3lpcFFXSk9MdDZOTWlWakNwT1FnNDh6QVdjazVYZDVVMkdaLU0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>noticia:1fo4ig4</t>
+          <t>noticia:bzr7eh</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-25 01:08</t>
+          <t>2026-10-25 07:09</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1792904880000</v>
+        <v>1792926572000</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
+          <t>Alerta naranja por riesgo de desbordes de ríos - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>hidrológica</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>roja</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -941,41 +941,57 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>diarioelpueblo.com.pe</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
+          <t>El Diario - Bolivia; El Mundo Bolivia; FmBolivia</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>-16.169</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-68.09</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>La Paz, La Paz</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>La Paz</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Nuestra Señora de La Paz</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQcmFrT3dwcEs0X3U2NWxnOGJwNnI2WHdWTGZYbzEyNnJzUWhkbU9TRWhfSlB5UkMwX2gyMmxYUmVNWmxNOVR6V0twRHpFMTVIYjBKbHQ2TXN2d2w5dkFpcWJCcUJMZldaX01sNWtQV2ZJOGpRVzR3NDVIU0pJc1BNVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNNGZKSDVaZkowWUFGSEUyTWR3d3dsc04waFBLLWUtcVpiTDYzbmNtYTN1RkFLbjAwN3dxT0xZc3pqc3REUXduZVltQ2Fud1BZLTh1bTNiTEJueVUwV0dERS1iUXZqMHd0UnFrQ3E2SFAzbm5lQ1I4U29MaHJFbWFvdVRTeFY4Wl9rSmc3RkpaQ2xwX0oz?oc=5 | https://news.google.com/rss/articles/CBMipwFBVV95cUxPZW00RkxJSklTelNrS2hqczJDWHlwcENFX2lnSEUyTEFPaDFRQ2JvMUcyd3NfYjg0UE9ORGxHRzB4ZDh3U0hQQ1JSQlhsaUY4N3ByMUUxei1SaUZnNlp6T3hsLVdiMGhKaXhsV1FNSUNQMHlvQ19qdk56SEF0d2RXVFctS0VPT25kNGZCRDdvZ2dxU0VoUUJKU0ZBd0ZycFNEZFh0T3ZjOA?oc=5 | https://news.google.com/rss/articles/CBMiwAFBVV95cUxPZm85aHphekQ4U3BZZkp1ZkF6ZVdSUHgtZmltS1FxUUgza1AwcndWWDJZOWctT0RiVmVabmg5SG42NnJWMlJMMnBlYTlYaVdSb09sR0dnVDdpT29faTdiaDUtZElJdlQ3eTdjR2VsWjlta1FOS1U2Vm1vV3JwWkpvbEw1ZUR3akgwQTZnQnVENjJtVkQtVUpKVEJTeWNJSE1CaEFKa2VqMmZXbWk3ekR4ZWpmZ1Z3elFQaWNaNFJuMXA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>noticia:r1uot6</t>
+          <t>noticia:1fo4ig4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-24 20:00</t>
+          <t>2026-10-25 01:08</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1792886439000</v>
+        <v>1792904880000</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>vuelco deja heridos en ruta Oruro – Huanuni - La Patria Bolivia</t>
+          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -984,18 +1000,18 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>roja</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1007,53 +1023,37 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>-17.97</v>
-      </c>
-      <c r="N8" t="n">
-        <v>-67.11</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Oruro, Oruro</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Oruro</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Oruro</t>
-        </is>
-      </c>
+          <t>diarioelpueblo.com.pe</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNNDQtMG1KT1lLWW5nem9Jbm5JWDZKNlRWZmFmRlBxWDlDeXlSWnJ5d2NsTlpxa0JIS25oVWVZOC1majZVbWhOVDIxR0dLOFlzY2VpVzVoVk1mQnF3dXVwLUFZVHc1UjlXZzF5T05CY3U0ZldLVkw1VzBTek5zanpjQW1xalltWHNiaXI3dTNR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQcmFrT3dwcEs0X3U2NWxnOGJwNnI2WHdWTGZYbzEyNnJzUWhkbU9TRWhfSlB5UkMwX2gyMmxYUmVNWmxNOVR6V0twRHpFMTVIYjBKbHQ2TXN2d2w5dkFpcWJCcUJMZldaX01sNWtQV2ZJOGpRVzR3NDVIU0pJc1BNVg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>noticia:1ytw450</t>
+          <t>noticia:r1uot6</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-24 18:58</t>
+          <t>2026-10-24 20:00</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1792882686000</v>
+        <v>1792886439000</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
+          <t>vuelco deja heridos en ruta Oruro – Huanuni - La Patria Bolivia</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1062,18 +1062,18 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>roja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1085,37 +1085,53 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>diarioelpueblo.com.pe</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
+          <t>La Patria Bolivia</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>-17.97</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-67.11</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Oruro, Oruro</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNZ1U3bEVuaVdjVE1zSU9lOHJZTVRZLVZaemhldGNnT1JBWDJvbzdvM3paVVNhLUlyWHF2akNuSXJOLXdyTGRuejRlV1FuMjVkTjA3NmdRdmgtRWlUeTFBV1dEMzBvejBxaXZJdUZZWkRVTF9VLU5BcjFGZGFEQ09WWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNNDQtMG1KT1lLWW5nem9Jbm5JWDZKNlRWZmFmRlBxWDlDeXlSWnJ5d2NsTlpxa0JIS25oVWVZOC1majZVbWhOVDIxR0dLOFlzY2VpVzVoVk1mQnF3dXVwLUFZVHc1UjlXZzF5T05CY3U0ZldLVkw1VzBTek5zanpjQW1xalltWHNiaXI3dTNR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>noticia:1g006zh</t>
+          <t>noticia:1ytw450</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-24 17:02</t>
+          <t>2026-10-24 18:58</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1792875752000</v>
+        <v>1792882686000</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a Mayaya deja siete heridos del grupo Los Chicos Fieles - El Potosí</t>
+          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1124,18 +1140,18 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>roja</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1143,57 +1159,41 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>EL DÍA - Noticias de Bolivia para el mundo; El Potosí; La Razón Digital Bolivia; Opinión Bolivia</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
-        <v>-19.58</v>
-      </c>
-      <c r="N10" t="n">
-        <v>-65.75</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Potosí, Potosí</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
+          <t>diarioelpueblo.com.pe</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPTGQwaVBfdG1JdVRMUTN4LVVvN0ppc3dreDJVVllDR3RmX0xpMzB4b0pvVTNSV1B6T0ZEWTdEZkNsRUdSNzhLaC1CWHN5WktNWk1nRWpTdVZiYjI3TlJlX2xlVTI5MjlRU2hiY1gteml4YWVFbDNPSVRBZmtITlQzbmhaUXVmcThRa2xsQTJIOXZuNzlSdm12MEdyOEZHdw?oc=5 | https://news.google.com/rss/articles/CBMizwFBVV95cUxPeGd3VWpCWXJ0YTJIeDJLcktzWG1jdUh0TjFXb01wSTkxbHNXZU94VWNDMkxnTjlJZVdpbkprMEY2NE80RXYyUWxUQXVnbl9lUXR2b28zTEh6cTJLVEQ4TUNja2kzRlhadVBFZFVwV1U2TlhseXZMZ20zZTZiUFpWRjdCOWNBMHU5XzdMV3JqQjV4TEE3bHRMOXR6Nm55eHZUNnFHSDdVRk8zVkY4RkVsUUtUN0JYdkREWGZncmJ3ZWc2T1BuUm1ZLTlfcHVabFE?oc=5 | https://news.google.com/rss/articles/CBMizAFBVV95cUxNYjNxaHg3YllRRTJYdFd1clAtUlROSGlFNVg5eUVZUGJoOEZ4MWM5QU5WQm1YTDc4NXc3SjhWMUw0TkZfSHlMLUQ1bmpTME1Kb1JaM0ExamFHYTd3VlU4MXRWdTZ1bzh1SGYtbGE1a3dBaG93bjg1OGc0S0JfRE43c3dVMVltN0dQQzNhQUNhM0FjVUNRUDRSamlJYlk2dEJpUTBuY2hBcTFucTVRN0ZtYnc5bzdmTV9LQm1uVUxaZS1tUE9IejhBVDRCdU_SAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNZ1U3bEVuaVdjVE1zSU9lOHJZTVRZLVZaemhldGNnT1JBWDJvbzdvM3paVVNhLUlyWHF2akNuSXJOLXdyTGRuejRlV1FuMjVkTjA3NmdRdmgtRWlUeTFBV1dEMzBvejBxaXZJdUZZWkRVTF9VLU5BcjFGZGFEQ09WWQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>noticia:1ukcn97</t>
+          <t>noticia:1g006zh</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-24 13:26</t>
+          <t>2026-10-24 17:02</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1792862794000</v>
+        <v>1792875752000</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Esta es la lista preliminar de los heridos en el accidente del grupo 'Los chicos fieles', el conductor está grave - El Deber</t>
+          <t>Accidente en la carretera a Mayaya deja siete heridos del grupo Los Chicos Fieles - El Potosí</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1213,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1221,46 +1221,62 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>El Deber; Red Uno</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
+          <t>EL DÍA - Noticias de Bolivia para el mundo; El Potosí; La Razón Digital Bolivia; Opinión Bolivia</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>-19.58</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-65.75</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Potosí, Potosí</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Potosí</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Potosí</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOczZKbFd1QzRpak92LXpPWXZXQXJObnBQTG9qRFBlUUV5dThMWXhzckFFUHAyb2thU1JwRmJDSEZfaEdTUXh1bjZvQWpYMGhfUno3cWZ4MGpldEpoQXhzSlVzTm5LLW9OcjB2MWRsdHQ2UlI2SjEtZ085ZTR5Z3pEVmtBTF9lc29Kd0RhaTRUWkM4eGZJNWhBSXZqWmxuNW10dlQwYW9mdzItcWZWTkU0?oc=5 | https://news.google.com/rss/articles/CBMivAFBVV95cUxPczBQcnE2SzFGMXc3b1lsTkNxVWRmS3Vnb01xOTV2WmVva3J2RVlteWpHZ3VJS2dNWGV5NW5FX3ZncnVKTEVDTGpBRndTU1FxeWxtaS1fb1FscGxXMWNXUE9zbHdob1AxVFl1eHB5OU1yUnNoOXJ6U21oVG9PVDA1ak1xQl9hUlB4V0RaQXJqZENGUm8zMUJEY3J0WW5ENE5ObWJLNmpWN0RkSmFJbnZUZGR5UFRPd3QyUFY4WQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPTGQwaVBfdG1JdVRMUTN4LVVvN0ppc3dreDJVVllDR3RmX0xpMzB4b0pvVTNSV1B6T0ZEWTdEZkNsRUdSNzhLaC1CWHN5WktNWk1nRWpTdVZiYjI3TlJlX2xlVTI5MjlRU2hiY1gteml4YWVFbDNPSVRBZmtITlQzbmhaUXVmcThRa2xsQTJIOXZuNzlSdm12MEdyOEZHdw?oc=5 | https://news.google.com/rss/articles/CBMizwFBVV95cUxPeGd3VWpCWXJ0YTJIeDJLcktzWG1jdUh0TjFXb01wSTkxbHNXZU94VWNDMkxnTjlJZVdpbkprMEY2NE80RXYyUWxUQXVnbl9lUXR2b28zTEh6cTJLVEQ4TUNja2kzRlhadVBFZFVwV1U2TlhseXZMZ20zZTZiUFpWRjdCOWNBMHU5XzdMV3JqQjV4TEE3bHRMOXR6Nm55eHZUNnFHSDdVRk8zVkY4RkVsUUtUN0JYdkREWGZncmJ3ZWc2T1BuUm1ZLTlfcHVabFE?oc=5 | https://news.google.com/rss/articles/CBMizAFBVV95cUxNYjNxaHg3YllRRTJYdFd1clAtUlROSGlFNVg5eUVZUGJoOEZ4MWM5QU5WQm1YTDc4NXc3SjhWMUw0TkZfSHlMLUQ1bmpTME1Kb1JaM0ExamFHYTd3VlU4MXRWdTZ1bzh1SGYtbGE1a3dBaG93bjg1OGc0S0JfRE43c3dVMVltN0dQQzNhQUNhM0FjVUNRUDRSamlJYlk2dEJpUTBuY2hBcTFucTVRN0ZtYnc5bzdmTV9LQm1uVUxaZS1tUE9IejhBVDRCdU_SAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>noticia:2avehj</t>
+          <t>noticia:1ukcn97</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-24 12:53</t>
+          <t>2026-10-24 13:26</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1792860813000</v>
+        <v>1792862794000</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sequía en Cochabamba: más de un centenar de cabezas de ganado murieron en el cono sur - Red Uno</t>
+          <t>Esta es la lista preliminar de los heridos en el accidente del grupo 'Los chicos fieles', el conductor está grave - El Deber</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>climatológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -1272,10 +1288,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1283,62 +1299,46 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Red Uno</t>
-        </is>
-      </c>
-      <c r="M12" t="n">
-        <v>-17.39</v>
-      </c>
-      <c r="N12" t="n">
-        <v>-66.16</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Cochabamba, Cochabamba</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
+          <t>El Deber; Red Uno</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOOFQxc2Vzc0QwS19ydC13RkRPZnZQU3JkSTl5U3kzdUdMSldTcm5HVEhWRzZyN19CLUlwcUs4MW03Ui1obVBtdzQ3QWFQc1RKdzh3MXJ5QkpRS2pRNm50V1lVb09ScGJnaVVlemVfZlRsWjdObnRmR1FGMnlMMHAyc2pMandndy10T2twcWx6OFh4UHdvbVlFbllwME9WQ2pQVjNTQzBxeTg5YnF3bDREeHVDYXpObFFIaTZZQWtYUE12cGQ1ZGRhT0syNjVhZWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOczZKbFd1QzRpak92LXpPWXZXQXJObnBQTG9qRFBlUUV5dThMWXhzckFFUHAyb2thU1JwRmJDSEZfaEdTUXh1bjZvQWpYMGhfUno3cWZ4MGpldEpoQXhzSlVzTm5LLW9OcjB2MWRsdHQ2UlI2SjEtZ085ZTR5Z3pEVmtBTF9lc29Kd0RhaTRUWkM4eGZJNWhBSXZqWmxuNW10dlQwYW9mdzItcWZWTkU0?oc=5 | https://news.google.com/rss/articles/CBMivAFBVV95cUxPczBQcnE2SzFGMXc3b1lsTkNxVWRmS3Vnb01xOTV2WmVva3J2RVlteWpHZ3VJS2dNWGV5NW5FX3ZncnVKTEVDTGpBRndTU1FxeWxtaS1fb1FscGxXMWNXUE9zbHdob1AxVFl1eHB5OU1yUnNoOXJ6U21oVG9PVDA1ak1xQl9hUlB4V0RaQXJqZENGUm8zMUJEY3J0WW5ENE5ObWJLNmpWN0RkSmFJbnZUZGR5UFRPd3QyUFY4WQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>noticia:3dv7b0</t>
+          <t>noticia:2avehj</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-24 11:43</t>
+          <t>2026-10-24 12:53</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1792856591000</v>
+        <v>1792860813000</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Accidente en Caranavi: vehículo de Los Chicos Fieles cae a un barranco y deja varios heridos - FmBolivia</t>
+          <t>Sequía en Cochabamba: más de un centenar de cabezas de ganado murieron en el cono sur - Red Uno</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>climatológica</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1361,62 +1361,62 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>FmBolivia; La Patria Bolivia; Red Uno</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>-15.813</v>
+        <v>-17.39</v>
       </c>
       <c r="N13" t="n">
-        <v>-67.46299999999999</v>
+        <v>-66.16</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Caranavi, La Paz</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Caranavi</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNeEFrOEtOMHZxMW42REFPU0x1MG5oQjlBMkJucWRLZ292alBXekJKeURBN3NLTVVadWI0OWF4UGtSVXBzTE01eWFSU1kyMUhNZ04zMWNMaUxnMDBBZ0EwTktXbjlaVTBUUmNqa3AwY19KNTU2LWh5LW9IVElVdTdnaHFPanJPd2FqMUxzaUhXZmVpYU1saGc?oc=5 | https://news.google.com/rss/articles/CBMi2wFBVV95cUxOdTVUZUQxVTdvYTdONDQxVlhUTzBOS2hKLW1rS1NUcmRYRnlCVlhIcHZlSjdsaktkQm5CWkFYa3lDQkxnMlh0b3prX0lha1BtbW1qS1VuYnNiX3FiZkYyNDJDR0tqZ0pKMU5TeC04SXV4UUJOTUlPUTB6ek01bzUxTUsydjZqZzI3S3ZLUnRWSUFUVk44WEpKUl9rbzRLb2IwYl9sLVlrYmt5d2ZHNUtGd3lRNnYzMlhuMkJOZW1XSUl2N1BxZWpHbm5XTDJhRUtnR190QWQ1TDlTUVk?oc=5 | https://news.google.com/rss/articles/CBMizAFBVV95cUxNcE1KaHZyUTJCSElxRU9nVzdhTnczWjJGTEhFMEs0bHp2cUdFeHd3VTB0NmVFcjdEN1dsZDZLY2k1ZFFUWkhKV19PU3V2czNyamh1ZE9YajVSVF8xczF6OFhZcWFvYV9EcWg4ZDNCb2p3enhXbFpRYnJMdGdaTXNrWUZSYVhKNTVicWlCLTJ5OE05Z1BvNEx1eEloUk5qTGN3ZHNzbzZWSVljbnRmSERJUWdxRDc0MjJxMGtycWJaaVhXQUUxVUlaWVZLOWE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOOFQxc2Vzc0QwS19ydC13RkRPZnZQU3JkSTl5U3kzdUdMSldTcm5HVEhWRzZyN19CLUlwcUs4MW03Ui1obVBtdzQ3QWFQc1RKdzh3MXJ5QkpRS2pRNm50V1lVb09ScGJnaVVlemVfZlRsWjdObnRmR1FGMnlMMHAyc2pMandndy10T2twcWx6OFh4UHdvbVlFbllwME9WQ2pQVjNTQzBxeTg5YnF3bDREeHVDYXpObFFIaTZZQWtYUE12cGQ1ZGRhT0syNjVhZWs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>clima:Potosí:2026-10-24:viento:1</t>
+          <t>noticia:3dv7b0</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-24 10:55</t>
+          <t>2026-10-24 11:43</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1792853727284</v>
+        <v>1792856591000</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Potosí 2026-10-24: 60.5 km/h de ráfagas pronosticadas</t>
+          <t>Accidente en Caranavi: vehículo de Los Chicos Fieles cae a un barranco y deja varios heridos - FmBolivia</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1431,7 +1431,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1439,57 +1439,57 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>FmBolivia; La Patria Bolivia; Red Uno</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>-19.58</v>
+        <v>-15.813</v>
       </c>
       <c r="N14" t="n">
-        <v>-65.75</v>
+        <v>-67.46299999999999</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Caranavi, La Paz</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Caranavi</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNeEFrOEtOMHZxMW42REFPU0x1MG5oQjlBMkJucWRLZ292alBXekJKeURBN3NLTVVadWI0OWF4UGtSVXBzTE01eWFSU1kyMUhNZ04zMWNMaUxnMDBBZ0EwTktXbjlaVTBUUmNqa3AwY19KNTU2LWh5LW9IVElVdTdnaHFPanJPd2FqMUxzaUhXZmVpYU1saGc?oc=5 | https://news.google.com/rss/articles/CBMi2wFBVV95cUxOdTVUZUQxVTdvYTdONDQxVlhUTzBOS2hKLW1rS1NUcmRYRnlCVlhIcHZlSjdsaktkQm5CWkFYa3lDQkxnMlh0b3prX0lha1BtbW1qS1VuYnNiX3FiZkYyNDJDR0tqZ0pKMU5TeC04SXV4UUJOTUlPUTB6ek01bzUxTUsydjZqZzI3S3ZLUnRWSUFUVk44WEpKUl9rbzRLb2IwYl9sLVlrYmt5d2ZHNUtGd3lRNnYzMlhuMkJOZW1XSUl2N1BxZWpHbm5XTDJhRUtnR190QWQ1TDlTUVk?oc=5 | https://news.google.com/rss/articles/CBMizAFBVV95cUxNcE1KaHZyUTJCSElxRU9nVzdhTnczWjJGTEhFMEs0bHp2cUdFeHd3VTB0NmVFcjdEN1dsZDZLY2k1ZFFUWkhKV19PU3V2czNyamh1ZE9YajVSVF8xczF6OFhZcWFvYV9EcWg4ZDNCb2p3enhXbFpRYnJMdGdaTXNrWUZSYVhKNTVicWlCLTJ5OE05Z1BvNEx1eEloUk5qTGN3ZHNzbzZWSVljbnRmSERJUWdxRDc0MjJxMGtycWJaaVhXQUUxVUlaWVZLOWE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>noticia:1ax0bpy</t>
+          <t>clima:Potosí:2026-10-24:viento:1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-24 10:32</t>
+          <t>2026-10-24 10:55</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1792852364000</v>
+        <v>1792853727284</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Creció el Bermejo tras la tormenta: así está el puerto de chalanas en este momento - Que Pasa Salta</t>
+          <t>Potosí 2026-10-24: 60.5 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1498,11 +1498,11 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1521,58 +1521,58 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Que Pasa Salta</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>-22.721</v>
+        <v>-19.58</v>
       </c>
       <c r="N15" t="n">
-        <v>-64.32599999999999</v>
+        <v>-65.75</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Bermejo, Tarija</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tarija</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Bermejo</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVld9IBfkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVldw?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>gdacs:WF1033142:0</t>
+          <t>noticia:1ax0bpy</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-24 07:06</t>
+          <t>2026-10-24 10:32</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1792839995000</v>
+        <v>1792852364000</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Green forest fire notification in Bolivia</t>
+          <t>Creció el Bermejo tras la tormenta: así está el puerto de chalanas en este momento - Que Pasa Salta</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1599,58 +1599,58 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>GDACS</t>
+          <t>Que Pasa Salta</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>-13.06332</v>
+        <v>-22.721</v>
       </c>
       <c r="N16" t="n">
-        <v>-67.66426</v>
+        <v>-64.32599999999999</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Bermejo, Tarija</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Tarija</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Ixiamas</t>
+          <t>Bermejo</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>http://www.gdacs.org/report.aspx?eventtype=WF&amp;eventid=1033142</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVld9IBfkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVldw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>noticia:1shhqva</t>
+          <t>gdacs:WF1033142:0</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-24 06:33</t>
+          <t>2026-10-24 07:06</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1792838034000</v>
+        <v>1792839995000</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
+          <t>Green forest fire notification in Bolivia</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1673,70 +1673,70 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>GDACS</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>-17.97</v>
+        <v>-13.06332</v>
       </c>
       <c r="N17" t="n">
-        <v>-67.11</v>
+        <v>-67.66426</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Ixiamas</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQYzB6N082XzFRRnVtcDVmUkYyWjcxUzV2Z3Frd1I0WDNXSnZtY0QzOU1PUkNLMktVT1Vra2FSeXhxZDRuOFZYZjFwejl6ejJTbWY2MGJuSGN3ZHdrdG5JUkgzSXBkbDYtaHlackY3OVFuNWdLcFNpdWNHRU9vNGdoVWx2ODFVdzJXYUxnM0tUcjJvZmc?oc=5 | https://news.google.com/rss/articles/CBMikAFBVV95cUxQS2FPaHd3UnFBRjRoa0lKUm1MNUQ5S00zN1RJZE5fWlVUQnhiY0lLcFRkY2JZak1mZ0c2WEVMVUNJVUJTMGFLNHg4S2ZKNTRqLXJHM09ET19hX1pZeTQwUkdEc2huTHVpcno2QTRZbnhralVRWXozcWc1a2pHUEpBeTV1cWgzTWRwaDEweURKeVE?oc=5</t>
+          <t>http://www.gdacs.org/report.aspx?eventtype=WF&amp;eventid=1033142</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>clima:Potosí:2026-10-25:viento:1</t>
+          <t>noticia:1shhqva</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-24 02:55</t>
+          <t>2026-10-24 06:33</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1792824927736</v>
+        <v>1792838034000</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Potosí 2026-10-25: 60.5 km/h de ráfagas pronosticadas</t>
+          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1751,62 +1751,62 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>-19.58</v>
+        <v>-17.97</v>
       </c>
       <c r="N18" t="n">
-        <v>-65.75</v>
+        <v>-67.11</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Oruro, Oruro</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Oruro</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Oruro</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQYzB6N082XzFRRnVtcDVmUkYyWjcxUzV2Z3Frd1I0WDNXSnZtY0QzOU1PUkNLMktVT1Vra2FSeXhxZDRuOFZYZjFwejl6ejJTbWY2MGJuSGN3ZHdrdG5JUkgzSXBkbDYtaHlackY3OVFuNWdLcFNpdWNHRU9vNGdoVWx2ODFVdzJXYUxnM0tUcjJvZmc?oc=5 | https://news.google.com/rss/articles/CBMikAFBVV95cUxQS2FPaHd3UnFBRjRoa0lKUm1MNUQ5S00zN1RJZE5fWlVUQnhiY0lLcFRkY2JZak1mZ0c2WEVMVUNJVUJTMGFLNHg4S2ZKNTRqLXJHM09ET19hX1pZeTQwUkdEc2huTHVpcno2QTRZbnhralVRWXozcWc1a2pHUEpBeTV1cWgzTWRwaDEweURKeVE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>noticia:1uil931</t>
+          <t>clima:Potosí:2026-10-25:viento:1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-23 22:49</t>
+          <t>2026-10-24 02:55</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1792810149000</v>
+        <v>1792824927736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Accidente de tránsito en la ruta hacia Alto Beni deja varios heridos - El Deber</t>
+          <t>Potosí 2026-10-25: 60.5 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1821,7 +1821,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1829,62 +1829,62 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>El Deber</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>-15.578</v>
+        <v>-19.58</v>
       </c>
       <c r="N19" t="n">
-        <v>-67.44</v>
+        <v>-65.75</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Alto Beni, La Paz</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Alto Beni</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQakFJRmx3RlJEMkVHU0pxWXZ2ZU1ib04tZy1yeTB2OGhrYk9CU3pMaDVpRThNZktZMS14UzA2Y1VIcEQtZDg3cEU2SmlzQnBmUVVvM0ZNYzZWNExWUXQ3aHpnd3lqOHFVV3pNbDRLS1NQNGtwb2RjSFpleHJkOG5zSXVtWjVIS1dLejNybktRWTJVZXh3WkFUQVE5T2tMdFdn?oc=5 | https://news.google.com/rss/articles/CBMilwFBVV95cUxQMF9BNnUzLURKNGRMUUJ1VXVRSXNnMlBsQnVXOG0tRlFtY3pvRDNPQmNJMWN2RzJVaWdoWndmcHFnTkZFZnJxRkZtMThYYWlwN09ueUgtei1pSE1hZ2FtSzN6elY4VXJHbzFxdll0eWh0ZkxwQkQ1SDZ5b0E3MlVENGZEWGZHUGlwVG4wd2x3OFNEMVpibnFr?oc=5 | https://news.google.com/rss/articles/CBMimgFBVV95cUxNbmwzSnd6c2tFMXBWY0tiemJqRm5CNllOT2p1U0FhdW5QNGFBVXlSZVM1ak5jNGZvcXNVaUQzN3ZQQTlPbmVjQ2Y5RFl2dWVLeUN5NUFodDF0alEyZWlmOHFZWkVVbjdQbkl3ZWtmS25wQWM2TmRZZDBGM2xlS0ZhUzAweXRmcmhVWGY5dV9CUnFBNGtWZHZDSWVB?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-24:viento:1</t>
+          <t>noticia:1uil931</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-23 20:55</t>
+          <t>2026-10-23 22:49</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1792803329663</v>
+        <v>1792810149000</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-24: 78.1 km/h de ráfagas pronosticadas</t>
+          <t>Accidente de tránsito en la ruta hacia Alto Beni deja varios heridos - El Deber</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1899,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1907,57 +1907,57 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>El Deber</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>-17.78</v>
+        <v>-15.578</v>
       </c>
       <c r="N20" t="n">
-        <v>-63.18</v>
+        <v>-67.44</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Alto Beni, La Paz</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Alto Beni</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQakFJRmx3RlJEMkVHU0pxWXZ2ZU1ib04tZy1yeTB2OGhrYk9CU3pMaDVpRThNZktZMS14UzA2Y1VIcEQtZDg3cEU2SmlzQnBmUVVvM0ZNYzZWNExWUXQ3aHpnd3lqOHFVV3pNbDRLS1NQNGtwb2RjSFpleHJkOG5zSXVtWjVIS1dLejNybktRWTJVZXh3WkFUQVE5T2tMdFdn?oc=5 | https://news.google.com/rss/articles/CBMilwFBVV95cUxQMF9BNnUzLURKNGRMUUJ1VXVRSXNnMlBsQnVXOG0tRlFtY3pvRDNPQmNJMWN2RzJVaWdoWndmcHFnTkZFZnJxRkZtMThYYWlwN09ueUgtei1pSE1hZ2FtSzN6elY4VXJHbzFxdll0eWh0ZkxwQkQ1SDZ5b0E3MlVENGZEWGZHUGlwVG4wd2x3OFNEMVpibnFr?oc=5 | https://news.google.com/rss/articles/CBMimgFBVV95cUxNbmwzSnd6c2tFMXBWY0tiemJqRm5CNllOT2p1U0FhdW5QNGFBVXlSZVM1ak5jNGZvcXNVaUQzN3ZQQTlPbmVjQ2Y5RFl2dWVLeUN5NUFodDF0alEyZWlmOHFZWkVVbjdQbkl3ZWtmS25wQWM2TmRZZDBGM2xlS0ZhUzAweXRmcmhVWGY5dV9CUnFBNGtWZHZDSWVB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>noticia:rabz5p</t>
+          <t>clima:Santa Cruz:2026-10-24:viento:1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-23 20:44</t>
+          <t>2026-10-23 20:55</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1792802686000</v>
+        <v>1792803329663</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tome previsiones: se pronostican lluvias y ambiente caluroso para este fin de semana en Cochabamba - Red Uno</t>
+          <t>Santa Cruz 2026-10-24: 78.1 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1966,11 +1966,11 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -1989,70 +1989,70 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>-17.39</v>
+        <v>-17.78</v>
       </c>
       <c r="N21" t="n">
-        <v>-66.16</v>
+        <v>-63.18</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Cochabamba, Cochabamba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTlU5NVFpY1RheTN5ZE1IbG5VYTh2Sk5hZHpHeWI3LVdnSFg2cFJFdnBCVkxiUjNKcUgyUW16SWxpMXFkMHdad2xFN043bklJeG1iQ0V1V3hBZk1Ga3NscjdPVWUySmt4bDNTdWlmSUdOMmNlZ2hkSWZFMmk4VGs0Nm9TcnRCTDhINmtnQU9zZDBUY05HcWpxN3FOX3N1dmVJblE0MGc5di1Ma1N2dGNxOUtoV1MzNnl1OXpRaTZ2UGxMc3RDWndubHVQNUd0eVROMGR2OGxVemtOaEc4bTNRaA?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>noticia:1jfk053</t>
+          <t>noticia:rabz5p</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-23 19:08</t>
+          <t>2026-10-23 20:44</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1792796931000</v>
+        <v>1792802686000</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sequía en Pasorapa: el ganado muere por falta de agua y alistan declaratoria de desastre - Red Uno</t>
+          <t>Tome previsiones: se pronostican lluvias y ambiente caluroso para este fin de semana en Cochabamba - Red Uno</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>climatológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -2071,14 +2071,14 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>-18.38</v>
+        <v>-17.39</v>
       </c>
       <c r="N22" t="n">
-        <v>-64.649</v>
+        <v>-66.16</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Pasorapa, Cochabamba</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2088,49 +2088,49 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Pasorapa</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNQVhTWE8zdE1BQ3lueWJPeV9wUDNsSmJpS0NJTWppMUY4QmlQSUFHVjRORmtrVHQ3MHB0T1pyS25PamxnY0hBQUtzOVRvSUNaUkdGb1RWSGl4dFA4Z3VINVpQTk1pZUpDdUIyUU5hZS1oNGhBa1RWcFhScVMwVTFrVlJaOFQ4OWFqRWVUZ051bHVJTlMxRTBhRFVLUEV2dTZFdDgtRkxJM3VvN3YzUWJfVk41ZWR5U1JoNmx0WFFkMmNTWGVleGNIQlNxWUJzdHIxSWtz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTlU5NVFpY1RheTN5ZE1IbG5VYTh2Sk5hZHpHeWI3LVdnSFg2cFJFdnBCVkxiUjNKcUgyUW16SWxpMXFkMHdad2xFN043bklJeG1iQ0V1V3hBZk1Ga3NscjdPVWUySmt4bDNTdWlmSUdOMmNlZ2hkSWZFMmk4VGs0Nm9TcnRCTDhINmtnQU9zZDBUY05HcWpxN3FOX3N1dmVJblE0MGc5di1Ma1N2dGNxOUtoV1MzNnl1OXpRaTZ2UGxMc3RDWndubHVQNUd0eVROMGR2OGxVemtOaEc4bTNRaA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>noticia:ix3l8o</t>
+          <t>noticia:1jfk053</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-23 18:25</t>
+          <t>2026-10-23 19:08</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1792794310000</v>
+        <v>1792796931000</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Oruro evalúa suspender clases presenciales por más de 200 casos de Coxsackie - Visión 360</t>
+          <t>Sequía en Pasorapa: el ganado muere por falta de agua y alistan declaratoria de desastre - Red Uno</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>climatológica</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2141,77 +2141,77 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Red Uno; Visión 360</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>-17.97</v>
+        <v>-18.38</v>
       </c>
       <c r="N23" t="n">
-        <v>-67.11</v>
+        <v>-64.649</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>Pasorapa, Cochabamba</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Pasorapa</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0c9IBywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0cw?oc=5 | https://news.google.com/rss/articles/CBMiywFBVV95cUxNMFdHaVpKRmMyOENDYm16UXJPenVSQnpmTE94bDc4UFhqakluMUdvZjAwamUxT3BVWUpJQm8xVHBWengxQmhWM1hjU3d2YXFrLXpVU2VrZDJiMXZLMlQ5bGxGOHFETFhYM0s2RjlUTlhkd0g2eXQweDFHaTlKNGNMUlJfOWg2a0JjTklXUWZKc1BmUXZuZFZ2MF9fV2lEYUY4LXNiNmk3cF9FNjVtTl9GWFotT2ltS0xXTnM1dENvSU9kbFRMalFrYVdXOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNQVhTWE8zdE1BQ3lueWJPeV9wUDNsSmJpS0NJTWppMUY4QmlQSUFHVjRORmtrVHQ3MHB0T1pyS25PamxnY0hBQUtzOVRvSUNaUkdGb1RWSGl4dFA4Z3VINVpQTk1pZUpDdUIyUU5hZS1oNGhBa1RWcFhScVMwVTFrVlJaOFQ4OWFqRWVUZ051bHVJTlMxRTBhRFVLUEV2dTZFdDgtRkxJM3VvN3YzUWJfVk41ZWR5U1JoNmx0WFFkMmNTWGVleGNIQlNxWUJzdHIxSWtz?oc=5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>noticia:1xqv9m7</t>
+          <t>noticia:ix3l8o</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-23 18:09</t>
+          <t>2026-10-23 18:25</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1792793370000</v>
+        <v>1792794310000</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tres heridos en tremendo choque cerca de Oncativo - El Diario del centro del país</t>
+          <t>Oruro evalúa suspender clases presenciales por más de 200 casos de Coxsackie - Visión 360</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -2219,61 +2219,77 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>El Diario del centro del país</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
+          <t>Red Uno; Visión 360</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>-17.97</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-67.11</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Oruro, Oruro</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZERhbTJMQUJVb3hmZFlSZmRGZkdBLWdFTGJVQzdqZkE4aGhhWmdQZ2JDRW1ndkJLWU90VTZ6Ti1JOUZzcFZfcE1zbkRHU1B3YTF4UkVzdllFa1p3SUlObURGamF0Vm9kc3dPLTZVWFJ4NWZZQmlySElPNHhZTnRGNGNZUWw2ZlI1eVBEQkNGNEhLWTNiLWJLUS0xYjA0UWRhc0d6bVN4aVVLSVdsQWlpMUZYdWw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0c9IBywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0cw?oc=5 | https://news.google.com/rss/articles/CBMiywFBVV95cUxNMFdHaVpKRmMyOENDYm16UXJPenVSQnpmTE94bDc4UFhqakluMUdvZjAwamUxT3BVWUpJQm8xVHBWengxQmhWM1hjU3d2YXFrLXpVU2VrZDJiMXZLMlQ5bGxGOHFETFhYM0s2RjlUTlhkd0g2eXQweDFHaTlKNGNMUlJfOWg2a0JjTklXUWZKc1BmUXZuZFZ2MF9fV2lEYUY4LXNiNmk3cF9FNjVtTl9GWFotT2ltS0xXTnM1dENvSU9kbFRMalFrYVdXOA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>noticia:1itd1r7</t>
+          <t>noticia:1xqv9m7</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-23 15:01</t>
+          <t>2026-10-23 18:09</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1792782098000</v>
+        <v>1792793370000</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Intensa lluvia y granizada en La Paz inundan vías y elevan el nivel de los ríos - eju.tv</t>
+          <t>Tres heridos en tremendo choque cerca de Oncativo - El Diario del centro del país</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2285,73 +2301,57 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>eju.tv</t>
-        </is>
-      </c>
-      <c r="M25" t="n">
-        <v>-16.169</v>
-      </c>
-      <c r="N25" t="n">
-        <v>-68.09</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>La Paz, La Paz</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>La Paz</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>Nuestra Señora de La Paz</t>
-        </is>
-      </c>
+          <t>El Diario del centro del país</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNWU9QWElKQXEyN3UxVm4xbzJzbEJ1TU1NTHZlRUp6YndmeU9GQnJKcTluVEJ2ZHQ5cGp3aWhlMUd5ektWQlBpUVNmZnZuRnJwMXlydzAzX0FBVnY5UDMzQTBkWVRNRUNJSlRvX3MyQVhMcEhIMW9WSUpXckVSd0RJWk1KMFBKWmJNU3diQVlEN1Y5aVV6eVBaZXpOMnFIWWxaMlRlY0ZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZERhbTJMQUJVb3hmZFlSZmRGZkdBLWdFTGJVQzdqZkE4aGhhWmdQZ2JDRW1ndkJLWU90VTZ6Ti1JOUZzcFZfcE1zbkRHU1B3YTF4UkVzdllFa1p3SUlObURGamF0Vm9kc3dPLTZVWFJ4NWZZQmlySElPNHhZTnRGNGNZUWw2ZlI1eVBEQkNGNEhLWTNiLWJLUS0xYjA0UWRhc0d6bVN4aVVLSVdsQWlpMUZYdWw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>noticia:51709n</t>
+          <t>noticia:1itd1r7</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-23 13:38</t>
+          <t>2026-10-23 15:01</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1792777139000</v>
+        <v>1792782098000</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - eju.tv</t>
+          <t>Intensa lluvia y granizada en La Paz inundan vías y elevan el nivel de los ríos - eju.tv</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2359,77 +2359,77 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Red Uno; eju.tv</t>
+          <t>eju.tv</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>-17.764</v>
+        <v>-16.169</v>
       </c>
       <c r="N26" t="n">
-        <v>-62.903</v>
+        <v>-68.09</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Cotoca, Santa Cruz</t>
+          <t>La Paz, La Paz</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Cotoca</t>
+          <t>Nuestra Señora de La Paz</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPcjZTSmprRGVoNlRqQmdBTE5VM3pRQ1ZFakFUbzVyMUhiaDVkT0liaG9UNEZXekV6bWsycUk4X1JCSEY5RjhNVlZaTk9ULUFuZkY3NnZuWmZ1a19leUhFdlIyQV9kLWxlSkxfeXFhcFRTZjZ2YkpQQlJ1dkNLMDBjaGZ4SkhyQ0RfcnhKSEg5WURCQVQwbENYTHEzUzJSaUEzMGo2bWdyS3lsM016LXc?oc=5 | https://news.google.com/rss/articles/CBMi0AFBVV95cUxOVGY3YVRLWWxYM0IycjF4dlNUeUhqZG90Yng4aWhmN3A5ai02WENWYnF4bWpoZHFKMGc1X0JPRHdRRVZfSlA4UmZFa2kxYkNIS3ZtQ1NvNlNCME51eVZTRkRKSUQ5MmRoaWl5Tkt5NHpPUEFwemN2YTV1djFwdHlqQnFqRHNPenhYcTlsanJPcXhpOVV1NmFBUXZyazQ2MkUzM0dSZy02ZllxTGtjcl9ldzdHSktTRlVaalZJc1pubUNQMWFTbzVEOUJ1UmhCdEJt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNWU9QWElKQXEyN3UxVm4xbzJzbEJ1TU1NTHZlRUp6YndmeU9GQnJKcTluVEJ2ZHQ5cGp3aWhlMUd5ektWQlBpUVNmZnZuRnJwMXlydzAzX0FBVnY5UDMzQTBkWVRNRUNJSlRvX3MyQVhMcEhIMW9WSUpXckVSd0RJWk1KMFBKWmJNU3diQVlEN1Y5aVV6eVBaZXpOMnFIWWxaMlRlY0ZB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>noticia:11rddql</t>
+          <t>noticia:51709n</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-23 13:22</t>
+          <t>2026-10-23 13:38</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1792776139000</v>
+        <v>1792777139000</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Intensifican acciones preventivas contra el dengue en Caranavi - El Diario - Bolivia</t>
+          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - eju.tv</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2437,77 +2437,77 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>Red Uno; eju.tv</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>-15.813</v>
+        <v>-17.764</v>
       </c>
       <c r="N27" t="n">
-        <v>-67.46299999999999</v>
+        <v>-62.903</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Caranavi, La Paz</t>
+          <t>Cotoca, Santa Cruz</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>Caranavi</t>
+          <t>Cotoca</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOMjhSeDJBek5iaFhDcnFzX1lKelgwZmUwLTJnbEhMdDRMelUxNks5Ti1pRHh3dDhTcC1YZEdqM3FJOGdqVHRvcXVhRlpCQzVDTEZMUFBkV1NrYVQ2LXRqTTBhcGRQc21CQ0VabzZaNExXb1BjTzJ2Uk5BcFF0VG5XOFNRa3lqUWlJSnRFUUVXYnNpbXB0LVVmSXVWSzJxcmVpdVVxUC1KOUhTQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPcjZTSmprRGVoNlRqQmdBTE5VM3pRQ1ZFakFUbzVyMUhiaDVkT0liaG9UNEZXekV6bWsycUk4X1JCSEY5RjhNVlZaTk9ULUFuZkY3NnZuWmZ1a19leUhFdlIyQV9kLWxlSkxfeXFhcFRTZjZ2YkpQQlJ1dkNLMDBjaGZ4SkhyQ0RfcnhKSEg5WURCQVQwbENYTHEzUzJSaUEzMGo2bWdyS3lsM016LXc?oc=5 | https://news.google.com/rss/articles/CBMi0AFBVV95cUxOVGY3YVRLWWxYM0IycjF4dlNUeUhqZG90Yng4aWhmN3A5ai02WENWYnF4bWpoZHFKMGc1X0JPRHdRRVZfSlA4UmZFa2kxYkNIS3ZtQ1NvNlNCME51eVZTRkRKSUQ5MmRoaWl5Tkt5NHpPUEFwemN2YTV1djFwdHlqQnFqRHNPenhYcTlsanJPcXhpOVV1NmFBUXZyazQ2MkUzM0dSZy02ZllxTGtjcl9ldzdHSktTRlVaalZJc1pubUNQMWFTbzVEOUJ1UmhCdEJt?oc=5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>noticia:fcm3nx</t>
+          <t>noticia:11rddql</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-23 12:58</t>
+          <t>2026-10-23 13:22</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1792774699000</v>
+        <v>1792776139000</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>[VIDEO] Así fue el accidente de moto que dejó un adolescente fallecido y un hombre gravemente herido - Red Uno</t>
+          <t>Intensifican acciones preventivas contra el dengue en Caranavi - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2519,57 +2519,73 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Red Uno</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
+          <t>El Diario - Bolivia</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>-15.813</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-67.46299999999999</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Caranavi, La Paz</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>La Paz</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Caranavi</t>
+        </is>
+      </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOSmJMazhUemNfRHpWcDBoTVFZMUpwdlVKVUtvUXZNTGRRRHlwLW5KNmNhcmFnd1czbi1yalhFMnpSS1dmUE9jVzNlOS1kMWZtRzBHZ2EtcDRDdU5Gc2JUQVIwM2xPa2lZVmswRi1SUFVPcm8xcHlGN3F2UThTSDdKMDNyYnJmVkcxazNLLVBLOWFYM09FVUpmVnN5RVhpSVo2V1VCVmFwQ1gzTmRUWVp2aXMwcmxHRS1GV2p3NTBtR2RzM2wwVHUzaGJkRXJYbHdvaDlhWm5YMTk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOMjhSeDJBek5iaFhDcnFzX1lKelgwZmUwLTJnbEhMdDRMelUxNks5Ti1pRHh3dDhTcC1YZEdqM3FJOGdqVHRvcXVhRlpCQzVDTEZMUFBkV1NrYVQ2LXRqTTBhcGRQc21CQ0VabzZaNExXb1BjTzJ2Uk5BcFF0VG5XOFNRa3lqUWlJSnRFUUVXYnNpbXB0LVVmSXVWSzJxcmVpdVVxUC1KOUhTQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>noticia:1cjx1qd</t>
+          <t>noticia:fcm3nx</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-23 12:39</t>
+          <t>2026-10-23 12:58</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1792773575000</v>
+        <v>1792774699000</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Más de 60 municipios en La Paz sufren falta de lluvias - La Patria Bolivia</t>
+          <t>[VIDEO] Así fue el accidente de moto que dejó un adolescente fallecido y un hombre gravemente herido - Red Uno</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2581,53 +2597,37 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
-        </is>
-      </c>
-      <c r="M29" t="n">
-        <v>-16.169</v>
-      </c>
-      <c r="N29" t="n">
-        <v>-68.09</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>La Paz, La Paz</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>La Paz</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>Nuestra Señora de La Paz</t>
-        </is>
-      </c>
+          <t>Red Uno</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE52Qi03Z1J6OS1CR2liRVZ0VlhCcmVQWFV6RUdGNXdrbzZRNXFjTWRaRnc1b3VoV0xaY3RIdncxNlNnYkxyUXo5MTlJWmMwWDNSMDE4ZHI2VkpWajFPaUF2SmRVYkk2eDZYQ1RfUU9ieENrZG9UVVFiaXZSeGI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOSmJMazhUemNfRHpWcDBoTVFZMUpwdlVKVUtvUXZNTGRRRHlwLW5KNmNhcmFnd1czbi1yalhFMnpSS1dmUE9jVzNlOS1kMWZtRzBHZ2EtcDRDdU5Gc2JUQVIwM2xPa2lZVmswRi1SUFVPcm8xcHlGN3F2UThTSDdKMDNyYnJmVkcxazNLLVBLOWFYM09FVUpmVnN5RVhpSVo2V1VCVmFwQ1gzTmRUWVp2aXMwcmxHRS1GV2p3NTBtR2RzM2wwVHUzaGJkRXJYbHdvaDlhWm5YMTk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>clima:Sucre:2026-10-23:viento:1</t>
+          <t>noticia:1cjx1qd</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-23 06:55</t>
+          <t>2026-10-23 12:39</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1792752927735</v>
+        <v>1792773575000</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sucre 2026-10-23: 66.2 km/h de ráfagas pronosticadas</t>
+          <t>Más de 60 municipios en La Paz sufren falta de lluvias - La Patria Bolivia</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2636,11 +2636,11 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -2659,40 +2659,40 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>La Patria Bolivia</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>-19.03</v>
+        <v>-16.169</v>
       </c>
       <c r="N30" t="n">
-        <v>-65.26000000000001</v>
+        <v>-68.09</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>La Paz, La Paz</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Chuquisaca</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Nuestra Señora de La Paz</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE52Qi03Z1J6OS1CR2liRVZ0VlhCcmVQWFV6RUdGNXdrbzZRNXFjTWRaRnc1b3VoV0xaY3RIdncxNlNnYkxyUXo5MTlJWmMwWDNSMDE4ZHI2VkpWajFPaUF2SmRVYkk2eDZYQ1RfUU9ieENrZG9UVVFiaXZSeGI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-24:viento:2</t>
+          <t>clima:Sucre:2026-10-23:viento:1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2701,11 +2701,11 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1792752927734</v>
+        <v>1792752927735</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-24: 85 km/h de ráfagas pronosticadas</t>
+          <t>Sucre 2026-10-23: 66.2 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2714,11 +2714,11 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -2741,24 +2741,24 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>-17.78</v>
+        <v>-19.03</v>
       </c>
       <c r="N31" t="n">
-        <v>-63.18</v>
+        <v>-65.26000000000001</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Chuquisaca</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2770,33 +2770,33 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>usgs:us6000u49c</t>
+          <t>clima:Santa Cruz:2026-10-24:viento:2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-22 22:45</t>
+          <t>2026-10-23 06:55</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1792723541183</v>
+        <v>1792752927734</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sismo M 4.5 - 58 km SW of Atocha, Bolivia</t>
+          <t>Santa Cruz 2026-10-24: 85 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>geológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -2815,58 +2815,58 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>USGS</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>-21.3469</v>
+        <v>-17.78</v>
       </c>
       <c r="N32" t="n">
-        <v>-66.5795</v>
+        <v>-63.18</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>58 km SW of Atocha, Bolivia</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>San Pablo</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>https://earthquake.usgs.gov/earthquakes/eventpage/us6000u49c</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-22:viento:1</t>
+          <t>usgs:us6000u49c</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-22 21:55</t>
+          <t>2026-10-22 22:45</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1792720528712</v>
+        <v>1792723541183</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-22: 67.7 km/h de ráfagas pronosticadas</t>
+          <t>Sismo M 4.5 - 58 km SW of Atocha, Bolivia</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>geológica</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -2893,40 +2893,40 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>USGS</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>-17.78</v>
+        <v>-21.3469</v>
       </c>
       <c r="N33" t="n">
-        <v>-63.18</v>
+        <v>-66.5795</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>58 km SW of Atocha, Bolivia</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>San Pablo</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://earthquake.usgs.gov/earthquakes/eventpage/us6000u49c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-23:viento:2</t>
+          <t>clima:Santa Cruz:2026-10-22:viento:1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-23: 83.9 km/h de ráfagas pronosticadas</t>
+          <t>Santa Cruz 2026-10-22: 67.7 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2948,11 +2948,11 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -3004,33 +3004,33 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>noticia:1hhvre7</t>
+          <t>clima:Santa Cruz:2026-10-23:viento:2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-22 19:36</t>
+          <t>2026-10-22 21:55</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1792712202000</v>
+        <v>1792720528712</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Virgen de Cotoca: Controlan incendio en depósito de materiales plásticos - El Mundo Bolivia</t>
+          <t>Santa Cruz 2026-10-23: 83.9 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -3049,18 +3049,18 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>El Mundo Bolivia</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>-17.764</v>
+        <v>-17.78</v>
       </c>
       <c r="N35" t="n">
-        <v>-62.903</v>
+        <v>-63.18</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Cotoca, Santa Cruz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -3070,32 +3070,32 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>Cotoca</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcDF6VE5FNzRaWGRuUzFKeXhnZ21DZTRaaEtrVEJEa1Z3ejg2VG1ONG1ENmlDWlkyVjlkQkJwS2F1XzBGMFQwSHd4OEwxTW1PbHdGcUh1ckV6SGpDd2hiN0dkeUVTcnFXT3RjOU1kLXZtVVdZY2hkZS1pcVpVUFhnRktqcHY5UnBrY0xUMDRETjl6N0pXT3A5amxhMA?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>noticia:bksnde</t>
+          <t>noticia:1hhvre7</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-22 17:01</t>
+          <t>2026-10-22 19:36</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1792702880000</v>
+        <v>1792712202000</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Reportan un incendio cerca de la carretera a Cotoca - eju.tv</t>
+          <t>Virgen de Cotoca: Controlan incendio en depósito de materiales plásticos - El Mundo Bolivia</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>eju.tv</t>
+          <t>El Mundo Bolivia</t>
         </is>
       </c>
       <c r="M36" t="n">
@@ -3153,27 +3153,27 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPNGtpbnBfRnRBalVudnBlZHdVQ0ZSaUplZmtvTGE0aTQzdkxWS3d4My1EZEJ1UE9FNFQ3RmpyZGVsbS1qNEM1QUVFRFAxM2pYT1VqQzRuVjRtZnVNUGlKODNMc0F1a3l6TUpuQmtlUWNlVTVEWWU5ZGZtQm5LWUp3Sg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcDF6VE5FNzRaWGRuUzFKeXhnZ21DZTRaaEtrVEJEa1Z3ejg2VG1ONG1ENmlDWlkyVjlkQkJwS2F1XzBGMFQwSHd4OEwxTW1PbHdGcUh1ckV6SGpDd2hiN0dkeUVTcnFXT3RjOU1kLXZtVVdZY2hkZS1pcVpVUFhnRktqcHY5UnBrY0xUMDRETjl6N0pXT3A5amxhMA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>noticia:17hz69v</t>
+          <t>noticia:bksnde</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-22 13:05</t>
+          <t>2026-10-22 17:01</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1792688709000</v>
+        <v>1792702880000</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Accidente en El Sillar deja al menos 29 heridos - La Razón Digital Bolivia</t>
+          <t>Reportan un incendio cerca de la carretera a Cotoca - eju.tv</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3182,18 +3182,18 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -3205,37 +3205,53 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>La Razón Digital Bolivia</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
+          <t>eju.tv</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>-17.764</v>
+      </c>
+      <c r="N37" t="n">
+        <v>-62.903</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Cotoca, Santa Cruz</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Cotoca</t>
+        </is>
+      </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPaXhTdm45YWZnWVFxVzJnb1ZwbUN4SmUtLVdJN0VJdFZBamRyQmFxN0RZelBfTklaSTVyOUZ3ajQ5MFB2TEN4Ukd6TE5ORFY5SEROVk1CZ25sRWJ1QnRBdTVfTktlby1NWXhaVWI5YnRvaDZWbHVjdDVoeFp5Tk5veFk5a19MSWJqcEJVV0dzV3k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPNGtpbnBfRnRBalVudnBlZHdVQ0ZSaUplZmtvTGE0aTQzdkxWS3d4My1EZEJ1UE9FNFQ3RmpyZGVsbS1qNEM1QUVFRFAxM2pYT1VqQzRuVjRtZnVNUGlKODNMc0F1a3l6TUpuQmtlUWNlVTVEWWU5ZGZtQm5LWUp3Sg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>noticia:1f1qb0</t>
+          <t>noticia:17hz69v</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-22 12:09</t>
+          <t>2026-10-22 13:05</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1792685373000</v>
+        <v>1792688709000</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Accidente en el tramo Locotal–Villa Tunari: la vía está transitable con precaución - Red Uno</t>
+          <t>Accidente en El Sillar deja al menos 29 heridos - La Razón Digital Bolivia</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3244,18 +3260,18 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -3267,73 +3283,57 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Red Uno</t>
-        </is>
-      </c>
-      <c r="M38" t="n">
-        <v>-16.556</v>
-      </c>
-      <c r="N38" t="n">
-        <v>-65.569</v>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>Villa Tunari, Cochabamba</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>Villa Tunari</t>
-        </is>
-      </c>
+          <t>La Razón Digital Bolivia</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTFozcEEwNXBqV19sS2VibXh0MGt0QlhsX1djSTFGQW5zNlFLRHZpNVVnZ1JmWDQ4LVRHX2Rmb3B5UU9qV0FZQmJCaUZYdmwyNG1NenJ4Qzlzd0NJTGs1SjMxdFRtRFBzSUkybGJfZFFaNFZBc21FSUJYSFVkQkVkSEhQaGw0UFVzeXctZHo3cjNsYm5weXJlOU1wcmFncnNhMC1BQUpvNWlDX1NxZXU4b09kVFFWR2tSVEk2UTdXXzB3TjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPaXhTdm45YWZnWVFxVzJnb1ZwbUN4SmUtLVdJN0VJdFZBamRyQmFxN0RZelBfTklaSTVyOUZ3ajQ5MFB2TEN4Ukd6TE5ORFY5SEROVk1CZ25sRWJ1QnRBdTVfTktlby1NWXhaVWI5YnRvaDZWbHVjdDVoeFp5Tk5veFk5a19MSWJqcEJVV0dzV3k?oc=5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>noticia:wi18tm</t>
+          <t>noticia:1f1qb0</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-22 11:53</t>
+          <t>2026-10-22 12:09</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1792684426000</v>
+        <v>1792685373000</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Accidente en El Sillar deja heridos y derrame de combustible: esto es lo último que se sabe - Red Uno</t>
+          <t>Accidente en el tramo Locotal–Villa Tunari: la vía está transitable con precaución - Red Uno</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>tecnológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -3348,54 +3348,70 @@
           <t>Red Uno</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
+      <c r="M39" t="n">
+        <v>-16.556</v>
+      </c>
+      <c r="N39" t="n">
+        <v>-65.569</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Villa Tunari, Cochabamba</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Villa Tunari</t>
+        </is>
+      </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPZHNBTEdaQm5Wby1lTF9mWlQ2aGg0MVc4S0MwVWJ3dUJ5WWU5X3IwYWhKRjk5VWtYWEJHRDF4QldVc29laVNPSTJNWFBDSkNFQlFSYTJUXzNMNF9hckFBN1I2T2xoQUtYQ2V6MDNTZHhHVk9qeTBCdHRpM2ZLd0pyOFRweUUxX19STzRHTHg5VUY5d1lhS0tDeXpCdklqcTZGT1J4R0xnSDhoak1EZ2dtNUhSTUV6b1o0U0VSdWY5X0E3U05Tc1dYVEN2WFZUeFhPMTBJTmowNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTFozcEEwNXBqV19sS2VibXh0MGt0QlhsX1djSTFGQW5zNlFLRHZpNVVnZ1JmWDQ4LVRHX2Rmb3B5UU9qV0FZQmJCaUZYdmwyNG1NenJ4Qzlzd0NJTGs1SjMxdFRtRFBzSUkybGJfZFFaNFZBc21FSUJYSFVkQkVkSEhQaGw0UFVzeXctZHo3cjNsYm5weXJlOU1wcmFncnNhMC1BQUpvNWlDX1NxZXU4b09kVFFWR2tSVEk2UTdXXzB3TjA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>noticia:12gfagq</t>
+          <t>noticia:wi18tm</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-22 11:28</t>
+          <t>2026-10-22 11:53</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1792682880000</v>
+        <v>1792684426000</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Reportan triple colisión entre dos camiones y un bus en la carretera Cochabamba-Santa Cruz - FmBolivia</t>
+          <t>Accidente en El Sillar deja heridos y derrame de combustible: esto es lo último que se sabe - Red Uno</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>tecnológica</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -3403,57 +3419,41 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>FmBolivia; Red Uno</t>
-        </is>
-      </c>
-      <c r="M40" t="n">
-        <v>-17.39</v>
-      </c>
-      <c r="N40" t="n">
-        <v>-66.16</v>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>Cochabamba, Cochabamba</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
+          <t>Red Uno</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNMTNBaFZNMU9SR25vdVBuNXlZY3g4VkFWYXRiQnNSaUFjemZhUHZWNHg4V2owU2xfNndBak94TnU2cHNUVXdNNWl2eUdHZVNMbVZweTR5M0o0bWdTNUN4QkoxUkI2TDBmVE03M09zRGhJRVFzV0tPZ1NCWEJLUkt1ZGN4UGduOUZMQnJoM0tMYTh0ZlFxaFJNUkJqaWFPazRlMzN3ajhjUEdUYXlZRndpb3RSdTFCX2tCZGJxQ0x4SlBISWJsRVoyN3ZR?oc=5 | https://news.google.com/rss/articles/CBMirwFBVV95cUxNNUROMzd1UDJRWVZZQ011cFd2c1FSdER1ZzdleU04cXpwYk5HaUZrLXoyU2NzdFk1dnNRUndhUWt0cG9DX09rSjlLcDItU0tzcmQtS3E4dDQ4ZF9HdGJLdk13ek9BNHJUWVlCcklrM25rZ01RbXhLalRBT1FGdDNReHdlTFZkNkJ5ZFd3N3NZVFVmOFUxbEhHN0RsaUxiSVZsM0lXVEFYSHVRQlhsOEtJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPZHNBTEdaQm5Wby1lTF9mWlQ2aGg0MVc4S0MwVWJ3dUJ5WWU5X3IwYWhKRjk5VWtYWEJHRDF4QldVc29laVNPSTJNWFBDSkNFQlFSYTJUXzNMNF9hckFBN1I2T2xoQUtYQ2V6MDNTZHhHVk9qeTBCdHRpM2ZLd0pyOFRweUUxX19STzRHTHg5VUY5d1lhS0tDeXpCdklqcTZGT1J4R0xnSDhoak1EZ2dtNUhSTUV6b1o0U0VSdWY5X0E3U05Tc1dYVEN2WFZUeFhPMTBJTmowNA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>noticia:1jl2oid</t>
+          <t>noticia:12gfagq</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-22 07:49</t>
+          <t>2026-10-22 11:28</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1792669785000</v>
+        <v>1792682880000</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - eju.tv</t>
+          <t>Reportan triple colisión entre dos camiones y un bus en la carretera Cochabamba-Santa Cruz - FmBolivia</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3462,18 +3462,18 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -3485,109 +3485,187 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Red Uno; eju.tv</t>
+          <t>FmBolivia; Red Uno</t>
         </is>
       </c>
       <c r="M41" t="n">
-        <v>-17.781</v>
+        <v>-17.39</v>
       </c>
       <c r="N41" t="n">
-        <v>-63.139</v>
+        <v>-66.16</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Santa Cruz, Santa Cruz</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQbTBrUmlla3FvVU1EX1pxcUI3SXYzbUFFMzlnRzhlSDJwMGpWWURxYjIwSkJBRGdCazMzT01hVy1qMFY3RnJLbC1XNXJ4bU55aDJVeXpNUlRsbzQ3T3hiRXJ5SWlhNmw5cDZFanNoWFBtQ01Gd3dscXltWmU5VHBSQlN3c2IwNGxuVE5tQ3lOT1RmNzRiVi1hc0hn?oc=5 | https://news.google.com/rss/articles/CBMiuwFBVV95cUxNVEh1bFlCanFuOTJid2EzYS1meG5oekFJcGFaME1fTk9sUnZpd3U0UXFHUFVJSW1jc1hzM2VFOFprT2xNYjBzbmswZmdJV3dremRIS0I4MDNzRjBnbEttWEhfOWZBbmFrRnNHWDFVLVFoM0VkZkxkaW4tMmZlSFJLei1heTFHMU0wSmxQVVRZN0cwaXQzcDBtZkdwTUFma0RXU2dwLXRnLTBkNGN3Vm1fV3hEdlM1dWZ1SEsw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNMTNBaFZNMU9SR25vdVBuNXlZY3g4VkFWYXRiQnNSaUFjemZhUHZWNHg4V2owU2xfNndBak94TnU2cHNUVXdNNWl2eUdHZVNMbVZweTR5M0o0bWdTNUN4QkoxUkI2TDBmVE03M09zRGhJRVFzV0tPZ1NCWEJLUkt1ZGN4UGduOUZMQnJoM0tMYTh0ZlFxaFJNUkJqaWFPazRlMzN3ajhjUEdUYXlZRndpb3RSdTFCX2tCZGJxQ0x4SlBISWJsRVoyN3ZR?oc=5 | https://news.google.com/rss/articles/CBMirwFBVV95cUxNNUROMzd1UDJRWVZZQ011cFd2c1FSdER1ZzdleU04cXpwYk5HaUZrLXoyU2NzdFk1dnNRUndhUWt0cG9DX09rSjlLcDItU0tzcmQtS3E4dDQ4ZF9HdGJLdk13ek9BNHJUWVlCcklrM25rZ01RbXhLalRBT1FGdDNReHdlTFZkNkJ5ZFd3N3NZVFVmOFUxbEhHN0RsaUxiSVZsM0lXVEFYSHVRQlhsOEtJ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>noticia:1jl2oid</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-10-22 07:49</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1792669785000</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - eju.tv</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>antropogénica</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>amarilla</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>2</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Red Uno; eju.tv</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>-17.781</v>
+      </c>
+      <c r="N42" t="n">
+        <v>-63.139</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Santa Cruz, Santa Cruz</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Santa Cruz de la Sierra</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQbTBrUmlla3FvVU1EX1pxcUI3SXYzbUFFMzlnRzhlSDJwMGpWWURxYjIwSkJBRGdCazMzT01hVy1qMFY3RnJLbC1XNXJ4bU55aDJVeXpNUlRsbzQ3T3hiRXJ5SWlhNmw5cDZFanNoWFBtQ01Gd3dscXltWmU5VHBSQlN3c2IwNGxuVE5tQ3lOT1RmNzRiVi1hc0hn?oc=5 | https://news.google.com/rss/articles/CBMiuwFBVV95cUxNVEh1bFlCanFuOTJid2EzYS1meG5oekFJcGFaME1fTk9sUnZpd3U0UXFHUFVJSW1jc1hzM2VFOFprT2xNYjBzbmswZmdJV3dremRIS0I4MDNzRjBnbEttWEhfOWZBbmFrRnNHWDFVLVFoM0VkZkxkaW4tMmZlSFJLei1heTFHMU0wSmxQVVRZN0cwaXQzcDBtZkdwTUFma0RXU2dwLXRnLTBkNGN3Vm1fV3hEdlM1dWZ1SEsw?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>noticia:n32ahi</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>2026-10-22 05:30</t>
         </is>
       </c>
-      <c r="C42" t="n">
+      <c r="C43" t="n">
         <v>1792661402000</v>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>Senamhi anuncia el inicio de la temporada de lluvias en Bolivia y prevé granizadas como la de La Paz - FmBolivia</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>meteorológica</t>
         </is>
       </c>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" t="inlineStr">
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="inlineStr">
         <is>
           <t>verde</t>
         </is>
       </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" t="inlineStr">
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="K42" t="n">
-        <v>1</v>
-      </c>
-      <c r="L42" t="inlineStr">
+      <c r="K43" t="n">
+        <v>1</v>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t>FmBolivia</t>
         </is>
       </c>
-      <c r="M42" t="n">
+      <c r="M43" t="n">
         <v>-16.169</v>
       </c>
-      <c r="N42" t="n">
+      <c r="N43" t="n">
         <v>-68.09</v>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>La Paz, La Paz</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>La Paz</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>Nuestra Señora de La Paz</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQNmVPRnVBMGQzdEI5SUp3Z3ZGVExwTUR6TWNadGQ1QldUS1o2QVFvUl9sVEZKMDVyQVVrS25rU1RSQlJKWXk1YzE0NUhidjhpcmFaSlhZUDZvcE9XcG1KTFNTYmowUU1CSFJNOVR2UHNmMk1iT3N0RVBteHkzZkgyRFROYk1pdkpxVHZya3N2X2FVLVQxbURFVVZlb1NzRjZzTE95TXFVUXFJNkVZakQ2bUhVQzB0SXk3TVhXUTJXa0dycTE1MWVQRFpDX3lDSWFqUGwzU2NtNA?oc=5</t>
         </is>
@@ -3604,7 +3682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S64"/>
+  <dimension ref="A1:S65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3707,7 +3785,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>noticia:1xi48lm</t>
+          <t>noticia:kaqalb</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3717,20 +3795,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-25 13:02</t>
+          <t>2026-10-25 15:29</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1792947732000</v>
+        <v>1792956564000</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>EL DÍA - Noticias de Bolivia para el mundo</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>climatológica</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -3743,13 +3821,13 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Reportan el incendio de dos camiones cisterna en la carretera a Camiri - EL DÍA - Noticias de Bolivia para el mundo</t>
+          <t>“El bolsillo no alcanza”: la sequía golpea al ganado en Pasorapa y piden tanques de agua - Red Uno</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNN0traUpaNVFIOU0zeFZod2tkQWhZZFQ1Q3dxc2xCVy1RNnJIX2xQbTlhT3RVckdNdHV4ZFVLQThvd2UzNDlCa3VmaWprTnU3R05rVkVkdEVCU1hFMlFsLTJ6REIySnl5VFJfdV9pQmVDTzlqUWFUSi1GQ0JvTVJVQ2dpeVBydnpMV0dYOThENTFRUDgxVFloSVg3bnN4dGo2aEVCbDFKaUgydWNISnJVUTNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNRm5FbDhxTlliZHdPdnplYVNrWVdsSFF2ZGp3c2t1MEJCdWJkOE5fLWU5SXhXc25JLU9leVNsdnJZUEFFRmlTOUtJLW5SZ3JpRDFlYmlaYlFLYVJrM3pud0plS2lXVllqdEd0cWRiMUlmRzZkdnRpT2twaGU4cm1TRm9uSEw4WkhjeEJGUVZMNlJmRnFnY0M2UWw3T3NqMXdFcXhETjdrRi1hSjh3UDIxZl9CamxvYXdHRDRkZGR0ZEtZNHREX0c5Ul9Fa3VKMlJh?oc=5</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -3759,14 +3837,14 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-20.05</v>
+        <v>-18.38</v>
       </c>
       <c r="O2" t="n">
-        <v>-63.486</v>
+        <v>-64.649</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Camiri, Santa Cruz</t>
+          <t>Pasorapa, Cochabamba</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -3776,19 +3854,19 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Camiri</t>
+          <t>Pasorapa</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>noticia:4blj1l</t>
+          <t>noticia:1xi48lm</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3798,15 +3876,15 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-25 12:59</t>
+          <t>2026-10-25 13:02</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1792947573000</v>
+        <v>1792947732000</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
+          <t>EL DÍA - Noticias de Bolivia para el mundo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -3824,13 +3902,13 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Santa Cruz: Dos cisternas se incendian tras colisionar - La Patria Bolivia</t>
+          <t>Reportan el incendio de dos camiones cisterna en la carretera a Camiri - EL DÍA - Noticias de Bolivia para el mundo</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQbHdpcUF6dXpjaW1TT1ZmdGJtUUVLMTNMRTVqVkFUdkNsZlRvenVkckFUWmI4NDFmc2ZHd2RVcWRSSE5YRVpOTUlESGw2V3JONXpwS0RISGNZd01SejNuMkY4NzFYYXp4aWo2RE9VMkFYUkVwZ3JRRmM5MWlRSjlBWk16azdkQ3FjdEtkaWc5NERkTzk2SllVOQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNN0traUpaNVFIOU0zeFZod2tkQWhZZFQ1Q3dxc2xCVy1RNnJIX2xQbTlhT3RVckdNdHV4ZFVLQThvd2UzNDlCa3VmaWprTnU3R05rVkVkdEVCU1hFMlFsLTJ6REIySnl5VFJfdV9pQmVDTzlqUWFUSi1GQ0JvTVJVQ2dpeVBydnpMV0dYOThENTFRUDgxVFloSVg3bnN4dGo2aEVCbDFKaUgydWNISnJVUTNB?oc=5</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -3840,14 +3918,14 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-17.781</v>
+        <v>-20.05</v>
       </c>
       <c r="O3" t="n">
-        <v>-63.139</v>
+        <v>-63.486</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Santa Cruz, Santa Cruz</t>
+          <t>Camiri, Santa Cruz</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -3862,34 +3940,32 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Camiri</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>manual:1c1299f3</t>
+          <t>noticia:4blj1l</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>registro</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-25 12:44</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>1792946640000</t>
-        </is>
+          <t>2026-10-25 12:59</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1792947573000</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Registro abierto (sin verificar)</t>
+          <t>La Patria Bolivia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -3897,90 +3973,82 @@
           <t>antropogénica</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G4" t="n">
+        <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Vuelco de minibus</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Registro de prueba del sistema. Ignorar. | Lugar indicado: Caranavi, La Paz | Registro abierto, sin verificar.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>-15.813</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>-67.463</t>
-        </is>
+          <t>Santa Cruz: Dos cisternas se incendian tras colisionar - La Patria Bolivia</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQbHdpcUF6dXpjaW1TT1ZmdGJtUUVLMTNMRTVqVkFUdkNsZlRvenVkckFUWmI4NDFmc2ZHd2RVcWRSSE5YRVpOTUlESGw2V3JONXpwS0RISGNZd01SejNuMkY4NzFYYXp4aWo2RE9VMkFYUkVwZ3JRRmM5MWlRSjlBWk16azdkQ3FjdEtkaWc5NERkTzk2SllVOQ?oc=5</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-17.781</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-63.139</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Caranavi, La Paz</t>
+          <t>Santa Cruz, Santa Cruz</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>nombre de municipio indicado por quien registra</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Caranavi</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>noticia:oww2zc</t>
+          <t>manual:1c1299f3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>registro</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-25 12:08</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>1792944531000</v>
+          <t>2026-10-25 12:44</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1792946640000</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>Registro abierto (sin verificar)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3988,62 +4056,72 @@
           <t>antropogénica</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Cierran la carretera a Camiri: dos cisternas chocan y provocan un voraz incendio - Red Uno</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQLXlqSFdvWUVhQUNadnpkdE5lUTZQS0lobThzUTZWbDNJTE94alVhaDBaYU9Fd09SSGt3UlR3Y0dfZlNIcml1ZktnWjctNk1Na3V4S0tINFNkMXM0OHBoV2lCTTBiYXlPUTA3T2ZkeXE2RElYWjhfVHd3Nng1Z0E4alBmOFI5NDFwX09kazZlSWl2OVR2ZVR6MDhvSHFnSmJKbTFXSEFDNFFYcWVDNGtYWEQ0bDhJel9CaEpEZWZ4SWN0TE9Ya0E?oc=5</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-20.05</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-63.486</v>
+          <t>Vuelco de minibus</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Registro de prueba del sistema. Ignorar. | Lugar indicado: Caranavi, La Paz | Registro abierto, sin verificar.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>-15.813</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>-67.463</t>
+        </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Camiri, Santa Cruz</t>
+          <t>Caranavi, La Paz</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
+          <t>nombre de municipio indicado por quien registra</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Camiri</t>
+          <t>Caranavi</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>noticia:1a4hhsd</t>
+          <t>noticia:oww2zc</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4053,15 +4131,15 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-25 11:56</t>
+          <t>2026-10-25 12:08</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1792943794000</v>
+        <v>1792944531000</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Opinión Bolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -4079,13 +4157,13 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Reportan el incendio de dos camiones cisterna en la carretera a Camiri - Opinión Bolivia</t>
+          <t>Cierran la carretera a Camiri: dos cisternas chocan y provocan un voraz incendio - Red Uno</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNUTdxSzBJVTZnajZQUXhyTVhwMlpvU0tyZGVBYnFwV2kyZWthenNRT1FDRVJFZnk4ZndGTFQ0cnFXZmZ1WHZaMFhUbWo0SWkzcjcxbjJwU3pKUXR4WEVZLVlRNFpxOUVMY2NNNUZsbmJSMk9xZG1sTklEdEtGSXJyUUp5b0R2dVpYcHJLdTRNRlRjcWpNNXg4c0Z4UWwteFc2dDRqVmpnQnFfQXgwN0twTzl4ZWhYdUtYWGfSAboBQVVfeXFMTVE3cUswSVU2Z2o2UFF4ck1YcDJab1NLcmRlQWJxcFdpMmVrYXpzUU9RQ0VSRWZ5OGZ3RkxUNHJxV2ZmdVh2WjBYVG1qNElpM3I3MW4ycFN6SlF0eFhFWS1ZUTRacTlFTGNjTTVGbG5iUjJPcWRtbE5JRHRLRklyclFKeW9EdnVaWHByS3U0TUZUY3FqTTV4OHNGeFFsLXhXNnQ0alZqZ0JxX0F4MDdLcE85eGVoWHVLWFhn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQLXlqSFdvWUVhQUNadnpkdE5lUTZQS0lobThzUTZWbDNJTE94alVhaDBaYU9Fd09SSGt3UlR3Y0dfZlNIcml1ZktnWjctNk1Na3V4S0tINFNkMXM0OHBoV2lCTTBiYXlPUTA3T2ZkeXE2RElYWjhfVHd3Nng1Z0E4alBmOFI5NDFwX09kazZlSWl2OVR2ZVR6MDhvSHFnSmJKbTFXSEFDNFFYcWVDNGtYWEQ0bDhJel9CaEpEZWZ4SWN0TE9Ya0E?oc=5</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -4124,7 +4202,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>noticia:1at00ey</t>
+          <t>noticia:1a4hhsd</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4134,15 +4212,15 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-25 11:19</t>
+          <t>2026-10-25 11:56</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1792941547000</v>
+        <v>1792943794000</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>Opinión Bolivia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4160,13 +4238,13 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Dos cisternas chocan y provocan voraz incendio en la ruta a Camiri - Red Uno</t>
+          <t>Reportan el incendio de dos camiones cisterna en la carretera a Camiri - Opinión Bolivia</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPTTF0OUdVS1c1a0lZWmk3bGxHdDJIalpWZTRyQTY3eWE2a2dWOHlsaldKZXpSLWN5c3BkUWdBRkJuSzhHdWl2ZjgwTFFFYnd0aTAxZ3dJU0hCekNZNm9aTTJSZUNfQjVIM3FrUUJ4NXAwa3paZ3BEek9xTVZNQWdnN01xRHloV1ZXZHV6N0JpUWo3RE9DMlFGdkNnWkloTjVVY3RBR1RSRUJJWFVtby1fMWFMNTdLZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNUTdxSzBJVTZnajZQUXhyTVhwMlpvU0tyZGVBYnFwV2kyZWthenNRT1FDRVJFZnk4ZndGTFQ0cnFXZmZ1WHZaMFhUbWo0SWkzcjcxbjJwU3pKUXR4WEVZLVlRNFpxOUVMY2NNNUZsbmJSMk9xZG1sTklEdEtGSXJyUUp5b0R2dVpYcHJLdTRNRlRjcWpNNXg4c0Z4UWwteFc2dDRqVmpnQnFfQXgwN0twTzl4ZWhYdUtYWGfSAboBQVVfeXFMTVE3cUswSVU2Z2o2UFF4ck1YcDJab1NLcmRlQWJxcFdpMmVrYXpzUU9RQ0VSRWZ5OGZ3RkxUNHJxV2ZmdVh2WjBYVG1qNElpM3I3MW4ycFN6SlF0eFhFWS1ZUTRacTlFTGNjTTVGbG5iUjJPcWRtbE5JRHRLRklyclFKeW9EdnVaWHByS3U0TUZUY3FqTTV4OHNGeFFsLXhXNnQ0alZqZ0JxX0F4MDdLcE85eGVoWHVLWFhn?oc=5</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -4205,7 +4283,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>noticia:1uf38hl</t>
+          <t>noticia:1at00ey</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4215,11 +4293,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-25 10:59</t>
+          <t>2026-10-25 11:19</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1792940350000</v>
+        <v>1792941547000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -4241,13 +4319,13 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>¡Cisterna con combustible en llamas! Reportan impresionante incendio en la carretera a Camiri - Red Uno</t>
+          <t>Dos cisternas chocan y provocan voraz incendio en la ruta a Camiri - Red Uno</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxORUhqeWpKY1FHRWoxaHN0UXFzS3dpeHh6N0NwLUJOZTlZcDVoNHN0VnI0by1qMWtZZEkxVmtUNjdNTFhjaEFQU2IyMlNwZW95WFBzbFJPVVB6TjJtdjNENk1LWVlsMUxUUzBNVzkxRk1HZ3lQU0s2M1lRVlRuaXlkMmJrd3AyTGpIdXItNkhlU3dhTzBRME56Rm1DSlZCYjNxSnNTbTFqNWRoUkdraHhlREhuYldqeFk2N3poWEx2M08?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPTTF0OUdVS1c1a0lZWmk3bGxHdDJIalpWZTRyQTY3eWE2a2dWOHlsaldKZXpSLWN5c3BkUWdBRkJuSzhHdWl2ZjgwTFFFYnd0aTAxZ3dJU0hCekNZNm9aTTJSZUNfQjVIM3FrUUJ4NXAwa3paZ3BEek9xTVZNQWdnN01xRHloV1ZXZHV6N0JpUWo3RE9DMlFGdkNnWkloTjVVY3RBR1RSRUJJWFVtby1fMWFMNTdLZw?oc=5</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -4286,7 +4364,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>noticia:1sg8pi0</t>
+          <t>noticia:1uf38hl</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4296,11 +4374,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-25 09:59</t>
+          <t>2026-10-25 10:59</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1792936752000</v>
+        <v>1792940350000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -4322,13 +4400,13 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Bus de agrupación musical sufre accidente rumbo al trópico de Cochabamba | VIDEO - Red Uno</t>
+          <t>¡Cisterna con combustible en llamas! Reportan impresionante incendio en la carretera a Camiri - Red Uno</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOVDVzVTJNM2JuQ25sMThEaVZNOUNRd3FGT3RhVnFrZXZ2NDQ1YlluTVdhbVNUQnA1MGNESHRSWVUzbC1kRVh3OTR0emtlTG91cmRWeFJ5dk5zb3p2WFRyMEJUV3FNRnY1WHhRUU9WLTlJcmNyNXJZZFdoM0JoZjNpa3hjUXhMM0xrUDJab2VadkM5RWZYQ3lWZTVDdzg1akxJT2lxcDVNNzI0NG1hejdfdkUyTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxORUhqeWpKY1FHRWoxaHN0UXFzS3dpeHh6N0NwLUJOZTlZcDVoNHN0VnI0by1qMWtZZEkxVmtUNjdNTFhjaEFQU2IyMlNwZW95WFBzbFJPVVB6TjJtdjNENk1LWVlsMUxUUzBNVzkxRk1HZ3lQU0s2M1lRVlRuaXlkMmJrd3AyTGpIdXItNkhlU3dhTzBRME56Rm1DSlZCYjNxSnNTbTFqNWRoUkdraHhlREhuYldqeFk2N3poWEx2M08?oc=5</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -4338,14 +4416,14 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-17.39</v>
+        <v>-20.05</v>
       </c>
       <c r="O9" t="n">
-        <v>-66.16</v>
+        <v>-63.486</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Cochabamba, Cochabamba</t>
+          <t>Camiri, Santa Cruz</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -4355,19 +4433,19 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Camiri</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>noticia:167wlhz</t>
+          <t>noticia:1sg8pi0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4377,11 +4455,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-25 07:53</t>
+          <t>2026-10-25 09:59</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1792929231000</v>
+        <v>1792936752000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -4390,7 +4468,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -4403,13 +4481,13 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>¡A sacar el paraguas! Santa cruz amanece con lluvia, frío y complicaciones en el tránsito vehicular - Red Uno</t>
+          <t>Bus de agrupación musical sufre accidente rumbo al trópico de Cochabamba | VIDEO - Red Uno</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOY1ZpYktLR3pUQXotUndVR3puUzVHbW1YTzNyUmJvUHB4Q2JmelRvOEdaRldOUm1xLVJnbGR5VWcxTjNEM3ZUYktCUWtVM0hKSjFuRGdpX0JxN0M5MVZBSG1aVURyVWktdmxwbUtRT19ydU5LdzNTZ2Zpb2ozdHlMUUdTVlAyVk4xODBnV0hyTXdVVndyNzV3VC1KMzFnV3lpcFFXSk9MdDZOTWlWakNwT1FnNDh6QVdjazVYZDVVMkdaLU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOVDVzVTJNM2JuQ25sMThEaVZNOUNRd3FGT3RhVnFrZXZ2NDQ1YlluTVdhbVNUQnA1MGNESHRSWVUzbC1kRVh3OTR0emtlTG91cmRWeFJ5dk5zb3p2WFRyMEJUV3FNRnY1WHhRUU9WLTlJcmNyNXJZZFdoM0JoZjNpa3hjUXhMM0xrUDJab2VadkM5RWZYQ3lWZTVDdzg1akxJT2lxcDVNNzI0NG1hejdfdkUyTQ?oc=5</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -4419,14 +4497,14 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-17.781</v>
+        <v>-17.39</v>
       </c>
       <c r="O10" t="n">
-        <v>-63.139</v>
+        <v>-66.16</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Santa Cruz, Santa Cruz</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -4436,19 +4514,19 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Cochabamba</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>noticia:bzr7eh</t>
+          <t>noticia:167wlhz</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4458,39 +4536,39 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-25 07:09</t>
+          <t>2026-10-25 07:53</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1792926572000</v>
+        <v>1792929231000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>hidrológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Alerta naranja por riesgo de desbordes de ríos - El Diario - Bolivia</t>
+          <t>¡A sacar el paraguas! Santa cruz amanece con lluvia, frío y complicaciones en el tránsito vehicular - Red Uno</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNNGZKSDVaZkowWUFGSEUyTWR3d3dsc04waFBLLWUtcVpiTDYzbmNtYTN1RkFLbjAwN3dxT0xZc3pqc3REUXduZVltQ2Fud1BZLTh1bTNiTEJueVUwV0dERS1iUXZqMHd0UnFrQ3E2SFAzbm5lQ1I4U29MaHJFbWFvdVRTeFY4Wl9rSmc3RkpaQ2xwX0oz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOY1ZpYktLR3pUQXotUndVR3puUzVHbW1YTzNyUmJvUHB4Q2JmelRvOEdaRldOUm1xLVJnbGR5VWcxTjNEM3ZUYktCUWtVM0hKSjFuRGdpX0JxN0M5MVZBSG1aVURyVWktdmxwbUtRT19ydU5LdzNTZ2Zpb2ozdHlMUUdTVlAyVk4xODBnV0hyTXdVVndyNzV3VC1KMzFnV3lpcFFXSk9MdDZOTWlWakNwT1FnNDh6QVdjazVYZDVVMkdaLU0?oc=5</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -4499,21 +4577,37 @@
       <c r="M11" t="n">
         <v>0</v>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>-17.781</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-63.139</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Santa Cruz, Santa Cruz</t>
+        </is>
+      </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Santa Cruz de la Sierra</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>noticia:1fo4ig4</t>
+          <t>noticia:bzr7eh</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4523,43 +4617,43 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-25 01:08</t>
+          <t>2026-10-25 07:09</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1792904880000</v>
+        <v>1792926572000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>diarioelpueblo.com.pe</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>hidrológica</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>roja</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
+          <t>Alerta naranja por riesgo de desbordes de ríos - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQcmFrT3dwcEs0X3U2NWxnOGJwNnI2WHdWTGZYbzEyNnJzUWhkbU9TRWhfSlB5UkMwX2gyMmxYUmVNWmxNOVR6V0twRHpFMTVIYjBKbHQ2TXN2d2w5dkFpcWJCcUJMZldaX01sNWtQV2ZJOGpRVzR3NDVIU0pJc1BNVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNNGZKSDVaZkowWUFGSEUyTWR3d3dsc04waFBLLWUtcVpiTDYzbmNtYTN1RkFLbjAwN3dxT0xZc3pqc3REUXduZVltQ2Fud1BZLTh1bTNiTEJueVUwV0dERS1iUXZqMHd0UnFrQ3E2SFAzbm5lQ1I4U29MaHJFbWFvdVRTeFY4Wl9rSmc3RkpaQ2xwX0oz?oc=5</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -4578,7 +4672,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>noticia:r1uot6</t>
+          <t>noticia:1fo4ig4</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4588,15 +4682,15 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-24 20:00</t>
+          <t>2026-10-25 01:08</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1792886439000</v>
+        <v>1792904880000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
+          <t>diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -4605,61 +4699,45 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>roja</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>vuelco deja heridos en ruta Oruro – Huanuni - La Patria Bolivia</t>
+          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNNDQtMG1KT1lLWW5nem9Jbm5JWDZKNlRWZmFmRlBxWDlDeXlSWnJ5d2NsTlpxa0JIS25oVWVZOC1majZVbWhOVDIxR0dLOFlzY2VpVzVoVk1mQnF3dXVwLUFZVHc1UjlXZzF5T05CY3U0ZldLVkw1VzBTek5zanpjQW1xalltWHNiaXI3dTNR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQcmFrT3dwcEs0X3U2NWxnOGJwNnI2WHdWTGZYbzEyNnJzUWhkbU9TRWhfSlB5UkMwX2gyMmxYUmVNWmxNOVR6V0twRHpFMTVIYjBKbHQ2TXN2d2w5dkFpcWJCcUJMZldaX01sNWtQV2ZJOGpRVzR3NDVIU0pJc1BNVg?oc=5</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>-17.97</v>
-      </c>
-      <c r="O13" t="n">
-        <v>-67.11</v>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Oruro, Oruro</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>Oruro</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>Oruro</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>noticia:1ytw450</t>
+          <t>noticia:r1uot6</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4669,15 +4747,15 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-24 18:58</t>
+          <t>2026-10-24 20:00</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1792882686000</v>
+        <v>1792886439000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>diarioelpueblo.com.pe</t>
+          <t>La Patria Bolivia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -4686,45 +4764,61 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>roja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
+          <t>vuelco deja heridos en ruta Oruro – Huanuni - La Patria Bolivia</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNZ1U3bEVuaVdjVE1zSU9lOHJZTVRZLVZaemhldGNnT1JBWDJvbzdvM3paVVNhLUlyWHF2akNuSXJOLXdyTGRuejRlV1FuMjVkTjA3NmdRdmgtRWlUeTFBV1dEMzBvejBxaXZJdUZZWkRVTF9VLU5BcjFGZGFEQ09WWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNNDQtMG1KT1lLWW5nem9Jbm5JWDZKNlRWZmFmRlBxWDlDeXlSWnJ5d2NsTlpxa0JIS25oVWVZOC1majZVbWhOVDIxR0dLOFlzY2VpVzVoVk1mQnF3dXVwLUFZVHc1UjlXZzF5T05CY3U0ZldLVkw1VzBTek5zanpjQW1xalltWHNiaXI3dTNR?oc=5</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-17.97</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-67.11</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Oruro, Oruro</t>
+        </is>
+      </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>noticia:1wcb22g</t>
+          <t>noticia:1ytw450</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4734,43 +4828,43 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-24 17:47</t>
+          <t>2026-10-24 18:58</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1792878475000</v>
+        <v>1792882686000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>El Mundo Bolivia</t>
+          <t>diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>hidrológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>roja</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Alerta naranja por ingreso de frente frío y desbordes de ríos en 6 departamentos - El Mundo Bolivia</t>
+          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPZW00RkxJSklTelNrS2hqczJDWHlwcENFX2lnSEUyTEFPaDFRQ2JvMUcyd3NfYjg0UE9ORGxHRzB4ZDh3U0hQQ1JSQlhsaUY4N3ByMUUxei1SaUZnNlp6T3hsLVdiMGhKaXhsV1FNSUNQMHlvQ19qdk56SEF0d2RXVFctS0VPT25kNGZCRDdvZ2dxU0VoUUJKU0ZBd0ZycFNEZFh0T3ZjOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNZ1U3bEVuaVdjVE1zSU9lOHJZTVRZLVZaemhldGNnT1JBWDJvbzdvM3paVVNhLUlyWHF2akNuSXJOLXdyTGRuejRlV1FuMjVkTjA3NmdRdmgtRWlUeTFBV1dEMzBvejBxaXZJdUZZWkRVTF9VLU5BcjFGZGFEQ09WWQ?oc=5</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -4789,7 +4883,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>noticia:1c1ju1f</t>
+          <t>noticia:1wcb22g</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4799,46 +4893,46 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-24 17:02</t>
+          <t>2026-10-24 17:47</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1792875752000</v>
+        <v>1792878475000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>La Razón Digital Bolivia</t>
+          <t>El Mundo Bolivia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>hidrológica</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a los Yungas deja siete heridos - La Razón Digital Bolivia</t>
+          <t>Alerta naranja por ingreso de frente frío y desbordes de ríos en 6 departamentos - El Mundo Bolivia</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPTGQwaVBfdG1JdVRMUTN4LVVvN0ppc3dreDJVVllDR3RmX0xpMzB4b0pvVTNSV1B6T0ZEWTdEZkNsRUdSNzhLaC1CWHN5WktNWk1nRWpTdVZiYjI3TlJlX2xlVTI5MjlRU2hiY1gteml4YWVFbDNPSVRBZmtITlQzbmhaUXVmcThRa2xsQTJIOXZuNzlSdm12MEdyOEZHdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPZW00RkxJSklTelNrS2hqczJDWHlwcENFX2lnSEUyTEFPaDFRQ2JvMUcyd3NfYjg0UE9ORGxHRzB4ZDh3U0hQQ1JSQlhsaUY4N3ByMUUxei1SaUZnNlp6T3hsLVdiMGhKaXhsV1FNSUNQMHlvQ19qdk56SEF0d2RXVFctS0VPT25kNGZCRDdvZ2dxU0VoUUJKU0ZBd0ZycFNEZFh0T3ZjOA?oc=5</t>
         </is>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
@@ -4854,7 +4948,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>noticia:14iwzop</t>
+          <t>noticia:1c1ju1f</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4864,15 +4958,15 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-24 13:40</t>
+          <t>2026-10-24 17:02</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1792863623000</v>
+        <v>1792875752000</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>EL DÍA - Noticias de Bolivia para el mundo</t>
+          <t>La Razón Digital Bolivia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -4890,13 +4984,13 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a Mayaya deja siete heridos de la agrupación Los Chicos Fieles - EL DÍA - Noticias de Bolivia para el mundo</t>
+          <t>Accidente en la carretera a los Yungas deja siete heridos - La Razón Digital Bolivia</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPeGd3VWpCWXJ0YTJIeDJLcktzWG1jdUh0TjFXb01wSTkxbHNXZU94VWNDMkxnTjlJZVdpbkprMEY2NE80RXYyUWxUQXVnbl9lUXR2b28zTEh6cTJLVEQ4TUNja2kzRlhadVBFZFVwV1U2TlhseXZMZ20zZTZiUFpWRjdCOWNBMHU5XzdMV3JqQjV4TEE3bHRMOXR6Nm55eHZUNnFHSDdVRk8zVkY4RkVsUUtUN0JYdkREWGZncmJ3ZWc2T1BuUm1ZLTlfcHVabFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPTGQwaVBfdG1JdVRMUTN4LVVvN0ppc3dreDJVVllDR3RmX0xpMzB4b0pvVTNSV1B6T0ZEWTdEZkNsRUdSNzhLaC1CWHN5WktNWk1nRWpTdVZiYjI3TlJlX2xlVTI5MjlRU2hiY1gteml4YWVFbDNPSVRBZmtITlQzbmhaUXVmcThRa2xsQTJIOXZuNzlSdm12MEdyOEZHdw?oc=5</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -4919,7 +5013,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>noticia:1ukcn97</t>
+          <t>noticia:14iwzop</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4929,15 +5023,15 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-24 13:26</t>
+          <t>2026-10-24 13:40</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1792862794000</v>
+        <v>1792863623000</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>El Deber</t>
+          <t>EL DÍA - Noticias de Bolivia para el mundo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -4955,20 +5049,20 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Esta es la lista preliminar de los heridos en el accidente del grupo 'Los chicos fieles', el conductor está grave - El Deber</t>
+          <t>Accidente en la carretera a Mayaya deja siete heridos de la agrupación Los Chicos Fieles - EL DÍA - Noticias de Bolivia para el mundo</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOczZKbFd1QzRpak92LXpPWXZXQXJObnBQTG9qRFBlUUV5dThMWXhzckFFUHAyb2thU1JwRmJDSEZfaEdTUXh1bjZvQWpYMGhfUno3cWZ4MGpldEpoQXhzSlVzTm5LLW9OcjB2MWRsdHQ2UlI2SjEtZ085ZTR5Z3pEVmtBTF9lc29Kd0RhaTRUWkM4eGZJNWhBSXZqWmxuNW10dlQwYW9mdzItcWZWTkU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPeGd3VWpCWXJ0YTJIeDJLcktzWG1jdUh0TjFXb01wSTkxbHNXZU94VWNDMkxnTjlJZVdpbkprMEY2NE80RXYyUWxUQXVnbl9lUXR2b28zTEh6cTJLVEQ4TUNja2kzRlhadVBFZFVwV1U2TlhseXZMZ20zZTZiUFpWRjdCOWNBMHU5XzdMV3JqQjV4TEE3bHRMOXR6Nm55eHZUNnFHSDdVRk8zVkY4RkVsUUtUN0JYdkREWGZncmJ3ZWc2T1BuUm1ZLTlfcHVabFE?oc=5</t>
         </is>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
@@ -4984,7 +5078,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>noticia:2avehj</t>
+          <t>noticia:1ukcn97</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4994,20 +5088,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-24 12:53</t>
+          <t>2026-10-24 13:26</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1792860813000</v>
+        <v>1792862794000</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>El Deber</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>climatológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -5020,52 +5114,36 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Sequía en Cochabamba: más de un centenar de cabezas de ganado murieron en el cono sur - Red Uno</t>
+          <t>Esta es la lista preliminar de los heridos en el accidente del grupo 'Los chicos fieles', el conductor está grave - El Deber</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOOFQxc2Vzc0QwS19ydC13RkRPZnZQU3JkSTl5U3kzdUdMSldTcm5HVEhWRzZyN19CLUlwcUs4MW03Ui1obVBtdzQ3QWFQc1RKdzh3MXJ5QkpRS2pRNm50V1lVb09ScGJnaVVlemVfZlRsWjdObnRmR1FGMnlMMHAyc2pMandndy10T2twcWx6OFh4UHdvbVlFbllwME9WQ2pQVjNTQzBxeTg5YnF3bDREeHVDYXpObFFIaTZZQWtYUE12cGQ1ZGRhT0syNjVhZWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOczZKbFd1QzRpak92LXpPWXZXQXJObnBQTG9qRFBlUUV5dThMWXhzckFFUHAyb2thU1JwRmJDSEZfaEdTUXh1bjZvQWpYMGhfUno3cWZ4MGpldEpoQXhzSlVzTm5LLW9OcjB2MWRsdHQ2UlI2SjEtZ085ZTR5Z3pEVmtBTF9lc29Kd0RhaTRUWkM4eGZJNWhBSXZqWmxuNW10dlQwYW9mdzItcWZWTkU0?oc=5</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>-17.39</v>
-      </c>
-      <c r="O19" t="n">
-        <v>-66.16</v>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Cochabamba, Cochabamba</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>noticia:1ksmg5u</t>
+          <t>noticia:2avehj</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5075,20 +5153,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-24 11:43</t>
+          <t>2026-10-24 12:53</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1792856591000</v>
+        <v>1792860813000</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>climatológica</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -5101,36 +5179,52 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Embarrancamiento deja heridos a integrantes de Los Chicos Fieles - La Patria Bolivia</t>
+          <t>Sequía en Cochabamba: más de un centenar de cabezas de ganado murieron en el cono sur - Red Uno</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNeEFrOEtOMHZxMW42REFPU0x1MG5oQjlBMkJucWRLZ292alBXekJKeURBN3NLTVVadWI0OWF4UGtSVXBzTE01eWFSU1kyMUhNZ04zMWNMaUxnMDBBZ0EwTktXbjlaVTBUUmNqa3AwY19KNTU2LWh5LW9IVElVdTdnaHFPanJPd2FqMUxzaUhXZmVpYU1saGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOOFQxc2Vzc0QwS19ydC13RkRPZnZQU3JkSTl5U3kzdUdMSldTcm5HVEhWRzZyN19CLUlwcUs4MW03Ui1obVBtdzQ3QWFQc1RKdzh3MXJ5QkpRS2pRNm50V1lVb09ScGJnaVVlemVfZlRsWjdObnRmR1FGMnlMMHAyc2pMandndy10T2twcWx6OFh4UHdvbVlFbllwME9WQ2pQVjNTQzBxeTg5YnF3bDREeHVDYXpObFFIaTZZQWtYUE12cGQ1ZGRhT0syNjVhZWs?oc=5</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-17.39</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-66.16</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Cochabamba, Cochabamba</t>
+        </is>
+      </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>noticia:mlyqgd</t>
+          <t>noticia:1ksmg5u</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5140,15 +5234,15 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-24 11:30</t>
+          <t>2026-10-24 11:43</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1792855818000</v>
+        <v>1792856591000</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Opinión Bolivia</t>
+          <t>La Patria Bolivia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -5166,20 +5260,20 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a Mayaya deja siete heridos de la agrupación Los Chicos Fieles - Opinión Bolivia</t>
+          <t>Embarrancamiento deja heridos a integrantes de Los Chicos Fieles - La Patria Bolivia</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYjNxaHg3YllRRTJYdFd1clAtUlROSGlFNVg5eUVZUGJoOEZ4MWM5QU5WQm1YTDc4NXc3SjhWMUw0TkZfSHlMLUQ1bmpTME1Kb1JaM0ExamFHYTd3VlU4MXRWdTZ1bzh1SGYtbGE1a3dBaG93bjg1OGc0S0JfRE43c3dVMVltN0dQQzNhQUNhM0FjVUNRUDRSamlJYlk2dEJpUTBuY2hBcTFucTVRN0ZtYnc5bzdmTV9LQm1uVUxaZS1tUE9IejhBVDRCdU_SAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNeEFrOEtOMHZxMW42REFPU0x1MG5oQjlBMkJucWRLZ292alBXekJKeURBN3NLTVVadWI0OWF4UGtSVXBzTE01eWFSU1kyMUhNZ04zMWNMaUxnMDBBZ0EwTktXbjlaVTBUUmNqa3AwY19KNTU2LWh5LW9IVElVdTdnaHFPanJPd2FqMUxzaUhXZmVpYU1saGc?oc=5</t>
         </is>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
@@ -5195,7 +5289,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>noticia:irf4jl</t>
+          <t>noticia:mlyqgd</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5237,7 +5331,7 @@
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNMXlMNXFWSWhhWWNDRFFKMncwS2JGWm0tWlJCd2x2RjZhdFhEQ0lBcVlFSS1WRVYxMEVJTWRHcTY3M0stdWhGdnVPRU13X2MwSVRWX25xVUQxa0R6Z1pqQ2dfY0VjUmw2aXFoWFNVNk15N2dBOENZLWlGSWJfMW0zejVoZ3ZwVHVQV1MzbzlnUlpRcWIxMHZxdkItZTc0QmMyRnBmSVRtVnZ5Y3gtdVpYNXFwcGdadGVCU3dRZ3EwOTdiWHU4OXJRdEFoNi1HcnA1U0HSAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYjNxaHg3YllRRTJYdFd1clAtUlROSGlFNVg5eUVZUGJoOEZ4MWM5QU5WQm1YTDc4NXc3SjhWMUw0TkZfSHlMLUQ1bmpTME1Kb1JaM0ExamFHYTd3VlU4MXRWdTZ1bzh1SGYtbGE1a3dBaG93bjg1OGc0S0JfRE43c3dVMVltN0dQQzNhQUNhM0FjVUNRUDRSamlJYlk2dEJpUTBuY2hBcTFucTVRN0ZtYnc5bzdmTV9LQm1uVUxaZS1tUE9IejhBVDRCdU_SAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -5260,7 +5354,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>noticia:1g006zh</t>
+          <t>noticia:irf4jl</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5270,15 +5364,15 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-24 11:25</t>
+          <t>2026-10-24 11:30</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1792855522000</v>
+        <v>1792855818000</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>El Potosí</t>
+          <t>Opinión Bolivia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -5296,13 +5390,13 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a Mayaya deja siete heridos del grupo Los Chicos Fieles - El Potosí</t>
+          <t>Accidente en la carretera a Mayaya deja siete heridos de la agrupación Los Chicos Fieles - Opinión Bolivia</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTC10eC1qSm1WRlY2YzA3VEJqOG1LUkx6bE9PdFYwTFBZMGFjU0RMYXliRkhXcTJHRlVzb0Y4QUU0WWJDQ1plS2NZamZ1YmFadE5qY3g4UE5aYVAwamtCUUNZaDB2YWJTdWRKS3R4a0hHUjVobUl0Y1dYZ2JPczAwak5kN1hjUEwwM1NtUDVWbnAzWTdnRng3RjFValFVVlZPdVZnWFlUODhPOE5aMTROQzVKVjVRS2VoaTlaQnBiUGRTNFk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNMXlMNXFWSWhhWWNDRFFKMncwS2JGWm0tWlJCd2x2RjZhdFhEQ0lBcVlFSS1WRVYxMEVJTWRHcTY3M0stdWhGdnVPRU13X2MwSVRWX25xVUQxa0R6Z1pqQ2dfY0VjUmw2aXFoWFNVNk15N2dBOENZLWlGSWJfMW0zejVoZ3ZwVHVQV1MzbzlnUlpRcWIxMHZxdkItZTc0QmMyRnBmSVRtVnZ5Y3gtdVpYNXFwcGdadGVCU3dRZ3EwOTdiWHU4OXJRdEFoNi1HcnA1U0HSAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -5311,60 +5405,44 @@
       <c r="M23" t="n">
         <v>7</v>
       </c>
-      <c r="N23" t="n">
-        <v>-19.58</v>
-      </c>
-      <c r="O23" t="n">
-        <v>-65.75</v>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Potosí, Potosí</t>
-        </is>
-      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>clima:Potosí:2026-10-24:viento:1</t>
+          <t>noticia:1g006zh</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-24 10:55</t>
+          <t>2026-10-24 11:25</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1792853727284</v>
+        <v>1792855522000</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>El Potosí</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5377,24 +5455,20 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Potosí 2026-10-24: 60.5 km/h de ráfagas pronosticadas</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
-        </is>
-      </c>
+          <t>Accidente en la carretera a Mayaya deja siete heridos del grupo Los Chicos Fieles - El Potosí</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTC10eC1qSm1WRlY2YzA3VEJqOG1LUkx6bE9PdFYwTFBZMGFjU0RMYXliRkhXcTJHRlVzb0Y4QUU0WWJDQ1plS2NZamZ1YmFadE5qY3g4UE5aYVAwamtCUUNZaDB2YWJTdWRKS3R4a0hHUjVobUl0Y1dYZ2JPczAwak5kN1hjUEwwM1NtUDVWbnAzWTdnRng3RjFValFVVlZPdVZnWFlUODhPOE5aMTROQzVKVjVRS2VoaTlaQnBiUGRTNFk?oc=5</t>
         </is>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N24" t="n">
         <v>-19.58</v>
@@ -5404,12 +5478,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Potosí, Potosí</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>capital (pronóstico puntual)</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -5426,25 +5500,25 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>noticia:1ax0bpy</t>
+          <t>clima:Potosí:2026-10-24:viento:1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-24 10:32</t>
+          <t>2026-10-24 10:55</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1792852364000</v>
+        <v>1792853727284</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Que Pasa Salta</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5453,22 +5527,26 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Creció el Bermejo tras la tormenta: así está el puerto de chalanas en este momento - Que Pasa Salta</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+          <t>Potosí 2026-10-24: 60.5 km/h de ráfagas pronosticadas</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVld9IBfkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVldw?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -5478,59 +5556,59 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>-22.721</v>
+        <v>-19.58</v>
       </c>
       <c r="O25" t="n">
-        <v>-64.32599999999999</v>
+        <v>-65.75</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bermejo, Tarija</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
+          <t>capital (pronóstico puntual)</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Tarija</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>Bermejo</t>
+          <t>Potosí</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>gdacs:WF1033142:0</t>
+          <t>noticia:1ax0bpy</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>gdacs</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-24 07:06</t>
+          <t>2026-10-24 10:32</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1792839995000</v>
+        <v>1792852364000</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>GDACS</t>
+          <t>Que Pasa Salta</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5543,17 +5621,13 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Green forest fire notification in Bolivia</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>On 21/10/2026, a forest fire started in Bolivia, until 24/10/2026.</t>
-        </is>
-      </c>
+          <t>Creció el Bermejo tras la tormenta: así está el puerto de chalanas en este momento - Que Pasa Salta</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>http://www.gdacs.org/report.aspx?eventtype=WF&amp;eventid=1033142</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVld9IBfkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVldw?oc=5</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -5563,59 +5637,59 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>-13.06332</v>
+        <v>-22.721</v>
       </c>
       <c r="O26" t="n">
-        <v>-67.66426</v>
+        <v>-64.32599999999999</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Bermejo, Tarija</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>coordenada de la fuente</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Tarija</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Ixiamas</t>
+          <t>Bermejo</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>noticia:1shhqva</t>
+          <t>gdacs:WF1033142:0</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>gdacs</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-10-24 06:33</t>
+          <t>2026-10-24 07:06</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1792838034000</v>
+        <v>1792839995000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>GDACS</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5628,13 +5702,17 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
+          <t>Green forest fire notification in Bolivia</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>On 21/10/2026, a forest fire started in Bolivia, until 24/10/2026.</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQYzB6N082XzFRRnVtcDVmUkYyWjcxUzV2Z3Frd1I0WDNXSnZtY0QzOU1PUkNLMktVT1Vra2FSeXhxZDRuOFZYZjFwejl6ejJTbWY2MGJuSGN3ZHdrdG5JUkgzSXBkbDYtaHlackY3OVFuNWdLcFNpdWNHRU9vNGdoVWx2ODFVdzJXYUxnM0tUcjJvZmc?oc=5</t>
+          <t>http://www.gdacs.org/report.aspx?eventtype=WF&amp;eventid=1033142</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -5644,82 +5722,78 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>-17.97</v>
+        <v>-13.06332</v>
       </c>
       <c r="O27" t="n">
-        <v>-67.11</v>
+        <v>-67.66426</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
+          <t>coordenada de la fuente</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Ixiamas</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>clima:Potosí:2026-10-25:viento:1</t>
+          <t>noticia:1shhqva</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-10-24 02:55</t>
+          <t>2026-10-24 06:33</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1792824927736</v>
+        <v>1792838034000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Potosí 2026-10-25: 60.5 km/h de ráfagas pronosticadas</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
-        </is>
-      </c>
+          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQYzB6N082XzFRRnVtcDVmUkYyWjcxUzV2Z3Frd1I0WDNXSnZtY0QzOU1PUkNLMktVT1Vra2FSeXhxZDRuOFZYZjFwejl6ejJTbWY2MGJuSGN3ZHdrdG5JUkgzSXBkbDYtaHlackY3OVFuNWdLcFNpdWNHRU9vNGdoVWx2ODFVdzJXYUxnM0tUcjJvZmc?oc=5</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -5729,59 +5803,59 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>-19.58</v>
+        <v>-17.97</v>
       </c>
       <c r="O28" t="n">
-        <v>-65.75</v>
+        <v>-67.11</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Oruro, Oruro</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>capital (pronóstico puntual)</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Oruro</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Oruro</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>noticia:mz6q0s</t>
+          <t>clima:Potosí:2026-10-25:viento:1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-10-23 23:09</t>
+          <t>2026-10-24 02:55</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1792811349000</v>
+        <v>1792824927736</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5794,36 +5868,56 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Revelan lista preliminar de heridos tras accidente de Los Chicos Fieles - Red Uno</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
+          <t>Potosí 2026-10-25: 60.5 km/h de ráfagas pronosticadas</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPczBQcnE2SzFGMXc3b1lsTkNxVWRmS3Vnb01xOTV2WmVva3J2RVlteWpHZ3VJS2dNWGV5NW5FX3ZncnVKTEVDTGpBRndTU1FxeWxtaS1fb1FscGxXMWNXUE9zbHdob1AxVFl1eHB5OU1yUnNoOXJ6U21oVG9PVDA1ak1xQl9hUlB4V0RaQXJqZENGUm8zMUJEY3J0WW5ENE5ObWJLNmpWN0RkSmFJbnZUZGR5UFRPd3QyUFY4WQ?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
-      </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-19.58</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-65.75</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Potosí</t>
+        </is>
+      </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
+          <t>capital (pronóstico puntual)</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Potosí</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Potosí</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>noticia:1uil931</t>
+          <t>noticia:mz6q0s</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5833,15 +5927,15 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-10-23 22:49</t>
+          <t>2026-10-23 23:09</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1792810149000</v>
+        <v>1792811349000</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>El Deber</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -5859,13 +5953,13 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Accidente de tránsito en la ruta hacia Alto Beni deja varios heridos - El Deber</t>
+          <t>Revelan lista preliminar de heridos tras accidente de Los Chicos Fieles - Red Uno</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQakFJRmx3RlJEMkVHU0pxWXZ2ZU1ib04tZy1yeTB2OGhrYk9CU3pMaDVpRThNZktZMS14UzA2Y1VIcEQtZDg3cEU2SmlzQnBmUVVvM0ZNYzZWNExWUXQ3aHpnd3lqOHFVV3pNbDRLS1NQNGtwb2RjSFpleHJkOG5zSXVtWjVIS1dLejNybktRWTJVZXh3WkFUQVE5T2tMdFdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPczBQcnE2SzFGMXc3b1lsTkNxVWRmS3Vnb01xOTV2WmVva3J2RVlteWpHZ3VJS2dNWGV5NW5FX3ZncnVKTEVDTGpBRndTU1FxeWxtaS1fb1FscGxXMWNXUE9zbHdob1AxVFl1eHB5OU1yUnNoOXJ6U21oVG9PVDA1ak1xQl9hUlB4V0RaQXJqZENGUm8zMUJEY3J0WW5ENE5ObWJLNmpWN0RkSmFJbnZUZGR5UFRPd3QyUFY4WQ?oc=5</t>
         </is>
       </c>
       <c r="L30" t="n">
@@ -5874,37 +5968,21 @@
       <c r="M30" t="n">
         <v>1</v>
       </c>
-      <c r="N30" t="n">
-        <v>-15.578</v>
-      </c>
-      <c r="O30" t="n">
-        <v>-67.44</v>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Alto Beni, La Paz</t>
-        </is>
-      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>La Paz</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>Alto Beni</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>noticia:1tliu4i</t>
+          <t>noticia:1uil931</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5914,11 +5992,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-10-23 22:18</t>
+          <t>2026-10-23 22:49</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1792808330000</v>
+        <v>1792810149000</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -5946,7 +6024,7 @@
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQMF9BNnUzLURKNGRMUUJ1VXVRSXNnMlBsQnVXOG0tRlFtY3pvRDNPQmNJMWN2RzJVaWdoWndmcHFnTkZFZnJxRkZtMThYYWlwN09ueUgtei1pSE1hZ2FtSzN6elY4VXJHbzFxdll0eWh0ZkxwQkQ1SDZ5b0E3MlVENGZEWGZHUGlwVG4wd2x3OFNEMVpibnFr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQakFJRmx3RlJEMkVHU0pxWXZ2ZU1ib04tZy1yeTB2OGhrYk9CU3pMaDVpRThNZktZMS14UzA2Y1VIcEQtZDg3cEU2SmlzQnBmUVVvM0ZNYzZWNExWUXQ3aHpnd3lqOHFVV3pNbDRLS1NQNGtwb2RjSFpleHJkOG5zSXVtWjVIS1dLejNybktRWTJVZXh3WkFUQVE5T2tMdFdn?oc=5</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -5985,7 +6063,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>noticia:1twc9ul</t>
+          <t>noticia:1tliu4i</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5995,11 +6073,11 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-23 22:16</t>
+          <t>2026-10-23 22:18</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1792808192000</v>
+        <v>1792808330000</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -6027,7 +6105,7 @@
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNbmwzSnd6c2tFMXBWY0tiemJqRm5CNllOT2p1U0FhdW5QNGFBVXlSZVM1ak5jNGZvcXNVaUQzN3ZQQTlPbmVjQ2Y5RFl2dWVLeUN5NUFodDF0alEyZWlmOHFZWkVVbjdQbkl3ZWtmS25wQWM2TmRZZDBGM2xlS0ZhUzAweXRmcmhVWGY5dV9CUnFBNGtWZHZDSWVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQMF9BNnUzLURKNGRMUUJ1VXVRSXNnMlBsQnVXOG0tRlFtY3pvRDNPQmNJMWN2RzJVaWdoWndmcHFnTkZFZnJxRkZtMThYYWlwN09ueUgtei1pSE1hZ2FtSzN6elY4VXJHbzFxdll0eWh0ZkxwQkQ1SDZ5b0E3MlVENGZEWGZHUGlwVG4wd2x3OFNEMVpibnFr?oc=5</t>
         </is>
       </c>
       <c r="L32" t="n">
@@ -6066,7 +6144,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>noticia:1dygpkp</t>
+          <t>noticia:1twc9ul</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6076,15 +6154,15 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-23 21:39</t>
+          <t>2026-10-23 22:16</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1792805983000</v>
+        <v>1792808192000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>El Deber</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6093,39 +6171,39 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>(Video) Así rescataron a uno de los integrantes de Los Chicos Fieles tras accidente en Caranavi - Red Uno</t>
+          <t>Accidente de tránsito en la ruta hacia Alto Beni deja varios heridos - El Deber</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOdTVUZUQxVTdvYTdONDQxVlhUTzBOS2hKLW1rS1NUcmRYRnlCVlhIcHZlSjdsaktkQm5CWkFYa3lDQkxnMlh0b3prX0lha1BtbW1qS1VuYnNiX3FiZkYyNDJDR0tqZ0pKMU5TeC04SXV4UUJOTUlPUTB6ek01bzUxTUsydjZqZzI3S3ZLUnRWSUFUVk44WEpKUl9rbzRLb2IwYl9sLVlrYmt5d2ZHNUtGd3lRNnYzMlhuMkJOZW1XSUl2N1BxZWpHbm5XTDJhRUtnR190QWQ1TDlTUVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNbmwzSnd6c2tFMXBWY0tiemJqRm5CNllOT2p1U0FhdW5QNGFBVXlSZVM1ak5jNGZvcXNVaUQzN3ZQQTlPbmVjQ2Y5RFl2dWVLeUN5NUFodDF0alEyZWlmOHFZWkVVbjdQbkl3ZWtmS25wQWM2TmRZZDBGM2xlS0ZhUzAweXRmcmhVWGY5dV9CUnFBNGtWZHZDSWVB?oc=5</t>
         </is>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N33" t="n">
-        <v>-15.813</v>
+        <v>-15.578</v>
       </c>
       <c r="O33" t="n">
-        <v>-67.46299999999999</v>
+        <v>-67.44</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Caranavi, La Paz</t>
+          <t>Alto Beni, La Paz</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -6140,14 +6218,14 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>Caranavi</t>
+          <t>Alto Beni</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>noticia:3dv7b0</t>
+          <t>noticia:1dygpkp</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6157,15 +6235,15 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-10-23 21:35</t>
+          <t>2026-10-23 21:39</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1792805700000</v>
+        <v>1792805983000</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FmBolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6174,29 +6252,29 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Accidente en Caranavi: vehículo de Los Chicos Fieles cae a un barranco y deja varios heridos - FmBolivia</t>
+          <t>(Video) Así rescataron a uno de los integrantes de Los Chicos Fieles tras accidente en Caranavi - Red Uno</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNcE1KaHZyUTJCSElxRU9nVzdhTnczWjJGTEhFMEs0bHp2cUdFeHd3VTB0NmVFcjdEN1dsZDZLY2k1ZFFUWkhKV19PU3V2czNyamh1ZE9YajVSVF8xczF6OFhZcWFvYV9EcWg4ZDNCb2p3enhXbFpRYnJMdGdaTXNrWUZSYVhKNTVicWlCLTJ5OE05Z1BvNEx1eEloUk5qTGN3ZHNzbzZWSVljbnRmSERJUWdxRDc0MjJxMGtycWJaaVhXQUUxVUlaWVZLOWE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOdTVUZUQxVTdvYTdONDQxVlhUTzBOS2hKLW1rS1NUcmRYRnlCVlhIcHZlSjdsaktkQm5CWkFYa3lDQkxnMlh0b3prX0lha1BtbW1qS1VuYnNiX3FiZkYyNDJDR0tqZ0pKMU5TeC04SXV4UUJOTUlPUTB6ek01bzUxTUsydjZqZzI3S3ZLUnRWSUFUVk44WEpKUl9rbzRLb2IwYl9sLVlrYmt5d2ZHNUtGd3lRNnYzMlhuMkJOZW1XSUl2N1BxZWpHbm5XTDJhRUtnR190QWQ1TDlTUVk?oc=5</t>
         </is>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>-15.813</v>
@@ -6228,30 +6306,30 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-24:viento:1</t>
+          <t>noticia:3dv7b0</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-23 20:55</t>
+          <t>2026-10-23 21:35</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1792803329663</v>
+        <v>1792805700000</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>FmBolivia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6264,74 +6342,70 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-24: 78.1 km/h de ráfagas pronosticadas</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
-        </is>
-      </c>
+          <t>Accidente en Caranavi: vehículo de Los Chicos Fieles cae a un barranco y deja varios heridos - FmBolivia</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNcE1KaHZyUTJCSElxRU9nVzdhTnczWjJGTEhFMEs0bHp2cUdFeHd3VTB0NmVFcjdEN1dsZDZLY2k1ZFFUWkhKV19PU3V2czNyamh1ZE9YajVSVF8xczF6OFhZcWFvYV9EcWg4ZDNCb2p3enhXbFpRYnJMdGdaTXNrWUZSYVhKNTVicWlCLTJ5OE05Z1BvNEx1eEloUk5qTGN3ZHNzbzZWSVljbnRmSERJUWdxRDc0MjJxMGtycWJaaVhXQUUxVUlaWVZLOWE?oc=5</t>
         </is>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" t="n">
-        <v>-17.78</v>
+        <v>-15.813</v>
       </c>
       <c r="O35" t="n">
-        <v>-63.18</v>
+        <v>-67.46299999999999</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Caranavi, La Paz</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>capital (pronóstico puntual)</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Caranavi</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>noticia:rabz5p</t>
+          <t>clima:Santa Cruz:2026-10-24:viento:1</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-10-23 20:44</t>
+          <t>2026-10-23 20:55</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1792802686000</v>
+        <v>1792803329663</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -6340,22 +6414,26 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Tome previsiones: se pronostican lluvias y ambiente caluroso para este fin de semana en Cochabamba - Red Uno</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
+          <t>Santa Cruz 2026-10-24: 78.1 km/h de ráfagas pronosticadas</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTlU5NVFpY1RheTN5ZE1IbG5VYTh2Sk5hZHpHeWI3LVdnSFg2cFJFdnBCVkxiUjNKcUgyUW16SWxpMXFkMHdad2xFN043bklJeG1iQ0V1V3hBZk1Ga3NscjdPVWUySmt4bDNTdWlmSUdOMmNlZ2hkSWZFMmk4VGs0Nm9TcnRCTDhINmtnQU9zZDBUY05HcWpxN3FOX3N1dmVJblE0MGc5di1Ma1N2dGNxOUtoV1MzNnl1OXpRaTZ2UGxMc3RDWndubHVQNUd0eVROMGR2OGxVemtOaEc4bTNRaA?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L36" t="n">
@@ -6365,36 +6443,36 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>-17.39</v>
+        <v>-17.78</v>
       </c>
       <c r="O36" t="n">
-        <v>-66.16</v>
+        <v>-63.18</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Cochabamba, Cochabamba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
+          <t>capital (pronóstico puntual)</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>noticia:1jfk053</t>
+          <t>noticia:rabz5p</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -6404,11 +6482,11 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-10-23 19:08</t>
+          <t>2026-10-23 20:44</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1792796931000</v>
+        <v>1792802686000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -6417,43 +6495,43 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>climatológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Sequía en Pasorapa: el ganado muere por falta de agua y alistan declaratoria de desastre - Red Uno</t>
+          <t>Tome previsiones: se pronostican lluvias y ambiente caluroso para este fin de semana en Cochabamba - Red Uno</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNQVhTWE8zdE1BQ3lueWJPeV9wUDNsSmJpS0NJTWppMUY4QmlQSUFHVjRORmtrVHQ3MHB0T1pyS25PamxnY0hBQUtzOVRvSUNaUkdGb1RWSGl4dFA4Z3VINVpQTk1pZUpDdUIyUU5hZS1oNGhBa1RWcFhScVMwVTFrVlJaOFQ4OWFqRWVUZ051bHVJTlMxRTBhRFVLUEV2dTZFdDgtRkxJM3VvN3YzUWJfVk41ZWR5U1JoNmx0WFFkMmNTWGVleGNIQlNxWUJzdHIxSWtz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTlU5NVFpY1RheTN5ZE1IbG5VYTh2Sk5hZHpHeWI3LVdnSFg2cFJFdnBCVkxiUjNKcUgyUW16SWxpMXFkMHdad2xFN043bklJeG1iQ0V1V3hBZk1Ga3NscjdPVWUySmt4bDNTdWlmSUdOMmNlZ2hkSWZFMmk4VGs0Nm9TcnRCTDhINmtnQU9zZDBUY05HcWpxN3FOX3N1dmVJblE0MGc5di1Ma1N2dGNxOUtoV1MzNnl1OXpRaTZ2UGxMc3RDWndubHVQNUd0eVROMGR2OGxVemtOaEc4bTNRaA?oc=5</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>-18.38</v>
+        <v>-17.39</v>
       </c>
       <c r="O37" t="n">
-        <v>-64.649</v>
+        <v>-66.16</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Pasorapa, Cochabamba</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -6468,14 +6546,14 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>Pasorapa</t>
+          <t>Cochabamba</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>noticia:ix3l8o</t>
+          <t>noticia:1jfk053</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6485,56 +6563,56 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-10-23 18:25</t>
+          <t>2026-10-23 19:08</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1792794310000</v>
+        <v>1792796931000</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Visión 360</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>climatológica</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Oruro evalúa suspender clases presenciales por más de 200 casos de Coxsackie - Visión 360</t>
+          <t>Sequía en Pasorapa: el ganado muere por falta de agua y alistan declaratoria de desastre - Red Uno</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0c9IBywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNQVhTWE8zdE1BQ3lueWJPeV9wUDNsSmJpS0NJTWppMUY4QmlQSUFHVjRORmtrVHQ3MHB0T1pyS25PamxnY0hBQUtzOVRvSUNaUkdGb1RWSGl4dFA4Z3VINVpQTk1pZUpDdUIyUU5hZS1oNGhBa1RWcFhScVMwVTFrVlJaOFQ4OWFqRWVUZ051bHVJTlMxRTBhRFVLUEV2dTZFdDgtRkxJM3VvN3YzUWJfVk41ZWR5U1JoNmx0WFFkMmNTWGVleGNIQlNxWUJzdHIxSWtz?oc=5</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>-17.97</v>
+        <v>-18.38</v>
       </c>
       <c r="O38" t="n">
-        <v>-67.11</v>
+        <v>-64.649</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>Pasorapa, Cochabamba</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -6544,19 +6622,19 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Pasorapa</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>noticia:1xqv9m7</t>
+          <t>noticia:ix3l8o</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6566,62 +6644,78 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-10-23 18:09</t>
+          <t>2026-10-23 18:25</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1792793370000</v>
+        <v>1792794310000</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>El Diario del centro del país</t>
+          <t>Visión 360</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Tres heridos en tremendo choque cerca de Oncativo - El Diario del centro del país</t>
+          <t>Oruro evalúa suspender clases presenciales por más de 200 casos de Coxsackie - Visión 360</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZERhbTJMQUJVb3hmZFlSZmRGZkdBLWdFTGJVQzdqZkE4aGhhWmdQZ2JDRW1ndkJLWU90VTZ6Ti1JOUZzcFZfcE1zbkRHU1B3YTF4UkVzdllFa1p3SUlObURGamF0Vm9kc3dPLTZVWFJ4NWZZQmlySElPNHhZTnRGNGNZUWw2ZlI1eVBEQkNGNEhLWTNiLWJLUS0xYjA0UWRhc0d6bVN4aVVLSVdsQWlpMUZYdWw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0c9IBywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0cw?oc=5</t>
         </is>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3</v>
-      </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>-17.97</v>
+      </c>
+      <c r="O39" t="n">
+        <v>-67.11</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Oruro, Oruro</t>
+        </is>
+      </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>noticia:1wuregl</t>
+          <t>noticia:1xqv9m7</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6631,78 +6725,62 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-10-23 15:39</t>
+          <t>2026-10-23 18:09</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1792784340000</v>
+        <v>1792793370000</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>FmBolivia</t>
+          <t>El Diario del centro del país</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>hidrológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Intensas lluvias inundan La Paz y activan alertas por el riesgo de desborde de ríos - FmBolivia</t>
+          <t>Tres heridos en tremendo choque cerca de Oncativo - El Diario del centro del país</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPZm85aHphekQ4U3BZZkp1ZkF6ZVdSUHgtZmltS1FxUUgza1AwcndWWDJZOWctT0RiVmVabmg5SG42NnJWMlJMMnBlYTlYaVdSb09sR0dnVDdpT29faTdiaDUtZElJdlQ3eTdjR2VsWjlta1FOS1U2Vm1vV3JwWkpvbEw1ZUR3akgwQTZnQnVENjJtVkQtVUpKVEJTeWNJSE1CaEFKa2VqMmZXbWk3ekR4ZWpmZ1Z3elFQaWNaNFJuMXA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZERhbTJMQUJVb3hmZFlSZmRGZkdBLWdFTGJVQzdqZkE4aGhhWmdQZ2JDRW1ndkJLWU90VTZ6Ti1JOUZzcFZfcE1zbkRHU1B3YTF4UkVzdllFa1p3SUlObURGamF0Vm9kc3dPLTZVWFJ4NWZZQmlySElPNHhZTnRGNGNZUWw2ZlI1eVBEQkNGNEhLWTNiLWJLUS0xYjA0UWRhc0d6bVN4aVVLSVdsQWlpMUZYdWw?oc=5</t>
         </is>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>-16.169</v>
-      </c>
-      <c r="O40" t="n">
-        <v>-68.09</v>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>La Paz, La Paz</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>La Paz</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>Nuestra Señora de La Paz</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>noticia:1570kkf</t>
+          <t>noticia:1wuregl</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6712,20 +6790,20 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-10-23 15:28</t>
+          <t>2026-10-23 15:39</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1792783705000</v>
+        <v>1792784340000</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>FmBolivia</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>hidrológica</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6738,13 +6816,13 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>¿Se suspenden las clases en Oruro? Más de 200 casos de Coxsackie activan evaluaciones - Red Uno</t>
+          <t>Intensas lluvias inundan La Paz y activan alertas por el riesgo de desborde de ríos - FmBolivia</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNMFdHaVpKRmMyOENDYm16UXJPenVSQnpmTE94bDc4UFhqakluMUdvZjAwamUxT3BVWUpJQm8xVHBWengxQmhWM1hjU3d2YXFrLXpVU2VrZDJiMXZLMlQ5bGxGOHFETFhYM0s2RjlUTlhkd0g2eXQweDFHaTlKNGNMUlJfOWg2a0JjTklXUWZKc1BmUXZuZFZ2MF9fV2lEYUY4LXNiNmk3cF9FNjVtTl9GWFotT2ltS0xXTnM1dENvSU9kbFRMalFrYVdXOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPZm85aHphekQ4U3BZZkp1ZkF6ZVdSUHgtZmltS1FxUUgza1AwcndWWDJZOWctT0RiVmVabmg5SG42NnJWMlJMMnBlYTlYaVdSb09sR0dnVDdpT29faTdiaDUtZElJdlQ3eTdjR2VsWjlta1FOS1U2Vm1vV3JwWkpvbEw1ZUR3akgwQTZnQnVENjJtVkQtVUpKVEJTeWNJSE1CaEFKa2VqMmZXbWk3ekR4ZWpmZ1Z3elFQaWNaNFJuMXA?oc=5</t>
         </is>
       </c>
       <c r="L41" t="n">
@@ -6754,14 +6832,14 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>-17.97</v>
+        <v>-16.169</v>
       </c>
       <c r="O41" t="n">
-        <v>-67.11</v>
+        <v>-68.09</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>La Paz, La Paz</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -6771,19 +6849,19 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Nuestra Señora de La Paz</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>noticia:1nzu2o8</t>
+          <t>noticia:1570kkf</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6793,39 +6871,39 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-10-23 15:20</t>
+          <t>2026-10-23 15:28</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1792783236000</v>
+        <v>1792783705000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>hidrológica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Alerta naranja por posibles desbordes en tres departamentos (15:20) - El Diario - Bolivia</t>
+          <t>¿Se suspenden las clases en Oruro? Más de 200 casos de Coxsackie activan evaluaciones - Red Uno</t>
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPTnBESV9OODZhNjY3T2M2X2NZcmk4clI0eFZsd3VLMVRwaUlSdF9wanZyVGxDNUlNTm5wbGpLN1lvX09mNGxFVkpIZDNGdi1pNDdfSGlESThfeVloQzJsNUMyNUpWUDhzTVJiYWJpNkQ1RHliRWljZlp3SlhtZ2FhU0pvV0syUmZIejJZWHlRdTBOTG4zaTc5cEsycW9IcEx2SkQtN01Gendlb1VR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNMFdHaVpKRmMyOENDYm16UXJPenVSQnpmTE94bDc4UFhqakluMUdvZjAwamUxT3BVWUpJQm8xVHBWengxQmhWM1hjU3d2YXFrLXpVU2VrZDJiMXZLMlQ5bGxGOHFETFhYM0s2RjlUTlhkd0g2eXQweDFHaTlKNGNMUlJfOWg2a0JjTklXUWZKc1BmUXZuZFZ2MF9fV2lEYUY4LXNiNmk3cF9FNjVtTl9GWFotT2ltS0xXTnM1dENvSU9kbFRMalFrYVdXOA?oc=5</t>
         </is>
       </c>
       <c r="L42" t="n">
@@ -6834,21 +6912,37 @@
       <c r="M42" t="n">
         <v>0</v>
       </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
+      <c r="N42" t="n">
+        <v>-17.97</v>
+      </c>
+      <c r="O42" t="n">
+        <v>-67.11</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Oruro, Oruro</t>
+        </is>
+      </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>noticia:1itd1r7</t>
+          <t>noticia:1nzu2o8</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6858,39 +6952,39 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-10-23 15:01</t>
+          <t>2026-10-23 15:20</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1792782098000</v>
+        <v>1792783236000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>eju.tv</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>hidrológica</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Intensa lluvia y granizada en La Paz inundan vías y elevan el nivel de los ríos - eju.tv</t>
+          <t>Alerta naranja por posibles desbordes en tres departamentos (15:20) - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNWU9QWElKQXEyN3UxVm4xbzJzbEJ1TU1NTHZlRUp6YndmeU9GQnJKcTluVEJ2ZHQ5cGp3aWhlMUd5ektWQlBpUVNmZnZuRnJwMXlydzAzX0FBVnY5UDMzQTBkWVRNRUNJSlRvX3MyQVhMcEhIMW9WSUpXckVSd0RJWk1KMFBKWmJNU3diQVlEN1Y5aVV6eVBaZXpOMnFIWWxaMlRlY0ZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPTnBESV9OODZhNjY3T2M2X2NZcmk4clI0eFZsd3VLMVRwaUlSdF9wanZyVGxDNUlNTm5wbGpLN1lvX09mNGxFVkpIZDNGdi1pNDdfSGlESThfeVloQzJsNUMyNUpWUDhzTVJiYWJpNkQ1RHliRWljZlp3SlhtZ2FhU0pvV0syUmZIejJZWHlRdTBOTG4zaTc5cEsycW9IcEx2SkQtN01Gendlb1VR?oc=5</t>
         </is>
       </c>
       <c r="L43" t="n">
@@ -6899,37 +6993,21 @@
       <c r="M43" t="n">
         <v>0</v>
       </c>
-      <c r="N43" t="n">
-        <v>-16.169</v>
-      </c>
-      <c r="O43" t="n">
-        <v>-68.09</v>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>La Paz, La Paz</t>
-        </is>
-      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>La Paz</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>Nuestra Señora de La Paz</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>noticia:1l4xxfk</t>
+          <t>noticia:1itd1r7</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6939,20 +7017,20 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-10-23 14:51</t>
+          <t>2026-10-23 15:01</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1792781480000</v>
+        <v>1792782098000</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>eju.tv</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6965,13 +7043,13 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
+          <t>Intensa lluvia y granizada en La Paz inundan vías y elevan el nivel de los ríos - eju.tv</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQS2FPaHd3UnFBRjRoa0lKUm1MNUQ5S00zN1RJZE5fWlVUQnhiY0lLcFRkY2JZak1mZ0c2WEVMVUNJVUJTMGFLNHg4S2ZKNTRqLXJHM09ET19hX1pZeTQwUkdEc2huTHVpcno2QTRZbnhralVRWXozcWc1a2pHUEpBeTV1cWgzTWRwaDEweURKeVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNWU9QWElKQXEyN3UxVm4xbzJzbEJ1TU1NTHZlRUp6YndmeU9GQnJKcTluVEJ2ZHQ5cGp3aWhlMUd5ektWQlBpUVNmZnZuRnJwMXlydzAzX0FBVnY5UDMzQTBkWVRNRUNJSlRvX3MyQVhMcEhIMW9WSUpXckVSd0RJWk1KMFBKWmJNU3diQVlEN1Y5aVV6eVBaZXpOMnFIWWxaMlRlY0ZB?oc=5</t>
         </is>
       </c>
       <c r="L44" t="n">
@@ -6981,14 +7059,14 @@
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>-17.97</v>
+        <v>-16.169</v>
       </c>
       <c r="O44" t="n">
-        <v>-67.11</v>
+        <v>-68.09</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>La Paz, La Paz</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -6998,19 +7076,19 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Nuestra Señora de La Paz</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>noticia:51709n</t>
+          <t>noticia:1l4xxfk</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -7020,56 +7098,56 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-10-23 13:38</t>
+          <t>2026-10-23 14:51</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1792777139000</v>
+        <v>1792781480000</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>eju.tv</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - eju.tv</t>
+          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPcjZTSmprRGVoNlRqQmdBTE5VM3pRQ1ZFakFUbzVyMUhiaDVkT0liaG9UNEZXekV6bWsycUk4X1JCSEY5RjhNVlZaTk9ULUFuZkY3NnZuWmZ1a19leUhFdlIyQV9kLWxlSkxfeXFhcFRTZjZ2YkpQQlJ1dkNLMDBjaGZ4SkhyQ0RfcnhKSEg5WURCQVQwbENYTHEzUzJSaUEzMGo2bWdyS3lsM016LXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQS2FPaHd3UnFBRjRoa0lKUm1MNUQ5S00zN1RJZE5fWlVUQnhiY0lLcFRkY2JZak1mZ0c2WEVMVUNJVUJTMGFLNHg4S2ZKNTRqLXJHM09ET19hX1pZeTQwUkdEc2huTHVpcno2QTRZbnhralVRWXozcWc1a2pHUEpBeTV1cWgzTWRwaDEweURKeVE?oc=5</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>-17.764</v>
+        <v>-17.97</v>
       </c>
       <c r="O45" t="n">
-        <v>-62.903</v>
+        <v>-67.11</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Cotoca, Santa Cruz</t>
+          <t>Oruro, Oruro</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -7079,19 +7157,19 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Oruro</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>Cotoca</t>
+          <t>Oruro</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>noticia:11rddql</t>
+          <t>noticia:51709n</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -7101,56 +7179,56 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-10-23 13:22</t>
+          <t>2026-10-23 13:38</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1792776139000</v>
+        <v>1792777139000</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>eju.tv</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Intensifican acciones preventivas contra el dengue en Caranavi - El Diario - Bolivia</t>
+          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - eju.tv</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOMjhSeDJBek5iaFhDcnFzX1lKelgwZmUwLTJnbEhMdDRMelUxNks5Ti1pRHh3dDhTcC1YZEdqM3FJOGdqVHRvcXVhRlpCQzVDTEZMUFBkV1NrYVQ2LXRqTTBhcGRQc21CQ0VabzZaNExXb1BjTzJ2Uk5BcFF0VG5XOFNRa3lqUWlJSnRFUUVXYnNpbXB0LVVmSXVWSzJxcmVpdVVxUC1KOUhTQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPcjZTSmprRGVoNlRqQmdBTE5VM3pRQ1ZFakFUbzVyMUhiaDVkT0liaG9UNEZXekV6bWsycUk4X1JCSEY5RjhNVlZaTk9ULUFuZkY3NnZuWmZ1a19leUhFdlIyQV9kLWxlSkxfeXFhcFRTZjZ2YkpQQlJ1dkNLMDBjaGZ4SkhyQ0RfcnhKSEg5WURCQVQwbENYTHEzUzJSaUEzMGo2bWdyS3lsM016LXc?oc=5</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N46" t="n">
-        <v>-15.813</v>
+        <v>-17.764</v>
       </c>
       <c r="O46" t="n">
-        <v>-67.46299999999999</v>
+        <v>-62.903</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Caranavi, La Paz</t>
+          <t>Cotoca, Santa Cruz</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -7160,19 +7238,19 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>Caranavi</t>
+          <t>Cotoca</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>noticia:fcm3nx</t>
+          <t>noticia:11rddql</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -7182,62 +7260,78 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-10-23 12:58</t>
+          <t>2026-10-23 13:22</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1792774699000</v>
+        <v>1792776139000</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>[VIDEO] Así fue el accidente de moto que dejó un adolescente fallecido y un hombre gravemente herido - Red Uno</t>
+          <t>Intensifican acciones preventivas contra el dengue en Caranavi - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOSmJMazhUemNfRHpWcDBoTVFZMUpwdlVKVUtvUXZNTGRRRHlwLW5KNmNhcmFnd1czbi1yalhFMnpSS1dmUE9jVzNlOS1kMWZtRzBHZ2EtcDRDdU5Gc2JUQVIwM2xPa2lZVmswRi1SUFVPcm8xcHlGN3F2UThTSDdKMDNyYnJmVkcxazNLLVBLOWFYM09FVUpmVnN5RVhpSVo2V1VCVmFwQ1gzTmRUWVp2aXMwcmxHRS1GV2p3NTBtR2RzM2wwVHUzaGJkRXJYbHdvaDlhWm5YMTk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOMjhSeDJBek5iaFhDcnFzX1lKelgwZmUwLTJnbEhMdDRMelUxNks5Ti1pRHh3dDhTcC1YZEdqM3FJOGdqVHRvcXVhRlpCQzVDTEZMUFBkV1NrYVQ2LXRqTTBhcGRQc21CQ0VabzZaNExXb1BjTzJ2Uk5BcFF0VG5XOFNRa3lqUWlJSnRFUUVXYnNpbXB0LVVmSXVWSzJxcmVpdVVxUC1KOUhTQQ?oc=5</t>
         </is>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>1</v>
-      </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>-15.813</v>
+      </c>
+      <c r="O47" t="n">
+        <v>-67.46299999999999</v>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Caranavi, La Paz</t>
+        </is>
+      </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>La Paz</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Caranavi</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>noticia:1cjx1qd</t>
+          <t>noticia:fcm3nx</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -7247,78 +7341,62 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-10-23 12:39</t>
+          <t>2026-10-23 12:58</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1792773575000</v>
+        <v>1792774699000</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Más de 60 municipios en La Paz sufren falta de lluvias - La Patria Bolivia</t>
+          <t>[VIDEO] Así fue el accidente de moto que dejó un adolescente fallecido y un hombre gravemente herido - Red Uno</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE52Qi03Z1J6OS1CR2liRVZ0VlhCcmVQWFV6RUdGNXdrbzZRNXFjTWRaRnc1b3VoV0xaY3RIdncxNlNnYkxyUXo5MTlJWmMwWDNSMDE4ZHI2VkpWajFPaUF2SmRVYkk2eDZYQ1RfUU9ieENrZG9UVVFiaXZSeGI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOSmJMazhUemNfRHpWcDBoTVFZMUpwdlVKVUtvUXZNTGRRRHlwLW5KNmNhcmFnd1czbi1yalhFMnpSS1dmUE9jVzNlOS1kMWZtRzBHZ2EtcDRDdU5Gc2JUQVIwM2xPa2lZVmswRi1SUFVPcm8xcHlGN3F2UThTSDdKMDNyYnJmVkcxazNLLVBLOWFYM09FVUpmVnN5RVhpSVo2V1VCVmFwQ1gzTmRUWVp2aXMwcmxHRS1GV2p3NTBtR2RzM2wwVHUzaGJkRXJYbHdvaDlhWm5YMTk?oc=5</t>
         </is>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>-16.169</v>
-      </c>
-      <c r="O48" t="n">
-        <v>-68.09</v>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>La Paz, La Paz</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>La Paz</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>Nuestra Señora de La Paz</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>noticia:11y8tre</t>
+          <t>noticia:1cjx1qd</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -7328,56 +7406,56 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-10-23 11:43</t>
+          <t>2026-10-23 12:39</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1792770197000</v>
+        <v>1792773575000</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>La Patria Bolivia</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - Red Uno</t>
+          <t>Más de 60 municipios en La Paz sufren falta de lluvias - La Patria Bolivia</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOVGY3YVRLWWxYM0IycjF4dlNUeUhqZG90Yng4aWhmN3A5ai02WENWYnF4bWpoZHFKMGc1X0JPRHdRRVZfSlA4UmZFa2kxYkNIS3ZtQ1NvNlNCME51eVZTRkRKSUQ5MmRoaWl5Tkt5NHpPUEFwemN2YTV1djFwdHlqQnFqRHNPenhYcTlsanJPcXhpOVV1NmFBUXZyazQ2MkUzM0dSZy02ZllxTGtjcl9ldzdHSktTRlVaalZJc1pubUNQMWFTbzVEOUJ1UmhCdEJt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE52Qi03Z1J6OS1CR2liRVZ0VlhCcmVQWFV6RUdGNXdrbzZRNXFjTWRaRnc1b3VoV0xaY3RIdncxNlNnYkxyUXo5MTlJWmMwWDNSMDE4ZHI2VkpWajFPaUF2SmRVYkk2eDZYQ1RfUU9ieENrZG9UVVFiaXZSeGI?oc=5</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>-17.764</v>
+        <v>-16.169</v>
       </c>
       <c r="O49" t="n">
-        <v>-62.903</v>
+        <v>-68.09</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Cotoca, Santa Cruz</t>
+          <t>La Paz, La Paz</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -7387,42 +7465,42 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>Cotoca</t>
+          <t>Nuestra Señora de La Paz</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>clima:Sucre:2026-10-23:viento:1</t>
+          <t>noticia:11y8tre</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-10-23 06:55</t>
+          <t>2026-10-23 11:43</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1792752927735</v>
+        <v>1792770197000</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7435,56 +7513,52 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Sucre 2026-10-23: 66.2 km/h de ráfagas pronosticadas</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
-        </is>
-      </c>
+          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - Red Uno</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOVGY3YVRLWWxYM0IycjF4dlNUeUhqZG90Yng4aWhmN3A5ai02WENWYnF4bWpoZHFKMGc1X0JPRHdRRVZfSlA4UmZFa2kxYkNIS3ZtQ1NvNlNCME51eVZTRkRKSUQ5MmRoaWl5Tkt5NHpPUEFwemN2YTV1djFwdHlqQnFqRHNPenhYcTlsanJPcXhpOVV1NmFBUXZyazQ2MkUzM0dSZy02ZllxTGtjcl9ldzdHSktTRlVaalZJc1pubUNQMWFTbzVEOUJ1UmhCdEJt?oc=5</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N50" t="n">
-        <v>-19.03</v>
+        <v>-17.764</v>
       </c>
       <c r="O50" t="n">
-        <v>-65.26000000000001</v>
+        <v>-62.903</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Cotoca, Santa Cruz</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>capital (pronóstico puntual)</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>Chuquisaca</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Cotoca</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-24:viento:2</t>
+          <t>clima:Sucre:2026-10-23:viento:1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7498,7 +7572,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1792752927734</v>
+        <v>1792752927735</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -7511,16 +7585,16 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-24: 85 km/h de ráfagas pronosticadas</t>
+          <t>Sucre 2026-10-23: 66.2 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -7540,14 +7614,14 @@
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>-17.78</v>
+        <v>-19.03</v>
       </c>
       <c r="O51" t="n">
-        <v>-63.18</v>
+        <v>-65.26000000000001</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -7557,65 +7631,65 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Chuquisaca</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Sucre</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>usgs:us6000u49c</t>
+          <t>clima:Santa Cruz:2026-10-24:viento:2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>usgs</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-10-22 22:45</t>
+          <t>2026-10-23 06:55</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1792723541183</v>
+        <v>1792752927734</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>USGS</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>geológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Sismo M 4.5 - 58 km SW of Atocha, Bolivia</t>
+          <t>Santa Cruz 2026-10-24: 85 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Profundidad 236 km</t>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://earthquake.usgs.gov/earthquakes/eventpage/us6000u49c</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L52" t="n">
@@ -7625,59 +7699,59 @@
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>-21.3469</v>
+        <v>-17.78</v>
       </c>
       <c r="O52" t="n">
-        <v>-66.5795</v>
+        <v>-63.18</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>58 km SW of Atocha, Bolivia</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>coordenada de la fuente</t>
+          <t>capital (pronóstico puntual)</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>San Pablo</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-22:viento:1</t>
+          <t>usgs:us6000u49c</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>usgs</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-10-22 21:55</t>
+          <t>2026-10-22 22:45</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1792720528712</v>
+        <v>1792723541183</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>USGS</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>geológica</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7690,17 +7764,17 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-22: 67.7 km/h de ráfagas pronosticadas</t>
+          <t>Sismo M 4.5 - 58 km SW of Atocha, Bolivia</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+          <t>Profundidad 236 km</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://earthquake.usgs.gov/earthquakes/eventpage/us6000u49c</t>
         </is>
       </c>
       <c r="L53" t="n">
@@ -7710,36 +7784,36 @@
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>-17.78</v>
+        <v>-21.3469</v>
       </c>
       <c r="O53" t="n">
-        <v>-63.18</v>
+        <v>-66.5795</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>58 km SW of Atocha, Bolivia</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>capital (pronóstico puntual)</t>
+          <t>coordenada de la fuente</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>San Pablo</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-23:viento:2</t>
+          <t>clima:Santa Cruz:2026-10-22:viento:1</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -7766,16 +7840,16 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-23: 83.9 km/h de ráfagas pronosticadas</t>
+          <t>Santa Cruz 2026-10-22: 67.7 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -7824,49 +7898,53 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>noticia:1hhvre7</t>
+          <t>clima:Santa Cruz:2026-10-23:viento:2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-10-22 19:36</t>
+          <t>2026-10-22 21:55</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1792712202000</v>
+        <v>1792720528712</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>El Mundo Bolivia</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Virgen de Cotoca: Controlan incendio en depósito de materiales plásticos - El Mundo Bolivia</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
+          <t>Santa Cruz 2026-10-23: 83.9 km/h de ráfagas pronosticadas</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcDF6VE5FNzRaWGRuUzFKeXhnZ21DZTRaaEtrVEJEa1Z3ejg2VG1ONG1ENmlDWlkyVjlkQkJwS2F1XzBGMFQwSHd4OEwxTW1PbHdGcUh1ckV6SGpDd2hiN0dkeUVTcnFXT3RjOU1kLXZtVVdZY2hkZS1pcVpVUFhnRktqcHY5UnBrY0xUMDRETjl6N0pXT3A5amxhMA?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L55" t="n">
@@ -7876,19 +7954,19 @@
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>-17.764</v>
+        <v>-17.78</v>
       </c>
       <c r="O55" t="n">
-        <v>-62.903</v>
+        <v>-63.18</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Cotoca, Santa Cruz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
+          <t>capital (pronóstico puntual)</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -7898,14 +7976,14 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>Cotoca</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>noticia:bksnde</t>
+          <t>noticia:1hhvre7</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7915,15 +7993,15 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-10-22 17:01</t>
+          <t>2026-10-22 19:36</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1792702880000</v>
+        <v>1792712202000</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>eju.tv</t>
+          <t>El Mundo Bolivia</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -7941,13 +8019,13 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Reportan un incendio cerca de la carretera a Cotoca - eju.tv</t>
+          <t>Virgen de Cotoca: Controlan incendio en depósito de materiales plásticos - El Mundo Bolivia</t>
         </is>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPNGtpbnBfRnRBalVudnBlZHdVQ0ZSaUplZmtvTGE0aTQzdkxWS3d4My1EZEJ1UE9FNFQ3RmpyZGVsbS1qNEM1QUVFRFAxM2pYT1VqQzRuVjRtZnVNUGlKODNMc0F1a3l6TUpuQmtlUWNlVTVEWWU5ZGZtQm5LWUp3Sg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcDF6VE5FNzRaWGRuUzFKeXhnZ21DZTRaaEtrVEJEa1Z3ejg2VG1ONG1ENmlDWlkyVjlkQkJwS2F1XzBGMFQwSHd4OEwxTW1PbHdGcUh1ckV6SGpDd2hiN0dkeUVTcnFXT3RjOU1kLXZtVVdZY2hkZS1pcVpVUFhnRktqcHY5UnBrY0xUMDRETjl6N0pXT3A5amxhMA?oc=5</t>
         </is>
       </c>
       <c r="L56" t="n">
@@ -7986,7 +8064,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>noticia:17hz69v</t>
+          <t>noticia:bksnde</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7996,15 +8074,15 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-10-22 13:05</t>
+          <t>2026-10-22 17:01</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1792688709000</v>
+        <v>1792702880000</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>La Razón Digital Bolivia</t>
+          <t>eju.tv</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -8013,45 +8091,61 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Accidente en El Sillar deja al menos 29 heridos - La Razón Digital Bolivia</t>
+          <t>Reportan un incendio cerca de la carretera a Cotoca - eju.tv</t>
         </is>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPaXhTdm45YWZnWVFxVzJnb1ZwbUN4SmUtLVdJN0VJdFZBamRyQmFxN0RZelBfTklaSTVyOUZ3ajQ5MFB2TEN4Ukd6TE5ORFY5SEROVk1CZ25sRWJ1QnRBdTVfTktlby1NWXhaVWI5YnRvaDZWbHVjdDVoeFp5Tk5veFk5a19MSWJqcEJVV0dzV3k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPNGtpbnBfRnRBalVudnBlZHdVQ0ZSaUplZmtvTGE0aTQzdkxWS3d4My1EZEJ1UE9FNFQ3RmpyZGVsbS1qNEM1QUVFRFAxM2pYT1VqQzRuVjRtZnVNUGlKODNMc0F1a3l6TUpuQmtlUWNlVTVEWWU5ZGZtQm5LWUp3Sg?oc=5</t>
         </is>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>29</v>
-      </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>-17.764</v>
+      </c>
+      <c r="O57" t="n">
+        <v>-62.903</v>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Cotoca, Santa Cruz</t>
+        </is>
+      </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>Cotoca</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>noticia:1f1qb0</t>
+          <t>noticia:17hz69v</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -8061,15 +8155,15 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-10-22 12:09</t>
+          <t>2026-10-22 13:05</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1792685373000</v>
+        <v>1792688709000</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>La Razón Digital Bolivia</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -8078,61 +8172,45 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Accidente en el tramo Locotal–Villa Tunari: la vía está transitable con precaución - Red Uno</t>
+          <t>Accidente en El Sillar deja al menos 29 heridos - La Razón Digital Bolivia</t>
         </is>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTFozcEEwNXBqV19sS2VibXh0MGt0QlhsX1djSTFGQW5zNlFLRHZpNVVnZ1JmWDQ4LVRHX2Rmb3B5UU9qV0FZQmJCaUZYdmwyNG1NenJ4Qzlzd0NJTGs1SjMxdFRtRFBzSUkybGJfZFFaNFZBc21FSUJYSFVkQkVkSEhQaGw0UFVzeXctZHo3cjNsYm5weXJlOU1wcmFncnNhMC1BQUpvNWlDX1NxZXU4b09kVFFWR2tSVEk2UTdXXzB3TjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPaXhTdm45YWZnWVFxVzJnb1ZwbUN4SmUtLVdJN0VJdFZBamRyQmFxN0RZelBfTklaSTVyOUZ3ajQ5MFB2TEN4Ukd6TE5ORFY5SEROVk1CZ25sRWJ1QnRBdTVfTktlby1NWXhaVWI5YnRvaDZWbHVjdDVoeFp5Tk5veFk5a19MSWJqcEJVV0dzV3k?oc=5</t>
         </is>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" t="n">
-        <v>-16.556</v>
-      </c>
-      <c r="O58" t="n">
-        <v>-65.569</v>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>Villa Tunari, Cochabamba</t>
-        </is>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>Villa Tunari</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>noticia:wi18tm</t>
+          <t>noticia:1f1qb0</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -8142,11 +8220,11 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-10-22 11:53</t>
+          <t>2026-10-22 12:09</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1792684426000</v>
+        <v>1792685373000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -8155,49 +8233,65 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>tecnológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Accidente en El Sillar deja heridos y derrame de combustible: esto es lo último que se sabe - Red Uno</t>
+          <t>Accidente en el tramo Locotal–Villa Tunari: la vía está transitable con precaución - Red Uno</t>
         </is>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPZHNBTEdaQm5Wby1lTF9mWlQ2aGg0MVc4S0MwVWJ3dUJ5WWU5X3IwYWhKRjk5VWtYWEJHRDF4QldVc29laVNPSTJNWFBDSkNFQlFSYTJUXzNMNF9hckFBN1I2T2xoQUtYQ2V6MDNTZHhHVk9qeTBCdHRpM2ZLd0pyOFRweUUxX19STzRHTHg5VUY5d1lhS0tDeXpCdklqcTZGT1J4R0xnSDhoak1EZ2dtNUhSTUV6b1o0U0VSdWY5X0E3U05Tc1dYVEN2WFZUeFhPMTBJTmowNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTFozcEEwNXBqV19sS2VibXh0MGt0QlhsX1djSTFGQW5zNlFLRHZpNVVnZ1JmWDQ4LVRHX2Rmb3B5UU9qV0FZQmJCaUZYdmwyNG1NenJ4Qzlzd0NJTGs1SjMxdFRtRFBzSUkybGJfZFFaNFZBc21FSUJYSFVkQkVkSEhQaGw0UFVzeXctZHo3cjNsYm5weXJlOU1wcmFncnNhMC1BQUpvNWlDX1NxZXU4b09kVFFWR2tSVEk2UTdXXzB3TjA?oc=5</t>
         </is>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>1</v>
-      </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>-16.556</v>
+      </c>
+      <c r="O59" t="n">
+        <v>-65.569</v>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Villa Tunari, Cochabamba</t>
+        </is>
+      </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Villa Tunari</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>noticia:12gfagq</t>
+          <t>noticia:wi18tm</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -8207,78 +8301,62 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-10-22 11:28</t>
+          <t>2026-10-22 11:53</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1792682880000</v>
+        <v>1792684426000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>FmBolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>tecnológica</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Reportan triple colisión entre dos camiones y un bus en la carretera Cochabamba-Santa Cruz - FmBolivia</t>
+          <t>Accidente en El Sillar deja heridos y derrame de combustible: esto es lo último que se sabe - Red Uno</t>
         </is>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNMTNBaFZNMU9SR25vdVBuNXlZY3g4VkFWYXRiQnNSaUFjemZhUHZWNHg4V2owU2xfNndBak94TnU2cHNUVXdNNWl2eUdHZVNMbVZweTR5M0o0bWdTNUN4QkoxUkI2TDBmVE03M09zRGhJRVFzV0tPZ1NCWEJLUkt1ZGN4UGduOUZMQnJoM0tMYTh0ZlFxaFJNUkJqaWFPazRlMzN3ajhjUEdUYXlZRndpb3RSdTFCX2tCZGJxQ0x4SlBISWJsRVoyN3ZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPZHNBTEdaQm5Wby1lTF9mWlQ2aGg0MVc4S0MwVWJ3dUJ5WWU5X3IwYWhKRjk5VWtYWEJHRDF4QldVc29laVNPSTJNWFBDSkNFQlFSYTJUXzNMNF9hckFBN1I2T2xoQUtYQ2V6MDNTZHhHVk9qeTBCdHRpM2ZLd0pyOFRweUUxX19STzRHTHg5VUY5d1lhS0tDeXpCdklqcTZGT1J4R0xnSDhoak1EZ2dtNUhSTUV6b1o0U0VSdWY5X0E3U05Tc1dYVEN2WFZUeFhPMTBJTmowNA?oc=5</t>
         </is>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="n">
-        <v>-17.39</v>
-      </c>
-      <c r="O60" t="n">
-        <v>-66.16</v>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>Cochabamba, Cochabamba</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>noticia:1uq1bxy</t>
+          <t>noticia:12gfagq</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -8288,15 +8366,15 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-10-22 10:44</t>
+          <t>2026-10-22 11:28</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1792680273000</v>
+        <v>1792682880000</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>FmBolivia</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -8314,13 +8392,13 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Reportan triple colisión en la carretera Cochabamba–Santa Cruz - Red Uno</t>
+          <t>Reportan triple colisión entre dos camiones y un bus en la carretera Cochabamba-Santa Cruz - FmBolivia</t>
         </is>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNNUROMzd1UDJRWVZZQ011cFd2c1FSdER1ZzdleU04cXpwYk5HaUZrLXoyU2NzdFk1dnNRUndhUWt0cG9DX09rSjlLcDItU0tzcmQtS3E4dDQ4ZF9HdGJLdk13ek9BNHJUWVlCcklrM25rZ01RbXhLalRBT1FGdDNReHdlTFZkNkJ5ZFd3N3NZVFVmOFUxbEhHN0RsaUxiSVZsM0lXVEFYSHVRQlhsOEtJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNMTNBaFZNMU9SR25vdVBuNXlZY3g4VkFWYXRiQnNSaUFjemZhUHZWNHg4V2owU2xfNndBak94TnU2cHNUVXdNNWl2eUdHZVNMbVZweTR5M0o0bWdTNUN4QkoxUkI2TDBmVE03M09zRGhJRVFzV0tPZ1NCWEJLUkt1ZGN4UGduOUZMQnJoM0tMYTh0ZlFxaFJNUkJqaWFPazRlMzN3ajhjUEdUYXlZRndpb3RSdTFCX2tCZGJxQ0x4SlBISWJsRVoyN3ZR?oc=5</t>
         </is>
       </c>
       <c r="L61" t="n">
@@ -8359,7 +8437,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>noticia:1jl2oid</t>
+          <t>noticia:1uq1bxy</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -8369,15 +8447,15 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-10-22 07:49</t>
+          <t>2026-10-22 10:44</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1792669785000</v>
+        <v>1792680273000</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>eju.tv</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -8386,39 +8464,39 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - eju.tv</t>
+          <t>Reportan triple colisión en la carretera Cochabamba–Santa Cruz - Red Uno</t>
         </is>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQbTBrUmlla3FvVU1EX1pxcUI3SXYzbUFFMzlnRzhlSDJwMGpWWURxYjIwSkJBRGdCazMzT01hVy1qMFY3RnJLbC1XNXJ4bU55aDJVeXpNUlRsbzQ3T3hiRXJ5SWlhNmw5cDZFanNoWFBtQ01Gd3dscXltWmU5VHBSQlN3c2IwNGxuVE5tQ3lOT1RmNzRiVi1hc0hn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNNUROMzd1UDJRWVZZQ011cFd2c1FSdER1ZzdleU04cXpwYk5HaUZrLXoyU2NzdFk1dnNRUndhUWt0cG9DX09rSjlLcDItU0tzcmQtS3E4dDQ4ZF9HdGJLdk13ek9BNHJUWVlCcklrM25rZ01RbXhLalRBT1FGdDNReHdlTFZkNkJ5ZFd3N3NZVFVmOFUxbEhHN0RsaUxiSVZsM0lXVEFYSHVRQlhsOEtJ?oc=5</t>
         </is>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>-17.781</v>
+        <v>-17.39</v>
       </c>
       <c r="O62" t="n">
-        <v>-63.139</v>
+        <v>-66.16</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Santa Cruz, Santa Cruz</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -8428,19 +8506,19 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Cochabamba</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>noticia:yqgeq</t>
+          <t>noticia:1jl2oid</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -8450,15 +8528,15 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-10-22 07:43</t>
+          <t>2026-10-22 07:49</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1792669426000</v>
+        <v>1792669785000</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>eju.tv</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -8476,13 +8554,13 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - Red Uno</t>
+          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - eju.tv</t>
         </is>
       </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNVEh1bFlCanFuOTJid2EzYS1meG5oekFJcGFaME1fTk9sUnZpd3U0UXFHUFVJSW1jc1hzM2VFOFprT2xNYjBzbmswZmdJV3dremRIS0I4MDNzRjBnbEttWEhfOWZBbmFrRnNHWDFVLVFoM0VkZkxkaW4tMmZlSFJLei1heTFHMU0wSmxQVVRZN0cwaXQzcDBtZkdwTUFma0RXU2dwLXRnLTBkNGN3Vm1fV3hEdlM1dWZ1SEsw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQbTBrUmlla3FvVU1EX1pxcUI3SXYzbUFFMzlnRzhlSDJwMGpWWURxYjIwSkJBRGdCazMzT01hVy1qMFY3RnJLbC1XNXJ4bU55aDJVeXpNUlRsbzQ3T3hiRXJ5SWlhNmw5cDZFanNoWFBtQ01Gd3dscXltWmU5VHBSQlN3c2IwNGxuVE5tQ3lOT1RmNzRiVi1hc0hn?oc=5</t>
         </is>
       </c>
       <c r="L63" t="n">
@@ -8521,7 +8599,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>noticia:n32ahi</t>
+          <t>noticia:yqgeq</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -8531,69 +8609,150 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-10-22 05:30</t>
+          <t>2026-10-22 07:43</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1792661402000</v>
+        <v>1792669426000</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>FmBolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Senamhi anuncia el inicio de la temporada de lluvias en Bolivia y prevé granizadas como la de La Paz - FmBolivia</t>
+          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - Red Uno</t>
         </is>
       </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNVEh1bFlCanFuOTJid2EzYS1meG5oekFJcGFaME1fTk9sUnZpd3U0UXFHUFVJSW1jc1hzM2VFOFprT2xNYjBzbmswZmdJV3dremRIS0I4MDNzRjBnbEttWEhfOWZBbmFrRnNHWDFVLVFoM0VkZkxkaW4tMmZlSFJLei1heTFHMU0wSmxQVVRZN0cwaXQzcDBtZkdwTUFma0RXU2dwLXRnLTBkNGN3Vm1fV3hEdlM1dWZ1SEsw?oc=5</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1</v>
+      </c>
+      <c r="N64" t="n">
+        <v>-17.781</v>
+      </c>
+      <c r="O64" t="n">
+        <v>-63.139</v>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Santa Cruz, Santa Cruz</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>Santa Cruz de la Sierra</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>noticia:n32ahi</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>noticia</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-10-22 05:30</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>1792661402000</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>FmBolivia</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>meteorológica</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>verde</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Senamhi anuncia el inicio de la temporada de lluvias en Bolivia y prevé granizadas como la de La Paz - FmBolivia</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
           <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQNmVPRnVBMGQzdEI5SUp3Z3ZGVExwTUR6TWNadGQ1QldUS1o2QVFvUl9sVEZKMDVyQVVrS25rU1RSQlJKWXk1YzE0NUhidjhpcmFaSlhZUDZvcE9XcG1KTFNTYmowUU1CSFJNOVR2UHNmMk1iT3N0RVBteHkzZkgyRFROYk1pdkpxVHZya3N2X2FVLVQxbURFVVZlb1NzRjZzTE95TXFVUXFJNkVZakQ2bUhVQzB0SXk3TVhXUTJXa0dycTE1MWVQRFpDX3lDSWFqUGwzU2NtNA?oc=5</t>
         </is>
       </c>
-      <c r="L64" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" t="n">
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
         <v>-16.169</v>
       </c>
-      <c r="O64" t="n">
+      <c r="O65" t="n">
         <v>-68.09</v>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>La Paz, La Paz</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>nombre de municipio en el titular</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr">
+      <c r="R65" t="inlineStr">
         <is>
           <t>La Paz</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>Nuestra Señora de La Paz</t>
         </is>
@@ -9163,7 +9322,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-10-25 15:05</t>
+          <t>2026-10-25 15:53</t>
         </is>
       </c>
     </row>
@@ -9186,7 +9345,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4">
@@ -9196,7 +9355,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5">
@@ -9243,7 +9402,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sala de Situación Bolivia – CCES. Base de eventos de amenazas (datos preliminares de fuentes abiertas). Consulta: 2026-10-25 15:05.</t>
+          <t>Sala de Situación Bolivia – CCES. Base de eventos de amenazas (datos preliminares de fuentes abiertas). Consulta: 2026-10-25 15:53.</t>
         </is>
       </c>
     </row>

--- a/docs/datos/datos_bolivia.xlsx
+++ b/docs/datos/datos_bolivia.xlsx
@@ -9322,7 +9322,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-10-25 15:53</t>
+          <t>2026-10-25 16:19</t>
         </is>
       </c>
     </row>
@@ -9402,7 +9402,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sala de Situación Bolivia – CCES. Base de eventos de amenazas (datos preliminares de fuentes abiertas). Consulta: 2026-10-25 15:53.</t>
+          <t>Sala de Situación Bolivia – CCES. Base de eventos de amenazas (datos preliminares de fuentes abiertas). Consulta: 2026-10-25 16:19.</t>
         </is>
       </c>
     </row>

--- a/docs/datos/datos_bolivia.xlsx
+++ b/docs/datos/datos_bolivia.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R43"/>
+  <dimension ref="A1:R44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -592,25 +592,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>noticia:1xi48lm</t>
+          <t>noticia:9ge0q3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-25 13:02</t>
+          <t>2026-10-25 15:19</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1792947732000</v>
+        <v>1792955960000</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Reportan el incendio de dos camiones cisterna en la carretera a Camiri - EL DÍA - Noticias de Bolivia para el mundo</t>
+          <t>Tarija: Evalúan daños tras intensa granizada en Chocloca - eju.tv</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -633,57 +633,57 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>EL DÍA - Noticias de Bolivia para el mundo; La Patria Bolivia; Opinión Bolivia; Red Uno</t>
+          <t>eju.tv</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>-20.05</v>
+        <v>-21.53</v>
       </c>
       <c r="N3" t="n">
-        <v>-63.486</v>
+        <v>-64.73</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Camiri, Santa Cruz</t>
+          <t>Tarija, Tarija</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Tarija</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Camiri</t>
+          <t>Tarija</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNN0traUpaNVFIOU0zeFZod2tkQWhZZFQ1Q3dxc2xCVy1RNnJIX2xQbTlhT3RVckdNdHV4ZFVLQThvd2UzNDlCa3VmaWprTnU3R05rVkVkdEVCU1hFMlFsLTJ6REIySnl5VFJfdV9pQmVDTzlqUWFUSi1GQ0JvTVJVQ2dpeVBydnpMV0dYOThENTFRUDgxVFloSVg3bnN4dGo2aEVCbDFKaUgydWNISnJVUTNB?oc=5 | https://news.google.com/rss/articles/CBMimAFBVV95cUxQbHdpcUF6dXpjaW1TT1ZmdGJtUUVLMTNMRTVqVkFUdkNsZlRvenVkckFUWmI4NDFmc2ZHd2RVcWRSSE5YRVpOTUlESGw2V3JONXpwS0RISGNZd01SejNuMkY4NzFYYXp4aWo2RE9VMkFYUkVwZ3JRRmM5MWlRSjlBWk16azdkQ3FjdEtkaWc5NERkTzk2SllVOQ?oc=5 | https://news.google.com/rss/articles/CBMixgFBVV95cUxQLXlqSFdvWUVhQUNadnpkdE5lUTZQS0lobThzUTZWbDNJTE94alVhaDBaYU9Fd09SSGt3UlR3Y0dfZlNIcml1ZktnWjctNk1Na3V4S0tINFNkMXM0OHBoV2lCTTBiYXlPUTA3T2ZkeXE2RElYWjhfVHd3Nng1Z0E4alBmOFI5NDFwX09kazZlSWl2OVR2ZVR6MDhvSHFnSmJKbTFXSEFDNFFYcWVDNGtYWEQ0bDhJel9CaEpEZWZ4SWN0TE9Ya0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxObHF1cjVaY2tOSndEMDFoRzZCcEgwZHg5VERFa25taUF0UXVyOHB4YkNTSkhaWVVoQXRrU2xyOWlxMkhQblphT0VWeHVyVzBDUHdyUF9WM1U1MnJSSExSbDRQeGgxV05PUzQ5eHdHTURfcVVWRktlZ0lHbUpMeHhUTk9EZzc5UQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>manual:1c1299f3</t>
+          <t>noticia:1xi48lm</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25 12:44</t>
+          <t>2026-10-25 13:02</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1792946640000</v>
+        <v>1792947732000</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Vuelco de minibus</t>
+          <t>Reportan el incendio de dos camiones cisterna en la carretera a Camiri - EL DÍA - Noticias de Bolivia para el mundo</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -692,18 +692,18 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -711,53 +711,57 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Registro abierto (sin verificar)</t>
+          <t>EL DÍA - Noticias de Bolivia para el mundo; La Patria Bolivia; Opinión Bolivia; Red Uno</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>-15.813</v>
+        <v>-20.05</v>
       </c>
       <c r="N4" t="n">
-        <v>-67.46299999999999</v>
+        <v>-63.486</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Caranavi, La Paz</t>
+          <t>Camiri, Santa Cruz</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Caranavi</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
+          <t>Camiri</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNN0traUpaNVFIOU0zeFZod2tkQWhZZFQ1Q3dxc2xCVy1RNnJIX2xQbTlhT3RVckdNdHV4ZFVLQThvd2UzNDlCa3VmaWprTnU3R05rVkVkdEVCU1hFMlFsLTJ6REIySnl5VFJfdV9pQmVDTzlqUWFUSi1GQ0JvTVJVQ2dpeVBydnpMV0dYOThENTFRUDgxVFloSVg3bnN4dGo2aEVCbDFKaUgydWNISnJVUTNB?oc=5 | https://news.google.com/rss/articles/CBMimAFBVV95cUxQbHdpcUF6dXpjaW1TT1ZmdGJtUUVLMTNMRTVqVkFUdkNsZlRvenVkckFUWmI4NDFmc2ZHd2RVcWRSSE5YRVpOTUlESGw2V3JONXpwS0RISGNZd01SejNuMkY4NzFYYXp4aWo2RE9VMkFYUkVwZ3JRRmM5MWlRSjlBWk16azdkQ3FjdEtkaWc5NERkTzk2SllVOQ?oc=5 | https://news.google.com/rss/articles/CBMixgFBVV95cUxQLXlqSFdvWUVhQUNadnpkdE5lUTZQS0lobThzUTZWbDNJTE94alVhaDBaYU9Fd09SSGt3UlR3Y0dfZlNIcml1ZktnWjctNk1Na3V4S0tINFNkMXM0OHBoV2lCTTBiYXlPUTA3T2ZkeXE2RElYWjhfVHd3Nng1Z0E4alBmOFI5NDFwX09kazZlSWl2OVR2ZVR6MDhvSHFnSmJKbTFXSEFDNFFYcWVDNGtYWEQ0bDhJel9CaEpEZWZ4SWN0TE9Ya0E?oc=5</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>noticia:1sg8pi0</t>
+          <t>manual:1c1299f3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-25 09:59</t>
+          <t>2026-10-25 12:44</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1792936752000</v>
+        <v>1792946640000</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bus de agrupación musical sufre accidente rumbo al trópico de Cochabamba | VIDEO - Red Uno</t>
+          <t>Vuelco de minibus</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -766,18 +770,18 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -789,58 +793,54 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>Registro abierto (sin verificar)</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>-17.39</v>
+        <v>-15.813</v>
       </c>
       <c r="N5" t="n">
-        <v>-66.16</v>
+        <v>-67.46299999999999</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Cochabamba, Cochabamba</t>
+          <t>Caranavi, La Paz</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOVDVzVTJNM2JuQ25sMThEaVZNOUNRd3FGT3RhVnFrZXZ2NDQ1YlluTVdhbVNUQnA1MGNESHRSWVUzbC1kRVh3OTR0emtlTG91cmRWeFJ5dk5zb3p2WFRyMEJUV3FNRnY1WHhRUU9WLTlJcmNyNXJZZFdoM0JoZjNpa3hjUXhMM0xrUDJab2VadkM5RWZYQ3lWZTVDdzg1akxJT2lxcDVNNzI0NG1hejdfdkUyTQ?oc=5</t>
-        </is>
-      </c>
+          <t>Caranavi</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>noticia:167wlhz</t>
+          <t>noticia:1sg8pi0</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-25 07:53</t>
+          <t>2026-10-25 09:59</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1792929231000</v>
+        <v>1792936752000</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>¡A sacar el paraguas! Santa cruz amanece con lluvia, frío y complicaciones en el tránsito vehicular - Red Uno</t>
+          <t>Bus de agrupación musical sufre accidente rumbo al trópico de Cochabamba | VIDEO - Red Uno</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -871,62 +871,62 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>-17.781</v>
+        <v>-17.39</v>
       </c>
       <c r="N6" t="n">
-        <v>-63.139</v>
+        <v>-66.16</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Santa Cruz, Santa Cruz</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOY1ZpYktLR3pUQXotUndVR3puUzVHbW1YTzNyUmJvUHB4Q2JmelRvOEdaRldOUm1xLVJnbGR5VWcxTjNEM3ZUYktCUWtVM0hKSjFuRGdpX0JxN0M5MVZBSG1aVURyVWktdmxwbUtRT19ydU5LdzNTZ2Zpb2ozdHlMUUdTVlAyVk4xODBnV0hyTXdVVndyNzV3VC1KMzFnV3lpcFFXSk9MdDZOTWlWakNwT1FnNDh6QVdjazVYZDVVMkdaLU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOVDVzVTJNM2JuQ25sMThEaVZNOUNRd3FGT3RhVnFrZXZ2NDQ1YlluTVdhbVNUQnA1MGNESHRSWVUzbC1kRVh3OTR0emtlTG91cmRWeFJ5dk5zb3p2WFRyMEJUV3FNRnY1WHhRUU9WLTlJcmNyNXJZZFdoM0JoZjNpa3hjUXhMM0xrUDJab2VadkM5RWZYQ3lWZTVDdzg1akxJT2lxcDVNNzI0NG1hejdfdkUyTQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>noticia:bzr7eh</t>
+          <t>noticia:167wlhz</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-25 07:09</t>
+          <t>2026-10-25 07:53</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1792926572000</v>
+        <v>1792929231000</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Alerta naranja por riesgo de desbordes de ríos - El Diario - Bolivia</t>
+          <t>¡A sacar el paraguas! Santa cruz amanece con lluvia, frío y complicaciones en el tránsito vehicular - Red Uno</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>hidrológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -941,74 +941,74 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia; El Mundo Bolivia; FmBolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>-16.169</v>
+        <v>-17.781</v>
       </c>
       <c r="N7" t="n">
-        <v>-68.09</v>
+        <v>-63.139</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>La Paz, La Paz</t>
+          <t>Santa Cruz, Santa Cruz</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Nuestra Señora de La Paz</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNNGZKSDVaZkowWUFGSEUyTWR3d3dsc04waFBLLWUtcVpiTDYzbmNtYTN1RkFLbjAwN3dxT0xZc3pqc3REUXduZVltQ2Fud1BZLTh1bTNiTEJueVUwV0dERS1iUXZqMHd0UnFrQ3E2SFAzbm5lQ1I4U29MaHJFbWFvdVRTeFY4Wl9rSmc3RkpaQ2xwX0oz?oc=5 | https://news.google.com/rss/articles/CBMipwFBVV95cUxPZW00RkxJSklTelNrS2hqczJDWHlwcENFX2lnSEUyTEFPaDFRQ2JvMUcyd3NfYjg0UE9ORGxHRzB4ZDh3U0hQQ1JSQlhsaUY4N3ByMUUxei1SaUZnNlp6T3hsLVdiMGhKaXhsV1FNSUNQMHlvQ19qdk56SEF0d2RXVFctS0VPT25kNGZCRDdvZ2dxU0VoUUJKU0ZBd0ZycFNEZFh0T3ZjOA?oc=5 | https://news.google.com/rss/articles/CBMiwAFBVV95cUxPZm85aHphekQ4U3BZZkp1ZkF6ZVdSUHgtZmltS1FxUUgza1AwcndWWDJZOWctT0RiVmVabmg5SG42NnJWMlJMMnBlYTlYaVdSb09sR0dnVDdpT29faTdiaDUtZElJdlQ3eTdjR2VsWjlta1FOS1U2Vm1vV3JwWkpvbEw1ZUR3akgwQTZnQnVENjJtVkQtVUpKVEJTeWNJSE1CaEFKa2VqMmZXbWk3ekR4ZWpmZ1Z3elFQaWNaNFJuMXA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOY1ZpYktLR3pUQXotUndVR3puUzVHbW1YTzNyUmJvUHB4Q2JmelRvOEdaRldOUm1xLVJnbGR5VWcxTjNEM3ZUYktCUWtVM0hKSjFuRGdpX0JxN0M5MVZBSG1aVURyVWktdmxwbUtRT19ydU5LdzNTZ2Zpb2ozdHlMUUdTVlAyVk4xODBnV0hyTXdVVndyNzV3VC1KMzFnV3lpcFFXSk9MdDZOTWlWakNwT1FnNDh6QVdjazVYZDVVMkdaLU0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>noticia:1fo4ig4</t>
+          <t>noticia:bzr7eh</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-25 01:08</t>
+          <t>2026-10-25 07:09</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1792904880000</v>
+        <v>1792926572000</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
+          <t>Alerta naranja por riesgo de desbordes de ríos - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>hidrológica</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>roja</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1019,41 +1019,57 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>diarioelpueblo.com.pe</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
+          <t>El Diario - Bolivia; El Mundo Bolivia; FmBolivia</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>-16.169</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-68.09</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>La Paz, La Paz</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>La Paz</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Nuestra Señora de La Paz</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQcmFrT3dwcEs0X3U2NWxnOGJwNnI2WHdWTGZYbzEyNnJzUWhkbU9TRWhfSlB5UkMwX2gyMmxYUmVNWmxNOVR6V0twRHpFMTVIYjBKbHQ2TXN2d2w5dkFpcWJCcUJMZldaX01sNWtQV2ZJOGpRVzR3NDVIU0pJc1BNVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNNGZKSDVaZkowWUFGSEUyTWR3d3dsc04waFBLLWUtcVpiTDYzbmNtYTN1RkFLbjAwN3dxT0xZc3pqc3REUXduZVltQ2Fud1BZLTh1bTNiTEJueVUwV0dERS1iUXZqMHd0UnFrQ3E2SFAzbm5lQ1I4U29MaHJFbWFvdVRTeFY4Wl9rSmc3RkpaQ2xwX0oz?oc=5 | https://news.google.com/rss/articles/CBMipwFBVV95cUxPZW00RkxJSklTelNrS2hqczJDWHlwcENFX2lnSEUyTEFPaDFRQ2JvMUcyd3NfYjg0UE9ORGxHRzB4ZDh3U0hQQ1JSQlhsaUY4N3ByMUUxei1SaUZnNlp6T3hsLVdiMGhKaXhsV1FNSUNQMHlvQ19qdk56SEF0d2RXVFctS0VPT25kNGZCRDdvZ2dxU0VoUUJKU0ZBd0ZycFNEZFh0T3ZjOA?oc=5 | https://news.google.com/rss/articles/CBMiwAFBVV95cUxPZm85aHphekQ4U3BZZkp1ZkF6ZVdSUHgtZmltS1FxUUgza1AwcndWWDJZOWctT0RiVmVabmg5SG42NnJWMlJMMnBlYTlYaVdSb09sR0dnVDdpT29faTdiaDUtZElJdlQ3eTdjR2VsWjlta1FOS1U2Vm1vV3JwWkpvbEw1ZUR3akgwQTZnQnVENjJtVkQtVUpKVEJTeWNJSE1CaEFKa2VqMmZXbWk3ekR4ZWpmZ1Z3elFQaWNaNFJuMXA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>noticia:r1uot6</t>
+          <t>noticia:1fo4ig4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-24 20:00</t>
+          <t>2026-10-25 01:08</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1792886439000</v>
+        <v>1792904880000</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>vuelco deja heridos en ruta Oruro – Huanuni - La Patria Bolivia</t>
+          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1062,18 +1078,18 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>roja</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1085,53 +1101,37 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>-17.97</v>
-      </c>
-      <c r="N9" t="n">
-        <v>-67.11</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Oruro, Oruro</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Oruro</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Oruro</t>
-        </is>
-      </c>
+          <t>diarioelpueblo.com.pe</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNNDQtMG1KT1lLWW5nem9Jbm5JWDZKNlRWZmFmRlBxWDlDeXlSWnJ5d2NsTlpxa0JIS25oVWVZOC1majZVbWhOVDIxR0dLOFlzY2VpVzVoVk1mQnF3dXVwLUFZVHc1UjlXZzF5T05CY3U0ZldLVkw1VzBTek5zanpjQW1xalltWHNiaXI3dTNR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQcmFrT3dwcEs0X3U2NWxnOGJwNnI2WHdWTGZYbzEyNnJzUWhkbU9TRWhfSlB5UkMwX2gyMmxYUmVNWmxNOVR6V0twRHpFMTVIYjBKbHQ2TXN2d2w5dkFpcWJCcUJMZldaX01sNWtQV2ZJOGpRVzR3NDVIU0pJc1BNVg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>noticia:1ytw450</t>
+          <t>noticia:r1uot6</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-24 18:58</t>
+          <t>2026-10-24 20:00</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1792882686000</v>
+        <v>1792886439000</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
+          <t>vuelco deja heridos en ruta Oruro – Huanuni - La Patria Bolivia</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1140,18 +1140,18 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>roja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1163,37 +1163,53 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>diarioelpueblo.com.pe</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
+          <t>La Patria Bolivia</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>-17.97</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-67.11</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Oruro, Oruro</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNZ1U3bEVuaVdjVE1zSU9lOHJZTVRZLVZaemhldGNnT1JBWDJvbzdvM3paVVNhLUlyWHF2akNuSXJOLXdyTGRuejRlV1FuMjVkTjA3NmdRdmgtRWlUeTFBV1dEMzBvejBxaXZJdUZZWkRVTF9VLU5BcjFGZGFEQ09WWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNNDQtMG1KT1lLWW5nem9Jbm5JWDZKNlRWZmFmRlBxWDlDeXlSWnJ5d2NsTlpxa0JIS25oVWVZOC1majZVbWhOVDIxR0dLOFlzY2VpVzVoVk1mQnF3dXVwLUFZVHc1UjlXZzF5T05CY3U0ZldLVkw1VzBTek5zanpjQW1xalltWHNiaXI3dTNR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>noticia:1g006zh</t>
+          <t>noticia:1ytw450</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-24 17:02</t>
+          <t>2026-10-24 18:58</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1792875752000</v>
+        <v>1792882686000</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a Mayaya deja siete heridos del grupo Los Chicos Fieles - El Potosí</t>
+          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1202,18 +1218,18 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>roja</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1221,57 +1237,41 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>EL DÍA - Noticias de Bolivia para el mundo; El Potosí; La Razón Digital Bolivia; Opinión Bolivia</t>
-        </is>
-      </c>
-      <c r="M11" t="n">
-        <v>-19.58</v>
-      </c>
-      <c r="N11" t="n">
-        <v>-65.75</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Potosí, Potosí</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
+          <t>diarioelpueblo.com.pe</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPTGQwaVBfdG1JdVRMUTN4LVVvN0ppc3dreDJVVllDR3RmX0xpMzB4b0pvVTNSV1B6T0ZEWTdEZkNsRUdSNzhLaC1CWHN5WktNWk1nRWpTdVZiYjI3TlJlX2xlVTI5MjlRU2hiY1gteml4YWVFbDNPSVRBZmtITlQzbmhaUXVmcThRa2xsQTJIOXZuNzlSdm12MEdyOEZHdw?oc=5 | https://news.google.com/rss/articles/CBMizwFBVV95cUxPeGd3VWpCWXJ0YTJIeDJLcktzWG1jdUh0TjFXb01wSTkxbHNXZU94VWNDMkxnTjlJZVdpbkprMEY2NE80RXYyUWxUQXVnbl9lUXR2b28zTEh6cTJLVEQ4TUNja2kzRlhadVBFZFVwV1U2TlhseXZMZ20zZTZiUFpWRjdCOWNBMHU5XzdMV3JqQjV4TEE3bHRMOXR6Nm55eHZUNnFHSDdVRk8zVkY4RkVsUUtUN0JYdkREWGZncmJ3ZWc2T1BuUm1ZLTlfcHVabFE?oc=5 | https://news.google.com/rss/articles/CBMizAFBVV95cUxNYjNxaHg3YllRRTJYdFd1clAtUlROSGlFNVg5eUVZUGJoOEZ4MWM5QU5WQm1YTDc4NXc3SjhWMUw0TkZfSHlMLUQ1bmpTME1Kb1JaM0ExamFHYTd3VlU4MXRWdTZ1bzh1SGYtbGE1a3dBaG93bjg1OGc0S0JfRE43c3dVMVltN0dQQzNhQUNhM0FjVUNRUDRSamlJYlk2dEJpUTBuY2hBcTFucTVRN0ZtYnc5bzdmTV9LQm1uVUxaZS1tUE9IejhBVDRCdU_SAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNZ1U3bEVuaVdjVE1zSU9lOHJZTVRZLVZaemhldGNnT1JBWDJvbzdvM3paVVNhLUlyWHF2akNuSXJOLXdyTGRuejRlV1FuMjVkTjA3NmdRdmgtRWlUeTFBV1dEMzBvejBxaXZJdUZZWkRVTF9VLU5BcjFGZGFEQ09WWQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>noticia:1ukcn97</t>
+          <t>noticia:1g006zh</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-24 13:26</t>
+          <t>2026-10-24 17:02</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1792862794000</v>
+        <v>1792875752000</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Esta es la lista preliminar de los heridos en el accidente del grupo 'Los chicos fieles', el conductor está grave - El Deber</t>
+          <t>Accidente en la carretera a Mayaya deja siete heridos del grupo Los Chicos Fieles - El Potosí</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1299,46 +1299,62 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>El Deber; Red Uno</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
+          <t>EL DÍA - Noticias de Bolivia para el mundo; El Potosí; La Razón Digital Bolivia; Opinión Bolivia</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>-19.58</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-65.75</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Potosí, Potosí</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Potosí</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Potosí</t>
+        </is>
+      </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOczZKbFd1QzRpak92LXpPWXZXQXJObnBQTG9qRFBlUUV5dThMWXhzckFFUHAyb2thU1JwRmJDSEZfaEdTUXh1bjZvQWpYMGhfUno3cWZ4MGpldEpoQXhzSlVzTm5LLW9OcjB2MWRsdHQ2UlI2SjEtZ085ZTR5Z3pEVmtBTF9lc29Kd0RhaTRUWkM4eGZJNWhBSXZqWmxuNW10dlQwYW9mdzItcWZWTkU0?oc=5 | https://news.google.com/rss/articles/CBMivAFBVV95cUxPczBQcnE2SzFGMXc3b1lsTkNxVWRmS3Vnb01xOTV2WmVva3J2RVlteWpHZ3VJS2dNWGV5NW5FX3ZncnVKTEVDTGpBRndTU1FxeWxtaS1fb1FscGxXMWNXUE9zbHdob1AxVFl1eHB5OU1yUnNoOXJ6U21oVG9PVDA1ak1xQl9hUlB4V0RaQXJqZENGUm8zMUJEY3J0WW5ENE5ObWJLNmpWN0RkSmFJbnZUZGR5UFRPd3QyUFY4WQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPTGQwaVBfdG1JdVRMUTN4LVVvN0ppc3dreDJVVllDR3RmX0xpMzB4b0pvVTNSV1B6T0ZEWTdEZkNsRUdSNzhLaC1CWHN5WktNWk1nRWpTdVZiYjI3TlJlX2xlVTI5MjlRU2hiY1gteml4YWVFbDNPSVRBZmtITlQzbmhaUXVmcThRa2xsQTJIOXZuNzlSdm12MEdyOEZHdw?oc=5 | https://news.google.com/rss/articles/CBMizwFBVV95cUxPeGd3VWpCWXJ0YTJIeDJLcktzWG1jdUh0TjFXb01wSTkxbHNXZU94VWNDMkxnTjlJZVdpbkprMEY2NE80RXYyUWxUQXVnbl9lUXR2b28zTEh6cTJLVEQ4TUNja2kzRlhadVBFZFVwV1U2TlhseXZMZ20zZTZiUFpWRjdCOWNBMHU5XzdMV3JqQjV4TEE3bHRMOXR6Nm55eHZUNnFHSDdVRk8zVkY4RkVsUUtUN0JYdkREWGZncmJ3ZWc2T1BuUm1ZLTlfcHVabFE?oc=5 | https://news.google.com/rss/articles/CBMizAFBVV95cUxNYjNxaHg3YllRRTJYdFd1clAtUlROSGlFNVg5eUVZUGJoOEZ4MWM5QU5WQm1YTDc4NXc3SjhWMUw0TkZfSHlMLUQ1bmpTME1Kb1JaM0ExamFHYTd3VlU4MXRWdTZ1bzh1SGYtbGE1a3dBaG93bjg1OGc0S0JfRE43c3dVMVltN0dQQzNhQUNhM0FjVUNRUDRSamlJYlk2dEJpUTBuY2hBcTFucTVRN0ZtYnc5bzdmTV9LQm1uVUxaZS1tUE9IejhBVDRCdU_SAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>noticia:2avehj</t>
+          <t>noticia:1ukcn97</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-24 12:53</t>
+          <t>2026-10-24 13:26</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1792860813000</v>
+        <v>1792862794000</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sequía en Cochabamba: más de un centenar de cabezas de ganado murieron en el cono sur - Red Uno</t>
+          <t>Esta es la lista preliminar de los heridos en el accidente del grupo 'Los chicos fieles', el conductor está grave - El Deber</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>climatológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1350,10 +1366,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1361,62 +1377,46 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Red Uno</t>
-        </is>
-      </c>
-      <c r="M13" t="n">
-        <v>-17.39</v>
-      </c>
-      <c r="N13" t="n">
-        <v>-66.16</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Cochabamba, Cochabamba</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
+          <t>El Deber; Red Uno</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOOFQxc2Vzc0QwS19ydC13RkRPZnZQU3JkSTl5U3kzdUdMSldTcm5HVEhWRzZyN19CLUlwcUs4MW03Ui1obVBtdzQ3QWFQc1RKdzh3MXJ5QkpRS2pRNm50V1lVb09ScGJnaVVlemVfZlRsWjdObnRmR1FGMnlMMHAyc2pMandndy10T2twcWx6OFh4UHdvbVlFbllwME9WQ2pQVjNTQzBxeTg5YnF3bDREeHVDYXpObFFIaTZZQWtYUE12cGQ1ZGRhT0syNjVhZWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOczZKbFd1QzRpak92LXpPWXZXQXJObnBQTG9qRFBlUUV5dThMWXhzckFFUHAyb2thU1JwRmJDSEZfaEdTUXh1bjZvQWpYMGhfUno3cWZ4MGpldEpoQXhzSlVzTm5LLW9OcjB2MWRsdHQ2UlI2SjEtZ085ZTR5Z3pEVmtBTF9lc29Kd0RhaTRUWkM4eGZJNWhBSXZqWmxuNW10dlQwYW9mdzItcWZWTkU0?oc=5 | https://news.google.com/rss/articles/CBMivAFBVV95cUxPczBQcnE2SzFGMXc3b1lsTkNxVWRmS3Vnb01xOTV2WmVva3J2RVlteWpHZ3VJS2dNWGV5NW5FX3ZncnVKTEVDTGpBRndTU1FxeWxtaS1fb1FscGxXMWNXUE9zbHdob1AxVFl1eHB5OU1yUnNoOXJ6U21oVG9PVDA1ak1xQl9hUlB4V0RaQXJqZENGUm8zMUJEY3J0WW5ENE5ObWJLNmpWN0RkSmFJbnZUZGR5UFRPd3QyUFY4WQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>noticia:3dv7b0</t>
+          <t>noticia:2avehj</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-24 11:43</t>
+          <t>2026-10-24 12:53</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1792856591000</v>
+        <v>1792860813000</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Accidente en Caranavi: vehículo de Los Chicos Fieles cae a un barranco y deja varios heridos - FmBolivia</t>
+          <t>Sequía en Cochabamba: más de un centenar de cabezas de ganado murieron en el cono sur - Red Uno</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>climatológica</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1439,62 +1439,62 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>FmBolivia; La Patria Bolivia; Red Uno</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>-15.813</v>
+        <v>-17.39</v>
       </c>
       <c r="N14" t="n">
-        <v>-67.46299999999999</v>
+        <v>-66.16</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Caranavi, La Paz</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Caranavi</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNeEFrOEtOMHZxMW42REFPU0x1MG5oQjlBMkJucWRLZ292alBXekJKeURBN3NLTVVadWI0OWF4UGtSVXBzTE01eWFSU1kyMUhNZ04zMWNMaUxnMDBBZ0EwTktXbjlaVTBUUmNqa3AwY19KNTU2LWh5LW9IVElVdTdnaHFPanJPd2FqMUxzaUhXZmVpYU1saGc?oc=5 | https://news.google.com/rss/articles/CBMi2wFBVV95cUxOdTVUZUQxVTdvYTdONDQxVlhUTzBOS2hKLW1rS1NUcmRYRnlCVlhIcHZlSjdsaktkQm5CWkFYa3lDQkxnMlh0b3prX0lha1BtbW1qS1VuYnNiX3FiZkYyNDJDR0tqZ0pKMU5TeC04SXV4UUJOTUlPUTB6ek01bzUxTUsydjZqZzI3S3ZLUnRWSUFUVk44WEpKUl9rbzRLb2IwYl9sLVlrYmt5d2ZHNUtGd3lRNnYzMlhuMkJOZW1XSUl2N1BxZWpHbm5XTDJhRUtnR190QWQ1TDlTUVk?oc=5 | https://news.google.com/rss/articles/CBMizAFBVV95cUxNcE1KaHZyUTJCSElxRU9nVzdhTnczWjJGTEhFMEs0bHp2cUdFeHd3VTB0NmVFcjdEN1dsZDZLY2k1ZFFUWkhKV19PU3V2czNyamh1ZE9YajVSVF8xczF6OFhZcWFvYV9EcWg4ZDNCb2p3enhXbFpRYnJMdGdaTXNrWUZSYVhKNTVicWlCLTJ5OE05Z1BvNEx1eEloUk5qTGN3ZHNzbzZWSVljbnRmSERJUWdxRDc0MjJxMGtycWJaaVhXQUUxVUlaWVZLOWE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOOFQxc2Vzc0QwS19ydC13RkRPZnZQU3JkSTl5U3kzdUdMSldTcm5HVEhWRzZyN19CLUlwcUs4MW03Ui1obVBtdzQ3QWFQc1RKdzh3MXJ5QkpRS2pRNm50V1lVb09ScGJnaVVlemVfZlRsWjdObnRmR1FGMnlMMHAyc2pMandndy10T2twcWx6OFh4UHdvbVlFbllwME9WQ2pQVjNTQzBxeTg5YnF3bDREeHVDYXpObFFIaTZZQWtYUE12cGQ1ZGRhT0syNjVhZWs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>clima:Potosí:2026-10-24:viento:1</t>
+          <t>noticia:3dv7b0</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-24 10:55</t>
+          <t>2026-10-24 11:43</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1792853727284</v>
+        <v>1792856591000</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Potosí 2026-10-24: 60.5 km/h de ráfagas pronosticadas</t>
+          <t>Accidente en Caranavi: vehículo de Los Chicos Fieles cae a un barranco y deja varios heridos - FmBolivia</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1509,7 +1509,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1517,57 +1517,57 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>FmBolivia; La Patria Bolivia; Red Uno</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>-19.58</v>
+        <v>-15.813</v>
       </c>
       <c r="N15" t="n">
-        <v>-65.75</v>
+        <v>-67.46299999999999</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Caranavi, La Paz</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Caranavi</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNeEFrOEtOMHZxMW42REFPU0x1MG5oQjlBMkJucWRLZ292alBXekJKeURBN3NLTVVadWI0OWF4UGtSVXBzTE01eWFSU1kyMUhNZ04zMWNMaUxnMDBBZ0EwTktXbjlaVTBUUmNqa3AwY19KNTU2LWh5LW9IVElVdTdnaHFPanJPd2FqMUxzaUhXZmVpYU1saGc?oc=5 | https://news.google.com/rss/articles/CBMi2wFBVV95cUxOdTVUZUQxVTdvYTdONDQxVlhUTzBOS2hKLW1rS1NUcmRYRnlCVlhIcHZlSjdsaktkQm5CWkFYa3lDQkxnMlh0b3prX0lha1BtbW1qS1VuYnNiX3FiZkYyNDJDR0tqZ0pKMU5TeC04SXV4UUJOTUlPUTB6ek01bzUxTUsydjZqZzI3S3ZLUnRWSUFUVk44WEpKUl9rbzRLb2IwYl9sLVlrYmt5d2ZHNUtGd3lRNnYzMlhuMkJOZW1XSUl2N1BxZWpHbm5XTDJhRUtnR190QWQ1TDlTUVk?oc=5 | https://news.google.com/rss/articles/CBMizAFBVV95cUxNcE1KaHZyUTJCSElxRU9nVzdhTnczWjJGTEhFMEs0bHp2cUdFeHd3VTB0NmVFcjdEN1dsZDZLY2k1ZFFUWkhKV19PU3V2czNyamh1ZE9YajVSVF8xczF6OFhZcWFvYV9EcWg4ZDNCb2p3enhXbFpRYnJMdGdaTXNrWUZSYVhKNTVicWlCLTJ5OE05Z1BvNEx1eEloUk5qTGN3ZHNzbzZWSVljbnRmSERJUWdxRDc0MjJxMGtycWJaaVhXQUUxVUlaWVZLOWE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>noticia:1ax0bpy</t>
+          <t>clima:Potosí:2026-10-24:viento:1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-24 10:32</t>
+          <t>2026-10-24 10:55</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1792852364000</v>
+        <v>1792853727284</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Creció el Bermejo tras la tormenta: así está el puerto de chalanas en este momento - Que Pasa Salta</t>
+          <t>Potosí 2026-10-24: 60.5 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1576,11 +1576,11 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1599,58 +1599,58 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Que Pasa Salta</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>-22.721</v>
+        <v>-19.58</v>
       </c>
       <c r="N16" t="n">
-        <v>-64.32599999999999</v>
+        <v>-65.75</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Bermejo, Tarija</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Tarija</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Bermejo</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVld9IBfkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVldw?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>gdacs:WF1033142:0</t>
+          <t>noticia:1ax0bpy</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-24 07:06</t>
+          <t>2026-10-24 10:32</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1792839995000</v>
+        <v>1792852364000</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Green forest fire notification in Bolivia</t>
+          <t>Creció el Bermejo tras la tormenta: así está el puerto de chalanas en este momento - Que Pasa Salta</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1677,58 +1677,58 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>GDACS</t>
+          <t>Que Pasa Salta</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>-13.06332</v>
+        <v>-22.721</v>
       </c>
       <c r="N17" t="n">
-        <v>-67.66426</v>
+        <v>-64.32599999999999</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Bermejo, Tarija</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Tarija</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Ixiamas</t>
+          <t>Bermejo</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>http://www.gdacs.org/report.aspx?eventtype=WF&amp;eventid=1033142</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVld9IBfkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVldw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>noticia:1shhqva</t>
+          <t>gdacs:WF1033142:0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-24 06:33</t>
+          <t>2026-10-24 07:06</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1792838034000</v>
+        <v>1792839995000</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
+          <t>Green forest fire notification in Bolivia</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1751,70 +1751,70 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>GDACS</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>-17.97</v>
+        <v>-13.06332</v>
       </c>
       <c r="N18" t="n">
-        <v>-67.11</v>
+        <v>-67.66426</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Ixiamas</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQYzB6N082XzFRRnVtcDVmUkYyWjcxUzV2Z3Frd1I0WDNXSnZtY0QzOU1PUkNLMktVT1Vra2FSeXhxZDRuOFZYZjFwejl6ejJTbWY2MGJuSGN3ZHdrdG5JUkgzSXBkbDYtaHlackY3OVFuNWdLcFNpdWNHRU9vNGdoVWx2ODFVdzJXYUxnM0tUcjJvZmc?oc=5 | https://news.google.com/rss/articles/CBMikAFBVV95cUxQS2FPaHd3UnFBRjRoa0lKUm1MNUQ5S00zN1RJZE5fWlVUQnhiY0lLcFRkY2JZak1mZ0c2WEVMVUNJVUJTMGFLNHg4S2ZKNTRqLXJHM09ET19hX1pZeTQwUkdEc2huTHVpcno2QTRZbnhralVRWXozcWc1a2pHUEpBeTV1cWgzTWRwaDEweURKeVE?oc=5</t>
+          <t>http://www.gdacs.org/report.aspx?eventtype=WF&amp;eventid=1033142</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>clima:Potosí:2026-10-25:viento:1</t>
+          <t>noticia:1shhqva</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-24 02:55</t>
+          <t>2026-10-24 06:33</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1792824927736</v>
+        <v>1792838034000</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Potosí 2026-10-25: 60.5 km/h de ráfagas pronosticadas</t>
+          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1829,62 +1829,62 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>-19.58</v>
+        <v>-17.97</v>
       </c>
       <c r="N19" t="n">
-        <v>-65.75</v>
+        <v>-67.11</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Oruro, Oruro</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Oruro</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Oruro</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQYzB6N082XzFRRnVtcDVmUkYyWjcxUzV2Z3Frd1I0WDNXSnZtY0QzOU1PUkNLMktVT1Vra2FSeXhxZDRuOFZYZjFwejl6ejJTbWY2MGJuSGN3ZHdrdG5JUkgzSXBkbDYtaHlackY3OVFuNWdLcFNpdWNHRU9vNGdoVWx2ODFVdzJXYUxnM0tUcjJvZmc?oc=5 | https://news.google.com/rss/articles/CBMikAFBVV95cUxQS2FPaHd3UnFBRjRoa0lKUm1MNUQ5S00zN1RJZE5fWlVUQnhiY0lLcFRkY2JZak1mZ0c2WEVMVUNJVUJTMGFLNHg4S2ZKNTRqLXJHM09ET19hX1pZeTQwUkdEc2huTHVpcno2QTRZbnhralVRWXozcWc1a2pHUEpBeTV1cWgzTWRwaDEweURKeVE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>noticia:1uil931</t>
+          <t>clima:Potosí:2026-10-25:viento:1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-23 22:49</t>
+          <t>2026-10-24 02:55</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1792810149000</v>
+        <v>1792824927736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Accidente de tránsito en la ruta hacia Alto Beni deja varios heridos - El Deber</t>
+          <t>Potosí 2026-10-25: 60.5 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1899,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1907,62 +1907,62 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>El Deber</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>-15.578</v>
+        <v>-19.58</v>
       </c>
       <c r="N20" t="n">
-        <v>-67.44</v>
+        <v>-65.75</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Alto Beni, La Paz</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Alto Beni</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQakFJRmx3RlJEMkVHU0pxWXZ2ZU1ib04tZy1yeTB2OGhrYk9CU3pMaDVpRThNZktZMS14UzA2Y1VIcEQtZDg3cEU2SmlzQnBmUVVvM0ZNYzZWNExWUXQ3aHpnd3lqOHFVV3pNbDRLS1NQNGtwb2RjSFpleHJkOG5zSXVtWjVIS1dLejNybktRWTJVZXh3WkFUQVE5T2tMdFdn?oc=5 | https://news.google.com/rss/articles/CBMilwFBVV95cUxQMF9BNnUzLURKNGRMUUJ1VXVRSXNnMlBsQnVXOG0tRlFtY3pvRDNPQmNJMWN2RzJVaWdoWndmcHFnTkZFZnJxRkZtMThYYWlwN09ueUgtei1pSE1hZ2FtSzN6elY4VXJHbzFxdll0eWh0ZkxwQkQ1SDZ5b0E3MlVENGZEWGZHUGlwVG4wd2x3OFNEMVpibnFr?oc=5 | https://news.google.com/rss/articles/CBMimgFBVV95cUxNbmwzSnd6c2tFMXBWY0tiemJqRm5CNllOT2p1U0FhdW5QNGFBVXlSZVM1ak5jNGZvcXNVaUQzN3ZQQTlPbmVjQ2Y5RFl2dWVLeUN5NUFodDF0alEyZWlmOHFZWkVVbjdQbkl3ZWtmS25wQWM2TmRZZDBGM2xlS0ZhUzAweXRmcmhVWGY5dV9CUnFBNGtWZHZDSWVB?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-24:viento:1</t>
+          <t>noticia:1uil931</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-23 20:55</t>
+          <t>2026-10-23 22:49</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1792803329663</v>
+        <v>1792810149000</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-24: 78.1 km/h de ráfagas pronosticadas</t>
+          <t>Accidente de tránsito en la ruta hacia Alto Beni deja varios heridos - El Deber</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1977,7 +1977,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1985,57 +1985,57 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>El Deber</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>-17.78</v>
+        <v>-15.578</v>
       </c>
       <c r="N21" t="n">
-        <v>-63.18</v>
+        <v>-67.44</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Alto Beni, La Paz</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Alto Beni</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQakFJRmx3RlJEMkVHU0pxWXZ2ZU1ib04tZy1yeTB2OGhrYk9CU3pMaDVpRThNZktZMS14UzA2Y1VIcEQtZDg3cEU2SmlzQnBmUVVvM0ZNYzZWNExWUXQ3aHpnd3lqOHFVV3pNbDRLS1NQNGtwb2RjSFpleHJkOG5zSXVtWjVIS1dLejNybktRWTJVZXh3WkFUQVE5T2tMdFdn?oc=5 | https://news.google.com/rss/articles/CBMilwFBVV95cUxQMF9BNnUzLURKNGRMUUJ1VXVRSXNnMlBsQnVXOG0tRlFtY3pvRDNPQmNJMWN2RzJVaWdoWndmcHFnTkZFZnJxRkZtMThYYWlwN09ueUgtei1pSE1hZ2FtSzN6elY4VXJHbzFxdll0eWh0ZkxwQkQ1SDZ5b0E3MlVENGZEWGZHUGlwVG4wd2x3OFNEMVpibnFr?oc=5 | https://news.google.com/rss/articles/CBMimgFBVV95cUxNbmwzSnd6c2tFMXBWY0tiemJqRm5CNllOT2p1U0FhdW5QNGFBVXlSZVM1ak5jNGZvcXNVaUQzN3ZQQTlPbmVjQ2Y5RFl2dWVLeUN5NUFodDF0alEyZWlmOHFZWkVVbjdQbkl3ZWtmS25wQWM2TmRZZDBGM2xlS0ZhUzAweXRmcmhVWGY5dV9CUnFBNGtWZHZDSWVB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>noticia:rabz5p</t>
+          <t>clima:Santa Cruz:2026-10-24:viento:1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-23 20:44</t>
+          <t>2026-10-23 20:55</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1792802686000</v>
+        <v>1792803329663</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Tome previsiones: se pronostican lluvias y ambiente caluroso para este fin de semana en Cochabamba - Red Uno</t>
+          <t>Santa Cruz 2026-10-24: 78.1 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2044,11 +2044,11 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -2067,70 +2067,70 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>-17.39</v>
+        <v>-17.78</v>
       </c>
       <c r="N22" t="n">
-        <v>-66.16</v>
+        <v>-63.18</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Cochabamba, Cochabamba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTlU5NVFpY1RheTN5ZE1IbG5VYTh2Sk5hZHpHeWI3LVdnSFg2cFJFdnBCVkxiUjNKcUgyUW16SWxpMXFkMHdad2xFN043bklJeG1iQ0V1V3hBZk1Ga3NscjdPVWUySmt4bDNTdWlmSUdOMmNlZ2hkSWZFMmk4VGs0Nm9TcnRCTDhINmtnQU9zZDBUY05HcWpxN3FOX3N1dmVJblE0MGc5di1Ma1N2dGNxOUtoV1MzNnl1OXpRaTZ2UGxMc3RDWndubHVQNUd0eVROMGR2OGxVemtOaEc4bTNRaA?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>noticia:1jfk053</t>
+          <t>noticia:rabz5p</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-23 19:08</t>
+          <t>2026-10-23 20:44</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1792796931000</v>
+        <v>1792802686000</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sequía en Pasorapa: el ganado muere por falta de agua y alistan declaratoria de desastre - Red Uno</t>
+          <t>Tome previsiones: se pronostican lluvias y ambiente caluroso para este fin de semana en Cochabamba - Red Uno</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>climatológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2149,14 +2149,14 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>-18.38</v>
+        <v>-17.39</v>
       </c>
       <c r="N23" t="n">
-        <v>-64.649</v>
+        <v>-66.16</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Pasorapa, Cochabamba</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2166,49 +2166,49 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Pasorapa</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNQVhTWE8zdE1BQ3lueWJPeV9wUDNsSmJpS0NJTWppMUY4QmlQSUFHVjRORmtrVHQ3MHB0T1pyS25PamxnY0hBQUtzOVRvSUNaUkdGb1RWSGl4dFA4Z3VINVpQTk1pZUpDdUIyUU5hZS1oNGhBa1RWcFhScVMwVTFrVlJaOFQ4OWFqRWVUZ051bHVJTlMxRTBhRFVLUEV2dTZFdDgtRkxJM3VvN3YzUWJfVk41ZWR5U1JoNmx0WFFkMmNTWGVleGNIQlNxWUJzdHIxSWtz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTlU5NVFpY1RheTN5ZE1IbG5VYTh2Sk5hZHpHeWI3LVdnSFg2cFJFdnBCVkxiUjNKcUgyUW16SWxpMXFkMHdad2xFN043bklJeG1iQ0V1V3hBZk1Ga3NscjdPVWUySmt4bDNTdWlmSUdOMmNlZ2hkSWZFMmk4VGs0Nm9TcnRCTDhINmtnQU9zZDBUY05HcWpxN3FOX3N1dmVJblE0MGc5di1Ma1N2dGNxOUtoV1MzNnl1OXpRaTZ2UGxMc3RDWndubHVQNUd0eVROMGR2OGxVemtOaEc4bTNRaA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>noticia:ix3l8o</t>
+          <t>noticia:1jfk053</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-23 18:25</t>
+          <t>2026-10-23 19:08</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1792794310000</v>
+        <v>1792796931000</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Oruro evalúa suspender clases presenciales por más de 200 casos de Coxsackie - Visión 360</t>
+          <t>Sequía en Pasorapa: el ganado muere por falta de agua y alistan declaratoria de desastre - Red Uno</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>climatológica</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2219,77 +2219,77 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Red Uno; Visión 360</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>-17.97</v>
+        <v>-18.38</v>
       </c>
       <c r="N24" t="n">
-        <v>-67.11</v>
+        <v>-64.649</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>Pasorapa, Cochabamba</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Pasorapa</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0c9IBywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0cw?oc=5 | https://news.google.com/rss/articles/CBMiywFBVV95cUxNMFdHaVpKRmMyOENDYm16UXJPenVSQnpmTE94bDc4UFhqakluMUdvZjAwamUxT3BVWUpJQm8xVHBWengxQmhWM1hjU3d2YXFrLXpVU2VrZDJiMXZLMlQ5bGxGOHFETFhYM0s2RjlUTlhkd0g2eXQweDFHaTlKNGNMUlJfOWg2a0JjTklXUWZKc1BmUXZuZFZ2MF9fV2lEYUY4LXNiNmk3cF9FNjVtTl9GWFotT2ltS0xXTnM1dENvSU9kbFRMalFrYVdXOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNQVhTWE8zdE1BQ3lueWJPeV9wUDNsSmJpS0NJTWppMUY4QmlQSUFHVjRORmtrVHQ3MHB0T1pyS25PamxnY0hBQUtzOVRvSUNaUkdGb1RWSGl4dFA4Z3VINVpQTk1pZUpDdUIyUU5hZS1oNGhBa1RWcFhScVMwVTFrVlJaOFQ4OWFqRWVUZ051bHVJTlMxRTBhRFVLUEV2dTZFdDgtRkxJM3VvN3YzUWJfVk41ZWR5U1JoNmx0WFFkMmNTWGVleGNIQlNxWUJzdHIxSWtz?oc=5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>noticia:1xqv9m7</t>
+          <t>noticia:ix3l8o</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-23 18:09</t>
+          <t>2026-10-23 18:25</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1792793370000</v>
+        <v>1792794310000</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tres heridos en tremendo choque cerca de Oncativo - El Diario del centro del país</t>
+          <t>Oruro evalúa suspender clases presenciales por más de 200 casos de Coxsackie - Visión 360</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2297,61 +2297,77 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>El Diario del centro del país</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
+          <t>Red Uno; Visión 360</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>-17.97</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-67.11</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Oruro, Oruro</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZERhbTJMQUJVb3hmZFlSZmRGZkdBLWdFTGJVQzdqZkE4aGhhWmdQZ2JDRW1ndkJLWU90VTZ6Ti1JOUZzcFZfcE1zbkRHU1B3YTF4UkVzdllFa1p3SUlObURGamF0Vm9kc3dPLTZVWFJ4NWZZQmlySElPNHhZTnRGNGNZUWw2ZlI1eVBEQkNGNEhLWTNiLWJLUS0xYjA0UWRhc0d6bVN4aVVLSVdsQWlpMUZYdWw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0c9IBywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0cw?oc=5 | https://news.google.com/rss/articles/CBMiywFBVV95cUxNMFdHaVpKRmMyOENDYm16UXJPenVSQnpmTE94bDc4UFhqakluMUdvZjAwamUxT3BVWUpJQm8xVHBWengxQmhWM1hjU3d2YXFrLXpVU2VrZDJiMXZLMlQ5bGxGOHFETFhYM0s2RjlUTlhkd0g2eXQweDFHaTlKNGNMUlJfOWg2a0JjTklXUWZKc1BmUXZuZFZ2MF9fV2lEYUY4LXNiNmk3cF9FNjVtTl9GWFotT2ltS0xXTnM1dENvSU9kbFRMalFrYVdXOA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>noticia:1itd1r7</t>
+          <t>noticia:1xqv9m7</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-23 15:01</t>
+          <t>2026-10-23 18:09</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1792782098000</v>
+        <v>1792793370000</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Intensa lluvia y granizada en La Paz inundan vías y elevan el nivel de los ríos - eju.tv</t>
+          <t>Tres heridos en tremendo choque cerca de Oncativo - El Diario del centro del país</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2363,73 +2379,57 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>eju.tv</t>
-        </is>
-      </c>
-      <c r="M26" t="n">
-        <v>-16.169</v>
-      </c>
-      <c r="N26" t="n">
-        <v>-68.09</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>La Paz, La Paz</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>La Paz</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>Nuestra Señora de La Paz</t>
-        </is>
-      </c>
+          <t>El Diario del centro del país</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNWU9QWElKQXEyN3UxVm4xbzJzbEJ1TU1NTHZlRUp6YndmeU9GQnJKcTluVEJ2ZHQ5cGp3aWhlMUd5ektWQlBpUVNmZnZuRnJwMXlydzAzX0FBVnY5UDMzQTBkWVRNRUNJSlRvX3MyQVhMcEhIMW9WSUpXckVSd0RJWk1KMFBKWmJNU3diQVlEN1Y5aVV6eVBaZXpOMnFIWWxaMlRlY0ZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZERhbTJMQUJVb3hmZFlSZmRGZkdBLWdFTGJVQzdqZkE4aGhhWmdQZ2JDRW1ndkJLWU90VTZ6Ti1JOUZzcFZfcE1zbkRHU1B3YTF4UkVzdllFa1p3SUlObURGamF0Vm9kc3dPLTZVWFJ4NWZZQmlySElPNHhZTnRGNGNZUWw2ZlI1eVBEQkNGNEhLWTNiLWJLUS0xYjA0UWRhc0d6bVN4aVVLSVdsQWlpMUZYdWw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>noticia:51709n</t>
+          <t>noticia:1itd1r7</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-23 13:38</t>
+          <t>2026-10-23 15:01</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1792777139000</v>
+        <v>1792782098000</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - eju.tv</t>
+          <t>Intensa lluvia y granizada en La Paz inundan vías y elevan el nivel de los ríos - eju.tv</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2437,77 +2437,77 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Red Uno; eju.tv</t>
+          <t>eju.tv</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>-17.764</v>
+        <v>-16.169</v>
       </c>
       <c r="N27" t="n">
-        <v>-62.903</v>
+        <v>-68.09</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Cotoca, Santa Cruz</t>
+          <t>La Paz, La Paz</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>Cotoca</t>
+          <t>Nuestra Señora de La Paz</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPcjZTSmprRGVoNlRqQmdBTE5VM3pRQ1ZFakFUbzVyMUhiaDVkT0liaG9UNEZXekV6bWsycUk4X1JCSEY5RjhNVlZaTk9ULUFuZkY3NnZuWmZ1a19leUhFdlIyQV9kLWxlSkxfeXFhcFRTZjZ2YkpQQlJ1dkNLMDBjaGZ4SkhyQ0RfcnhKSEg5WURCQVQwbENYTHEzUzJSaUEzMGo2bWdyS3lsM016LXc?oc=5 | https://news.google.com/rss/articles/CBMi0AFBVV95cUxOVGY3YVRLWWxYM0IycjF4dlNUeUhqZG90Yng4aWhmN3A5ai02WENWYnF4bWpoZHFKMGc1X0JPRHdRRVZfSlA4UmZFa2kxYkNIS3ZtQ1NvNlNCME51eVZTRkRKSUQ5MmRoaWl5Tkt5NHpPUEFwemN2YTV1djFwdHlqQnFqRHNPenhYcTlsanJPcXhpOVV1NmFBUXZyazQ2MkUzM0dSZy02ZllxTGtjcl9ldzdHSktTRlVaalZJc1pubUNQMWFTbzVEOUJ1UmhCdEJt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNWU9QWElKQXEyN3UxVm4xbzJzbEJ1TU1NTHZlRUp6YndmeU9GQnJKcTluVEJ2ZHQ5cGp3aWhlMUd5ektWQlBpUVNmZnZuRnJwMXlydzAzX0FBVnY5UDMzQTBkWVRNRUNJSlRvX3MyQVhMcEhIMW9WSUpXckVSd0RJWk1KMFBKWmJNU3diQVlEN1Y5aVV6eVBaZXpOMnFIWWxaMlRlY0ZB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>noticia:11rddql</t>
+          <t>noticia:51709n</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-23 13:22</t>
+          <t>2026-10-23 13:38</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1792776139000</v>
+        <v>1792777139000</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Intensifican acciones preventivas contra el dengue en Caranavi - El Diario - Bolivia</t>
+          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - eju.tv</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2515,77 +2515,77 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>Red Uno; eju.tv</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>-15.813</v>
+        <v>-17.764</v>
       </c>
       <c r="N28" t="n">
-        <v>-67.46299999999999</v>
+        <v>-62.903</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Caranavi, La Paz</t>
+          <t>Cotoca, Santa Cruz</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>Caranavi</t>
+          <t>Cotoca</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOMjhSeDJBek5iaFhDcnFzX1lKelgwZmUwLTJnbEhMdDRMelUxNks5Ti1pRHh3dDhTcC1YZEdqM3FJOGdqVHRvcXVhRlpCQzVDTEZMUFBkV1NrYVQ2LXRqTTBhcGRQc21CQ0VabzZaNExXb1BjTzJ2Uk5BcFF0VG5XOFNRa3lqUWlJSnRFUUVXYnNpbXB0LVVmSXVWSzJxcmVpdVVxUC1KOUhTQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPcjZTSmprRGVoNlRqQmdBTE5VM3pRQ1ZFakFUbzVyMUhiaDVkT0liaG9UNEZXekV6bWsycUk4X1JCSEY5RjhNVlZaTk9ULUFuZkY3NnZuWmZ1a19leUhFdlIyQV9kLWxlSkxfeXFhcFRTZjZ2YkpQQlJ1dkNLMDBjaGZ4SkhyQ0RfcnhKSEg5WURCQVQwbENYTHEzUzJSaUEzMGo2bWdyS3lsM016LXc?oc=5 | https://news.google.com/rss/articles/CBMi0AFBVV95cUxOVGY3YVRLWWxYM0IycjF4dlNUeUhqZG90Yng4aWhmN3A5ai02WENWYnF4bWpoZHFKMGc1X0JPRHdRRVZfSlA4UmZFa2kxYkNIS3ZtQ1NvNlNCME51eVZTRkRKSUQ5MmRoaWl5Tkt5NHpPUEFwemN2YTV1djFwdHlqQnFqRHNPenhYcTlsanJPcXhpOVV1NmFBUXZyazQ2MkUzM0dSZy02ZllxTGtjcl9ldzdHSktTRlVaalZJc1pubUNQMWFTbzVEOUJ1UmhCdEJt?oc=5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>noticia:fcm3nx</t>
+          <t>noticia:11rddql</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-23 12:58</t>
+          <t>2026-10-23 13:22</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1792774699000</v>
+        <v>1792776139000</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>[VIDEO] Así fue el accidente de moto que dejó un adolescente fallecido y un hombre gravemente herido - Red Uno</t>
+          <t>Intensifican acciones preventivas contra el dengue en Caranavi - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2597,57 +2597,73 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Red Uno</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
+          <t>El Diario - Bolivia</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>-15.813</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-67.46299999999999</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Caranavi, La Paz</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>La Paz</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Caranavi</t>
+        </is>
+      </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOSmJMazhUemNfRHpWcDBoTVFZMUpwdlVKVUtvUXZNTGRRRHlwLW5KNmNhcmFnd1czbi1yalhFMnpSS1dmUE9jVzNlOS1kMWZtRzBHZ2EtcDRDdU5Gc2JUQVIwM2xPa2lZVmswRi1SUFVPcm8xcHlGN3F2UThTSDdKMDNyYnJmVkcxazNLLVBLOWFYM09FVUpmVnN5RVhpSVo2V1VCVmFwQ1gzTmRUWVp2aXMwcmxHRS1GV2p3NTBtR2RzM2wwVHUzaGJkRXJYbHdvaDlhWm5YMTk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOMjhSeDJBek5iaFhDcnFzX1lKelgwZmUwLTJnbEhMdDRMelUxNks5Ti1pRHh3dDhTcC1YZEdqM3FJOGdqVHRvcXVhRlpCQzVDTEZMUFBkV1NrYVQ2LXRqTTBhcGRQc21CQ0VabzZaNExXb1BjTzJ2Uk5BcFF0VG5XOFNRa3lqUWlJSnRFUUVXYnNpbXB0LVVmSXVWSzJxcmVpdVVxUC1KOUhTQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>noticia:1cjx1qd</t>
+          <t>noticia:fcm3nx</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-23 12:39</t>
+          <t>2026-10-23 12:58</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1792773575000</v>
+        <v>1792774699000</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Más de 60 municipios en La Paz sufren falta de lluvias - La Patria Bolivia</t>
+          <t>[VIDEO] Así fue el accidente de moto que dejó un adolescente fallecido y un hombre gravemente herido - Red Uno</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2659,53 +2675,37 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
-        </is>
-      </c>
-      <c r="M30" t="n">
-        <v>-16.169</v>
-      </c>
-      <c r="N30" t="n">
-        <v>-68.09</v>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>La Paz, La Paz</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>La Paz</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>Nuestra Señora de La Paz</t>
-        </is>
-      </c>
+          <t>Red Uno</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE52Qi03Z1J6OS1CR2liRVZ0VlhCcmVQWFV6RUdGNXdrbzZRNXFjTWRaRnc1b3VoV0xaY3RIdncxNlNnYkxyUXo5MTlJWmMwWDNSMDE4ZHI2VkpWajFPaUF2SmRVYkk2eDZYQ1RfUU9ieENrZG9UVVFiaXZSeGI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOSmJMazhUemNfRHpWcDBoTVFZMUpwdlVKVUtvUXZNTGRRRHlwLW5KNmNhcmFnd1czbi1yalhFMnpSS1dmUE9jVzNlOS1kMWZtRzBHZ2EtcDRDdU5Gc2JUQVIwM2xPa2lZVmswRi1SUFVPcm8xcHlGN3F2UThTSDdKMDNyYnJmVkcxazNLLVBLOWFYM09FVUpmVnN5RVhpSVo2V1VCVmFwQ1gzTmRUWVp2aXMwcmxHRS1GV2p3NTBtR2RzM2wwVHUzaGJkRXJYbHdvaDlhWm5YMTk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>clima:Sucre:2026-10-23:viento:1</t>
+          <t>noticia:1cjx1qd</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-23 06:55</t>
+          <t>2026-10-23 12:39</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1792752927735</v>
+        <v>1792773575000</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sucre 2026-10-23: 66.2 km/h de ráfagas pronosticadas</t>
+          <t>Más de 60 municipios en La Paz sufren falta de lluvias - La Patria Bolivia</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2714,11 +2714,11 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -2737,40 +2737,40 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>La Patria Bolivia</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>-19.03</v>
+        <v>-16.169</v>
       </c>
       <c r="N31" t="n">
-        <v>-65.26000000000001</v>
+        <v>-68.09</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>La Paz, La Paz</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Chuquisaca</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Nuestra Señora de La Paz</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE52Qi03Z1J6OS1CR2liRVZ0VlhCcmVQWFV6RUdGNXdrbzZRNXFjTWRaRnc1b3VoV0xaY3RIdncxNlNnYkxyUXo5MTlJWmMwWDNSMDE4ZHI2VkpWajFPaUF2SmRVYkk2eDZYQ1RfUU9ieENrZG9UVVFiaXZSeGI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-24:viento:2</t>
+          <t>clima:Sucre:2026-10-23:viento:1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2779,11 +2779,11 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1792752927734</v>
+        <v>1792752927735</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-24: 85 km/h de ráfagas pronosticadas</t>
+          <t>Sucre 2026-10-23: 66.2 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2792,11 +2792,11 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -2819,24 +2819,24 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>-17.78</v>
+        <v>-19.03</v>
       </c>
       <c r="N32" t="n">
-        <v>-63.18</v>
+        <v>-65.26000000000001</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Chuquisaca</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -2848,33 +2848,33 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>usgs:us6000u49c</t>
+          <t>clima:Santa Cruz:2026-10-24:viento:2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-22 22:45</t>
+          <t>2026-10-23 06:55</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1792723541183</v>
+        <v>1792752927734</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sismo M 4.5 - 58 km SW of Atocha, Bolivia</t>
+          <t>Santa Cruz 2026-10-24: 85 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>geológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -2893,58 +2893,58 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>USGS</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>-21.3469</v>
+        <v>-17.78</v>
       </c>
       <c r="N33" t="n">
-        <v>-66.5795</v>
+        <v>-63.18</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>58 km SW of Atocha, Bolivia</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>San Pablo</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>https://earthquake.usgs.gov/earthquakes/eventpage/us6000u49c</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-22:viento:1</t>
+          <t>usgs:us6000u49c</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-22 21:55</t>
+          <t>2026-10-22 22:45</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1792720528712</v>
+        <v>1792723541183</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-22: 67.7 km/h de ráfagas pronosticadas</t>
+          <t>Sismo M 4.5 - 58 km SW of Atocha, Bolivia</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>geológica</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -2971,40 +2971,40 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>USGS</t>
         </is>
       </c>
       <c r="M34" t="n">
-        <v>-17.78</v>
+        <v>-21.3469</v>
       </c>
       <c r="N34" t="n">
-        <v>-63.18</v>
+        <v>-66.5795</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>58 km SW of Atocha, Bolivia</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>San Pablo</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://earthquake.usgs.gov/earthquakes/eventpage/us6000u49c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-23:viento:2</t>
+          <t>clima:Santa Cruz:2026-10-22:viento:1</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-23: 83.9 km/h de ráfagas pronosticadas</t>
+          <t>Santa Cruz 2026-10-22: 67.7 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3026,11 +3026,11 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -3082,33 +3082,33 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>noticia:1hhvre7</t>
+          <t>clima:Santa Cruz:2026-10-23:viento:2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-22 19:36</t>
+          <t>2026-10-22 21:55</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1792712202000</v>
+        <v>1792720528712</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Virgen de Cotoca: Controlan incendio en depósito de materiales plásticos - El Mundo Bolivia</t>
+          <t>Santa Cruz 2026-10-23: 83.9 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -3127,18 +3127,18 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>El Mundo Bolivia</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="M36" t="n">
-        <v>-17.764</v>
+        <v>-17.78</v>
       </c>
       <c r="N36" t="n">
-        <v>-62.903</v>
+        <v>-63.18</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Cotoca, Santa Cruz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3148,32 +3148,32 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>Cotoca</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcDF6VE5FNzRaWGRuUzFKeXhnZ21DZTRaaEtrVEJEa1Z3ejg2VG1ONG1ENmlDWlkyVjlkQkJwS2F1XzBGMFQwSHd4OEwxTW1PbHdGcUh1ckV6SGpDd2hiN0dkeUVTcnFXT3RjOU1kLXZtVVdZY2hkZS1pcVpVUFhnRktqcHY5UnBrY0xUMDRETjl6N0pXT3A5amxhMA?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>noticia:bksnde</t>
+          <t>noticia:1hhvre7</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-22 17:01</t>
+          <t>2026-10-22 19:36</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1792702880000</v>
+        <v>1792712202000</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Reportan un incendio cerca de la carretera a Cotoca - eju.tv</t>
+          <t>Virgen de Cotoca: Controlan incendio en depósito de materiales plásticos - El Mundo Bolivia</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>eju.tv</t>
+          <t>El Mundo Bolivia</t>
         </is>
       </c>
       <c r="M37" t="n">
@@ -3231,27 +3231,27 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPNGtpbnBfRnRBalVudnBlZHdVQ0ZSaUplZmtvTGE0aTQzdkxWS3d4My1EZEJ1UE9FNFQ3RmpyZGVsbS1qNEM1QUVFRFAxM2pYT1VqQzRuVjRtZnVNUGlKODNMc0F1a3l6TUpuQmtlUWNlVTVEWWU5ZGZtQm5LWUp3Sg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcDF6VE5FNzRaWGRuUzFKeXhnZ21DZTRaaEtrVEJEa1Z3ejg2VG1ONG1ENmlDWlkyVjlkQkJwS2F1XzBGMFQwSHd4OEwxTW1PbHdGcUh1ckV6SGpDd2hiN0dkeUVTcnFXT3RjOU1kLXZtVVdZY2hkZS1pcVpVUFhnRktqcHY5UnBrY0xUMDRETjl6N0pXT3A5amxhMA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>noticia:17hz69v</t>
+          <t>noticia:bksnde</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-22 13:05</t>
+          <t>2026-10-22 17:01</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1792688709000</v>
+        <v>1792702880000</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Accidente en El Sillar deja al menos 29 heridos - La Razón Digital Bolivia</t>
+          <t>Reportan un incendio cerca de la carretera a Cotoca - eju.tv</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3260,18 +3260,18 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -3283,37 +3283,53 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>La Razón Digital Bolivia</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
+          <t>eju.tv</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>-17.764</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-62.903</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Cotoca, Santa Cruz</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Cotoca</t>
+        </is>
+      </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPaXhTdm45YWZnWVFxVzJnb1ZwbUN4SmUtLVdJN0VJdFZBamRyQmFxN0RZelBfTklaSTVyOUZ3ajQ5MFB2TEN4Ukd6TE5ORFY5SEROVk1CZ25sRWJ1QnRBdTVfTktlby1NWXhaVWI5YnRvaDZWbHVjdDVoeFp5Tk5veFk5a19MSWJqcEJVV0dzV3k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPNGtpbnBfRnRBalVudnBlZHdVQ0ZSaUplZmtvTGE0aTQzdkxWS3d4My1EZEJ1UE9FNFQ3RmpyZGVsbS1qNEM1QUVFRFAxM2pYT1VqQzRuVjRtZnVNUGlKODNMc0F1a3l6TUpuQmtlUWNlVTVEWWU5ZGZtQm5LWUp3Sg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>noticia:1f1qb0</t>
+          <t>noticia:17hz69v</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-22 12:09</t>
+          <t>2026-10-22 13:05</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1792685373000</v>
+        <v>1792688709000</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Accidente en el tramo Locotal–Villa Tunari: la vía está transitable con precaución - Red Uno</t>
+          <t>Accidente en El Sillar deja al menos 29 heridos - La Razón Digital Bolivia</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3322,18 +3338,18 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -3345,73 +3361,57 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Red Uno</t>
-        </is>
-      </c>
-      <c r="M39" t="n">
-        <v>-16.556</v>
-      </c>
-      <c r="N39" t="n">
-        <v>-65.569</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>Villa Tunari, Cochabamba</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>Villa Tunari</t>
-        </is>
-      </c>
+          <t>La Razón Digital Bolivia</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTFozcEEwNXBqV19sS2VibXh0MGt0QlhsX1djSTFGQW5zNlFLRHZpNVVnZ1JmWDQ4LVRHX2Rmb3B5UU9qV0FZQmJCaUZYdmwyNG1NenJ4Qzlzd0NJTGs1SjMxdFRtRFBzSUkybGJfZFFaNFZBc21FSUJYSFVkQkVkSEhQaGw0UFVzeXctZHo3cjNsYm5weXJlOU1wcmFncnNhMC1BQUpvNWlDX1NxZXU4b09kVFFWR2tSVEk2UTdXXzB3TjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPaXhTdm45YWZnWVFxVzJnb1ZwbUN4SmUtLVdJN0VJdFZBamRyQmFxN0RZelBfTklaSTVyOUZ3ajQ5MFB2TEN4Ukd6TE5ORFY5SEROVk1CZ25sRWJ1QnRBdTVfTktlby1NWXhaVWI5YnRvaDZWbHVjdDVoeFp5Tk5veFk5a19MSWJqcEJVV0dzV3k?oc=5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>noticia:wi18tm</t>
+          <t>noticia:1f1qb0</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-22 11:53</t>
+          <t>2026-10-22 12:09</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1792684426000</v>
+        <v>1792685373000</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Accidente en El Sillar deja heridos y derrame de combustible: esto es lo último que se sabe - Red Uno</t>
+          <t>Accidente en el tramo Locotal–Villa Tunari: la vía está transitable con precaución - Red Uno</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>tecnológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -3426,54 +3426,70 @@
           <t>Red Uno</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
+      <c r="M40" t="n">
+        <v>-16.556</v>
+      </c>
+      <c r="N40" t="n">
+        <v>-65.569</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Villa Tunari, Cochabamba</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Villa Tunari</t>
+        </is>
+      </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPZHNBTEdaQm5Wby1lTF9mWlQ2aGg0MVc4S0MwVWJ3dUJ5WWU5X3IwYWhKRjk5VWtYWEJHRDF4QldVc29laVNPSTJNWFBDSkNFQlFSYTJUXzNMNF9hckFBN1I2T2xoQUtYQ2V6MDNTZHhHVk9qeTBCdHRpM2ZLd0pyOFRweUUxX19STzRHTHg5VUY5d1lhS0tDeXpCdklqcTZGT1J4R0xnSDhoak1EZ2dtNUhSTUV6b1o0U0VSdWY5X0E3U05Tc1dYVEN2WFZUeFhPMTBJTmowNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTFozcEEwNXBqV19sS2VibXh0MGt0QlhsX1djSTFGQW5zNlFLRHZpNVVnZ1JmWDQ4LVRHX2Rmb3B5UU9qV0FZQmJCaUZYdmwyNG1NenJ4Qzlzd0NJTGs1SjMxdFRtRFBzSUkybGJfZFFaNFZBc21FSUJYSFVkQkVkSEhQaGw0UFVzeXctZHo3cjNsYm5weXJlOU1wcmFncnNhMC1BQUpvNWlDX1NxZXU4b09kVFFWR2tSVEk2UTdXXzB3TjA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>noticia:12gfagq</t>
+          <t>noticia:wi18tm</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-22 11:28</t>
+          <t>2026-10-22 11:53</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1792682880000</v>
+        <v>1792684426000</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Reportan triple colisión entre dos camiones y un bus en la carretera Cochabamba-Santa Cruz - FmBolivia</t>
+          <t>Accidente en El Sillar deja heridos y derrame de combustible: esto es lo último que se sabe - Red Uno</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>tecnológica</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -3481,57 +3497,41 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>FmBolivia; Red Uno</t>
-        </is>
-      </c>
-      <c r="M41" t="n">
-        <v>-17.39</v>
-      </c>
-      <c r="N41" t="n">
-        <v>-66.16</v>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>Cochabamba, Cochabamba</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
+          <t>Red Uno</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNMTNBaFZNMU9SR25vdVBuNXlZY3g4VkFWYXRiQnNSaUFjemZhUHZWNHg4V2owU2xfNndBak94TnU2cHNUVXdNNWl2eUdHZVNMbVZweTR5M0o0bWdTNUN4QkoxUkI2TDBmVE03M09zRGhJRVFzV0tPZ1NCWEJLUkt1ZGN4UGduOUZMQnJoM0tMYTh0ZlFxaFJNUkJqaWFPazRlMzN3ajhjUEdUYXlZRndpb3RSdTFCX2tCZGJxQ0x4SlBISWJsRVoyN3ZR?oc=5 | https://news.google.com/rss/articles/CBMirwFBVV95cUxNNUROMzd1UDJRWVZZQ011cFd2c1FSdER1ZzdleU04cXpwYk5HaUZrLXoyU2NzdFk1dnNRUndhUWt0cG9DX09rSjlLcDItU0tzcmQtS3E4dDQ4ZF9HdGJLdk13ek9BNHJUWVlCcklrM25rZ01RbXhLalRBT1FGdDNReHdlTFZkNkJ5ZFd3N3NZVFVmOFUxbEhHN0RsaUxiSVZsM0lXVEFYSHVRQlhsOEtJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPZHNBTEdaQm5Wby1lTF9mWlQ2aGg0MVc4S0MwVWJ3dUJ5WWU5X3IwYWhKRjk5VWtYWEJHRDF4QldVc29laVNPSTJNWFBDSkNFQlFSYTJUXzNMNF9hckFBN1I2T2xoQUtYQ2V6MDNTZHhHVk9qeTBCdHRpM2ZLd0pyOFRweUUxX19STzRHTHg5VUY5d1lhS0tDeXpCdklqcTZGT1J4R0xnSDhoak1EZ2dtNUhSTUV6b1o0U0VSdWY5X0E3U05Tc1dYVEN2WFZUeFhPMTBJTmowNA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>noticia:1jl2oid</t>
+          <t>noticia:12gfagq</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-22 07:49</t>
+          <t>2026-10-22 11:28</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1792669785000</v>
+        <v>1792682880000</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - eju.tv</t>
+          <t>Reportan triple colisión entre dos camiones y un bus en la carretera Cochabamba-Santa Cruz - FmBolivia</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3540,18 +3540,18 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -3563,109 +3563,187 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Red Uno; eju.tv</t>
+          <t>FmBolivia; Red Uno</t>
         </is>
       </c>
       <c r="M42" t="n">
-        <v>-17.781</v>
+        <v>-17.39</v>
       </c>
       <c r="N42" t="n">
-        <v>-63.139</v>
+        <v>-66.16</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Santa Cruz, Santa Cruz</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQbTBrUmlla3FvVU1EX1pxcUI3SXYzbUFFMzlnRzhlSDJwMGpWWURxYjIwSkJBRGdCazMzT01hVy1qMFY3RnJLbC1XNXJ4bU55aDJVeXpNUlRsbzQ3T3hiRXJ5SWlhNmw5cDZFanNoWFBtQ01Gd3dscXltWmU5VHBSQlN3c2IwNGxuVE5tQ3lOT1RmNzRiVi1hc0hn?oc=5 | https://news.google.com/rss/articles/CBMiuwFBVV95cUxNVEh1bFlCanFuOTJid2EzYS1meG5oekFJcGFaME1fTk9sUnZpd3U0UXFHUFVJSW1jc1hzM2VFOFprT2xNYjBzbmswZmdJV3dremRIS0I4MDNzRjBnbEttWEhfOWZBbmFrRnNHWDFVLVFoM0VkZkxkaW4tMmZlSFJLei1heTFHMU0wSmxQVVRZN0cwaXQzcDBtZkdwTUFma0RXU2dwLXRnLTBkNGN3Vm1fV3hEdlM1dWZ1SEsw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNMTNBaFZNMU9SR25vdVBuNXlZY3g4VkFWYXRiQnNSaUFjemZhUHZWNHg4V2owU2xfNndBak94TnU2cHNUVXdNNWl2eUdHZVNMbVZweTR5M0o0bWdTNUN4QkoxUkI2TDBmVE03M09zRGhJRVFzV0tPZ1NCWEJLUkt1ZGN4UGduOUZMQnJoM0tMYTh0ZlFxaFJNUkJqaWFPazRlMzN3ajhjUEdUYXlZRndpb3RSdTFCX2tCZGJxQ0x4SlBISWJsRVoyN3ZR?oc=5 | https://news.google.com/rss/articles/CBMirwFBVV95cUxNNUROMzd1UDJRWVZZQ011cFd2c1FSdER1ZzdleU04cXpwYk5HaUZrLXoyU2NzdFk1dnNRUndhUWt0cG9DX09rSjlLcDItU0tzcmQtS3E4dDQ4ZF9HdGJLdk13ek9BNHJUWVlCcklrM25rZ01RbXhLalRBT1FGdDNReHdlTFZkNkJ5ZFd3N3NZVFVmOFUxbEhHN0RsaUxiSVZsM0lXVEFYSHVRQlhsOEtJ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>noticia:1jl2oid</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-10-22 07:49</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1792669785000</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - eju.tv</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>antropogénica</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>amarilla</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>2</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Red Uno; eju.tv</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>-17.781</v>
+      </c>
+      <c r="N43" t="n">
+        <v>-63.139</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Santa Cruz, Santa Cruz</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Santa Cruz de la Sierra</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQbTBrUmlla3FvVU1EX1pxcUI3SXYzbUFFMzlnRzhlSDJwMGpWWURxYjIwSkJBRGdCazMzT01hVy1qMFY3RnJLbC1XNXJ4bU55aDJVeXpNUlRsbzQ3T3hiRXJ5SWlhNmw5cDZFanNoWFBtQ01Gd3dscXltWmU5VHBSQlN3c2IwNGxuVE5tQ3lOT1RmNzRiVi1hc0hn?oc=5 | https://news.google.com/rss/articles/CBMiuwFBVV95cUxNVEh1bFlCanFuOTJid2EzYS1meG5oekFJcGFaME1fTk9sUnZpd3U0UXFHUFVJSW1jc1hzM2VFOFprT2xNYjBzbmswZmdJV3dremRIS0I4MDNzRjBnbEttWEhfOWZBbmFrRnNHWDFVLVFoM0VkZkxkaW4tMmZlSFJLei1heTFHMU0wSmxQVVRZN0cwaXQzcDBtZkdwTUFma0RXU2dwLXRnLTBkNGN3Vm1fV3hEdlM1dWZ1SEsw?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>noticia:n32ahi</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>2026-10-22 05:30</t>
         </is>
       </c>
-      <c r="C43" t="n">
+      <c r="C44" t="n">
         <v>1792661402000</v>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>Senamhi anuncia el inicio de la temporada de lluvias en Bolivia y prevé granizadas como la de La Paz - FmBolivia</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>meteorológica</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="inlineStr">
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="inlineStr">
         <is>
           <t>verde</t>
         </is>
       </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="inlineStr">
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="K43" t="n">
-        <v>1</v>
-      </c>
-      <c r="L43" t="inlineStr">
+      <c r="K44" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t>FmBolivia</t>
         </is>
       </c>
-      <c r="M43" t="n">
+      <c r="M44" t="n">
         <v>-16.169</v>
       </c>
-      <c r="N43" t="n">
+      <c r="N44" t="n">
         <v>-68.09</v>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>La Paz, La Paz</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>La Paz</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>Nuestra Señora de La Paz</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQNmVPRnVBMGQzdEI5SUp3Z3ZGVExwTUR6TWNadGQ1QldUS1o2QVFvUl9sVEZKMDVyQVVrS25rU1RSQlJKWXk1YzE0NUhidjhpcmFaSlhZUDZvcE9XcG1KTFNTYmowUU1CSFJNOVR2UHNmMk1iT3N0RVBteHkzZkgyRFROYk1pdkpxVHZya3N2X2FVLVQxbURFVVZlb1NzRjZzTE95TXFVUXFJNkVZakQ2bUhVQzB0SXk3TVhXUTJXa0dycTE1MWVQRFpDX3lDSWFqUGwzU2NtNA?oc=5</t>
         </is>
@@ -3682,7 +3760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S65"/>
+  <dimension ref="A1:S66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3866,7 +3944,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>noticia:1xi48lm</t>
+          <t>noticia:9ge0q3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3876,20 +3954,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-25 13:02</t>
+          <t>2026-10-25 15:19</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1792947732000</v>
+        <v>1792955960000</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>EL DÍA - Noticias de Bolivia para el mundo</t>
+          <t>eju.tv</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -3902,13 +3980,13 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Reportan el incendio de dos camiones cisterna en la carretera a Camiri - EL DÍA - Noticias de Bolivia para el mundo</t>
+          <t>Tarija: Evalúan daños tras intensa granizada en Chocloca - eju.tv</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNN0traUpaNVFIOU0zeFZod2tkQWhZZFQ1Q3dxc2xCVy1RNnJIX2xQbTlhT3RVckdNdHV4ZFVLQThvd2UzNDlCa3VmaWprTnU3R05rVkVkdEVCU1hFMlFsLTJ6REIySnl5VFJfdV9pQmVDTzlqUWFUSi1GQ0JvTVJVQ2dpeVBydnpMV0dYOThENTFRUDgxVFloSVg3bnN4dGo2aEVCbDFKaUgydWNISnJVUTNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxObHF1cjVaY2tOSndEMDFoRzZCcEgwZHg5VERFa25taUF0UXVyOHB4YkNTSkhaWVVoQXRrU2xyOWlxMkhQblphT0VWeHVyVzBDUHdyUF9WM1U1MnJSSExSbDRQeGgxV05PUzQ5eHdHTURfcVVWRktlZ0lHbUpMeHhUTk9EZzc5UQ?oc=5</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -3918,14 +3996,14 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-20.05</v>
+        <v>-21.53</v>
       </c>
       <c r="O3" t="n">
-        <v>-63.486</v>
+        <v>-64.73</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Camiri, Santa Cruz</t>
+          <t>Tarija, Tarija</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -3935,19 +4013,19 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Tarija</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Camiri</t>
+          <t>Tarija</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>noticia:4blj1l</t>
+          <t>noticia:1xi48lm</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3957,15 +4035,15 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-25 12:59</t>
+          <t>2026-10-25 13:02</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1792947573000</v>
+        <v>1792947732000</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
+          <t>EL DÍA - Noticias de Bolivia para el mundo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -3983,13 +4061,13 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Santa Cruz: Dos cisternas se incendian tras colisionar - La Patria Bolivia</t>
+          <t>Reportan el incendio de dos camiones cisterna en la carretera a Camiri - EL DÍA - Noticias de Bolivia para el mundo</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQbHdpcUF6dXpjaW1TT1ZmdGJtUUVLMTNMRTVqVkFUdkNsZlRvenVkckFUWmI4NDFmc2ZHd2RVcWRSSE5YRVpOTUlESGw2V3JONXpwS0RISGNZd01SejNuMkY4NzFYYXp4aWo2RE9VMkFYUkVwZ3JRRmM5MWlRSjlBWk16azdkQ3FjdEtkaWc5NERkTzk2SllVOQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNN0traUpaNVFIOU0zeFZod2tkQWhZZFQ1Q3dxc2xCVy1RNnJIX2xQbTlhT3RVckdNdHV4ZFVLQThvd2UzNDlCa3VmaWprTnU3R05rVkVkdEVCU1hFMlFsLTJ6REIySnl5VFJfdV9pQmVDTzlqUWFUSi1GQ0JvTVJVQ2dpeVBydnpMV0dYOThENTFRUDgxVFloSVg3bnN4dGo2aEVCbDFKaUgydWNISnJVUTNB?oc=5</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -3999,14 +4077,14 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-17.781</v>
+        <v>-20.05</v>
       </c>
       <c r="O4" t="n">
-        <v>-63.139</v>
+        <v>-63.486</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Santa Cruz, Santa Cruz</t>
+          <t>Camiri, Santa Cruz</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -4021,34 +4099,32 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Camiri</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>manual:1c1299f3</t>
+          <t>noticia:4blj1l</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>registro</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-25 12:44</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>1792946640000</t>
-        </is>
+          <t>2026-10-25 12:59</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1792947573000</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Registro abierto (sin verificar)</t>
+          <t>La Patria Bolivia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -4056,90 +4132,82 @@
           <t>antropogénica</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G5" t="n">
+        <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Vuelco de minibus</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Registro de prueba del sistema. Ignorar. | Lugar indicado: Caranavi, La Paz | Registro abierto, sin verificar.</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>-15.813</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>-67.463</t>
-        </is>
+          <t>Santa Cruz: Dos cisternas se incendian tras colisionar - La Patria Bolivia</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQbHdpcUF6dXpjaW1TT1ZmdGJtUUVLMTNMRTVqVkFUdkNsZlRvenVkckFUWmI4NDFmc2ZHd2RVcWRSSE5YRVpOTUlESGw2V3JONXpwS0RISGNZd01SejNuMkY4NzFYYXp4aWo2RE9VMkFYUkVwZ3JRRmM5MWlRSjlBWk16azdkQ3FjdEtkaWc5NERkTzk2SllVOQ?oc=5</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-17.781</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-63.139</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Caranavi, La Paz</t>
+          <t>Santa Cruz, Santa Cruz</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>nombre de municipio indicado por quien registra</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Caranavi</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>noticia:oww2zc</t>
+          <t>manual:1c1299f3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>registro</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-25 12:08</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>1792944531000</v>
+          <t>2026-10-25 12:44</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1792946640000</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>Registro abierto (sin verificar)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -4147,62 +4215,72 @@
           <t>antropogénica</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Cierran la carretera a Camiri: dos cisternas chocan y provocan un voraz incendio - Red Uno</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQLXlqSFdvWUVhQUNadnpkdE5lUTZQS0lobThzUTZWbDNJTE94alVhaDBaYU9Fd09SSGt3UlR3Y0dfZlNIcml1ZktnWjctNk1Na3V4S0tINFNkMXM0OHBoV2lCTTBiYXlPUTA3T2ZkeXE2RElYWjhfVHd3Nng1Z0E4alBmOFI5NDFwX09kazZlSWl2OVR2ZVR6MDhvSHFnSmJKbTFXSEFDNFFYcWVDNGtYWEQ0bDhJel9CaEpEZWZ4SWN0TE9Ya0E?oc=5</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>-20.05</v>
-      </c>
-      <c r="O6" t="n">
-        <v>-63.486</v>
+          <t>Vuelco de minibus</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Registro de prueba del sistema. Ignorar. | Lugar indicado: Caranavi, La Paz | Registro abierto, sin verificar.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>-15.813</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>-67.463</t>
+        </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Camiri, Santa Cruz</t>
+          <t>Caranavi, La Paz</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
+          <t>nombre de municipio indicado por quien registra</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>Camiri</t>
+          <t>Caranavi</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>noticia:1a4hhsd</t>
+          <t>noticia:oww2zc</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4212,15 +4290,15 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-25 11:56</t>
+          <t>2026-10-25 12:08</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1792943794000</v>
+        <v>1792944531000</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Opinión Bolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4238,13 +4316,13 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Reportan el incendio de dos camiones cisterna en la carretera a Camiri - Opinión Bolivia</t>
+          <t>Cierran la carretera a Camiri: dos cisternas chocan y provocan un voraz incendio - Red Uno</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNUTdxSzBJVTZnajZQUXhyTVhwMlpvU0tyZGVBYnFwV2kyZWthenNRT1FDRVJFZnk4ZndGTFQ0cnFXZmZ1WHZaMFhUbWo0SWkzcjcxbjJwU3pKUXR4WEVZLVlRNFpxOUVMY2NNNUZsbmJSMk9xZG1sTklEdEtGSXJyUUp5b0R2dVpYcHJLdTRNRlRjcWpNNXg4c0Z4UWwteFc2dDRqVmpnQnFfQXgwN0twTzl4ZWhYdUtYWGfSAboBQVVfeXFMTVE3cUswSVU2Z2o2UFF4ck1YcDJab1NLcmRlQWJxcFdpMmVrYXpzUU9RQ0VSRWZ5OGZ3RkxUNHJxV2ZmdVh2WjBYVG1qNElpM3I3MW4ycFN6SlF0eFhFWS1ZUTRacTlFTGNjTTVGbG5iUjJPcWRtbE5JRHRLRklyclFKeW9EdnVaWHByS3U0TUZUY3FqTTV4OHNGeFFsLXhXNnQ0alZqZ0JxX0F4MDdLcE85eGVoWHVLWFhn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQLXlqSFdvWUVhQUNadnpkdE5lUTZQS0lobThzUTZWbDNJTE94alVhaDBaYU9Fd09SSGt3UlR3Y0dfZlNIcml1ZktnWjctNk1Na3V4S0tINFNkMXM0OHBoV2lCTTBiYXlPUTA3T2ZkeXE2RElYWjhfVHd3Nng1Z0E4alBmOFI5NDFwX09kazZlSWl2OVR2ZVR6MDhvSHFnSmJKbTFXSEFDNFFYcWVDNGtYWEQ0bDhJel9CaEpEZWZ4SWN0TE9Ya0E?oc=5</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -4283,7 +4361,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>noticia:1at00ey</t>
+          <t>noticia:1a4hhsd</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4293,15 +4371,15 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-25 11:19</t>
+          <t>2026-10-25 11:56</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1792941547000</v>
+        <v>1792943794000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>Opinión Bolivia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -4319,13 +4397,13 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Dos cisternas chocan y provocan voraz incendio en la ruta a Camiri - Red Uno</t>
+          <t>Reportan el incendio de dos camiones cisterna en la carretera a Camiri - Opinión Bolivia</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPTTF0OUdVS1c1a0lZWmk3bGxHdDJIalpWZTRyQTY3eWE2a2dWOHlsaldKZXpSLWN5c3BkUWdBRkJuSzhHdWl2ZjgwTFFFYnd0aTAxZ3dJU0hCekNZNm9aTTJSZUNfQjVIM3FrUUJ4NXAwa3paZ3BEek9xTVZNQWdnN01xRHloV1ZXZHV6N0JpUWo3RE9DMlFGdkNnWkloTjVVY3RBR1RSRUJJWFVtby1fMWFMNTdLZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNUTdxSzBJVTZnajZQUXhyTVhwMlpvU0tyZGVBYnFwV2kyZWthenNRT1FDRVJFZnk4ZndGTFQ0cnFXZmZ1WHZaMFhUbWo0SWkzcjcxbjJwU3pKUXR4WEVZLVlRNFpxOUVMY2NNNUZsbmJSMk9xZG1sTklEdEtGSXJyUUp5b0R2dVpYcHJLdTRNRlRjcWpNNXg4c0Z4UWwteFc2dDRqVmpnQnFfQXgwN0twTzl4ZWhYdUtYWGfSAboBQVVfeXFMTVE3cUswSVU2Z2o2UFF4ck1YcDJab1NLcmRlQWJxcFdpMmVrYXpzUU9RQ0VSRWZ5OGZ3RkxUNHJxV2ZmdVh2WjBYVG1qNElpM3I3MW4ycFN6SlF0eFhFWS1ZUTRacTlFTGNjTTVGbG5iUjJPcWRtbE5JRHRLRklyclFKeW9EdnVaWHByS3U0TUZUY3FqTTV4OHNGeFFsLXhXNnQ0alZqZ0JxX0F4MDdLcE85eGVoWHVLWFhn?oc=5</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -4364,7 +4442,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>noticia:1uf38hl</t>
+          <t>noticia:1at00ey</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4374,11 +4452,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-25 10:59</t>
+          <t>2026-10-25 11:19</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1792940350000</v>
+        <v>1792941547000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -4400,13 +4478,13 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>¡Cisterna con combustible en llamas! Reportan impresionante incendio en la carretera a Camiri - Red Uno</t>
+          <t>Dos cisternas chocan y provocan voraz incendio en la ruta a Camiri - Red Uno</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxORUhqeWpKY1FHRWoxaHN0UXFzS3dpeHh6N0NwLUJOZTlZcDVoNHN0VnI0by1qMWtZZEkxVmtUNjdNTFhjaEFQU2IyMlNwZW95WFBzbFJPVVB6TjJtdjNENk1LWVlsMUxUUzBNVzkxRk1HZ3lQU0s2M1lRVlRuaXlkMmJrd3AyTGpIdXItNkhlU3dhTzBRME56Rm1DSlZCYjNxSnNTbTFqNWRoUkdraHhlREhuYldqeFk2N3poWEx2M08?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPTTF0OUdVS1c1a0lZWmk3bGxHdDJIalpWZTRyQTY3eWE2a2dWOHlsaldKZXpSLWN5c3BkUWdBRkJuSzhHdWl2ZjgwTFFFYnd0aTAxZ3dJU0hCekNZNm9aTTJSZUNfQjVIM3FrUUJ4NXAwa3paZ3BEek9xTVZNQWdnN01xRHloV1ZXZHV6N0JpUWo3RE9DMlFGdkNnWkloTjVVY3RBR1RSRUJJWFVtby1fMWFMNTdLZw?oc=5</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -4445,7 +4523,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>noticia:1sg8pi0</t>
+          <t>noticia:1uf38hl</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4455,11 +4533,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-25 09:59</t>
+          <t>2026-10-25 10:59</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1792936752000</v>
+        <v>1792940350000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -4481,13 +4559,13 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Bus de agrupación musical sufre accidente rumbo al trópico de Cochabamba | VIDEO - Red Uno</t>
+          <t>¡Cisterna con combustible en llamas! Reportan impresionante incendio en la carretera a Camiri - Red Uno</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOVDVzVTJNM2JuQ25sMThEaVZNOUNRd3FGT3RhVnFrZXZ2NDQ1YlluTVdhbVNUQnA1MGNESHRSWVUzbC1kRVh3OTR0emtlTG91cmRWeFJ5dk5zb3p2WFRyMEJUV3FNRnY1WHhRUU9WLTlJcmNyNXJZZFdoM0JoZjNpa3hjUXhMM0xrUDJab2VadkM5RWZYQ3lWZTVDdzg1akxJT2lxcDVNNzI0NG1hejdfdkUyTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxORUhqeWpKY1FHRWoxaHN0UXFzS3dpeHh6N0NwLUJOZTlZcDVoNHN0VnI0by1qMWtZZEkxVmtUNjdNTFhjaEFQU2IyMlNwZW95WFBzbFJPVVB6TjJtdjNENk1LWVlsMUxUUzBNVzkxRk1HZ3lQU0s2M1lRVlRuaXlkMmJrd3AyTGpIdXItNkhlU3dhTzBRME56Rm1DSlZCYjNxSnNTbTFqNWRoUkdraHhlREhuYldqeFk2N3poWEx2M08?oc=5</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -4497,14 +4575,14 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-17.39</v>
+        <v>-20.05</v>
       </c>
       <c r="O10" t="n">
-        <v>-66.16</v>
+        <v>-63.486</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Cochabamba, Cochabamba</t>
+          <t>Camiri, Santa Cruz</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -4514,19 +4592,19 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Camiri</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>noticia:167wlhz</t>
+          <t>noticia:1sg8pi0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4536,11 +4614,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-25 07:53</t>
+          <t>2026-10-25 09:59</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1792929231000</v>
+        <v>1792936752000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -4549,7 +4627,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -4562,13 +4640,13 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>¡A sacar el paraguas! Santa cruz amanece con lluvia, frío y complicaciones en el tránsito vehicular - Red Uno</t>
+          <t>Bus de agrupación musical sufre accidente rumbo al trópico de Cochabamba | VIDEO - Red Uno</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOY1ZpYktLR3pUQXotUndVR3puUzVHbW1YTzNyUmJvUHB4Q2JmelRvOEdaRldOUm1xLVJnbGR5VWcxTjNEM3ZUYktCUWtVM0hKSjFuRGdpX0JxN0M5MVZBSG1aVURyVWktdmxwbUtRT19ydU5LdzNTZ2Zpb2ozdHlMUUdTVlAyVk4xODBnV0hyTXdVVndyNzV3VC1KMzFnV3lpcFFXSk9MdDZOTWlWakNwT1FnNDh6QVdjazVYZDVVMkdaLU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOVDVzVTJNM2JuQ25sMThEaVZNOUNRd3FGT3RhVnFrZXZ2NDQ1YlluTVdhbVNUQnA1MGNESHRSWVUzbC1kRVh3OTR0emtlTG91cmRWeFJ5dk5zb3p2WFRyMEJUV3FNRnY1WHhRUU9WLTlJcmNyNXJZZFdoM0JoZjNpa3hjUXhMM0xrUDJab2VadkM5RWZYQ3lWZTVDdzg1akxJT2lxcDVNNzI0NG1hejdfdkUyTQ?oc=5</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -4578,14 +4656,14 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-17.781</v>
+        <v>-17.39</v>
       </c>
       <c r="O11" t="n">
-        <v>-63.139</v>
+        <v>-66.16</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Santa Cruz, Santa Cruz</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -4595,19 +4673,19 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Cochabamba</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>noticia:bzr7eh</t>
+          <t>noticia:167wlhz</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4617,39 +4695,39 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-25 07:09</t>
+          <t>2026-10-25 07:53</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1792926572000</v>
+        <v>1792929231000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>hidrológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Alerta naranja por riesgo de desbordes de ríos - El Diario - Bolivia</t>
+          <t>¡A sacar el paraguas! Santa cruz amanece con lluvia, frío y complicaciones en el tránsito vehicular - Red Uno</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNNGZKSDVaZkowWUFGSEUyTWR3d3dsc04waFBLLWUtcVpiTDYzbmNtYTN1RkFLbjAwN3dxT0xZc3pqc3REUXduZVltQ2Fud1BZLTh1bTNiTEJueVUwV0dERS1iUXZqMHd0UnFrQ3E2SFAzbm5lQ1I4U29MaHJFbWFvdVRTeFY4Wl9rSmc3RkpaQ2xwX0oz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOY1ZpYktLR3pUQXotUndVR3puUzVHbW1YTzNyUmJvUHB4Q2JmelRvOEdaRldOUm1xLVJnbGR5VWcxTjNEM3ZUYktCUWtVM0hKSjFuRGdpX0JxN0M5MVZBSG1aVURyVWktdmxwbUtRT19ydU5LdzNTZ2Zpb2ozdHlMUUdTVlAyVk4xODBnV0hyTXdVVndyNzV3VC1KMzFnV3lpcFFXSk9MdDZOTWlWakNwT1FnNDh6QVdjazVYZDVVMkdaLU0?oc=5</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -4658,21 +4736,37 @@
       <c r="M12" t="n">
         <v>0</v>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>-17.781</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-63.139</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Santa Cruz, Santa Cruz</t>
+        </is>
+      </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Santa Cruz de la Sierra</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>noticia:1fo4ig4</t>
+          <t>noticia:bzr7eh</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4682,43 +4776,43 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-25 01:08</t>
+          <t>2026-10-25 07:09</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1792904880000</v>
+        <v>1792926572000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>diarioelpueblo.com.pe</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>hidrológica</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>roja</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
+          <t>Alerta naranja por riesgo de desbordes de ríos - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQcmFrT3dwcEs0X3U2NWxnOGJwNnI2WHdWTGZYbzEyNnJzUWhkbU9TRWhfSlB5UkMwX2gyMmxYUmVNWmxNOVR6V0twRHpFMTVIYjBKbHQ2TXN2d2w5dkFpcWJCcUJMZldaX01sNWtQV2ZJOGpRVzR3NDVIU0pJc1BNVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNNGZKSDVaZkowWUFGSEUyTWR3d3dsc04waFBLLWUtcVpiTDYzbmNtYTN1RkFLbjAwN3dxT0xZc3pqc3REUXduZVltQ2Fud1BZLTh1bTNiTEJueVUwV0dERS1iUXZqMHd0UnFrQ3E2SFAzbm5lQ1I4U29MaHJFbWFvdVRTeFY4Wl9rSmc3RkpaQ2xwX0oz?oc=5</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -4737,7 +4831,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>noticia:r1uot6</t>
+          <t>noticia:1fo4ig4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4747,15 +4841,15 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-24 20:00</t>
+          <t>2026-10-25 01:08</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1792886439000</v>
+        <v>1792904880000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
+          <t>diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -4764,61 +4858,45 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>roja</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>vuelco deja heridos en ruta Oruro – Huanuni - La Patria Bolivia</t>
+          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNNDQtMG1KT1lLWW5nem9Jbm5JWDZKNlRWZmFmRlBxWDlDeXlSWnJ5d2NsTlpxa0JIS25oVWVZOC1majZVbWhOVDIxR0dLOFlzY2VpVzVoVk1mQnF3dXVwLUFZVHc1UjlXZzF5T05CY3U0ZldLVkw1VzBTek5zanpjQW1xalltWHNiaXI3dTNR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQcmFrT3dwcEs0X3U2NWxnOGJwNnI2WHdWTGZYbzEyNnJzUWhkbU9TRWhfSlB5UkMwX2gyMmxYUmVNWmxNOVR6V0twRHpFMTVIYjBKbHQ2TXN2d2w5dkFpcWJCcUJMZldaX01sNWtQV2ZJOGpRVzR3NDVIU0pJc1BNVg?oc=5</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>-17.97</v>
-      </c>
-      <c r="O14" t="n">
-        <v>-67.11</v>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Oruro, Oruro</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>Oruro</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>Oruro</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>noticia:1ytw450</t>
+          <t>noticia:r1uot6</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4828,15 +4906,15 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-24 18:58</t>
+          <t>2026-10-24 20:00</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1792882686000</v>
+        <v>1792886439000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>diarioelpueblo.com.pe</t>
+          <t>La Patria Bolivia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -4845,45 +4923,61 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>roja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
+          <t>vuelco deja heridos en ruta Oruro – Huanuni - La Patria Bolivia</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNZ1U3bEVuaVdjVE1zSU9lOHJZTVRZLVZaemhldGNnT1JBWDJvbzdvM3paVVNhLUlyWHF2akNuSXJOLXdyTGRuejRlV1FuMjVkTjA3NmdRdmgtRWlUeTFBV1dEMzBvejBxaXZJdUZZWkRVTF9VLU5BcjFGZGFEQ09WWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNNDQtMG1KT1lLWW5nem9Jbm5JWDZKNlRWZmFmRlBxWDlDeXlSWnJ5d2NsTlpxa0JIS25oVWVZOC1majZVbWhOVDIxR0dLOFlzY2VpVzVoVk1mQnF3dXVwLUFZVHc1UjlXZzF5T05CY3U0ZldLVkw1VzBTek5zanpjQW1xalltWHNiaXI3dTNR?oc=5</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-17.97</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-67.11</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Oruro, Oruro</t>
+        </is>
+      </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>noticia:1wcb22g</t>
+          <t>noticia:1ytw450</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4893,43 +4987,43 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-24 17:47</t>
+          <t>2026-10-24 18:58</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1792878475000</v>
+        <v>1792882686000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>El Mundo Bolivia</t>
+          <t>diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>hidrológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>roja</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Alerta naranja por ingreso de frente frío y desbordes de ríos en 6 departamentos - El Mundo Bolivia</t>
+          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPZW00RkxJSklTelNrS2hqczJDWHlwcENFX2lnSEUyTEFPaDFRQ2JvMUcyd3NfYjg0UE9ORGxHRzB4ZDh3U0hQQ1JSQlhsaUY4N3ByMUUxei1SaUZnNlp6T3hsLVdiMGhKaXhsV1FNSUNQMHlvQ19qdk56SEF0d2RXVFctS0VPT25kNGZCRDdvZ2dxU0VoUUJKU0ZBd0ZycFNEZFh0T3ZjOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNZ1U3bEVuaVdjVE1zSU9lOHJZTVRZLVZaemhldGNnT1JBWDJvbzdvM3paVVNhLUlyWHF2akNuSXJOLXdyTGRuejRlV1FuMjVkTjA3NmdRdmgtRWlUeTFBV1dEMzBvejBxaXZJdUZZWkRVTF9VLU5BcjFGZGFEQ09WWQ?oc=5</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -4948,7 +5042,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>noticia:1c1ju1f</t>
+          <t>noticia:1wcb22g</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4958,46 +5052,46 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-24 17:02</t>
+          <t>2026-10-24 17:47</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1792875752000</v>
+        <v>1792878475000</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>La Razón Digital Bolivia</t>
+          <t>El Mundo Bolivia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>hidrológica</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a los Yungas deja siete heridos - La Razón Digital Bolivia</t>
+          <t>Alerta naranja por ingreso de frente frío y desbordes de ríos en 6 departamentos - El Mundo Bolivia</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPTGQwaVBfdG1JdVRMUTN4LVVvN0ppc3dreDJVVllDR3RmX0xpMzB4b0pvVTNSV1B6T0ZEWTdEZkNsRUdSNzhLaC1CWHN5WktNWk1nRWpTdVZiYjI3TlJlX2xlVTI5MjlRU2hiY1gteml4YWVFbDNPSVRBZmtITlQzbmhaUXVmcThRa2xsQTJIOXZuNzlSdm12MEdyOEZHdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPZW00RkxJSklTelNrS2hqczJDWHlwcENFX2lnSEUyTEFPaDFRQ2JvMUcyd3NfYjg0UE9ORGxHRzB4ZDh3U0hQQ1JSQlhsaUY4N3ByMUUxei1SaUZnNlp6T3hsLVdiMGhKaXhsV1FNSUNQMHlvQ19qdk56SEF0d2RXVFctS0VPT25kNGZCRDdvZ2dxU0VoUUJKU0ZBd0ZycFNEZFh0T3ZjOA?oc=5</t>
         </is>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
@@ -5013,7 +5107,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>noticia:14iwzop</t>
+          <t>noticia:1c1ju1f</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5023,15 +5117,15 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-24 13:40</t>
+          <t>2026-10-24 17:02</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1792863623000</v>
+        <v>1792875752000</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>EL DÍA - Noticias de Bolivia para el mundo</t>
+          <t>La Razón Digital Bolivia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -5049,13 +5143,13 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a Mayaya deja siete heridos de la agrupación Los Chicos Fieles - EL DÍA - Noticias de Bolivia para el mundo</t>
+          <t>Accidente en la carretera a los Yungas deja siete heridos - La Razón Digital Bolivia</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPeGd3VWpCWXJ0YTJIeDJLcktzWG1jdUh0TjFXb01wSTkxbHNXZU94VWNDMkxnTjlJZVdpbkprMEY2NE80RXYyUWxUQXVnbl9lUXR2b28zTEh6cTJLVEQ4TUNja2kzRlhadVBFZFVwV1U2TlhseXZMZ20zZTZiUFpWRjdCOWNBMHU5XzdMV3JqQjV4TEE3bHRMOXR6Nm55eHZUNnFHSDdVRk8zVkY4RkVsUUtUN0JYdkREWGZncmJ3ZWc2T1BuUm1ZLTlfcHVabFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPTGQwaVBfdG1JdVRMUTN4LVVvN0ppc3dreDJVVllDR3RmX0xpMzB4b0pvVTNSV1B6T0ZEWTdEZkNsRUdSNzhLaC1CWHN5WktNWk1nRWpTdVZiYjI3TlJlX2xlVTI5MjlRU2hiY1gteml4YWVFbDNPSVRBZmtITlQzbmhaUXVmcThRa2xsQTJIOXZuNzlSdm12MEdyOEZHdw?oc=5</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -5078,7 +5172,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>noticia:1ukcn97</t>
+          <t>noticia:14iwzop</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5088,15 +5182,15 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-24 13:26</t>
+          <t>2026-10-24 13:40</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1792862794000</v>
+        <v>1792863623000</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>El Deber</t>
+          <t>EL DÍA - Noticias de Bolivia para el mundo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -5114,20 +5208,20 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Esta es la lista preliminar de los heridos en el accidente del grupo 'Los chicos fieles', el conductor está grave - El Deber</t>
+          <t>Accidente en la carretera a Mayaya deja siete heridos de la agrupación Los Chicos Fieles - EL DÍA - Noticias de Bolivia para el mundo</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOczZKbFd1QzRpak92LXpPWXZXQXJObnBQTG9qRFBlUUV5dThMWXhzckFFUHAyb2thU1JwRmJDSEZfaEdTUXh1bjZvQWpYMGhfUno3cWZ4MGpldEpoQXhzSlVzTm5LLW9OcjB2MWRsdHQ2UlI2SjEtZ085ZTR5Z3pEVmtBTF9lc29Kd0RhaTRUWkM4eGZJNWhBSXZqWmxuNW10dlQwYW9mdzItcWZWTkU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPeGd3VWpCWXJ0YTJIeDJLcktzWG1jdUh0TjFXb01wSTkxbHNXZU94VWNDMkxnTjlJZVdpbkprMEY2NE80RXYyUWxUQXVnbl9lUXR2b28zTEh6cTJLVEQ4TUNja2kzRlhadVBFZFVwV1U2TlhseXZMZ20zZTZiUFpWRjdCOWNBMHU5XzdMV3JqQjV4TEE3bHRMOXR6Nm55eHZUNnFHSDdVRk8zVkY4RkVsUUtUN0JYdkREWGZncmJ3ZWc2T1BuUm1ZLTlfcHVabFE?oc=5</t>
         </is>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
@@ -5143,7 +5237,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>noticia:2avehj</t>
+          <t>noticia:1ukcn97</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5153,20 +5247,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-24 12:53</t>
+          <t>2026-10-24 13:26</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1792860813000</v>
+        <v>1792862794000</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>El Deber</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>climatológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -5179,52 +5273,36 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Sequía en Cochabamba: más de un centenar de cabezas de ganado murieron en el cono sur - Red Uno</t>
+          <t>Esta es la lista preliminar de los heridos en el accidente del grupo 'Los chicos fieles', el conductor está grave - El Deber</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOOFQxc2Vzc0QwS19ydC13RkRPZnZQU3JkSTl5U3kzdUdMSldTcm5HVEhWRzZyN19CLUlwcUs4MW03Ui1obVBtdzQ3QWFQc1RKdzh3MXJ5QkpRS2pRNm50V1lVb09ScGJnaVVlemVfZlRsWjdObnRmR1FGMnlMMHAyc2pMandndy10T2twcWx6OFh4UHdvbVlFbllwME9WQ2pQVjNTQzBxeTg5YnF3bDREeHVDYXpObFFIaTZZQWtYUE12cGQ1ZGRhT0syNjVhZWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOczZKbFd1QzRpak92LXpPWXZXQXJObnBQTG9qRFBlUUV5dThMWXhzckFFUHAyb2thU1JwRmJDSEZfaEdTUXh1bjZvQWpYMGhfUno3cWZ4MGpldEpoQXhzSlVzTm5LLW9OcjB2MWRsdHQ2UlI2SjEtZ085ZTR5Z3pEVmtBTF9lc29Kd0RhaTRUWkM4eGZJNWhBSXZqWmxuNW10dlQwYW9mdzItcWZWTkU0?oc=5</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>-17.39</v>
-      </c>
-      <c r="O20" t="n">
-        <v>-66.16</v>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Cochabamba, Cochabamba</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>noticia:1ksmg5u</t>
+          <t>noticia:2avehj</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5234,20 +5312,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-24 11:43</t>
+          <t>2026-10-24 12:53</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1792856591000</v>
+        <v>1792860813000</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>climatológica</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -5260,36 +5338,52 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Embarrancamiento deja heridos a integrantes de Los Chicos Fieles - La Patria Bolivia</t>
+          <t>Sequía en Cochabamba: más de un centenar de cabezas de ganado murieron en el cono sur - Red Uno</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNeEFrOEtOMHZxMW42REFPU0x1MG5oQjlBMkJucWRLZ292alBXekJKeURBN3NLTVVadWI0OWF4UGtSVXBzTE01eWFSU1kyMUhNZ04zMWNMaUxnMDBBZ0EwTktXbjlaVTBUUmNqa3AwY19KNTU2LWh5LW9IVElVdTdnaHFPanJPd2FqMUxzaUhXZmVpYU1saGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOOFQxc2Vzc0QwS19ydC13RkRPZnZQU3JkSTl5U3kzdUdMSldTcm5HVEhWRzZyN19CLUlwcUs4MW03Ui1obVBtdzQ3QWFQc1RKdzh3MXJ5QkpRS2pRNm50V1lVb09ScGJnaVVlemVfZlRsWjdObnRmR1FGMnlMMHAyc2pMandndy10T2twcWx6OFh4UHdvbVlFbllwME9WQ2pQVjNTQzBxeTg5YnF3bDREeHVDYXpObFFIaTZZQWtYUE12cGQ1ZGRhT0syNjVhZWs?oc=5</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-17.39</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-66.16</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Cochabamba, Cochabamba</t>
+        </is>
+      </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>noticia:mlyqgd</t>
+          <t>noticia:1ksmg5u</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5299,15 +5393,15 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-24 11:30</t>
+          <t>2026-10-24 11:43</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1792855818000</v>
+        <v>1792856591000</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Opinión Bolivia</t>
+          <t>La Patria Bolivia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -5325,20 +5419,20 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a Mayaya deja siete heridos de la agrupación Los Chicos Fieles - Opinión Bolivia</t>
+          <t>Embarrancamiento deja heridos a integrantes de Los Chicos Fieles - La Patria Bolivia</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYjNxaHg3YllRRTJYdFd1clAtUlROSGlFNVg5eUVZUGJoOEZ4MWM5QU5WQm1YTDc4NXc3SjhWMUw0TkZfSHlMLUQ1bmpTME1Kb1JaM0ExamFHYTd3VlU4MXRWdTZ1bzh1SGYtbGE1a3dBaG93bjg1OGc0S0JfRE43c3dVMVltN0dQQzNhQUNhM0FjVUNRUDRSamlJYlk2dEJpUTBuY2hBcTFucTVRN0ZtYnc5bzdmTV9LQm1uVUxaZS1tUE9IejhBVDRCdU_SAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNeEFrOEtOMHZxMW42REFPU0x1MG5oQjlBMkJucWRLZ292alBXekJKeURBN3NLTVVadWI0OWF4UGtSVXBzTE01eWFSU1kyMUhNZ04zMWNMaUxnMDBBZ0EwTktXbjlaVTBUUmNqa3AwY19KNTU2LWh5LW9IVElVdTdnaHFPanJPd2FqMUxzaUhXZmVpYU1saGc?oc=5</t>
         </is>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
@@ -5354,7 +5448,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>noticia:irf4jl</t>
+          <t>noticia:mlyqgd</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5396,7 +5490,7 @@
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNMXlMNXFWSWhhWWNDRFFKMncwS2JGWm0tWlJCd2x2RjZhdFhEQ0lBcVlFSS1WRVYxMEVJTWRHcTY3M0stdWhGdnVPRU13X2MwSVRWX25xVUQxa0R6Z1pqQ2dfY0VjUmw2aXFoWFNVNk15N2dBOENZLWlGSWJfMW0zejVoZ3ZwVHVQV1MzbzlnUlpRcWIxMHZxdkItZTc0QmMyRnBmSVRtVnZ5Y3gtdVpYNXFwcGdadGVCU3dRZ3EwOTdiWHU4OXJRdEFoNi1HcnA1U0HSAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYjNxaHg3YllRRTJYdFd1clAtUlROSGlFNVg5eUVZUGJoOEZ4MWM5QU5WQm1YTDc4NXc3SjhWMUw0TkZfSHlMLUQ1bmpTME1Kb1JaM0ExamFHYTd3VlU4MXRWdTZ1bzh1SGYtbGE1a3dBaG93bjg1OGc0S0JfRE43c3dVMVltN0dQQzNhQUNhM0FjVUNRUDRSamlJYlk2dEJpUTBuY2hBcTFucTVRN0ZtYnc5bzdmTV9LQm1uVUxaZS1tUE9IejhBVDRCdU_SAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -5419,7 +5513,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>noticia:1g006zh</t>
+          <t>noticia:irf4jl</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5429,15 +5523,15 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-24 11:25</t>
+          <t>2026-10-24 11:30</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1792855522000</v>
+        <v>1792855818000</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>El Potosí</t>
+          <t>Opinión Bolivia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -5455,13 +5549,13 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a Mayaya deja siete heridos del grupo Los Chicos Fieles - El Potosí</t>
+          <t>Accidente en la carretera a Mayaya deja siete heridos de la agrupación Los Chicos Fieles - Opinión Bolivia</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTC10eC1qSm1WRlY2YzA3VEJqOG1LUkx6bE9PdFYwTFBZMGFjU0RMYXliRkhXcTJHRlVzb0Y4QUU0WWJDQ1plS2NZamZ1YmFadE5qY3g4UE5aYVAwamtCUUNZaDB2YWJTdWRKS3R4a0hHUjVobUl0Y1dYZ2JPczAwak5kN1hjUEwwM1NtUDVWbnAzWTdnRng3RjFValFVVlZPdVZnWFlUODhPOE5aMTROQzVKVjVRS2VoaTlaQnBiUGRTNFk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNMXlMNXFWSWhhWWNDRFFKMncwS2JGWm0tWlJCd2x2RjZhdFhEQ0lBcVlFSS1WRVYxMEVJTWRHcTY3M0stdWhGdnVPRU13X2MwSVRWX25xVUQxa0R6Z1pqQ2dfY0VjUmw2aXFoWFNVNk15N2dBOENZLWlGSWJfMW0zejVoZ3ZwVHVQV1MzbzlnUlpRcWIxMHZxdkItZTc0QmMyRnBmSVRtVnZ5Y3gtdVpYNXFwcGdadGVCU3dRZ3EwOTdiWHU4OXJRdEFoNi1HcnA1U0HSAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -5470,60 +5564,44 @@
       <c r="M24" t="n">
         <v>7</v>
       </c>
-      <c r="N24" t="n">
-        <v>-19.58</v>
-      </c>
-      <c r="O24" t="n">
-        <v>-65.75</v>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Potosí, Potosí</t>
-        </is>
-      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>clima:Potosí:2026-10-24:viento:1</t>
+          <t>noticia:1g006zh</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-24 10:55</t>
+          <t>2026-10-24 11:25</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1792853727284</v>
+        <v>1792855522000</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>El Potosí</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5536,24 +5614,20 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Potosí 2026-10-24: 60.5 km/h de ráfagas pronosticadas</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
-        </is>
-      </c>
+          <t>Accidente en la carretera a Mayaya deja siete heridos del grupo Los Chicos Fieles - El Potosí</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTC10eC1qSm1WRlY2YzA3VEJqOG1LUkx6bE9PdFYwTFBZMGFjU0RMYXliRkhXcTJHRlVzb0Y4QUU0WWJDQ1plS2NZamZ1YmFadE5qY3g4UE5aYVAwamtCUUNZaDB2YWJTdWRKS3R4a0hHUjVobUl0Y1dYZ2JPczAwak5kN1hjUEwwM1NtUDVWbnAzWTdnRng3RjFValFVVlZPdVZnWFlUODhPOE5aMTROQzVKVjVRS2VoaTlaQnBiUGRTNFk?oc=5</t>
         </is>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N25" t="n">
         <v>-19.58</v>
@@ -5563,12 +5637,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Potosí, Potosí</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>capital (pronóstico puntual)</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -5585,25 +5659,25 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>noticia:1ax0bpy</t>
+          <t>clima:Potosí:2026-10-24:viento:1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-24 10:32</t>
+          <t>2026-10-24 10:55</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1792852364000</v>
+        <v>1792853727284</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Que Pasa Salta</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5612,22 +5686,26 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Creció el Bermejo tras la tormenta: así está el puerto de chalanas en este momento - Que Pasa Salta</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+          <t>Potosí 2026-10-24: 60.5 km/h de ráfagas pronosticadas</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVld9IBfkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVldw?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -5637,59 +5715,59 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>-22.721</v>
+        <v>-19.58</v>
       </c>
       <c r="O26" t="n">
-        <v>-64.32599999999999</v>
+        <v>-65.75</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bermejo, Tarija</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
+          <t>capital (pronóstico puntual)</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Tarija</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Bermejo</t>
+          <t>Potosí</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>gdacs:WF1033142:0</t>
+          <t>noticia:1ax0bpy</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>gdacs</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-10-24 07:06</t>
+          <t>2026-10-24 10:32</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1792839995000</v>
+        <v>1792852364000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>GDACS</t>
+          <t>Que Pasa Salta</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5702,17 +5780,13 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Green forest fire notification in Bolivia</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>On 21/10/2026, a forest fire started in Bolivia, until 24/10/2026.</t>
-        </is>
-      </c>
+          <t>Creció el Bermejo tras la tormenta: así está el puerto de chalanas en este momento - Que Pasa Salta</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>http://www.gdacs.org/report.aspx?eventtype=WF&amp;eventid=1033142</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVld9IBfkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVldw?oc=5</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -5722,59 +5796,59 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>-13.06332</v>
+        <v>-22.721</v>
       </c>
       <c r="O27" t="n">
-        <v>-67.66426</v>
+        <v>-64.32599999999999</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Bermejo, Tarija</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>coordenada de la fuente</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Tarija</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>Ixiamas</t>
+          <t>Bermejo</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>noticia:1shhqva</t>
+          <t>gdacs:WF1033142:0</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>gdacs</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-10-24 06:33</t>
+          <t>2026-10-24 07:06</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1792838034000</v>
+        <v>1792839995000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>GDACS</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5787,13 +5861,17 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+          <t>Green forest fire notification in Bolivia</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>On 21/10/2026, a forest fire started in Bolivia, until 24/10/2026.</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQYzB6N082XzFRRnVtcDVmUkYyWjcxUzV2Z3Frd1I0WDNXSnZtY0QzOU1PUkNLMktVT1Vra2FSeXhxZDRuOFZYZjFwejl6ejJTbWY2MGJuSGN3ZHdrdG5JUkgzSXBkbDYtaHlackY3OVFuNWdLcFNpdWNHRU9vNGdoVWx2ODFVdzJXYUxnM0tUcjJvZmc?oc=5</t>
+          <t>http://www.gdacs.org/report.aspx?eventtype=WF&amp;eventid=1033142</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -5803,82 +5881,78 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>-17.97</v>
+        <v>-13.06332</v>
       </c>
       <c r="O28" t="n">
-        <v>-67.11</v>
+        <v>-67.66426</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
+          <t>coordenada de la fuente</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Ixiamas</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>clima:Potosí:2026-10-25:viento:1</t>
+          <t>noticia:1shhqva</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-10-24 02:55</t>
+          <t>2026-10-24 06:33</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1792824927736</v>
+        <v>1792838034000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Potosí 2026-10-25: 60.5 km/h de ráfagas pronosticadas</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
-        </is>
-      </c>
+          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQYzB6N082XzFRRnVtcDVmUkYyWjcxUzV2Z3Frd1I0WDNXSnZtY0QzOU1PUkNLMktVT1Vra2FSeXhxZDRuOFZYZjFwejl6ejJTbWY2MGJuSGN3ZHdrdG5JUkgzSXBkbDYtaHlackY3OVFuNWdLcFNpdWNHRU9vNGdoVWx2ODFVdzJXYUxnM0tUcjJvZmc?oc=5</t>
         </is>
       </c>
       <c r="L29" t="n">
@@ -5888,59 +5962,59 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>-19.58</v>
+        <v>-17.97</v>
       </c>
       <c r="O29" t="n">
-        <v>-65.75</v>
+        <v>-67.11</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Oruro, Oruro</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>capital (pronóstico puntual)</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Oruro</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Oruro</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>noticia:mz6q0s</t>
+          <t>clima:Potosí:2026-10-25:viento:1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-10-23 23:09</t>
+          <t>2026-10-24 02:55</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1792811349000</v>
+        <v>1792824927736</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5953,36 +6027,56 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Revelan lista preliminar de heridos tras accidente de Los Chicos Fieles - Red Uno</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
+          <t>Potosí 2026-10-25: 60.5 km/h de ráfagas pronosticadas</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPczBQcnE2SzFGMXc3b1lsTkNxVWRmS3Vnb01xOTV2WmVva3J2RVlteWpHZ3VJS2dNWGV5NW5FX3ZncnVKTEVDTGpBRndTU1FxeWxtaS1fb1FscGxXMWNXUE9zbHdob1AxVFl1eHB5OU1yUnNoOXJ6U21oVG9PVDA1ak1xQl9hUlB4V0RaQXJqZENGUm8zMUJEY3J0WW5ENE5ObWJLNmpWN0RkSmFJbnZUZGR5UFRPd3QyUFY4WQ?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
-      </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-19.58</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-65.75</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Potosí</t>
+        </is>
+      </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
+          <t>capital (pronóstico puntual)</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Potosí</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Potosí</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>noticia:1uil931</t>
+          <t>noticia:mz6q0s</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5992,15 +6086,15 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-10-23 22:49</t>
+          <t>2026-10-23 23:09</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1792810149000</v>
+        <v>1792811349000</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>El Deber</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6018,13 +6112,13 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Accidente de tránsito en la ruta hacia Alto Beni deja varios heridos - El Deber</t>
+          <t>Revelan lista preliminar de heridos tras accidente de Los Chicos Fieles - Red Uno</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQakFJRmx3RlJEMkVHU0pxWXZ2ZU1ib04tZy1yeTB2OGhrYk9CU3pMaDVpRThNZktZMS14UzA2Y1VIcEQtZDg3cEU2SmlzQnBmUVVvM0ZNYzZWNExWUXQ3aHpnd3lqOHFVV3pNbDRLS1NQNGtwb2RjSFpleHJkOG5zSXVtWjVIS1dLejNybktRWTJVZXh3WkFUQVE5T2tMdFdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPczBQcnE2SzFGMXc3b1lsTkNxVWRmS3Vnb01xOTV2WmVva3J2RVlteWpHZ3VJS2dNWGV5NW5FX3ZncnVKTEVDTGpBRndTU1FxeWxtaS1fb1FscGxXMWNXUE9zbHdob1AxVFl1eHB5OU1yUnNoOXJ6U21oVG9PVDA1ak1xQl9hUlB4V0RaQXJqZENGUm8zMUJEY3J0WW5ENE5ObWJLNmpWN0RkSmFJbnZUZGR5UFRPd3QyUFY4WQ?oc=5</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -6033,37 +6127,21 @@
       <c r="M31" t="n">
         <v>1</v>
       </c>
-      <c r="N31" t="n">
-        <v>-15.578</v>
-      </c>
-      <c r="O31" t="n">
-        <v>-67.44</v>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Alto Beni, La Paz</t>
-        </is>
-      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>La Paz</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>Alto Beni</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>noticia:1tliu4i</t>
+          <t>noticia:1uil931</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6073,11 +6151,11 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-23 22:18</t>
+          <t>2026-10-23 22:49</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1792808330000</v>
+        <v>1792810149000</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -6105,7 +6183,7 @@
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQMF9BNnUzLURKNGRMUUJ1VXVRSXNnMlBsQnVXOG0tRlFtY3pvRDNPQmNJMWN2RzJVaWdoWndmcHFnTkZFZnJxRkZtMThYYWlwN09ueUgtei1pSE1hZ2FtSzN6elY4VXJHbzFxdll0eWh0ZkxwQkQ1SDZ5b0E3MlVENGZEWGZHUGlwVG4wd2x3OFNEMVpibnFr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQakFJRmx3RlJEMkVHU0pxWXZ2ZU1ib04tZy1yeTB2OGhrYk9CU3pMaDVpRThNZktZMS14UzA2Y1VIcEQtZDg3cEU2SmlzQnBmUVVvM0ZNYzZWNExWUXQ3aHpnd3lqOHFVV3pNbDRLS1NQNGtwb2RjSFpleHJkOG5zSXVtWjVIS1dLejNybktRWTJVZXh3WkFUQVE5T2tMdFdn?oc=5</t>
         </is>
       </c>
       <c r="L32" t="n">
@@ -6144,7 +6222,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>noticia:1twc9ul</t>
+          <t>noticia:1tliu4i</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6154,11 +6232,11 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-23 22:16</t>
+          <t>2026-10-23 22:18</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1792808192000</v>
+        <v>1792808330000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -6186,7 +6264,7 @@
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNbmwzSnd6c2tFMXBWY0tiemJqRm5CNllOT2p1U0FhdW5QNGFBVXlSZVM1ak5jNGZvcXNVaUQzN3ZQQTlPbmVjQ2Y5RFl2dWVLeUN5NUFodDF0alEyZWlmOHFZWkVVbjdQbkl3ZWtmS25wQWM2TmRZZDBGM2xlS0ZhUzAweXRmcmhVWGY5dV9CUnFBNGtWZHZDSWVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQMF9BNnUzLURKNGRMUUJ1VXVRSXNnMlBsQnVXOG0tRlFtY3pvRDNPQmNJMWN2RzJVaWdoWndmcHFnTkZFZnJxRkZtMThYYWlwN09ueUgtei1pSE1hZ2FtSzN6elY4VXJHbzFxdll0eWh0ZkxwQkQ1SDZ5b0E3MlVENGZEWGZHUGlwVG4wd2x3OFNEMVpibnFr?oc=5</t>
         </is>
       </c>
       <c r="L33" t="n">
@@ -6225,7 +6303,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>noticia:1dygpkp</t>
+          <t>noticia:1twc9ul</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6235,15 +6313,15 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-10-23 21:39</t>
+          <t>2026-10-23 22:16</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1792805983000</v>
+        <v>1792808192000</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>El Deber</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6252,39 +6330,39 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>(Video) Así rescataron a uno de los integrantes de Los Chicos Fieles tras accidente en Caranavi - Red Uno</t>
+          <t>Accidente de tránsito en la ruta hacia Alto Beni deja varios heridos - El Deber</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOdTVUZUQxVTdvYTdONDQxVlhUTzBOS2hKLW1rS1NUcmRYRnlCVlhIcHZlSjdsaktkQm5CWkFYa3lDQkxnMlh0b3prX0lha1BtbW1qS1VuYnNiX3FiZkYyNDJDR0tqZ0pKMU5TeC04SXV4UUJOTUlPUTB6ek01bzUxTUsydjZqZzI3S3ZLUnRWSUFUVk44WEpKUl9rbzRLb2IwYl9sLVlrYmt5d2ZHNUtGd3lRNnYzMlhuMkJOZW1XSUl2N1BxZWpHbm5XTDJhRUtnR190QWQ1TDlTUVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNbmwzSnd6c2tFMXBWY0tiemJqRm5CNllOT2p1U0FhdW5QNGFBVXlSZVM1ak5jNGZvcXNVaUQzN3ZQQTlPbmVjQ2Y5RFl2dWVLeUN5NUFodDF0alEyZWlmOHFZWkVVbjdQbkl3ZWtmS25wQWM2TmRZZDBGM2xlS0ZhUzAweXRmcmhVWGY5dV9CUnFBNGtWZHZDSWVB?oc=5</t>
         </is>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N34" t="n">
-        <v>-15.813</v>
+        <v>-15.578</v>
       </c>
       <c r="O34" t="n">
-        <v>-67.46299999999999</v>
+        <v>-67.44</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Caranavi, La Paz</t>
+          <t>Alto Beni, La Paz</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -6299,14 +6377,14 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>Caranavi</t>
+          <t>Alto Beni</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>noticia:3dv7b0</t>
+          <t>noticia:1dygpkp</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -6316,15 +6394,15 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-23 21:35</t>
+          <t>2026-10-23 21:39</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1792805700000</v>
+        <v>1792805983000</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FmBolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -6333,29 +6411,29 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Accidente en Caranavi: vehículo de Los Chicos Fieles cae a un barranco y deja varios heridos - FmBolivia</t>
+          <t>(Video) Así rescataron a uno de los integrantes de Los Chicos Fieles tras accidente en Caranavi - Red Uno</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNcE1KaHZyUTJCSElxRU9nVzdhTnczWjJGTEhFMEs0bHp2cUdFeHd3VTB0NmVFcjdEN1dsZDZLY2k1ZFFUWkhKV19PU3V2czNyamh1ZE9YajVSVF8xczF6OFhZcWFvYV9EcWg4ZDNCb2p3enhXbFpRYnJMdGdaTXNrWUZSYVhKNTVicWlCLTJ5OE05Z1BvNEx1eEloUk5qTGN3ZHNzbzZWSVljbnRmSERJUWdxRDc0MjJxMGtycWJaaVhXQUUxVUlaWVZLOWE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOdTVUZUQxVTdvYTdONDQxVlhUTzBOS2hKLW1rS1NUcmRYRnlCVlhIcHZlSjdsaktkQm5CWkFYa3lDQkxnMlh0b3prX0lha1BtbW1qS1VuYnNiX3FiZkYyNDJDR0tqZ0pKMU5TeC04SXV4UUJOTUlPUTB6ek01bzUxTUsydjZqZzI3S3ZLUnRWSUFUVk44WEpKUl9rbzRLb2IwYl9sLVlrYmt5d2ZHNUtGd3lRNnYzMlhuMkJOZW1XSUl2N1BxZWpHbm5XTDJhRUtnR190QWQ1TDlTUVk?oc=5</t>
         </is>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>-15.813</v>
@@ -6387,30 +6465,30 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-24:viento:1</t>
+          <t>noticia:3dv7b0</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-10-23 20:55</t>
+          <t>2026-10-23 21:35</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1792803329663</v>
+        <v>1792805700000</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>FmBolivia</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6423,74 +6501,70 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-24: 78.1 km/h de ráfagas pronosticadas</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
-        </is>
-      </c>
+          <t>Accidente en Caranavi: vehículo de Los Chicos Fieles cae a un barranco y deja varios heridos - FmBolivia</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNcE1KaHZyUTJCSElxRU9nVzdhTnczWjJGTEhFMEs0bHp2cUdFeHd3VTB0NmVFcjdEN1dsZDZLY2k1ZFFUWkhKV19PU3V2czNyamh1ZE9YajVSVF8xczF6OFhZcWFvYV9EcWg4ZDNCb2p3enhXbFpRYnJMdGdaTXNrWUZSYVhKNTVicWlCLTJ5OE05Z1BvNEx1eEloUk5qTGN3ZHNzbzZWSVljbnRmSERJUWdxRDc0MjJxMGtycWJaaVhXQUUxVUlaWVZLOWE?oc=5</t>
         </is>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N36" t="n">
-        <v>-17.78</v>
+        <v>-15.813</v>
       </c>
       <c r="O36" t="n">
-        <v>-63.18</v>
+        <v>-67.46299999999999</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Caranavi, La Paz</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>capital (pronóstico puntual)</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Caranavi</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>noticia:rabz5p</t>
+          <t>clima:Santa Cruz:2026-10-24:viento:1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-10-23 20:44</t>
+          <t>2026-10-23 20:55</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1792802686000</v>
+        <v>1792803329663</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -6499,22 +6573,26 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Tome previsiones: se pronostican lluvias y ambiente caluroso para este fin de semana en Cochabamba - Red Uno</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
+          <t>Santa Cruz 2026-10-24: 78.1 km/h de ráfagas pronosticadas</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTlU5NVFpY1RheTN5ZE1IbG5VYTh2Sk5hZHpHeWI3LVdnSFg2cFJFdnBCVkxiUjNKcUgyUW16SWxpMXFkMHdad2xFN043bklJeG1iQ0V1V3hBZk1Ga3NscjdPVWUySmt4bDNTdWlmSUdOMmNlZ2hkSWZFMmk4VGs0Nm9TcnRCTDhINmtnQU9zZDBUY05HcWpxN3FOX3N1dmVJblE0MGc5di1Ma1N2dGNxOUtoV1MzNnl1OXpRaTZ2UGxMc3RDWndubHVQNUd0eVROMGR2OGxVemtOaEc4bTNRaA?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L37" t="n">
@@ -6524,36 +6602,36 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>-17.39</v>
+        <v>-17.78</v>
       </c>
       <c r="O37" t="n">
-        <v>-66.16</v>
+        <v>-63.18</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Cochabamba, Cochabamba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
+          <t>capital (pronóstico puntual)</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>noticia:1jfk053</t>
+          <t>noticia:rabz5p</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6563,11 +6641,11 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-10-23 19:08</t>
+          <t>2026-10-23 20:44</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1792796931000</v>
+        <v>1792802686000</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -6576,43 +6654,43 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>climatológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Sequía en Pasorapa: el ganado muere por falta de agua y alistan declaratoria de desastre - Red Uno</t>
+          <t>Tome previsiones: se pronostican lluvias y ambiente caluroso para este fin de semana en Cochabamba - Red Uno</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNQVhTWE8zdE1BQ3lueWJPeV9wUDNsSmJpS0NJTWppMUY4QmlQSUFHVjRORmtrVHQ3MHB0T1pyS25PamxnY0hBQUtzOVRvSUNaUkdGb1RWSGl4dFA4Z3VINVpQTk1pZUpDdUIyUU5hZS1oNGhBa1RWcFhScVMwVTFrVlJaOFQ4OWFqRWVUZ051bHVJTlMxRTBhRFVLUEV2dTZFdDgtRkxJM3VvN3YzUWJfVk41ZWR5U1JoNmx0WFFkMmNTWGVleGNIQlNxWUJzdHIxSWtz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTlU5NVFpY1RheTN5ZE1IbG5VYTh2Sk5hZHpHeWI3LVdnSFg2cFJFdnBCVkxiUjNKcUgyUW16SWxpMXFkMHdad2xFN043bklJeG1iQ0V1V3hBZk1Ga3NscjdPVWUySmt4bDNTdWlmSUdOMmNlZ2hkSWZFMmk4VGs0Nm9TcnRCTDhINmtnQU9zZDBUY05HcWpxN3FOX3N1dmVJblE0MGc5di1Ma1N2dGNxOUtoV1MzNnl1OXpRaTZ2UGxMc3RDWndubHVQNUd0eVROMGR2OGxVemtOaEc4bTNRaA?oc=5</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>-18.38</v>
+        <v>-17.39</v>
       </c>
       <c r="O38" t="n">
-        <v>-64.649</v>
+        <v>-66.16</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Pasorapa, Cochabamba</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -6627,14 +6705,14 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>Pasorapa</t>
+          <t>Cochabamba</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>noticia:ix3l8o</t>
+          <t>noticia:1jfk053</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6644,56 +6722,56 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-10-23 18:25</t>
+          <t>2026-10-23 19:08</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1792794310000</v>
+        <v>1792796931000</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Visión 360</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>climatológica</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Oruro evalúa suspender clases presenciales por más de 200 casos de Coxsackie - Visión 360</t>
+          <t>Sequía en Pasorapa: el ganado muere por falta de agua y alistan declaratoria de desastre - Red Uno</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0c9IBywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNQVhTWE8zdE1BQ3lueWJPeV9wUDNsSmJpS0NJTWppMUY4QmlQSUFHVjRORmtrVHQ3MHB0T1pyS25PamxnY0hBQUtzOVRvSUNaUkdGb1RWSGl4dFA4Z3VINVpQTk1pZUpDdUIyUU5hZS1oNGhBa1RWcFhScVMwVTFrVlJaOFQ4OWFqRWVUZ051bHVJTlMxRTBhRFVLUEV2dTZFdDgtRkxJM3VvN3YzUWJfVk41ZWR5U1JoNmx0WFFkMmNTWGVleGNIQlNxWUJzdHIxSWtz?oc=5</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>-17.97</v>
+        <v>-18.38</v>
       </c>
       <c r="O39" t="n">
-        <v>-67.11</v>
+        <v>-64.649</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>Pasorapa, Cochabamba</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -6703,19 +6781,19 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Pasorapa</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>noticia:1xqv9m7</t>
+          <t>noticia:ix3l8o</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6725,62 +6803,78 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-10-23 18:09</t>
+          <t>2026-10-23 18:25</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1792793370000</v>
+        <v>1792794310000</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>El Diario del centro del país</t>
+          <t>Visión 360</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Tres heridos en tremendo choque cerca de Oncativo - El Diario del centro del país</t>
+          <t>Oruro evalúa suspender clases presenciales por más de 200 casos de Coxsackie - Visión 360</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZERhbTJMQUJVb3hmZFlSZmRGZkdBLWdFTGJVQzdqZkE4aGhhWmdQZ2JDRW1ndkJLWU90VTZ6Ti1JOUZzcFZfcE1zbkRHU1B3YTF4UkVzdllFa1p3SUlObURGamF0Vm9kc3dPLTZVWFJ4NWZZQmlySElPNHhZTnRGNGNZUWw2ZlI1eVBEQkNGNEhLWTNiLWJLUS0xYjA0UWRhc0d6bVN4aVVLSVdsQWlpMUZYdWw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0c9IBywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0cw?oc=5</t>
         </is>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3</v>
-      </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>-17.97</v>
+      </c>
+      <c r="O40" t="n">
+        <v>-67.11</v>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Oruro, Oruro</t>
+        </is>
+      </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>noticia:1wuregl</t>
+          <t>noticia:1xqv9m7</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6790,78 +6884,62 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-10-23 15:39</t>
+          <t>2026-10-23 18:09</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1792784340000</v>
+        <v>1792793370000</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FmBolivia</t>
+          <t>El Diario del centro del país</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>hidrológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Intensas lluvias inundan La Paz y activan alertas por el riesgo de desborde de ríos - FmBolivia</t>
+          <t>Tres heridos en tremendo choque cerca de Oncativo - El Diario del centro del país</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPZm85aHphekQ4U3BZZkp1ZkF6ZVdSUHgtZmltS1FxUUgza1AwcndWWDJZOWctT0RiVmVabmg5SG42NnJWMlJMMnBlYTlYaVdSb09sR0dnVDdpT29faTdiaDUtZElJdlQ3eTdjR2VsWjlta1FOS1U2Vm1vV3JwWkpvbEw1ZUR3akgwQTZnQnVENjJtVkQtVUpKVEJTeWNJSE1CaEFKa2VqMmZXbWk3ekR4ZWpmZ1Z3elFQaWNaNFJuMXA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZERhbTJMQUJVb3hmZFlSZmRGZkdBLWdFTGJVQzdqZkE4aGhhWmdQZ2JDRW1ndkJLWU90VTZ6Ti1JOUZzcFZfcE1zbkRHU1B3YTF4UkVzdllFa1p3SUlObURGamF0Vm9kc3dPLTZVWFJ4NWZZQmlySElPNHhZTnRGNGNZUWw2ZlI1eVBEQkNGNEhLWTNiLWJLUS0xYjA0UWRhc0d6bVN4aVVLSVdsQWlpMUZYdWw?oc=5</t>
         </is>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
-        <v>-16.169</v>
-      </c>
-      <c r="O41" t="n">
-        <v>-68.09</v>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>La Paz, La Paz</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>La Paz</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>Nuestra Señora de La Paz</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>noticia:1570kkf</t>
+          <t>noticia:1wuregl</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6871,20 +6949,20 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-10-23 15:28</t>
+          <t>2026-10-23 15:39</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1792783705000</v>
+        <v>1792784340000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>FmBolivia</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>hidrológica</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6897,13 +6975,13 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>¿Se suspenden las clases en Oruro? Más de 200 casos de Coxsackie activan evaluaciones - Red Uno</t>
+          <t>Intensas lluvias inundan La Paz y activan alertas por el riesgo de desborde de ríos - FmBolivia</t>
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNMFdHaVpKRmMyOENDYm16UXJPenVSQnpmTE94bDc4UFhqakluMUdvZjAwamUxT3BVWUpJQm8xVHBWengxQmhWM1hjU3d2YXFrLXpVU2VrZDJiMXZLMlQ5bGxGOHFETFhYM0s2RjlUTlhkd0g2eXQweDFHaTlKNGNMUlJfOWg2a0JjTklXUWZKc1BmUXZuZFZ2MF9fV2lEYUY4LXNiNmk3cF9FNjVtTl9GWFotT2ltS0xXTnM1dENvSU9kbFRMalFrYVdXOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPZm85aHphekQ4U3BZZkp1ZkF6ZVdSUHgtZmltS1FxUUgza1AwcndWWDJZOWctT0RiVmVabmg5SG42NnJWMlJMMnBlYTlYaVdSb09sR0dnVDdpT29faTdiaDUtZElJdlQ3eTdjR2VsWjlta1FOS1U2Vm1vV3JwWkpvbEw1ZUR3akgwQTZnQnVENjJtVkQtVUpKVEJTeWNJSE1CaEFKa2VqMmZXbWk3ekR4ZWpmZ1Z3elFQaWNaNFJuMXA?oc=5</t>
         </is>
       </c>
       <c r="L42" t="n">
@@ -6913,14 +6991,14 @@
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>-17.97</v>
+        <v>-16.169</v>
       </c>
       <c r="O42" t="n">
-        <v>-67.11</v>
+        <v>-68.09</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>La Paz, La Paz</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -6930,19 +7008,19 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Nuestra Señora de La Paz</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>noticia:1nzu2o8</t>
+          <t>noticia:1570kkf</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6952,39 +7030,39 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-10-23 15:20</t>
+          <t>2026-10-23 15:28</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1792783236000</v>
+        <v>1792783705000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>hidrológica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Alerta naranja por posibles desbordes en tres departamentos (15:20) - El Diario - Bolivia</t>
+          <t>¿Se suspenden las clases en Oruro? Más de 200 casos de Coxsackie activan evaluaciones - Red Uno</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPTnBESV9OODZhNjY3T2M2X2NZcmk4clI0eFZsd3VLMVRwaUlSdF9wanZyVGxDNUlNTm5wbGpLN1lvX09mNGxFVkpIZDNGdi1pNDdfSGlESThfeVloQzJsNUMyNUpWUDhzTVJiYWJpNkQ1RHliRWljZlp3SlhtZ2FhU0pvV0syUmZIejJZWHlRdTBOTG4zaTc5cEsycW9IcEx2SkQtN01Gendlb1VR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNMFdHaVpKRmMyOENDYm16UXJPenVSQnpmTE94bDc4UFhqakluMUdvZjAwamUxT3BVWUpJQm8xVHBWengxQmhWM1hjU3d2YXFrLXpVU2VrZDJiMXZLMlQ5bGxGOHFETFhYM0s2RjlUTlhkd0g2eXQweDFHaTlKNGNMUlJfOWg2a0JjTklXUWZKc1BmUXZuZFZ2MF9fV2lEYUY4LXNiNmk3cF9FNjVtTl9GWFotT2ltS0xXTnM1dENvSU9kbFRMalFrYVdXOA?oc=5</t>
         </is>
       </c>
       <c r="L43" t="n">
@@ -6993,21 +7071,37 @@
       <c r="M43" t="n">
         <v>0</v>
       </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
+      <c r="N43" t="n">
+        <v>-17.97</v>
+      </c>
+      <c r="O43" t="n">
+        <v>-67.11</v>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Oruro, Oruro</t>
+        </is>
+      </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>noticia:1itd1r7</t>
+          <t>noticia:1nzu2o8</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -7017,39 +7111,39 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-10-23 15:01</t>
+          <t>2026-10-23 15:20</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1792782098000</v>
+        <v>1792783236000</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>eju.tv</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>hidrológica</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Intensa lluvia y granizada en La Paz inundan vías y elevan el nivel de los ríos - eju.tv</t>
+          <t>Alerta naranja por posibles desbordes en tres departamentos (15:20) - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNWU9QWElKQXEyN3UxVm4xbzJzbEJ1TU1NTHZlRUp6YndmeU9GQnJKcTluVEJ2ZHQ5cGp3aWhlMUd5ektWQlBpUVNmZnZuRnJwMXlydzAzX0FBVnY5UDMzQTBkWVRNRUNJSlRvX3MyQVhMcEhIMW9WSUpXckVSd0RJWk1KMFBKWmJNU3diQVlEN1Y5aVV6eVBaZXpOMnFIWWxaMlRlY0ZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPTnBESV9OODZhNjY3T2M2X2NZcmk4clI0eFZsd3VLMVRwaUlSdF9wanZyVGxDNUlNTm5wbGpLN1lvX09mNGxFVkpIZDNGdi1pNDdfSGlESThfeVloQzJsNUMyNUpWUDhzTVJiYWJpNkQ1RHliRWljZlp3SlhtZ2FhU0pvV0syUmZIejJZWHlRdTBOTG4zaTc5cEsycW9IcEx2SkQtN01Gendlb1VR?oc=5</t>
         </is>
       </c>
       <c r="L44" t="n">
@@ -7058,37 +7152,21 @@
       <c r="M44" t="n">
         <v>0</v>
       </c>
-      <c r="N44" t="n">
-        <v>-16.169</v>
-      </c>
-      <c r="O44" t="n">
-        <v>-68.09</v>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>La Paz, La Paz</t>
-        </is>
-      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>La Paz</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>Nuestra Señora de La Paz</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>noticia:1l4xxfk</t>
+          <t>noticia:1itd1r7</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -7098,20 +7176,20 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-10-23 14:51</t>
+          <t>2026-10-23 15:01</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1792781480000</v>
+        <v>1792782098000</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>eju.tv</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7124,13 +7202,13 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
+          <t>Intensa lluvia y granizada en La Paz inundan vías y elevan el nivel de los ríos - eju.tv</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQS2FPaHd3UnFBRjRoa0lKUm1MNUQ5S00zN1RJZE5fWlVUQnhiY0lLcFRkY2JZak1mZ0c2WEVMVUNJVUJTMGFLNHg4S2ZKNTRqLXJHM09ET19hX1pZeTQwUkdEc2huTHVpcno2QTRZbnhralVRWXozcWc1a2pHUEpBeTV1cWgzTWRwaDEweURKeVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNWU9QWElKQXEyN3UxVm4xbzJzbEJ1TU1NTHZlRUp6YndmeU9GQnJKcTluVEJ2ZHQ5cGp3aWhlMUd5ektWQlBpUVNmZnZuRnJwMXlydzAzX0FBVnY5UDMzQTBkWVRNRUNJSlRvX3MyQVhMcEhIMW9WSUpXckVSd0RJWk1KMFBKWmJNU3diQVlEN1Y5aVV6eVBaZXpOMnFIWWxaMlRlY0ZB?oc=5</t>
         </is>
       </c>
       <c r="L45" t="n">
@@ -7140,14 +7218,14 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>-17.97</v>
+        <v>-16.169</v>
       </c>
       <c r="O45" t="n">
-        <v>-67.11</v>
+        <v>-68.09</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>La Paz, La Paz</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -7157,19 +7235,19 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Nuestra Señora de La Paz</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>noticia:51709n</t>
+          <t>noticia:1l4xxfk</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -7179,56 +7257,56 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-10-23 13:38</t>
+          <t>2026-10-23 14:51</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1792777139000</v>
+        <v>1792781480000</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>eju.tv</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - eju.tv</t>
+          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPcjZTSmprRGVoNlRqQmdBTE5VM3pRQ1ZFakFUbzVyMUhiaDVkT0liaG9UNEZXekV6bWsycUk4X1JCSEY5RjhNVlZaTk9ULUFuZkY3NnZuWmZ1a19leUhFdlIyQV9kLWxlSkxfeXFhcFRTZjZ2YkpQQlJ1dkNLMDBjaGZ4SkhyQ0RfcnhKSEg5WURCQVQwbENYTHEzUzJSaUEzMGo2bWdyS3lsM016LXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQS2FPaHd3UnFBRjRoa0lKUm1MNUQ5S00zN1RJZE5fWlVUQnhiY0lLcFRkY2JZak1mZ0c2WEVMVUNJVUJTMGFLNHg4S2ZKNTRqLXJHM09ET19hX1pZeTQwUkdEc2huTHVpcno2QTRZbnhralVRWXozcWc1a2pHUEpBeTV1cWgzTWRwaDEweURKeVE?oc=5</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>-17.764</v>
+        <v>-17.97</v>
       </c>
       <c r="O46" t="n">
-        <v>-62.903</v>
+        <v>-67.11</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Cotoca, Santa Cruz</t>
+          <t>Oruro, Oruro</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -7238,19 +7316,19 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Oruro</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>Cotoca</t>
+          <t>Oruro</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>noticia:11rddql</t>
+          <t>noticia:51709n</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -7260,56 +7338,56 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-10-23 13:22</t>
+          <t>2026-10-23 13:38</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1792776139000</v>
+        <v>1792777139000</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>eju.tv</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Intensifican acciones preventivas contra el dengue en Caranavi - El Diario - Bolivia</t>
+          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - eju.tv</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOMjhSeDJBek5iaFhDcnFzX1lKelgwZmUwLTJnbEhMdDRMelUxNks5Ti1pRHh3dDhTcC1YZEdqM3FJOGdqVHRvcXVhRlpCQzVDTEZMUFBkV1NrYVQ2LXRqTTBhcGRQc21CQ0VabzZaNExXb1BjTzJ2Uk5BcFF0VG5XOFNRa3lqUWlJSnRFUUVXYnNpbXB0LVVmSXVWSzJxcmVpdVVxUC1KOUhTQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPcjZTSmprRGVoNlRqQmdBTE5VM3pRQ1ZFakFUbzVyMUhiaDVkT0liaG9UNEZXekV6bWsycUk4X1JCSEY5RjhNVlZaTk9ULUFuZkY3NnZuWmZ1a19leUhFdlIyQV9kLWxlSkxfeXFhcFRTZjZ2YkpQQlJ1dkNLMDBjaGZ4SkhyQ0RfcnhKSEg5WURCQVQwbENYTHEzUzJSaUEzMGo2bWdyS3lsM016LXc?oc=5</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N47" t="n">
-        <v>-15.813</v>
+        <v>-17.764</v>
       </c>
       <c r="O47" t="n">
-        <v>-67.46299999999999</v>
+        <v>-62.903</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Caranavi, La Paz</t>
+          <t>Cotoca, Santa Cruz</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -7319,19 +7397,19 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>Caranavi</t>
+          <t>Cotoca</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>noticia:fcm3nx</t>
+          <t>noticia:11rddql</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -7341,62 +7419,78 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-10-23 12:58</t>
+          <t>2026-10-23 13:22</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1792774699000</v>
+        <v>1792776139000</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>[VIDEO] Así fue el accidente de moto que dejó un adolescente fallecido y un hombre gravemente herido - Red Uno</t>
+          <t>Intensifican acciones preventivas contra el dengue en Caranavi - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOSmJMazhUemNfRHpWcDBoTVFZMUpwdlVKVUtvUXZNTGRRRHlwLW5KNmNhcmFnd1czbi1yalhFMnpSS1dmUE9jVzNlOS1kMWZtRzBHZ2EtcDRDdU5Gc2JUQVIwM2xPa2lZVmswRi1SUFVPcm8xcHlGN3F2UThTSDdKMDNyYnJmVkcxazNLLVBLOWFYM09FVUpmVnN5RVhpSVo2V1VCVmFwQ1gzTmRUWVp2aXMwcmxHRS1GV2p3NTBtR2RzM2wwVHUzaGJkRXJYbHdvaDlhWm5YMTk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOMjhSeDJBek5iaFhDcnFzX1lKelgwZmUwLTJnbEhMdDRMelUxNks5Ti1pRHh3dDhTcC1YZEdqM3FJOGdqVHRvcXVhRlpCQzVDTEZMUFBkV1NrYVQ2LXRqTTBhcGRQc21CQ0VabzZaNExXb1BjTzJ2Uk5BcFF0VG5XOFNRa3lqUWlJSnRFUUVXYnNpbXB0LVVmSXVWSzJxcmVpdVVxUC1KOUhTQQ?oc=5</t>
         </is>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>1</v>
-      </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>-15.813</v>
+      </c>
+      <c r="O48" t="n">
+        <v>-67.46299999999999</v>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Caranavi, La Paz</t>
+        </is>
+      </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>La Paz</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Caranavi</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>noticia:1cjx1qd</t>
+          <t>noticia:fcm3nx</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -7406,78 +7500,62 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-10-23 12:39</t>
+          <t>2026-10-23 12:58</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1792773575000</v>
+        <v>1792774699000</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Más de 60 municipios en La Paz sufren falta de lluvias - La Patria Bolivia</t>
+          <t>[VIDEO] Así fue el accidente de moto que dejó un adolescente fallecido y un hombre gravemente herido - Red Uno</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE52Qi03Z1J6OS1CR2liRVZ0VlhCcmVQWFV6RUdGNXdrbzZRNXFjTWRaRnc1b3VoV0xaY3RIdncxNlNnYkxyUXo5MTlJWmMwWDNSMDE4ZHI2VkpWajFPaUF2SmRVYkk2eDZYQ1RfUU9ieENrZG9UVVFiaXZSeGI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOSmJMazhUemNfRHpWcDBoTVFZMUpwdlVKVUtvUXZNTGRRRHlwLW5KNmNhcmFnd1czbi1yalhFMnpSS1dmUE9jVzNlOS1kMWZtRzBHZ2EtcDRDdU5Gc2JUQVIwM2xPa2lZVmswRi1SUFVPcm8xcHlGN3F2UThTSDdKMDNyYnJmVkcxazNLLVBLOWFYM09FVUpmVnN5RVhpSVo2V1VCVmFwQ1gzTmRUWVp2aXMwcmxHRS1GV2p3NTBtR2RzM2wwVHUzaGJkRXJYbHdvaDlhWm5YMTk?oc=5</t>
         </is>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="n">
-        <v>-16.169</v>
-      </c>
-      <c r="O49" t="n">
-        <v>-68.09</v>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>La Paz, La Paz</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>La Paz</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>Nuestra Señora de La Paz</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>noticia:11y8tre</t>
+          <t>noticia:1cjx1qd</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -7487,56 +7565,56 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-10-23 11:43</t>
+          <t>2026-10-23 12:39</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1792770197000</v>
+        <v>1792773575000</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>La Patria Bolivia</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - Red Uno</t>
+          <t>Más de 60 municipios en La Paz sufren falta de lluvias - La Patria Bolivia</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOVGY3YVRLWWxYM0IycjF4dlNUeUhqZG90Yng4aWhmN3A5ai02WENWYnF4bWpoZHFKMGc1X0JPRHdRRVZfSlA4UmZFa2kxYkNIS3ZtQ1NvNlNCME51eVZTRkRKSUQ5MmRoaWl5Tkt5NHpPUEFwemN2YTV1djFwdHlqQnFqRHNPenhYcTlsanJPcXhpOVV1NmFBUXZyazQ2MkUzM0dSZy02ZllxTGtjcl9ldzdHSktTRlVaalZJc1pubUNQMWFTbzVEOUJ1UmhCdEJt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE52Qi03Z1J6OS1CR2liRVZ0VlhCcmVQWFV6RUdGNXdrbzZRNXFjTWRaRnc1b3VoV0xaY3RIdncxNlNnYkxyUXo5MTlJWmMwWDNSMDE4ZHI2VkpWajFPaUF2SmRVYkk2eDZYQ1RfUU9ieENrZG9UVVFiaXZSeGI?oc=5</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>-17.764</v>
+        <v>-16.169</v>
       </c>
       <c r="O50" t="n">
-        <v>-62.903</v>
+        <v>-68.09</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Cotoca, Santa Cruz</t>
+          <t>La Paz, La Paz</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -7546,42 +7624,42 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>Cotoca</t>
+          <t>Nuestra Señora de La Paz</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>clima:Sucre:2026-10-23:viento:1</t>
+          <t>noticia:11y8tre</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-10-23 06:55</t>
+          <t>2026-10-23 11:43</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1792752927735</v>
+        <v>1792770197000</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7594,56 +7672,52 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Sucre 2026-10-23: 66.2 km/h de ráfagas pronosticadas</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
-        </is>
-      </c>
+          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - Red Uno</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOVGY3YVRLWWxYM0IycjF4dlNUeUhqZG90Yng4aWhmN3A5ai02WENWYnF4bWpoZHFKMGc1X0JPRHdRRVZfSlA4UmZFa2kxYkNIS3ZtQ1NvNlNCME51eVZTRkRKSUQ5MmRoaWl5Tkt5NHpPUEFwemN2YTV1djFwdHlqQnFqRHNPenhYcTlsanJPcXhpOVV1NmFBUXZyazQ2MkUzM0dSZy02ZllxTGtjcl9ldzdHSktTRlVaalZJc1pubUNQMWFTbzVEOUJ1UmhCdEJt?oc=5</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N51" t="n">
-        <v>-19.03</v>
+        <v>-17.764</v>
       </c>
       <c r="O51" t="n">
-        <v>-65.26000000000001</v>
+        <v>-62.903</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Cotoca, Santa Cruz</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>capital (pronóstico puntual)</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Chuquisaca</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Cotoca</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-24:viento:2</t>
+          <t>clima:Sucre:2026-10-23:viento:1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -7657,7 +7731,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1792752927734</v>
+        <v>1792752927735</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -7670,16 +7744,16 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-24: 85 km/h de ráfagas pronosticadas</t>
+          <t>Sucre 2026-10-23: 66.2 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -7699,14 +7773,14 @@
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>-17.78</v>
+        <v>-19.03</v>
       </c>
       <c r="O52" t="n">
-        <v>-63.18</v>
+        <v>-65.26000000000001</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -7716,65 +7790,65 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Chuquisaca</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Sucre</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>usgs:us6000u49c</t>
+          <t>clima:Santa Cruz:2026-10-24:viento:2</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>usgs</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-10-22 22:45</t>
+          <t>2026-10-23 06:55</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1792723541183</v>
+        <v>1792752927734</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>USGS</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>geológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Sismo M 4.5 - 58 km SW of Atocha, Bolivia</t>
+          <t>Santa Cruz 2026-10-24: 85 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Profundidad 236 km</t>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://earthquake.usgs.gov/earthquakes/eventpage/us6000u49c</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L53" t="n">
@@ -7784,59 +7858,59 @@
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>-21.3469</v>
+        <v>-17.78</v>
       </c>
       <c r="O53" t="n">
-        <v>-66.5795</v>
+        <v>-63.18</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>58 km SW of Atocha, Bolivia</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>coordenada de la fuente</t>
+          <t>capital (pronóstico puntual)</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>San Pablo</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-22:viento:1</t>
+          <t>usgs:us6000u49c</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>usgs</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-10-22 21:55</t>
+          <t>2026-10-22 22:45</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1792720528712</v>
+        <v>1792723541183</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>USGS</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>geológica</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7849,17 +7923,17 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-22: 67.7 km/h de ráfagas pronosticadas</t>
+          <t>Sismo M 4.5 - 58 km SW of Atocha, Bolivia</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+          <t>Profundidad 236 km</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://earthquake.usgs.gov/earthquakes/eventpage/us6000u49c</t>
         </is>
       </c>
       <c r="L54" t="n">
@@ -7869,36 +7943,36 @@
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>-17.78</v>
+        <v>-21.3469</v>
       </c>
       <c r="O54" t="n">
-        <v>-63.18</v>
+        <v>-66.5795</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>58 km SW of Atocha, Bolivia</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>capital (pronóstico puntual)</t>
+          <t>coordenada de la fuente</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>San Pablo</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-23:viento:2</t>
+          <t>clima:Santa Cruz:2026-10-22:viento:1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -7925,16 +7999,16 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-23: 83.9 km/h de ráfagas pronosticadas</t>
+          <t>Santa Cruz 2026-10-22: 67.7 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7983,49 +8057,53 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>noticia:1hhvre7</t>
+          <t>clima:Santa Cruz:2026-10-23:viento:2</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-10-22 19:36</t>
+          <t>2026-10-22 21:55</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1792712202000</v>
+        <v>1792720528712</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>El Mundo Bolivia</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Virgen de Cotoca: Controlan incendio en depósito de materiales plásticos - El Mundo Bolivia</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
+          <t>Santa Cruz 2026-10-23: 83.9 km/h de ráfagas pronosticadas</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcDF6VE5FNzRaWGRuUzFKeXhnZ21DZTRaaEtrVEJEa1Z3ejg2VG1ONG1ENmlDWlkyVjlkQkJwS2F1XzBGMFQwSHd4OEwxTW1PbHdGcUh1ckV6SGpDd2hiN0dkeUVTcnFXT3RjOU1kLXZtVVdZY2hkZS1pcVpVUFhnRktqcHY5UnBrY0xUMDRETjl6N0pXT3A5amxhMA?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L56" t="n">
@@ -8035,19 +8113,19 @@
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>-17.764</v>
+        <v>-17.78</v>
       </c>
       <c r="O56" t="n">
-        <v>-62.903</v>
+        <v>-63.18</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Cotoca, Santa Cruz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
+          <t>capital (pronóstico puntual)</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -8057,14 +8135,14 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>Cotoca</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>noticia:bksnde</t>
+          <t>noticia:1hhvre7</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -8074,15 +8152,15 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-10-22 17:01</t>
+          <t>2026-10-22 19:36</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1792702880000</v>
+        <v>1792712202000</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>eju.tv</t>
+          <t>El Mundo Bolivia</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -8100,13 +8178,13 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Reportan un incendio cerca de la carretera a Cotoca - eju.tv</t>
+          <t>Virgen de Cotoca: Controlan incendio en depósito de materiales plásticos - El Mundo Bolivia</t>
         </is>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPNGtpbnBfRnRBalVudnBlZHdVQ0ZSaUplZmtvTGE0aTQzdkxWS3d4My1EZEJ1UE9FNFQ3RmpyZGVsbS1qNEM1QUVFRFAxM2pYT1VqQzRuVjRtZnVNUGlKODNMc0F1a3l6TUpuQmtlUWNlVTVEWWU5ZGZtQm5LWUp3Sg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcDF6VE5FNzRaWGRuUzFKeXhnZ21DZTRaaEtrVEJEa1Z3ejg2VG1ONG1ENmlDWlkyVjlkQkJwS2F1XzBGMFQwSHd4OEwxTW1PbHdGcUh1ckV6SGpDd2hiN0dkeUVTcnFXT3RjOU1kLXZtVVdZY2hkZS1pcVpVUFhnRktqcHY5UnBrY0xUMDRETjl6N0pXT3A5amxhMA?oc=5</t>
         </is>
       </c>
       <c r="L57" t="n">
@@ -8145,7 +8223,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>noticia:17hz69v</t>
+          <t>noticia:bksnde</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -8155,15 +8233,15 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-10-22 13:05</t>
+          <t>2026-10-22 17:01</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1792688709000</v>
+        <v>1792702880000</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>La Razón Digital Bolivia</t>
+          <t>eju.tv</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -8172,45 +8250,61 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Accidente en El Sillar deja al menos 29 heridos - La Razón Digital Bolivia</t>
+          <t>Reportan un incendio cerca de la carretera a Cotoca - eju.tv</t>
         </is>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPaXhTdm45YWZnWVFxVzJnb1ZwbUN4SmUtLVdJN0VJdFZBamRyQmFxN0RZelBfTklaSTVyOUZ3ajQ5MFB2TEN4Ukd6TE5ORFY5SEROVk1CZ25sRWJ1QnRBdTVfTktlby1NWXhaVWI5YnRvaDZWbHVjdDVoeFp5Tk5veFk5a19MSWJqcEJVV0dzV3k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPNGtpbnBfRnRBalVudnBlZHdVQ0ZSaUplZmtvTGE0aTQzdkxWS3d4My1EZEJ1UE9FNFQ3RmpyZGVsbS1qNEM1QUVFRFAxM2pYT1VqQzRuVjRtZnVNUGlKODNMc0F1a3l6TUpuQmtlUWNlVTVEWWU5ZGZtQm5LWUp3Sg?oc=5</t>
         </is>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>29</v>
-      </c>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>-17.764</v>
+      </c>
+      <c r="O58" t="n">
+        <v>-62.903</v>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Cotoca, Santa Cruz</t>
+        </is>
+      </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>Cotoca</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>noticia:1f1qb0</t>
+          <t>noticia:17hz69v</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -8220,15 +8314,15 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-10-22 12:09</t>
+          <t>2026-10-22 13:05</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1792685373000</v>
+        <v>1792688709000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>La Razón Digital Bolivia</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -8237,61 +8331,45 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Accidente en el tramo Locotal–Villa Tunari: la vía está transitable con precaución - Red Uno</t>
+          <t>Accidente en El Sillar deja al menos 29 heridos - La Razón Digital Bolivia</t>
         </is>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTFozcEEwNXBqV19sS2VibXh0MGt0QlhsX1djSTFGQW5zNlFLRHZpNVVnZ1JmWDQ4LVRHX2Rmb3B5UU9qV0FZQmJCaUZYdmwyNG1NenJ4Qzlzd0NJTGs1SjMxdFRtRFBzSUkybGJfZFFaNFZBc21FSUJYSFVkQkVkSEhQaGw0UFVzeXctZHo3cjNsYm5weXJlOU1wcmFncnNhMC1BQUpvNWlDX1NxZXU4b09kVFFWR2tSVEk2UTdXXzB3TjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPaXhTdm45YWZnWVFxVzJnb1ZwbUN4SmUtLVdJN0VJdFZBamRyQmFxN0RZelBfTklaSTVyOUZ3ajQ5MFB2TEN4Ukd6TE5ORFY5SEROVk1CZ25sRWJ1QnRBdTVfTktlby1NWXhaVWI5YnRvaDZWbHVjdDVoeFp5Tk5veFk5a19MSWJqcEJVV0dzV3k?oc=5</t>
         </is>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="n">
-        <v>-16.556</v>
-      </c>
-      <c r="O59" t="n">
-        <v>-65.569</v>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>Villa Tunari, Cochabamba</t>
-        </is>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>Villa Tunari</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>noticia:wi18tm</t>
+          <t>noticia:1f1qb0</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -8301,11 +8379,11 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-10-22 11:53</t>
+          <t>2026-10-22 12:09</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1792684426000</v>
+        <v>1792685373000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -8314,49 +8392,65 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>tecnológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Accidente en El Sillar deja heridos y derrame de combustible: esto es lo último que se sabe - Red Uno</t>
+          <t>Accidente en el tramo Locotal–Villa Tunari: la vía está transitable con precaución - Red Uno</t>
         </is>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPZHNBTEdaQm5Wby1lTF9mWlQ2aGg0MVc4S0MwVWJ3dUJ5WWU5X3IwYWhKRjk5VWtYWEJHRDF4QldVc29laVNPSTJNWFBDSkNFQlFSYTJUXzNMNF9hckFBN1I2T2xoQUtYQ2V6MDNTZHhHVk9qeTBCdHRpM2ZLd0pyOFRweUUxX19STzRHTHg5VUY5d1lhS0tDeXpCdklqcTZGT1J4R0xnSDhoak1EZ2dtNUhSTUV6b1o0U0VSdWY5X0E3U05Tc1dYVEN2WFZUeFhPMTBJTmowNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTFozcEEwNXBqV19sS2VibXh0MGt0QlhsX1djSTFGQW5zNlFLRHZpNVVnZ1JmWDQ4LVRHX2Rmb3B5UU9qV0FZQmJCaUZYdmwyNG1NenJ4Qzlzd0NJTGs1SjMxdFRtRFBzSUkybGJfZFFaNFZBc21FSUJYSFVkQkVkSEhQaGw0UFVzeXctZHo3cjNsYm5weXJlOU1wcmFncnNhMC1BQUpvNWlDX1NxZXU4b09kVFFWR2tSVEk2UTdXXzB3TjA?oc=5</t>
         </is>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>1</v>
-      </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>-16.556</v>
+      </c>
+      <c r="O60" t="n">
+        <v>-65.569</v>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Villa Tunari, Cochabamba</t>
+        </is>
+      </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>Villa Tunari</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>noticia:12gfagq</t>
+          <t>noticia:wi18tm</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -8366,78 +8460,62 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-10-22 11:28</t>
+          <t>2026-10-22 11:53</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1792682880000</v>
+        <v>1792684426000</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>FmBolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>tecnológica</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Reportan triple colisión entre dos camiones y un bus en la carretera Cochabamba-Santa Cruz - FmBolivia</t>
+          <t>Accidente en El Sillar deja heridos y derrame de combustible: esto es lo último que se sabe - Red Uno</t>
         </is>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNMTNBaFZNMU9SR25vdVBuNXlZY3g4VkFWYXRiQnNSaUFjemZhUHZWNHg4V2owU2xfNndBak94TnU2cHNUVXdNNWl2eUdHZVNMbVZweTR5M0o0bWdTNUN4QkoxUkI2TDBmVE03M09zRGhJRVFzV0tPZ1NCWEJLUkt1ZGN4UGduOUZMQnJoM0tMYTh0ZlFxaFJNUkJqaWFPazRlMzN3ajhjUEdUYXlZRndpb3RSdTFCX2tCZGJxQ0x4SlBISWJsRVoyN3ZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPZHNBTEdaQm5Wby1lTF9mWlQ2aGg0MVc4S0MwVWJ3dUJ5WWU5X3IwYWhKRjk5VWtYWEJHRDF4QldVc29laVNPSTJNWFBDSkNFQlFSYTJUXzNMNF9hckFBN1I2T2xoQUtYQ2V6MDNTZHhHVk9qeTBCdHRpM2ZLd0pyOFRweUUxX19STzRHTHg5VUY5d1lhS0tDeXpCdklqcTZGT1J4R0xnSDhoak1EZ2dtNUhSTUV6b1o0U0VSdWY5X0E3U05Tc1dYVEN2WFZUeFhPMTBJTmowNA?oc=5</t>
         </is>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="n">
-        <v>-17.39</v>
-      </c>
-      <c r="O61" t="n">
-        <v>-66.16</v>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>Cochabamba, Cochabamba</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>noticia:1uq1bxy</t>
+          <t>noticia:12gfagq</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -8447,15 +8525,15 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-10-22 10:44</t>
+          <t>2026-10-22 11:28</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1792680273000</v>
+        <v>1792682880000</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>FmBolivia</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -8473,13 +8551,13 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Reportan triple colisión en la carretera Cochabamba–Santa Cruz - Red Uno</t>
+          <t>Reportan triple colisión entre dos camiones y un bus en la carretera Cochabamba-Santa Cruz - FmBolivia</t>
         </is>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNNUROMzd1UDJRWVZZQ011cFd2c1FSdER1ZzdleU04cXpwYk5HaUZrLXoyU2NzdFk1dnNRUndhUWt0cG9DX09rSjlLcDItU0tzcmQtS3E4dDQ4ZF9HdGJLdk13ek9BNHJUWVlCcklrM25rZ01RbXhLalRBT1FGdDNReHdlTFZkNkJ5ZFd3N3NZVFVmOFUxbEhHN0RsaUxiSVZsM0lXVEFYSHVRQlhsOEtJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNMTNBaFZNMU9SR25vdVBuNXlZY3g4VkFWYXRiQnNSaUFjemZhUHZWNHg4V2owU2xfNndBak94TnU2cHNUVXdNNWl2eUdHZVNMbVZweTR5M0o0bWdTNUN4QkoxUkI2TDBmVE03M09zRGhJRVFzV0tPZ1NCWEJLUkt1ZGN4UGduOUZMQnJoM0tMYTh0ZlFxaFJNUkJqaWFPazRlMzN3ajhjUEdUYXlZRndpb3RSdTFCX2tCZGJxQ0x4SlBISWJsRVoyN3ZR?oc=5</t>
         </is>
       </c>
       <c r="L62" t="n">
@@ -8518,7 +8596,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>noticia:1jl2oid</t>
+          <t>noticia:1uq1bxy</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -8528,15 +8606,15 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-10-22 07:49</t>
+          <t>2026-10-22 10:44</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1792669785000</v>
+        <v>1792680273000</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>eju.tv</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -8545,39 +8623,39 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - eju.tv</t>
+          <t>Reportan triple colisión en la carretera Cochabamba–Santa Cruz - Red Uno</t>
         </is>
       </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQbTBrUmlla3FvVU1EX1pxcUI3SXYzbUFFMzlnRzhlSDJwMGpWWURxYjIwSkJBRGdCazMzT01hVy1qMFY3RnJLbC1XNXJ4bU55aDJVeXpNUlRsbzQ3T3hiRXJ5SWlhNmw5cDZFanNoWFBtQ01Gd3dscXltWmU5VHBSQlN3c2IwNGxuVE5tQ3lOT1RmNzRiVi1hc0hn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNNUROMzd1UDJRWVZZQ011cFd2c1FSdER1ZzdleU04cXpwYk5HaUZrLXoyU2NzdFk1dnNRUndhUWt0cG9DX09rSjlLcDItU0tzcmQtS3E4dDQ4ZF9HdGJLdk13ek9BNHJUWVlCcklrM25rZ01RbXhLalRBT1FGdDNReHdlTFZkNkJ5ZFd3N3NZVFVmOFUxbEhHN0RsaUxiSVZsM0lXVEFYSHVRQlhsOEtJ?oc=5</t>
         </is>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>-17.781</v>
+        <v>-17.39</v>
       </c>
       <c r="O63" t="n">
-        <v>-63.139</v>
+        <v>-66.16</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Santa Cruz, Santa Cruz</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -8587,19 +8665,19 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Cochabamba</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>noticia:yqgeq</t>
+          <t>noticia:1jl2oid</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -8609,15 +8687,15 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-10-22 07:43</t>
+          <t>2026-10-22 07:49</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1792669426000</v>
+        <v>1792669785000</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>eju.tv</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -8635,13 +8713,13 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - Red Uno</t>
+          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - eju.tv</t>
         </is>
       </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNVEh1bFlCanFuOTJid2EzYS1meG5oekFJcGFaME1fTk9sUnZpd3U0UXFHUFVJSW1jc1hzM2VFOFprT2xNYjBzbmswZmdJV3dremRIS0I4MDNzRjBnbEttWEhfOWZBbmFrRnNHWDFVLVFoM0VkZkxkaW4tMmZlSFJLei1heTFHMU0wSmxQVVRZN0cwaXQzcDBtZkdwTUFma0RXU2dwLXRnLTBkNGN3Vm1fV3hEdlM1dWZ1SEsw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQbTBrUmlla3FvVU1EX1pxcUI3SXYzbUFFMzlnRzhlSDJwMGpWWURxYjIwSkJBRGdCazMzT01hVy1qMFY3RnJLbC1XNXJ4bU55aDJVeXpNUlRsbzQ3T3hiRXJ5SWlhNmw5cDZFanNoWFBtQ01Gd3dscXltWmU5VHBSQlN3c2IwNGxuVE5tQ3lOT1RmNzRiVi1hc0hn?oc=5</t>
         </is>
       </c>
       <c r="L64" t="n">
@@ -8680,7 +8758,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>noticia:n32ahi</t>
+          <t>noticia:yqgeq</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -8690,69 +8768,150 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-10-22 05:30</t>
+          <t>2026-10-22 07:43</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1792661402000</v>
+        <v>1792669426000</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>FmBolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Senamhi anuncia el inicio de la temporada de lluvias en Bolivia y prevé granizadas como la de La Paz - FmBolivia</t>
+          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - Red Uno</t>
         </is>
       </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNVEh1bFlCanFuOTJid2EzYS1meG5oekFJcGFaME1fTk9sUnZpd3U0UXFHUFVJSW1jc1hzM2VFOFprT2xNYjBzbmswZmdJV3dremRIS0I4MDNzRjBnbEttWEhfOWZBbmFrRnNHWDFVLVFoM0VkZkxkaW4tMmZlSFJLei1heTFHMU0wSmxQVVRZN0cwaXQzcDBtZkdwTUFma0RXU2dwLXRnLTBkNGN3Vm1fV3hEdlM1dWZ1SEsw?oc=5</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1</v>
+      </c>
+      <c r="N65" t="n">
+        <v>-17.781</v>
+      </c>
+      <c r="O65" t="n">
+        <v>-63.139</v>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Santa Cruz, Santa Cruz</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>Santa Cruz de la Sierra</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>noticia:n32ahi</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>noticia</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-10-22 05:30</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>1792661402000</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>FmBolivia</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>meteorológica</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>verde</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Senamhi anuncia el inicio de la temporada de lluvias en Bolivia y prevé granizadas como la de La Paz - FmBolivia</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
           <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQNmVPRnVBMGQzdEI5SUp3Z3ZGVExwTUR6TWNadGQ1QldUS1o2QVFvUl9sVEZKMDVyQVVrS25rU1RSQlJKWXk1YzE0NUhidjhpcmFaSlhZUDZvcE9XcG1KTFNTYmowUU1CSFJNOVR2UHNmMk1iT3N0RVBteHkzZkgyRFROYk1pdkpxVHZya3N2X2FVLVQxbURFVVZlb1NzRjZzTE95TXFVUXFJNkVZakQ2bUhVQzB0SXk3TVhXUTJXa0dycTE1MWVQRFpDX3lDSWFqUGwzU2NtNA?oc=5</t>
         </is>
       </c>
-      <c r="L65" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" t="n">
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
         <v>-16.169</v>
       </c>
-      <c r="O65" t="n">
+      <c r="O66" t="n">
         <v>-68.09</v>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>La Paz, La Paz</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>nombre de municipio en el titular</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr">
+      <c r="R66" t="inlineStr">
         <is>
           <t>La Paz</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="S66" t="inlineStr">
         <is>
           <t>Nuestra Señora de La Paz</t>
         </is>
@@ -9322,7 +9481,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-10-25 16:19</t>
+          <t>2026-10-25 16:56</t>
         </is>
       </c>
     </row>
@@ -9345,7 +9504,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4">
@@ -9355,7 +9514,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5">
@@ -9402,7 +9561,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sala de Situación Bolivia – CCES. Base de eventos de amenazas (datos preliminares de fuentes abiertas). Consulta: 2026-10-25 16:19.</t>
+          <t>Sala de Situación Bolivia – CCES. Base de eventos de amenazas (datos preliminares de fuentes abiertas). Consulta: 2026-10-25 16:56.</t>
         </is>
       </c>
     </row>

--- a/docs/datos/datos_bolivia.xlsx
+++ b/docs/datos/datos_bolivia.xlsx
@@ -9481,7 +9481,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-10-25 16:56</t>
+          <t>2026-10-25 17:23</t>
         </is>
       </c>
     </row>
@@ -9561,7 +9561,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sala de Situación Bolivia – CCES. Base de eventos de amenazas (datos preliminares de fuentes abiertas). Consulta: 2026-10-25 16:56.</t>
+          <t>Sala de Situación Bolivia – CCES. Base de eventos de amenazas (datos preliminares de fuentes abiertas). Consulta: 2026-10-25 17:23.</t>
         </is>
       </c>
     </row>

--- a/docs/datos/datos_bolivia.xlsx
+++ b/docs/datos/datos_bolivia.xlsx
@@ -9481,7 +9481,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-10-25 17:23</t>
+          <t>2026-10-25 17:29</t>
         </is>
       </c>
     </row>
@@ -9561,7 +9561,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sala de Situación Bolivia – CCES. Base de eventos de amenazas (datos preliminares de fuentes abiertas). Consulta: 2026-10-25 17:23.</t>
+          <t>Sala de Situación Bolivia – CCES. Base de eventos de amenazas (datos preliminares de fuentes abiertas). Consulta: 2026-10-25 17:29.</t>
         </is>
       </c>
     </row>

--- a/docs/datos/datos_bolivia.xlsx
+++ b/docs/datos/datos_bolivia.xlsx
@@ -9481,7 +9481,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-10-25 17:29</t>
+          <t>2026-10-25 17:40</t>
         </is>
       </c>
     </row>
@@ -9561,7 +9561,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sala de Situación Bolivia – CCES. Base de eventos de amenazas (datos preliminares de fuentes abiertas). Consulta: 2026-10-25 17:29.</t>
+          <t>Sala de Situación Bolivia – CCES. Base de eventos de amenazas (datos preliminares de fuentes abiertas). Consulta: 2026-10-25 17:40.</t>
         </is>
       </c>
     </row>

--- a/docs/datos/datos_bolivia.xlsx
+++ b/docs/datos/datos_bolivia.xlsx
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNN0traUpaNVFIOU0zeFZod2tkQWhZZFQ1Q3dxc2xCVy1RNnJIX2xQbTlhT3RVckdNdHV4ZFVLQThvd2UzNDlCa3VmaWprTnU3R05rVkVkdEVCU1hFMlFsLTJ6REIySnl5VFJfdV9pQmVDTzlqUWFUSi1GQ0JvTVJVQ2dpeVBydnpMV0dYOThENTFRUDgxVFloSVg3bnN4dGo2aEVCbDFKaUgydWNISnJVUTNB?oc=5 | https://news.google.com/rss/articles/CBMimAFBVV95cUxQbHdpcUF6dXpjaW1TT1ZmdGJtUUVLMTNMRTVqVkFUdkNsZlRvenVkckFUWmI4NDFmc2ZHd2RVcWRSSE5YRVpOTUlESGw2V3JONXpwS0RISGNZd01SejNuMkY4NzFYYXp4aWo2RE9VMkFYUkVwZ3JRRmM5MWlRSjlBWk16azdkQ3FjdEtkaWc5NERkTzk2SllVOQ?oc=5 | https://news.google.com/rss/articles/CBMixgFBVV95cUxQLXlqSFdvWUVhQUNadnpkdE5lUTZQS0lobThzUTZWbDNJTE94alVhaDBaYU9Fd09SSGt3UlR3Y0dfZlNIcml1ZktnWjctNk1Na3V4S0tINFNkMXM0OHBoV2lCTTBiYXlPUTA3T2ZkeXE2RElYWjhfVHd3Nng1Z0E4alBmOFI5NDFwX09kazZlSWl2OVR2ZVR6MDhvSHFnSmJKbTFXSEFDNFFYcWVDNGtYWEQ0bDhJel9CaEpEZWZ4SWN0TE9Ya0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNN0traUpaNVFIOU0zeFZod2tkQWhZZFQ1Q3dxc2xCVy1RNnJIX2xQbTlhT3RVckdNdHV4ZFVLQThvd2UzNDlCa3VmaWprTnU3R05rVkVkdEVCU1hFMlFsLTJ6REIySnl5VFJfdV9pQmVDTzlqUWFUSi1GQ0JvTVJVQ2dpeVBydnpMV0dYOThENTFRUDgxVFloSVg3bnN4dGo2aEVCbDFKaUgydWNISnJVUTNB?oc=5 | https://news.google.com/rss/articles/CBMimAFBVV95cUxQbHdpcUF6dXpjaW1TT1ZmdGJtUUVLMTNMRTVqVkFUdkNsZlRvenVkckFUWmI4NDFmc2ZHd2RVcWRSSE5YRVpOTUlESGw2V3JONXpwS0RISGNZd01SejNuMkY4NzFYYXp4aWo2RE9VMkFYUkVwZ3JRRmM5MWlRSjlBWk16azdkQ3FjdEtkaWc5NERkTzk2SllVOQ?oc=5 | https://news.google.com/rss/articles/CBMitwFBVV95cUxORzdWNjUxSGtVYnpWMlZNR1J3cmhRNngzNG1LS2VHQ19PMmFRTDNLd1RoelhMUG8yYU15STdsUk84cFF6WDF5elhUMGpFVU1NVnpqTGlEbXZsd0lWazNBQUZjV0Z3YkhpdFVqMFI1d1liWHROejBzcUxqYkhIaG00cUFaQ1FfTm5feGV6N1EyUTNZMzFlV3N3RmNZTGIxaDQ3UHFjOTNCMGNESmtCb2RVQm0xd3NRb1E?oc=5</t>
         </is>
       </c>
     </row>
@@ -3760,7 +3760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S66"/>
+  <dimension ref="A1:S67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4280,7 +4280,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>noticia:oww2zc</t>
+          <t>noticia:1bn18rv</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4290,15 +4290,15 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-25 12:08</t>
+          <t>2026-10-25 12:32</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1792944531000</v>
+        <v>1792945968000</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>EL DÍA - Noticias de Bolivia para el mundo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4316,13 +4316,13 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Cierran la carretera a Camiri: dos cisternas chocan y provocan un voraz incendio - Red Uno</t>
+          <t>Reportan el incendio de dos camiones cisterna en la carretera a Camiri - EL DÍA - Noticias de Bolivia para el mundo</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQLXlqSFdvWUVhQUNadnpkdE5lUTZQS0lobThzUTZWbDNJTE94alVhaDBaYU9Fd09SSGt3UlR3Y0dfZlNIcml1ZktnWjctNk1Na3V4S0tINFNkMXM0OHBoV2lCTTBiYXlPUTA3T2ZkeXE2RElYWjhfVHd3Nng1Z0E4alBmOFI5NDFwX09kazZlSWl2OVR2ZVR6MDhvSHFnSmJKbTFXSEFDNFFYcWVDNGtYWEQ0bDhJel9CaEpEZWZ4SWN0TE9Ya0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxORzdWNjUxSGtVYnpWMlZNR1J3cmhRNngzNG1LS2VHQ19PMmFRTDNLd1RoelhMUG8yYU15STdsUk84cFF6WDF5elhUMGpFVU1NVnpqTGlEbXZsd0lWazNBQUZjV0Z3YkhpdFVqMFI1d1liWHROejBzcUxqYkhIaG00cUFaQ1FfTm5feGV6N1EyUTNZMzFlV3N3RmNZTGIxaDQ3UHFjOTNCMGNESmtCb2RVQm0xd3NRb1E?oc=5</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -4361,7 +4361,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>noticia:1a4hhsd</t>
+          <t>noticia:oww2zc</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4371,15 +4371,15 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-25 11:56</t>
+          <t>2026-10-25 12:08</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1792943794000</v>
+        <v>1792944531000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Opinión Bolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -4397,13 +4397,13 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Reportan el incendio de dos camiones cisterna en la carretera a Camiri - Opinión Bolivia</t>
+          <t>Cierran la carretera a Camiri: dos cisternas chocan y provocan un voraz incendio - Red Uno</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNUTdxSzBJVTZnajZQUXhyTVhwMlpvU0tyZGVBYnFwV2kyZWthenNRT1FDRVJFZnk4ZndGTFQ0cnFXZmZ1WHZaMFhUbWo0SWkzcjcxbjJwU3pKUXR4WEVZLVlRNFpxOUVMY2NNNUZsbmJSMk9xZG1sTklEdEtGSXJyUUp5b0R2dVpYcHJLdTRNRlRjcWpNNXg4c0Z4UWwteFc2dDRqVmpnQnFfQXgwN0twTzl4ZWhYdUtYWGfSAboBQVVfeXFMTVE3cUswSVU2Z2o2UFF4ck1YcDJab1NLcmRlQWJxcFdpMmVrYXpzUU9RQ0VSRWZ5OGZ3RkxUNHJxV2ZmdVh2WjBYVG1qNElpM3I3MW4ycFN6SlF0eFhFWS1ZUTRacTlFTGNjTTVGbG5iUjJPcWRtbE5JRHRLRklyclFKeW9EdnVaWHByS3U0TUZUY3FqTTV4OHNGeFFsLXhXNnQ0alZqZ0JxX0F4MDdLcE85eGVoWHVLWFhn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQLXlqSFdvWUVhQUNadnpkdE5lUTZQS0lobThzUTZWbDNJTE94alVhaDBaYU9Fd09SSGt3UlR3Y0dfZlNIcml1ZktnWjctNk1Na3V4S0tINFNkMXM0OHBoV2lCTTBiYXlPUTA3T2ZkeXE2RElYWjhfVHd3Nng1Z0E4alBmOFI5NDFwX09kazZlSWl2OVR2ZVR6MDhvSHFnSmJKbTFXSEFDNFFYcWVDNGtYWEQ0bDhJel9CaEpEZWZ4SWN0TE9Ya0E?oc=5</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -4442,7 +4442,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>noticia:1at00ey</t>
+          <t>noticia:1a4hhsd</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4452,15 +4452,15 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-25 11:19</t>
+          <t>2026-10-25 11:56</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1792941547000</v>
+        <v>1792943794000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>Opinión Bolivia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -4478,13 +4478,13 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Dos cisternas chocan y provocan voraz incendio en la ruta a Camiri - Red Uno</t>
+          <t>Reportan el incendio de dos camiones cisterna en la carretera a Camiri - Opinión Bolivia</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPTTF0OUdVS1c1a0lZWmk3bGxHdDJIalpWZTRyQTY3eWE2a2dWOHlsaldKZXpSLWN5c3BkUWdBRkJuSzhHdWl2ZjgwTFFFYnd0aTAxZ3dJU0hCekNZNm9aTTJSZUNfQjVIM3FrUUJ4NXAwa3paZ3BEek9xTVZNQWdnN01xRHloV1ZXZHV6N0JpUWo3RE9DMlFGdkNnWkloTjVVY3RBR1RSRUJJWFVtby1fMWFMNTdLZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNUTdxSzBJVTZnajZQUXhyTVhwMlpvU0tyZGVBYnFwV2kyZWthenNRT1FDRVJFZnk4ZndGTFQ0cnFXZmZ1WHZaMFhUbWo0SWkzcjcxbjJwU3pKUXR4WEVZLVlRNFpxOUVMY2NNNUZsbmJSMk9xZG1sTklEdEtGSXJyUUp5b0R2dVpYcHJLdTRNRlRjcWpNNXg4c0Z4UWwteFc2dDRqVmpnQnFfQXgwN0twTzl4ZWhYdUtYWGfSAboBQVVfeXFMTVE3cUswSVU2Z2o2UFF4ck1YcDJab1NLcmRlQWJxcFdpMmVrYXpzUU9RQ0VSRWZ5OGZ3RkxUNHJxV2ZmdVh2WjBYVG1qNElpM3I3MW4ycFN6SlF0eFhFWS1ZUTRacTlFTGNjTTVGbG5iUjJPcWRtbE5JRHRLRklyclFKeW9EdnVaWHByS3U0TUZUY3FqTTV4OHNGeFFsLXhXNnQ0alZqZ0JxX0F4MDdLcE85eGVoWHVLWFhn?oc=5</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -4523,7 +4523,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>noticia:1uf38hl</t>
+          <t>noticia:1at00ey</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4533,11 +4533,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-25 10:59</t>
+          <t>2026-10-25 11:19</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1792940350000</v>
+        <v>1792941547000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -4559,13 +4559,13 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>¡Cisterna con combustible en llamas! Reportan impresionante incendio en la carretera a Camiri - Red Uno</t>
+          <t>Dos cisternas chocan y provocan voraz incendio en la ruta a Camiri - Red Uno</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxORUhqeWpKY1FHRWoxaHN0UXFzS3dpeHh6N0NwLUJOZTlZcDVoNHN0VnI0by1qMWtZZEkxVmtUNjdNTFhjaEFQU2IyMlNwZW95WFBzbFJPVVB6TjJtdjNENk1LWVlsMUxUUzBNVzkxRk1HZ3lQU0s2M1lRVlRuaXlkMmJrd3AyTGpIdXItNkhlU3dhTzBRME56Rm1DSlZCYjNxSnNTbTFqNWRoUkdraHhlREhuYldqeFk2N3poWEx2M08?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPTTF0OUdVS1c1a0lZWmk3bGxHdDJIalpWZTRyQTY3eWE2a2dWOHlsaldKZXpSLWN5c3BkUWdBRkJuSzhHdWl2ZjgwTFFFYnd0aTAxZ3dJU0hCekNZNm9aTTJSZUNfQjVIM3FrUUJ4NXAwa3paZ3BEek9xTVZNQWdnN01xRHloV1ZXZHV6N0JpUWo3RE9DMlFGdkNnWkloTjVVY3RBR1RSRUJJWFVtby1fMWFMNTdLZw?oc=5</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -4604,7 +4604,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>noticia:1sg8pi0</t>
+          <t>noticia:1uf38hl</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4614,11 +4614,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-25 09:59</t>
+          <t>2026-10-25 10:59</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1792936752000</v>
+        <v>1792940350000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -4640,13 +4640,13 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Bus de agrupación musical sufre accidente rumbo al trópico de Cochabamba | VIDEO - Red Uno</t>
+          <t>¡Cisterna con combustible en llamas! Reportan impresionante incendio en la carretera a Camiri - Red Uno</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOVDVzVTJNM2JuQ25sMThEaVZNOUNRd3FGT3RhVnFrZXZ2NDQ1YlluTVdhbVNUQnA1MGNESHRSWVUzbC1kRVh3OTR0emtlTG91cmRWeFJ5dk5zb3p2WFRyMEJUV3FNRnY1WHhRUU9WLTlJcmNyNXJZZFdoM0JoZjNpa3hjUXhMM0xrUDJab2VadkM5RWZYQ3lWZTVDdzg1akxJT2lxcDVNNzI0NG1hejdfdkUyTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxORUhqeWpKY1FHRWoxaHN0UXFzS3dpeHh6N0NwLUJOZTlZcDVoNHN0VnI0by1qMWtZZEkxVmtUNjdNTFhjaEFQU2IyMlNwZW95WFBzbFJPVVB6TjJtdjNENk1LWVlsMUxUUzBNVzkxRk1HZ3lQU0s2M1lRVlRuaXlkMmJrd3AyTGpIdXItNkhlU3dhTzBRME56Rm1DSlZCYjNxSnNTbTFqNWRoUkdraHhlREhuYldqeFk2N3poWEx2M08?oc=5</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -4656,14 +4656,14 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-17.39</v>
+        <v>-20.05</v>
       </c>
       <c r="O11" t="n">
-        <v>-66.16</v>
+        <v>-63.486</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Cochabamba, Cochabamba</t>
+          <t>Camiri, Santa Cruz</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -4673,19 +4673,19 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Camiri</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>noticia:167wlhz</t>
+          <t>noticia:1sg8pi0</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4695,11 +4695,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-25 07:53</t>
+          <t>2026-10-25 09:59</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1792929231000</v>
+        <v>1792936752000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -4721,13 +4721,13 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>¡A sacar el paraguas! Santa cruz amanece con lluvia, frío y complicaciones en el tránsito vehicular - Red Uno</t>
+          <t>Bus de agrupación musical sufre accidente rumbo al trópico de Cochabamba | VIDEO - Red Uno</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOY1ZpYktLR3pUQXotUndVR3puUzVHbW1YTzNyUmJvUHB4Q2JmelRvOEdaRldOUm1xLVJnbGR5VWcxTjNEM3ZUYktCUWtVM0hKSjFuRGdpX0JxN0M5MVZBSG1aVURyVWktdmxwbUtRT19ydU5LdzNTZ2Zpb2ozdHlMUUdTVlAyVk4xODBnV0hyTXdVVndyNzV3VC1KMzFnV3lpcFFXSk9MdDZOTWlWakNwT1FnNDh6QVdjazVYZDVVMkdaLU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOVDVzVTJNM2JuQ25sMThEaVZNOUNRd3FGT3RhVnFrZXZ2NDQ1YlluTVdhbVNUQnA1MGNESHRSWVUzbC1kRVh3OTR0emtlTG91cmRWeFJ5dk5zb3p2WFRyMEJUV3FNRnY1WHhRUU9WLTlJcmNyNXJZZFdoM0JoZjNpa3hjUXhMM0xrUDJab2VadkM5RWZYQ3lWZTVDdzg1akxJT2lxcDVNNzI0NG1hejdfdkUyTQ?oc=5</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -4737,14 +4737,14 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-17.781</v>
+        <v>-17.39</v>
       </c>
       <c r="O12" t="n">
-        <v>-63.139</v>
+        <v>-66.16</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Santa Cruz, Santa Cruz</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -4754,19 +4754,19 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Cochabamba</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>noticia:bzr7eh</t>
+          <t>noticia:167wlhz</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4776,39 +4776,39 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-25 07:09</t>
+          <t>2026-10-25 07:53</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1792926572000</v>
+        <v>1792929231000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>hidrológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Alerta naranja por riesgo de desbordes de ríos - El Diario - Bolivia</t>
+          <t>¡A sacar el paraguas! Santa cruz amanece con lluvia, frío y complicaciones en el tránsito vehicular - Red Uno</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNNGZKSDVaZkowWUFGSEUyTWR3d3dsc04waFBLLWUtcVpiTDYzbmNtYTN1RkFLbjAwN3dxT0xZc3pqc3REUXduZVltQ2Fud1BZLTh1bTNiTEJueVUwV0dERS1iUXZqMHd0UnFrQ3E2SFAzbm5lQ1I4U29MaHJFbWFvdVRTeFY4Wl9rSmc3RkpaQ2xwX0oz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOY1ZpYktLR3pUQXotUndVR3puUzVHbW1YTzNyUmJvUHB4Q2JmelRvOEdaRldOUm1xLVJnbGR5VWcxTjNEM3ZUYktCUWtVM0hKSjFuRGdpX0JxN0M5MVZBSG1aVURyVWktdmxwbUtRT19ydU5LdzNTZ2Zpb2ozdHlMUUdTVlAyVk4xODBnV0hyTXdVVndyNzV3VC1KMzFnV3lpcFFXSk9MdDZOTWlWakNwT1FnNDh6QVdjazVYZDVVMkdaLU0?oc=5</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -4817,21 +4817,37 @@
       <c r="M13" t="n">
         <v>0</v>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>-17.781</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-63.139</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Santa Cruz, Santa Cruz</t>
+        </is>
+      </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Santa Cruz de la Sierra</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>noticia:1fo4ig4</t>
+          <t>noticia:bzr7eh</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4841,43 +4857,43 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-25 01:08</t>
+          <t>2026-10-25 07:09</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1792904880000</v>
+        <v>1792926572000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>diarioelpueblo.com.pe</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>hidrológica</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>roja</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
+          <t>Alerta naranja por riesgo de desbordes de ríos - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQcmFrT3dwcEs0X3U2NWxnOGJwNnI2WHdWTGZYbzEyNnJzUWhkbU9TRWhfSlB5UkMwX2gyMmxYUmVNWmxNOVR6V0twRHpFMTVIYjBKbHQ2TXN2d2w5dkFpcWJCcUJMZldaX01sNWtQV2ZJOGpRVzR3NDVIU0pJc1BNVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNNGZKSDVaZkowWUFGSEUyTWR3d3dsc04waFBLLWUtcVpiTDYzbmNtYTN1RkFLbjAwN3dxT0xZc3pqc3REUXduZVltQ2Fud1BZLTh1bTNiTEJueVUwV0dERS1iUXZqMHd0UnFrQ3E2SFAzbm5lQ1I4U29MaHJFbWFvdVRTeFY4Wl9rSmc3RkpaQ2xwX0oz?oc=5</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -4896,7 +4912,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>noticia:r1uot6</t>
+          <t>noticia:1fo4ig4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4906,15 +4922,15 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-24 20:00</t>
+          <t>2026-10-25 01:08</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1792886439000</v>
+        <v>1792904880000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
+          <t>diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -4923,61 +4939,45 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>roja</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>vuelco deja heridos en ruta Oruro – Huanuni - La Patria Bolivia</t>
+          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNNDQtMG1KT1lLWW5nem9Jbm5JWDZKNlRWZmFmRlBxWDlDeXlSWnJ5d2NsTlpxa0JIS25oVWVZOC1majZVbWhOVDIxR0dLOFlzY2VpVzVoVk1mQnF3dXVwLUFZVHc1UjlXZzF5T05CY3U0ZldLVkw1VzBTek5zanpjQW1xalltWHNiaXI3dTNR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQcmFrT3dwcEs0X3U2NWxnOGJwNnI2WHdWTGZYbzEyNnJzUWhkbU9TRWhfSlB5UkMwX2gyMmxYUmVNWmxNOVR6V0twRHpFMTVIYjBKbHQ2TXN2d2w5dkFpcWJCcUJMZldaX01sNWtQV2ZJOGpRVzR3NDVIU0pJc1BNVg?oc=5</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>-17.97</v>
-      </c>
-      <c r="O15" t="n">
-        <v>-67.11</v>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Oruro, Oruro</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>Oruro</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>Oruro</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>noticia:1ytw450</t>
+          <t>noticia:r1uot6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4987,15 +4987,15 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-24 18:58</t>
+          <t>2026-10-24 20:00</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1792882686000</v>
+        <v>1792886439000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>diarioelpueblo.com.pe</t>
+          <t>La Patria Bolivia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -5004,45 +5004,61 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>roja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
+          <t>vuelco deja heridos en ruta Oruro – Huanuni - La Patria Bolivia</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNZ1U3bEVuaVdjVE1zSU9lOHJZTVRZLVZaemhldGNnT1JBWDJvbzdvM3paVVNhLUlyWHF2akNuSXJOLXdyTGRuejRlV1FuMjVkTjA3NmdRdmgtRWlUeTFBV1dEMzBvejBxaXZJdUZZWkRVTF9VLU5BcjFGZGFEQ09WWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNNDQtMG1KT1lLWW5nem9Jbm5JWDZKNlRWZmFmRlBxWDlDeXlSWnJ5d2NsTlpxa0JIS25oVWVZOC1majZVbWhOVDIxR0dLOFlzY2VpVzVoVk1mQnF3dXVwLUFZVHc1UjlXZzF5T05CY3U0ZldLVkw1VzBTek5zanpjQW1xalltWHNiaXI3dTNR?oc=5</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-17.97</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-67.11</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Oruro, Oruro</t>
+        </is>
+      </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>noticia:1wcb22g</t>
+          <t>noticia:1ytw450</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5052,43 +5068,43 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-24 17:47</t>
+          <t>2026-10-24 18:58</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1792878475000</v>
+        <v>1792882686000</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>El Mundo Bolivia</t>
+          <t>diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>hidrológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>roja</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Alerta naranja por ingreso de frente frío y desbordes de ríos en 6 departamentos - El Mundo Bolivia</t>
+          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPZW00RkxJSklTelNrS2hqczJDWHlwcENFX2lnSEUyTEFPaDFRQ2JvMUcyd3NfYjg0UE9ORGxHRzB4ZDh3U0hQQ1JSQlhsaUY4N3ByMUUxei1SaUZnNlp6T3hsLVdiMGhKaXhsV1FNSUNQMHlvQ19qdk56SEF0d2RXVFctS0VPT25kNGZCRDdvZ2dxU0VoUUJKU0ZBd0ZycFNEZFh0T3ZjOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNZ1U3bEVuaVdjVE1zSU9lOHJZTVRZLVZaemhldGNnT1JBWDJvbzdvM3paVVNhLUlyWHF2akNuSXJOLXdyTGRuejRlV1FuMjVkTjA3NmdRdmgtRWlUeTFBV1dEMzBvejBxaXZJdUZZWkRVTF9VLU5BcjFGZGFEQ09WWQ?oc=5</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -5107,7 +5123,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>noticia:1c1ju1f</t>
+          <t>noticia:1wcb22g</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5117,46 +5133,46 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-24 17:02</t>
+          <t>2026-10-24 17:47</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1792875752000</v>
+        <v>1792878475000</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>La Razón Digital Bolivia</t>
+          <t>El Mundo Bolivia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>hidrológica</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a los Yungas deja siete heridos - La Razón Digital Bolivia</t>
+          <t>Alerta naranja por ingreso de frente frío y desbordes de ríos en 6 departamentos - El Mundo Bolivia</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPTGQwaVBfdG1JdVRMUTN4LVVvN0ppc3dreDJVVllDR3RmX0xpMzB4b0pvVTNSV1B6T0ZEWTdEZkNsRUdSNzhLaC1CWHN5WktNWk1nRWpTdVZiYjI3TlJlX2xlVTI5MjlRU2hiY1gteml4YWVFbDNPSVRBZmtITlQzbmhaUXVmcThRa2xsQTJIOXZuNzlSdm12MEdyOEZHdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPZW00RkxJSklTelNrS2hqczJDWHlwcENFX2lnSEUyTEFPaDFRQ2JvMUcyd3NfYjg0UE9ORGxHRzB4ZDh3U0hQQ1JSQlhsaUY4N3ByMUUxei1SaUZnNlp6T3hsLVdiMGhKaXhsV1FNSUNQMHlvQ19qdk56SEF0d2RXVFctS0VPT25kNGZCRDdvZ2dxU0VoUUJKU0ZBd0ZycFNEZFh0T3ZjOA?oc=5</t>
         </is>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
@@ -5172,7 +5188,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>noticia:14iwzop</t>
+          <t>noticia:1c1ju1f</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5182,15 +5198,15 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-24 13:40</t>
+          <t>2026-10-24 17:02</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1792863623000</v>
+        <v>1792875752000</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>EL DÍA - Noticias de Bolivia para el mundo</t>
+          <t>La Razón Digital Bolivia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -5208,13 +5224,13 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a Mayaya deja siete heridos de la agrupación Los Chicos Fieles - EL DÍA - Noticias de Bolivia para el mundo</t>
+          <t>Accidente en la carretera a los Yungas deja siete heridos - La Razón Digital Bolivia</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPeGd3VWpCWXJ0YTJIeDJLcktzWG1jdUh0TjFXb01wSTkxbHNXZU94VWNDMkxnTjlJZVdpbkprMEY2NE80RXYyUWxUQXVnbl9lUXR2b28zTEh6cTJLVEQ4TUNja2kzRlhadVBFZFVwV1U2TlhseXZMZ20zZTZiUFpWRjdCOWNBMHU5XzdMV3JqQjV4TEE3bHRMOXR6Nm55eHZUNnFHSDdVRk8zVkY4RkVsUUtUN0JYdkREWGZncmJ3ZWc2T1BuUm1ZLTlfcHVabFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPTGQwaVBfdG1JdVRMUTN4LVVvN0ppc3dreDJVVllDR3RmX0xpMzB4b0pvVTNSV1B6T0ZEWTdEZkNsRUdSNzhLaC1CWHN5WktNWk1nRWpTdVZiYjI3TlJlX2xlVTI5MjlRU2hiY1gteml4YWVFbDNPSVRBZmtITlQzbmhaUXVmcThRa2xsQTJIOXZuNzlSdm12MEdyOEZHdw?oc=5</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -5237,7 +5253,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>noticia:1ukcn97</t>
+          <t>noticia:14iwzop</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5247,15 +5263,15 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-24 13:26</t>
+          <t>2026-10-24 13:40</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1792862794000</v>
+        <v>1792863623000</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>El Deber</t>
+          <t>EL DÍA - Noticias de Bolivia para el mundo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -5273,20 +5289,20 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Esta es la lista preliminar de los heridos en el accidente del grupo 'Los chicos fieles', el conductor está grave - El Deber</t>
+          <t>Accidente en la carretera a Mayaya deja siete heridos de la agrupación Los Chicos Fieles - EL DÍA - Noticias de Bolivia para el mundo</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOczZKbFd1QzRpak92LXpPWXZXQXJObnBQTG9qRFBlUUV5dThMWXhzckFFUHAyb2thU1JwRmJDSEZfaEdTUXh1bjZvQWpYMGhfUno3cWZ4MGpldEpoQXhzSlVzTm5LLW9OcjB2MWRsdHQ2UlI2SjEtZ085ZTR5Z3pEVmtBTF9lc29Kd0RhaTRUWkM4eGZJNWhBSXZqWmxuNW10dlQwYW9mdzItcWZWTkU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPeGd3VWpCWXJ0YTJIeDJLcktzWG1jdUh0TjFXb01wSTkxbHNXZU94VWNDMkxnTjlJZVdpbkprMEY2NE80RXYyUWxUQXVnbl9lUXR2b28zTEh6cTJLVEQ4TUNja2kzRlhadVBFZFVwV1U2TlhseXZMZ20zZTZiUFpWRjdCOWNBMHU5XzdMV3JqQjV4TEE3bHRMOXR6Nm55eHZUNnFHSDdVRk8zVkY4RkVsUUtUN0JYdkREWGZncmJ3ZWc2T1BuUm1ZLTlfcHVabFE?oc=5</t>
         </is>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
@@ -5302,7 +5318,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>noticia:2avehj</t>
+          <t>noticia:1ukcn97</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5312,20 +5328,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-24 12:53</t>
+          <t>2026-10-24 13:26</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1792860813000</v>
+        <v>1792862794000</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>El Deber</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>climatológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -5338,52 +5354,36 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Sequía en Cochabamba: más de un centenar de cabezas de ganado murieron en el cono sur - Red Uno</t>
+          <t>Esta es la lista preliminar de los heridos en el accidente del grupo 'Los chicos fieles', el conductor está grave - El Deber</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOOFQxc2Vzc0QwS19ydC13RkRPZnZQU3JkSTl5U3kzdUdMSldTcm5HVEhWRzZyN19CLUlwcUs4MW03Ui1obVBtdzQ3QWFQc1RKdzh3MXJ5QkpRS2pRNm50V1lVb09ScGJnaVVlemVfZlRsWjdObnRmR1FGMnlMMHAyc2pMandndy10T2twcWx6OFh4UHdvbVlFbllwME9WQ2pQVjNTQzBxeTg5YnF3bDREeHVDYXpObFFIaTZZQWtYUE12cGQ1ZGRhT0syNjVhZWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOczZKbFd1QzRpak92LXpPWXZXQXJObnBQTG9qRFBlUUV5dThMWXhzckFFUHAyb2thU1JwRmJDSEZfaEdTUXh1bjZvQWpYMGhfUno3cWZ4MGpldEpoQXhzSlVzTm5LLW9OcjB2MWRsdHQ2UlI2SjEtZ085ZTR5Z3pEVmtBTF9lc29Kd0RhaTRUWkM4eGZJNWhBSXZqWmxuNW10dlQwYW9mdzItcWZWTkU0?oc=5</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>-17.39</v>
-      </c>
-      <c r="O21" t="n">
-        <v>-66.16</v>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Cochabamba, Cochabamba</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>noticia:1ksmg5u</t>
+          <t>noticia:2avehj</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5393,20 +5393,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-24 11:43</t>
+          <t>2026-10-24 12:53</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1792856591000</v>
+        <v>1792860813000</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>climatológica</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5419,36 +5419,52 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Embarrancamiento deja heridos a integrantes de Los Chicos Fieles - La Patria Bolivia</t>
+          <t>Sequía en Cochabamba: más de un centenar de cabezas de ganado murieron en el cono sur - Red Uno</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNeEFrOEtOMHZxMW42REFPU0x1MG5oQjlBMkJucWRLZ292alBXekJKeURBN3NLTVVadWI0OWF4UGtSVXBzTE01eWFSU1kyMUhNZ04zMWNMaUxnMDBBZ0EwTktXbjlaVTBUUmNqa3AwY19KNTU2LWh5LW9IVElVdTdnaHFPanJPd2FqMUxzaUhXZmVpYU1saGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOOFQxc2Vzc0QwS19ydC13RkRPZnZQU3JkSTl5U3kzdUdMSldTcm5HVEhWRzZyN19CLUlwcUs4MW03Ui1obVBtdzQ3QWFQc1RKdzh3MXJ5QkpRS2pRNm50V1lVb09ScGJnaVVlemVfZlRsWjdObnRmR1FGMnlMMHAyc2pMandndy10T2twcWx6OFh4UHdvbVlFbllwME9WQ2pQVjNTQzBxeTg5YnF3bDREeHVDYXpObFFIaTZZQWtYUE12cGQ1ZGRhT0syNjVhZWs?oc=5</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-17.39</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-66.16</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Cochabamba, Cochabamba</t>
+        </is>
+      </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>noticia:mlyqgd</t>
+          <t>noticia:1ksmg5u</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5458,15 +5474,15 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-24 11:30</t>
+          <t>2026-10-24 11:43</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1792855818000</v>
+        <v>1792856591000</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Opinión Bolivia</t>
+          <t>La Patria Bolivia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -5484,20 +5500,20 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a Mayaya deja siete heridos de la agrupación Los Chicos Fieles - Opinión Bolivia</t>
+          <t>Embarrancamiento deja heridos a integrantes de Los Chicos Fieles - La Patria Bolivia</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYjNxaHg3YllRRTJYdFd1clAtUlROSGlFNVg5eUVZUGJoOEZ4MWM5QU5WQm1YTDc4NXc3SjhWMUw0TkZfSHlMLUQ1bmpTME1Kb1JaM0ExamFHYTd3VlU4MXRWdTZ1bzh1SGYtbGE1a3dBaG93bjg1OGc0S0JfRE43c3dVMVltN0dQQzNhQUNhM0FjVUNRUDRSamlJYlk2dEJpUTBuY2hBcTFucTVRN0ZtYnc5bzdmTV9LQm1uVUxaZS1tUE9IejhBVDRCdU_SAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNeEFrOEtOMHZxMW42REFPU0x1MG5oQjlBMkJucWRLZ292alBXekJKeURBN3NLTVVadWI0OWF4UGtSVXBzTE01eWFSU1kyMUhNZ04zMWNMaUxnMDBBZ0EwTktXbjlaVTBUUmNqa3AwY19KNTU2LWh5LW9IVElVdTdnaHFPanJPd2FqMUxzaUhXZmVpYU1saGc?oc=5</t>
         </is>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
@@ -5513,7 +5529,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>noticia:irf4jl</t>
+          <t>noticia:mlyqgd</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5555,7 +5571,7 @@
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNMXlMNXFWSWhhWWNDRFFKMncwS2JGWm0tWlJCd2x2RjZhdFhEQ0lBcVlFSS1WRVYxMEVJTWRHcTY3M0stdWhGdnVPRU13X2MwSVRWX25xVUQxa0R6Z1pqQ2dfY0VjUmw2aXFoWFNVNk15N2dBOENZLWlGSWJfMW0zejVoZ3ZwVHVQV1MzbzlnUlpRcWIxMHZxdkItZTc0QmMyRnBmSVRtVnZ5Y3gtdVpYNXFwcGdadGVCU3dRZ3EwOTdiWHU4OXJRdEFoNi1HcnA1U0HSAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYjNxaHg3YllRRTJYdFd1clAtUlROSGlFNVg5eUVZUGJoOEZ4MWM5QU5WQm1YTDc4NXc3SjhWMUw0TkZfSHlMLUQ1bmpTME1Kb1JaM0ExamFHYTd3VlU4MXRWdTZ1bzh1SGYtbGE1a3dBaG93bjg1OGc0S0JfRE43c3dVMVltN0dQQzNhQUNhM0FjVUNRUDRSamlJYlk2dEJpUTBuY2hBcTFucTVRN0ZtYnc5bzdmTV9LQm1uVUxaZS1tUE9IejhBVDRCdU_SAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -5578,7 +5594,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>noticia:1g006zh</t>
+          <t>noticia:irf4jl</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5588,15 +5604,15 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-24 11:25</t>
+          <t>2026-10-24 11:30</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1792855522000</v>
+        <v>1792855818000</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>El Potosí</t>
+          <t>Opinión Bolivia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5614,13 +5630,13 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a Mayaya deja siete heridos del grupo Los Chicos Fieles - El Potosí</t>
+          <t>Accidente en la carretera a Mayaya deja siete heridos de la agrupación Los Chicos Fieles - Opinión Bolivia</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTC10eC1qSm1WRlY2YzA3VEJqOG1LUkx6bE9PdFYwTFBZMGFjU0RMYXliRkhXcTJHRlVzb0Y4QUU0WWJDQ1plS2NZamZ1YmFadE5qY3g4UE5aYVAwamtCUUNZaDB2YWJTdWRKS3R4a0hHUjVobUl0Y1dYZ2JPczAwak5kN1hjUEwwM1NtUDVWbnAzWTdnRng3RjFValFVVlZPdVZnWFlUODhPOE5aMTROQzVKVjVRS2VoaTlaQnBiUGRTNFk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNMXlMNXFWSWhhWWNDRFFKMncwS2JGWm0tWlJCd2x2RjZhdFhEQ0lBcVlFSS1WRVYxMEVJTWRHcTY3M0stdWhGdnVPRU13X2MwSVRWX25xVUQxa0R6Z1pqQ2dfY0VjUmw2aXFoWFNVNk15N2dBOENZLWlGSWJfMW0zejVoZ3ZwVHVQV1MzbzlnUlpRcWIxMHZxdkItZTc0QmMyRnBmSVRtVnZ5Y3gtdVpYNXFwcGdadGVCU3dRZ3EwOTdiWHU4OXJRdEFoNi1HcnA1U0HSAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -5629,60 +5645,44 @@
       <c r="M25" t="n">
         <v>7</v>
       </c>
-      <c r="N25" t="n">
-        <v>-19.58</v>
-      </c>
-      <c r="O25" t="n">
-        <v>-65.75</v>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Potosí, Potosí</t>
-        </is>
-      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>clima:Potosí:2026-10-24:viento:1</t>
+          <t>noticia:1g006zh</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-24 10:55</t>
+          <t>2026-10-24 11:25</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1792853727284</v>
+        <v>1792855522000</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>El Potosí</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5695,24 +5695,20 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Potosí 2026-10-24: 60.5 km/h de ráfagas pronosticadas</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
-        </is>
-      </c>
+          <t>Accidente en la carretera a Mayaya deja siete heridos del grupo Los Chicos Fieles - El Potosí</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTC10eC1qSm1WRlY2YzA3VEJqOG1LUkx6bE9PdFYwTFBZMGFjU0RMYXliRkhXcTJHRlVzb0Y4QUU0WWJDQ1plS2NZamZ1YmFadE5qY3g4UE5aYVAwamtCUUNZaDB2YWJTdWRKS3R4a0hHUjVobUl0Y1dYZ2JPczAwak5kN1hjUEwwM1NtUDVWbnAzWTdnRng3RjFValFVVlZPdVZnWFlUODhPOE5aMTROQzVKVjVRS2VoaTlaQnBiUGRTNFk?oc=5</t>
         </is>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N26" t="n">
         <v>-19.58</v>
@@ -5722,12 +5718,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Potosí, Potosí</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>capital (pronóstico puntual)</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -5744,25 +5740,25 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>noticia:1ax0bpy</t>
+          <t>clima:Potosí:2026-10-24:viento:1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-10-24 10:32</t>
+          <t>2026-10-24 10:55</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1792852364000</v>
+        <v>1792853727284</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Que Pasa Salta</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5771,22 +5767,26 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Creció el Bermejo tras la tormenta: así está el puerto de chalanas en este momento - Que Pasa Salta</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
+          <t>Potosí 2026-10-24: 60.5 km/h de ráfagas pronosticadas</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVld9IBfkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVldw?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -5796,59 +5796,59 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>-22.721</v>
+        <v>-19.58</v>
       </c>
       <c r="O27" t="n">
-        <v>-64.32599999999999</v>
+        <v>-65.75</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bermejo, Tarija</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
+          <t>capital (pronóstico puntual)</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Tarija</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>Bermejo</t>
+          <t>Potosí</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>gdacs:WF1033142:0</t>
+          <t>noticia:1ax0bpy</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>gdacs</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-10-24 07:06</t>
+          <t>2026-10-24 10:32</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1792839995000</v>
+        <v>1792852364000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>GDACS</t>
+          <t>Que Pasa Salta</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5861,17 +5861,13 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Green forest fire notification in Bolivia</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>On 21/10/2026, a forest fire started in Bolivia, until 24/10/2026.</t>
-        </is>
-      </c>
+          <t>Creció el Bermejo tras la tormenta: así está el puerto de chalanas en este momento - Que Pasa Salta</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>http://www.gdacs.org/report.aspx?eventtype=WF&amp;eventid=1033142</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVld9IBfkFVX3lxTE1FLXBhWWd1Y3JVekZENnJucm9GTXpRcG1Bemx4eVNUbzVaYjBlUXlhUm5UUHl1QTNKRmY5RnVfTHFKT2Z4UkZOSDFCUWN1aEtZSDI5ZS0yM1lNSmdyQlJlMzNhWUhUclo0Y2pqQjBrdjZnRzlBR3FDOEk1MUVldw?oc=5</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -5881,59 +5877,59 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>-13.06332</v>
+        <v>-22.721</v>
       </c>
       <c r="O28" t="n">
-        <v>-67.66426</v>
+        <v>-64.32599999999999</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Bermejo, Tarija</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>coordenada de la fuente</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Tarija</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>Ixiamas</t>
+          <t>Bermejo</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>noticia:1shhqva</t>
+          <t>gdacs:WF1033142:0</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>gdacs</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-10-24 06:33</t>
+          <t>2026-10-24 07:06</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1792838034000</v>
+        <v>1792839995000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>GDACS</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5946,13 +5942,17 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
+          <t>Green forest fire notification in Bolivia</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>On 21/10/2026, a forest fire started in Bolivia, until 24/10/2026.</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQYzB6N082XzFRRnVtcDVmUkYyWjcxUzV2Z3Frd1I0WDNXSnZtY0QzOU1PUkNLMktVT1Vra2FSeXhxZDRuOFZYZjFwejl6ejJTbWY2MGJuSGN3ZHdrdG5JUkgzSXBkbDYtaHlackY3OVFuNWdLcFNpdWNHRU9vNGdoVWx2ODFVdzJXYUxnM0tUcjJvZmc?oc=5</t>
+          <t>http://www.gdacs.org/report.aspx?eventtype=WF&amp;eventid=1033142</t>
         </is>
       </c>
       <c r="L29" t="n">
@@ -5962,82 +5962,78 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>-17.97</v>
+        <v>-13.06332</v>
       </c>
       <c r="O29" t="n">
-        <v>-67.11</v>
+        <v>-67.66426</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
+          <t>coordenada de la fuente</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Ixiamas</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>clima:Potosí:2026-10-25:viento:1</t>
+          <t>noticia:1shhqva</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-10-24 02:55</t>
+          <t>2026-10-24 06:33</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1792824927736</v>
+        <v>1792838034000</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Potosí 2026-10-25: 60.5 km/h de ráfagas pronosticadas</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
-        </is>
-      </c>
+          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQYzB6N082XzFRRnVtcDVmUkYyWjcxUzV2Z3Frd1I0WDNXSnZtY0QzOU1PUkNLMktVT1Vra2FSeXhxZDRuOFZYZjFwejl6ejJTbWY2MGJuSGN3ZHdrdG5JUkgzSXBkbDYtaHlackY3OVFuNWdLcFNpdWNHRU9vNGdoVWx2ODFVdzJXYUxnM0tUcjJvZmc?oc=5</t>
         </is>
       </c>
       <c r="L30" t="n">
@@ -6047,59 +6043,59 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>-19.58</v>
+        <v>-17.97</v>
       </c>
       <c r="O30" t="n">
-        <v>-65.75</v>
+        <v>-67.11</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Oruro, Oruro</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>capital (pronóstico puntual)</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Oruro</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Oruro</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>noticia:mz6q0s</t>
+          <t>clima:Potosí:2026-10-25:viento:1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-10-23 23:09</t>
+          <t>2026-10-24 02:55</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1792811349000</v>
+        <v>1792824927736</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6112,36 +6108,56 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Revelan lista preliminar de heridos tras accidente de Los Chicos Fieles - Red Uno</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
+          <t>Potosí 2026-10-25: 60.5 km/h de ráfagas pronosticadas</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPczBQcnE2SzFGMXc3b1lsTkNxVWRmS3Vnb01xOTV2WmVva3J2RVlteWpHZ3VJS2dNWGV5NW5FX3ZncnVKTEVDTGpBRndTU1FxeWxtaS1fb1FscGxXMWNXUE9zbHdob1AxVFl1eHB5OU1yUnNoOXJ6U21oVG9PVDA1ak1xQl9hUlB4V0RaQXJqZENGUm8zMUJEY3J0WW5ENE5ObWJLNmpWN0RkSmFJbnZUZGR5UFRPd3QyUFY4WQ?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
-      </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-19.58</v>
+      </c>
+      <c r="O31" t="n">
+        <v>-65.75</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Potosí</t>
+        </is>
+      </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
+          <t>capital (pronóstico puntual)</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Potosí</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Potosí</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>noticia:1uil931</t>
+          <t>noticia:mz6q0s</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6151,15 +6167,15 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-23 22:49</t>
+          <t>2026-10-23 23:09</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1792810149000</v>
+        <v>1792811349000</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>El Deber</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6177,13 +6193,13 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Accidente de tránsito en la ruta hacia Alto Beni deja varios heridos - El Deber</t>
+          <t>Revelan lista preliminar de heridos tras accidente de Los Chicos Fieles - Red Uno</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQakFJRmx3RlJEMkVHU0pxWXZ2ZU1ib04tZy1yeTB2OGhrYk9CU3pMaDVpRThNZktZMS14UzA2Y1VIcEQtZDg3cEU2SmlzQnBmUVVvM0ZNYzZWNExWUXQ3aHpnd3lqOHFVV3pNbDRLS1NQNGtwb2RjSFpleHJkOG5zSXVtWjVIS1dLejNybktRWTJVZXh3WkFUQVE5T2tMdFdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPczBQcnE2SzFGMXc3b1lsTkNxVWRmS3Vnb01xOTV2WmVva3J2RVlteWpHZ3VJS2dNWGV5NW5FX3ZncnVKTEVDTGpBRndTU1FxeWxtaS1fb1FscGxXMWNXUE9zbHdob1AxVFl1eHB5OU1yUnNoOXJ6U21oVG9PVDA1ak1xQl9hUlB4V0RaQXJqZENGUm8zMUJEY3J0WW5ENE5ObWJLNmpWN0RkSmFJbnZUZGR5UFRPd3QyUFY4WQ?oc=5</t>
         </is>
       </c>
       <c r="L32" t="n">
@@ -6192,37 +6208,21 @@
       <c r="M32" t="n">
         <v>1</v>
       </c>
-      <c r="N32" t="n">
-        <v>-15.578</v>
-      </c>
-      <c r="O32" t="n">
-        <v>-67.44</v>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Alto Beni, La Paz</t>
-        </is>
-      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>La Paz</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>Alto Beni</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>noticia:1tliu4i</t>
+          <t>noticia:1uil931</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6232,11 +6232,11 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-23 22:18</t>
+          <t>2026-10-23 22:49</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1792808330000</v>
+        <v>1792810149000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQMF9BNnUzLURKNGRMUUJ1VXVRSXNnMlBsQnVXOG0tRlFtY3pvRDNPQmNJMWN2RzJVaWdoWndmcHFnTkZFZnJxRkZtMThYYWlwN09ueUgtei1pSE1hZ2FtSzN6elY4VXJHbzFxdll0eWh0ZkxwQkQ1SDZ5b0E3MlVENGZEWGZHUGlwVG4wd2x3OFNEMVpibnFr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQakFJRmx3RlJEMkVHU0pxWXZ2ZU1ib04tZy1yeTB2OGhrYk9CU3pMaDVpRThNZktZMS14UzA2Y1VIcEQtZDg3cEU2SmlzQnBmUVVvM0ZNYzZWNExWUXQ3aHpnd3lqOHFVV3pNbDRLS1NQNGtwb2RjSFpleHJkOG5zSXVtWjVIS1dLejNybktRWTJVZXh3WkFUQVE5T2tMdFdn?oc=5</t>
         </is>
       </c>
       <c r="L33" t="n">
@@ -6303,7 +6303,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>noticia:1twc9ul</t>
+          <t>noticia:1tliu4i</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6313,11 +6313,11 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-10-23 22:16</t>
+          <t>2026-10-23 22:18</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1792808192000</v>
+        <v>1792808330000</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNbmwzSnd6c2tFMXBWY0tiemJqRm5CNllOT2p1U0FhdW5QNGFBVXlSZVM1ak5jNGZvcXNVaUQzN3ZQQTlPbmVjQ2Y5RFl2dWVLeUN5NUFodDF0alEyZWlmOHFZWkVVbjdQbkl3ZWtmS25wQWM2TmRZZDBGM2xlS0ZhUzAweXRmcmhVWGY5dV9CUnFBNGtWZHZDSWVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQMF9BNnUzLURKNGRMUUJ1VXVRSXNnMlBsQnVXOG0tRlFtY3pvRDNPQmNJMWN2RzJVaWdoWndmcHFnTkZFZnJxRkZtMThYYWlwN09ueUgtei1pSE1hZ2FtSzN6elY4VXJHbzFxdll0eWh0ZkxwQkQ1SDZ5b0E3MlVENGZEWGZHUGlwVG4wd2x3OFNEMVpibnFr?oc=5</t>
         </is>
       </c>
       <c r="L34" t="n">
@@ -6384,7 +6384,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>noticia:1dygpkp</t>
+          <t>noticia:1twc9ul</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -6394,15 +6394,15 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-23 21:39</t>
+          <t>2026-10-23 22:16</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1792805983000</v>
+        <v>1792808192000</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>El Deber</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -6411,39 +6411,39 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>(Video) Así rescataron a uno de los integrantes de Los Chicos Fieles tras accidente en Caranavi - Red Uno</t>
+          <t>Accidente de tránsito en la ruta hacia Alto Beni deja varios heridos - El Deber</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOdTVUZUQxVTdvYTdONDQxVlhUTzBOS2hKLW1rS1NUcmRYRnlCVlhIcHZlSjdsaktkQm5CWkFYa3lDQkxnMlh0b3prX0lha1BtbW1qS1VuYnNiX3FiZkYyNDJDR0tqZ0pKMU5TeC04SXV4UUJOTUlPUTB6ek01bzUxTUsydjZqZzI3S3ZLUnRWSUFUVk44WEpKUl9rbzRLb2IwYl9sLVlrYmt5d2ZHNUtGd3lRNnYzMlhuMkJOZW1XSUl2N1BxZWpHbm5XTDJhRUtnR190QWQ1TDlTUVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNbmwzSnd6c2tFMXBWY0tiemJqRm5CNllOT2p1U0FhdW5QNGFBVXlSZVM1ak5jNGZvcXNVaUQzN3ZQQTlPbmVjQ2Y5RFl2dWVLeUN5NUFodDF0alEyZWlmOHFZWkVVbjdQbkl3ZWtmS25wQWM2TmRZZDBGM2xlS0ZhUzAweXRmcmhVWGY5dV9CUnFBNGtWZHZDSWVB?oc=5</t>
         </is>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" t="n">
-        <v>-15.813</v>
+        <v>-15.578</v>
       </c>
       <c r="O35" t="n">
-        <v>-67.46299999999999</v>
+        <v>-67.44</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Caranavi, La Paz</t>
+          <t>Alto Beni, La Paz</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -6458,14 +6458,14 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>Caranavi</t>
+          <t>Alto Beni</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>noticia:3dv7b0</t>
+          <t>noticia:1dygpkp</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -6475,15 +6475,15 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-10-23 21:35</t>
+          <t>2026-10-23 21:39</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1792805700000</v>
+        <v>1792805983000</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FmBolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -6492,29 +6492,29 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Accidente en Caranavi: vehículo de Los Chicos Fieles cae a un barranco y deja varios heridos - FmBolivia</t>
+          <t>(Video) Así rescataron a uno de los integrantes de Los Chicos Fieles tras accidente en Caranavi - Red Uno</t>
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNcE1KaHZyUTJCSElxRU9nVzdhTnczWjJGTEhFMEs0bHp2cUdFeHd3VTB0NmVFcjdEN1dsZDZLY2k1ZFFUWkhKV19PU3V2czNyamh1ZE9YajVSVF8xczF6OFhZcWFvYV9EcWg4ZDNCb2p3enhXbFpRYnJMdGdaTXNrWUZSYVhKNTVicWlCLTJ5OE05Z1BvNEx1eEloUk5qTGN3ZHNzbzZWSVljbnRmSERJUWdxRDc0MjJxMGtycWJaaVhXQUUxVUlaWVZLOWE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOdTVUZUQxVTdvYTdONDQxVlhUTzBOS2hKLW1rS1NUcmRYRnlCVlhIcHZlSjdsaktkQm5CWkFYa3lDQkxnMlh0b3prX0lha1BtbW1qS1VuYnNiX3FiZkYyNDJDR0tqZ0pKMU5TeC04SXV4UUJOTUlPUTB6ek01bzUxTUsydjZqZzI3S3ZLUnRWSUFUVk44WEpKUl9rbzRLb2IwYl9sLVlrYmt5d2ZHNUtGd3lRNnYzMlhuMkJOZW1XSUl2N1BxZWpHbm5XTDJhRUtnR190QWQ1TDlTUVk?oc=5</t>
         </is>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
         <v>-15.813</v>
@@ -6546,30 +6546,30 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-24:viento:1</t>
+          <t>noticia:3dv7b0</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-10-23 20:55</t>
+          <t>2026-10-23 21:35</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1792803329663</v>
+        <v>1792805700000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>FmBolivia</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6582,74 +6582,70 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-24: 78.1 km/h de ráfagas pronosticadas</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
-        </is>
-      </c>
+          <t>Accidente en Caranavi: vehículo de Los Chicos Fieles cae a un barranco y deja varios heridos - FmBolivia</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNcE1KaHZyUTJCSElxRU9nVzdhTnczWjJGTEhFMEs0bHp2cUdFeHd3VTB0NmVFcjdEN1dsZDZLY2k1ZFFUWkhKV19PU3V2czNyamh1ZE9YajVSVF8xczF6OFhZcWFvYV9EcWg4ZDNCb2p3enhXbFpRYnJMdGdaTXNrWUZSYVhKNTVicWlCLTJ5OE05Z1BvNEx1eEloUk5qTGN3ZHNzbzZWSVljbnRmSERJUWdxRDc0MjJxMGtycWJaaVhXQUUxVUlaWVZLOWE?oc=5</t>
         </is>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N37" t="n">
-        <v>-17.78</v>
+        <v>-15.813</v>
       </c>
       <c r="O37" t="n">
-        <v>-63.18</v>
+        <v>-67.46299999999999</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Caranavi, La Paz</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>capital (pronóstico puntual)</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Caranavi</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>noticia:rabz5p</t>
+          <t>clima:Santa Cruz:2026-10-24:viento:1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-10-23 20:44</t>
+          <t>2026-10-23 20:55</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1792802686000</v>
+        <v>1792803329663</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -6658,22 +6654,26 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Tome previsiones: se pronostican lluvias y ambiente caluroso para este fin de semana en Cochabamba - Red Uno</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
+          <t>Santa Cruz 2026-10-24: 78.1 km/h de ráfagas pronosticadas</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTlU5NVFpY1RheTN5ZE1IbG5VYTh2Sk5hZHpHeWI3LVdnSFg2cFJFdnBCVkxiUjNKcUgyUW16SWxpMXFkMHdad2xFN043bklJeG1iQ0V1V3hBZk1Ga3NscjdPVWUySmt4bDNTdWlmSUdOMmNlZ2hkSWZFMmk4VGs0Nm9TcnRCTDhINmtnQU9zZDBUY05HcWpxN3FOX3N1dmVJblE0MGc5di1Ma1N2dGNxOUtoV1MzNnl1OXpRaTZ2UGxMc3RDWndubHVQNUd0eVROMGR2OGxVemtOaEc4bTNRaA?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L38" t="n">
@@ -6683,36 +6683,36 @@
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>-17.39</v>
+        <v>-17.78</v>
       </c>
       <c r="O38" t="n">
-        <v>-66.16</v>
+        <v>-63.18</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Cochabamba, Cochabamba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
+          <t>capital (pronóstico puntual)</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>noticia:1jfk053</t>
+          <t>noticia:rabz5p</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6722,11 +6722,11 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-10-23 19:08</t>
+          <t>2026-10-23 20:44</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1792796931000</v>
+        <v>1792802686000</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -6735,43 +6735,43 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>climatológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Sequía en Pasorapa: el ganado muere por falta de agua y alistan declaratoria de desastre - Red Uno</t>
+          <t>Tome previsiones: se pronostican lluvias y ambiente caluroso para este fin de semana en Cochabamba - Red Uno</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNQVhTWE8zdE1BQ3lueWJPeV9wUDNsSmJpS0NJTWppMUY4QmlQSUFHVjRORmtrVHQ3MHB0T1pyS25PamxnY0hBQUtzOVRvSUNaUkdGb1RWSGl4dFA4Z3VINVpQTk1pZUpDdUIyUU5hZS1oNGhBa1RWcFhScVMwVTFrVlJaOFQ4OWFqRWVUZ051bHVJTlMxRTBhRFVLUEV2dTZFdDgtRkxJM3VvN3YzUWJfVk41ZWR5U1JoNmx0WFFkMmNTWGVleGNIQlNxWUJzdHIxSWtz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTlU5NVFpY1RheTN5ZE1IbG5VYTh2Sk5hZHpHeWI3LVdnSFg2cFJFdnBCVkxiUjNKcUgyUW16SWxpMXFkMHdad2xFN043bklJeG1iQ0V1V3hBZk1Ga3NscjdPVWUySmt4bDNTdWlmSUdOMmNlZ2hkSWZFMmk4VGs0Nm9TcnRCTDhINmtnQU9zZDBUY05HcWpxN3FOX3N1dmVJblE0MGc5di1Ma1N2dGNxOUtoV1MzNnl1OXpRaTZ2UGxMc3RDWndubHVQNUd0eVROMGR2OGxVemtOaEc4bTNRaA?oc=5</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>-18.38</v>
+        <v>-17.39</v>
       </c>
       <c r="O39" t="n">
-        <v>-64.649</v>
+        <v>-66.16</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Pasorapa, Cochabamba</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -6786,14 +6786,14 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>Pasorapa</t>
+          <t>Cochabamba</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>noticia:ix3l8o</t>
+          <t>noticia:1jfk053</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6803,56 +6803,56 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-10-23 18:25</t>
+          <t>2026-10-23 19:08</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1792794310000</v>
+        <v>1792796931000</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Visión 360</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>climatológica</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Oruro evalúa suspender clases presenciales por más de 200 casos de Coxsackie - Visión 360</t>
+          <t>Sequía en Pasorapa: el ganado muere por falta de agua y alistan declaratoria de desastre - Red Uno</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0c9IBywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNQVhTWE8zdE1BQ3lueWJPeV9wUDNsSmJpS0NJTWppMUY4QmlQSUFHVjRORmtrVHQ3MHB0T1pyS25PamxnY0hBQUtzOVRvSUNaUkdGb1RWSGl4dFA4Z3VINVpQTk1pZUpDdUIyUU5hZS1oNGhBa1RWcFhScVMwVTFrVlJaOFQ4OWFqRWVUZ051bHVJTlMxRTBhRFVLUEV2dTZFdDgtRkxJM3VvN3YzUWJfVk41ZWR5U1JoNmx0WFFkMmNTWGVleGNIQlNxWUJzdHIxSWtz?oc=5</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>-17.97</v>
+        <v>-18.38</v>
       </c>
       <c r="O40" t="n">
-        <v>-67.11</v>
+        <v>-64.649</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>Pasorapa, Cochabamba</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -6862,19 +6862,19 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Pasorapa</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>noticia:1xqv9m7</t>
+          <t>noticia:ix3l8o</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6884,62 +6884,78 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-10-23 18:09</t>
+          <t>2026-10-23 18:25</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1792793370000</v>
+        <v>1792794310000</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>El Diario del centro del país</t>
+          <t>Visión 360</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Tres heridos en tremendo choque cerca de Oncativo - El Diario del centro del país</t>
+          <t>Oruro evalúa suspender clases presenciales por más de 200 casos de Coxsackie - Visión 360</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZERhbTJMQUJVb3hmZFlSZmRGZkdBLWdFTGJVQzdqZkE4aGhhWmdQZ2JDRW1ndkJLWU90VTZ6Ti1JOUZzcFZfcE1zbkRHU1B3YTF4UkVzdllFa1p3SUlObURGamF0Vm9kc3dPLTZVWFJ4NWZZQmlySElPNHhZTnRGNGNZUWw2ZlI1eVBEQkNGNEhLWTNiLWJLUS0xYjA0UWRhc0d6bVN4aVVLSVdsQWlpMUZYdWw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0c9IBywFBVV95cUxQR0kzVkkyR29mcVdqUkdHcHgtVjlfX2Q2RkIxYzdaNTkyelktVDdta3dybWRFRzF1QkpTclZ6MUJVb1AxeENJMFZNOUhsTVBjRTUzXy1iVjdXTFhaZ3JNd1h6dWtvSzlCeE9WYVdILWk3UkdfLXc3Rm9QR1ZfN0dmd3ZEdjdpNDR6Z3F1Z0pDOEgwMVRuaXVMSkUwVWp5LXFOUE52VXczc05GT2RWdXlNR2tTYjNrbnRGbkRhdlVhM0ZaSGVHUkd1dGN0cw?oc=5</t>
         </is>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3</v>
-      </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>-17.97</v>
+      </c>
+      <c r="O41" t="n">
+        <v>-67.11</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Oruro, Oruro</t>
+        </is>
+      </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>noticia:1wuregl</t>
+          <t>noticia:1xqv9m7</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6949,78 +6965,62 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-10-23 15:39</t>
+          <t>2026-10-23 18:09</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1792784340000</v>
+        <v>1792793370000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FmBolivia</t>
+          <t>El Diario del centro del país</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>hidrológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Intensas lluvias inundan La Paz y activan alertas por el riesgo de desborde de ríos - FmBolivia</t>
+          <t>Tres heridos en tremendo choque cerca de Oncativo - El Diario del centro del país</t>
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPZm85aHphekQ4U3BZZkp1ZkF6ZVdSUHgtZmltS1FxUUgza1AwcndWWDJZOWctT0RiVmVabmg5SG42NnJWMlJMMnBlYTlYaVdSb09sR0dnVDdpT29faTdiaDUtZElJdlQ3eTdjR2VsWjlta1FOS1U2Vm1vV3JwWkpvbEw1ZUR3akgwQTZnQnVENjJtVkQtVUpKVEJTeWNJSE1CaEFKa2VqMmZXbWk3ekR4ZWpmZ1Z3elFQaWNaNFJuMXA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZERhbTJMQUJVb3hmZFlSZmRGZkdBLWdFTGJVQzdqZkE4aGhhWmdQZ2JDRW1ndkJLWU90VTZ6Ti1JOUZzcFZfcE1zbkRHU1B3YTF4UkVzdllFa1p3SUlObURGamF0Vm9kc3dPLTZVWFJ4NWZZQmlySElPNHhZTnRGNGNZUWw2ZlI1eVBEQkNGNEhLWTNiLWJLUS0xYjA0UWRhc0d6bVN4aVVLSVdsQWlpMUZYdWw?oc=5</t>
         </is>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="n">
-        <v>-16.169</v>
-      </c>
-      <c r="O42" t="n">
-        <v>-68.09</v>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>La Paz, La Paz</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>La Paz</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>Nuestra Señora de La Paz</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>noticia:1570kkf</t>
+          <t>noticia:1wuregl</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -7030,20 +7030,20 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-10-23 15:28</t>
+          <t>2026-10-23 15:39</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1792783705000</v>
+        <v>1792784340000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>FmBolivia</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>hidrológica</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7056,13 +7056,13 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>¿Se suspenden las clases en Oruro? Más de 200 casos de Coxsackie activan evaluaciones - Red Uno</t>
+          <t>Intensas lluvias inundan La Paz y activan alertas por el riesgo de desborde de ríos - FmBolivia</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNMFdHaVpKRmMyOENDYm16UXJPenVSQnpmTE94bDc4UFhqakluMUdvZjAwamUxT3BVWUpJQm8xVHBWengxQmhWM1hjU3d2YXFrLXpVU2VrZDJiMXZLMlQ5bGxGOHFETFhYM0s2RjlUTlhkd0g2eXQweDFHaTlKNGNMUlJfOWg2a0JjTklXUWZKc1BmUXZuZFZ2MF9fV2lEYUY4LXNiNmk3cF9FNjVtTl9GWFotT2ltS0xXTnM1dENvSU9kbFRMalFrYVdXOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPZm85aHphekQ4U3BZZkp1ZkF6ZVdSUHgtZmltS1FxUUgza1AwcndWWDJZOWctT0RiVmVabmg5SG42NnJWMlJMMnBlYTlYaVdSb09sR0dnVDdpT29faTdiaDUtZElJdlQ3eTdjR2VsWjlta1FOS1U2Vm1vV3JwWkpvbEw1ZUR3akgwQTZnQnVENjJtVkQtVUpKVEJTeWNJSE1CaEFKa2VqMmZXbWk3ekR4ZWpmZ1Z3elFQaWNaNFJuMXA?oc=5</t>
         </is>
       </c>
       <c r="L43" t="n">
@@ -7072,14 +7072,14 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>-17.97</v>
+        <v>-16.169</v>
       </c>
       <c r="O43" t="n">
-        <v>-67.11</v>
+        <v>-68.09</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>La Paz, La Paz</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -7089,19 +7089,19 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Nuestra Señora de La Paz</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>noticia:1nzu2o8</t>
+          <t>noticia:1570kkf</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -7111,39 +7111,39 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-10-23 15:20</t>
+          <t>2026-10-23 15:28</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1792783236000</v>
+        <v>1792783705000</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>hidrológica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Alerta naranja por posibles desbordes en tres departamentos (15:20) - El Diario - Bolivia</t>
+          <t>¿Se suspenden las clases en Oruro? Más de 200 casos de Coxsackie activan evaluaciones - Red Uno</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPTnBESV9OODZhNjY3T2M2X2NZcmk4clI0eFZsd3VLMVRwaUlSdF9wanZyVGxDNUlNTm5wbGpLN1lvX09mNGxFVkpIZDNGdi1pNDdfSGlESThfeVloQzJsNUMyNUpWUDhzTVJiYWJpNkQ1RHliRWljZlp3SlhtZ2FhU0pvV0syUmZIejJZWHlRdTBOTG4zaTc5cEsycW9IcEx2SkQtN01Gendlb1VR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNMFdHaVpKRmMyOENDYm16UXJPenVSQnpmTE94bDc4UFhqakluMUdvZjAwamUxT3BVWUpJQm8xVHBWengxQmhWM1hjU3d2YXFrLXpVU2VrZDJiMXZLMlQ5bGxGOHFETFhYM0s2RjlUTlhkd0g2eXQweDFHaTlKNGNMUlJfOWg2a0JjTklXUWZKc1BmUXZuZFZ2MF9fV2lEYUY4LXNiNmk3cF9FNjVtTl9GWFotT2ltS0xXTnM1dENvSU9kbFRMalFrYVdXOA?oc=5</t>
         </is>
       </c>
       <c r="L44" t="n">
@@ -7152,21 +7152,37 @@
       <c r="M44" t="n">
         <v>0</v>
       </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
+      <c r="N44" t="n">
+        <v>-17.97</v>
+      </c>
+      <c r="O44" t="n">
+        <v>-67.11</v>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Oruro, Oruro</t>
+        </is>
+      </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>noticia:1itd1r7</t>
+          <t>noticia:1nzu2o8</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -7176,39 +7192,39 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-10-23 15:01</t>
+          <t>2026-10-23 15:20</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1792782098000</v>
+        <v>1792783236000</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>eju.tv</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>hidrológica</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Intensa lluvia y granizada en La Paz inundan vías y elevan el nivel de los ríos - eju.tv</t>
+          <t>Alerta naranja por posibles desbordes en tres departamentos (15:20) - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNWU9QWElKQXEyN3UxVm4xbzJzbEJ1TU1NTHZlRUp6YndmeU9GQnJKcTluVEJ2ZHQ5cGp3aWhlMUd5ektWQlBpUVNmZnZuRnJwMXlydzAzX0FBVnY5UDMzQTBkWVRNRUNJSlRvX3MyQVhMcEhIMW9WSUpXckVSd0RJWk1KMFBKWmJNU3diQVlEN1Y5aVV6eVBaZXpOMnFIWWxaMlRlY0ZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPTnBESV9OODZhNjY3T2M2X2NZcmk4clI0eFZsd3VLMVRwaUlSdF9wanZyVGxDNUlNTm5wbGpLN1lvX09mNGxFVkpIZDNGdi1pNDdfSGlESThfeVloQzJsNUMyNUpWUDhzTVJiYWJpNkQ1RHliRWljZlp3SlhtZ2FhU0pvV0syUmZIejJZWHlRdTBOTG4zaTc5cEsycW9IcEx2SkQtN01Gendlb1VR?oc=5</t>
         </is>
       </c>
       <c r="L45" t="n">
@@ -7217,37 +7233,21 @@
       <c r="M45" t="n">
         <v>0</v>
       </c>
-      <c r="N45" t="n">
-        <v>-16.169</v>
-      </c>
-      <c r="O45" t="n">
-        <v>-68.09</v>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>La Paz, La Paz</t>
-        </is>
-      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>La Paz</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>Nuestra Señora de La Paz</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>noticia:1l4xxfk</t>
+          <t>noticia:1itd1r7</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -7257,20 +7257,20 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-10-23 14:51</t>
+          <t>2026-10-23 15:01</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1792781480000</v>
+        <v>1792782098000</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>eju.tv</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7283,13 +7283,13 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
+          <t>Intensa lluvia y granizada en La Paz inundan vías y elevan el nivel de los ríos - eju.tv</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQS2FPaHd3UnFBRjRoa0lKUm1MNUQ5S00zN1RJZE5fWlVUQnhiY0lLcFRkY2JZak1mZ0c2WEVMVUNJVUJTMGFLNHg4S2ZKNTRqLXJHM09ET19hX1pZeTQwUkdEc2huTHVpcno2QTRZbnhralVRWXozcWc1a2pHUEpBeTV1cWgzTWRwaDEweURKeVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNWU9QWElKQXEyN3UxVm4xbzJzbEJ1TU1NTHZlRUp6YndmeU9GQnJKcTluVEJ2ZHQ5cGp3aWhlMUd5ektWQlBpUVNmZnZuRnJwMXlydzAzX0FBVnY5UDMzQTBkWVRNRUNJSlRvX3MyQVhMcEhIMW9WSUpXckVSd0RJWk1KMFBKWmJNU3diQVlEN1Y5aVV6eVBaZXpOMnFIWWxaMlRlY0ZB?oc=5</t>
         </is>
       </c>
       <c r="L46" t="n">
@@ -7299,14 +7299,14 @@
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>-17.97</v>
+        <v>-16.169</v>
       </c>
       <c r="O46" t="n">
-        <v>-67.11</v>
+        <v>-68.09</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Oruro, Oruro</t>
+          <t>La Paz, La Paz</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -7316,19 +7316,19 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>Oruro</t>
+          <t>Nuestra Señora de La Paz</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>noticia:51709n</t>
+          <t>noticia:1l4xxfk</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -7338,56 +7338,56 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-10-23 13:38</t>
+          <t>2026-10-23 14:51</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1792777139000</v>
+        <v>1792781480000</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>eju.tv</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - eju.tv</t>
+          <t>Oruro reporta más de 200 casos de coxsackie - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPcjZTSmprRGVoNlRqQmdBTE5VM3pRQ1ZFakFUbzVyMUhiaDVkT0liaG9UNEZXekV6bWsycUk4X1JCSEY5RjhNVlZaTk9ULUFuZkY3NnZuWmZ1a19leUhFdlIyQV9kLWxlSkxfeXFhcFRTZjZ2YkpQQlJ1dkNLMDBjaGZ4SkhyQ0RfcnhKSEg5WURCQVQwbENYTHEzUzJSaUEzMGo2bWdyS3lsM016LXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQS2FPaHd3UnFBRjRoa0lKUm1MNUQ5S00zN1RJZE5fWlVUQnhiY0lLcFRkY2JZak1mZ0c2WEVMVUNJVUJTMGFLNHg4S2ZKNTRqLXJHM09ET19hX1pZeTQwUkdEc2huTHVpcno2QTRZbnhralVRWXozcWc1a2pHUEpBeTV1cWgzTWRwaDEweURKeVE?oc=5</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>-17.764</v>
+        <v>-17.97</v>
       </c>
       <c r="O47" t="n">
-        <v>-62.903</v>
+        <v>-67.11</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Cotoca, Santa Cruz</t>
+          <t>Oruro, Oruro</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -7397,19 +7397,19 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Oruro</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>Cotoca</t>
+          <t>Oruro</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>noticia:11rddql</t>
+          <t>noticia:51709n</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -7419,56 +7419,56 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-10-23 13:22</t>
+          <t>2026-10-23 13:38</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1792776139000</v>
+        <v>1792777139000</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia</t>
+          <t>eju.tv</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>biológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Intensifican acciones preventivas contra el dengue en Caranavi - El Diario - Bolivia</t>
+          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - eju.tv</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOMjhSeDJBek5iaFhDcnFzX1lKelgwZmUwLTJnbEhMdDRMelUxNks5Ti1pRHh3dDhTcC1YZEdqM3FJOGdqVHRvcXVhRlpCQzVDTEZMUFBkV1NrYVQ2LXRqTTBhcGRQc21CQ0VabzZaNExXb1BjTzJ2Uk5BcFF0VG5XOFNRa3lqUWlJSnRFUUVXYnNpbXB0LVVmSXVWSzJxcmVpdVVxUC1KOUhTQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPcjZTSmprRGVoNlRqQmdBTE5VM3pRQ1ZFakFUbzVyMUhiaDVkT0liaG9UNEZXekV6bWsycUk4X1JCSEY5RjhNVlZaTk9ULUFuZkY3NnZuWmZ1a19leUhFdlIyQV9kLWxlSkxfeXFhcFRTZjZ2YkpQQlJ1dkNLMDBjaGZ4SkhyQ0RfcnhKSEg5WURCQVQwbENYTHEzUzJSaUEzMGo2bWdyS3lsM016LXc?oc=5</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N48" t="n">
-        <v>-15.813</v>
+        <v>-17.764</v>
       </c>
       <c r="O48" t="n">
-        <v>-67.46299999999999</v>
+        <v>-62.903</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Caranavi, La Paz</t>
+          <t>Cotoca, Santa Cruz</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -7478,19 +7478,19 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>Caranavi</t>
+          <t>Cotoca</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>noticia:fcm3nx</t>
+          <t>noticia:11rddql</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -7500,62 +7500,78 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-10-23 12:58</t>
+          <t>2026-10-23 13:22</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1792774699000</v>
+        <v>1792776139000</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>El Diario - Bolivia</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>biológica</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>[VIDEO] Así fue el accidente de moto que dejó un adolescente fallecido y un hombre gravemente herido - Red Uno</t>
+          <t>Intensifican acciones preventivas contra el dengue en Caranavi - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOSmJMazhUemNfRHpWcDBoTVFZMUpwdlVKVUtvUXZNTGRRRHlwLW5KNmNhcmFnd1czbi1yalhFMnpSS1dmUE9jVzNlOS1kMWZtRzBHZ2EtcDRDdU5Gc2JUQVIwM2xPa2lZVmswRi1SUFVPcm8xcHlGN3F2UThTSDdKMDNyYnJmVkcxazNLLVBLOWFYM09FVUpmVnN5RVhpSVo2V1VCVmFwQ1gzTmRUWVp2aXMwcmxHRS1GV2p3NTBtR2RzM2wwVHUzaGJkRXJYbHdvaDlhWm5YMTk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOMjhSeDJBek5iaFhDcnFzX1lKelgwZmUwLTJnbEhMdDRMelUxNks5Ti1pRHh3dDhTcC1YZEdqM3FJOGdqVHRvcXVhRlpCQzVDTEZMUFBkV1NrYVQ2LXRqTTBhcGRQc21CQ0VabzZaNExXb1BjTzJ2Uk5BcFF0VG5XOFNRa3lqUWlJSnRFUUVXYnNpbXB0LVVmSXVWSzJxcmVpdVVxUC1KOUhTQQ?oc=5</t>
         </is>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>1</v>
-      </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>-15.813</v>
+      </c>
+      <c r="O49" t="n">
+        <v>-67.46299999999999</v>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Caranavi, La Paz</t>
+        </is>
+      </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>La Paz</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Caranavi</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>noticia:1cjx1qd</t>
+          <t>noticia:fcm3nx</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -7565,78 +7581,62 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-10-23 12:39</t>
+          <t>2026-10-23 12:58</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1792773575000</v>
+        <v>1792774699000</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Más de 60 municipios en La Paz sufren falta de lluvias - La Patria Bolivia</t>
+          <t>[VIDEO] Así fue el accidente de moto que dejó un adolescente fallecido y un hombre gravemente herido - Red Uno</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE52Qi03Z1J6OS1CR2liRVZ0VlhCcmVQWFV6RUdGNXdrbzZRNXFjTWRaRnc1b3VoV0xaY3RIdncxNlNnYkxyUXo5MTlJWmMwWDNSMDE4ZHI2VkpWajFPaUF2SmRVYkk2eDZYQ1RfUU9ieENrZG9UVVFiaXZSeGI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOSmJMazhUemNfRHpWcDBoTVFZMUpwdlVKVUtvUXZNTGRRRHlwLW5KNmNhcmFnd1czbi1yalhFMnpSS1dmUE9jVzNlOS1kMWZtRzBHZ2EtcDRDdU5Gc2JUQVIwM2xPa2lZVmswRi1SUFVPcm8xcHlGN3F2UThTSDdKMDNyYnJmVkcxazNLLVBLOWFYM09FVUpmVnN5RVhpSVo2V1VCVmFwQ1gzTmRUWVp2aXMwcmxHRS1GV2p3NTBtR2RzM2wwVHUzaGJkRXJYbHdvaDlhWm5YMTk?oc=5</t>
         </is>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="n">
-        <v>-16.169</v>
-      </c>
-      <c r="O50" t="n">
-        <v>-68.09</v>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>La Paz, La Paz</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>La Paz</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>Nuestra Señora de La Paz</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>noticia:11y8tre</t>
+          <t>noticia:1cjx1qd</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7646,56 +7646,56 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-10-23 11:43</t>
+          <t>2026-10-23 12:39</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1792770197000</v>
+        <v>1792773575000</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>La Patria Bolivia</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - Red Uno</t>
+          <t>Más de 60 municipios en La Paz sufren falta de lluvias - La Patria Bolivia</t>
         </is>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOVGY3YVRLWWxYM0IycjF4dlNUeUhqZG90Yng4aWhmN3A5ai02WENWYnF4bWpoZHFKMGc1X0JPRHdRRVZfSlA4UmZFa2kxYkNIS3ZtQ1NvNlNCME51eVZTRkRKSUQ5MmRoaWl5Tkt5NHpPUEFwemN2YTV1djFwdHlqQnFqRHNPenhYcTlsanJPcXhpOVV1NmFBUXZyazQ2MkUzM0dSZy02ZllxTGtjcl9ldzdHSktTRlVaalZJc1pubUNQMWFTbzVEOUJ1UmhCdEJt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE52Qi03Z1J6OS1CR2liRVZ0VlhCcmVQWFV6RUdGNXdrbzZRNXFjTWRaRnc1b3VoV0xaY3RIdncxNlNnYkxyUXo5MTlJWmMwWDNSMDE4ZHI2VkpWajFPaUF2SmRVYkk2eDZYQ1RfUU9ieENrZG9UVVFiaXZSeGI?oc=5</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>-17.764</v>
+        <v>-16.169</v>
       </c>
       <c r="O51" t="n">
-        <v>-62.903</v>
+        <v>-68.09</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Cotoca, Santa Cruz</t>
+          <t>La Paz, La Paz</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -7705,42 +7705,42 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>Cotoca</t>
+          <t>Nuestra Señora de La Paz</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>clima:Sucre:2026-10-23:viento:1</t>
+          <t>noticia:11y8tre</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>noticia</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-10-23 06:55</t>
+          <t>2026-10-23 11:43</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1792752927735</v>
+        <v>1792770197000</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7753,56 +7753,52 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Sucre 2026-10-23: 66.2 km/h de ráfagas pronosticadas</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
-        </is>
-      </c>
+          <t>Un fallecido y un herido tras un accidente de moto en la carretera a Virgen de Cotoca - Red Uno</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOVGY3YVRLWWxYM0IycjF4dlNUeUhqZG90Yng4aWhmN3A5ai02WENWYnF4bWpoZHFKMGc1X0JPRHdRRVZfSlA4UmZFa2kxYkNIS3ZtQ1NvNlNCME51eVZTRkRKSUQ5MmRoaWl5Tkt5NHpPUEFwemN2YTV1djFwdHlqQnFqRHNPenhYcTlsanJPcXhpOVV1NmFBUXZyazQ2MkUzM0dSZy02ZllxTGtjcl9ldzdHSktTRlVaalZJc1pubUNQMWFTbzVEOUJ1UmhCdEJt?oc=5</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N52" t="n">
-        <v>-19.03</v>
+        <v>-17.764</v>
       </c>
       <c r="O52" t="n">
-        <v>-65.26000000000001</v>
+        <v>-62.903</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Cotoca, Santa Cruz</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>capital (pronóstico puntual)</t>
+          <t>nombre de municipio en el titular</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>Chuquisaca</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>Sucre</t>
+          <t>Cotoca</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-24:viento:2</t>
+          <t>clima:Sucre:2026-10-23:viento:1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -7816,7 +7812,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1792752927734</v>
+        <v>1792752927735</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -7829,16 +7825,16 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-24: 85 km/h de ráfagas pronosticadas</t>
+          <t>Sucre 2026-10-23: 66.2 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -7858,14 +7854,14 @@
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>-17.78</v>
+        <v>-19.03</v>
       </c>
       <c r="O53" t="n">
-        <v>-63.18</v>
+        <v>-65.26000000000001</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Sucre</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -7875,65 +7871,65 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Chuquisaca</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Sucre</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>usgs:us6000u49c</t>
+          <t>clima:Santa Cruz:2026-10-24:viento:2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>usgs</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-10-22 22:45</t>
+          <t>2026-10-23 06:55</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1792723541183</v>
+        <v>1792752927734</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>USGS</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>geológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Sismo M 4.5 - 58 km SW of Atocha, Bolivia</t>
+          <t>Santa Cruz 2026-10-24: 85 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Profundidad 236 km</t>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://earthquake.usgs.gov/earthquakes/eventpage/us6000u49c</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L54" t="n">
@@ -7943,59 +7939,59 @@
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>-21.3469</v>
+        <v>-17.78</v>
       </c>
       <c r="O54" t="n">
-        <v>-66.5795</v>
+        <v>-63.18</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>58 km SW of Atocha, Bolivia</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>coordenada de la fuente</t>
+          <t>capital (pronóstico puntual)</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>San Pablo</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-22:viento:1</t>
+          <t>usgs:us6000u49c</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>usgs</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-10-22 21:55</t>
+          <t>2026-10-22 22:45</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1792720528712</v>
+        <v>1792723541183</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Open-Meteo (pronóstico)</t>
+          <t>USGS</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>geológica</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8008,17 +8004,17 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-22: 67.7 km/h de ráfagas pronosticadas</t>
+          <t>Sismo M 4.5 - 58 km SW of Atocha, Bolivia</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+          <t>Profundidad 236 km</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://earthquake.usgs.gov/earthquakes/eventpage/us6000u49c</t>
         </is>
       </c>
       <c r="L55" t="n">
@@ -8028,36 +8024,36 @@
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>-17.78</v>
+        <v>-21.3469</v>
       </c>
       <c r="O55" t="n">
-        <v>-63.18</v>
+        <v>-66.5795</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>58 km SW of Atocha, Bolivia</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>capital (pronóstico puntual)</t>
+          <t>coordenada de la fuente</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>San Pablo</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>clima:Santa Cruz:2026-10-23:viento:2</t>
+          <t>clima:Santa Cruz:2026-10-22:viento:1</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -8084,16 +8080,16 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Santa Cruz 2026-10-23: 83.9 km/h de ráfagas pronosticadas</t>
+          <t>Santa Cruz 2026-10-22: 67.7 km/h de ráfagas pronosticadas</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -8142,49 +8138,53 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>noticia:1hhvre7</t>
+          <t>clima:Santa Cruz:2026-10-23:viento:2</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>noticia</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-10-22 19:36</t>
+          <t>2026-10-22 21:55</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1792712202000</v>
+        <v>1792720528712</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>El Mundo Bolivia</t>
+          <t>Open-Meteo (pronóstico)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Virgen de Cotoca: Controlan incendio en depósito de materiales plásticos - El Mundo Bolivia</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
+          <t>Santa Cruz 2026-10-23: 83.9 km/h de ráfagas pronosticadas</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Pronóstico de modelo, no es alerta oficial. Compare con SENAMHI.</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcDF6VE5FNzRaWGRuUzFKeXhnZ21DZTRaaEtrVEJEa1Z3ejg2VG1ONG1ENmlDWlkyVjlkQkJwS2F1XzBGMFQwSHd4OEwxTW1PbHdGcUh1ckV6SGpDd2hiN0dkeUVTcnFXT3RjOU1kLXZtVVdZY2hkZS1pcVpVUFhnRktqcHY5UnBrY0xUMDRETjl6N0pXT3A5amxhMA?oc=5</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="L57" t="n">
@@ -8194,19 +8194,19 @@
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>-17.764</v>
+        <v>-17.78</v>
       </c>
       <c r="O57" t="n">
-        <v>-62.903</v>
+        <v>-63.18</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Cotoca, Santa Cruz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
+          <t>capital (pronóstico puntual)</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -8216,14 +8216,14 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>Cotoca</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>noticia:bksnde</t>
+          <t>noticia:1hhvre7</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -8233,15 +8233,15 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-10-22 17:01</t>
+          <t>2026-10-22 19:36</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1792702880000</v>
+        <v>1792712202000</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>eju.tv</t>
+          <t>El Mundo Bolivia</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -8259,13 +8259,13 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Reportan un incendio cerca de la carretera a Cotoca - eju.tv</t>
+          <t>Virgen de Cotoca: Controlan incendio en depósito de materiales plásticos - El Mundo Bolivia</t>
         </is>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPNGtpbnBfRnRBalVudnBlZHdVQ0ZSaUplZmtvTGE0aTQzdkxWS3d4My1EZEJ1UE9FNFQ3RmpyZGVsbS1qNEM1QUVFRFAxM2pYT1VqQzRuVjRtZnVNUGlKODNMc0F1a3l6TUpuQmtlUWNlVTVEWWU5ZGZtQm5LWUp3Sg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcDF6VE5FNzRaWGRuUzFKeXhnZ21DZTRaaEtrVEJEa1Z3ejg2VG1ONG1ENmlDWlkyVjlkQkJwS2F1XzBGMFQwSHd4OEwxTW1PbHdGcUh1ckV6SGpDd2hiN0dkeUVTcnFXT3RjOU1kLXZtVVdZY2hkZS1pcVpVUFhnRktqcHY5UnBrY0xUMDRETjl6N0pXT3A5amxhMA?oc=5</t>
         </is>
       </c>
       <c r="L58" t="n">
@@ -8304,7 +8304,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>noticia:17hz69v</t>
+          <t>noticia:bksnde</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -8314,15 +8314,15 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-10-22 13:05</t>
+          <t>2026-10-22 17:01</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1792688709000</v>
+        <v>1792702880000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>La Razón Digital Bolivia</t>
+          <t>eju.tv</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -8331,45 +8331,61 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Accidente en El Sillar deja al menos 29 heridos - La Razón Digital Bolivia</t>
+          <t>Reportan un incendio cerca de la carretera a Cotoca - eju.tv</t>
         </is>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPaXhTdm45YWZnWVFxVzJnb1ZwbUN4SmUtLVdJN0VJdFZBamRyQmFxN0RZelBfTklaSTVyOUZ3ajQ5MFB2TEN4Ukd6TE5ORFY5SEROVk1CZ25sRWJ1QnRBdTVfTktlby1NWXhaVWI5YnRvaDZWbHVjdDVoeFp5Tk5veFk5a19MSWJqcEJVV0dzV3k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPNGtpbnBfRnRBalVudnBlZHdVQ0ZSaUplZmtvTGE0aTQzdkxWS3d4My1EZEJ1UE9FNFQ3RmpyZGVsbS1qNEM1QUVFRFAxM2pYT1VqQzRuVjRtZnVNUGlKODNMc0F1a3l6TUpuQmtlUWNlVTVEWWU5ZGZtQm5LWUp3Sg?oc=5</t>
         </is>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>29</v>
-      </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>-17.764</v>
+      </c>
+      <c r="O59" t="n">
+        <v>-62.903</v>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Cotoca, Santa Cruz</t>
+        </is>
+      </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Cotoca</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>noticia:1f1qb0</t>
+          <t>noticia:17hz69v</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -8379,15 +8395,15 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-10-22 12:09</t>
+          <t>2026-10-22 13:05</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1792685373000</v>
+        <v>1792688709000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>La Razón Digital Bolivia</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -8396,61 +8412,45 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Accidente en el tramo Locotal–Villa Tunari: la vía está transitable con precaución - Red Uno</t>
+          <t>Accidente en El Sillar deja al menos 29 heridos - La Razón Digital Bolivia</t>
         </is>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTFozcEEwNXBqV19sS2VibXh0MGt0QlhsX1djSTFGQW5zNlFLRHZpNVVnZ1JmWDQ4LVRHX2Rmb3B5UU9qV0FZQmJCaUZYdmwyNG1NenJ4Qzlzd0NJTGs1SjMxdFRtRFBzSUkybGJfZFFaNFZBc21FSUJYSFVkQkVkSEhQaGw0UFVzeXctZHo3cjNsYm5weXJlOU1wcmFncnNhMC1BQUpvNWlDX1NxZXU4b09kVFFWR2tSVEk2UTdXXzB3TjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPaXhTdm45YWZnWVFxVzJnb1ZwbUN4SmUtLVdJN0VJdFZBamRyQmFxN0RZelBfTklaSTVyOUZ3ajQ5MFB2TEN4Ukd6TE5ORFY5SEROVk1CZ25sRWJ1QnRBdTVfTktlby1NWXhaVWI5YnRvaDZWbHVjdDVoeFp5Tk5veFk5a19MSWJqcEJVV0dzV3k?oc=5</t>
         </is>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="n">
-        <v>-16.556</v>
-      </c>
-      <c r="O60" t="n">
-        <v>-65.569</v>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>Villa Tunari, Cochabamba</t>
-        </is>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>Villa Tunari</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>noticia:wi18tm</t>
+          <t>noticia:1f1qb0</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -8460,11 +8460,11 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-10-22 11:53</t>
+          <t>2026-10-22 12:09</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1792684426000</v>
+        <v>1792685373000</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -8473,49 +8473,65 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>tecnológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Accidente en El Sillar deja heridos y derrame de combustible: esto es lo último que se sabe - Red Uno</t>
+          <t>Accidente en el tramo Locotal–Villa Tunari: la vía está transitable con precaución - Red Uno</t>
         </is>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPZHNBTEdaQm5Wby1lTF9mWlQ2aGg0MVc4S0MwVWJ3dUJ5WWU5X3IwYWhKRjk5VWtYWEJHRDF4QldVc29laVNPSTJNWFBDSkNFQlFSYTJUXzNMNF9hckFBN1I2T2xoQUtYQ2V6MDNTZHhHVk9qeTBCdHRpM2ZLd0pyOFRweUUxX19STzRHTHg5VUY5d1lhS0tDeXpCdklqcTZGT1J4R0xnSDhoak1EZ2dtNUhSTUV6b1o0U0VSdWY5X0E3U05Tc1dYVEN2WFZUeFhPMTBJTmowNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOTFozcEEwNXBqV19sS2VibXh0MGt0QlhsX1djSTFGQW5zNlFLRHZpNVVnZ1JmWDQ4LVRHX2Rmb3B5UU9qV0FZQmJCaUZYdmwyNG1NenJ4Qzlzd0NJTGs1SjMxdFRtRFBzSUkybGJfZFFaNFZBc21FSUJYSFVkQkVkSEhQaGw0UFVzeXctZHo3cjNsYm5weXJlOU1wcmFncnNhMC1BQUpvNWlDX1NxZXU4b09kVFFWR2tSVEk2UTdXXzB3TjA?oc=5</t>
         </is>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>1</v>
-      </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>-16.556</v>
+      </c>
+      <c r="O61" t="n">
+        <v>-65.569</v>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Villa Tunari, Cochabamba</t>
+        </is>
+      </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>sin ubicar</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr"/>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Cochabamba</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Villa Tunari</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>noticia:12gfagq</t>
+          <t>noticia:wi18tm</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -8525,78 +8541,62 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-10-22 11:28</t>
+          <t>2026-10-22 11:53</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1792682880000</v>
+        <v>1792684426000</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>FmBolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>tecnológica</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Reportan triple colisión entre dos camiones y un bus en la carretera Cochabamba-Santa Cruz - FmBolivia</t>
+          <t>Accidente en El Sillar deja heridos y derrame de combustible: esto es lo último que se sabe - Red Uno</t>
         </is>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNMTNBaFZNMU9SR25vdVBuNXlZY3g4VkFWYXRiQnNSaUFjemZhUHZWNHg4V2owU2xfNndBak94TnU2cHNUVXdNNWl2eUdHZVNMbVZweTR5M0o0bWdTNUN4QkoxUkI2TDBmVE03M09zRGhJRVFzV0tPZ1NCWEJLUkt1ZGN4UGduOUZMQnJoM0tMYTh0ZlFxaFJNUkJqaWFPazRlMzN3ajhjUEdUYXlZRndpb3RSdTFCX2tCZGJxQ0x4SlBISWJsRVoyN3ZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPZHNBTEdaQm5Wby1lTF9mWlQ2aGg0MVc4S0MwVWJ3dUJ5WWU5X3IwYWhKRjk5VWtYWEJHRDF4QldVc29laVNPSTJNWFBDSkNFQlFSYTJUXzNMNF9hckFBN1I2T2xoQUtYQ2V6MDNTZHhHVk9qeTBCdHRpM2ZLd0pyOFRweUUxX19STzRHTHg5VUY5d1lhS0tDeXpCdklqcTZGT1J4R0xnSDhoak1EZ2dtNUhSTUV6b1o0U0VSdWY5X0E3U05Tc1dYVEN2WFZUeFhPMTBJTmowNA?oc=5</t>
         </is>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="n">
-        <v>-17.39</v>
-      </c>
-      <c r="O62" t="n">
-        <v>-66.16</v>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>Cochabamba, Cochabamba</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>nombre de municipio en el titular</t>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
+          <t>sin ubicar</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>noticia:1uq1bxy</t>
+          <t>noticia:12gfagq</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -8606,15 +8606,15 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-10-22 10:44</t>
+          <t>2026-10-22 11:28</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1792680273000</v>
+        <v>1792682880000</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>FmBolivia</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -8632,13 +8632,13 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Reportan triple colisión en la carretera Cochabamba–Santa Cruz - Red Uno</t>
+          <t>Reportan triple colisión entre dos camiones y un bus en la carretera Cochabamba-Santa Cruz - FmBolivia</t>
         </is>
       </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNNUROMzd1UDJRWVZZQ011cFd2c1FSdER1ZzdleU04cXpwYk5HaUZrLXoyU2NzdFk1dnNRUndhUWt0cG9DX09rSjlLcDItU0tzcmQtS3E4dDQ4ZF9HdGJLdk13ek9BNHJUWVlCcklrM25rZ01RbXhLalRBT1FGdDNReHdlTFZkNkJ5ZFd3N3NZVFVmOFUxbEhHN0RsaUxiSVZsM0lXVEFYSHVRQlhsOEtJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNMTNBaFZNMU9SR25vdVBuNXlZY3g4VkFWYXRiQnNSaUFjemZhUHZWNHg4V2owU2xfNndBak94TnU2cHNUVXdNNWl2eUdHZVNMbVZweTR5M0o0bWdTNUN4QkoxUkI2TDBmVE03M09zRGhJRVFzV0tPZ1NCWEJLUkt1ZGN4UGduOUZMQnJoM0tMYTh0ZlFxaFJNUkJqaWFPazRlMzN3ajhjUEdUYXlZRndpb3RSdTFCX2tCZGJxQ0x4SlBISWJsRVoyN3ZR?oc=5</t>
         </is>
       </c>
       <c r="L63" t="n">
@@ -8677,7 +8677,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>noticia:1jl2oid</t>
+          <t>noticia:1uq1bxy</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -8687,15 +8687,15 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-10-22 07:49</t>
+          <t>2026-10-22 10:44</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1792669785000</v>
+        <v>1792680273000</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>eju.tv</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -8704,39 +8704,39 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - eju.tv</t>
+          <t>Reportan triple colisión en la carretera Cochabamba–Santa Cruz - Red Uno</t>
         </is>
       </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQbTBrUmlla3FvVU1EX1pxcUI3SXYzbUFFMzlnRzhlSDJwMGpWWURxYjIwSkJBRGdCazMzT01hVy1qMFY3RnJLbC1XNXJ4bU55aDJVeXpNUlRsbzQ3T3hiRXJ5SWlhNmw5cDZFanNoWFBtQ01Gd3dscXltWmU5VHBSQlN3c2IwNGxuVE5tQ3lOT1RmNzRiVi1hc0hn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNNUROMzd1UDJRWVZZQ011cFd2c1FSdER1ZzdleU04cXpwYk5HaUZrLXoyU2NzdFk1dnNRUndhUWt0cG9DX09rSjlLcDItU0tzcmQtS3E4dDQ4ZF9HdGJLdk13ek9BNHJUWVlCcklrM25rZ01RbXhLalRBT1FGdDNReHdlTFZkNkJ5ZFd3N3NZVFVmOFUxbEhHN0RsaUxiSVZsM0lXVEFYSHVRQlhsOEtJ?oc=5</t>
         </is>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>-17.781</v>
+        <v>-17.39</v>
       </c>
       <c r="O64" t="n">
-        <v>-63.139</v>
+        <v>-66.16</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Santa Cruz, Santa Cruz</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -8746,19 +8746,19 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Cochabamba</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>noticia:yqgeq</t>
+          <t>noticia:1jl2oid</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -8768,15 +8768,15 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-10-22 07:43</t>
+          <t>2026-10-22 07:49</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1792669426000</v>
+        <v>1792669785000</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>eju.tv</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -8794,13 +8794,13 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - Red Uno</t>
+          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - eju.tv</t>
         </is>
       </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNVEh1bFlCanFuOTJid2EzYS1meG5oekFJcGFaME1fTk9sUnZpd3U0UXFHUFVJSW1jc1hzM2VFOFprT2xNYjBzbmswZmdJV3dremRIS0I4MDNzRjBnbEttWEhfOWZBbmFrRnNHWDFVLVFoM0VkZkxkaW4tMmZlSFJLei1heTFHMU0wSmxQVVRZN0cwaXQzcDBtZkdwTUFma0RXU2dwLXRnLTBkNGN3Vm1fV3hEdlM1dWZ1SEsw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQbTBrUmlla3FvVU1EX1pxcUI3SXYzbUFFMzlnRzhlSDJwMGpWWURxYjIwSkJBRGdCazMzT01hVy1qMFY3RnJLbC1XNXJ4bU55aDJVeXpNUlRsbzQ3T3hiRXJ5SWlhNmw5cDZFanNoWFBtQ01Gd3dscXltWmU5VHBSQlN3c2IwNGxuVE5tQ3lOT1RmNzRiVi1hc0hn?oc=5</t>
         </is>
       </c>
       <c r="L65" t="n">
@@ -8839,7 +8839,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>noticia:n32ahi</t>
+          <t>noticia:yqgeq</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -8849,69 +8849,150 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-10-22 05:30</t>
+          <t>2026-10-22 07:43</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1792661402000</v>
+        <v>1792669426000</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>FmBolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Senamhi anuncia el inicio de la temporada de lluvias en Bolivia y prevé granizadas como la de La Paz - FmBolivia</t>
+          <t>Accidente en Santa Cruz deja un vehículo volcado y un conductor herido - Red Uno</t>
         </is>
       </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNVEh1bFlCanFuOTJid2EzYS1meG5oekFJcGFaME1fTk9sUnZpd3U0UXFHUFVJSW1jc1hzM2VFOFprT2xNYjBzbmswZmdJV3dremRIS0I4MDNzRjBnbEttWEhfOWZBbmFrRnNHWDFVLVFoM0VkZkxkaW4tMmZlSFJLei1heTFHMU0wSmxQVVRZN0cwaXQzcDBtZkdwTUFma0RXU2dwLXRnLTBkNGN3Vm1fV3hEdlM1dWZ1SEsw?oc=5</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1</v>
+      </c>
+      <c r="N66" t="n">
+        <v>-17.781</v>
+      </c>
+      <c r="O66" t="n">
+        <v>-63.139</v>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Santa Cruz, Santa Cruz</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>nombre de municipio en el titular</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>Santa Cruz de la Sierra</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>noticia:n32ahi</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>noticia</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-10-22 05:30</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>1792661402000</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>FmBolivia</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>meteorológica</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>verde</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Senamhi anuncia el inicio de la temporada de lluvias en Bolivia y prevé granizadas como la de La Paz - FmBolivia</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
           <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQNmVPRnVBMGQzdEI5SUp3Z3ZGVExwTUR6TWNadGQ1QldUS1o2QVFvUl9sVEZKMDVyQVVrS25rU1RSQlJKWXk1YzE0NUhidjhpcmFaSlhZUDZvcE9XcG1KTFNTYmowUU1CSFJNOVR2UHNmMk1iT3N0RVBteHkzZkgyRFROYk1pdkpxVHZya3N2X2FVLVQxbURFVVZlb1NzRjZzTE95TXFVUXFJNkVZakQ2bUhVQzB0SXk3TVhXUTJXa0dycTE1MWVQRFpDX3lDSWFqUGwzU2NtNA?oc=5</t>
         </is>
       </c>
-      <c r="L66" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" t="n">
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="n">
         <v>-16.169</v>
       </c>
-      <c r="O66" t="n">
+      <c r="O67" t="n">
         <v>-68.09</v>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="P67" t="inlineStr">
         <is>
           <t>La Paz, La Paz</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t>nombre de municipio en el titular</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr">
+      <c r="R67" t="inlineStr">
         <is>
           <t>La Paz</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
+      <c r="S67" t="inlineStr">
         <is>
           <t>Nuestra Señora de La Paz</t>
         </is>
@@ -9481,7 +9562,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-10-25 17:40</t>
+          <t>2026-10-25 17:54</t>
         </is>
       </c>
     </row>
@@ -9504,7 +9585,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4">
@@ -9561,7 +9642,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sala de Situación Bolivia – CCES. Base de eventos de amenazas (datos preliminares de fuentes abiertas). Consulta: 2026-10-25 17:40.</t>
+          <t>Sala de Situación Bolivia – CCES. Base de eventos de amenazas (datos preliminares de fuentes abiertas). Consulta: 2026-10-25 17:54.</t>
         </is>
       </c>
     </row>

--- a/docs/datos/datos_bolivia.xlsx
+++ b/docs/datos/datos_bolivia.xlsx
@@ -9562,7 +9562,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-10-25 17:54</t>
+          <t>2026-10-25 18:19</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sala de Situación Bolivia – CCES. Base de eventos de amenazas (datos preliminares de fuentes abiertas). Consulta: 2026-10-25 17:54.</t>
+          <t>Sala de Situación Bolivia – CCES. Base de eventos de amenazas (datos preliminares de fuentes abiertas). Consulta: 2026-10-25 18:19.</t>
         </is>
       </c>
     </row>

--- a/docs/datos/datos_bolivia.xlsx
+++ b/docs/datos/datos_bolivia.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R44"/>
+  <dimension ref="A1:R45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,25 +514,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>noticia:kaqalb</t>
+          <t>noticia:1dz6gcb</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-25 15:29</t>
+          <t>2026-10-25 18:13</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1792956564000</v>
+        <v>1792966431000</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>“El bolsillo no alcanza”: la sequía golpea al ganado en Pasorapa y piden tanques de agua - Red Uno</t>
+          <t>Voraz incendio en Sacaba: tienda de k'oas queda consumida por las llamas - Red Uno</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>climatológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -563,14 +563,14 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>-18.38</v>
+        <v>-17.305</v>
       </c>
       <c r="N2" t="n">
-        <v>-64.649</v>
+        <v>-66.05</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Pasorapa, Cochabamba</t>
+          <t>Sacaba, Cochabamba</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -580,37 +580,37 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Pasorapa</t>
+          <t>Sacaba</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNRm5FbDhxTlliZHdPdnplYVNrWVdsSFF2ZGp3c2t1MEJCdWJkOE5fLWU5SXhXc25JLU9leVNsdnJZUEFFRmlTOUtJLW5SZ3JpRDFlYmlaYlFLYVJrM3pud0plS2lXVllqdEd0cWRiMUlmRzZkdnRpT2twaGU4cm1TRm9uSEw4WkhjeEJGUVZMNlJmRnFnY0M2UWw3T3NqMXdFcXhETjdrRi1hSjh3UDIxZl9CamxvYXdHRDRkZGR0ZEtZNHREX0c5Ul9Fa3VKMlJh?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOdGpCX3BVejVUcGJ1MzFHMERuSXlFR0t2VjRNVWRjcHdKZ2RSU04yUkVMSjBfUFBIUXBZWUpjSDNONUhoV3VtMWJKYUJyU2ttY0J2eHdTalQ1LVJPWE5qNlBKOUY3R3VZamxzbk5mZ3J4c0MzOGtOOXVQbTBmclY4aTE5Q3RtaEdnTVdmR3lNV0ZYZW1NdllVQ21qUlA4WFY4X1RtaDVNaS12RjBCeDM2Ri1fSGd6eWNfUlZBdWZ5dEhYbnZWMFg2SVVVa0M5UWlSU1E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>noticia:9ge0q3</t>
+          <t>noticia:kaqalb</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-25 15:19</t>
+          <t>2026-10-25 15:29</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1792955960000</v>
+        <v>1792956564000</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Tarija: Evalúan daños tras intensa granizada en Chocloca - eju.tv</t>
+          <t>“El bolsillo no alcanza”: la sequía golpea al ganado en Pasorapa y piden tanques de agua - Red Uno</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>climatológica</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -637,58 +637,58 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>eju.tv</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>-21.53</v>
+        <v>-18.38</v>
       </c>
       <c r="N3" t="n">
-        <v>-64.73</v>
+        <v>-64.649</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Tarija, Tarija</t>
+          <t>Pasorapa, Cochabamba</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tarija</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Tarija</t>
+          <t>Pasorapa</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxObHF1cjVaY2tOSndEMDFoRzZCcEgwZHg5VERFa25taUF0UXVyOHB4YkNTSkhaWVVoQXRrU2xyOWlxMkhQblphT0VWeHVyVzBDUHdyUF9WM1U1MnJSSExSbDRQeGgxV05PUzQ5eHdHTURfcVVWRktlZ0lHbUpMeHhUTk9EZzc5UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNRm5FbDhxTlliZHdPdnplYVNrWVdsSFF2ZGp3c2t1MEJCdWJkOE5fLWU5SXhXc25JLU9leVNsdnJZUEFFRmlTOUtJLW5SZ3JpRDFlYmlaYlFLYVJrM3pud0plS2lXVllqdEd0cWRiMUlmRzZkdnRpT2twaGU4cm1TRm9uSEw4WkhjeEJGUVZMNlJmRnFnY0M2UWw3T3NqMXdFcXhETjdrRi1hSjh3UDIxZl9CamxvYXdHRDRkZGR0ZEtZNHREX0c5Ul9Fa3VKMlJh?oc=5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>noticia:1xi48lm</t>
+          <t>noticia:9ge0q3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25 13:02</t>
+          <t>2026-10-25 15:19</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1792947732000</v>
+        <v>1792955960000</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Reportan el incendio de dos camiones cisterna en la carretera a Camiri - EL DÍA - Noticias de Bolivia para el mundo</t>
+          <t>Tarija: Evalúan daños tras intensa granizada en Chocloca - eju.tv</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -711,57 +711,57 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>EL DÍA - Noticias de Bolivia para el mundo; La Patria Bolivia; Opinión Bolivia; Red Uno</t>
+          <t>eju.tv</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>-20.05</v>
+        <v>-21.53</v>
       </c>
       <c r="N4" t="n">
-        <v>-63.486</v>
+        <v>-64.73</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Camiri, Santa Cruz</t>
+          <t>Tarija, Tarija</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Tarija</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Camiri</t>
+          <t>Tarija</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNN0traUpaNVFIOU0zeFZod2tkQWhZZFQ1Q3dxc2xCVy1RNnJIX2xQbTlhT3RVckdNdHV4ZFVLQThvd2UzNDlCa3VmaWprTnU3R05rVkVkdEVCU1hFMlFsLTJ6REIySnl5VFJfdV9pQmVDTzlqUWFUSi1GQ0JvTVJVQ2dpeVBydnpMV0dYOThENTFRUDgxVFloSVg3bnN4dGo2aEVCbDFKaUgydWNISnJVUTNB?oc=5 | https://news.google.com/rss/articles/CBMimAFBVV95cUxQbHdpcUF6dXpjaW1TT1ZmdGJtUUVLMTNMRTVqVkFUdkNsZlRvenVkckFUWmI4NDFmc2ZHd2RVcWRSSE5YRVpOTUlESGw2V3JONXpwS0RISGNZd01SejNuMkY4NzFYYXp4aWo2RE9VMkFYUkVwZ3JRRmM5MWlRSjlBWk16azdkQ3FjdEtkaWc5NERkTzk2SllVOQ?oc=5 | https://news.google.com/rss/articles/CBMitwFBVV95cUxORzdWNjUxSGtVYnpWMlZNR1J3cmhRNngzNG1LS2VHQ19PMmFRTDNLd1RoelhMUG8yYU15STdsUk84cFF6WDF5elhUMGpFVU1NVnpqTGlEbXZsd0lWazNBQUZjV0Z3YkhpdFVqMFI1d1liWHROejBzcUxqYkhIaG00cUFaQ1FfTm5feGV6N1EyUTNZMzFlV3N3RmNZTGIxaDQ3UHFjOTNCMGNESmtCb2RVQm0xd3NRb1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxObHF1cjVaY2tOSndEMDFoRzZCcEgwZHg5VERFa25taUF0UXVyOHB4YkNTSkhaWVVoQXRrU2xyOWlxMkhQblphT0VWeHVyVzBDUHdyUF9WM1U1MnJSSExSbDRQeGgxV05PUzQ5eHdHTURfcVVWRktlZ0lHbUpMeHhUTk9EZzc5UQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>manual:1c1299f3</t>
+          <t>noticia:1xi48lm</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-25 12:44</t>
+          <t>2026-10-25 13:02</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1792946640000</v>
+        <v>1792947732000</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Vuelco de minibus</t>
+          <t>Reportan el incendio de dos camiones cisterna en la carretera a Camiri - EL DÍA - Noticias de Bolivia para el mundo</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -770,18 +770,18 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -789,53 +789,57 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Registro abierto (sin verificar)</t>
+          <t>EL DÍA - Noticias de Bolivia para el mundo; La Patria Bolivia; Opinión Bolivia; Red Uno</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>-15.813</v>
+        <v>-20.05</v>
       </c>
       <c r="N5" t="n">
-        <v>-67.46299999999999</v>
+        <v>-63.486</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Caranavi, La Paz</t>
+          <t>Camiri, Santa Cruz</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Caranavi</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr"/>
+          <t>Camiri</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNN0traUpaNVFIOU0zeFZod2tkQWhZZFQ1Q3dxc2xCVy1RNnJIX2xQbTlhT3RVckdNdHV4ZFVLQThvd2UzNDlCa3VmaWprTnU3R05rVkVkdEVCU1hFMlFsLTJ6REIySnl5VFJfdV9pQmVDTzlqUWFUSi1GQ0JvTVJVQ2dpeVBydnpMV0dYOThENTFRUDgxVFloSVg3bnN4dGo2aEVCbDFKaUgydWNISnJVUTNB?oc=5 | https://news.google.com/rss/articles/CBMimAFBVV95cUxQbHdpcUF6dXpjaW1TT1ZmdGJtUUVLMTNMRTVqVkFUdkNsZlRvenVkckFUWmI4NDFmc2ZHd2RVcWRSSE5YRVpOTUlESGw2V3JONXpwS0RISGNZd01SejNuMkY4NzFYYXp4aWo2RE9VMkFYUkVwZ3JRRmM5MWlRSjlBWk16azdkQ3FjdEtkaWc5NERkTzk2SllVOQ?oc=5 | https://news.google.com/rss/articles/CBMitwFBVV95cUxORzdWNjUxSGtVYnpWMlZNR1J3cmhRNngzNG1LS2VHQ19PMmFRTDNLd1RoelhMUG8yYU15STdsUk84cFF6WDF5elhUMGpFVU1NVnpqTGlEbXZsd0lWazNBQUZjV0Z3YkhpdFVqMFI1d1liWHROejBzcUxqYkhIaG00cUFaQ1FfTm5feGV6N1EyUTNZMzFlV3N3RmNZTGIxaDQ3UHFjOTNCMGNESmtCb2RVQm0xd3NRb1E?oc=5</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>noticia:1sg8pi0</t>
+          <t>manual:1c1299f3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-25 09:59</t>
+          <t>2026-10-25 12:44</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1792936752000</v>
+        <v>1792946640000</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bus de agrupación musical sufre accidente rumbo al trópico de Cochabamba | VIDEO - Red Uno</t>
+          <t>Vuelco de minibus</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -844,18 +848,18 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>verde</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -867,58 +871,54 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Red Uno</t>
+          <t>Registro abierto (sin verificar)</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>-17.39</v>
+        <v>-15.813</v>
       </c>
       <c r="N6" t="n">
-        <v>-66.16</v>
+        <v>-67.46299999999999</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Cochabamba, Cochabamba</t>
+          <t>Caranavi, La Paz</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Cochabamba</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOVDVzVTJNM2JuQ25sMThEaVZNOUNRd3FGT3RhVnFrZXZ2NDQ1YlluTVdhbVNUQnA1MGNESHRSWVUzbC1kRVh3OTR0emtlTG91cmRWeFJ5dk5zb3p2WFRyMEJUV3FNRnY1WHhRUU9WLTlJcmNyNXJZZFdoM0JoZjNpa3hjUXhMM0xrUDJab2VadkM5RWZYQ3lWZTVDdzg1akxJT2lxcDVNNzI0NG1hejdfdkUyTQ?oc=5</t>
-        </is>
-      </c>
+          <t>Caranavi</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>noticia:167wlhz</t>
+          <t>noticia:1sg8pi0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-25 07:53</t>
+          <t>2026-10-25 09:59</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1792929231000</v>
+        <v>1792936752000</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>¡A sacar el paraguas! Santa cruz amanece con lluvia, frío y complicaciones en el tránsito vehicular - Red Uno</t>
+          <t>Bus de agrupación musical sufre accidente rumbo al trópico de Cochabamba | VIDEO - Red Uno</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>meteorológica</t>
+          <t>antropogénica</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -949,62 +949,62 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>-17.781</v>
+        <v>-17.39</v>
       </c>
       <c r="N7" t="n">
-        <v>-63.139</v>
+        <v>-66.16</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Santa Cruz, Santa Cruz</t>
+          <t>Cochabamba, Cochabamba</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Santa Cruz de la Sierra</t>
+          <t>Cochabamba</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOY1ZpYktLR3pUQXotUndVR3puUzVHbW1YTzNyUmJvUHB4Q2JmelRvOEdaRldOUm1xLVJnbGR5VWcxTjNEM3ZUYktCUWtVM0hKSjFuRGdpX0JxN0M5MVZBSG1aVURyVWktdmxwbUtRT19ydU5LdzNTZ2Zpb2ozdHlMUUdTVlAyVk4xODBnV0hyTXdVVndyNzV3VC1KMzFnV3lpcFFXSk9MdDZOTWlWakNwT1FnNDh6QVdjazVYZDVVMkdaLU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOVDVzVTJNM2JuQ25sMThEaVZNOUNRd3FGT3RhVnFrZXZ2NDQ1YlluTVdhbVNUQnA1MGNESHRSWVUzbC1kRVh3OTR0emtlTG91cmRWeFJ5dk5zb3p2WFRyMEJUV3FNRnY1WHhRUU9WLTlJcmNyNXJZZFdoM0JoZjNpa3hjUXhMM0xrUDJab2VadkM5RWZYQ3lWZTVDdzg1akxJT2lxcDVNNzI0NG1hejdfdkUyTQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>noticia:bzr7eh</t>
+          <t>noticia:167wlhz</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-25 07:09</t>
+          <t>2026-10-25 07:53</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1792926572000</v>
+        <v>1792929231000</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Alerta naranja por riesgo de desbordes de ríos - El Diario - Bolivia</t>
+          <t>¡A sacar el paraguas! Santa cruz amanece con lluvia, frío y complicaciones en el tránsito vehicular - Red Uno</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>hidrológica</t>
+          <t>meteorológica</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>naranja</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1019,74 +1019,74 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>El Diario - Bolivia; El Mundo Bolivia; FmBolivia</t>
+          <t>Red Uno</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>-16.169</v>
+        <v>-17.781</v>
       </c>
       <c r="N8" t="n">
-        <v>-68.09</v>
+        <v>-63.139</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>La Paz, La Paz</t>
+          <t>Santa Cruz, Santa Cruz</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>La Paz</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Nuestra Señora de La Paz</t>
+          <t>Santa Cruz de la Sierra</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNNGZKSDVaZkowWUFGSEUyTWR3d3dsc04waFBLLWUtcVpiTDYzbmNtYTN1RkFLbjAwN3dxT0xZc3pqc3REUXduZVltQ2Fud1BZLTh1bTNiTEJueVUwV0dERS1iUXZqMHd0UnFrQ3E2SFAzbm5lQ1I4U29MaHJFbWFvdVRTeFY4Wl9rSmc3RkpaQ2xwX0oz?oc=5 | https://news.google.com/rss/articles/CBMipwFBVV95cUxPZW00RkxJSklTelNrS2hqczJDWHlwcENFX2lnSEUyTEFPaDFRQ2JvMUcyd3NfYjg0UE9ORGxHRzB4ZDh3U0hQQ1JSQlhsaUY4N3ByMUUxei1SaUZnNlp6T3hsLVdiMGhKaXhsV1FNSUNQMHlvQ19qdk56SEF0d2RXVFctS0VPT25kNGZCRDdvZ2dxU0VoUUJKU0ZBd0ZycFNEZFh0T3ZjOA?oc=5 | https://news.google.com/rss/articles/CBMiwAFBVV95cUxPZm85aHphekQ4U3BZZkp1ZkF6ZVdSUHgtZmltS1FxUUgza1AwcndWWDJZOWctT0RiVmVabmg5SG42NnJWMlJMMnBlYTlYaVdSb09sR0dnVDdpT29faTdiaDUtZElJdlQ3eTdjR2VsWjlta1FOS1U2Vm1vV3JwWkpvbEw1ZUR3akgwQTZnQnVENjJtVkQtVUpKVEJTeWNJSE1CaEFKa2VqMmZXbWk3ekR4ZWpmZ1Z3elFQaWNaNFJuMXA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOY1ZpYktLR3pUQXotUndVR3puUzVHbW1YTzNyUmJvUHB4Q2JmelRvOEdaRldOUm1xLVJnbGR5VWcxTjNEM3ZUYktCUWtVM0hKSjFuRGdpX0JxN0M5MVZBSG1aVURyVWktdmxwbUtRT19ydU5LdzNTZ2Zpb2ozdHlMUUdTVlAyVk4xODBnV0hyTXdVVndyNzV3VC1KMzFnV3lpcFFXSk9MdDZOTWlWakNwT1FnNDh6QVdjazVYZDVVMkdaLU0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>noticia:1fo4ig4</t>
+          <t>noticia:bzr7eh</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-25 01:08</t>
+          <t>2026-10-25 07:09</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1792904880000</v>
+        <v>1792926572000</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
+          <t>Alerta naranja por riesgo de desbordes de ríos - El Diario - Bolivia</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>antropogénica</t>
+          <t>hidrológica</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>roja</t>
+          <t>naranja</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1097,41 +1097,57 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>diarioelpueblo.com.pe</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
+          <t>El Diario - Bolivia; El Mundo Bolivia; FmBolivia</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>-16.169</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-68.09</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>La Paz, La Paz</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>La Paz</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Nuestra Señora de La Paz</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQcmFrT3dwcEs0X3U2NWxnOGJwNnI2WHdWTGZYbzEyNnJzUWhkbU9TRWhfSlB5UkMwX2gyMmxYUmVNWmxNOVR6V0twRHpFMTVIYjBKbHQ2TXN2d2w5dkFpcWJCcUJMZldaX01sNWtQV2ZJOGpRVzR3NDVIU0pJc1BNVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNNGZKSDVaZkowWUFGSEUyTWR3d3dsc04waFBLLWUtcVpiTDYzbmNtYTN1RkFLbjAwN3dxT0xZc3pqc3REUXduZVltQ2Fud1BZLTh1bTNiTEJueVUwV0dERS1iUXZqMHd0UnFrQ3E2SFAzbm5lQ1I4U29MaHJFbWFvdVRTeFY4Wl9rSmc3RkpaQ2xwX0oz?oc=5 | https://news.google.com/rss/articles/CBMipwFBVV95cUxPZW00RkxJSklTelNrS2hqczJDWHlwcENFX2lnSEUyTEFPaDFRQ2JvMUcyd3NfYjg0UE9ORGxHRzB4ZDh3U0hQQ1JSQlhsaUY4N3ByMUUxei1SaUZnNlp6T3hsLVdiMGhKaXhsV1FNSUNQMHlvQ19qdk56SEF0d2RXVFctS0VPT25kNGZCRDdvZ2dxU0VoUUJKU0ZBd0ZycFNEZFh0T3ZjOA?oc=5 | https://news.google.com/rss/articles/CBMiwAFBVV95cUxPZm85aHphekQ4U3BZZkp1ZkF6ZVdSUHgtZmltS1FxUUgza1AwcndWWDJZOWctT0RiVmVabmg5SG42NnJWMlJMMnBlYTlYaVdSb09sR0dnVDdpT29faTdiaDUtZElJdlQ3eTdjR2VsWjlta1FOS1U2Vm1vV3JwWkpvbEw1ZUR3akgwQTZnQnVENjJtVkQtVUpKVEJTeWNJSE1CaEFKa2VqMmZXbWk3ekR4ZWpmZ1Z3elFQaWNaNFJuMXA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>noticia:r1uot6</t>
+          <t>noticia:1fo4ig4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-24 20:00</t>
+          <t>2026-10-25 01:08</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1792886439000</v>
+        <v>1792904880000</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>vuelco deja heridos en ruta Oruro – Huanuni - La Patria Bolivia</t>
+          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1140,18 +1156,18 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>roja</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1163,53 +1179,37 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>La Patria Bolivia</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
-        <v>-17.97</v>
-      </c>
-      <c r="N10" t="n">
-        <v>-67.11</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Oruro, Oruro</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Oruro</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Oruro</t>
-        </is>
-      </c>
+          <t>diarioelpueblo.com.pe</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNNDQtMG1KT1lLWW5nem9Jbm5JWDZKNlRWZmFmRlBxWDlDeXlSWnJ5d2NsTlpxa0JIS25oVWVZOC1majZVbWhOVDIxR0dLOFlzY2VpVzVoVk1mQnF3dXVwLUFZVHc1UjlXZzF5T05CY3U0ZldLVkw1VzBTek5zanpjQW1xalltWHNiaXI3dTNR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQcmFrT3dwcEs0X3U2NWxnOGJwNnI2WHdWTGZYbzEyNnJzUWhkbU9TRWhfSlB5UkMwX2gyMmxYUmVNWmxNOVR6V0twRHpFMTVIYjBKbHQ2TXN2d2w5dkFpcWJCcUJMZldaX01sNWtQV2ZJOGpRVzR3NDVIU0pJc1BNVg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>noticia:1ytw450</t>
+          <t>noticia:r1uot6</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-24 18:58</t>
+          <t>2026-10-24 20:00</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1792882686000</v>
+        <v>1792886439000</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
+          <t>vuelco deja heridos en ruta Oruro – Huanuni - La Patria Bolivia</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1218,18 +1218,18 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>roja</t>
+          <t>amarilla</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1241,37 +1241,53 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>diarioelpueblo.com.pe</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
+          <t>La Patria Bolivia</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>-17.97</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-67.11</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Oruro, Oruro</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Oruro</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNZ1U3bEVuaVdjVE1zSU9lOHJZTVRZLVZaemhldGNnT1JBWDJvbzdvM3paVVNhLUlyWHF2akNuSXJOLXdyTGRuejRlV1FuMjVkTjA3NmdRdmgtRWlUeTFBV1dEMzBvejBxaXZJdUZZWkRVTF9VLU5BcjFGZGFEQ09WWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNNDQtMG1KT1lLWW5nem9Jbm5JWDZKNlRWZmFmRlBxWDlDeXlSWnJ5d2NsTlpxa0JIS25oVWVZOC1majZVbWhOVDIxR0dLOFlzY2VpVzVoVk1mQnF3dXVwLUFZVHc1UjlXZzF5T05CY3U0ZldLVkw1VzBTek5zanpjQW1xalltWHNiaXI3dTNR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>noticia:1g006zh</t>
+          <t>noticia:1ytw450</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-24 17:02</t>
+          <t>2026-10-24 18:58</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1792875752000</v>
+        <v>1792882686000</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Accidente en la carretera a Mayaya deja siete heridos del grupo Los Chicos Fieles - El Potosí</t>
+          <t>BOLIVIA: ACCIDENTE 10 FALLECIDOS - diarioelpueblo.com.pe</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1280,18 +1296,18 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>amarilla</t>
+          <t>roja</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1299,57 +1315,41 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>EL DÍA - Noticias de Bolivia para el mundo; El Potosí; La Razón Digital Bolivia; Opinión Bolivia</t>
-        </is>
-      </c>
-      <c r="M12" t="n">
-        <v>-19.58</v>
-      </c>
-      <c r="N12" t="n">
-        <v>-65.75</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Potosí, Potosí</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Potosí</t>
-        </is>
-      </c>
+          <t>diarioelpueblo.com.pe</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPTGQwaVBfdG1JdVRMUTN4LVVvN0ppc3dreDJVVllDR3RmX0xpMzB4b0pvVTNSV1B6T0ZEWTdEZkNsRUdSNzhLaC1CWHN5WktNWk1nRWpTdVZiYjI3TlJlX2xlVTI5MjlRU2hiY1gteml4YWVFbDNPSVRBZmtITlQzbmhaUXVmcThRa2xsQTJIOXZuNzlSdm12MEdyOEZHdw?oc=5 | https://news.google.com/rss/articles/CBMizwFBVV95cUxPeGd3VWpCWXJ0YTJIeDJLcktzWG1jdUh0TjFXb01wSTkxbHNXZU94VWNDMkxnTjlJZVdpbkprMEY2NE80RXYyUWxUQXVnbl9lUXR2b28zTEh6cTJLVEQ4TUNja2kzRlhadVBFZFVwV1U2TlhseXZMZ20zZTZiUFpWRjdCOWNBMHU5XzdMV3JqQjV4TEE3bHRMOXR6Nm55eHZUNnFHSDdVRk8zVkY4RkVsUUtUN0JYdkREWGZncmJ3ZWc2T1BuUm1ZLTlfcHVabFE?oc=5 | https://news.google.com/rss/articles/CBMizAFBVV95cUxNYjNxaHg3YllRRTJYdFd1clAtUlROSGlFNVg5eUVZUGJoOEZ4MWM5QU5WQm1YTDc4NXc3SjhWMUw0TkZfSHlMLUQ1bmpTME1Kb1JaM0ExamFHYTd3VlU4MXRWdTZ1bzh1SGYtbGE1a3dBaG93bjg1OGc0S0JfRE43c3dVMVltN0dQQzNhQUNhM0FjVUNRUDRSamlJYlk2dEJpUTBuY2hBcTFucTVRN0ZtYnc5bzdmTV9LQm1uVUxaZS1tUE9IejhBVDRCdU_SAdIBQVVfeXFMTTF5TDVxVkloYVljQ0RRSjJ3MEtiRlptLVpSQndsdkY2YXRYRENJQXFZRUktVkVWMTBFSU1kR3E2NzNLLXVoRnZ1T0VNd19jMElUVl9ucVVEMWtEemdaakNnX2NFY1JsNmlxaFhTVTZNeTdnQThDWS1pRkliXzFtM3o1aGd2cFR1UFdTM285Z1JaUXFiMTB2cXZCLWU3NEJjMkZwZklUbVZ2eWN4LXVaWDVxcHBnWnRlQlN3UWdxMDk3Ylh1ODlyUXRBaDYtR3JwNVNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNZ1U3bEVuaVdjVE1zSU9lOHJZTVRZLVZaemhldGNnT1JBWDJvbzdvM3paVVNhLUlyWHF2akNuSXJOLXdyTGRuejRlV1FuMjVkTjA3NmdRdmgtRWlUeTFBV1dEMzBvejBxaXZJdUZZWkRVTF9VLU5BcjFGZGFEQ09WWQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>noticia:1ukcn97</t>
+          <t>noticia:1g006zh</t>
         </is>
       </c>
       <c r="B13" t="inline